--- a/data/global/2026-01-week04/titles.xlsx
+++ b/data/global/2026-01-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K222"/>
+  <dimension ref="A1:K208"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,28 +436,28 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רוקפור והקאמרטה הישראלית ירושלים - רוקפור והתזמורת LIVE</v>
+        <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026  11:10-01-21</v>
+        <v>5 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24438&amp;forum=music&amp;viewmode=all</v>
+        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>5 hours ago</v>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>2:59</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>Lana Lubany</v>
       </c>
       <c r="H2" t="str">
-        <v>אלבומים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I2" t="str">
         <v/>
@@ -466,33 +466,33 @@
         <v/>
       </c>
       <c r="K2" t="str">
-        <v>רוקפור והקאמרטה הישראלית ירושלים - רוקפור והתזמורת LIVE</v>
+        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>חנן בן ארי - חנן בן ארי - Live 2022</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>2026  11:48-01-17</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24100&amp;forum=music&amp;viewmode=all</v>
+        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>11 hours ago</v>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>4:21</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="H3" t="str">
-        <v>אלבומים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I3" t="str">
         <v/>
@@ -501,33 +501,33 @@
         <v/>
       </c>
       <c r="K3" t="str">
-        <v>חנן בן ארי - חנן בן ארי - Live 2022</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>עדן בן זקן - רולקס וקסקט</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>2026  08:41-01-14</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24436&amp;forum=music&amp;viewmode=all</v>
+        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E4" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>4:09</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="H4" t="str">
-        <v>אלבומים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I4" t="str">
         <v/>
@@ -536,33 +536,33 @@
         <v/>
       </c>
       <c r="K4" t="str">
-        <v>עדן בן זקן - רולקס וקסקט</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>2026  08:40-01-14</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24439&amp;forum=music&amp;viewmode=all</v>
+        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>2:34</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="H5" t="str">
-        <v>אלבומים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -571,33 +571,33 @@
         <v/>
       </c>
       <c r="K5" t="str">
-        <v>רינת בר - לא נשארו בי דמעות EP 2026</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>אייל גולן - בית מפואר</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B6" t="str">
-        <v>2025  02:18-12-31</v>
+        <v>2 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24395&amp;forum=music&amp;viewmode=all</v>
+        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>3:10</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>Olivia Dean</v>
       </c>
       <c r="H6" t="str">
-        <v>אלבומים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I6" t="str">
         <v/>
@@ -606,33 +606,33 @@
         <v/>
       </c>
       <c r="K6" t="str">
-        <v>אייל גולן - בית מפואר</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B7" t="str">
-        <v>2025  02:16-12-31</v>
+        <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24396&amp;forum=music&amp;viewmode=all</v>
+        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E7" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>3:21</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="H7" t="str">
-        <v>אלבומים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I7" t="str">
         <v/>
@@ -641,33 +641,33 @@
         <v/>
       </c>
       <c r="K7" t="str">
-        <v>הפרויקט של דודי לוי ואבטיפוס - הפטריקים</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>שיר לוי - ילד מוזר</v>
+        <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>2025  02:14-12-31</v>
+        <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24394&amp;forum=music&amp;viewmode=all</v>
+        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E8" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>3:06</v>
       </c>
       <c r="G8" t="str">
-        <v/>
+        <v>The Avett Brothers</v>
       </c>
       <c r="H8" t="str">
-        <v>אלבומים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I8" t="str">
         <v/>
@@ -676,33 +676,33 @@
         <v/>
       </c>
       <c r="K8" t="str">
-        <v>שיר לוי - ילד מוזר</v>
+        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>פיטר רוט - 50</v>
+        <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>2025  02:13-12-31</v>
+        <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24407&amp;forum=music&amp;viewmode=all</v>
+        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E9" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>3:21</v>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>Jordana Bryant</v>
       </c>
       <c r="H9" t="str">
-        <v>אלבומים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I9" t="str">
         <v/>
@@ -711,33 +711,33 @@
         <v/>
       </c>
       <c r="K9" t="str">
-        <v>פיטר רוט - 50</v>
+        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אגם בוחבוט - עשרים ואחת</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B10" t="str">
-        <v>2025  02:11-12-31</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24403&amp;forum=music&amp;viewmode=all</v>
+        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E10" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>7:21</v>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>Katy Perry</v>
       </c>
       <c r="H10" t="str">
-        <v>אלבומים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I10" t="str">
         <v/>
@@ -746,33 +746,33 @@
         <v/>
       </c>
       <c r="K10" t="str">
-        <v>אגם בוחבוט - עשרים ואחת</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>רבקה זוהר - רסיסים של אור</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B11" t="str">
-        <v>2025  02:09-12-31</v>
+        <v>3 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24402&amp;forum=music&amp;viewmode=all</v>
+        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E11" t="str">
-        <v/>
+        <v>3 days ago</v>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>3:17</v>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>Lauren Watkins</v>
       </c>
       <c r="H11" t="str">
-        <v>אלבומים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I11" t="str">
         <v/>
@@ -781,33 +781,33 @@
         <v/>
       </c>
       <c r="K11" t="str">
-        <v>רבקה זוהר - רסיסים של אור</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
+        <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B12" t="str">
-        <v>2025  02:08-12-31</v>
+        <v>4 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24345&amp;forum=music&amp;viewmode=all</v>
+        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E12" t="str">
-        <v/>
+        <v>4 days ago</v>
       </c>
       <c r="F12" t="str">
-        <v/>
+        <v>3:45</v>
       </c>
       <c r="G12" t="str">
-        <v/>
+        <v>Tones And I</v>
       </c>
       <c r="H12" t="str">
-        <v>אלבומים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I12" t="str">
         <v/>
@@ -816,33 +816,33 @@
         <v/>
       </c>
       <c r="K12" t="str">
-        <v>קורין אלאל וחברים! - קורין אלאל הופעות אחרונות</v>
+        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B13" t="str">
-        <v>2025  02:05-12-31</v>
+        <v>4 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24404&amp;forum=music&amp;viewmode=all</v>
+        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E13" t="str">
-        <v/>
+        <v>4 days ago</v>
       </c>
       <c r="F13" t="str">
-        <v/>
+        <v>3:57</v>
       </c>
       <c r="G13" t="str">
-        <v/>
+        <v>Ashleigh Dallas</v>
       </c>
       <c r="H13" t="str">
-        <v>אלבומים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I13" t="str">
         <v/>
@@ -851,33 +851,33 @@
         <v/>
       </c>
       <c r="K13" t="str">
-        <v>אהוד בנאי ובנו הנדלר - פליטי הדאב</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Imagine פסטיגל - שירי התחרות</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>2025  02:04-12-31</v>
+        <v>6 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24418&amp;forum=music&amp;viewmode=all</v>
+        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E14" t="str">
-        <v/>
+        <v>6 days ago</v>
       </c>
       <c r="F14" t="str">
-        <v/>
+        <v>3:03</v>
       </c>
       <c r="G14" t="str">
-        <v/>
+        <v>Charlie Puth</v>
       </c>
       <c r="H14" t="str">
-        <v>אלבומים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I14" t="str">
         <v/>
@@ -886,33 +886,33 @@
         <v/>
       </c>
       <c r="K14" t="str">
-        <v>Imagine פסטיגל - שירי התחרות</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>השמחות - חובות אבודים</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B15" t="str">
-        <v>2025  02:02-12-31</v>
+        <v>6 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24425&amp;forum=music&amp;viewmode=all</v>
+        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E15" t="str">
-        <v/>
+        <v>6 days ago</v>
       </c>
       <c r="F15" t="str">
-        <v/>
+        <v>4:27</v>
       </c>
       <c r="G15" t="str">
-        <v/>
+        <v>Chappell Roan</v>
       </c>
       <c r="H15" t="str">
-        <v>אלבומים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I15" t="str">
         <v/>
@@ -921,30 +921,30 @@
         <v/>
       </c>
       <c r="K15" t="str">
-        <v>השמחות - חובות אבודים</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B16" t="str">
-        <v>10 hours ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
+        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E16" t="str">
-        <v>10 hours ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="F16" t="str">
-        <v>4:21</v>
+        <v>4:34</v>
       </c>
       <c r="G16" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Armik</v>
       </c>
       <c r="H16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -956,30 +956,30 @@
         <v/>
       </c>
       <c r="K16" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
+        <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>1 day ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
+        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E17" t="str">
-        <v>1 day ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="F17" t="str">
-        <v>4:09</v>
+        <v>2:54</v>
       </c>
       <c r="G17" t="str">
-        <v>Dermot Kennedy</v>
+        <v>LØLØ</v>
       </c>
       <c r="H17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -991,30 +991,30 @@
         <v/>
       </c>
       <c r="K17" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
+        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
+        <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B18" t="str">
-        <v>1 day ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
+        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E18" t="str">
-        <v>1 day ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="F18" t="str">
-        <v>2:34</v>
+        <v>3:25</v>
       </c>
       <c r="G18" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="H18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1026,30 +1026,30 @@
         <v/>
       </c>
       <c r="K18" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
+        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
+        <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>2 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
+        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E19" t="str">
-        <v>2 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="F19" t="str">
-        <v>3:10</v>
+        <v>2:01</v>
       </c>
       <c r="G19" t="str">
-        <v>Olivia Dean</v>
+        <v>Alan Walker</v>
       </c>
       <c r="H19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1061,30 +1061,30 @@
         <v/>
       </c>
       <c r="K19" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
+        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
+        <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>2 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
+        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E20" t="str">
-        <v>2 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="F20" t="str">
-        <v>3:21</v>
+        <v>2:25</v>
       </c>
       <c r="G20" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Charli xcx</v>
       </c>
       <c r="H20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1096,30 +1096,30 @@
         <v/>
       </c>
       <c r="K20" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
+        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video)</v>
+        <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B21" t="str">
-        <v>2 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
+        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E21" t="str">
-        <v>2 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="F21" t="str">
-        <v>3:06</v>
+        <v>1:14</v>
       </c>
       <c r="G21" t="str">
-        <v>The Avett Brothers</v>
+        <v>Labrinth</v>
       </c>
       <c r="H21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1131,30 +1131,30 @@
         <v/>
       </c>
       <c r="K21" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
+        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video)</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B22" t="str">
-        <v>2 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
+        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E22" t="str">
-        <v>2 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="F22" t="str">
-        <v>3:21</v>
+        <v>2:59</v>
       </c>
       <c r="G22" t="str">
-        <v>Jordana Bryant</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="H22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1166,30 +1166,30 @@
         <v/>
       </c>
       <c r="K22" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
+        <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B23" t="str">
-        <v>2 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
+        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E23" t="str">
-        <v>2 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="F23" t="str">
-        <v>7:21</v>
+        <v>2:29</v>
       </c>
       <c r="G23" t="str">
-        <v>Katy Perry</v>
+        <v>Girl Tones</v>
       </c>
       <c r="H23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1201,30 +1201,30 @@
         <v/>
       </c>
       <c r="K23" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
+        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B24" t="str">
-        <v>3 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
+        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E24" t="str">
-        <v>3 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="F24" t="str">
-        <v>3:17</v>
+        <v>2:34</v>
       </c>
       <c r="G24" t="str">
-        <v>Lauren Watkins</v>
+        <v>Jagwar Twin</v>
       </c>
       <c r="H24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1236,30 +1236,30 @@
         <v/>
       </c>
       <c r="K24" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Just A Mess (Live acoustic studio session)</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
+        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E25" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="F25" t="str">
-        <v>3:45</v>
+        <v>3:48</v>
       </c>
       <c r="G25" t="str">
-        <v>Tones And I</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="H25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1271,30 +1271,30 @@
         <v/>
       </c>
       <c r="K25" t="str">
-        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
       </c>
       <c r="B26" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
+        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E26" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="F26" t="str">
-        <v>3:57</v>
+        <v>3:32</v>
       </c>
       <c r="G26" t="str">
-        <v>Ashleigh Dallas</v>
+        <v>The Beaches</v>
       </c>
       <c r="H26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1306,30 +1306,30 @@
         <v/>
       </c>
       <c r="K26" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
       </c>
       <c r="B27" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
+        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E27" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="F27" t="str">
-        <v>3:03</v>
+        <v>3:49</v>
       </c>
       <c r="G27" t="str">
-        <v>Charlie Puth</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="H27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1341,18 +1341,18 @@
         <v/>
       </c>
       <c r="K27" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
+        <v>Madison Beer - bad enough (Official Music Video)</v>
       </c>
       <c r="B28" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
+        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-22</v>
@@ -1361,10 +1361,10 @@
         <v>6 days ago</v>
       </c>
       <c r="F28" t="str">
-        <v>4:27</v>
+        <v>4:28</v>
       </c>
       <c r="G28" t="str">
-        <v>Chappell Roan</v>
+        <v>Madison Beer</v>
       </c>
       <c r="H28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1376,18 +1376,18 @@
         <v/>
       </c>
       <c r="K28" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
+        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Ty Myers - Message to You (Official Video)</v>
       </c>
       <c r="B29" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
+        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-22</v>
@@ -1396,10 +1396,10 @@
         <v>6 days ago</v>
       </c>
       <c r="F29" t="str">
-        <v>4:34</v>
+        <v>3:37</v>
       </c>
       <c r="G29" t="str">
-        <v>Armik</v>
+        <v>Ty Myers</v>
       </c>
       <c r="H29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1411,18 +1411,18 @@
         <v/>
       </c>
       <c r="K29" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>LØLØ - 007 (Official Music Video)</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
       </c>
       <c r="B30" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
+        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-22</v>
@@ -1431,10 +1431,10 @@
         <v>6 days ago</v>
       </c>
       <c r="F30" t="str">
-        <v>2:54</v>
+        <v>3:35</v>
       </c>
       <c r="G30" t="str">
-        <v>LØLØ</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="H30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1446,18 +1446,18 @@
         <v/>
       </c>
       <c r="K30" t="str">
-        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer)</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
       </c>
       <c r="B31" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
+        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-22</v>
@@ -1466,10 +1466,10 @@
         <v>6 days ago</v>
       </c>
       <c r="F31" t="str">
-        <v>3:25</v>
+        <v>2:31</v>
       </c>
       <c r="G31" t="str">
-        <v>Tenille Townes</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="H31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1481,30 +1481,30 @@
         <v/>
       </c>
       <c r="K31" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video)</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
       </c>
       <c r="B32" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
+        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E32" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="F32" t="str">
-        <v>2:01</v>
+        <v>3:21</v>
       </c>
       <c r="G32" t="str">
-        <v>Alan Walker</v>
+        <v>Lily Allen</v>
       </c>
       <c r="H32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1516,30 +1516,30 @@
         <v/>
       </c>
       <c r="K32" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio)</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
       </c>
       <c r="B33" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
+        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E33" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="F33" t="str">
-        <v>2:25</v>
+        <v>5:24</v>
       </c>
       <c r="G33" t="str">
-        <v>Charli xcx</v>
+        <v>Nickless</v>
       </c>
       <c r="H33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1551,30 +1551,30 @@
         <v/>
       </c>
       <c r="K33" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer)</v>
+        <v>Peach PRC - Back To You (Official Audio)</v>
       </c>
       <c r="B34" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
+        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E34" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="F34" t="str">
-        <v>1:14</v>
+        <v>3:11</v>
       </c>
       <c r="G34" t="str">
-        <v>Labrinth</v>
+        <v>Peach PRC</v>
       </c>
       <c r="H34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1586,30 +1586,30 @@
         <v/>
       </c>
       <c r="K34" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
+        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
       </c>
       <c r="B35" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
+        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E35" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="F35" t="str">
-        <v>2:59</v>
+        <v>4:11</v>
       </c>
       <c r="G35" t="str">
-        <v>Charlie Puth</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="H35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1621,30 +1621,30 @@
         <v/>
       </c>
       <c r="K35" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Girl Tones - Volcano (Visualizer)</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B36" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
+        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E36" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="F36" t="str">
-        <v>2:29</v>
+        <v>3:31</v>
       </c>
       <c r="G36" t="str">
-        <v>Girl Tones</v>
+        <v>OneRepublic</v>
       </c>
       <c r="H36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1656,30 +1656,30 @@
         <v/>
       </c>
       <c r="K36" t="str">
-        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
       </c>
       <c r="B37" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
+        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E37" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="F37" t="str">
-        <v>2:34</v>
+        <v>4:16</v>
       </c>
       <c r="G37" t="str">
-        <v>Jagwar Twin</v>
+        <v>Ty Myers</v>
       </c>
       <c r="H37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1691,30 +1691,30 @@
         <v/>
       </c>
       <c r="K37" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B38" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
+        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E38" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="F38" t="str">
-        <v>3:48</v>
+        <v>4:42</v>
       </c>
       <c r="G38" t="str">
-        <v>Caroline Jones</v>
+        <v>JavaJazzFest</v>
       </c>
       <c r="H38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1726,30 +1726,30 @@
         <v/>
       </c>
       <c r="K38" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
+        <v>Teo Glacier - Don't Mind (Music Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
+        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E39" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="F39" t="str">
-        <v>3:32</v>
+        <v>2:47</v>
       </c>
       <c r="G39" t="str">
-        <v>The Beaches</v>
+        <v>Teo Glacier</v>
       </c>
       <c r="H39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,30 +1761,30 @@
         <v/>
       </c>
       <c r="K39" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
+        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
+        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E40" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="F40" t="str">
-        <v>3:49</v>
+        <v>3:59</v>
       </c>
       <c r="G40" t="str">
-        <v>Dolly Parton</v>
+        <v>Brigitte Calls Me Baby</v>
       </c>
       <c r="H40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1796,30 +1796,30 @@
         <v/>
       </c>
       <c r="K40" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Madison Beer - bad enough (Official Music Video)</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
       </c>
       <c r="B41" t="str">
-        <v>6 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
+        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E41" t="str">
-        <v>6 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="F41" t="str">
-        <v>4:28</v>
+        <v>4:09</v>
       </c>
       <c r="G41" t="str">
-        <v>Madison Beer</v>
+        <v>Louie TheSinger</v>
       </c>
       <c r="H41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1831,30 +1831,30 @@
         <v/>
       </c>
       <c r="K41" t="str">
-        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Ty Myers - Message to You (Official Video)</v>
+        <v>ella jane - When I Was Beautiful (Live)</v>
       </c>
       <c r="B42" t="str">
-        <v>6 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
+        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E42" t="str">
-        <v>6 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="F42" t="str">
-        <v>3:37</v>
+        <v>3:24</v>
       </c>
       <c r="G42" t="str">
-        <v>Ty Myers</v>
+        <v>ella jane</v>
       </c>
       <c r="H42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1866,30 +1866,30 @@
         <v/>
       </c>
       <c r="K42" t="str">
-        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
+        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
+        <v>Johnny Orlando - Emilia (Official Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>6 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
+        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E43" t="str">
-        <v>6 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="F43" t="str">
-        <v>3:35</v>
+        <v>3:14</v>
       </c>
       <c r="G43" t="str">
-        <v>Megan Moroney</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="H43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1901,30 +1901,30 @@
         <v/>
       </c>
       <c r="K43" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
+        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
+        <v>Kungs, Theophilus London - Galaxy (official video)</v>
       </c>
       <c r="B44" t="str">
-        <v>6 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
+        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E44" t="str">
-        <v>6 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="F44" t="str">
-        <v>2:31</v>
+        <v>3:32</v>
       </c>
       <c r="G44" t="str">
-        <v>Julia Cole Music</v>
+        <v>Kungs</v>
       </c>
       <c r="H44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1936,30 +1936,30 @@
         <v/>
       </c>
       <c r="K44" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
+        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) (Official Music Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>7 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
+        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E45" t="str">
-        <v>7 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="F45" t="str">
-        <v>3:21</v>
+        <v>3:15</v>
       </c>
       <c r="G45" t="str">
-        <v>Lily Allen</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="H45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1971,30 +1971,30 @@
         <v/>
       </c>
       <c r="K45" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) (Official Music Video) - Billy Raffoul</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>7 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
+        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E46" t="str">
-        <v>7 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="F46" t="str">
-        <v>5:24</v>
+        <v>3:03</v>
       </c>
       <c r="G46" t="str">
-        <v>Nickless</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="H46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2006,30 +2006,30 @@
         <v/>
       </c>
       <c r="K46" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Peach PRC - Back To You (Official Audio)</v>
+        <v>Stephen Sanchez - Sweet Love</v>
       </c>
       <c r="B47" t="str">
-        <v>7 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
+        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E47" t="str">
-        <v>7 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="F47" t="str">
-        <v>3:11</v>
+        <v>3:04</v>
       </c>
       <c r="G47" t="str">
-        <v>Peach PRC</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="H47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2041,30 +2041,30 @@
         <v/>
       </c>
       <c r="K47" t="str">
-        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
+        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
+        <v>Bruno Mars - I Just Might [Official Music Video]</v>
       </c>
       <c r="B48" t="str">
-        <v>7 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
+        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E48" t="str">
-        <v>7 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="F48" t="str">
-        <v>4:11</v>
+        <v>3:33</v>
       </c>
       <c r="G48" t="str">
-        <v>Ocean Alley</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="H48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2076,30 +2076,30 @@
         <v/>
       </c>
       <c r="K48" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
+        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
       </c>
       <c r="B49" t="str">
-        <v>7 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
+        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E49" t="str">
-        <v>7 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="F49" t="str">
-        <v>3:31</v>
+        <v>2:53</v>
       </c>
       <c r="G49" t="str">
-        <v>OneRepublic</v>
+        <v>MAX</v>
       </c>
       <c r="H49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2111,30 +2111,30 @@
         <v/>
       </c>
       <c r="K49" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>7 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
+        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E50" t="str">
-        <v>7 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="F50" t="str">
-        <v>4:16</v>
+        <v>4:11</v>
       </c>
       <c r="G50" t="str">
-        <v>Ty Myers</v>
+        <v>Jessie J</v>
       </c>
       <c r="H50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2146,30 +2146,30 @@
         <v/>
       </c>
       <c r="K50" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>8 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
+        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E51" t="str">
-        <v>8 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="F51" t="str">
-        <v>4:42</v>
+        <v>2:45</v>
       </c>
       <c r="G51" t="str">
-        <v>JavaJazzFest</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="H51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2181,30 +2181,30 @@
         <v/>
       </c>
       <c r="K51" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video)</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>9 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
+        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E52" t="str">
-        <v>9 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="F52" t="str">
-        <v>2:47</v>
+        <v>4:00</v>
       </c>
       <c r="G52" t="str">
-        <v>Teo Glacier</v>
+        <v>Brandon Lake and Cody Johnson</v>
       </c>
       <c r="H52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2216,30 +2216,30 @@
         <v/>
       </c>
       <c r="K52" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
       </c>
       <c r="B53" t="str">
-        <v>9 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
+        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E53" t="str">
-        <v>9 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="F53" t="str">
-        <v>3:59</v>
+        <v>3:27</v>
       </c>
       <c r="G53" t="str">
-        <v>Brigitte Calls Me Baby</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="H53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2251,30 +2251,30 @@
         <v/>
       </c>
       <c r="K53" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
       </c>
       <c r="B54" t="str">
-        <v>10 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
+        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E54" t="str">
-        <v>10 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="F54" t="str">
-        <v>4:09</v>
+        <v>3:25</v>
       </c>
       <c r="G54" t="str">
-        <v>Louie TheSinger</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="H54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2286,30 +2286,30 @@
         <v/>
       </c>
       <c r="K54" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ella jane - When I Was Beautiful (Live)</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B55" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
+        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E55" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="F55" t="str">
-        <v>3:24</v>
+        <v>3:34</v>
       </c>
       <c r="G55" t="str">
-        <v>ella jane</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="H55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2321,30 +2321,30 @@
         <v/>
       </c>
       <c r="K55" t="str">
-        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Johnny Orlando - Emilia (Official Video)</v>
+        <v>Train - Mittens (Live on TODAY)</v>
       </c>
       <c r="B56" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
+        <v>https://www.youtube.com/watch?v=R2k_wPsAHKQ</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E56" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="F56" t="str">
-        <v>3:14</v>
+        <v>3:17</v>
       </c>
       <c r="G56" t="str">
-        <v>Johnny Orlando</v>
+        <v>Train</v>
       </c>
       <c r="H56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2356,30 +2356,30 @@
         <v/>
       </c>
       <c r="K56" t="str">
-        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
+        <v>Train - Mittens (Live on TODAY) - Train</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video)</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
+        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E57" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="F57" t="str">
-        <v>3:32</v>
+        <v>2:25</v>
       </c>
       <c r="G57" t="str">
-        <v>Kungs</v>
+        <v>Joseph</v>
       </c>
       <c r="H57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2391,30 +2391,30 @@
         <v/>
       </c>
       <c r="K57" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B58" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
+        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E58" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="F58" t="str">
-        <v>3:15</v>
+        <v>3:26</v>
       </c>
       <c r="G58" t="str">
-        <v>Billy Raffoul</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="H58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2426,30 +2426,30 @@
         <v/>
       </c>
       <c r="K58" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B59" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
+        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E59" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="F59" t="str">
-        <v>3:03</v>
+        <v>4:46</v>
       </c>
       <c r="G59" t="str">
-        <v>NathanEvanss</v>
+        <v>Keith Urban</v>
       </c>
       <c r="H59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2461,30 +2461,30 @@
         <v/>
       </c>
       <c r="K59" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Stephen Sanchez - Sweet Love</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B60" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
+        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E60" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="F60" t="str">
-        <v>3:04</v>
+        <v>3:24</v>
       </c>
       <c r="G60" t="str">
-        <v>Stephen Sanchez</v>
+        <v>Keith Urban</v>
       </c>
       <c r="H60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2496,30 +2496,30 @@
         <v/>
       </c>
       <c r="K60" t="str">
-        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video]</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
       </c>
       <c r="B61" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
+        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E61" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="F61" t="str">
-        <v>3:33</v>
+        <v>2:52</v>
       </c>
       <c r="G61" t="str">
-        <v>Bruno Mars</v>
+        <v>Madonna</v>
       </c>
       <c r="H61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2531,30 +2531,30 @@
         <v/>
       </c>
       <c r="K61" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
       </c>
       <c r="B62" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
+        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E62" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="F62" t="str">
-        <v>2:53</v>
+        <v>2:06</v>
       </c>
       <c r="G62" t="str">
-        <v>MAX</v>
+        <v>Estas Tonne</v>
       </c>
       <c r="H62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2566,30 +2566,30 @@
         <v/>
       </c>
       <c r="K62" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estas Tonne</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
+        <v>Anna Graves - Burn On (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
+        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E63" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="F63" t="str">
-        <v>4:11</v>
+        <v>3:09</v>
       </c>
       <c r="G63" t="str">
-        <v>Jessie J</v>
+        <v>Anna Graves</v>
       </c>
       <c r="H63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2601,30 +2601,30 @@
         <v/>
       </c>
       <c r="K63" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
+        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
+        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E64" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="F64" t="str">
-        <v>2:45</v>
+        <v>5:11</v>
       </c>
       <c r="G64" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="H64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2636,30 +2636,30 @@
         <v/>
       </c>
       <c r="K64" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
       </c>
       <c r="B65" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
+        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E65" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="F65" t="str">
-        <v>4:00</v>
+        <v>3:40</v>
       </c>
       <c r="G65" t="str">
-        <v>Brandon Lake and Cody Johnson</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="H65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2671,30 +2671,30 @@
         <v/>
       </c>
       <c r="K65" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B66" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
+        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E66" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="F66" t="str">
-        <v>3:27</v>
+        <v>3:49</v>
       </c>
       <c r="G66" t="str">
-        <v>The Kid LAROI.</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="H66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2706,18 +2706,18 @@
         <v/>
       </c>
       <c r="K66" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
+        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-22</v>
@@ -2726,10 +2726,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="F67" t="str">
-        <v>3:25</v>
+        <v>3:42</v>
       </c>
       <c r="G67" t="str">
-        <v>Olivia Dean</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="H67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2741,18 +2741,18 @@
         <v/>
       </c>
       <c r="K67" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
+        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-22</v>
@@ -2761,10 +2761,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="F68" t="str">
-        <v>3:34</v>
+        <v>5:11</v>
       </c>
       <c r="G68" t="str">
-        <v>Demi Lovato</v>
+        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
       <c r="H68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2776,18 +2776,18 @@
         <v/>
       </c>
       <c r="K68" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Train - Mittens (Live on TODAY)</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=R2k_wPsAHKQ</v>
+        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-22</v>
@@ -2796,10 +2796,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="F69" t="str">
-        <v>3:17</v>
+        <v>3:57</v>
       </c>
       <c r="G69" t="str">
-        <v>Train</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="H69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2811,18 +2811,18 @@
         <v/>
       </c>
       <c r="K69" t="str">
-        <v>Train - Mittens (Live on TODAY) - Train</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
+        <v>Grace Enger - All My Songs (Official Lyric Video)</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
+        <v>https://www.youtube.com/watch?v=gWyaiGAFVO8</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-22</v>
@@ -2831,10 +2831,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="F70" t="str">
-        <v>2:25</v>
+        <v>3:29</v>
       </c>
       <c r="G70" t="str">
-        <v>Joseph</v>
+        <v>Grace Enger</v>
       </c>
       <c r="H70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2846,18 +2846,18 @@
         <v/>
       </c>
       <c r="K70" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
+        <v>Grace Enger - All My Songs (Official Lyric Video) - Grace Enger</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Alan Walker - Broken Strings (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
+        <v>https://www.youtube.com/watch?v=jwQKcW474Tc</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-22</v>
@@ -2866,10 +2866,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="F71" t="str">
-        <v>3:26</v>
+        <v>3:10</v>
       </c>
       <c r="G71" t="str">
-        <v>Demi Lovato</v>
+        <v>Alan Walker and 2 more</v>
       </c>
       <c r="H71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2881,18 +2881,18 @@
         <v/>
       </c>
       <c r="K71" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>Alan Walker - Broken Strings (Official Music Video) - Alan Walker and 2 more</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>Emilia Tarrant - Break Up With Myself</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
+        <v>https://www.youtube.com/watch?v=3N7iKwqENP0</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-22</v>
@@ -2901,10 +2901,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="F72" t="str">
-        <v>4:46</v>
+        <v>4:04</v>
       </c>
       <c r="G72" t="str">
-        <v>Keith Urban</v>
+        <v>Emilia Tarrant</v>
       </c>
       <c r="H72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2916,30 +2916,30 @@
         <v/>
       </c>
       <c r="K72" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>Emilia Tarrant - Break Up With Myself - Emilia Tarrant</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026)</v>
       </c>
       <c r="B73" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
+        <v>https://www.youtube.com/watch?v=sKG5ZIzCnFQ</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E73" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="F73" t="str">
-        <v>3:24</v>
+        <v>3:09</v>
       </c>
       <c r="G73" t="str">
-        <v>Keith Urban</v>
+        <v>Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
       </c>
       <c r="H73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2951,30 +2951,30 @@
         <v/>
       </c>
       <c r="K73" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026) - Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
+        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer)</v>
       </c>
       <c r="B74" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
+        <v>https://www.youtube.com/watch?v=Koj30I91_8k</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E74" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="F74" t="str">
-        <v>2:52</v>
+        <v>2:27</v>
       </c>
       <c r="G74" t="str">
-        <v>Madonna</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="H74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2986,30 +2986,30 @@
         <v/>
       </c>
       <c r="K74" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
+        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
+        <v>Maggie Lindemann - fate</v>
       </c>
       <c r="B75" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
+        <v>https://www.youtube.com/watch?v=xZdWEmnRK4g</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E75" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="F75" t="str">
-        <v>2:06</v>
+        <v>2:12</v>
       </c>
       <c r="G75" t="str">
-        <v>Estas Tonne</v>
+        <v>Maggie Lindemann</v>
       </c>
       <c r="H75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3021,30 +3021,30 @@
         <v/>
       </c>
       <c r="K75" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estas Tonne</v>
+        <v>Maggie Lindemann - fate - Maggie Lindemann</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Anna Graves - Burn On (Official Music Video)</v>
+        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023)</v>
       </c>
       <c r="B76" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
+        <v>https://www.youtube.com/watch?v=wo9yPPCh75Q</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E76" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="F76" t="str">
-        <v>3:09</v>
+        <v>4:44</v>
       </c>
       <c r="G76" t="str">
-        <v>Anna Graves</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="H76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3056,30 +3056,30 @@
         <v/>
       </c>
       <c r="K76" t="str">
-        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
+        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023) - Cliff Richard</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025</v>
       </c>
       <c r="B77" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
+        <v>https://www.youtube.com/watch?v=ND6maRwmzHk</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E77" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="F77" t="str">
-        <v>5:11</v>
+        <v>1:00:09</v>
       </c>
       <c r="G77" t="str">
-        <v>Ocean Alley</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="H77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,30 +3091,30 @@
         <v/>
       </c>
       <c r="K77" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
+        <v>RAYE - Black Mascara. (Live at The Royal Albert Hall)</v>
       </c>
       <c r="B78" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
+        <v>https://www.youtube.com/watch?v=9jMMOYr-VhE</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E78" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="F78" t="str">
-        <v>3:40</v>
+        <v>4:15</v>
       </c>
       <c r="G78" t="str">
-        <v>Zara Larsson</v>
+        <v>RAYE</v>
       </c>
       <c r="H78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3126,30 +3126,30 @@
         <v/>
       </c>
       <c r="K78" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
+        <v>RAYE - Black Mascara. (Live at The Royal Albert Hall) - RAYE</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
+        <v>Madison Cunningham - My Full Name (Garden Session)</v>
       </c>
       <c r="B79" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
+        <v>https://www.youtube.com/watch?v=o2F-QmqdNtI</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E79" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="F79" t="str">
-        <v>3:49</v>
+        <v>4:07</v>
       </c>
       <c r="G79" t="str">
-        <v>Lauren Watkins</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="H79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3161,30 +3161,30 @@
         <v/>
       </c>
       <c r="K79" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Madison Cunningham - My Full Name (Garden Session) - Madison Cunningham</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions)</v>
       </c>
       <c r="B80" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
+        <v>https://www.youtube.com/watch?v=5-6cEVLqE90</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E80" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="F80" t="str">
-        <v>3:42</v>
+        <v>3:10</v>
       </c>
       <c r="G80" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="H80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3196,30 +3196,30 @@
         <v/>
       </c>
       <c r="K80" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
+        <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions) - Teddy Swims</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower)</v>
       </c>
       <c r="B81" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
+        <v>https://www.youtube.com/watch?v=ivPSbcEMwCs</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E81" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="F81" t="str">
-        <v>5:11</v>
+        <v>3:47</v>
       </c>
       <c r="G81" t="str">
-        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Christina Aguilera</v>
       </c>
       <c r="H81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3231,30 +3231,30 @@
         <v/>
       </c>
       <c r="K81" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower) - Christina Aguilera</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
+        <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025)</v>
       </c>
       <c r="B82" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
+        <v>https://www.youtube.com/watch?v=tYpOHbXFnm0</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E82" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="F82" t="str">
-        <v>3:57</v>
+        <v>3:58</v>
       </c>
       <c r="G82" t="str">
-        <v>Lainey Wilson</v>
+        <v>RAYE</v>
       </c>
       <c r="H82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3266,30 +3266,30 @@
         <v/>
       </c>
       <c r="K82" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
+        <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025) - RAYE</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Grace Enger - All My Songs (Official Lyric Video)</v>
+        <v>Dasha - Here For The Party (Official Audio)</v>
       </c>
       <c r="B83" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=gWyaiGAFVO8</v>
+        <v>https://www.youtube.com/watch?v=rSO9oYUnO2k</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E83" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="F83" t="str">
-        <v>3:29</v>
+        <v>3:30</v>
       </c>
       <c r="G83" t="str">
-        <v>Grace Enger</v>
+        <v>Dasha</v>
       </c>
       <c r="H83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3301,30 +3301,30 @@
         <v/>
       </c>
       <c r="K83" t="str">
-        <v>Grace Enger - All My Songs (Official Lyric Video) - Grace Enger</v>
+        <v>Dasha - Here For The Party (Official Audio) - Dasha</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Alan Walker - Broken Strings (Official Music Video)</v>
+        <v>Lady Gaga in Harlequin Live: One Night Only</v>
       </c>
       <c r="B84" t="str">
-        <v>2 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=jwQKcW474Tc</v>
+        <v>https://www.youtube.com/watch?v=c231tCsQalU</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E84" t="str">
-        <v>2 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="F84" t="str">
-        <v>3:10</v>
+        <v>51:49</v>
       </c>
       <c r="G84" t="str">
-        <v>Alan Walker and 2 more</v>
+        <v>Lady Gaga and YouTube</v>
       </c>
       <c r="H84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3336,30 +3336,30 @@
         <v/>
       </c>
       <c r="K84" t="str">
-        <v>Alan Walker - Broken Strings (Official Music Video) - Alan Walker and 2 more</v>
+        <v>Lady Gaga in Harlequin Live: One Night Only - Lady Gaga and YouTube</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Emilia Tarrant - Break Up With Myself</v>
+        <v>Sabrina Carpenter - Such A Funny Way (Official Lyric Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>2 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=3N7iKwqENP0</v>
+        <v>https://www.youtube.com/watch?v=oaJKUCgSSkc</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E85" t="str">
-        <v>2 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="F85" t="str">
-        <v>4:04</v>
+        <v>3:53</v>
       </c>
       <c r="G85" t="str">
-        <v>Emilia Tarrant</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="H85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3371,30 +3371,30 @@
         <v/>
       </c>
       <c r="K85" t="str">
-        <v>Emilia Tarrant - Break Up With Myself - Emilia Tarrant</v>
+        <v>Sabrina Carpenter - Such A Funny Way (Official Lyric Video) - Sabrina Carpenter</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026)</v>
+        <v>Megan Moroney - Beautiful Things (Official Fan Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>3 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=sKG5ZIzCnFQ</v>
+        <v>https://www.youtube.com/watch?v=0Gxu80LxI0w</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E86" t="str">
-        <v>3 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="F86" t="str">
-        <v>3:09</v>
+        <v>3:56</v>
       </c>
       <c r="G86" t="str">
-        <v>Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="H86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3406,30 +3406,30 @@
         <v/>
       </c>
       <c r="K86" t="str">
-        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026) - Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Megan Moroney - Beautiful Things (Official Fan Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer)</v>
+        <v>Jason Derulo - Miracle</v>
       </c>
       <c r="B87" t="str">
-        <v>3 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=Koj30I91_8k</v>
+        <v>https://www.youtube.com/watch?v=7sjshHJwkOE</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E87" t="str">
-        <v>3 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="F87" t="str">
-        <v>2:27</v>
+        <v>4:16</v>
       </c>
       <c r="G87" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="H87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3441,30 +3441,30 @@
         <v/>
       </c>
       <c r="K87" t="str">
-        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer) - Lauren Spencer Smith</v>
+        <v>Jason Derulo - Miracle - Jason Derulo</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Maggie Lindemann - fate</v>
+        <v>Sananda Maitreya - Pretty Baby (Live)</v>
       </c>
       <c r="B88" t="str">
-        <v>3 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=xZdWEmnRK4g</v>
+        <v>https://www.youtube.com/watch?v=yv1c5G5HZt8</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E88" t="str">
-        <v>3 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="F88" t="str">
-        <v>2:12</v>
+        <v>3:29</v>
       </c>
       <c r="G88" t="str">
-        <v>Maggie Lindemann</v>
+        <v>Sananda Maitreya</v>
       </c>
       <c r="H88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3476,30 +3476,30 @@
         <v/>
       </c>
       <c r="K88" t="str">
-        <v>Maggie Lindemann - fate - Maggie Lindemann</v>
+        <v>Sananda Maitreya - Pretty Baby (Live) - Sananda Maitreya</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023)</v>
+        <v>Faded - 10th Anniversary (Performance Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>3 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=wo9yPPCh75Q</v>
+        <v>https://www.youtube.com/watch?v=EXVg23U3NRw</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E89" t="str">
-        <v>3 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="F89" t="str">
-        <v>4:44</v>
+        <v>3:25</v>
       </c>
       <c r="G89" t="str">
-        <v>Cliff Richard</v>
+        <v>Alan Walker and 2 more</v>
       </c>
       <c r="H89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3511,30 +3511,30 @@
         <v/>
       </c>
       <c r="K89" t="str">
-        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023) - Cliff Richard</v>
+        <v>Faded - 10th Anniversary (Performance Video) - Alan Walker and 2 more</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025</v>
+        <v>What Are You Doing New Year's Eve (Live from the Eiffel Tower - Official Lyric Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>3 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=ND6maRwmzHk</v>
+        <v>https://www.youtube.com/watch?v=Bpb67fSUzEQ</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E90" t="str">
-        <v>3 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="F90" t="str">
-        <v>1:00:09</v>
+        <v>4:06</v>
       </c>
       <c r="G90" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Christina Aguilera</v>
       </c>
       <c r="H90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3546,30 +3546,30 @@
         <v/>
       </c>
       <c r="K90" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025 - Purple Disco Machine</v>
+        <v>What Are You Doing New Year's Eve (Live from the Eiffel Tower - Official Lyric Video) - Christina Aguilera</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>RAYE - Black Mascara. (Live at The Royal Albert Hall)</v>
+        <v>Have Yourself a Merry Little Christmas (Live from the Eiffel Tower - Official Lyric Video)</v>
       </c>
       <c r="B91" t="str">
-        <v>3 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=9jMMOYr-VhE</v>
+        <v>https://www.youtube.com/watch?v=gkwb6kZloLA</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E91" t="str">
-        <v>3 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="F91" t="str">
-        <v>4:15</v>
+        <v>4:03</v>
       </c>
       <c r="G91" t="str">
-        <v>RAYE</v>
+        <v>Christina Aguilera</v>
       </c>
       <c r="H91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3581,30 +3581,30 @@
         <v/>
       </c>
       <c r="K91" t="str">
-        <v>RAYE - Black Mascara. (Live at The Royal Albert Hall) - RAYE</v>
+        <v>Have Yourself a Merry Little Christmas (Live from the Eiffel Tower - Official Lyric Video) - Christina Aguilera</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Madison Cunningham - My Full Name (Garden Session)</v>
+        <v>Chris Rea - Driving Home for Christmas - (Live on National Lottery Stars, 2000)</v>
       </c>
       <c r="B92" t="str">
-        <v>3 weeks ago</v>
+        <v>1 year ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=o2F-QmqdNtI</v>
+        <v>https://www.youtube.com/watch?v=Jckb3dnS5fw</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E92" t="str">
-        <v>3 weeks ago</v>
+        <v>1 year ago</v>
       </c>
       <c r="F92" t="str">
-        <v>4:07</v>
+        <v>4:11</v>
       </c>
       <c r="G92" t="str">
-        <v>Madison Cunningham</v>
+        <v>Chris Rea Official</v>
       </c>
       <c r="H92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3616,30 +3616,30 @@
         <v/>
       </c>
       <c r="K92" t="str">
-        <v>Madison Cunningham - My Full Name (Garden Session) - Madison Cunningham</v>
+        <v>Chris Rea - Driving Home for Christmas - (Live on National Lottery Stars, 2000) - Chris Rea Official</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions)</v>
+        <v>Jessie J - I'll Never Know Why (The Royal Variety Performance 2025)</v>
       </c>
       <c r="B93" t="str">
-        <v>3 weeks ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=5-6cEVLqE90</v>
+        <v>https://www.youtube.com/watch?v=DPA8v4YS8AY</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E93" t="str">
-        <v>3 weeks ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="F93" t="str">
-        <v>3:10</v>
+        <v>4:08</v>
       </c>
       <c r="G93" t="str">
-        <v>Teddy Swims</v>
+        <v>Jessie J</v>
       </c>
       <c r="H93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3651,30 +3651,30 @@
         <v/>
       </c>
       <c r="K93" t="str">
-        <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions) - Teddy Swims</v>
+        <v>Jessie J - I'll Never Know Why (The Royal Variety Performance 2025) - Jessie J</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower)</v>
+        <v>Craig David - Walking Away (Official HD Video)</v>
       </c>
       <c r="B94" t="str">
-        <v>3 weeks ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=ivPSbcEMwCs</v>
+        <v>https://www.youtube.com/watch?v=v8Yu21pEbqw</v>
       </c>
       <c r="D94" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E94" t="str">
-        <v>3 weeks ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="F94" t="str">
-        <v>3:47</v>
+        <v>3:34</v>
       </c>
       <c r="G94" t="str">
-        <v>Christina Aguilera</v>
+        <v>Craig David</v>
       </c>
       <c r="H94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3686,30 +3686,30 @@
         <v/>
       </c>
       <c r="K94" t="str">
-        <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower) - Christina Aguilera</v>
+        <v>Craig David - Walking Away (Official HD Video) - Craig David</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025)</v>
+        <v>Christina Aguilera, Yseult - Ave Maria (Live from the Eiffel Tower - Official Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>3 weeks ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=tYpOHbXFnm0</v>
+        <v>https://www.youtube.com/watch?v=sq2u9Cfn2B8</v>
       </c>
       <c r="D95" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E95" t="str">
-        <v>3 weeks ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="F95" t="str">
-        <v>3:58</v>
+        <v>4:37</v>
       </c>
       <c r="G95" t="str">
-        <v>RAYE</v>
+        <v>Christina Aguilera</v>
       </c>
       <c r="H95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3721,30 +3721,30 @@
         <v/>
       </c>
       <c r="K95" t="str">
-        <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025) - RAYE</v>
+        <v>Christina Aguilera, Yseult - Ave Maria (Live from the Eiffel Tower - Official Video) - Christina Aguilera</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Dasha - Here For The Party (Official Audio)</v>
+        <v>Shawn Mendes &amp; Niall Horan - This Town (Live from London)</v>
       </c>
       <c r="B96" t="str">
-        <v>3 weeks ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=rSO9oYUnO2k</v>
+        <v>https://www.youtube.com/watch?v=Ea2DSMNIK5w</v>
       </c>
       <c r="D96" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E96" t="str">
-        <v>3 weeks ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="F96" t="str">
-        <v>3:30</v>
+        <v>6:27</v>
       </c>
       <c r="G96" t="str">
-        <v>Dasha</v>
+        <v>Shawn Mendes and Niall Horan</v>
       </c>
       <c r="H96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3756,30 +3756,30 @@
         <v/>
       </c>
       <c r="K96" t="str">
-        <v>Dasha - Here For The Party (Official Audio) - Dasha</v>
+        <v>Shawn Mendes &amp; Niall Horan - This Town (Live from London) - Shawn Mendes and Niall Horan</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Lady Gaga in Harlequin Live: One Night Only</v>
+        <v>Shakira - Zoo (From "Zootopia 2")</v>
       </c>
       <c r="B97" t="str">
-        <v>4 weeks ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=c231tCsQalU</v>
+        <v>https://www.youtube.com/watch?v=kCIf6yaJisQ</v>
       </c>
       <c r="D97" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E97" t="str">
-        <v>4 weeks ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="F97" t="str">
-        <v>51:49</v>
+        <v>2:07</v>
       </c>
       <c r="G97" t="str">
-        <v>Lady Gaga and YouTube</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="H97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3791,30 +3791,30 @@
         <v/>
       </c>
       <c r="K97" t="str">
-        <v>Lady Gaga in Harlequin Live: One Night Only - Lady Gaga and YouTube</v>
+        <v>Shakira - Zoo (From "Zootopia 2") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Sabrina Carpenter - Such A Funny Way (Official Lyric Video)</v>
+        <v>Within Temptation - Ice Queen (Acoustic) | 2025 Reimagined Edition</v>
       </c>
       <c r="B98" t="str">
-        <v>4 weeks ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=oaJKUCgSSkc</v>
+        <v>https://www.youtube.com/watch?v=f1Iqm16vWDQ</v>
       </c>
       <c r="D98" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E98" t="str">
-        <v>4 weeks ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="F98" t="str">
-        <v>3:53</v>
+        <v>3:40</v>
       </c>
       <c r="G98" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>Within Temptation</v>
       </c>
       <c r="H98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3826,30 +3826,30 @@
         <v/>
       </c>
       <c r="K98" t="str">
-        <v>Sabrina Carpenter - Such A Funny Way (Official Lyric Video) - Sabrina Carpenter</v>
+        <v>Within Temptation - Ice Queen (Acoustic) | 2025 Reimagined Edition - Within Temptation</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Megan Moroney - Beautiful Things (Official Fan Video)</v>
+        <v>OneRepublic - Give Me Something (for Arknights Endfield) (Official Audio)</v>
       </c>
       <c r="B99" t="str">
-        <v>4 weeks ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=0Gxu80LxI0w</v>
+        <v>https://www.youtube.com/watch?v=4eqzUNO-ONs</v>
       </c>
       <c r="D99" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E99" t="str">
-        <v>4 weeks ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="F99" t="str">
-        <v>3:56</v>
+        <v>2:43</v>
       </c>
       <c r="G99" t="str">
-        <v>Megan Moroney</v>
+        <v>OneRepublic</v>
       </c>
       <c r="H99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3861,30 +3861,30 @@
         <v/>
       </c>
       <c r="K99" t="str">
-        <v>Megan Moroney - Beautiful Things (Official Fan Video) - Megan Moroney</v>
+        <v>OneRepublic - Give Me Something (for Arknights Endfield) (Official Audio) - OneRepublic</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Jason Derulo - Miracle</v>
+        <v>Passenger | The Road Is Long</v>
       </c>
       <c r="B100" t="str">
-        <v>4 weeks ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=7sjshHJwkOE</v>
+        <v>https://www.youtube.com/watch?v=oi4aTOc-IX4</v>
       </c>
       <c r="D100" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E100" t="str">
-        <v>4 weeks ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="F100" t="str">
-        <v>4:16</v>
+        <v>4:01</v>
       </c>
       <c r="G100" t="str">
-        <v>Jason Derulo</v>
+        <v>Passenger</v>
       </c>
       <c r="H100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3896,30 +3896,30 @@
         <v/>
       </c>
       <c r="K100" t="str">
-        <v>Jason Derulo - Miracle - Jason Derulo</v>
+        <v>Passenger | The Road Is Long - Passenger</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Sananda Maitreya - Pretty Baby (Live)</v>
+        <v>Black Honey - Carroll Avenue (Live at RAK)</v>
       </c>
       <c r="B101" t="str">
-        <v>4 weeks ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=yv1c5G5HZt8</v>
+        <v>https://www.youtube.com/watch?v=LPXTE3a6QrM</v>
       </c>
       <c r="D101" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E101" t="str">
-        <v>4 weeks ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="F101" t="str">
-        <v>3:29</v>
+        <v>3:19</v>
       </c>
       <c r="G101" t="str">
-        <v>Sananda Maitreya</v>
+        <v>Black Honey</v>
       </c>
       <c r="H101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3931,4247 +3931,3757 @@
         <v/>
       </c>
       <c r="K101" t="str">
-        <v>Sananda Maitreya - Pretty Baby (Live) - Sananda Maitreya</v>
+        <v>Black Honey - Carroll Avenue (Live at RAK) - Black Honey</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Faded - 10th Anniversary (Performance Video)</v>
+        <v>Opening Night</v>
       </c>
       <c r="B102" t="str">
-        <v>4 weeks ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=EXVg23U3NRw</v>
+        <v>https://music.apple.com/us/song/opening-night/1870313501</v>
       </c>
       <c r="D102" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E102" t="str">
-        <v>4 weeks ago</v>
+        <v>HELP(2)</v>
       </c>
       <c r="F102" t="str">
-        <v>3:25</v>
+        <v>4:19</v>
       </c>
       <c r="G102" t="str">
-        <v>Alan Walker and 2 more</v>
+        <v>Arctic Monkeys</v>
       </c>
       <c r="H102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/arctic-monkeys/62820413</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/opening-night/1870313498</v>
       </c>
       <c r="K102" t="str">
-        <v>Faded - 10th Anniversary (Performance Video) - Alan Walker and 2 more</v>
+        <v>Opening Night - Arctic Monkeys</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>What Are You Doing New Year's Eve (Live from the Eiffel Tower - Official Lyric Video)</v>
+        <v>Wish I Didn't</v>
       </c>
       <c r="B103" t="str">
-        <v>4 weeks ago</v>
+        <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=Bpb67fSUzEQ</v>
+        <v>https://music.apple.com/us/song/wish-i-didnt/1851297073</v>
       </c>
       <c r="D103" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E103" t="str">
-        <v>4 weeks ago</v>
+        <v>Cloud 9</v>
       </c>
       <c r="F103" t="str">
-        <v>4:06</v>
+        <v>3:29</v>
       </c>
       <c r="G103" t="str">
-        <v>Christina Aguilera</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="H103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
       </c>
       <c r="J103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/wish-i-didnt/1851296746</v>
       </c>
       <c r="K103" t="str">
-        <v>What Are You Doing New Year's Eve (Live from the Eiffel Tower - Official Lyric Video) - Christina Aguilera</v>
+        <v>Wish I Didn't - Megan Moroney</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Have Yourself a Merry Little Christmas (Live from the Eiffel Tower - Official Lyric Video)</v>
+        <v>AIR FORCE (BLACK DEMARCO)</v>
       </c>
       <c r="B104" t="str">
-        <v>4 weeks ago</v>
+        <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://www.youtube.com/watch?v=gkwb6kZloLA</v>
+        <v>https://music.apple.com/us/song/air-force-black-demarco/1862935169</v>
       </c>
       <c r="D104" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E104" t="str">
-        <v>4 weeks ago</v>
+        <v>Don't Be Dumb</v>
       </c>
       <c r="F104" t="str">
-        <v>4:03</v>
+        <v>3:44</v>
       </c>
       <c r="G104" t="str">
-        <v>Christina Aguilera</v>
+        <v>A$AP Rocky</v>
       </c>
       <c r="H104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/a%24ap-rocky/481488005</v>
       </c>
       <c r="J104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/air-force-black-demarco/1862934946</v>
       </c>
       <c r="K104" t="str">
-        <v>Have Yourself a Merry Little Christmas (Live from the Eiffel Tower - Official Lyric Video) - Christina Aguilera</v>
+        <v>AIR FORCE (BLACK DEMARCO) - A$AP Rocky</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Chris Rea - Driving Home for Christmas - (Live on National Lottery Stars, 2000)</v>
+        <v>Wall of Sound</v>
       </c>
       <c r="B105" t="str">
-        <v>1 year ago</v>
+        <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://www.youtube.com/watch?v=Jckb3dnS5fw</v>
+        <v>https://music.apple.com/us/song/wall-of-sound/1852566426</v>
       </c>
       <c r="D105" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E105" t="str">
-        <v>1 year ago</v>
+        <v>Wuthering Heights</v>
       </c>
       <c r="F105" t="str">
-        <v>4:11</v>
+        <v>2:24</v>
       </c>
       <c r="G105" t="str">
-        <v>Chris Rea Official</v>
+        <v>Charli xcx</v>
       </c>
       <c r="H105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
       </c>
       <c r="J105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/wall-of-sound/1852566184</v>
       </c>
       <c r="K105" t="str">
-        <v>Chris Rea - Driving Home for Christmas - (Live on National Lottery Stars, 2000) - Chris Rea Official</v>
+        <v>Wall of Sound - Charli xcx</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Jessie J - I'll Never Know Why (The Royal Variety Performance 2025)</v>
+        <v>Where's My Phone?</v>
       </c>
       <c r="B106" t="str">
-        <v>1 month ago</v>
+        <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://www.youtube.com/watch?v=DPA8v4YS8AY</v>
+        <v>https://music.apple.com/us/song/wheres-my-phone/1860622553</v>
       </c>
       <c r="D106" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E106" t="str">
-        <v>1 month ago</v>
+        <v>Nothing's About to Happen to Me</v>
       </c>
       <c r="F106" t="str">
-        <v>4:08</v>
+        <v>3:09</v>
       </c>
       <c r="G106" t="str">
-        <v>Jessie J</v>
+        <v>Mitski</v>
       </c>
       <c r="H106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/mitski/497546276</v>
       </c>
       <c r="J106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/wheres-my-phone/1860622550</v>
       </c>
       <c r="K106" t="str">
-        <v>Jessie J - I'll Never Know Why (The Royal Variety Performance 2025) - Jessie J</v>
+        <v>Where's My Phone? - Mitski</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Craig David - Walking Away (Official HD Video)</v>
+        <v>100</v>
       </c>
       <c r="B107" t="str">
-        <v>1 month ago</v>
+        <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://www.youtube.com/watch?v=v8Yu21pEbqw</v>
+        <v>https://music.apple.com/us/song/100/1858754874</v>
       </c>
       <c r="D107" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E107" t="str">
-        <v>1 month ago</v>
+        <v>Do You Still Love Me?</v>
       </c>
       <c r="F107" t="str">
-        <v>3:34</v>
+        <v>3:54</v>
       </c>
       <c r="G107" t="str">
-        <v>Craig David</v>
+        <v>Ella Mai</v>
       </c>
       <c r="H107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/ella-mai/1160482144</v>
       </c>
       <c r="J107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/100/1858754868</v>
       </c>
       <c r="K107" t="str">
-        <v>Craig David - Walking Away (Official HD Video) - Craig David</v>
+        <v>100 - Ella Mai</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Christina Aguilera, Yseult - Ave Maria (Live from the Eiffel Tower - Official Video)</v>
+        <v>Por un P*****o no se llora (Salud mi Reina)</v>
       </c>
       <c r="B108" t="str">
-        <v>1 month ago</v>
+        <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://www.youtube.com/watch?v=sq2u9Cfn2B8</v>
+        <v>https://music.apple.com/us/song/por-un-p-o-no-se-llora-salud-mi-reina/1862587826</v>
       </c>
       <c r="D108" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E108" t="str">
-        <v>1 month ago</v>
+        <v>Por un P*****o no se llora (Salud mi Reina) - Single</v>
       </c>
       <c r="F108" t="str">
-        <v>4:37</v>
+        <v>2:31</v>
       </c>
       <c r="G108" t="str">
-        <v>Christina Aguilera</v>
+        <v>Manuel Turizo</v>
       </c>
       <c r="H108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/manuel-turizo/1186116587</v>
       </c>
       <c r="J108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/por-un-p-o-no-se-llora-salud-mi-reina/1862587821</v>
       </c>
       <c r="K108" t="str">
-        <v>Christina Aguilera, Yseult - Ave Maria (Live from the Eiffel Tower - Official Video) - Christina Aguilera</v>
+        <v>Por un P*****o no se llora (Salud mi Reina) - Manuel Turizo</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Shawn Mendes &amp; Niall Horan - This Town (Live from London)</v>
+        <v>Flo Jackson</v>
       </c>
       <c r="B109" t="str">
-        <v>1 month ago</v>
+        <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://www.youtube.com/watch?v=Ea2DSMNIK5w</v>
+        <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
       </c>
       <c r="D109" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E109" t="str">
-        <v>1 month ago</v>
+        <v>Flo Jackson - Single</v>
       </c>
       <c r="F109" t="str">
-        <v>6:27</v>
+        <v>2:23</v>
       </c>
       <c r="G109" t="str">
-        <v>Shawn Mendes and Niall Horan</v>
+        <v>Flo Milli</v>
       </c>
       <c r="H109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
       </c>
       <c r="J109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
       </c>
       <c r="K109" t="str">
-        <v>Shawn Mendes &amp; Niall Horan - This Town (Live from London) - Shawn Mendes and Niall Horan</v>
+        <v>Flo Jackson - Flo Milli</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Shakira - Zoo (From "Zootopia 2")</v>
+        <v>L.U.C.K.Y</v>
       </c>
       <c r="B110" t="str">
-        <v>1 month ago</v>
+        <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://www.youtube.com/watch?v=kCIf6yaJisQ</v>
+        <v>https://music.apple.com/us/song/l-u-c-k-y/1861895147</v>
       </c>
       <c r="D110" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E110" t="str">
-        <v>1 month ago</v>
+        <v>Ö</v>
       </c>
       <c r="F110" t="str">
-        <v>2:07</v>
+        <v>2:18</v>
       </c>
       <c r="G110" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>Fcukers</v>
       </c>
       <c r="H110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I110" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="J110" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/l-u-c-k-y/1861895134</v>
       </c>
       <c r="K110" t="str">
-        <v>Shakira - Zoo (From "Zootopia 2") - DisneyMusicVEVO</v>
+        <v>L.U.C.K.Y - Fcukers</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Within Temptation - Ice Queen (Acoustic) | 2025 Reimagined Edition</v>
+        <v>Reclusive</v>
       </c>
       <c r="B111" t="str">
-        <v>1 month ago</v>
+        <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://www.youtube.com/watch?v=f1Iqm16vWDQ</v>
+        <v>https://music.apple.com/us/song/reclusive/1860405760</v>
       </c>
       <c r="D111" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E111" t="str">
-        <v>1 month ago</v>
+        <v>sounds for someone</v>
       </c>
       <c r="F111" t="str">
-        <v>3:40</v>
+        <v>3:06</v>
       </c>
       <c r="G111" t="str">
-        <v>Within Temptation</v>
+        <v>Elmiene</v>
       </c>
       <c r="H111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I111" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/elmiene/1599562425</v>
       </c>
       <c r="J111" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/reclusive/1860405416</v>
       </c>
       <c r="K111" t="str">
-        <v>Within Temptation - Ice Queen (Acoustic) | 2025 Reimagined Edition - Within Temptation</v>
+        <v>Reclusive - Elmiene</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>OneRepublic - Give Me Something (for Arknights Endfield) (Official Audio)</v>
+        <v>Site Unseen (feat. Waxahatchee)</v>
       </c>
       <c r="B112" t="str">
-        <v>1 month ago</v>
+        <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://www.youtube.com/watch?v=4eqzUNO-ONs</v>
+        <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
       </c>
       <c r="D112" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E112" t="str">
-        <v>1 month ago</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="F112" t="str">
-        <v>2:43</v>
+        <v>2:46</v>
       </c>
       <c r="G112" t="str">
-        <v>OneRepublic</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="H112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I112" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="J112" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
       </c>
       <c r="K112" t="str">
-        <v>OneRepublic - Give Me Something (for Arknights Endfield) (Official Audio) - OneRepublic</v>
+        <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Passenger | The Road Is Long</v>
+        <v>Puppet Parade</v>
       </c>
       <c r="B113" t="str">
-        <v>1 month ago</v>
+        <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://www.youtube.com/watch?v=oi4aTOc-IX4</v>
+        <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
       </c>
       <c r="D113" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E113" t="str">
-        <v>1 month ago</v>
+        <v>Megadeth</v>
       </c>
       <c r="F113" t="str">
-        <v>4:01</v>
+        <v>4:40</v>
       </c>
       <c r="G113" t="str">
-        <v>Passenger</v>
+        <v>Megadeth</v>
       </c>
       <c r="H113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I113" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/megadeth/488289</v>
       </c>
       <c r="J113" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
       </c>
       <c r="K113" t="str">
-        <v>Passenger | The Road Is Long - Passenger</v>
+        <v>Puppet Parade - Megadeth</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Black Honey - Carroll Avenue (Live at RAK)</v>
+        <v>Raft In The Sea</v>
       </c>
       <c r="B114" t="str">
-        <v>1 month ago</v>
+        <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://www.youtube.com/watch?v=LPXTE3a6QrM</v>
+        <v>https://music.apple.com/us/song/raft-in-the-sea/1847662987</v>
       </c>
       <c r="D114" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E114" t="str">
-        <v>1 month ago</v>
+        <v>Cerulean</v>
       </c>
       <c r="F114" t="str">
-        <v>3:19</v>
+        <v>3:35</v>
       </c>
       <c r="G114" t="str">
-        <v>Black Honey</v>
+        <v>Danny L Harle</v>
       </c>
       <c r="H114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I114" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/danny-l-harle/985576556</v>
       </c>
       <c r="J114" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/raft-in-the-sea/1847662970</v>
       </c>
       <c r="K114" t="str">
-        <v>Black Honey - Carroll Avenue (Live at RAK) - Black Honey</v>
+        <v>Raft In The Sea - Danny L Harle</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Bastille - SAVE MY SOUL (Piano Version)</v>
+        <v>Good Night Baby</v>
       </c>
       <c r="B115" t="str">
-        <v>1 month ago</v>
+        <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://www.youtube.com/watch?v=paLJCQy5j-I</v>
+        <v>https://music.apple.com/us/song/good-night-baby/1849917462</v>
       </c>
       <c r="D115" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E115" t="str">
-        <v>1 month ago</v>
+        <v>Butterfly</v>
       </c>
       <c r="F115" t="str">
-        <v>2:41</v>
+        <v>4:21</v>
       </c>
       <c r="G115" t="str">
-        <v>BASTILLEvideos</v>
+        <v>Daphni</v>
       </c>
       <c r="H115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I115" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/daphni/1282779393</v>
       </c>
       <c r="J115" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/good-night-baby/1849916838</v>
       </c>
       <c r="K115" t="str">
-        <v>Bastille - SAVE MY SOUL (Piano Version) - BASTILLEvideos</v>
+        <v>Good Night Baby - Daphni</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Opening Night</v>
+        <v>CAMBIARÉ</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/opening-night/1870313501</v>
+        <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
       </c>
       <c r="D116" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E116" t="str">
-        <v>HELP(2)</v>
+        <v>CAMBIARÉ - Single</v>
       </c>
       <c r="F116" t="str">
-        <v>4:19</v>
+        <v>3:01</v>
       </c>
       <c r="G116" t="str">
-        <v>Arctic Monkeys</v>
+        <v>Luis Fonsi</v>
       </c>
       <c r="H116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I116" t="str">
-        <v>https://music.apple.com/us/artist/arctic-monkeys/62820413</v>
+        <v>https://music.apple.com/us/artist/luis-fonsi/102834</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/album/opening-night/1870313498</v>
+        <v>https://music.apple.com/us/album/cambiar%C3%A9/1867545265</v>
       </c>
       <c r="K116" t="str">
-        <v>Opening Night - Arctic Monkeys</v>
+        <v>CAMBIARÉ - Luis Fonsi</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Wish I Didn't</v>
+        <v>Orange County (feat. Bizarrap, Kara Jackson &amp; Anoushka Shankar)</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/wish-i-didnt/1851297073</v>
+        <v>https://music.apple.com/us/song/orange-county-feat-bizarrap-kara-jackson-anoushka-shankar/1837237867</v>
       </c>
       <c r="D117" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E117" t="str">
-        <v>Cloud 9</v>
+        <v>The Mountain</v>
       </c>
       <c r="F117" t="str">
-        <v>3:29</v>
+        <v>3:28</v>
       </c>
       <c r="G117" t="str">
-        <v>Megan Moroney</v>
+        <v>Gorillaz</v>
       </c>
       <c r="H117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I117" t="str">
-        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
+        <v>https://music.apple.com/us/artist/gorillaz/567072</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/album/wish-i-didnt/1851296746</v>
+        <v>https://music.apple.com/us/album/orange-county-feat-bizarrap-kara-jackson-anoushka-shankar/1837237742</v>
       </c>
       <c r="K117" t="str">
-        <v>Wish I Didn't - Megan Moroney</v>
+        <v>Orange County (feat. Bizarrap, Kara Jackson &amp; Anoushka Shankar) - Gorillaz</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>AIR FORCE (BLACK DEMARCO)</v>
+        <v>Lluvia</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/air-force-black-demarco/1862935169</v>
+        <v>https://music.apple.com/us/song/lluvia/1868476403</v>
       </c>
       <c r="D118" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E118" t="str">
-        <v>Don't Be Dumb</v>
+        <v>LA 8VA MARAVILLA</v>
       </c>
       <c r="F118" t="str">
-        <v>3:44</v>
+        <v>3:24</v>
       </c>
       <c r="G118" t="str">
-        <v>A$AP Rocky</v>
+        <v>Arcángel</v>
       </c>
       <c r="H118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I118" t="str">
-        <v>https://music.apple.com/us/artist/a%24ap-rocky/481488005</v>
+        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/album/air-force-black-demarco/1862934946</v>
+        <v>https://music.apple.com/us/album/lluvia/1868476390</v>
       </c>
       <c r="K118" t="str">
-        <v>AIR FORCE (BLACK DEMARCO) - A$AP Rocky</v>
+        <v>Lluvia - Arcángel</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Wall of Sound</v>
+        <v>Knife</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/wall-of-sound/1852566426</v>
+        <v>https://music.apple.com/us/song/knife/1862720450</v>
       </c>
       <c r="D119" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E119" t="str">
-        <v>Wuthering Heights</v>
+        <v>THE SIN : VANISH</v>
       </c>
       <c r="F119" t="str">
-        <v>2:24</v>
+        <v>2:19</v>
       </c>
       <c r="G119" t="str">
-        <v>Charli xcx</v>
+        <v>ENHYPEN</v>
       </c>
       <c r="H119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I119" t="str">
-        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
+        <v>https://music.apple.com/us/artist/enhypen/1541011620</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/album/wall-of-sound/1852566184</v>
+        <v>https://music.apple.com/us/album/knife/1862720020</v>
       </c>
       <c r="K119" t="str">
-        <v>Wall of Sound - Charli xcx</v>
+        <v>Knife - ENHYPEN</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Where's My Phone?</v>
+        <v>bad enough</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/wheres-my-phone/1860622553</v>
+        <v>https://music.apple.com/us/song/bad-enough/1846949125</v>
       </c>
       <c r="D120" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E120" t="str">
-        <v>Nothing's About to Happen to Me</v>
+        <v>locket</v>
       </c>
       <c r="F120" t="str">
-        <v>3:09</v>
+        <v>3:42</v>
       </c>
       <c r="G120" t="str">
-        <v>Mitski</v>
+        <v>Madison Beer</v>
       </c>
       <c r="H120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I120" t="str">
-        <v>https://music.apple.com/us/artist/mitski/497546276</v>
+        <v>https://music.apple.com/us/artist/madison-beer/696146587</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/album/wheres-my-phone/1860622550</v>
+        <v>https://music.apple.com/us/album/bad-enough/1846949115</v>
       </c>
       <c r="K120" t="str">
-        <v>Where's My Phone? - Mitski</v>
+        <v>bad enough - Madison Beer</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>100</v>
+        <v>bad</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/100/1858754874</v>
+        <v>https://music.apple.com/us/song/bad/1851566880</v>
       </c>
       <c r="D121" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E121" t="str">
-        <v>Do You Still Love Me?</v>
+        <v>bad - Single</v>
       </c>
       <c r="F121" t="str">
-        <v>3:54</v>
+        <v>2:41</v>
       </c>
       <c r="G121" t="str">
-        <v>Ella Mai</v>
+        <v>Saint Harison</v>
       </c>
       <c r="H121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I121" t="str">
-        <v>https://music.apple.com/us/artist/ella-mai/1160482144</v>
+        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/album/100/1858754868</v>
+        <v>https://music.apple.com/us/album/bad/1851566879</v>
       </c>
       <c r="K121" t="str">
-        <v>100 - Ella Mai</v>
+        <v>bad - Saint Harison</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Por un P*****o no se llora (Salud mi Reina)</v>
+        <v>Beat Yourself Up</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/por-un-p-o-no-se-llora-salud-mi-reina/1862587826</v>
+        <v>https://music.apple.com/us/song/beat-yourself-up/1845189973</v>
       </c>
       <c r="D122" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E122" t="str">
-        <v>Por un P*****o no se llora (Salud mi Reina) - Single</v>
+        <v>Whatever's Clever!</v>
       </c>
       <c r="F122" t="str">
-        <v>2:31</v>
+        <v>2:58</v>
       </c>
       <c r="G122" t="str">
-        <v>Manuel Turizo</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="H122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I122" t="str">
-        <v>https://music.apple.com/us/artist/manuel-turizo/1186116587</v>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/album/por-un-p-o-no-se-llora-salud-mi-reina/1862587821</v>
+        <v>https://music.apple.com/us/album/beat-yourself-up/1845189970</v>
       </c>
       <c r="K122" t="str">
-        <v>Por un P*****o no se llora (Salud mi Reina) - Manuel Turizo</v>
+        <v>Beat Yourself Up - Charlie Puth</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Flo Jackson</v>
+        <v>Roommates</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
+        <v>https://music.apple.com/us/song/roommates/1854567105</v>
       </c>
       <c r="D123" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E123" t="str">
-        <v>Flo Jackson - Single</v>
+        <v>luck... or something</v>
       </c>
       <c r="F123" t="str">
-        <v>2:23</v>
+        <v>2:52</v>
       </c>
       <c r="G123" t="str">
-        <v>Flo Milli</v>
+        <v>Hilary Duff</v>
       </c>
       <c r="H123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I123" t="str">
-        <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
+        <v>https://music.apple.com/us/artist/hilary-duff/3296003</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
+        <v>https://music.apple.com/us/album/roommates/1854567102</v>
       </c>
       <c r="K123" t="str">
-        <v>Flo Jackson - Flo Milli</v>
+        <v>Roommates - Hilary Duff</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>L.U.C.K.Y</v>
+        <v>2SIDED</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/l-u-c-k-y/1861895147</v>
+        <v>https://music.apple.com/us/song/2sided/1862571197</v>
       </c>
       <c r="D124" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E124" t="str">
-        <v>Ö</v>
+        <v>Ambiguous Desire</v>
       </c>
       <c r="F124" t="str">
-        <v>2:18</v>
+        <v>2:57</v>
       </c>
       <c r="G124" t="str">
-        <v>Fcukers</v>
+        <v>Arlo Parks</v>
       </c>
       <c r="H124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I124" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/album/l-u-c-k-y/1861895134</v>
+        <v>https://music.apple.com/us/album/2sided/1862570378</v>
       </c>
       <c r="K124" t="str">
-        <v>L.U.C.K.Y - Fcukers</v>
+        <v>2SIDED - Arlo Parks</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Reclusive</v>
+        <v>Feel Alive</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/reclusive/1860405760</v>
+        <v>https://music.apple.com/us/song/feel-alive/1851368171</v>
       </c>
       <c r="D125" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E125" t="str">
-        <v>sounds for someone</v>
+        <v>ODYSSEY</v>
       </c>
       <c r="F125" t="str">
-        <v>3:06</v>
+        <v>2:48</v>
       </c>
       <c r="G125" t="str">
-        <v>Elmiene</v>
+        <v>ILLENIUM</v>
       </c>
       <c r="H125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I125" t="str">
-        <v>https://music.apple.com/us/artist/elmiene/1599562425</v>
+        <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/album/reclusive/1860405416</v>
+        <v>https://music.apple.com/us/album/feel-alive/1851368154</v>
       </c>
       <c r="K125" t="str">
-        <v>Reclusive - Elmiene</v>
+        <v>Feel Alive - ILLENIUM</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Site Unseen (feat. Waxahatchee)</v>
+        <v>God Spoke</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
+        <v>https://music.apple.com/us/song/god-spoke/1853069638</v>
       </c>
       <c r="D126" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E126" t="str">
-        <v>Creature of Habit</v>
+        <v>COSMIC OPERA ACT I</v>
       </c>
       <c r="F126" t="str">
-        <v>2:46</v>
+        <v>1:14</v>
       </c>
       <c r="G126" t="str">
-        <v>Courtney Barnett</v>
+        <v>Labrinth</v>
       </c>
       <c r="H126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I126" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
+        <v>https://music.apple.com/us/album/god-spoke/1853069628</v>
       </c>
       <c r="K126" t="str">
-        <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
+        <v>God Spoke - Labrinth</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Puppet Parade</v>
+        <v>Risk Takers</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
+        <v>https://music.apple.com/us/song/risk-takers/1866642666</v>
       </c>
       <c r="D127" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E127" t="str">
-        <v>Megadeth</v>
+        <v>El Mundo Es Tuyo (Inspired by Clika The Movie)</v>
       </c>
       <c r="F127" t="str">
-        <v>4:40</v>
+        <v>2:35</v>
       </c>
       <c r="G127" t="str">
-        <v>Megadeth</v>
+        <v>Herencia de Patrones</v>
       </c>
       <c r="H127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I127" t="str">
-        <v>https://music.apple.com/us/artist/megadeth/488289</v>
+        <v>https://music.apple.com/us/artist/herencia-de-patrones/1295294734</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
+        <v>https://music.apple.com/us/album/risk-takers/1866642665</v>
       </c>
       <c r="K127" t="str">
-        <v>Puppet Parade - Megadeth</v>
+        <v>Risk Takers - Herencia de Patrones</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Raft In The Sea</v>
+        <v>Never Comin' Back</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/raft-in-the-sea/1847662987</v>
+        <v>https://music.apple.com/us/song/never-comin-back/1862970557</v>
       </c>
       <c r="D128" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E128" t="str">
-        <v>Cerulean</v>
+        <v>Never Comin' Back - Single</v>
       </c>
       <c r="F128" t="str">
-        <v>3:35</v>
+        <v>3:57</v>
       </c>
       <c r="G128" t="str">
-        <v>Danny L Harle</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="H128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I128" t="str">
-        <v>https://music.apple.com/us/artist/danny-l-harle/985576556</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/album/raft-in-the-sea/1847662970</v>
+        <v>https://music.apple.com/us/album/never-comin-back/1862970555</v>
       </c>
       <c r="K128" t="str">
-        <v>Raft In The Sea - Danny L Harle</v>
+        <v>Never Comin' Back - Flatland Cavalry</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Good Night Baby</v>
+        <v>Lay Your Heartache Onto Mine (Songs From and Inspired by the Paramount+ Original Series Landman (Volume II))</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/good-night-baby/1849917462</v>
+        <v>https://music.apple.com/us/song/lay-your-heartache-onto-mine-songs-from-and-inspired/1867273711</v>
       </c>
       <c r="D129" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E129" t="str">
-        <v>Butterfly</v>
+        <v>Lay Your Heartache Onto Mine (Songs From and Inspired by the Paramount+ Original Series Landman (Volume II)) - Single</v>
       </c>
       <c r="F129" t="str">
-        <v>4:21</v>
+        <v>3:18</v>
       </c>
       <c r="G129" t="str">
-        <v>Daphni</v>
+        <v>Carter Faith</v>
       </c>
       <c r="H129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I129" t="str">
-        <v>https://music.apple.com/us/artist/daphni/1282779393</v>
+        <v>https://music.apple.com/us/artist/carter-faith/1489205896</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/album/good-night-baby/1849916838</v>
+        <v>https://music.apple.com/us/album/lay-your-heartache-onto-mine-songs-from-and-inspired/1867273471</v>
       </c>
       <c r="K129" t="str">
-        <v>Good Night Baby - Daphni</v>
+        <v>Lay Your Heartache Onto Mine (Songs From and Inspired by the Paramount+ Original Series Landman (Volume II)) - Carter Faith</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>CAMBIARÉ</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
+        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
       </c>
       <c r="D130" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E130" t="str">
-        <v>CAMBIARÉ - Single</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
       </c>
       <c r="F130" t="str">
-        <v>3:01</v>
+        <v>3:47</v>
       </c>
       <c r="G130" t="str">
-        <v>Luis Fonsi</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="H130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I130" t="str">
-        <v>https://music.apple.com/us/artist/luis-fonsi/102834</v>
+        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/album/cambiar%C3%A9/1867545265</v>
+        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
       </c>
       <c r="K130" t="str">
-        <v>CAMBIARÉ - Luis Fonsi</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Orange County (feat. Bizarrap, Kara Jackson &amp; Anoushka Shankar)</v>
+        <v>Traffic Lights (feat. Thom Yorke)</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/orange-county-feat-bizarrap-kara-jackson-anoushka-shankar/1837237867</v>
+        <v>https://music.apple.com/us/song/traffic-lights-feat-thom-yorke/1861644315</v>
       </c>
       <c r="D131" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E131" t="str">
-        <v>The Mountain</v>
+        <v>Honora</v>
       </c>
       <c r="F131" t="str">
-        <v>3:28</v>
+        <v>5:41</v>
       </c>
       <c r="G131" t="str">
-        <v>Gorillaz</v>
+        <v>Flea</v>
       </c>
       <c r="H131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I131" t="str">
-        <v>https://music.apple.com/us/artist/gorillaz/567072</v>
+        <v>https://music.apple.com/us/artist/flea/463953572</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/album/orange-county-feat-bizarrap-kara-jackson-anoushka-shankar/1837237742</v>
+        <v>https://music.apple.com/us/album/traffic-lights-feat-thom-yorke/1861644307</v>
       </c>
       <c r="K131" t="str">
-        <v>Orange County (feat. Bizarrap, Kara Jackson &amp; Anoushka Shankar) - Gorillaz</v>
+        <v>Traffic Lights (feat. Thom Yorke) - Flea</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Lluvia</v>
+        <v>Inferno (from "Heated Rivalry")</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/lluvia/1868476403</v>
+        <v>https://music.apple.com/us/song/inferno-from-heated-rivalry/1868783886</v>
       </c>
       <c r="D132" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E132" t="str">
-        <v>LA 8VA MARAVILLA</v>
+        <v>Heated Rivalry (Original Series Soundtrack)</v>
       </c>
       <c r="F132" t="str">
-        <v>3:24</v>
+        <v>4:26</v>
       </c>
       <c r="G132" t="str">
-        <v>Arcángel</v>
+        <v>Peter Peter</v>
       </c>
       <c r="H132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I132" t="str">
-        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
+        <v>https://music.apple.com/us/artist/peter-peter/71305428</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/album/lluvia/1868476390</v>
+        <v>https://music.apple.com/us/album/inferno-from-heated-rivalry/1868783596</v>
       </c>
       <c r="K132" t="str">
-        <v>Lluvia - Arcángel</v>
+        <v>Inferno (from "Heated Rivalry") - Peter Peter</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Knife</v>
+        <v>Yo Yan</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/knife/1862720450</v>
+        <v>https://music.apple.com/us/song/yo-yan/1867888651</v>
       </c>
       <c r="D133" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E133" t="str">
-        <v>THE SIN : VANISH</v>
+        <v>Kora - Single</v>
       </c>
       <c r="F133" t="str">
-        <v>2:19</v>
+        <v>2:00</v>
       </c>
       <c r="G133" t="str">
-        <v>ENHYPEN</v>
+        <v>Skrillex</v>
       </c>
       <c r="H133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I133" t="str">
-        <v>https://music.apple.com/us/artist/enhypen/1541011620</v>
+        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/album/knife/1862720020</v>
+        <v>https://music.apple.com/us/album/yo-yan/1867888650</v>
       </c>
       <c r="K133" t="str">
-        <v>Knife - ENHYPEN</v>
+        <v>Yo Yan - Skrillex</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>bad enough</v>
+        <v>Jogodo</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/bad-enough/1846949125</v>
+        <v>https://music.apple.com/us/song/jogodo/1867908454</v>
       </c>
       <c r="D134" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E134" t="str">
-        <v>locket</v>
+        <v>REAL, Vol. 1 - EP</v>
       </c>
       <c r="F134" t="str">
-        <v>3:42</v>
+        <v>3:08</v>
       </c>
       <c r="G134" t="str">
-        <v>Madison Beer</v>
+        <v>Wizkid</v>
       </c>
       <c r="H134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I134" t="str">
-        <v>https://music.apple.com/us/artist/madison-beer/696146587</v>
+        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/album/bad-enough/1846949115</v>
+        <v>https://music.apple.com/us/album/jogodo/1867908237</v>
       </c>
       <c r="K134" t="str">
-        <v>bad enough - Madison Beer</v>
+        <v>Jogodo - Wizkid</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>bad</v>
+        <v>Made It Out Alive</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/bad/1851566880</v>
+        <v>https://music.apple.com/us/song/made-it-out-alive/1867596345</v>
       </c>
       <c r="D135" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E135" t="str">
-        <v>bad - Single</v>
+        <v>Suffering From Success</v>
       </c>
       <c r="F135" t="str">
-        <v>2:41</v>
+        <v>3:00</v>
       </c>
       <c r="G135" t="str">
-        <v>Saint Harison</v>
+        <v>Dee Mula</v>
       </c>
       <c r="H135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I135" t="str">
-        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
+        <v>https://music.apple.com/us/artist/dee-mula/1330325377</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/album/bad/1851566879</v>
+        <v>https://music.apple.com/us/album/made-it-out-alive/1867596343</v>
       </c>
       <c r="K135" t="str">
-        <v>bad - Saint Harison</v>
+        <v>Made It Out Alive - Dee Mula</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Beat Yourself Up</v>
+        <v>One of Them Ones</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/beat-yourself-up/1845189973</v>
+        <v>https://music.apple.com/us/song/one-of-them-ones/1868850365</v>
       </c>
       <c r="D136" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E136" t="str">
-        <v>Whatever's Clever!</v>
+        <v>One of Them Ones - Single</v>
       </c>
       <c r="F136" t="str">
-        <v>2:58</v>
+        <v>3:05</v>
       </c>
       <c r="G136" t="str">
-        <v>Charlie Puth</v>
+        <v>Veeze</v>
       </c>
       <c r="H136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I136" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v>https://music.apple.com/us/artist/veeze/1464999308</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/album/beat-yourself-up/1845189970</v>
+        <v>https://music.apple.com/us/album/one-of-them-ones/1868850364</v>
       </c>
       <c r="K136" t="str">
-        <v>Beat Yourself Up - Charlie Puth</v>
+        <v>One of Them Ones - Veeze</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Roommates</v>
+        <v>Como Es Que Se Hace</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/roommates/1854567105</v>
+        <v>https://music.apple.com/us/song/como-es-que-se-hace/1864227584</v>
       </c>
       <c r="D137" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E137" t="str">
-        <v>luck... or something</v>
+        <v>Como Es Que Se Hace - Single</v>
       </c>
       <c r="F137" t="str">
-        <v>2:52</v>
+        <v>3:25</v>
       </c>
       <c r="G137" t="str">
-        <v>Hilary Duff</v>
+        <v>Yandel</v>
       </c>
       <c r="H137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I137" t="str">
-        <v>https://music.apple.com/us/artist/hilary-duff/3296003</v>
+        <v>https://music.apple.com/us/artist/yandel/72929426</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/album/roommates/1854567102</v>
+        <v>https://music.apple.com/us/album/como-es-que-se-hace/1864227582</v>
       </c>
       <c r="K137" t="str">
-        <v>Roommates - Hilary Duff</v>
+        <v>Como Es Que Se Hace - Yandel</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>2SIDED</v>
+        <v>Ever Since U Left Me (I Went Deaf)</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/2sided/1862571197</v>
+        <v>https://music.apple.com/us/song/ever-since-u-left-me-i-went-deaf/1863124175</v>
       </c>
       <c r="D138" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E138" t="str">
-        <v>Ambiguous Desire</v>
+        <v>Coke Wave 3.5: Narcos</v>
       </c>
       <c r="F138" t="str">
-        <v>2:57</v>
+        <v>2:16</v>
       </c>
       <c r="G138" t="str">
-        <v>Arlo Parks</v>
+        <v>French Montana</v>
       </c>
       <c r="H138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I138" t="str">
-        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
+        <v>https://music.apple.com/us/artist/french-montana/475816358</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/album/2sided/1862570378</v>
+        <v>https://music.apple.com/us/album/ever-since-u-left-me-i-went-deaf/1863124168</v>
       </c>
       <c r="K138" t="str">
-        <v>2SIDED - Arlo Parks</v>
+        <v>Ever Since U Left Me (I Went Deaf) - French Montana</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Feel Alive</v>
+        <v>Ay Dale</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/feel-alive/1851368171</v>
+        <v>https://music.apple.com/us/song/ay-dale/1862897966</v>
       </c>
       <c r="D139" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E139" t="str">
-        <v>ODYSSEY</v>
+        <v>Ay Dale - Single</v>
       </c>
       <c r="F139" t="str">
-        <v>2:48</v>
+        <v>2:26</v>
       </c>
       <c r="G139" t="str">
-        <v>ILLENIUM</v>
+        <v>Farruko</v>
       </c>
       <c r="H139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I139" t="str">
-        <v>https://music.apple.com/us/artist/illenium/645420096</v>
+        <v>https://music.apple.com/us/artist/farruko/364377482</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/album/feel-alive/1851368154</v>
+        <v>https://music.apple.com/us/album/ay-dale/1862897623</v>
       </c>
       <c r="K139" t="str">
-        <v>Feel Alive - ILLENIUM</v>
+        <v>Ay Dale - Farruko</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>God Spoke</v>
+        <v>Teary Eyes</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/god-spoke/1853069638</v>
+        <v>https://music.apple.com/us/song/teary-eyes/1869534187</v>
       </c>
       <c r="D140" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E140" t="str">
-        <v>COSMIC OPERA ACT I</v>
+        <v>Slime Cry</v>
       </c>
       <c r="F140" t="str">
-        <v>1:14</v>
+        <v>2:45</v>
       </c>
       <c r="G140" t="str">
-        <v>Labrinth</v>
+        <v>YoungBoy Never Broke Again</v>
       </c>
       <c r="H140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I140" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/youngboy-never-broke-again/1168822104</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/album/god-spoke/1853069628</v>
+        <v>https://music.apple.com/us/album/teary-eyes/1869534167</v>
       </c>
       <c r="K140" t="str">
-        <v>God Spoke - Labrinth</v>
+        <v>Teary Eyes - YoungBoy Never Broke Again</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Risk Takers</v>
+        <v>Bop It</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/risk-takers/1866642666</v>
+        <v>https://music.apple.com/us/song/bop-it/1867023470</v>
       </c>
       <c r="D141" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E141" t="str">
-        <v>El Mundo Es Tuyo (Inspired by Clika The Movie)</v>
+        <v>KUNTOLOGY 101</v>
       </c>
       <c r="F141" t="str">
-        <v>2:35</v>
+        <v>2:50</v>
       </c>
       <c r="G141" t="str">
-        <v>Herencia de Patrones</v>
+        <v>Aliyah's Interlude</v>
       </c>
       <c r="H141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I141" t="str">
-        <v>https://music.apple.com/us/artist/herencia-de-patrones/1295294734</v>
+        <v>https://music.apple.com/us/artist/aliyahs-interlude/1708765232</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/album/risk-takers/1866642665</v>
+        <v>https://music.apple.com/us/album/bop-it/1867023466</v>
       </c>
       <c r="K141" t="str">
-        <v>Risk Takers - Herencia de Patrones</v>
+        <v>Bop It - Aliyah's Interlude</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Never Comin' Back</v>
+        <v>My Everything</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/never-comin-back/1862970557</v>
+        <v>https://music.apple.com/us/song/my-everything/1862940302</v>
       </c>
       <c r="D142" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E142" t="str">
-        <v>Never Comin' Back - Single</v>
+        <v>My Everything - Single</v>
       </c>
       <c r="F142" t="str">
-        <v>3:57</v>
+        <v>2:33</v>
       </c>
       <c r="G142" t="str">
-        <v>Flatland Cavalry</v>
+        <v>Lecrae</v>
       </c>
       <c r="H142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I142" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/lecrae/130043072</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/album/never-comin-back/1862970555</v>
+        <v>https://music.apple.com/us/album/my-everything/1862940301</v>
       </c>
       <c r="K142" t="str">
-        <v>Never Comin' Back - Flatland Cavalry</v>
+        <v>My Everything - Lecrae</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Lay Your Heartache Onto Mine (Songs From and Inspired by the Paramount+ Original Series Landman (Volume II))</v>
+        <v>Whole Other Life</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/lay-your-heartache-onto-mine-songs-from-and-inspired/1867273711</v>
+        <v>https://music.apple.com/us/song/whole-other-life/1858374798</v>
       </c>
       <c r="D143" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E143" t="str">
-        <v>Lay Your Heartache Onto Mine (Songs From and Inspired by the Paramount+ Original Series Landman (Volume II)) - Single</v>
+        <v>Nat &amp; Alex Wolff</v>
       </c>
       <c r="F143" t="str">
-        <v>3:18</v>
+        <v>3:30</v>
       </c>
       <c r="G143" t="str">
-        <v>Carter Faith</v>
+        <v>Nat &amp; Alex Wolff</v>
       </c>
       <c r="H143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I143" t="str">
-        <v>https://music.apple.com/us/artist/carter-faith/1489205896</v>
+        <v>https://music.apple.com/us/artist/nat-alex-wolff/470903139</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/album/lay-your-heartache-onto-mine-songs-from-and-inspired/1867273471</v>
+        <v>https://music.apple.com/us/album/whole-other-life/1858374775</v>
       </c>
       <c r="K143" t="str">
-        <v>Lay Your Heartache Onto Mine (Songs From and Inspired by the Paramount+ Original Series Landman (Volume II)) - Carter Faith</v>
+        <v>Whole Other Life - Nat &amp; Alex Wolff</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
+        <v>Belladona</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
+        <v>https://music.apple.com/us/song/belladona/1862538378</v>
       </c>
       <c r="D144" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E144" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
+        <v>Belladona</v>
       </c>
       <c r="F144" t="str">
-        <v>3:47</v>
+        <v>3:32</v>
       </c>
       <c r="G144" t="str">
-        <v>Dolly Parton</v>
+        <v>Kenia Os</v>
       </c>
       <c r="H144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I144" t="str">
-        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
+        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
+        <v>https://music.apple.com/us/album/belladona/1862538030</v>
       </c>
       <c r="K144" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
+        <v>Belladona - Kenia Os</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Traffic Lights (feat. Thom Yorke)</v>
+        <v>Addicted to Love (From "Tell Me Lies (Season 3)")</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/traffic-lights-feat-thom-yorke/1861644315</v>
+        <v>https://music.apple.com/us/song/addicted-to-love-from-tell-me-lies-season-3/1867024880</v>
       </c>
       <c r="D145" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E145" t="str">
-        <v>Honora</v>
+        <v>Addicted to Love (From "Tell Me Lies (Season 3)") - Single</v>
       </c>
       <c r="F145" t="str">
-        <v>5:41</v>
+        <v>3:05</v>
       </c>
       <c r="G145" t="str">
-        <v>Flea</v>
+        <v>CHVRCHES</v>
       </c>
       <c r="H145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I145" t="str">
-        <v>https://music.apple.com/us/artist/flea/463953572</v>
+        <v>https://music.apple.com/us/artist/chvrches/566867492</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/album/traffic-lights-feat-thom-yorke/1861644307</v>
+        <v>https://music.apple.com/us/album/addicted-to-love-from-tell-me-lies-season-3/1867024879</v>
       </c>
       <c r="K145" t="str">
-        <v>Traffic Lights (feat. Thom Yorke) - Flea</v>
+        <v>Addicted to Love (From "Tell Me Lies (Season 3)") - CHVRCHES</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Inferno (from "Heated Rivalry")</v>
+        <v>Lie2Me</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/inferno-from-heated-rivalry/1868783886</v>
+        <v>https://music.apple.com/us/song/lie2me/1862762675</v>
       </c>
       <c r="D146" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E146" t="str">
-        <v>Heated Rivalry (Original Series Soundtrack)</v>
+        <v>Lie2Me - Single</v>
       </c>
       <c r="F146" t="str">
-        <v>4:26</v>
+        <v>3:03</v>
       </c>
       <c r="G146" t="str">
-        <v>Peter Peter</v>
+        <v>DC THE DON</v>
       </c>
       <c r="H146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I146" t="str">
-        <v>https://music.apple.com/us/artist/peter-peter/71305428</v>
+        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/album/inferno-from-heated-rivalry/1868783596</v>
+        <v>https://music.apple.com/us/album/lie2me/1862762674</v>
       </c>
       <c r="K146" t="str">
-        <v>Inferno (from "Heated Rivalry") - Peter Peter</v>
+        <v>Lie2Me - DC THE DON</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Yo Yan</v>
+        <v>High On Heaven</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/yo-yan/1867888651</v>
+        <v>https://music.apple.com/us/song/high-on-heaven/1859071765</v>
       </c>
       <c r="D147" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E147" t="str">
-        <v>Kora - Single</v>
+        <v>High On Heaven - Single</v>
       </c>
       <c r="F147" t="str">
-        <v>2:00</v>
+        <v>3:19</v>
       </c>
       <c r="G147" t="str">
-        <v>Skrillex</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="H147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I147" t="str">
-        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
+        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/album/yo-yan/1867888650</v>
+        <v>https://music.apple.com/us/album/high-on-heaven/1859071764</v>
       </c>
       <c r="K147" t="str">
-        <v>Yo Yan - Skrillex</v>
+        <v>High On Heaven - Nessa Barrett</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Jogodo</v>
+        <v>Most Wanted</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/jogodo/1867908454</v>
+        <v>https://music.apple.com/us/song/most-wanted/1844866135</v>
       </c>
       <c r="D148" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E148" t="str">
-        <v>REAL, Vol. 1 - EP</v>
+        <v>My Ego Told Me To</v>
       </c>
       <c r="F148" t="str">
-        <v>3:08</v>
+        <v>2:15</v>
       </c>
       <c r="G148" t="str">
-        <v>Wizkid</v>
+        <v>Leigh-Anne</v>
       </c>
       <c r="H148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I148" t="str">
-        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
+        <v>https://music.apple.com/us/artist/leigh-anne/1691386195</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/album/jogodo/1867908237</v>
+        <v>https://music.apple.com/us/album/most-wanted/1844865923</v>
       </c>
       <c r="K148" t="str">
-        <v>Jogodo - Wizkid</v>
+        <v>Most Wanted - Leigh-Anne</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Made It Out Alive</v>
+        <v>Anything Is Possible</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/made-it-out-alive/1867596345</v>
+        <v>https://music.apple.com/us/song/anything-is-possible/1867583228</v>
       </c>
       <c r="D149" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E149" t="str">
-        <v>Suffering From Success</v>
+        <v>Charlie The Wonderdog (Original Songs from the Motion Picture) - Single</v>
       </c>
       <c r="F149" t="str">
-        <v>3:00</v>
+        <v>2:57</v>
       </c>
       <c r="G149" t="str">
-        <v>Dee Mula</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="H149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I149" t="str">
-        <v>https://music.apple.com/us/artist/dee-mula/1330325377</v>
+        <v>https://music.apple.com/us/artist/bryan-adams/85932</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/album/made-it-out-alive/1867596343</v>
+        <v>https://music.apple.com/us/album/anything-is-possible/1867583221</v>
       </c>
       <c r="K149" t="str">
-        <v>Made It Out Alive - Dee Mula</v>
+        <v>Anything Is Possible - Bryan Adams</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>One of Them Ones</v>
+        <v>Volcano</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/one-of-them-ones/1868850365</v>
+        <v>https://music.apple.com/us/song/volcano/1862739924</v>
       </c>
       <c r="D150" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E150" t="str">
-        <v>One of Them Ones - Single</v>
+        <v>Volcano - Single</v>
       </c>
       <c r="F150" t="str">
-        <v>3:05</v>
+        <v>2:28</v>
       </c>
       <c r="G150" t="str">
-        <v>Veeze</v>
+        <v>Girl Tones</v>
       </c>
       <c r="H150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I150" t="str">
-        <v>https://music.apple.com/us/artist/veeze/1464999308</v>
+        <v>https://music.apple.com/us/artist/girl-tones/1761267584</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/album/one-of-them-ones/1868850364</v>
+        <v>https://music.apple.com/us/album/volcano/1862739923</v>
       </c>
       <c r="K150" t="str">
-        <v>One of Them Ones - Veeze</v>
+        <v>Volcano - Girl Tones</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Como Es Que Se Hace</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/como-es-que-se-hace/1864227584</v>
+        <v>https://music.apple.com/us/song/into-oblivion/1868804164</v>
       </c>
       <c r="D151" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E151" t="str">
-        <v>Como Es Que Se Hace - Single</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="F151" t="str">
-        <v>3:25</v>
+        <v>3:34</v>
       </c>
       <c r="G151" t="str">
-        <v>Yandel</v>
+        <v>Lamb of God</v>
       </c>
       <c r="H151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I151" t="str">
-        <v>https://music.apple.com/us/artist/yandel/72929426</v>
+        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/album/como-es-que-se-hace/1864227582</v>
+        <v>https://music.apple.com/us/album/into-oblivion/1868804163</v>
       </c>
       <c r="K151" t="str">
-        <v>Como Es Que Se Hace - Yandel</v>
+        <v>Into Oblivion - Lamb of God</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Ever Since U Left Me (I Went Deaf)</v>
+        <v>Beer and Blood Stains</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/ever-since-u-left-me-i-went-deaf/1863124175</v>
+        <v>https://music.apple.com/us/song/beer-and-blood-stains/1838992321</v>
       </c>
       <c r="D152" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E152" t="str">
-        <v>Coke Wave 3.5: Narcos</v>
+        <v>Listen Up!</v>
       </c>
       <c r="F152" t="str">
-        <v>2:16</v>
+        <v>3:19</v>
       </c>
       <c r="G152" t="str">
-        <v>French Montana</v>
+        <v>New Found Glory</v>
       </c>
       <c r="H152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I152" t="str">
-        <v>https://music.apple.com/us/artist/french-montana/475816358</v>
+        <v>https://music.apple.com/us/artist/new-found-glory/65551</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/album/ever-since-u-left-me-i-went-deaf/1863124168</v>
+        <v>https://music.apple.com/us/album/beer-and-blood-stains/1838991916</v>
       </c>
       <c r="K152" t="str">
-        <v>Ever Since U Left Me (I Went Deaf) - French Montana</v>
+        <v>Beer and Blood Stains - New Found Glory</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Ay Dale</v>
+        <v>Numb</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/ay-dale/1862897966</v>
+        <v>https://music.apple.com/us/song/numb/1860136324</v>
       </c>
       <c r="D153" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E153" t="str">
-        <v>Ay Dale - Single</v>
+        <v>Numb - Single</v>
       </c>
       <c r="F153" t="str">
-        <v>2:26</v>
+        <v>2:13</v>
       </c>
       <c r="G153" t="str">
-        <v>Farruko</v>
+        <v>Marc E. Bassy</v>
       </c>
       <c r="H153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I153" t="str">
-        <v>https://music.apple.com/us/artist/farruko/364377482</v>
+        <v>https://music.apple.com/us/artist/marc-e-bassy/899254194</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/album/ay-dale/1862897623</v>
+        <v>https://music.apple.com/us/album/numb/1860136319</v>
       </c>
       <c r="K153" t="str">
-        <v>Ay Dale - Farruko</v>
+        <v>Numb - Marc E. Bassy</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Teary Eyes</v>
+        <v>Foxtrot</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/teary-eyes/1869534187</v>
+        <v>https://music.apple.com/us/song/foxtrot/1860110201</v>
       </c>
       <c r="D154" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E154" t="str">
-        <v>Slime Cry</v>
+        <v>Saputjiji</v>
       </c>
       <c r="F154" t="str">
-        <v>2:45</v>
+        <v>1:33</v>
       </c>
       <c r="G154" t="str">
-        <v>YoungBoy Never Broke Again</v>
+        <v>Tanya Tagaq</v>
       </c>
       <c r="H154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I154" t="str">
-        <v>https://music.apple.com/us/artist/youngboy-never-broke-again/1168822104</v>
+        <v>https://music.apple.com/us/artist/tanya-tagaq/257545265</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/album/teary-eyes/1869534167</v>
+        <v>https://music.apple.com/us/album/foxtrot/1860109752</v>
       </c>
       <c r="K154" t="str">
-        <v>Teary Eyes - YoungBoy Never Broke Again</v>
+        <v>Foxtrot - Tanya Tagaq</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Bop It</v>
+        <v>Digital Winter</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/bop-it/1867023470</v>
+        <v>https://music.apple.com/us/song/digital-winter/1820332238</v>
       </c>
       <c r="D155" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E155" t="str">
-        <v>KUNTOLOGY 101</v>
+        <v>Stand On My Shoulders</v>
       </c>
       <c r="F155" t="str">
-        <v>2:50</v>
+        <v>3:45</v>
       </c>
       <c r="G155" t="str">
-        <v>Aliyah's Interlude</v>
+        <v>Ya Tseen</v>
       </c>
       <c r="H155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I155" t="str">
-        <v>https://music.apple.com/us/artist/aliyahs-interlude/1708765232</v>
+        <v>https://music.apple.com/us/artist/ya-tseen/1549782831</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/album/bop-it/1867023466</v>
+        <v>https://music.apple.com/us/album/digital-winter/1820332224</v>
       </c>
       <c r="K155" t="str">
-        <v>Bop It - Aliyah's Interlude</v>
+        <v>Digital Winter - Ya Tseen</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>My Everything</v>
+        <v>Back To You</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/my-everything/1862940302</v>
+        <v>https://music.apple.com/us/song/back-to-you/1861380254</v>
       </c>
       <c r="D156" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E156" t="str">
-        <v>My Everything - Single</v>
+        <v>Porcelain</v>
       </c>
       <c r="F156" t="str">
-        <v>2:33</v>
+        <v>3:10</v>
       </c>
       <c r="G156" t="str">
-        <v>Lecrae</v>
+        <v>Peach PRC</v>
       </c>
       <c r="H156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I156" t="str">
-        <v>https://music.apple.com/us/artist/lecrae/130043072</v>
+        <v>https://music.apple.com/us/artist/peach-prc/1469263677</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/album/my-everything/1862940301</v>
+        <v>https://music.apple.com/us/album/back-to-you/1861380240</v>
       </c>
       <c r="K156" t="str">
-        <v>My Everything - Lecrae</v>
+        <v>Back To You - Peach PRC</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Whole Other Life</v>
+        <v>Sleepwalker's Pendulum</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/whole-other-life/1858374798</v>
+        <v>https://music.apple.com/us/song/sleepwalkers-pendulum/1826115116</v>
       </c>
       <c r="D157" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E157" t="str">
-        <v>Nat &amp; Alex Wolff</v>
+        <v>Dreamer+</v>
       </c>
       <c r="F157" t="str">
-        <v>3:30</v>
+        <v>3:22</v>
       </c>
       <c r="G157" t="str">
-        <v>Nat &amp; Alex Wolff</v>
+        <v>Sassy 009</v>
       </c>
       <c r="H157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I157" t="str">
-        <v>https://music.apple.com/us/artist/nat-alex-wolff/470903139</v>
+        <v>https://music.apple.com/us/artist/sassy-009/1277035471</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/album/whole-other-life/1858374775</v>
+        <v>https://music.apple.com/us/album/sleepwalkers-pendulum/1826114506</v>
       </c>
       <c r="K157" t="str">
-        <v>Whole Other Life - Nat &amp; Alex Wolff</v>
+        <v>Sleepwalker's Pendulum - Sassy 009</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Belladona</v>
+        <v>Ruin Me</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/belladona/1862538378</v>
+        <v>https://music.apple.com/us/song/ruin-me/1850741533</v>
       </c>
       <c r="D158" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E158" t="str">
-        <v>Belladona</v>
+        <v>HEAD FIRST - EP</v>
       </c>
       <c r="F158" t="str">
-        <v>3:32</v>
+        <v>2:31</v>
       </c>
       <c r="G158" t="str">
-        <v>Kenia Os</v>
+        <v>Corbyn Besson</v>
       </c>
       <c r="H158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I158" t="str">
-        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
+        <v>https://music.apple.com/us/artist/corbyn-besson/810434797</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/album/belladona/1862538030</v>
+        <v>https://music.apple.com/us/album/ruin-me/1850741514</v>
       </c>
       <c r="K158" t="str">
-        <v>Belladona - Kenia Os</v>
+        <v>Ruin Me - Corbyn Besson</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Addicted to Love (From "Tell Me Lies (Season 3)")</v>
+        <v>w-w-w-w-w</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/addicted-to-love-from-tell-me-lies-season-3/1867024880</v>
+        <v>https://music.apple.com/us/song/w-w-w-w-w/1846462521</v>
       </c>
       <c r="D159" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E159" t="str">
-        <v>Addicted to Love (From "Tell Me Lies (Season 3)") - Single</v>
+        <v>the apple tree under the sea</v>
       </c>
       <c r="F159" t="str">
-        <v>3:05</v>
+        <v>4:26</v>
       </c>
       <c r="G159" t="str">
-        <v>CHVRCHES</v>
+        <v>hemlocke springs</v>
       </c>
       <c r="H159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I159" t="str">
-        <v>https://music.apple.com/us/artist/chvrches/566867492</v>
+        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/album/addicted-to-love-from-tell-me-lies-season-3/1867024879</v>
+        <v>https://music.apple.com/us/album/w-w-w-w-w/1846462383</v>
       </c>
       <c r="K159" t="str">
-        <v>Addicted to Love (From "Tell Me Lies (Season 3)") - CHVRCHES</v>
+        <v>w-w-w-w-w - hemlocke springs</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Lie2Me</v>
+        <v>Struggle Bus</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/lie2me/1862762675</v>
+        <v>https://music.apple.com/us/song/struggle-bus/1862024076</v>
       </c>
       <c r="D160" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E160" t="str">
-        <v>Lie2Me - Single</v>
+        <v>Struggle Bus - Single</v>
       </c>
       <c r="F160" t="str">
-        <v>3:03</v>
+        <v>3:20</v>
       </c>
       <c r="G160" t="str">
-        <v>DC THE DON</v>
+        <v>Iris Copperman</v>
       </c>
       <c r="H160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I160" t="str">
-        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
+        <v>https://music.apple.com/us/artist/iris-copperman/1741269048</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/album/lie2me/1862762674</v>
+        <v>https://music.apple.com/us/album/struggle-bus/1862024075</v>
       </c>
       <c r="K160" t="str">
-        <v>Lie2Me - DC THE DON</v>
+        <v>Struggle Bus - Iris Copperman</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>High On Heaven</v>
+        <v>Over</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/high-on-heaven/1859071765</v>
+        <v>https://music.apple.com/us/song/over/1862351820</v>
       </c>
       <c r="D161" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E161" t="str">
-        <v>High On Heaven - Single</v>
+        <v>Over - Single</v>
       </c>
       <c r="F161" t="str">
-        <v>3:19</v>
+        <v>3:49</v>
       </c>
       <c r="G161" t="str">
-        <v>Nessa Barrett</v>
+        <v>Sydney Rose</v>
       </c>
       <c r="H161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I161" t="str">
-        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
+        <v>https://music.apple.com/us/artist/sydney-rose/354936789</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/album/high-on-heaven/1859071764</v>
+        <v>https://music.apple.com/us/album/over/1862351811</v>
       </c>
       <c r="K161" t="str">
-        <v>High On Heaven - Nessa Barrett</v>
+        <v>Over - Sydney Rose</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Most Wanted</v>
+        <v>Lean</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/most-wanted/1844866135</v>
+        <v>https://music.apple.com/us/song/lean/1862829540</v>
       </c>
       <c r="D162" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E162" t="str">
-        <v>My Ego Told Me To</v>
+        <v>Lean - Single</v>
       </c>
       <c r="F162" t="str">
-        <v>2:15</v>
+        <v>3:53</v>
       </c>
       <c r="G162" t="str">
-        <v>Leigh-Anne</v>
+        <v>Charlotte Day Wilson</v>
       </c>
       <c r="H162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I162" t="str">
-        <v>https://music.apple.com/us/artist/leigh-anne/1691386195</v>
+        <v>https://music.apple.com/us/artist/charlotte-day-wilson/1053594538</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/album/most-wanted/1844865923</v>
+        <v>https://music.apple.com/us/album/lean/1862829538</v>
       </c>
       <c r="K162" t="str">
-        <v>Most Wanted - Leigh-Anne</v>
+        <v>Lean - Charlotte Day Wilson</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Anything Is Possible</v>
+        <v>F**k It Up</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/anything-is-possible/1867583228</v>
+        <v>https://music.apple.com/us/song/f-k-it-up/1849002929</v>
       </c>
       <c r="D163" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E163" t="str">
-        <v>Charlie The Wonderdog (Original Songs from the Motion Picture) - Single</v>
+        <v>F**k It Up - EP</v>
       </c>
       <c r="F163" t="str">
-        <v>2:57</v>
+        <v>3:32</v>
       </c>
       <c r="G163" t="str">
-        <v>Bryan Adams</v>
+        <v>Master Peace</v>
       </c>
       <c r="H163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I163" t="str">
-        <v>https://music.apple.com/us/artist/bryan-adams/85932</v>
+        <v>https://music.apple.com/us/artist/master-peace/1477196856</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/album/anything-is-possible/1867583221</v>
+        <v>https://music.apple.com/us/album/f-k-it-up/1849002928</v>
       </c>
       <c r="K163" t="str">
-        <v>Anything Is Possible - Bryan Adams</v>
+        <v>F**k It Up - Master Peace</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Volcano</v>
+        <v>La Carrera</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/volcano/1862739924</v>
+        <v>https://music.apple.com/us/song/la-carrera/1863188476</v>
       </c>
       <c r="D164" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E164" t="str">
-        <v>Volcano - Single</v>
+        <v>La Carrera - Single</v>
       </c>
       <c r="F164" t="str">
-        <v>2:28</v>
+        <v>3:40</v>
       </c>
       <c r="G164" t="str">
-        <v>Girl Tones</v>
+        <v>Moa Rivera</v>
       </c>
       <c r="H164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I164" t="str">
-        <v>https://music.apple.com/us/artist/girl-tones/1761267584</v>
+        <v>https://music.apple.com/us/artist/moa-rivera/1636808812</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/album/volcano/1862739923</v>
+        <v>https://music.apple.com/us/album/la-carrera/1863188474</v>
       </c>
       <c r="K164" t="str">
-        <v>Volcano - Girl Tones</v>
+        <v>La Carrera - Moa Rivera</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Into Oblivion</v>
+        <v>No Lube So Rude</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/into-oblivion/1868804164</v>
+        <v>https://music.apple.com/us/song/no-lube-so-rude/1856065376</v>
       </c>
       <c r="D165" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E165" t="str">
-        <v>Into Oblivion</v>
+        <v>No Lube So Rude</v>
       </c>
       <c r="F165" t="str">
-        <v>3:34</v>
+        <v>2:48</v>
       </c>
       <c r="G165" t="str">
-        <v>Lamb of God</v>
+        <v>Peaches</v>
       </c>
       <c r="H165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I165" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/peaches/3028600</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/album/into-oblivion/1868804163</v>
+        <v>https://music.apple.com/us/album/no-lube-so-rude/1856064995</v>
       </c>
       <c r="K165" t="str">
-        <v>Into Oblivion - Lamb of God</v>
+        <v>No Lube So Rude - Peaches</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Beer and Blood Stains</v>
+        <v>Somersaults</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/beer-and-blood-stains/1838992321</v>
+        <v>https://music.apple.com/us/song/somersaults/1847159408</v>
       </c>
       <c r="D166" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E166" t="str">
-        <v>Listen Up!</v>
+        <v>Somersaults</v>
       </c>
       <c r="F166" t="str">
-        <v>3:19</v>
+        <v>4:32</v>
       </c>
       <c r="G166" t="str">
-        <v>New Found Glory</v>
+        <v>deathcrash</v>
       </c>
       <c r="H166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I166" t="str">
-        <v>https://music.apple.com/us/artist/new-found-glory/65551</v>
+        <v>https://music.apple.com/us/artist/deathcrash/1461469738</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/album/beer-and-blood-stains/1838991916</v>
+        <v>https://music.apple.com/us/album/somersaults/1847159406</v>
       </c>
       <c r="K166" t="str">
-        <v>Beer and Blood Stains - New Found Glory</v>
+        <v>Somersaults - deathcrash</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Numb</v>
+        <v>2005</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/numb/1860136324</v>
+        <v>https://music.apple.com/us/song/2005/1854873143</v>
       </c>
       <c r="D167" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E167" t="str">
-        <v>Numb - Single</v>
+        <v>Almost There</v>
       </c>
       <c r="F167" t="str">
-        <v>2:13</v>
+        <v>3:52</v>
       </c>
       <c r="G167" t="str">
-        <v>Marc E. Bassy</v>
+        <v>The Academy Is...</v>
       </c>
       <c r="H167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I167" t="str">
-        <v>https://music.apple.com/us/artist/marc-e-bassy/899254194</v>
+        <v>https://music.apple.com/us/artist/the-academy-is/75024274</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/album/numb/1860136319</v>
+        <v>https://music.apple.com/us/album/2005/1854873133</v>
       </c>
       <c r="K167" t="str">
-        <v>Numb - Marc E. Bassy</v>
+        <v>2005 - The Academy Is...</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Foxtrot</v>
+        <v>I Had a Ball</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/foxtrot/1860110201</v>
+        <v>https://music.apple.com/us/song/i-had-a-ball/1863330906</v>
       </c>
       <c r="D168" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E168" t="str">
-        <v>Saputjiji</v>
+        <v>Palm Royale Season 2 (Apple TV Original Series Soundtrack)</v>
       </c>
       <c r="F168" t="str">
-        <v>1:33</v>
+        <v>4:14</v>
       </c>
       <c r="G168" t="str">
-        <v>Tanya Tagaq</v>
+        <v>Kristen Wiig</v>
       </c>
       <c r="H168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I168" t="str">
-        <v>https://music.apple.com/us/artist/tanya-tagaq/257545265</v>
+        <v>https://music.apple.com/us/artist/kristen-wiig/273077223</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/album/foxtrot/1860109752</v>
+        <v>https://music.apple.com/us/album/i-had-a-ball/1863330900</v>
       </c>
       <c r="K168" t="str">
-        <v>Foxtrot - Tanya Tagaq</v>
+        <v>I Had a Ball - Kristen Wiig</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Digital Winter</v>
+        <v>IDB</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/digital-winter/1820332238</v>
+        <v>https://music.apple.com/us/song/idb/1859084151</v>
       </c>
       <c r="D169" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E169" t="str">
-        <v>Stand On My Shoulders</v>
+        <v>IDB - Single</v>
       </c>
       <c r="F169" t="str">
-        <v>3:45</v>
+        <v>2:52</v>
       </c>
       <c r="G169" t="str">
-        <v>Ya Tseen</v>
+        <v>42 Dugg</v>
       </c>
       <c r="H169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I169" t="str">
-        <v>https://music.apple.com/us/artist/ya-tseen/1549782831</v>
+        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/album/digital-winter/1820332224</v>
+        <v>https://music.apple.com/us/album/idb/1859084147</v>
       </c>
       <c r="K169" t="str">
-        <v>Digital Winter - Ya Tseen</v>
+        <v>IDB - 42 Dugg</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Back To You</v>
+        <v>Feel This Way</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/back-to-you/1861380254</v>
+        <v>https://music.apple.com/us/song/feel-this-way/1862902478</v>
       </c>
       <c r="D170" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E170" t="str">
-        <v>Porcelain</v>
+        <v>Feel This Way - Single</v>
       </c>
       <c r="F170" t="str">
-        <v>3:10</v>
+        <v>3:04</v>
       </c>
       <c r="G170" t="str">
-        <v>Peach PRC</v>
+        <v>Josh Baker</v>
       </c>
       <c r="H170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I170" t="str">
-        <v>https://music.apple.com/us/artist/peach-prc/1469263677</v>
+        <v>https://music.apple.com/us/artist/josh-baker/150294413</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/album/back-to-you/1861380240</v>
+        <v>https://music.apple.com/us/album/feel-this-way/1862902476</v>
       </c>
       <c r="K170" t="str">
-        <v>Back To You - Peach PRC</v>
+        <v>Feel This Way - Josh Baker</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Sleepwalker's Pendulum</v>
+        <v>Falling</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/sleepwalkers-pendulum/1826115116</v>
+        <v>https://music.apple.com/us/song/falling/1861598107</v>
       </c>
       <c r="D171" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E171" t="str">
-        <v>Dreamer+</v>
+        <v>Falling - Single</v>
       </c>
       <c r="F171" t="str">
-        <v>3:22</v>
+        <v>3:02</v>
       </c>
       <c r="G171" t="str">
-        <v>Sassy 009</v>
+        <v>Shimza</v>
       </c>
       <c r="H171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I171" t="str">
-        <v>https://music.apple.com/us/artist/sassy-009/1277035471</v>
+        <v>https://music.apple.com/us/artist/shimza/697739898</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/album/sleepwalkers-pendulum/1826114506</v>
+        <v>https://music.apple.com/us/album/falling/1861598106</v>
       </c>
       <c r="K171" t="str">
-        <v>Sleepwalker's Pendulum - Sassy 009</v>
+        <v>Falling - Shimza</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Ruin Me</v>
+        <v>Message to You</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/ruin-me/1850741533</v>
+        <v>https://music.apple.com/us/song/message-to-you/1867275596</v>
       </c>
       <c r="D172" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E172" t="str">
-        <v>HEAD FIRST - EP</v>
+        <v>Heavy On The Soul</v>
       </c>
       <c r="F172" t="str">
-        <v>2:31</v>
+        <v>3:37</v>
       </c>
       <c r="G172" t="str">
-        <v>Corbyn Besson</v>
+        <v>Ty Myers</v>
       </c>
       <c r="H172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I172" t="str">
-        <v>https://music.apple.com/us/artist/corbyn-besson/810434797</v>
+        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/album/ruin-me/1850741514</v>
+        <v>https://music.apple.com/us/album/message-to-you/1867275110</v>
       </c>
       <c r="K172" t="str">
-        <v>Ruin Me - Corbyn Besson</v>
+        <v>Message to You - Ty Myers</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>w-w-w-w-w</v>
+        <v>NOTHING IS REAL</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/w-w-w-w-w/1846462521</v>
+        <v>https://music.apple.com/us/song/nothing-is-real/1866859742</v>
       </c>
       <c r="D173" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E173" t="str">
-        <v>the apple tree under the sea</v>
+        <v>NOTHING IS REAL - Single</v>
       </c>
       <c r="F173" t="str">
-        <v>4:26</v>
+        <v>3:06</v>
       </c>
       <c r="G173" t="str">
-        <v>hemlocke springs</v>
+        <v>DESTIN CONRAD</v>
       </c>
       <c r="H173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I173" t="str">
-        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
+        <v>https://music.apple.com/us/artist/destin-conrad/852999989</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/album/w-w-w-w-w/1846462383</v>
+        <v>https://music.apple.com/us/album/nothing-is-real/1866859497</v>
       </c>
       <c r="K173" t="str">
-        <v>w-w-w-w-w - hemlocke springs</v>
+        <v>NOTHING IS REAL - DESTIN CONRAD</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Struggle Bus</v>
+        <v>CUÉNTAME</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/struggle-bus/1862024076</v>
+        <v>https://music.apple.com/us/song/cu%C3%A9ntame/1862973854</v>
       </c>
       <c r="D174" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E174" t="str">
-        <v>Struggle Bus - Single</v>
+        <v>CUÉNTAME - Single</v>
       </c>
       <c r="F174" t="str">
-        <v>3:20</v>
+        <v>2:42</v>
       </c>
       <c r="G174" t="str">
-        <v>Iris Copperman</v>
+        <v>FloyyMenor</v>
       </c>
       <c r="H174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I174" t="str">
-        <v>https://music.apple.com/us/artist/iris-copperman/1741269048</v>
+        <v>https://music.apple.com/us/artist/floyymenor/1676497551</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/album/struggle-bus/1862024075</v>
+        <v>https://music.apple.com/us/album/cu%C3%A9ntame/1862973853</v>
       </c>
       <c r="K174" t="str">
-        <v>Struggle Bus - Iris Copperman</v>
+        <v>CUÉNTAME - FloyyMenor</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Over</v>
+        <v>DANCE...</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/over/1862351820</v>
+        <v>https://music.apple.com/us/song/dance/1867531306</v>
       </c>
       <c r="D175" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E175" t="str">
-        <v>Over - Single</v>
+        <v>WOR$T GIRL IN AMERICA</v>
       </c>
       <c r="F175" t="str">
-        <v>3:49</v>
+        <v>4:47</v>
       </c>
       <c r="G175" t="str">
-        <v>Sydney Rose</v>
+        <v>Slayyyter</v>
       </c>
       <c r="H175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I175" t="str">
-        <v>https://music.apple.com/us/artist/sydney-rose/354936789</v>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/album/over/1862351811</v>
+        <v>https://music.apple.com/us/album/dance/1867530577</v>
       </c>
       <c r="K175" t="str">
-        <v>Over - Sydney Rose</v>
+        <v>DANCE... - Slayyyter</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Lean</v>
+        <v>welcome to the circus</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/lean/1862829540</v>
+        <v>https://music.apple.com/us/song/welcome-to-the-circus/1861011604</v>
       </c>
       <c r="D176" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E176" t="str">
-        <v>Lean - Single</v>
+        <v>welcome to the circus - Single</v>
       </c>
       <c r="F176" t="str">
-        <v>3:53</v>
+        <v>2:29</v>
       </c>
       <c r="G176" t="str">
-        <v>Charlotte Day Wilson</v>
+        <v>Jagwar Twin</v>
       </c>
       <c r="H176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I176" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-day-wilson/1053594538</v>
+        <v>https://music.apple.com/us/artist/jagwar-twin/1429051937</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/album/lean/1862829538</v>
+        <v>https://music.apple.com/us/album/welcome-to-the-circus/1861011603</v>
       </c>
       <c r="K176" t="str">
-        <v>Lean - Charlotte Day Wilson</v>
+        <v>welcome to the circus - Jagwar Twin</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>F**k It Up</v>
+        <v>playlist</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/f-k-it-up/1849002929</v>
+        <v>https://music.apple.com/us/song/playlist/1859009927</v>
       </c>
       <c r="D177" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E177" t="str">
-        <v>F**k It Up - EP</v>
+        <v>playlist - Single</v>
       </c>
       <c r="F177" t="str">
-        <v>3:32</v>
+        <v>2:44</v>
       </c>
       <c r="G177" t="str">
-        <v>Master Peace</v>
+        <v>Tenroc</v>
       </c>
       <c r="H177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I177" t="str">
-        <v>https://music.apple.com/us/artist/master-peace/1477196856</v>
+        <v>https://music.apple.com/us/artist/tenroc/1711844910</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/album/f-k-it-up/1849002928</v>
+        <v>https://music.apple.com/us/album/playlist/1859009923</v>
       </c>
       <c r="K177" t="str">
-        <v>F**k It Up - Master Peace</v>
+        <v>playlist - Tenroc</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>La Carrera</v>
+        <v>Marlboro Man</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/la-carrera/1863188476</v>
+        <v>https://music.apple.com/us/song/marlboro-man/1862008741</v>
       </c>
       <c r="D178" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E178" t="str">
-        <v>La Carrera - Single</v>
+        <v>Marlboro Man - Single</v>
       </c>
       <c r="F178" t="str">
-        <v>3:40</v>
+        <v>3:23</v>
       </c>
       <c r="G178" t="str">
-        <v>Moa Rivera</v>
+        <v>Midland</v>
       </c>
       <c r="H178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I178" t="str">
-        <v>https://music.apple.com/us/artist/moa-rivera/1636808812</v>
+        <v>https://music.apple.com/us/artist/midland/1171869852</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/album/la-carrera/1863188474</v>
+        <v>https://music.apple.com/us/album/marlboro-man/1862008740</v>
       </c>
       <c r="K178" t="str">
-        <v>La Carrera - Moa Rivera</v>
+        <v>Marlboro Man - Midland</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>No Lube So Rude</v>
+        <v>Enabling</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/no-lube-so-rude/1856065376</v>
+        <v>https://music.apple.com/us/song/enabling/1860993048</v>
       </c>
       <c r="D179" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E179" t="str">
-        <v>No Lube So Rude</v>
+        <v>Enabling - Single</v>
       </c>
       <c r="F179" t="str">
-        <v>2:48</v>
+        <v>3:18</v>
       </c>
       <c r="G179" t="str">
-        <v>Peaches</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="H179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I179" t="str">
-        <v>https://music.apple.com/us/artist/peaches/3028600</v>
+        <v>https://music.apple.com/us/artist/tenille-townes/1367713770</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/album/no-lube-so-rude/1856064995</v>
+        <v>https://music.apple.com/us/album/enabling/1860992859</v>
       </c>
       <c r="K179" t="str">
-        <v>No Lube So Rude - Peaches</v>
+        <v>Enabling - Tenille Townes</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Somersaults</v>
+        <v>Two Broken Hearts</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/somersaults/1847159408</v>
+        <v>https://music.apple.com/us/song/two-broken-hearts/1841485428</v>
       </c>
       <c r="D180" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E180" t="str">
-        <v>Somersaults</v>
+        <v>Steel Town</v>
       </c>
       <c r="F180" t="str">
-        <v>4:32</v>
+        <v>3:53</v>
       </c>
       <c r="G180" t="str">
-        <v>deathcrash</v>
+        <v>Morgan Evans</v>
       </c>
       <c r="H180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I180" t="str">
-        <v>https://music.apple.com/us/artist/deathcrash/1461469738</v>
+        <v>https://music.apple.com/us/artist/morgan-evans/262665075</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/album/somersaults/1847159406</v>
+        <v>https://music.apple.com/us/album/two-broken-hearts/1841484758</v>
       </c>
       <c r="K180" t="str">
-        <v>Somersaults - deathcrash</v>
+        <v>Two Broken Hearts - Morgan Evans</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>2005</v>
+        <v>Lost in My Bed</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/2005/1854873143</v>
+        <v>https://music.apple.com/us/song/lost-in-my-bed/1862222274</v>
       </c>
       <c r="D181" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E181" t="str">
-        <v>Almost There</v>
+        <v>Lost in My Bed - Single</v>
       </c>
       <c r="F181" t="str">
-        <v>3:52</v>
+        <v>3:46</v>
       </c>
       <c r="G181" t="str">
-        <v>The Academy Is...</v>
+        <v>Khalil</v>
       </c>
       <c r="H181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I181" t="str">
-        <v>https://music.apple.com/us/artist/the-academy-is/75024274</v>
+        <v>https://music.apple.com/us/artist/khalil/1223181975</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/album/2005/1854873133</v>
+        <v>https://music.apple.com/us/album/lost-in-my-bed/1862222272</v>
       </c>
       <c r="K181" t="str">
-        <v>2005 - The Academy Is...</v>
+        <v>Lost in My Bed - Khalil</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>I Had a Ball</v>
+        <v>Father Time</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/i-had-a-ball/1863330906</v>
+        <v>https://music.apple.com/us/song/father-time/1858611581</v>
       </c>
       <c r="D182" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E182" t="str">
-        <v>Palm Royale Season 2 (Apple TV Original Series Soundtrack)</v>
+        <v>Honey Water</v>
       </c>
       <c r="F182" t="str">
-        <v>4:14</v>
+        <v>1:58</v>
       </c>
       <c r="G182" t="str">
-        <v>Kristen Wiig</v>
+        <v>Girlfriend</v>
       </c>
       <c r="H182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I182" t="str">
-        <v>https://music.apple.com/us/artist/kristen-wiig/273077223</v>
+        <v>https://music.apple.com/us/artist/girlfriend/1511096374</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/album/i-had-a-ball/1863330900</v>
+        <v>https://music.apple.com/us/album/father-time/1858611265</v>
       </c>
       <c r="K182" t="str">
-        <v>I Had a Ball - Kristen Wiig</v>
+        <v>Father Time - Girlfriend</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>IDB</v>
+        <v>MVLAN</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/idb/1859084151</v>
+        <v>https://music.apple.com/us/song/mvlan/1867584574</v>
       </c>
       <c r="D183" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E183" t="str">
-        <v>IDB - Single</v>
+        <v>MVLAN - Single</v>
       </c>
       <c r="F183" t="str">
-        <v>2:52</v>
+        <v>3:41</v>
       </c>
       <c r="G183" t="str">
-        <v>42 Dugg</v>
+        <v>YOVNGCHIMI</v>
       </c>
       <c r="H183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I183" t="str">
-        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
+        <v>https://music.apple.com/us/artist/yovngchimi/1558257759</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/album/idb/1859084147</v>
+        <v>https://music.apple.com/us/album/mvlan/1867584573</v>
       </c>
       <c r="K183" t="str">
-        <v>IDB - 42 Dugg</v>
+        <v>MVLAN - YOVNGCHIMI</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Feel This Way</v>
+        <v>Name In Blood</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/feel-this-way/1862902478</v>
+        <v>https://music.apple.com/us/song/name-in-blood/1859687600</v>
       </c>
       <c r="D184" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E184" t="str">
-        <v>Feel This Way - Single</v>
+        <v>Engines of Demolition</v>
       </c>
       <c r="F184" t="str">
-        <v>3:04</v>
+        <v>4:36</v>
       </c>
       <c r="G184" t="str">
-        <v>Josh Baker</v>
+        <v>Black Label Society</v>
       </c>
       <c r="H184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I184" t="str">
-        <v>https://music.apple.com/us/artist/josh-baker/150294413</v>
+        <v>https://music.apple.com/us/artist/black-label-society/2778807</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/album/feel-this-way/1862902476</v>
+        <v>https://music.apple.com/us/album/name-in-blood/1859687597</v>
       </c>
       <c r="K184" t="str">
-        <v>Feel This Way - Josh Baker</v>
+        <v>Name In Blood - Black Label Society</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Falling</v>
+        <v>Eyeball</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/falling/1861598107</v>
+        <v>https://music.apple.com/us/song/eyeball/1862539350</v>
       </c>
       <c r="D185" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E185" t="str">
-        <v>Falling - Single</v>
+        <v>Eyeball - EP</v>
       </c>
       <c r="F185" t="str">
-        <v>3:02</v>
+        <v>2:14</v>
       </c>
       <c r="G185" t="str">
-        <v>Shimza</v>
+        <v>They Might Be Giants</v>
       </c>
       <c r="H185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I185" t="str">
-        <v>https://music.apple.com/us/artist/shimza/697739898</v>
+        <v>https://music.apple.com/us/artist/they-might-be-giants/149020</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/album/falling/1861598106</v>
+        <v>https://music.apple.com/us/album/eyeball/1862539346</v>
       </c>
       <c r="K185" t="str">
-        <v>Falling - Shimza</v>
+        <v>Eyeball - They Might Be Giants</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Message to You</v>
+        <v>Long Gone</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/message-to-you/1867275596</v>
+        <v>https://music.apple.com/us/song/long-gone/1847573926</v>
       </c>
       <c r="D186" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E186" t="str">
-        <v>Heavy On The Soul</v>
+        <v>Tenterhooks</v>
       </c>
       <c r="F186" t="str">
-        <v>3:37</v>
+        <v>3:55</v>
       </c>
       <c r="G186" t="str">
-        <v>Ty Myers</v>
+        <v>Silversun Pickups</v>
       </c>
       <c r="H186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I186" t="str">
-        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
+        <v>https://music.apple.com/us/artist/silversun-pickups/74752665</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/album/message-to-you/1867275110</v>
+        <v>https://music.apple.com/us/album/long-gone/1847573918</v>
       </c>
       <c r="K186" t="str">
-        <v>Message to You - Ty Myers</v>
+        <v>Long Gone - Silversun Pickups</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>NOTHING IS REAL</v>
+        <v>iloveitiloveitiloveit</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/nothing-is-real/1866859742</v>
+        <v>https://music.apple.com/us/song/iloveitiloveitiloveit/1867034427</v>
       </c>
       <c r="D187" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E187" t="str">
-        <v>NOTHING IS REAL - Single</v>
+        <v>iloveitiloveitiloveit - Single</v>
       </c>
       <c r="F187" t="str">
-        <v>3:06</v>
+        <v>3:03</v>
       </c>
       <c r="G187" t="str">
-        <v>DESTIN CONRAD</v>
+        <v>Bella Kay</v>
       </c>
       <c r="H187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I187" t="str">
-        <v>https://music.apple.com/us/artist/destin-conrad/852999989</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/album/nothing-is-real/1866859497</v>
+        <v>https://music.apple.com/us/album/iloveitiloveitiloveit/1867034426</v>
       </c>
       <c r="K187" t="str">
-        <v>NOTHING IS REAL - DESTIN CONRAD</v>
+        <v>iloveitiloveitiloveit - Bella Kay</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>CUÉNTAME</v>
+        <v>To The Edge</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/cu%C3%A9ntame/1862973854</v>
+        <v>https://music.apple.com/us/song/to-the-edge/1863513891</v>
       </c>
       <c r="D188" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E188" t="str">
-        <v>CUÉNTAME - Single</v>
+        <v>To The Edge - Single</v>
       </c>
       <c r="F188" t="str">
-        <v>2:42</v>
+        <v>3:19</v>
       </c>
       <c r="G188" t="str">
-        <v>FloyyMenor</v>
+        <v>Alex Jude</v>
       </c>
       <c r="H188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I188" t="str">
-        <v>https://music.apple.com/us/artist/floyymenor/1676497551</v>
+        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/album/cu%C3%A9ntame/1862973853</v>
+        <v>https://music.apple.com/us/album/to-the-edge/1863513887</v>
       </c>
       <c r="K188" t="str">
-        <v>CUÉNTAME - FloyyMenor</v>
+        <v>To The Edge - Alex Jude</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>DANCE...</v>
+        <v>demons</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/dance/1867531306</v>
+        <v>https://music.apple.com/us/song/demons/1861978106</v>
       </c>
       <c r="D189" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E189" t="str">
-        <v>WOR$T GIRL IN AMERICA</v>
+        <v>demons - Single</v>
       </c>
       <c r="F189" t="str">
-        <v>4:47</v>
+        <v>3:10</v>
       </c>
       <c r="G189" t="str">
-        <v>Slayyyter</v>
+        <v>Josiah Queen</v>
       </c>
       <c r="H189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I189" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/josiah-queen/1498117530</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/album/dance/1867530577</v>
+        <v>https://music.apple.com/us/album/demons/1861978105</v>
       </c>
       <c r="K189" t="str">
-        <v>DANCE... - Slayyyter</v>
+        <v>demons - Josiah Queen</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>welcome to the circus</v>
+        <v>Everyone Wants To Feel Like You Do</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/welcome-to-the-circus/1861011604</v>
+        <v>https://music.apple.com/us/song/everyone-wants-to-feel-like-you-do/1841949027</v>
       </c>
       <c r="D190" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E190" t="str">
-        <v>welcome to the circus - Single</v>
+        <v>Valentine</v>
       </c>
       <c r="F190" t="str">
-        <v>2:29</v>
+        <v>4:03</v>
       </c>
       <c r="G190" t="str">
-        <v>Jagwar Twin</v>
+        <v>Courtney Marie Andrews</v>
       </c>
       <c r="H190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I190" t="str">
-        <v>https://music.apple.com/us/artist/jagwar-twin/1429051937</v>
+        <v>https://music.apple.com/us/artist/courtney-marie-andrews/287157006</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/album/welcome-to-the-circus/1861011603</v>
+        <v>https://music.apple.com/us/album/everyone-wants-to-feel-like-you-do/1841948802</v>
       </c>
       <c r="K190" t="str">
-        <v>welcome to the circus - Jagwar Twin</v>
+        <v>Everyone Wants To Feel Like You Do - Courtney Marie Andrews</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>playlist</v>
+        <v>Nothing Comes Easy</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/playlist/1859009927</v>
+        <v>https://music.apple.com/us/song/nothing-comes-easy/1862757046</v>
       </c>
       <c r="D191" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E191" t="str">
-        <v>playlist - Single</v>
+        <v>Nothing Comes Easy - Single</v>
       </c>
       <c r="F191" t="str">
-        <v>2:44</v>
+        <v>2:54</v>
       </c>
       <c r="G191" t="str">
-        <v>Tenroc</v>
+        <v>Joy Oladokun</v>
       </c>
       <c r="H191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I191" t="str">
-        <v>https://music.apple.com/us/artist/tenroc/1711844910</v>
+        <v>https://music.apple.com/us/artist/joy-oladokun/699636664</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/album/playlist/1859009923</v>
+        <v>https://music.apple.com/us/album/nothing-comes-easy/1862756744</v>
       </c>
       <c r="K191" t="str">
-        <v>playlist - Tenroc</v>
+        <v>Nothing Comes Easy - Joy Oladokun</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Marlboro Man</v>
+        <v>Against the Dying of the Light</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/marlboro-man/1862008741</v>
+        <v>https://music.apple.com/us/song/against-the-dying-of-the-light/1860962165</v>
       </c>
       <c r="D192" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E192" t="str">
-        <v>Marlboro Man - Single</v>
+        <v>Against the Dying of the Light</v>
       </c>
       <c r="F192" t="str">
-        <v>3:23</v>
+        <v>2:28</v>
       </c>
       <c r="G192" t="str">
-        <v>Midland</v>
+        <v>José González</v>
       </c>
       <c r="H192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I192" t="str">
-        <v>https://music.apple.com/us/artist/midland/1171869852</v>
+        <v>https://music.apple.com/us/artist/jos%C3%A9-gonz%C3%A1lez/153417030</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/album/marlboro-man/1862008740</v>
+        <v>https://music.apple.com/us/album/against-the-dying-of-the-light/1860962162</v>
       </c>
       <c r="K192" t="str">
-        <v>Marlboro Man - Midland</v>
+        <v>Against the Dying of the Light - José González</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Enabling</v>
+        <v>Big Boy Problems</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/enabling/1860993048</v>
+        <v>https://music.apple.com/us/song/big-boy-problems/1851062438</v>
       </c>
       <c r="D193" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E193" t="str">
-        <v>Enabling - Single</v>
+        <v>Cynthia</v>
       </c>
       <c r="F193" t="str">
-        <v>3:18</v>
+        <v>2:30</v>
       </c>
       <c r="G193" t="str">
-        <v>Tenille Townes</v>
+        <v>Sydney Ross Mitchell</v>
       </c>
       <c r="H193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I193" t="str">
-        <v>https://music.apple.com/us/artist/tenille-townes/1367713770</v>
+        <v>https://music.apple.com/us/artist/sydney-ross-mitchell/1373996317</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/album/enabling/1860992859</v>
+        <v>https://music.apple.com/us/album/big-boy-problems/1851062193</v>
       </c>
       <c r="K193" t="str">
-        <v>Enabling - Tenille Townes</v>
+        <v>Big Boy Problems - Sydney Ross Mitchell</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Two Broken Hearts</v>
+        <v>Griever</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/two-broken-hearts/1841485428</v>
+        <v>https://music.apple.com/us/song/griever/1860950900</v>
       </c>
       <c r="D194" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E194" t="str">
-        <v>Steel Town</v>
+        <v>Griever - Single</v>
       </c>
       <c r="F194" t="str">
-        <v>3:53</v>
+        <v>2:31</v>
       </c>
       <c r="G194" t="str">
-        <v>Morgan Evans</v>
+        <v>Avery Cochrane</v>
       </c>
       <c r="H194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I194" t="str">
-        <v>https://music.apple.com/us/artist/morgan-evans/262665075</v>
+        <v>https://music.apple.com/us/artist/avery-cochrane/1556978969</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/album/two-broken-hearts/1841484758</v>
+        <v>https://music.apple.com/us/album/griever/1860950897</v>
       </c>
       <c r="K194" t="str">
-        <v>Two Broken Hearts - Morgan Evans</v>
+        <v>Griever - Avery Cochrane</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Lost in My Bed</v>
+        <v>7 BESOS</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/lost-in-my-bed/1862222274</v>
+        <v>https://music.apple.com/us/song/7-besos/1862927855</v>
       </c>
       <c r="D195" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E195" t="str">
-        <v>Lost in My Bed - Single</v>
+        <v>7 BESOS - Single</v>
       </c>
       <c r="F195" t="str">
-        <v>3:46</v>
+        <v>3:21</v>
       </c>
       <c r="G195" t="str">
-        <v>Khalil</v>
+        <v>LEGADO 7</v>
       </c>
       <c r="H195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I195" t="str">
-        <v>https://music.apple.com/us/artist/khalil/1223181975</v>
+        <v>https://music.apple.com/us/artist/legado-7/997011422</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/album/lost-in-my-bed/1862222272</v>
+        <v>https://music.apple.com/us/album/7-besos/1862927851</v>
       </c>
       <c r="K195" t="str">
-        <v>Lost in My Bed - Khalil</v>
+        <v>7 BESOS - LEGADO 7</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Father Time</v>
+        <v>UN LEÑO</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/father-time/1858611581</v>
+        <v>https://music.apple.com/us/song/un-le%C3%B1o/1862904727</v>
       </c>
       <c r="D196" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E196" t="str">
-        <v>Honey Water</v>
+        <v>UN LEÑO - Single</v>
       </c>
       <c r="F196" t="str">
-        <v>1:58</v>
+        <v>3:00</v>
       </c>
       <c r="G196" t="str">
-        <v>Girlfriend</v>
+        <v>Armenta</v>
       </c>
       <c r="H196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I196" t="str">
-        <v>https://music.apple.com/us/artist/girlfriend/1511096374</v>
+        <v>https://music.apple.com/us/artist/armenta/1479504876</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/album/father-time/1858611265</v>
+        <v>https://music.apple.com/us/album/un-le%C3%B1o/1862904402</v>
       </c>
       <c r="K196" t="str">
-        <v>Father Time - Girlfriend</v>
+        <v>UN LEÑO - Armenta</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>MVLAN</v>
+        <v>Queen's Goodbye</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/mvlan/1867584574</v>
+        <v>https://music.apple.com/us/song/queens-goodbye/1858554528</v>
       </c>
       <c r="D197" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E197" t="str">
-        <v>MVLAN - Single</v>
+        <v>Mārara</v>
       </c>
       <c r="F197" t="str">
-        <v>3:41</v>
+        <v>3:46</v>
       </c>
       <c r="G197" t="str">
-        <v>YOVNGCHIMI</v>
+        <v>15 15</v>
       </c>
       <c r="H197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I197" t="str">
-        <v>https://music.apple.com/us/artist/yovngchimi/1558257759</v>
+        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/album/mvlan/1867584573</v>
+        <v>https://music.apple.com/us/album/queens-goodbye/1858554036</v>
       </c>
       <c r="K197" t="str">
-        <v>MVLAN - YOVNGCHIMI</v>
+        <v>Queen's Goodbye - 15 15</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Name In Blood</v>
+        <v>Bring Me Back To Life</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/name-in-blood/1859687600</v>
+        <v>https://music.apple.com/us/song/bring-me-back-to-life/1851634795</v>
       </c>
       <c r="D198" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E198" t="str">
-        <v>Engines of Demolition</v>
+        <v>Melancholia - EP</v>
       </c>
       <c r="F198" t="str">
-        <v>4:36</v>
+        <v>3:24</v>
       </c>
       <c r="G198" t="str">
-        <v>Black Label Society</v>
+        <v>JELISA</v>
       </c>
       <c r="H198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I198" t="str">
-        <v>https://music.apple.com/us/artist/black-label-society/2778807</v>
+        <v>https://music.apple.com/us/artist/jelisa/1588318671</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/album/name-in-blood/1859687597</v>
+        <v>https://music.apple.com/us/album/bring-me-back-to-life/1851634783</v>
       </c>
       <c r="K198" t="str">
-        <v>Name In Blood - Black Label Society</v>
+        <v>Bring Me Back To Life - JELISA</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Eyeball</v>
+        <v>I Don't Care</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/eyeball/1862539350</v>
+        <v>https://music.apple.com/us/song/i-dont-care/1868429644</v>
       </c>
       <c r="D199" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E199" t="str">
-        <v>Eyeball - EP</v>
+        <v>I Don't Care - Single</v>
       </c>
       <c r="F199" t="str">
-        <v>2:14</v>
+        <v>3:49</v>
       </c>
       <c r="G199" t="str">
-        <v>They Might Be Giants</v>
+        <v>Buffalo Traffic Jam</v>
       </c>
       <c r="H199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I199" t="str">
-        <v>https://music.apple.com/us/artist/they-might-be-giants/149020</v>
+        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/album/eyeball/1862539346</v>
+        <v>https://music.apple.com/us/album/i-dont-care/1868429639</v>
       </c>
       <c r="K199" t="str">
-        <v>Eyeball - They Might Be Giants</v>
+        <v>I Don't Care - Buffalo Traffic Jam</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Long Gone</v>
+        <v>Elastico (feat. KATE LINN)</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/long-gone/1847573926</v>
+        <v>https://music.apple.com/us/song/elastico-feat-kate-linn/1862157500</v>
       </c>
       <c r="D200" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E200" t="str">
-        <v>Tenterhooks</v>
+        <v>Elastico (feat. KATE LINN) - Single</v>
       </c>
       <c r="F200" t="str">
-        <v>3:55</v>
+        <v>3:20</v>
       </c>
       <c r="G200" t="str">
-        <v>Silversun Pickups</v>
+        <v>Fantomel</v>
       </c>
       <c r="H200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I200" t="str">
-        <v>https://music.apple.com/us/artist/silversun-pickups/74752665</v>
+        <v>https://music.apple.com/us/artist/fantomel/1736085960</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/album/long-gone/1847573918</v>
+        <v>https://music.apple.com/us/album/elastico-feat-kate-linn/1862157496</v>
       </c>
       <c r="K200" t="str">
-        <v>Long Gone - Silversun Pickups</v>
+        <v>Elastico (feat. KATE LINN) - Fantomel</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>iloveitiloveitiloveit</v>
+        <v>Black &amp; Gold</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/iloveitiloveitiloveit/1867034427</v>
+        <v>https://music.apple.com/us/song/black-gold/1853914794</v>
       </c>
       <c r="D201" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E201" t="str">
-        <v>iloveitiloveitiloveit - Single</v>
+        <v>Black &amp; Gold - Single</v>
       </c>
       <c r="F201" t="str">
-        <v>3:03</v>
+        <v>3:12</v>
       </c>
       <c r="G201" t="str">
-        <v>Bella Kay</v>
+        <v>Claptone</v>
       </c>
       <c r="H201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I201" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/claptone/470488523</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/album/iloveitiloveitiloveit/1867034426</v>
+        <v>https://music.apple.com/us/album/black-gold/1853914793</v>
       </c>
       <c r="K201" t="str">
-        <v>iloveitiloveitiloveit - Bella Kay</v>
+        <v>Black &amp; Gold - Claptone</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>To The Edge</v>
+        <v>Close Your Eyes</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/to-the-edge/1863513891</v>
+        <v>https://music.apple.com/us/song/close-your-eyes/1860632907</v>
       </c>
       <c r="D202" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E202" t="str">
-        <v>To The Edge - Single</v>
+        <v>Close Your Eyes - Single</v>
       </c>
       <c r="F202" t="str">
-        <v>3:19</v>
+        <v>3:33</v>
       </c>
       <c r="G202" t="str">
-        <v>Alex Jude</v>
+        <v>Adam Beyer</v>
       </c>
       <c r="H202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I202" t="str">
-        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
+        <v>https://music.apple.com/us/artist/adam-beyer/101672291</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/album/to-the-edge/1863513887</v>
+        <v>https://music.apple.com/us/album/close-your-eyes/1860632569</v>
       </c>
       <c r="K202" t="str">
-        <v>To The Edge - Alex Jude</v>
+        <v>Close Your Eyes - Adam Beyer</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>demons</v>
+        <v>Movement</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/demons/1861978106</v>
+        <v>https://music.apple.com/us/song/movement/1867063797</v>
       </c>
       <c r="D203" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E203" t="str">
-        <v>demons - Single</v>
+        <v>Movement - Single</v>
       </c>
       <c r="F203" t="str">
-        <v>3:10</v>
+        <v>3:07</v>
       </c>
       <c r="G203" t="str">
-        <v>Josiah Queen</v>
+        <v>Crankdat</v>
       </c>
       <c r="H203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I203" t="str">
-        <v>https://music.apple.com/us/artist/josiah-queen/1498117530</v>
+        <v>https://music.apple.com/us/artist/crankdat/1073027547</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/album/demons/1861978105</v>
+        <v>https://music.apple.com/us/album/movement/1867063796</v>
       </c>
       <c r="K203" t="str">
-        <v>demons - Josiah Queen</v>
+        <v>Movement - Crankdat</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Everyone Wants To Feel Like You Do</v>
+        <v>Ayi Giri</v>
       </c>
       <c r="B204" t="str">
         <v/>
       </c>
       <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/everyone-wants-to-feel-like-you-do/1841949027</v>
+        <v>https://music.apple.com/us/song/ayi-giri/1867306651</v>
       </c>
       <c r="D204" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E204" t="str">
-        <v>Valentine</v>
+        <v>Ayi Giri / Dopamine Machine - Single</v>
       </c>
       <c r="F204" t="str">
-        <v>4:03</v>
+        <v>3:06</v>
       </c>
       <c r="G204" t="str">
-        <v>Courtney Marie Andrews</v>
+        <v>Lilly Palmer</v>
       </c>
       <c r="H204" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I204" t="str">
-        <v>https://music.apple.com/us/artist/courtney-marie-andrews/287157006</v>
+        <v>https://music.apple.com/us/artist/lilly-palmer/340777023</v>
       </c>
       <c r="J204" t="str">
-        <v>https://music.apple.com/us/album/everyone-wants-to-feel-like-you-do/1841948802</v>
+        <v>https://music.apple.com/us/album/ayi-giri/1867306650</v>
       </c>
       <c r="K204" t="str">
-        <v>Everyone Wants To Feel Like You Do - Courtney Marie Andrews</v>
+        <v>Ayi Giri - Lilly Palmer</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Nothing Comes Easy</v>
+        <v>It's A Sin</v>
       </c>
       <c r="B205" t="str">
         <v/>
       </c>
       <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/nothing-comes-easy/1862757046</v>
+        <v>https://music.apple.com/us/song/its-a-sin/1861930282</v>
       </c>
       <c r="D205" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E205" t="str">
-        <v>Nothing Comes Easy - Single</v>
+        <v>It's A Sin - Single</v>
       </c>
       <c r="F205" t="str">
-        <v>2:54</v>
+        <v>4:40</v>
       </c>
       <c r="G205" t="str">
-        <v>Joy Oladokun</v>
+        <v>Ghost</v>
       </c>
       <c r="H205" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I205" t="str">
-        <v>https://music.apple.com/us/artist/joy-oladokun/699636664</v>
+        <v>https://music.apple.com/us/artist/ghost/600730426</v>
       </c>
       <c r="J205" t="str">
-        <v>https://music.apple.com/us/album/nothing-comes-easy/1862756744</v>
+        <v>https://music.apple.com/us/album/its-a-sin/1861930280</v>
       </c>
       <c r="K205" t="str">
-        <v>Nothing Comes Easy - Joy Oladokun</v>
+        <v>It's A Sin - Ghost</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Against the Dying of the Light</v>
+        <v>Krushers Of The World</v>
       </c>
       <c r="B206" t="str">
         <v/>
       </c>
       <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/against-the-dying-of-the-light/1860962165</v>
+        <v>https://music.apple.com/us/song/krushers-of-the-world/1837718526</v>
       </c>
       <c r="D206" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E206" t="str">
-        <v>Against the Dying of the Light</v>
+        <v>Krushers Of The World</v>
       </c>
       <c r="F206" t="str">
-        <v>2:28</v>
+        <v>4:20</v>
       </c>
       <c r="G206" t="str">
-        <v>José González</v>
+        <v>Kreator</v>
       </c>
       <c r="H206" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I206" t="str">
-        <v>https://music.apple.com/us/artist/jos%C3%A9-gonz%C3%A1lez/153417030</v>
+        <v>https://music.apple.com/us/artist/kreator/3258504</v>
       </c>
       <c r="J206" t="str">
-        <v>https://music.apple.com/us/album/against-the-dying-of-the-light/1860962162</v>
+        <v>https://music.apple.com/us/album/krushers-of-the-world/1837718517</v>
       </c>
       <c r="K206" t="str">
-        <v>Against the Dying of the Light - José González</v>
+        <v>Krushers Of The World - Kreator</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Big Boy Problems</v>
+        <v>Thoroughbreds</v>
       </c>
       <c r="B207" t="str">
         <v/>
       </c>
       <c r="C207" t="str">
-        <v>https://music.apple.com/us/song/big-boy-problems/1851062438</v>
+        <v>https://music.apple.com/us/song/thoroughbreds/1863532917</v>
       </c>
       <c r="D207" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E207" t="str">
-        <v>Cynthia</v>
+        <v>Peace In Place</v>
       </c>
       <c r="F207" t="str">
-        <v>2:30</v>
+        <v>3:24</v>
       </c>
       <c r="G207" t="str">
-        <v>Sydney Ross Mitchell</v>
+        <v>Poison the Well</v>
       </c>
       <c r="H207" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I207" t="str">
-        <v>https://music.apple.com/us/artist/sydney-ross-mitchell/1373996317</v>
+        <v>https://music.apple.com/us/artist/poison-the-well/1710155</v>
       </c>
       <c r="J207" t="str">
-        <v>https://music.apple.com/us/album/big-boy-problems/1851062193</v>
+        <v>https://music.apple.com/us/album/thoroughbreds/1863532634</v>
       </c>
       <c r="K207" t="str">
-        <v>Big Boy Problems - Sydney Ross Mitchell</v>
+        <v>Thoroughbreds - Poison the Well</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Griever</v>
+        <v>Adversary</v>
       </c>
       <c r="B208" t="str">
         <v/>
       </c>
       <c r="C208" t="str">
-        <v>https://music.apple.com/us/song/griever/1860950900</v>
+        <v>https://music.apple.com/us/song/adversary/1861901940</v>
       </c>
       <c r="D208" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="E208" t="str">
-        <v>Griever - Single</v>
+        <v>Descent</v>
       </c>
       <c r="F208" t="str">
-        <v>2:31</v>
+        <v>3:17</v>
       </c>
       <c r="G208" t="str">
-        <v>Avery Cochrane</v>
+        <v>Immolation</v>
       </c>
       <c r="H208" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="I208" t="str">
-        <v>https://music.apple.com/us/artist/avery-cochrane/1556978969</v>
+        <v>https://music.apple.com/us/artist/immolation/64874488</v>
       </c>
       <c r="J208" t="str">
-        <v>https://music.apple.com/us/album/griever/1860950897</v>
+        <v>https://music.apple.com/us/album/adversary/1861901597</v>
       </c>
       <c r="K208" t="str">
-        <v>Griever - Avery Cochrane</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="str">
-        <v>7 BESOS</v>
-      </c>
-      <c r="B209" t="str">
-        <v/>
-      </c>
-      <c r="C209" t="str">
-        <v>https://music.apple.com/us/song/7-besos/1862927855</v>
-      </c>
-      <c r="D209" t="str">
-        <v>2026-01-22</v>
-      </c>
-      <c r="E209" t="str">
-        <v>7 BESOS - Single</v>
-      </c>
-      <c r="F209" t="str">
-        <v>3:21</v>
-      </c>
-      <c r="G209" t="str">
-        <v>LEGADO 7</v>
-      </c>
-      <c r="H209" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="I209" t="str">
-        <v>https://music.apple.com/us/artist/legado-7/997011422</v>
-      </c>
-      <c r="J209" t="str">
-        <v>https://music.apple.com/us/album/7-besos/1862927851</v>
-      </c>
-      <c r="K209" t="str">
-        <v>7 BESOS - LEGADO 7</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="str">
-        <v>UN LEÑO</v>
-      </c>
-      <c r="B210" t="str">
-        <v/>
-      </c>
-      <c r="C210" t="str">
-        <v>https://music.apple.com/us/song/un-le%C3%B1o/1862904727</v>
-      </c>
-      <c r="D210" t="str">
-        <v>2026-01-22</v>
-      </c>
-      <c r="E210" t="str">
-        <v>UN LEÑO - Single</v>
-      </c>
-      <c r="F210" t="str">
-        <v>3:00</v>
-      </c>
-      <c r="G210" t="str">
-        <v>Armenta</v>
-      </c>
-      <c r="H210" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="I210" t="str">
-        <v>https://music.apple.com/us/artist/armenta/1479504876</v>
-      </c>
-      <c r="J210" t="str">
-        <v>https://music.apple.com/us/album/un-le%C3%B1o/1862904402</v>
-      </c>
-      <c r="K210" t="str">
-        <v>UN LEÑO - Armenta</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="str">
-        <v>Queen's Goodbye</v>
-      </c>
-      <c r="B211" t="str">
-        <v/>
-      </c>
-      <c r="C211" t="str">
-        <v>https://music.apple.com/us/song/queens-goodbye/1858554528</v>
-      </c>
-      <c r="D211" t="str">
-        <v>2026-01-22</v>
-      </c>
-      <c r="E211" t="str">
-        <v>Mārara</v>
-      </c>
-      <c r="F211" t="str">
-        <v>3:46</v>
-      </c>
-      <c r="G211" t="str">
-        <v>15 15</v>
-      </c>
-      <c r="H211" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="I211" t="str">
-        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
-      </c>
-      <c r="J211" t="str">
-        <v>https://music.apple.com/us/album/queens-goodbye/1858554036</v>
-      </c>
-      <c r="K211" t="str">
-        <v>Queen's Goodbye - 15 15</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="str">
-        <v>Bring Me Back To Life</v>
-      </c>
-      <c r="B212" t="str">
-        <v/>
-      </c>
-      <c r="C212" t="str">
-        <v>https://music.apple.com/us/song/bring-me-back-to-life/1851634795</v>
-      </c>
-      <c r="D212" t="str">
-        <v>2026-01-22</v>
-      </c>
-      <c r="E212" t="str">
-        <v>Melancholia - EP</v>
-      </c>
-      <c r="F212" t="str">
-        <v>3:24</v>
-      </c>
-      <c r="G212" t="str">
-        <v>JELISA</v>
-      </c>
-      <c r="H212" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="I212" t="str">
-        <v>https://music.apple.com/us/artist/jelisa/1588318671</v>
-      </c>
-      <c r="J212" t="str">
-        <v>https://music.apple.com/us/album/bring-me-back-to-life/1851634783</v>
-      </c>
-      <c r="K212" t="str">
-        <v>Bring Me Back To Life - JELISA</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="str">
-        <v>I Don't Care</v>
-      </c>
-      <c r="B213" t="str">
-        <v/>
-      </c>
-      <c r="C213" t="str">
-        <v>https://music.apple.com/us/song/i-dont-care/1868429644</v>
-      </c>
-      <c r="D213" t="str">
-        <v>2026-01-22</v>
-      </c>
-      <c r="E213" t="str">
-        <v>I Don't Care - Single</v>
-      </c>
-      <c r="F213" t="str">
-        <v>3:49</v>
-      </c>
-      <c r="G213" t="str">
-        <v>Buffalo Traffic Jam</v>
-      </c>
-      <c r="H213" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="I213" t="str">
-        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
-      </c>
-      <c r="J213" t="str">
-        <v>https://music.apple.com/us/album/i-dont-care/1868429639</v>
-      </c>
-      <c r="K213" t="str">
-        <v>I Don't Care - Buffalo Traffic Jam</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="str">
-        <v>Elastico (feat. KATE LINN)</v>
-      </c>
-      <c r="B214" t="str">
-        <v/>
-      </c>
-      <c r="C214" t="str">
-        <v>https://music.apple.com/us/song/elastico-feat-kate-linn/1862157500</v>
-      </c>
-      <c r="D214" t="str">
-        <v>2026-01-22</v>
-      </c>
-      <c r="E214" t="str">
-        <v>Elastico (feat. KATE LINN) - Single</v>
-      </c>
-      <c r="F214" t="str">
-        <v>3:20</v>
-      </c>
-      <c r="G214" t="str">
-        <v>Fantomel</v>
-      </c>
-      <c r="H214" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="I214" t="str">
-        <v>https://music.apple.com/us/artist/fantomel/1736085960</v>
-      </c>
-      <c r="J214" t="str">
-        <v>https://music.apple.com/us/album/elastico-feat-kate-linn/1862157496</v>
-      </c>
-      <c r="K214" t="str">
-        <v>Elastico (feat. KATE LINN) - Fantomel</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="str">
-        <v>Black &amp; Gold</v>
-      </c>
-      <c r="B215" t="str">
-        <v/>
-      </c>
-      <c r="C215" t="str">
-        <v>https://music.apple.com/us/song/black-gold/1853914794</v>
-      </c>
-      <c r="D215" t="str">
-        <v>2026-01-22</v>
-      </c>
-      <c r="E215" t="str">
-        <v>Black &amp; Gold - Single</v>
-      </c>
-      <c r="F215" t="str">
-        <v>3:12</v>
-      </c>
-      <c r="G215" t="str">
-        <v>Claptone</v>
-      </c>
-      <c r="H215" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="I215" t="str">
-        <v>https://music.apple.com/us/artist/claptone/470488523</v>
-      </c>
-      <c r="J215" t="str">
-        <v>https://music.apple.com/us/album/black-gold/1853914793</v>
-      </c>
-      <c r="K215" t="str">
-        <v>Black &amp; Gold - Claptone</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="str">
-        <v>Close Your Eyes</v>
-      </c>
-      <c r="B216" t="str">
-        <v/>
-      </c>
-      <c r="C216" t="str">
-        <v>https://music.apple.com/us/song/close-your-eyes/1860632907</v>
-      </c>
-      <c r="D216" t="str">
-        <v>2026-01-22</v>
-      </c>
-      <c r="E216" t="str">
-        <v>Close Your Eyes - Single</v>
-      </c>
-      <c r="F216" t="str">
-        <v>3:33</v>
-      </c>
-      <c r="G216" t="str">
-        <v>Adam Beyer</v>
-      </c>
-      <c r="H216" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="I216" t="str">
-        <v>https://music.apple.com/us/artist/adam-beyer/101672291</v>
-      </c>
-      <c r="J216" t="str">
-        <v>https://music.apple.com/us/album/close-your-eyes/1860632569</v>
-      </c>
-      <c r="K216" t="str">
-        <v>Close Your Eyes - Adam Beyer</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="str">
-        <v>Movement</v>
-      </c>
-      <c r="B217" t="str">
-        <v/>
-      </c>
-      <c r="C217" t="str">
-        <v>https://music.apple.com/us/song/movement/1867063797</v>
-      </c>
-      <c r="D217" t="str">
-        <v>2026-01-22</v>
-      </c>
-      <c r="E217" t="str">
-        <v>Movement - Single</v>
-      </c>
-      <c r="F217" t="str">
-        <v>3:07</v>
-      </c>
-      <c r="G217" t="str">
-        <v>Crankdat</v>
-      </c>
-      <c r="H217" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="I217" t="str">
-        <v>https://music.apple.com/us/artist/crankdat/1073027547</v>
-      </c>
-      <c r="J217" t="str">
-        <v>https://music.apple.com/us/album/movement/1867063796</v>
-      </c>
-      <c r="K217" t="str">
-        <v>Movement - Crankdat</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="str">
-        <v>Ayi Giri</v>
-      </c>
-      <c r="B218" t="str">
-        <v/>
-      </c>
-      <c r="C218" t="str">
-        <v>https://music.apple.com/us/song/ayi-giri/1867306651</v>
-      </c>
-      <c r="D218" t="str">
-        <v>2026-01-22</v>
-      </c>
-      <c r="E218" t="str">
-        <v>Ayi Giri / Dopamine Machine - Single</v>
-      </c>
-      <c r="F218" t="str">
-        <v>3:06</v>
-      </c>
-      <c r="G218" t="str">
-        <v>Lilly Palmer</v>
-      </c>
-      <c r="H218" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="I218" t="str">
-        <v>https://music.apple.com/us/artist/lilly-palmer/340777023</v>
-      </c>
-      <c r="J218" t="str">
-        <v>https://music.apple.com/us/album/ayi-giri/1867306650</v>
-      </c>
-      <c r="K218" t="str">
-        <v>Ayi Giri - Lilly Palmer</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="str">
-        <v>It's A Sin</v>
-      </c>
-      <c r="B219" t="str">
-        <v/>
-      </c>
-      <c r="C219" t="str">
-        <v>https://music.apple.com/us/song/its-a-sin/1861930282</v>
-      </c>
-      <c r="D219" t="str">
-        <v>2026-01-22</v>
-      </c>
-      <c r="E219" t="str">
-        <v>It's A Sin - Single</v>
-      </c>
-      <c r="F219" t="str">
-        <v>4:40</v>
-      </c>
-      <c r="G219" t="str">
-        <v>Ghost</v>
-      </c>
-      <c r="H219" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="I219" t="str">
-        <v>https://music.apple.com/us/artist/ghost/600730426</v>
-      </c>
-      <c r="J219" t="str">
-        <v>https://music.apple.com/us/album/its-a-sin/1861930280</v>
-      </c>
-      <c r="K219" t="str">
-        <v>It's A Sin - Ghost</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="str">
-        <v>Krushers Of The World</v>
-      </c>
-      <c r="B220" t="str">
-        <v/>
-      </c>
-      <c r="C220" t="str">
-        <v>https://music.apple.com/us/song/krushers-of-the-world/1837718526</v>
-      </c>
-      <c r="D220" t="str">
-        <v>2026-01-22</v>
-      </c>
-      <c r="E220" t="str">
-        <v>Krushers Of The World</v>
-      </c>
-      <c r="F220" t="str">
-        <v>4:20</v>
-      </c>
-      <c r="G220" t="str">
-        <v>Kreator</v>
-      </c>
-      <c r="H220" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="I220" t="str">
-        <v>https://music.apple.com/us/artist/kreator/3258504</v>
-      </c>
-      <c r="J220" t="str">
-        <v>https://music.apple.com/us/album/krushers-of-the-world/1837718517</v>
-      </c>
-      <c r="K220" t="str">
-        <v>Krushers Of The World - Kreator</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="str">
-        <v>Thoroughbreds</v>
-      </c>
-      <c r="B221" t="str">
-        <v/>
-      </c>
-      <c r="C221" t="str">
-        <v>https://music.apple.com/us/song/thoroughbreds/1863532917</v>
-      </c>
-      <c r="D221" t="str">
-        <v>2026-01-22</v>
-      </c>
-      <c r="E221" t="str">
-        <v>Peace In Place</v>
-      </c>
-      <c r="F221" t="str">
-        <v>3:24</v>
-      </c>
-      <c r="G221" t="str">
-        <v>Poison the Well</v>
-      </c>
-      <c r="H221" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="I221" t="str">
-        <v>https://music.apple.com/us/artist/poison-the-well/1710155</v>
-      </c>
-      <c r="J221" t="str">
-        <v>https://music.apple.com/us/album/thoroughbreds/1863532634</v>
-      </c>
-      <c r="K221" t="str">
-        <v>Thoroughbreds - Poison the Well</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="str">
-        <v>Adversary</v>
-      </c>
-      <c r="B222" t="str">
-        <v/>
-      </c>
-      <c r="C222" t="str">
-        <v>https://music.apple.com/us/song/adversary/1861901940</v>
-      </c>
-      <c r="D222" t="str">
-        <v>2026-01-22</v>
-      </c>
-      <c r="E222" t="str">
-        <v>Descent</v>
-      </c>
-      <c r="F222" t="str">
-        <v>3:17</v>
-      </c>
-      <c r="G222" t="str">
-        <v>Immolation</v>
-      </c>
-      <c r="H222" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="I222" t="str">
-        <v>https://music.apple.com/us/artist/immolation/64874488</v>
-      </c>
-      <c r="J222" t="str">
-        <v>https://music.apple.com/us/album/adversary/1861901597</v>
-      </c>
-      <c r="K222" t="str">
         <v>Adversary - Immolation</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K222"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K208"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-01-week04/titles.xlsx
+++ b/data/global/2026-01-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L208"/>
+  <dimension ref="A1:L209"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -439,19 +439,19 @@
         <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>6 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>6 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>2:59</v>
@@ -477,19 +477,19 @@
         <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>12 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>12 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:21</v>
@@ -521,7 +521,7 @@
         <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -857,19 +857,19 @@
         <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B13" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>3:57</v>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1541,19 +1541,19 @@
         <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>2:31</v>
@@ -1585,7 +1585,7 @@
         <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1731,19 +1731,19 @@
         <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B36" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>3:31</v>
@@ -1775,7 +1775,7 @@
         <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=R2k_wPsAHKQ</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=gWyaiGAFVO8</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=jwQKcW474Tc</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=3N7iKwqENP0</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=sKG5ZIzCnFQ</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=Koj30I91_8k</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=xZdWEmnRK4g</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=wo9yPPCh75Q</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=ND6maRwmzHk</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=9jMMOYr-VhE</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=o2F-QmqdNtI</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=5-6cEVLqE90</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=ivPSbcEMwCs</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=tYpOHbXFnm0</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=rSO9oYUnO2k</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=c231tCsQalU</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=oaJKUCgSSkc</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=0Gxu80LxI0w</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=7sjshHJwkOE</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=yv1c5G5HZt8</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=EXVg23U3NRw</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=Bpb67fSUzEQ</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=gkwb6kZloLA</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=Jckb3dnS5fw</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=DPA8v4YS8AY</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=v8Yu21pEbqw</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=sq2u9Cfn2B8</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=Ea2DSMNIK5w</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=kCIf6yaJisQ</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=f1Iqm16vWDQ</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=4eqzUNO-ONs</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=oi4aTOc-IX4</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=LPXTE3a6QrM</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4236,40 +4236,40 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Opening Night</v>
+        <v>Aperture</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/opening-night/1870313501</v>
+        <v>https://music.apple.com/us/song/aperture/1870984033</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E102" t="str">
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>HELP(2)</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G102" t="str">
-        <v>4:19</v>
+        <v>5:11</v>
       </c>
       <c r="H102" t="str">
-        <v>Arctic Monkeys</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/arctic-monkeys/62820413</v>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/opening-night/1870313498</v>
+        <v>https://music.apple.com/us/album/aperture/1870984032</v>
       </c>
       <c r="L102" t="str">
-        <v>Opening Night - Arctic Monkeys</v>
+        <v>Aperture - Harry Styles</v>
       </c>
     </row>
     <row r="103">
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/wish-i-didnt/1851297073</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/air-force-black-demarco/1862935169</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/wall-of-sound/1852566426</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/wheres-my-phone/1860622553</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/100/1858754874</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/por-un-p-o-no-se-llora-salud-mi-reina/1862587826</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4502,40 +4502,40 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Flo Jackson</v>
+        <v>Opening Night</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
+        <v>https://music.apple.com/us/song/opening-night/1870313501</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E109" t="str">
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Flo Jackson - Single</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G109" t="str">
-        <v>2:23</v>
+        <v>4:19</v>
       </c>
       <c r="H109" t="str">
-        <v>Flo Milli</v>
+        <v>Arctic Monkeys</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
+        <v>https://music.apple.com/us/artist/arctic-monkeys/62820413</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
+        <v>https://music.apple.com/us/album/opening-night/1870313498</v>
       </c>
       <c r="L109" t="str">
-        <v>Flo Jackson - Flo Milli</v>
+        <v>Opening Night - Arctic Monkeys</v>
       </c>
     </row>
     <row r="110">
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/l-u-c-k-y/1861895147</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/reclusive/1860405760</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4616,78 +4616,78 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Site Unseen (feat. Waxahatchee)</v>
+        <v>Flo Jackson</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
+        <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E112" t="str">
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Creature of Habit</v>
+        <v>Flo Jackson - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>2:46</v>
+        <v>2:23</v>
       </c>
       <c r="H112" t="str">
-        <v>Courtney Barnett</v>
+        <v>Flo Milli</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
+        <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
       </c>
       <c r="L112" t="str">
-        <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
+        <v>Flo Jackson - Flo Milli</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Puppet Parade</v>
+        <v>Site Unseen (feat. Waxahatchee)</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
+        <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E113" t="str">
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Megadeth</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G113" t="str">
-        <v>4:40</v>
+        <v>2:46</v>
       </c>
       <c r="H113" t="str">
-        <v>Megadeth</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/megadeth/488289</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
+        <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
       </c>
       <c r="L113" t="str">
-        <v>Puppet Parade - Megadeth</v>
+        <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
       </c>
     </row>
     <row r="114">
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/raft-in-the-sea/1847662987</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/good-night-baby/1849917462</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4768,3541 +4768,3579 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>CAMBIARÉ</v>
+        <v>Puppet Parade</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
+        <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E116" t="str">
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>CAMBIARÉ - Single</v>
+        <v>Megadeth</v>
       </c>
       <c r="G116" t="str">
-        <v>3:01</v>
+        <v>4:40</v>
       </c>
       <c r="H116" t="str">
-        <v>Luis Fonsi</v>
+        <v>Megadeth</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/luis-fonsi/102834</v>
+        <v>https://music.apple.com/us/artist/megadeth/488289</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/cambiar%C3%A9/1867545265</v>
+        <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
       </c>
       <c r="L116" t="str">
-        <v>CAMBIARÉ - Luis Fonsi</v>
+        <v>Puppet Parade - Megadeth</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Orange County (feat. Bizarrap, Kara Jackson &amp; Anoushka Shankar)</v>
+        <v>CAMBIARÉ</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/orange-county-feat-bizarrap-kara-jackson-anoushka-shankar/1837237867</v>
+        <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E117" t="str">
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>The Mountain</v>
+        <v>CAMBIARÉ - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:28</v>
+        <v>3:01</v>
       </c>
       <c r="H117" t="str">
-        <v>Gorillaz</v>
+        <v>Luis Fonsi</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/gorillaz/567072</v>
+        <v>https://music.apple.com/us/artist/luis-fonsi/102834</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/orange-county-feat-bizarrap-kara-jackson-anoushka-shankar/1837237742</v>
+        <v>https://music.apple.com/us/album/cambiar%C3%A9/1867545265</v>
       </c>
       <c r="L117" t="str">
-        <v>Orange County (feat. Bizarrap, Kara Jackson &amp; Anoushka Shankar) - Gorillaz</v>
+        <v>CAMBIARÉ - Luis Fonsi</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Lluvia</v>
+        <v>Orange County (feat. Bizarrap, Kara Jackson &amp; Anoushka Shankar)</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/lluvia/1868476403</v>
+        <v>https://music.apple.com/us/song/orange-county-feat-bizarrap-kara-jackson-anoushka-shankar/1837237867</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E118" t="str">
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>LA 8VA MARAVILLA</v>
+        <v>The Mountain</v>
       </c>
       <c r="G118" t="str">
-        <v>3:24</v>
+        <v>3:28</v>
       </c>
       <c r="H118" t="str">
-        <v>Arcángel</v>
+        <v>Gorillaz</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
+        <v>https://music.apple.com/us/artist/gorillaz/567072</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/lluvia/1868476390</v>
+        <v>https://music.apple.com/us/album/orange-county-feat-bizarrap-kara-jackson-anoushka-shankar/1837237742</v>
       </c>
       <c r="L118" t="str">
-        <v>Lluvia - Arcángel</v>
+        <v>Orange County (feat. Bizarrap, Kara Jackson &amp; Anoushka Shankar) - Gorillaz</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Knife</v>
+        <v>Lluvia</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/knife/1862720450</v>
+        <v>https://music.apple.com/us/song/lluvia/1868476403</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E119" t="str">
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>THE SIN : VANISH</v>
+        <v>LA 8VA MARAVILLA</v>
       </c>
       <c r="G119" t="str">
-        <v>2:19</v>
+        <v>3:24</v>
       </c>
       <c r="H119" t="str">
-        <v>ENHYPEN</v>
+        <v>Arcángel</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/enhypen/1541011620</v>
+        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/knife/1862720020</v>
+        <v>https://music.apple.com/us/album/lluvia/1868476390</v>
       </c>
       <c r="L119" t="str">
-        <v>Knife - ENHYPEN</v>
+        <v>Lluvia - Arcángel</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>bad enough</v>
+        <v>Knife</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/bad-enough/1846949125</v>
+        <v>https://music.apple.com/us/song/knife/1862720450</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E120" t="str">
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>locket</v>
+        <v>THE SIN : VANISH</v>
       </c>
       <c r="G120" t="str">
-        <v>3:42</v>
+        <v>2:19</v>
       </c>
       <c r="H120" t="str">
-        <v>Madison Beer</v>
+        <v>ENHYPEN</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/madison-beer/696146587</v>
+        <v>https://music.apple.com/us/artist/enhypen/1541011620</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/bad-enough/1846949115</v>
+        <v>https://music.apple.com/us/album/knife/1862720020</v>
       </c>
       <c r="L120" t="str">
-        <v>bad enough - Madison Beer</v>
+        <v>Knife - ENHYPEN</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>bad</v>
+        <v>bad enough</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/bad/1851566880</v>
+        <v>https://music.apple.com/us/song/bad-enough/1846949125</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E121" t="str">
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>bad - Single</v>
+        <v>locket</v>
       </c>
       <c r="G121" t="str">
-        <v>2:41</v>
+        <v>3:42</v>
       </c>
       <c r="H121" t="str">
-        <v>Saint Harison</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
+        <v>https://music.apple.com/us/artist/madison-beer/696146587</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/bad/1851566879</v>
+        <v>https://music.apple.com/us/album/bad-enough/1846949115</v>
       </c>
       <c r="L121" t="str">
-        <v>bad - Saint Harison</v>
+        <v>bad enough - Madison Beer</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Beat Yourself Up</v>
+        <v>bad</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/beat-yourself-up/1845189973</v>
+        <v>https://music.apple.com/us/song/bad/1851566880</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E122" t="str">
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Whatever's Clever!</v>
+        <v>bad - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>2:58</v>
+        <v>2:41</v>
       </c>
       <c r="H122" t="str">
-        <v>Charlie Puth</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/beat-yourself-up/1845189970</v>
+        <v>https://music.apple.com/us/album/bad/1851566879</v>
       </c>
       <c r="L122" t="str">
-        <v>Beat Yourself Up - Charlie Puth</v>
+        <v>bad - Saint Harison</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Roommates</v>
+        <v>Beat Yourself Up</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/roommates/1854567105</v>
+        <v>https://music.apple.com/us/song/beat-yourself-up/1845189973</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E123" t="str">
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>luck... or something</v>
+        <v>Whatever's Clever!</v>
       </c>
       <c r="G123" t="str">
-        <v>2:52</v>
+        <v>2:58</v>
       </c>
       <c r="H123" t="str">
-        <v>Hilary Duff</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/hilary-duff/3296003</v>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/roommates/1854567102</v>
+        <v>https://music.apple.com/us/album/beat-yourself-up/1845189970</v>
       </c>
       <c r="L123" t="str">
-        <v>Roommates - Hilary Duff</v>
+        <v>Beat Yourself Up - Charlie Puth</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>2SIDED</v>
+        <v>Roommates</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/2sided/1862571197</v>
+        <v>https://music.apple.com/us/song/roommates/1854567105</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E124" t="str">
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Ambiguous Desire</v>
+        <v>luck... or something</v>
       </c>
       <c r="G124" t="str">
-        <v>2:57</v>
+        <v>2:52</v>
       </c>
       <c r="H124" t="str">
-        <v>Arlo Parks</v>
+        <v>Hilary Duff</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
+        <v>https://music.apple.com/us/artist/hilary-duff/3296003</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/2sided/1862570378</v>
+        <v>https://music.apple.com/us/album/roommates/1854567102</v>
       </c>
       <c r="L124" t="str">
-        <v>2SIDED - Arlo Parks</v>
+        <v>Roommates - Hilary Duff</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Feel Alive</v>
+        <v>2SIDED</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/feel-alive/1851368171</v>
+        <v>https://music.apple.com/us/song/2sided/1862571197</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E125" t="str">
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>ODYSSEY</v>
+        <v>Ambiguous Desire</v>
       </c>
       <c r="G125" t="str">
-        <v>2:48</v>
+        <v>2:57</v>
       </c>
       <c r="H125" t="str">
-        <v>ILLENIUM</v>
+        <v>Arlo Parks</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/illenium/645420096</v>
+        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/feel-alive/1851368154</v>
+        <v>https://music.apple.com/us/album/2sided/1862570378</v>
       </c>
       <c r="L125" t="str">
-        <v>Feel Alive - ILLENIUM</v>
+        <v>2SIDED - Arlo Parks</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>God Spoke</v>
+        <v>Feel Alive</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/god-spoke/1853069638</v>
+        <v>https://music.apple.com/us/song/feel-alive/1851368171</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E126" t="str">
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>COSMIC OPERA ACT I</v>
+        <v>ODYSSEY</v>
       </c>
       <c r="G126" t="str">
-        <v>1:14</v>
+        <v>2:48</v>
       </c>
       <c r="H126" t="str">
-        <v>Labrinth</v>
+        <v>ILLENIUM</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/god-spoke/1853069628</v>
+        <v>https://music.apple.com/us/album/feel-alive/1851368154</v>
       </c>
       <c r="L126" t="str">
-        <v>God Spoke - Labrinth</v>
+        <v>Feel Alive - ILLENIUM</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Risk Takers</v>
+        <v>God Spoke</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/risk-takers/1866642666</v>
+        <v>https://music.apple.com/us/song/god-spoke/1853069638</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E127" t="str">
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>El Mundo Es Tuyo (Inspired by Clika The Movie)</v>
+        <v>COSMIC OPERA ACT I</v>
       </c>
       <c r="G127" t="str">
-        <v>2:35</v>
+        <v>1:14</v>
       </c>
       <c r="H127" t="str">
-        <v>Herencia de Patrones</v>
+        <v>Labrinth</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/herencia-de-patrones/1295294734</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/risk-takers/1866642665</v>
+        <v>https://music.apple.com/us/album/god-spoke/1853069628</v>
       </c>
       <c r="L127" t="str">
-        <v>Risk Takers - Herencia de Patrones</v>
+        <v>God Spoke - Labrinth</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Never Comin' Back</v>
+        <v>Risk Takers</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/never-comin-back/1862970557</v>
+        <v>https://music.apple.com/us/song/risk-takers/1866642666</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E128" t="str">
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Never Comin' Back - Single</v>
+        <v>El Mundo Es Tuyo (Inspired by Clika The Movie)</v>
       </c>
       <c r="G128" t="str">
-        <v>3:57</v>
+        <v>2:35</v>
       </c>
       <c r="H128" t="str">
-        <v>Flatland Cavalry</v>
+        <v>Herencia de Patrones</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/herencia-de-patrones/1295294734</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/never-comin-back/1862970555</v>
+        <v>https://music.apple.com/us/album/risk-takers/1866642665</v>
       </c>
       <c r="L128" t="str">
-        <v>Never Comin' Back - Flatland Cavalry</v>
+        <v>Risk Takers - Herencia de Patrones</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Lay Your Heartache Onto Mine (Songs From and Inspired by the Paramount+ Original Series Landman (Volume II))</v>
+        <v>Never Comin' Back</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/lay-your-heartache-onto-mine-songs-from-and-inspired/1867273711</v>
+        <v>https://music.apple.com/us/song/never-comin-back/1862970557</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E129" t="str">
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Lay Your Heartache Onto Mine (Songs From and Inspired by the Paramount+ Original Series Landman (Volume II)) - Single</v>
+        <v>Never Comin' Back - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:18</v>
+        <v>3:57</v>
       </c>
       <c r="H129" t="str">
-        <v>Carter Faith</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/carter-faith/1489205896</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/lay-your-heartache-onto-mine-songs-from-and-inspired/1867273471</v>
+        <v>https://music.apple.com/us/album/never-comin-back/1862970555</v>
       </c>
       <c r="L129" t="str">
-        <v>Lay Your Heartache Onto Mine (Songs From and Inspired by the Paramount+ Original Series Landman (Volume II)) - Carter Faith</v>
+        <v>Never Comin' Back - Flatland Cavalry</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
+        <v>Lay Your Heartache Onto Mine (Songs From and Inspired by the Paramount+ Original Series Landman (Volume II))</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
+        <v>https://music.apple.com/us/song/lay-your-heartache-onto-mine-songs-from-and-inspired/1867273711</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E130" t="str">
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
+        <v>Lay Your Heartache Onto Mine (Songs From and Inspired by the Paramount+ Original Series Landman (Volume II)) - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:47</v>
+        <v>3:18</v>
       </c>
       <c r="H130" t="str">
-        <v>Dolly Parton</v>
+        <v>Carter Faith</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
+        <v>https://music.apple.com/us/artist/carter-faith/1489205896</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
+        <v>https://music.apple.com/us/album/lay-your-heartache-onto-mine-songs-from-and-inspired/1867273471</v>
       </c>
       <c r="L130" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
+        <v>Lay Your Heartache Onto Mine (Songs From and Inspired by the Paramount+ Original Series Landman (Volume II)) - Carter Faith</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Traffic Lights (feat. Thom Yorke)</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/traffic-lights-feat-thom-yorke/1861644315</v>
+        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E131" t="str">
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Honora</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>5:41</v>
+        <v>3:47</v>
       </c>
       <c r="H131" t="str">
-        <v>Flea</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/flea/463953572</v>
+        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/traffic-lights-feat-thom-yorke/1861644307</v>
+        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
       </c>
       <c r="L131" t="str">
-        <v>Traffic Lights (feat. Thom Yorke) - Flea</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Inferno (from "Heated Rivalry")</v>
+        <v>Traffic Lights (feat. Thom Yorke)</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/inferno-from-heated-rivalry/1868783886</v>
+        <v>https://music.apple.com/us/song/traffic-lights-feat-thom-yorke/1861644315</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E132" t="str">
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Heated Rivalry (Original Series Soundtrack)</v>
+        <v>Honora</v>
       </c>
       <c r="G132" t="str">
-        <v>4:26</v>
+        <v>5:41</v>
       </c>
       <c r="H132" t="str">
-        <v>Peter Peter</v>
+        <v>Flea</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/peter-peter/71305428</v>
+        <v>https://music.apple.com/us/artist/flea/463953572</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/inferno-from-heated-rivalry/1868783596</v>
+        <v>https://music.apple.com/us/album/traffic-lights-feat-thom-yorke/1861644307</v>
       </c>
       <c r="L132" t="str">
-        <v>Inferno (from "Heated Rivalry") - Peter Peter</v>
+        <v>Traffic Lights (feat. Thom Yorke) - Flea</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Yo Yan</v>
+        <v>Inferno (from "Heated Rivalry")</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/yo-yan/1867888651</v>
+        <v>https://music.apple.com/us/song/inferno-from-heated-rivalry/1868783886</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E133" t="str">
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Kora - Single</v>
+        <v>Heated Rivalry (Original Series Soundtrack)</v>
       </c>
       <c r="G133" t="str">
-        <v>2:00</v>
+        <v>4:26</v>
       </c>
       <c r="H133" t="str">
-        <v>Skrillex</v>
+        <v>Peter Peter</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
+        <v>https://music.apple.com/us/artist/peter-peter/71305428</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/yo-yan/1867888650</v>
+        <v>https://music.apple.com/us/album/inferno-from-heated-rivalry/1868783596</v>
       </c>
       <c r="L133" t="str">
-        <v>Yo Yan - Skrillex</v>
+        <v>Inferno (from "Heated Rivalry") - Peter Peter</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Jogodo</v>
+        <v>Yo Yan</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/jogodo/1867908454</v>
+        <v>https://music.apple.com/us/song/yo-yan/1867888651</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E134" t="str">
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>REAL, Vol. 1 - EP</v>
+        <v>Kora - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>3:08</v>
+        <v>2:00</v>
       </c>
       <c r="H134" t="str">
-        <v>Wizkid</v>
+        <v>Skrillex</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
+        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/jogodo/1867908237</v>
+        <v>https://music.apple.com/us/album/yo-yan/1867888650</v>
       </c>
       <c r="L134" t="str">
-        <v>Jogodo - Wizkid</v>
+        <v>Yo Yan - Skrillex</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Made It Out Alive</v>
+        <v>Jogodo</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/made-it-out-alive/1867596345</v>
+        <v>https://music.apple.com/us/song/jogodo/1867908454</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E135" t="str">
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Suffering From Success</v>
+        <v>REAL, Vol. 1 - EP</v>
       </c>
       <c r="G135" t="str">
-        <v>3:00</v>
+        <v>3:08</v>
       </c>
       <c r="H135" t="str">
-        <v>Dee Mula</v>
+        <v>Wizkid</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/dee-mula/1330325377</v>
+        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/made-it-out-alive/1867596343</v>
+        <v>https://music.apple.com/us/album/jogodo/1867908237</v>
       </c>
       <c r="L135" t="str">
-        <v>Made It Out Alive - Dee Mula</v>
+        <v>Jogodo - Wizkid</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>One of Them Ones</v>
+        <v>Made It Out Alive</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/one-of-them-ones/1868850365</v>
+        <v>https://music.apple.com/us/song/made-it-out-alive/1867596345</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E136" t="str">
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>One of Them Ones - Single</v>
+        <v>Suffering From Success</v>
       </c>
       <c r="G136" t="str">
-        <v>3:05</v>
+        <v>3:00</v>
       </c>
       <c r="H136" t="str">
-        <v>Veeze</v>
+        <v>Dee Mula</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/veeze/1464999308</v>
+        <v>https://music.apple.com/us/artist/dee-mula/1330325377</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/one-of-them-ones/1868850364</v>
+        <v>https://music.apple.com/us/album/made-it-out-alive/1867596343</v>
       </c>
       <c r="L136" t="str">
-        <v>One of Them Ones - Veeze</v>
+        <v>Made It Out Alive - Dee Mula</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Como Es Que Se Hace</v>
+        <v>One of Them Ones</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/como-es-que-se-hace/1864227584</v>
+        <v>https://music.apple.com/us/song/one-of-them-ones/1868850365</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E137" t="str">
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Como Es Que Se Hace - Single</v>
+        <v>One of Them Ones - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>3:25</v>
+        <v>3:05</v>
       </c>
       <c r="H137" t="str">
-        <v>Yandel</v>
+        <v>Veeze</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/yandel/72929426</v>
+        <v>https://music.apple.com/us/artist/veeze/1464999308</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/como-es-que-se-hace/1864227582</v>
+        <v>https://music.apple.com/us/album/one-of-them-ones/1868850364</v>
       </c>
       <c r="L137" t="str">
-        <v>Como Es Que Se Hace - Yandel</v>
+        <v>One of Them Ones - Veeze</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Ever Since U Left Me (I Went Deaf)</v>
+        <v>Como Es Que Se Hace</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/ever-since-u-left-me-i-went-deaf/1863124175</v>
+        <v>https://music.apple.com/us/song/como-es-que-se-hace/1864227584</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E138" t="str">
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Coke Wave 3.5: Narcos</v>
+        <v>Como Es Que Se Hace - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>2:16</v>
+        <v>3:25</v>
       </c>
       <c r="H138" t="str">
-        <v>French Montana</v>
+        <v>Yandel</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/french-montana/475816358</v>
+        <v>https://music.apple.com/us/artist/yandel/72929426</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/ever-since-u-left-me-i-went-deaf/1863124168</v>
+        <v>https://music.apple.com/us/album/como-es-que-se-hace/1864227582</v>
       </c>
       <c r="L138" t="str">
-        <v>Ever Since U Left Me (I Went Deaf) - French Montana</v>
+        <v>Como Es Que Se Hace - Yandel</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Ay Dale</v>
+        <v>Ever Since U Left Me (I Went Deaf)</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/ay-dale/1862897966</v>
+        <v>https://music.apple.com/us/song/ever-since-u-left-me-i-went-deaf/1863124175</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E139" t="str">
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Ay Dale - Single</v>
+        <v>Coke Wave 3.5: Narcos</v>
       </c>
       <c r="G139" t="str">
-        <v>2:26</v>
+        <v>2:16</v>
       </c>
       <c r="H139" t="str">
-        <v>Farruko</v>
+        <v>French Montana</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/farruko/364377482</v>
+        <v>https://music.apple.com/us/artist/french-montana/475816358</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/ay-dale/1862897623</v>
+        <v>https://music.apple.com/us/album/ever-since-u-left-me-i-went-deaf/1863124168</v>
       </c>
       <c r="L139" t="str">
-        <v>Ay Dale - Farruko</v>
+        <v>Ever Since U Left Me (I Went Deaf) - French Montana</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Teary Eyes</v>
+        <v>Ay Dale</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/teary-eyes/1869534187</v>
+        <v>https://music.apple.com/us/song/ay-dale/1862897966</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E140" t="str">
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Slime Cry</v>
+        <v>Ay Dale - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>2:45</v>
+        <v>2:26</v>
       </c>
       <c r="H140" t="str">
-        <v>YoungBoy Never Broke Again</v>
+        <v>Farruko</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/youngboy-never-broke-again/1168822104</v>
+        <v>https://music.apple.com/us/artist/farruko/364377482</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/teary-eyes/1869534167</v>
+        <v>https://music.apple.com/us/album/ay-dale/1862897623</v>
       </c>
       <c r="L140" t="str">
-        <v>Teary Eyes - YoungBoy Never Broke Again</v>
+        <v>Ay Dale - Farruko</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Bop It</v>
+        <v>Teary Eyes</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/bop-it/1867023470</v>
+        <v>https://music.apple.com/us/song/teary-eyes/1869534187</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E141" t="str">
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>KUNTOLOGY 101</v>
+        <v>Slime Cry</v>
       </c>
       <c r="G141" t="str">
-        <v>2:50</v>
+        <v>2:45</v>
       </c>
       <c r="H141" t="str">
-        <v>Aliyah's Interlude</v>
+        <v>YoungBoy Never Broke Again</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/aliyahs-interlude/1708765232</v>
+        <v>https://music.apple.com/us/artist/youngboy-never-broke-again/1168822104</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/bop-it/1867023466</v>
+        <v>https://music.apple.com/us/album/teary-eyes/1869534167</v>
       </c>
       <c r="L141" t="str">
-        <v>Bop It - Aliyah's Interlude</v>
+        <v>Teary Eyes - YoungBoy Never Broke Again</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>My Everything</v>
+        <v>Bop It</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/my-everything/1862940302</v>
+        <v>https://music.apple.com/us/song/bop-it/1867023470</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E142" t="str">
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>My Everything - Single</v>
+        <v>KUNTOLOGY 101</v>
       </c>
       <c r="G142" t="str">
-        <v>2:33</v>
+        <v>2:50</v>
       </c>
       <c r="H142" t="str">
-        <v>Lecrae</v>
+        <v>Aliyah's Interlude</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/lecrae/130043072</v>
+        <v>https://music.apple.com/us/artist/aliyahs-interlude/1708765232</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/my-everything/1862940301</v>
+        <v>https://music.apple.com/us/album/bop-it/1867023466</v>
       </c>
       <c r="L142" t="str">
-        <v>My Everything - Lecrae</v>
+        <v>Bop It - Aliyah's Interlude</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Whole Other Life</v>
+        <v>My Everything</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/whole-other-life/1858374798</v>
+        <v>https://music.apple.com/us/song/my-everything/1862940302</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E143" t="str">
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Nat &amp; Alex Wolff</v>
+        <v>My Everything - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>3:30</v>
+        <v>2:33</v>
       </c>
       <c r="H143" t="str">
-        <v>Nat &amp; Alex Wolff</v>
+        <v>Lecrae</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/nat-alex-wolff/470903139</v>
+        <v>https://music.apple.com/us/artist/lecrae/130043072</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/whole-other-life/1858374775</v>
+        <v>https://music.apple.com/us/album/my-everything/1862940301</v>
       </c>
       <c r="L143" t="str">
-        <v>Whole Other Life - Nat &amp; Alex Wolff</v>
+        <v>My Everything - Lecrae</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Belladona</v>
+        <v>Whole Other Life</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/belladona/1862538378</v>
+        <v>https://music.apple.com/us/song/whole-other-life/1858374798</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E144" t="str">
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Belladona</v>
+        <v>Nat &amp; Alex Wolff</v>
       </c>
       <c r="G144" t="str">
-        <v>3:32</v>
+        <v>3:30</v>
       </c>
       <c r="H144" t="str">
-        <v>Kenia Os</v>
+        <v>Nat &amp; Alex Wolff</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
+        <v>https://music.apple.com/us/artist/nat-alex-wolff/470903139</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/belladona/1862538030</v>
+        <v>https://music.apple.com/us/album/whole-other-life/1858374775</v>
       </c>
       <c r="L144" t="str">
-        <v>Belladona - Kenia Os</v>
+        <v>Whole Other Life - Nat &amp; Alex Wolff</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Addicted to Love (From "Tell Me Lies (Season 3)")</v>
+        <v>Belladona</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/addicted-to-love-from-tell-me-lies-season-3/1867024880</v>
+        <v>https://music.apple.com/us/song/belladona/1862538378</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E145" t="str">
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Addicted to Love (From "Tell Me Lies (Season 3)") - Single</v>
+        <v>Belladona</v>
       </c>
       <c r="G145" t="str">
-        <v>3:05</v>
+        <v>3:32</v>
       </c>
       <c r="H145" t="str">
-        <v>CHVRCHES</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/chvrches/566867492</v>
+        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/addicted-to-love-from-tell-me-lies-season-3/1867024879</v>
+        <v>https://music.apple.com/us/album/belladona/1862538030</v>
       </c>
       <c r="L145" t="str">
-        <v>Addicted to Love (From "Tell Me Lies (Season 3)") - CHVRCHES</v>
+        <v>Belladona - Kenia Os</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Lie2Me</v>
+        <v>Addicted to Love (From "Tell Me Lies (Season 3)")</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/lie2me/1862762675</v>
+        <v>https://music.apple.com/us/song/addicted-to-love-from-tell-me-lies-season-3/1867024880</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E146" t="str">
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Lie2Me - Single</v>
+        <v>Addicted to Love (From "Tell Me Lies (Season 3)") - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:03</v>
+        <v>3:05</v>
       </c>
       <c r="H146" t="str">
-        <v>DC THE DON</v>
+        <v>CHVRCHES</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
+        <v>https://music.apple.com/us/artist/chvrches/566867492</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/lie2me/1862762674</v>
+        <v>https://music.apple.com/us/album/addicted-to-love-from-tell-me-lies-season-3/1867024879</v>
       </c>
       <c r="L146" t="str">
-        <v>Lie2Me - DC THE DON</v>
+        <v>Addicted to Love (From "Tell Me Lies (Season 3)") - CHVRCHES</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>High On Heaven</v>
+        <v>Lie2Me</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/high-on-heaven/1859071765</v>
+        <v>https://music.apple.com/us/song/lie2me/1862762675</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E147" t="str">
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>High On Heaven - Single</v>
+        <v>Lie2Me - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:19</v>
+        <v>3:03</v>
       </c>
       <c r="H147" t="str">
-        <v>Nessa Barrett</v>
+        <v>DC THE DON</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
+        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/high-on-heaven/1859071764</v>
+        <v>https://music.apple.com/us/album/lie2me/1862762674</v>
       </c>
       <c r="L147" t="str">
-        <v>High On Heaven - Nessa Barrett</v>
+        <v>Lie2Me - DC THE DON</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Most Wanted</v>
+        <v>High On Heaven</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/most-wanted/1844866135</v>
+        <v>https://music.apple.com/us/song/high-on-heaven/1859071765</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E148" t="str">
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>My Ego Told Me To</v>
+        <v>High On Heaven - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>2:15</v>
+        <v>3:19</v>
       </c>
       <c r="H148" t="str">
-        <v>Leigh-Anne</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/leigh-anne/1691386195</v>
+        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/most-wanted/1844865923</v>
+        <v>https://music.apple.com/us/album/high-on-heaven/1859071764</v>
       </c>
       <c r="L148" t="str">
-        <v>Most Wanted - Leigh-Anne</v>
+        <v>High On Heaven - Nessa Barrett</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Anything Is Possible</v>
+        <v>Most Wanted</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/anything-is-possible/1867583228</v>
+        <v>https://music.apple.com/us/song/most-wanted/1844866135</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E149" t="str">
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Charlie The Wonderdog (Original Songs from the Motion Picture) - Single</v>
+        <v>My Ego Told Me To</v>
       </c>
       <c r="G149" t="str">
-        <v>2:57</v>
+        <v>2:15</v>
       </c>
       <c r="H149" t="str">
-        <v>Bryan Adams</v>
+        <v>Leigh-Anne</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/bryan-adams/85932</v>
+        <v>https://music.apple.com/us/artist/leigh-anne/1691386195</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/anything-is-possible/1867583221</v>
+        <v>https://music.apple.com/us/album/most-wanted/1844865923</v>
       </c>
       <c r="L149" t="str">
-        <v>Anything Is Possible - Bryan Adams</v>
+        <v>Most Wanted - Leigh-Anne</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Volcano</v>
+        <v>Anything Is Possible</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/volcano/1862739924</v>
+        <v>https://music.apple.com/us/song/anything-is-possible/1867583228</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E150" t="str">
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Volcano - Single</v>
+        <v>Charlie The Wonderdog (Original Songs from the Motion Picture) - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:28</v>
+        <v>2:57</v>
       </c>
       <c r="H150" t="str">
-        <v>Girl Tones</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/girl-tones/1761267584</v>
+        <v>https://music.apple.com/us/artist/bryan-adams/85932</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/volcano/1862739923</v>
+        <v>https://music.apple.com/us/album/anything-is-possible/1867583221</v>
       </c>
       <c r="L150" t="str">
-        <v>Volcano - Girl Tones</v>
+        <v>Anything Is Possible - Bryan Adams</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Into Oblivion</v>
+        <v>Volcano</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/into-oblivion/1868804164</v>
+        <v>https://music.apple.com/us/song/volcano/1862739924</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E151" t="str">
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Into Oblivion</v>
+        <v>Volcano - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:34</v>
+        <v>2:28</v>
       </c>
       <c r="H151" t="str">
-        <v>Lamb of God</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/girl-tones/1761267584</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/into-oblivion/1868804163</v>
+        <v>https://music.apple.com/us/album/volcano/1862739923</v>
       </c>
       <c r="L151" t="str">
-        <v>Into Oblivion - Lamb of God</v>
+        <v>Volcano - Girl Tones</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Beer and Blood Stains</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/beer-and-blood-stains/1838992321</v>
+        <v>https://music.apple.com/us/song/into-oblivion/1868804164</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E152" t="str">
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Listen Up!</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G152" t="str">
-        <v>3:19</v>
+        <v>3:34</v>
       </c>
       <c r="H152" t="str">
-        <v>New Found Glory</v>
+        <v>Lamb of God</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/new-found-glory/65551</v>
+        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/beer-and-blood-stains/1838991916</v>
+        <v>https://music.apple.com/us/album/into-oblivion/1868804163</v>
       </c>
       <c r="L152" t="str">
-        <v>Beer and Blood Stains - New Found Glory</v>
+        <v>Into Oblivion - Lamb of God</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Numb</v>
+        <v>Beer and Blood Stains</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/numb/1860136324</v>
+        <v>https://music.apple.com/us/song/beer-and-blood-stains/1838992321</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E153" t="str">
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Numb - Single</v>
+        <v>Listen Up!</v>
       </c>
       <c r="G153" t="str">
-        <v>2:13</v>
+        <v>3:19</v>
       </c>
       <c r="H153" t="str">
-        <v>Marc E. Bassy</v>
+        <v>New Found Glory</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/marc-e-bassy/899254194</v>
+        <v>https://music.apple.com/us/artist/new-found-glory/65551</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/numb/1860136319</v>
+        <v>https://music.apple.com/us/album/beer-and-blood-stains/1838991916</v>
       </c>
       <c r="L153" t="str">
-        <v>Numb - Marc E. Bassy</v>
+        <v>Beer and Blood Stains - New Found Glory</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Foxtrot</v>
+        <v>Numb</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/foxtrot/1860110201</v>
+        <v>https://music.apple.com/us/song/numb/1860136324</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E154" t="str">
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Saputjiji</v>
+        <v>Numb - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>1:33</v>
+        <v>2:13</v>
       </c>
       <c r="H154" t="str">
-        <v>Tanya Tagaq</v>
+        <v>Marc E. Bassy</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/tanya-tagaq/257545265</v>
+        <v>https://music.apple.com/us/artist/marc-e-bassy/899254194</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/foxtrot/1860109752</v>
+        <v>https://music.apple.com/us/album/numb/1860136319</v>
       </c>
       <c r="L154" t="str">
-        <v>Foxtrot - Tanya Tagaq</v>
+        <v>Numb - Marc E. Bassy</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Digital Winter</v>
+        <v>Foxtrot</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/digital-winter/1820332238</v>
+        <v>https://music.apple.com/us/song/foxtrot/1860110201</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E155" t="str">
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Stand On My Shoulders</v>
+        <v>Saputjiji</v>
       </c>
       <c r="G155" t="str">
-        <v>3:45</v>
+        <v>1:33</v>
       </c>
       <c r="H155" t="str">
-        <v>Ya Tseen</v>
+        <v>Tanya Tagaq</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/ya-tseen/1549782831</v>
+        <v>https://music.apple.com/us/artist/tanya-tagaq/257545265</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/digital-winter/1820332224</v>
+        <v>https://music.apple.com/us/album/foxtrot/1860109752</v>
       </c>
       <c r="L155" t="str">
-        <v>Digital Winter - Ya Tseen</v>
+        <v>Foxtrot - Tanya Tagaq</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Back To You</v>
+        <v>Digital Winter</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/back-to-you/1861380254</v>
+        <v>https://music.apple.com/us/song/digital-winter/1820332238</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E156" t="str">
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Porcelain</v>
+        <v>Stand On My Shoulders</v>
       </c>
       <c r="G156" t="str">
-        <v>3:10</v>
+        <v>3:45</v>
       </c>
       <c r="H156" t="str">
-        <v>Peach PRC</v>
+        <v>Ya Tseen</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/peach-prc/1469263677</v>
+        <v>https://music.apple.com/us/artist/ya-tseen/1549782831</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/back-to-you/1861380240</v>
+        <v>https://music.apple.com/us/album/digital-winter/1820332224</v>
       </c>
       <c r="L156" t="str">
-        <v>Back To You - Peach PRC</v>
+        <v>Digital Winter - Ya Tseen</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Sleepwalker's Pendulum</v>
+        <v>Back To You</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/sleepwalkers-pendulum/1826115116</v>
+        <v>https://music.apple.com/us/song/back-to-you/1861380254</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E157" t="str">
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Dreamer+</v>
+        <v>Porcelain</v>
       </c>
       <c r="G157" t="str">
-        <v>3:22</v>
+        <v>3:10</v>
       </c>
       <c r="H157" t="str">
-        <v>Sassy 009</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/sassy-009/1277035471</v>
+        <v>https://music.apple.com/us/artist/peach-prc/1469263677</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/sleepwalkers-pendulum/1826114506</v>
+        <v>https://music.apple.com/us/album/back-to-you/1861380240</v>
       </c>
       <c r="L157" t="str">
-        <v>Sleepwalker's Pendulum - Sassy 009</v>
+        <v>Back To You - Peach PRC</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Ruin Me</v>
+        <v>Sleepwalker's Pendulum</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/ruin-me/1850741533</v>
+        <v>https://music.apple.com/us/song/sleepwalkers-pendulum/1826115116</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E158" t="str">
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>HEAD FIRST - EP</v>
+        <v>Dreamer+</v>
       </c>
       <c r="G158" t="str">
-        <v>2:31</v>
+        <v>3:22</v>
       </c>
       <c r="H158" t="str">
-        <v>Corbyn Besson</v>
+        <v>Sassy 009</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/corbyn-besson/810434797</v>
+        <v>https://music.apple.com/us/artist/sassy-009/1277035471</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/ruin-me/1850741514</v>
+        <v>https://music.apple.com/us/album/sleepwalkers-pendulum/1826114506</v>
       </c>
       <c r="L158" t="str">
-        <v>Ruin Me - Corbyn Besson</v>
+        <v>Sleepwalker's Pendulum - Sassy 009</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>w-w-w-w-w</v>
+        <v>Ruin Me</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/w-w-w-w-w/1846462521</v>
+        <v>https://music.apple.com/us/song/ruin-me/1850741533</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E159" t="str">
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>the apple tree under the sea</v>
+        <v>HEAD FIRST - EP</v>
       </c>
       <c r="G159" t="str">
-        <v>4:26</v>
+        <v>2:31</v>
       </c>
       <c r="H159" t="str">
-        <v>hemlocke springs</v>
+        <v>Corbyn Besson</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
+        <v>https://music.apple.com/us/artist/corbyn-besson/810434797</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/w-w-w-w-w/1846462383</v>
+        <v>https://music.apple.com/us/album/ruin-me/1850741514</v>
       </c>
       <c r="L159" t="str">
-        <v>w-w-w-w-w - hemlocke springs</v>
+        <v>Ruin Me - Corbyn Besson</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Struggle Bus</v>
+        <v>w-w-w-w-w</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/struggle-bus/1862024076</v>
+        <v>https://music.apple.com/us/song/w-w-w-w-w/1846462521</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E160" t="str">
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Struggle Bus - Single</v>
+        <v>the apple tree under the sea</v>
       </c>
       <c r="G160" t="str">
-        <v>3:20</v>
+        <v>4:26</v>
       </c>
       <c r="H160" t="str">
-        <v>Iris Copperman</v>
+        <v>hemlocke springs</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/iris-copperman/1741269048</v>
+        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/struggle-bus/1862024075</v>
+        <v>https://music.apple.com/us/album/w-w-w-w-w/1846462383</v>
       </c>
       <c r="L160" t="str">
-        <v>Struggle Bus - Iris Copperman</v>
+        <v>w-w-w-w-w - hemlocke springs</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Over</v>
+        <v>Struggle Bus</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/over/1862351820</v>
+        <v>https://music.apple.com/us/song/struggle-bus/1862024076</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E161" t="str">
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Over - Single</v>
+        <v>Struggle Bus - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:49</v>
+        <v>3:20</v>
       </c>
       <c r="H161" t="str">
-        <v>Sydney Rose</v>
+        <v>Iris Copperman</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/sydney-rose/354936789</v>
+        <v>https://music.apple.com/us/artist/iris-copperman/1741269048</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/over/1862351811</v>
+        <v>https://music.apple.com/us/album/struggle-bus/1862024075</v>
       </c>
       <c r="L161" t="str">
-        <v>Over - Sydney Rose</v>
+        <v>Struggle Bus - Iris Copperman</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Lean</v>
+        <v>Over</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/lean/1862829540</v>
+        <v>https://music.apple.com/us/song/over/1862351820</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E162" t="str">
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Lean - Single</v>
+        <v>Over - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:53</v>
+        <v>3:49</v>
       </c>
       <c r="H162" t="str">
-        <v>Charlotte Day Wilson</v>
+        <v>Sydney Rose</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-day-wilson/1053594538</v>
+        <v>https://music.apple.com/us/artist/sydney-rose/354936789</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/lean/1862829538</v>
+        <v>https://music.apple.com/us/album/over/1862351811</v>
       </c>
       <c r="L162" t="str">
-        <v>Lean - Charlotte Day Wilson</v>
+        <v>Over - Sydney Rose</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>F**k It Up</v>
+        <v>Lean</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/f-k-it-up/1849002929</v>
+        <v>https://music.apple.com/us/song/lean/1862829540</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E163" t="str">
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>F**k It Up - EP</v>
+        <v>Lean - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:32</v>
+        <v>3:53</v>
       </c>
       <c r="H163" t="str">
-        <v>Master Peace</v>
+        <v>Charlotte Day Wilson</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/master-peace/1477196856</v>
+        <v>https://music.apple.com/us/artist/charlotte-day-wilson/1053594538</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/f-k-it-up/1849002928</v>
+        <v>https://music.apple.com/us/album/lean/1862829538</v>
       </c>
       <c r="L163" t="str">
-        <v>F**k It Up - Master Peace</v>
+        <v>Lean - Charlotte Day Wilson</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>La Carrera</v>
+        <v>F**k It Up</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/la-carrera/1863188476</v>
+        <v>https://music.apple.com/us/song/f-k-it-up/1849002929</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E164" t="str">
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>La Carrera - Single</v>
+        <v>F**k It Up - EP</v>
       </c>
       <c r="G164" t="str">
-        <v>3:40</v>
+        <v>3:32</v>
       </c>
       <c r="H164" t="str">
-        <v>Moa Rivera</v>
+        <v>Master Peace</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/moa-rivera/1636808812</v>
+        <v>https://music.apple.com/us/artist/master-peace/1477196856</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/la-carrera/1863188474</v>
+        <v>https://music.apple.com/us/album/f-k-it-up/1849002928</v>
       </c>
       <c r="L164" t="str">
-        <v>La Carrera - Moa Rivera</v>
+        <v>F**k It Up - Master Peace</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>No Lube So Rude</v>
+        <v>La Carrera</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/no-lube-so-rude/1856065376</v>
+        <v>https://music.apple.com/us/song/la-carrera/1863188476</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E165" t="str">
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>No Lube So Rude</v>
+        <v>La Carrera - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>2:48</v>
+        <v>3:40</v>
       </c>
       <c r="H165" t="str">
-        <v>Peaches</v>
+        <v>Moa Rivera</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/peaches/3028600</v>
+        <v>https://music.apple.com/us/artist/moa-rivera/1636808812</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/no-lube-so-rude/1856064995</v>
+        <v>https://music.apple.com/us/album/la-carrera/1863188474</v>
       </c>
       <c r="L165" t="str">
-        <v>No Lube So Rude - Peaches</v>
+        <v>La Carrera - Moa Rivera</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Somersaults</v>
+        <v>No Lube So Rude</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/somersaults/1847159408</v>
+        <v>https://music.apple.com/us/song/no-lube-so-rude/1856065376</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E166" t="str">
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Somersaults</v>
+        <v>No Lube So Rude</v>
       </c>
       <c r="G166" t="str">
-        <v>4:32</v>
+        <v>2:48</v>
       </c>
       <c r="H166" t="str">
-        <v>deathcrash</v>
+        <v>Peaches</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/deathcrash/1461469738</v>
+        <v>https://music.apple.com/us/artist/peaches/3028600</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/somersaults/1847159406</v>
+        <v>https://music.apple.com/us/album/no-lube-so-rude/1856064995</v>
       </c>
       <c r="L166" t="str">
-        <v>Somersaults - deathcrash</v>
+        <v>No Lube So Rude - Peaches</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>2005</v>
+        <v>Somersaults</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/2005/1854873143</v>
+        <v>https://music.apple.com/us/song/somersaults/1847159408</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E167" t="str">
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Almost There</v>
+        <v>Somersaults</v>
       </c>
       <c r="G167" t="str">
-        <v>3:52</v>
+        <v>4:32</v>
       </c>
       <c r="H167" t="str">
-        <v>The Academy Is...</v>
+        <v>deathcrash</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/the-academy-is/75024274</v>
+        <v>https://music.apple.com/us/artist/deathcrash/1461469738</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/2005/1854873133</v>
+        <v>https://music.apple.com/us/album/somersaults/1847159406</v>
       </c>
       <c r="L167" t="str">
-        <v>2005 - The Academy Is...</v>
+        <v>Somersaults - deathcrash</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>I Had a Ball</v>
+        <v>2005</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/i-had-a-ball/1863330906</v>
+        <v>https://music.apple.com/us/song/2005/1854873143</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E168" t="str">
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Palm Royale Season 2 (Apple TV Original Series Soundtrack)</v>
+        <v>Almost There</v>
       </c>
       <c r="G168" t="str">
-        <v>4:14</v>
+        <v>3:52</v>
       </c>
       <c r="H168" t="str">
-        <v>Kristen Wiig</v>
+        <v>The Academy Is...</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/kristen-wiig/273077223</v>
+        <v>https://music.apple.com/us/artist/the-academy-is/75024274</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/i-had-a-ball/1863330900</v>
+        <v>https://music.apple.com/us/album/2005/1854873133</v>
       </c>
       <c r="L168" t="str">
-        <v>I Had a Ball - Kristen Wiig</v>
+        <v>2005 - The Academy Is...</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>IDB</v>
+        <v>I Had a Ball</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/idb/1859084151</v>
+        <v>https://music.apple.com/us/song/i-had-a-ball/1863330906</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E169" t="str">
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>IDB - Single</v>
+        <v>Palm Royale Season 2 (Apple TV Original Series Soundtrack)</v>
       </c>
       <c r="G169" t="str">
-        <v>2:52</v>
+        <v>4:14</v>
       </c>
       <c r="H169" t="str">
-        <v>42 Dugg</v>
+        <v>Kristen Wiig</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
+        <v>https://music.apple.com/us/artist/kristen-wiig/273077223</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/idb/1859084147</v>
+        <v>https://music.apple.com/us/album/i-had-a-ball/1863330900</v>
       </c>
       <c r="L169" t="str">
-        <v>IDB - 42 Dugg</v>
+        <v>I Had a Ball - Kristen Wiig</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Feel This Way</v>
+        <v>IDB</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/feel-this-way/1862902478</v>
+        <v>https://music.apple.com/us/song/idb/1859084151</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E170" t="str">
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Feel This Way - Single</v>
+        <v>IDB - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:04</v>
+        <v>2:52</v>
       </c>
       <c r="H170" t="str">
-        <v>Josh Baker</v>
+        <v>42 Dugg</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/josh-baker/150294413</v>
+        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/feel-this-way/1862902476</v>
+        <v>https://music.apple.com/us/album/idb/1859084147</v>
       </c>
       <c r="L170" t="str">
-        <v>Feel This Way - Josh Baker</v>
+        <v>IDB - 42 Dugg</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Falling</v>
+        <v>Feel This Way</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/falling/1861598107</v>
+        <v>https://music.apple.com/us/song/feel-this-way/1862902478</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E171" t="str">
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Falling - Single</v>
+        <v>Feel This Way - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>3:02</v>
+        <v>3:04</v>
       </c>
       <c r="H171" t="str">
-        <v>Shimza</v>
+        <v>Josh Baker</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/shimza/697739898</v>
+        <v>https://music.apple.com/us/artist/josh-baker/150294413</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/falling/1861598106</v>
+        <v>https://music.apple.com/us/album/feel-this-way/1862902476</v>
       </c>
       <c r="L171" t="str">
-        <v>Falling - Shimza</v>
+        <v>Feel This Way - Josh Baker</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Message to You</v>
+        <v>Falling</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/message-to-you/1867275596</v>
+        <v>https://music.apple.com/us/song/falling/1861598107</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E172" t="str">
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Heavy On The Soul</v>
+        <v>Falling - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:37</v>
+        <v>3:02</v>
       </c>
       <c r="H172" t="str">
-        <v>Ty Myers</v>
+        <v>Shimza</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
+        <v>https://music.apple.com/us/artist/shimza/697739898</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/message-to-you/1867275110</v>
+        <v>https://music.apple.com/us/album/falling/1861598106</v>
       </c>
       <c r="L172" t="str">
-        <v>Message to You - Ty Myers</v>
+        <v>Falling - Shimza</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>NOTHING IS REAL</v>
+        <v>Message to You</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/nothing-is-real/1866859742</v>
+        <v>https://music.apple.com/us/song/message-to-you/1867275596</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E173" t="str">
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>NOTHING IS REAL - Single</v>
+        <v>Heavy On The Soul</v>
       </c>
       <c r="G173" t="str">
-        <v>3:06</v>
+        <v>3:37</v>
       </c>
       <c r="H173" t="str">
-        <v>DESTIN CONRAD</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/destin-conrad/852999989</v>
+        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/nothing-is-real/1866859497</v>
+        <v>https://music.apple.com/us/album/message-to-you/1867275110</v>
       </c>
       <c r="L173" t="str">
-        <v>NOTHING IS REAL - DESTIN CONRAD</v>
+        <v>Message to You - Ty Myers</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>CUÉNTAME</v>
+        <v>NOTHING IS REAL</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/cu%C3%A9ntame/1862973854</v>
+        <v>https://music.apple.com/us/song/nothing-is-real/1866859742</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E174" t="str">
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>CUÉNTAME - Single</v>
+        <v>NOTHING IS REAL - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:42</v>
+        <v>3:06</v>
       </c>
       <c r="H174" t="str">
-        <v>FloyyMenor</v>
+        <v>DESTIN CONRAD</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/floyymenor/1676497551</v>
+        <v>https://music.apple.com/us/artist/destin-conrad/852999989</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/cu%C3%A9ntame/1862973853</v>
+        <v>https://music.apple.com/us/album/nothing-is-real/1866859497</v>
       </c>
       <c r="L174" t="str">
-        <v>CUÉNTAME - FloyyMenor</v>
+        <v>NOTHING IS REAL - DESTIN CONRAD</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>DANCE...</v>
+        <v>CUÉNTAME</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/dance/1867531306</v>
+        <v>https://music.apple.com/us/song/cu%C3%A9ntame/1862973854</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E175" t="str">
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>WOR$T GIRL IN AMERICA</v>
+        <v>CUÉNTAME - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>4:47</v>
+        <v>2:42</v>
       </c>
       <c r="H175" t="str">
-        <v>Slayyyter</v>
+        <v>FloyyMenor</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/floyymenor/1676497551</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/dance/1867530577</v>
+        <v>https://music.apple.com/us/album/cu%C3%A9ntame/1862973853</v>
       </c>
       <c r="L175" t="str">
-        <v>DANCE... - Slayyyter</v>
+        <v>CUÉNTAME - FloyyMenor</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>welcome to the circus</v>
+        <v>DANCE...</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/welcome-to-the-circus/1861011604</v>
+        <v>https://music.apple.com/us/song/dance/1867531306</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E176" t="str">
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>welcome to the circus - Single</v>
+        <v>WOR$T GIRL IN AMERICA</v>
       </c>
       <c r="G176" t="str">
-        <v>2:29</v>
+        <v>4:47</v>
       </c>
       <c r="H176" t="str">
-        <v>Jagwar Twin</v>
+        <v>Slayyyter</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/jagwar-twin/1429051937</v>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/welcome-to-the-circus/1861011603</v>
+        <v>https://music.apple.com/us/album/dance/1867530577</v>
       </c>
       <c r="L176" t="str">
-        <v>welcome to the circus - Jagwar Twin</v>
+        <v>DANCE... - Slayyyter</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>playlist</v>
+        <v>welcome to the circus</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/playlist/1859009927</v>
+        <v>https://music.apple.com/us/song/welcome-to-the-circus/1861011604</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E177" t="str">
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>playlist - Single</v>
+        <v>welcome to the circus - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:44</v>
+        <v>2:29</v>
       </c>
       <c r="H177" t="str">
-        <v>Tenroc</v>
+        <v>Jagwar Twin</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/tenroc/1711844910</v>
+        <v>https://music.apple.com/us/artist/jagwar-twin/1429051937</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/playlist/1859009923</v>
+        <v>https://music.apple.com/us/album/welcome-to-the-circus/1861011603</v>
       </c>
       <c r="L177" t="str">
-        <v>playlist - Tenroc</v>
+        <v>welcome to the circus - Jagwar Twin</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Marlboro Man</v>
+        <v>playlist</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/marlboro-man/1862008741</v>
+        <v>https://music.apple.com/us/song/playlist/1859009927</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E178" t="str">
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Marlboro Man - Single</v>
+        <v>playlist - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:23</v>
+        <v>2:44</v>
       </c>
       <c r="H178" t="str">
-        <v>Midland</v>
+        <v>Tenroc</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/midland/1171869852</v>
+        <v>https://music.apple.com/us/artist/tenroc/1711844910</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/marlboro-man/1862008740</v>
+        <v>https://music.apple.com/us/album/playlist/1859009923</v>
       </c>
       <c r="L178" t="str">
-        <v>Marlboro Man - Midland</v>
+        <v>playlist - Tenroc</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Enabling</v>
+        <v>Marlboro Man</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/enabling/1860993048</v>
+        <v>https://music.apple.com/us/song/marlboro-man/1862008741</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E179" t="str">
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Enabling - Single</v>
+        <v>Marlboro Man - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:18</v>
+        <v>3:23</v>
       </c>
       <c r="H179" t="str">
-        <v>Tenille Townes</v>
+        <v>Midland</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/tenille-townes/1367713770</v>
+        <v>https://music.apple.com/us/artist/midland/1171869852</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/enabling/1860992859</v>
+        <v>https://music.apple.com/us/album/marlboro-man/1862008740</v>
       </c>
       <c r="L179" t="str">
-        <v>Enabling - Tenille Townes</v>
+        <v>Marlboro Man - Midland</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Two Broken Hearts</v>
+        <v>Enabling</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/two-broken-hearts/1841485428</v>
+        <v>https://music.apple.com/us/song/enabling/1860993048</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E180" t="str">
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Steel Town</v>
+        <v>Enabling - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:53</v>
+        <v>3:18</v>
       </c>
       <c r="H180" t="str">
-        <v>Morgan Evans</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/morgan-evans/262665075</v>
+        <v>https://music.apple.com/us/artist/tenille-townes/1367713770</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/two-broken-hearts/1841484758</v>
+        <v>https://music.apple.com/us/album/enabling/1860992859</v>
       </c>
       <c r="L180" t="str">
-        <v>Two Broken Hearts - Morgan Evans</v>
+        <v>Enabling - Tenille Townes</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Lost in My Bed</v>
+        <v>Two Broken Hearts</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/lost-in-my-bed/1862222274</v>
+        <v>https://music.apple.com/us/song/two-broken-hearts/1841485428</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E181" t="str">
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Lost in My Bed - Single</v>
+        <v>Steel Town</v>
       </c>
       <c r="G181" t="str">
-        <v>3:46</v>
+        <v>3:53</v>
       </c>
       <c r="H181" t="str">
-        <v>Khalil</v>
+        <v>Morgan Evans</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/khalil/1223181975</v>
+        <v>https://music.apple.com/us/artist/morgan-evans/262665075</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/lost-in-my-bed/1862222272</v>
+        <v>https://music.apple.com/us/album/two-broken-hearts/1841484758</v>
       </c>
       <c r="L181" t="str">
-        <v>Lost in My Bed - Khalil</v>
+        <v>Two Broken Hearts - Morgan Evans</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Father Time</v>
+        <v>Lost in My Bed</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/father-time/1858611581</v>
+        <v>https://music.apple.com/us/song/lost-in-my-bed/1862222274</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E182" t="str">
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Honey Water</v>
+        <v>Lost in My Bed - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>1:58</v>
+        <v>3:46</v>
       </c>
       <c r="H182" t="str">
-        <v>Girlfriend</v>
+        <v>Khalil</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/girlfriend/1511096374</v>
+        <v>https://music.apple.com/us/artist/khalil/1223181975</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/father-time/1858611265</v>
+        <v>https://music.apple.com/us/album/lost-in-my-bed/1862222272</v>
       </c>
       <c r="L182" t="str">
-        <v>Father Time - Girlfriend</v>
+        <v>Lost in My Bed - Khalil</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>MVLAN</v>
+        <v>Father Time</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/mvlan/1867584574</v>
+        <v>https://music.apple.com/us/song/father-time/1858611581</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E183" t="str">
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>MVLAN - Single</v>
+        <v>Honey Water</v>
       </c>
       <c r="G183" t="str">
-        <v>3:41</v>
+        <v>1:58</v>
       </c>
       <c r="H183" t="str">
-        <v>YOVNGCHIMI</v>
+        <v>Girlfriend</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/yovngchimi/1558257759</v>
+        <v>https://music.apple.com/us/artist/girlfriend/1511096374</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/mvlan/1867584573</v>
+        <v>https://music.apple.com/us/album/father-time/1858611265</v>
       </c>
       <c r="L183" t="str">
-        <v>MVLAN - YOVNGCHIMI</v>
+        <v>Father Time - Girlfriend</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Name In Blood</v>
+        <v>MVLAN</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/name-in-blood/1859687600</v>
+        <v>https://music.apple.com/us/song/mvlan/1867584574</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E184" t="str">
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Engines of Demolition</v>
+        <v>MVLAN - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>4:36</v>
+        <v>3:41</v>
       </c>
       <c r="H184" t="str">
-        <v>Black Label Society</v>
+        <v>YOVNGCHIMI</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/black-label-society/2778807</v>
+        <v>https://music.apple.com/us/artist/yovngchimi/1558257759</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/name-in-blood/1859687597</v>
+        <v>https://music.apple.com/us/album/mvlan/1867584573</v>
       </c>
       <c r="L184" t="str">
-        <v>Name In Blood - Black Label Society</v>
+        <v>MVLAN - YOVNGCHIMI</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Eyeball</v>
+        <v>Name In Blood</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/eyeball/1862539350</v>
+        <v>https://music.apple.com/us/song/name-in-blood/1859687600</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E185" t="str">
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Eyeball - EP</v>
+        <v>Engines of Demolition</v>
       </c>
       <c r="G185" t="str">
-        <v>2:14</v>
+        <v>4:36</v>
       </c>
       <c r="H185" t="str">
-        <v>They Might Be Giants</v>
+        <v>Black Label Society</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/they-might-be-giants/149020</v>
+        <v>https://music.apple.com/us/artist/black-label-society/2778807</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/eyeball/1862539346</v>
+        <v>https://music.apple.com/us/album/name-in-blood/1859687597</v>
       </c>
       <c r="L185" t="str">
-        <v>Eyeball - They Might Be Giants</v>
+        <v>Name In Blood - Black Label Society</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Long Gone</v>
+        <v>Eyeball</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/long-gone/1847573926</v>
+        <v>https://music.apple.com/us/song/eyeball/1862539350</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E186" t="str">
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Tenterhooks</v>
+        <v>Eyeball - EP</v>
       </c>
       <c r="G186" t="str">
-        <v>3:55</v>
+        <v>2:14</v>
       </c>
       <c r="H186" t="str">
-        <v>Silversun Pickups</v>
+        <v>They Might Be Giants</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/silversun-pickups/74752665</v>
+        <v>https://music.apple.com/us/artist/they-might-be-giants/149020</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/long-gone/1847573918</v>
+        <v>https://music.apple.com/us/album/eyeball/1862539346</v>
       </c>
       <c r="L186" t="str">
-        <v>Long Gone - Silversun Pickups</v>
+        <v>Eyeball - They Might Be Giants</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>iloveitiloveitiloveit</v>
+        <v>Long Gone</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/iloveitiloveitiloveit/1867034427</v>
+        <v>https://music.apple.com/us/song/long-gone/1847573926</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E187" t="str">
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>iloveitiloveitiloveit - Single</v>
+        <v>Tenterhooks</v>
       </c>
       <c r="G187" t="str">
-        <v>3:03</v>
+        <v>3:55</v>
       </c>
       <c r="H187" t="str">
-        <v>Bella Kay</v>
+        <v>Silversun Pickups</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/silversun-pickups/74752665</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/iloveitiloveitiloveit/1867034426</v>
+        <v>https://music.apple.com/us/album/long-gone/1847573918</v>
       </c>
       <c r="L187" t="str">
-        <v>iloveitiloveitiloveit - Bella Kay</v>
+        <v>Long Gone - Silversun Pickups</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>To The Edge</v>
+        <v>iloveitiloveitiloveit</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/to-the-edge/1863513891</v>
+        <v>https://music.apple.com/us/song/iloveitiloveitiloveit/1867034427</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E188" t="str">
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>To The Edge - Single</v>
+        <v>iloveitiloveitiloveit - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:19</v>
+        <v>3:03</v>
       </c>
       <c r="H188" t="str">
-        <v>Alex Jude</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/to-the-edge/1863513887</v>
+        <v>https://music.apple.com/us/album/iloveitiloveitiloveit/1867034426</v>
       </c>
       <c r="L188" t="str">
-        <v>To The Edge - Alex Jude</v>
+        <v>iloveitiloveitiloveit - Bella Kay</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>demons</v>
+        <v>To The Edge</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/demons/1861978106</v>
+        <v>https://music.apple.com/us/song/to-the-edge/1863513891</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E189" t="str">
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>demons - Single</v>
+        <v>To The Edge - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:10</v>
+        <v>3:19</v>
       </c>
       <c r="H189" t="str">
-        <v>Josiah Queen</v>
+        <v>Alex Jude</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/josiah-queen/1498117530</v>
+        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/demons/1861978105</v>
+        <v>https://music.apple.com/us/album/to-the-edge/1863513887</v>
       </c>
       <c r="L189" t="str">
-        <v>demons - Josiah Queen</v>
+        <v>To The Edge - Alex Jude</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Everyone Wants To Feel Like You Do</v>
+        <v>demons</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/everyone-wants-to-feel-like-you-do/1841949027</v>
+        <v>https://music.apple.com/us/song/demons/1861978106</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E190" t="str">
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Valentine</v>
+        <v>demons - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>4:03</v>
+        <v>3:10</v>
       </c>
       <c r="H190" t="str">
-        <v>Courtney Marie Andrews</v>
+        <v>Josiah Queen</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/courtney-marie-andrews/287157006</v>
+        <v>https://music.apple.com/us/artist/josiah-queen/1498117530</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/everyone-wants-to-feel-like-you-do/1841948802</v>
+        <v>https://music.apple.com/us/album/demons/1861978105</v>
       </c>
       <c r="L190" t="str">
-        <v>Everyone Wants To Feel Like You Do - Courtney Marie Andrews</v>
+        <v>demons - Josiah Queen</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Nothing Comes Easy</v>
+        <v>Everyone Wants To Feel Like You Do</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/nothing-comes-easy/1862757046</v>
+        <v>https://music.apple.com/us/song/everyone-wants-to-feel-like-you-do/1841949027</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E191" t="str">
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Nothing Comes Easy - Single</v>
+        <v>Valentine</v>
       </c>
       <c r="G191" t="str">
-        <v>2:54</v>
+        <v>4:03</v>
       </c>
       <c r="H191" t="str">
-        <v>Joy Oladokun</v>
+        <v>Courtney Marie Andrews</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/joy-oladokun/699636664</v>
+        <v>https://music.apple.com/us/artist/courtney-marie-andrews/287157006</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/nothing-comes-easy/1862756744</v>
+        <v>https://music.apple.com/us/album/everyone-wants-to-feel-like-you-do/1841948802</v>
       </c>
       <c r="L191" t="str">
-        <v>Nothing Comes Easy - Joy Oladokun</v>
+        <v>Everyone Wants To Feel Like You Do - Courtney Marie Andrews</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Against the Dying of the Light</v>
+        <v>Nothing Comes Easy</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/against-the-dying-of-the-light/1860962165</v>
+        <v>https://music.apple.com/us/song/nothing-comes-easy/1862757046</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E192" t="str">
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Against the Dying of the Light</v>
+        <v>Nothing Comes Easy - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>2:28</v>
+        <v>2:54</v>
       </c>
       <c r="H192" t="str">
-        <v>José González</v>
+        <v>Joy Oladokun</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/jos%C3%A9-gonz%C3%A1lez/153417030</v>
+        <v>https://music.apple.com/us/artist/joy-oladokun/699636664</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/against-the-dying-of-the-light/1860962162</v>
+        <v>https://music.apple.com/us/album/nothing-comes-easy/1862756744</v>
       </c>
       <c r="L192" t="str">
-        <v>Against the Dying of the Light - José González</v>
+        <v>Nothing Comes Easy - Joy Oladokun</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Big Boy Problems</v>
+        <v>Against the Dying of the Light</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/big-boy-problems/1851062438</v>
+        <v>https://music.apple.com/us/song/against-the-dying-of-the-light/1860962165</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E193" t="str">
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Cynthia</v>
+        <v>Against the Dying of the Light</v>
       </c>
       <c r="G193" t="str">
-        <v>2:30</v>
+        <v>2:28</v>
       </c>
       <c r="H193" t="str">
-        <v>Sydney Ross Mitchell</v>
+        <v>José González</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/sydney-ross-mitchell/1373996317</v>
+        <v>https://music.apple.com/us/artist/jos%C3%A9-gonz%C3%A1lez/153417030</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/big-boy-problems/1851062193</v>
+        <v>https://music.apple.com/us/album/against-the-dying-of-the-light/1860962162</v>
       </c>
       <c r="L193" t="str">
-        <v>Big Boy Problems - Sydney Ross Mitchell</v>
+        <v>Against the Dying of the Light - José González</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Griever</v>
+        <v>Big Boy Problems</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/griever/1860950900</v>
+        <v>https://music.apple.com/us/song/big-boy-problems/1851062438</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E194" t="str">
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Griever - Single</v>
+        <v>Cynthia</v>
       </c>
       <c r="G194" t="str">
-        <v>2:31</v>
+        <v>2:30</v>
       </c>
       <c r="H194" t="str">
-        <v>Avery Cochrane</v>
+        <v>Sydney Ross Mitchell</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/avery-cochrane/1556978969</v>
+        <v>https://music.apple.com/us/artist/sydney-ross-mitchell/1373996317</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/griever/1860950897</v>
+        <v>https://music.apple.com/us/album/big-boy-problems/1851062193</v>
       </c>
       <c r="L194" t="str">
-        <v>Griever - Avery Cochrane</v>
+        <v>Big Boy Problems - Sydney Ross Mitchell</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>7 BESOS</v>
+        <v>Griever</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/7-besos/1862927855</v>
+        <v>https://music.apple.com/us/song/griever/1860950900</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E195" t="str">
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>7 BESOS - Single</v>
+        <v>Griever - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:21</v>
+        <v>2:31</v>
       </c>
       <c r="H195" t="str">
-        <v>LEGADO 7</v>
+        <v>Avery Cochrane</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/legado-7/997011422</v>
+        <v>https://music.apple.com/us/artist/avery-cochrane/1556978969</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/7-besos/1862927851</v>
+        <v>https://music.apple.com/us/album/griever/1860950897</v>
       </c>
       <c r="L195" t="str">
-        <v>7 BESOS - LEGADO 7</v>
+        <v>Griever - Avery Cochrane</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>UN LEÑO</v>
+        <v>7 BESOS</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/un-le%C3%B1o/1862904727</v>
+        <v>https://music.apple.com/us/song/7-besos/1862927855</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E196" t="str">
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>UN LEÑO - Single</v>
+        <v>7 BESOS - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>3:00</v>
+        <v>3:21</v>
       </c>
       <c r="H196" t="str">
-        <v>Armenta</v>
+        <v>LEGADO 7</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/armenta/1479504876</v>
+        <v>https://music.apple.com/us/artist/legado-7/997011422</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/un-le%C3%B1o/1862904402</v>
+        <v>https://music.apple.com/us/album/7-besos/1862927851</v>
       </c>
       <c r="L196" t="str">
-        <v>UN LEÑO - Armenta</v>
+        <v>7 BESOS - LEGADO 7</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Queen's Goodbye</v>
+        <v>UN LEÑO</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/queens-goodbye/1858554528</v>
+        <v>https://music.apple.com/us/song/un-le%C3%B1o/1862904727</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E197" t="str">
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Mārara</v>
+        <v>UN LEÑO - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>3:46</v>
+        <v>3:00</v>
       </c>
       <c r="H197" t="str">
-        <v>15 15</v>
+        <v>Armenta</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
+        <v>https://music.apple.com/us/artist/armenta/1479504876</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/queens-goodbye/1858554036</v>
+        <v>https://music.apple.com/us/album/un-le%C3%B1o/1862904402</v>
       </c>
       <c r="L197" t="str">
-        <v>Queen's Goodbye - 15 15</v>
+        <v>UN LEÑO - Armenta</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Bring Me Back To Life</v>
+        <v>Queen's Goodbye</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/bring-me-back-to-life/1851634795</v>
+        <v>https://music.apple.com/us/song/queens-goodbye/1858554528</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E198" t="str">
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Melancholia - EP</v>
+        <v>Mārara</v>
       </c>
       <c r="G198" t="str">
-        <v>3:24</v>
+        <v>3:46</v>
       </c>
       <c r="H198" t="str">
-        <v>JELISA</v>
+        <v>15 15</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/jelisa/1588318671</v>
+        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/bring-me-back-to-life/1851634783</v>
+        <v>https://music.apple.com/us/album/queens-goodbye/1858554036</v>
       </c>
       <c r="L198" t="str">
-        <v>Bring Me Back To Life - JELISA</v>
+        <v>Queen's Goodbye - 15 15</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>I Don't Care</v>
+        <v>Bring Me Back To Life</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/i-dont-care/1868429644</v>
+        <v>https://music.apple.com/us/song/bring-me-back-to-life/1851634795</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E199" t="str">
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>I Don't Care - Single</v>
+        <v>Melancholia - EP</v>
       </c>
       <c r="G199" t="str">
-        <v>3:49</v>
+        <v>3:24</v>
       </c>
       <c r="H199" t="str">
-        <v>Buffalo Traffic Jam</v>
+        <v>JELISA</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
+        <v>https://music.apple.com/us/artist/jelisa/1588318671</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/i-dont-care/1868429639</v>
+        <v>https://music.apple.com/us/album/bring-me-back-to-life/1851634783</v>
       </c>
       <c r="L199" t="str">
-        <v>I Don't Care - Buffalo Traffic Jam</v>
+        <v>Bring Me Back To Life - JELISA</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Elastico (feat. KATE LINN)</v>
+        <v>I Don't Care</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/elastico-feat-kate-linn/1862157500</v>
+        <v>https://music.apple.com/us/song/i-dont-care/1868429644</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E200" t="str">
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Elastico (feat. KATE LINN) - Single</v>
+        <v>I Don't Care - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>3:20</v>
+        <v>3:49</v>
       </c>
       <c r="H200" t="str">
-        <v>Fantomel</v>
+        <v>Buffalo Traffic Jam</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/fantomel/1736085960</v>
+        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/elastico-feat-kate-linn/1862157496</v>
+        <v>https://music.apple.com/us/album/i-dont-care/1868429639</v>
       </c>
       <c r="L200" t="str">
-        <v>Elastico (feat. KATE LINN) - Fantomel</v>
+        <v>I Don't Care - Buffalo Traffic Jam</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Black &amp; Gold</v>
+        <v>Elastico (feat. KATE LINN)</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/black-gold/1853914794</v>
+        <v>https://music.apple.com/us/song/elastico-feat-kate-linn/1862157500</v>
       </c>
       <c r="D201" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E201" t="str">
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>Black &amp; Gold - Single</v>
+        <v>Elastico (feat. KATE LINN) - Single</v>
       </c>
       <c r="G201" t="str">
-        <v>3:12</v>
+        <v>3:20</v>
       </c>
       <c r="H201" t="str">
-        <v>Claptone</v>
+        <v>Fantomel</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/claptone/470488523</v>
+        <v>https://music.apple.com/us/artist/fantomel/1736085960</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/black-gold/1853914793</v>
+        <v>https://music.apple.com/us/album/elastico-feat-kate-linn/1862157496</v>
       </c>
       <c r="L201" t="str">
-        <v>Black &amp; Gold - Claptone</v>
+        <v>Elastico (feat. KATE LINN) - Fantomel</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Close Your Eyes</v>
+        <v>Black &amp; Gold</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/close-your-eyes/1860632907</v>
+        <v>https://music.apple.com/us/song/black-gold/1853914794</v>
       </c>
       <c r="D202" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E202" t="str">
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>Close Your Eyes - Single</v>
+        <v>Black &amp; Gold - Single</v>
       </c>
       <c r="G202" t="str">
-        <v>3:33</v>
+        <v>3:12</v>
       </c>
       <c r="H202" t="str">
-        <v>Adam Beyer</v>
+        <v>Claptone</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/adam-beyer/101672291</v>
+        <v>https://music.apple.com/us/artist/claptone/470488523</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/close-your-eyes/1860632569</v>
+        <v>https://music.apple.com/us/album/black-gold/1853914793</v>
       </c>
       <c r="L202" t="str">
-        <v>Close Your Eyes - Adam Beyer</v>
+        <v>Black &amp; Gold - Claptone</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Movement</v>
+        <v>Close Your Eyes</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/movement/1867063797</v>
+        <v>https://music.apple.com/us/song/close-your-eyes/1860632907</v>
       </c>
       <c r="D203" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E203" t="str">
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>Movement - Single</v>
+        <v>Close Your Eyes - Single</v>
       </c>
       <c r="G203" t="str">
-        <v>3:07</v>
+        <v>3:33</v>
       </c>
       <c r="H203" t="str">
-        <v>Crankdat</v>
+        <v>Adam Beyer</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/crankdat/1073027547</v>
+        <v>https://music.apple.com/us/artist/adam-beyer/101672291</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/movement/1867063796</v>
+        <v>https://music.apple.com/us/album/close-your-eyes/1860632569</v>
       </c>
       <c r="L203" t="str">
-        <v>Movement - Crankdat</v>
+        <v>Close Your Eyes - Adam Beyer</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Ayi Giri</v>
+        <v>Movement</v>
       </c>
       <c r="B204" t="str">
         <v/>
       </c>
       <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/ayi-giri/1867306651</v>
+        <v>https://music.apple.com/us/song/movement/1867063797</v>
       </c>
       <c r="D204" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E204" t="str">
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>Ayi Giri / Dopamine Machine - Single</v>
+        <v>Movement - Single</v>
       </c>
       <c r="G204" t="str">
-        <v>3:06</v>
+        <v>3:07</v>
       </c>
       <c r="H204" t="str">
-        <v>Lilly Palmer</v>
+        <v>Crankdat</v>
       </c>
       <c r="I204" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/lilly-palmer/340777023</v>
+        <v>https://music.apple.com/us/artist/crankdat/1073027547</v>
       </c>
       <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/ayi-giri/1867306650</v>
+        <v>https://music.apple.com/us/album/movement/1867063796</v>
       </c>
       <c r="L204" t="str">
-        <v>Ayi Giri - Lilly Palmer</v>
+        <v>Movement - Crankdat</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>It's A Sin</v>
+        <v>Ayi Giri</v>
       </c>
       <c r="B205" t="str">
         <v/>
       </c>
       <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/its-a-sin/1861930282</v>
+        <v>https://music.apple.com/us/song/ayi-giri/1867306651</v>
       </c>
       <c r="D205" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E205" t="str">
         <v/>
       </c>
       <c r="F205" t="str">
-        <v>It's A Sin - Single</v>
+        <v>Ayi Giri / Dopamine Machine - Single</v>
       </c>
       <c r="G205" t="str">
-        <v>4:40</v>
+        <v>3:06</v>
       </c>
       <c r="H205" t="str">
-        <v>Ghost</v>
+        <v>Lilly Palmer</v>
       </c>
       <c r="I205" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/ghost/600730426</v>
+        <v>https://music.apple.com/us/artist/lilly-palmer/340777023</v>
       </c>
       <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/its-a-sin/1861930280</v>
+        <v>https://music.apple.com/us/album/ayi-giri/1867306650</v>
       </c>
       <c r="L205" t="str">
-        <v>It's A Sin - Ghost</v>
+        <v>Ayi Giri - Lilly Palmer</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Krushers Of The World</v>
+        <v>It's A Sin</v>
       </c>
       <c r="B206" t="str">
         <v/>
       </c>
       <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/krushers-of-the-world/1837718526</v>
+        <v>https://music.apple.com/us/song/its-a-sin/1861930282</v>
       </c>
       <c r="D206" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E206" t="str">
         <v/>
       </c>
       <c r="F206" t="str">
-        <v>Krushers Of The World</v>
+        <v>It's A Sin - Single</v>
       </c>
       <c r="G206" t="str">
-        <v>4:20</v>
+        <v>4:40</v>
       </c>
       <c r="H206" t="str">
-        <v>Kreator</v>
+        <v>Ghost</v>
       </c>
       <c r="I206" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/kreator/3258504</v>
+        <v>https://music.apple.com/us/artist/ghost/600730426</v>
       </c>
       <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/krushers-of-the-world/1837718517</v>
+        <v>https://music.apple.com/us/album/its-a-sin/1861930280</v>
       </c>
       <c r="L206" t="str">
-        <v>Krushers Of The World - Kreator</v>
+        <v>It's A Sin - Ghost</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Thoroughbreds</v>
+        <v>Krushers Of The World</v>
       </c>
       <c r="B207" t="str">
         <v/>
       </c>
       <c r="C207" t="str">
-        <v>https://music.apple.com/us/song/thoroughbreds/1863532917</v>
+        <v>https://music.apple.com/us/song/krushers-of-the-world/1837718526</v>
       </c>
       <c r="D207" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E207" t="str">
         <v/>
       </c>
       <c r="F207" t="str">
-        <v>Peace In Place</v>
+        <v>Krushers Of The World</v>
       </c>
       <c r="G207" t="str">
-        <v>3:24</v>
+        <v>4:20</v>
       </c>
       <c r="H207" t="str">
-        <v>Poison the Well</v>
+        <v>Kreator</v>
       </c>
       <c r="I207" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J207" t="str">
-        <v>https://music.apple.com/us/artist/poison-the-well/1710155</v>
+        <v>https://music.apple.com/us/artist/kreator/3258504</v>
       </c>
       <c r="K207" t="str">
-        <v>https://music.apple.com/us/album/thoroughbreds/1863532634</v>
+        <v>https://music.apple.com/us/album/krushers-of-the-world/1837718517</v>
       </c>
       <c r="L207" t="str">
-        <v>Thoroughbreds - Poison the Well</v>
+        <v>Krushers Of The World - Kreator</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
+        <v>Thoroughbreds</v>
+      </c>
+      <c r="B208" t="str">
+        <v/>
+      </c>
+      <c r="C208" t="str">
+        <v>https://music.apple.com/us/song/thoroughbreds/1863532917</v>
+      </c>
+      <c r="D208" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E208" t="str">
+        <v/>
+      </c>
+      <c r="F208" t="str">
+        <v>Peace In Place</v>
+      </c>
+      <c r="G208" t="str">
+        <v>3:24</v>
+      </c>
+      <c r="H208" t="str">
+        <v>Poison the Well</v>
+      </c>
+      <c r="I208" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J208" t="str">
+        <v>https://music.apple.com/us/artist/poison-the-well/1710155</v>
+      </c>
+      <c r="K208" t="str">
+        <v>https://music.apple.com/us/album/thoroughbreds/1863532634</v>
+      </c>
+      <c r="L208" t="str">
+        <v>Thoroughbreds - Poison the Well</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
         <v>Adversary</v>
       </c>
-      <c r="B208" t="str">
-        <v/>
-      </c>
-      <c r="C208" t="str">
+      <c r="B209" t="str">
+        <v/>
+      </c>
+      <c r="C209" t="str">
         <v>https://music.apple.com/us/song/adversary/1861901940</v>
       </c>
-      <c r="D208" t="str">
-        <v>2026-01-22</v>
-      </c>
-      <c r="E208" t="str">
-        <v/>
-      </c>
-      <c r="F208" t="str">
+      <c r="D209" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E209" t="str">
+        <v/>
+      </c>
+      <c r="F209" t="str">
         <v>Descent</v>
       </c>
-      <c r="G208" t="str">
+      <c r="G209" t="str">
         <v>3:17</v>
       </c>
-      <c r="H208" t="str">
+      <c r="H209" t="str">
         <v>Immolation</v>
       </c>
-      <c r="I208" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J208" t="str">
+      <c r="I209" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J209" t="str">
         <v>https://music.apple.com/us/artist/immolation/64874488</v>
       </c>
-      <c r="K208" t="str">
+      <c r="K209" t="str">
         <v>https://music.apple.com/us/album/adversary/1861901597</v>
       </c>
-      <c r="L208" t="str">
+      <c r="L209" t="str">
         <v>Adversary - Immolation</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L208"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L209"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-01-week04/titles.xlsx
+++ b/data/global/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>2:59</v>
@@ -477,7 +477,7 @@
         <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:21</v>
@@ -553,7 +553,7 @@
         <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:34</v>
@@ -1921,7 +1921,7 @@
         <v>Louie TheSinger "Texas Gold" Official Music Video</v>
       </c>
       <c r="B41" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>4:09</v>

--- a/data/global/2026-01-week04/titles.xlsx
+++ b/data/global/2026-01-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L209"/>
+  <dimension ref="A1:L189"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -439,7 +439,7 @@
         <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>2:59</v>
@@ -477,7 +477,7 @@
         <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:21</v>
@@ -667,7 +667,7 @@
         <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:06</v>
@@ -705,7 +705,7 @@
         <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G9" t="str">
         <v>3:21</v>
@@ -1123,7 +1123,7 @@
         <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>2:25</v>
@@ -1161,7 +1161,7 @@
         <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B21" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>1:14</v>
@@ -1199,7 +1199,7 @@
         <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B22" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G22" t="str">
         <v>2:59</v>
@@ -1237,7 +1237,7 @@
         <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B23" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>2:29</v>
@@ -1275,7 +1275,7 @@
         <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B24" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G24" t="str">
         <v>2:34</v>
@@ -1313,7 +1313,7 @@
         <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G25" t="str">
         <v>3:48</v>
@@ -1351,7 +1351,7 @@
         <v>The Beaches - I Ran (So Far Away) Official Audio</v>
       </c>
       <c r="B26" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>3:32</v>
@@ -1389,7 +1389,7 @@
         <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
       </c>
       <c r="B27" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G27" t="str">
         <v>3:49</v>
@@ -1427,7 +1427,7 @@
         <v>Madison Beer - bad enough (Official Music Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>4:28</v>
@@ -1465,7 +1465,7 @@
         <v>Ty Myers - Message to You (Official Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>3:37</v>
@@ -1503,7 +1503,7 @@
         <v>Megan Moroney - Wish I Didn't (Official Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>3:35</v>
@@ -1693,7 +1693,7 @@
         <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
       </c>
       <c r="B35" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>4:11</v>
@@ -1883,7 +1883,7 @@
         <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>3:59</v>
@@ -2187,7 +2187,7 @@
         <v>Bruno Mars - I Just Might [Official Music Video]</v>
       </c>
       <c r="B48" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G48" t="str">
         <v>3:33</v>
@@ -2225,7 +2225,7 @@
         <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
       </c>
       <c r="B49" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G49" t="str">
         <v>2:53</v>
@@ -2263,7 +2263,7 @@
         <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G50" t="str">
         <v>4:11</v>
@@ -2301,7 +2301,7 @@
         <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G51" t="str">
         <v>2:45</v>
@@ -2339,7 +2339,7 @@
         <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G52" t="str">
         <v>4:00</v>
@@ -2377,7 +2377,7 @@
         <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
       </c>
       <c r="B53" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G53" t="str">
         <v>3:27</v>
@@ -3099,7 +3099,7 @@
         <v>Emilia Tarrant - Break Up With Myself</v>
       </c>
       <c r="B72" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=3N7iKwqENP0</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G72" t="str">
         <v>4:04</v>
@@ -3517,7 +3517,7 @@
         <v>Dasha - Here For The Party (Official Audio)</v>
       </c>
       <c r="B83" t="str">
-        <v>3 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=rSO9oYUnO2k</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>3 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G83" t="str">
         <v>3:30</v>
@@ -4274,13 +4274,13 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Wish I Didn't</v>
+        <v>Opening Night</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/wish-i-didnt/1851297073</v>
+        <v>https://music.apple.com/us/song/opening-night/1870313501</v>
       </c>
       <c r="D103" t="str">
         <v>2026-01-23</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Cloud 9</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G103" t="str">
-        <v>3:29</v>
+        <v>4:19</v>
       </c>
       <c r="H103" t="str">
-        <v>Megan Moroney</v>
+        <v>Arctic Monkeys</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
+        <v>https://music.apple.com/us/artist/arctic-monkeys/62820413</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/wish-i-didnt/1851296746</v>
+        <v>https://music.apple.com/us/album/opening-night/1870313498</v>
       </c>
       <c r="L103" t="str">
-        <v>Wish I Didn't - Megan Moroney</v>
+        <v>Opening Night - Arctic Monkeys</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>AIR FORCE (BLACK DEMARCO)</v>
+        <v>FLACKITO JODYE (feat. Tokischa)</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/air-force-black-demarco/1862935169</v>
+        <v>https://music.apple.com/us/song/flackito-jodye-feat-tokischa/1870968779</v>
       </c>
       <c r="D104" t="str">
         <v>2026-01-23</v>
@@ -4330,7 +4330,7 @@
         <v>Don't Be Dumb</v>
       </c>
       <c r="G104" t="str">
-        <v>3:44</v>
+        <v>2:20</v>
       </c>
       <c r="H104" t="str">
         <v>A$AP Rocky</v>
@@ -4342,21 +4342,21 @@
         <v>https://music.apple.com/us/artist/a%24ap-rocky/481488005</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/air-force-black-demarco/1862934946</v>
+        <v>https://music.apple.com/us/album/flackito-jodye-feat-tokischa/1870968596</v>
       </c>
       <c r="L104" t="str">
-        <v>AIR FORCE (BLACK DEMARCO) - A$AP Rocky</v>
+        <v>FLACKITO JODYE (feat. Tokischa) - A$AP Rocky</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Wall of Sound</v>
+        <v>CAMBIARÉ</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/wall-of-sound/1852566426</v>
+        <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
       </c>
       <c r="D105" t="str">
         <v>2026-01-23</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Wuthering Heights</v>
+        <v>CAMBIARÉ - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>2:24</v>
+        <v>3:01</v>
       </c>
       <c r="H105" t="str">
-        <v>Charli xcx</v>
+        <v>Luis Fonsi</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
+        <v>https://music.apple.com/us/artist/luis-fonsi/102834</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/wall-of-sound/1852566184</v>
+        <v>https://music.apple.com/us/album/cambiar%C3%A9/1867545265</v>
       </c>
       <c r="L105" t="str">
-        <v>Wall of Sound - Charli xcx</v>
+        <v>CAMBIARÉ - Luis Fonsi</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Where's My Phone?</v>
+        <v>Last of a Dying Breed</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/wheres-my-phone/1860622553</v>
+        <v>https://music.apple.com/us/song/last-of-a-dying-breed/1849706852</v>
       </c>
       <c r="D106" t="str">
         <v>2026-01-23</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Nothing's About to Happen to Me</v>
+        <v>Piss In The Wind</v>
       </c>
       <c r="G106" t="str">
-        <v>3:09</v>
+        <v>2:29</v>
       </c>
       <c r="H106" t="str">
-        <v>Mitski</v>
+        <v>Joji</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/mitski/497546276</v>
+        <v>https://music.apple.com/us/artist/joji/1258279972</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/wheres-my-phone/1860622550</v>
+        <v>https://music.apple.com/us/album/last-of-a-dying-breed/1849706656</v>
       </c>
       <c r="L106" t="str">
-        <v>Where's My Phone? - Mitski</v>
+        <v>Last of a Dying Breed - Joji</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>100</v>
+        <v>High Key</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/100/1858754874</v>
+        <v>https://music.apple.com/us/song/high-key/1847702418</v>
       </c>
       <c r="D107" t="str">
         <v>2026-01-23</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Do You Still Love Me?</v>
+        <v>Vacancy</v>
       </c>
       <c r="G107" t="str">
-        <v>3:54</v>
+        <v>2:12</v>
       </c>
       <c r="H107" t="str">
-        <v>Ella Mai</v>
+        <v>Ari Lennox</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/ella-mai/1160482144</v>
+        <v>https://music.apple.com/us/artist/ari-lennox/448854570</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/100/1858754868</v>
+        <v>https://music.apple.com/us/album/high-key/1847702412</v>
       </c>
       <c r="L107" t="str">
-        <v>100 - Ella Mai</v>
+        <v>High Key - Ari Lennox</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Por un P*****o no se llora (Salud mi Reina)</v>
+        <v>scared</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/por-un-p-o-no-se-llora-salud-mi-reina/1862587826</v>
+        <v>https://music.apple.com/us/song/scared/1862292863</v>
       </c>
       <c r="D108" t="str">
         <v>2026-01-23</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Por un P*****o no se llora (Salud mi Reina) - Single</v>
+        <v>scared - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>2:31</v>
+        <v>4:03</v>
       </c>
       <c r="H108" t="str">
-        <v>Manuel Turizo</v>
+        <v>Fred again..</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/manuel-turizo/1186116587</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/por-un-p-o-no-se-llora-salud-mi-reina/1862587821</v>
+        <v>https://music.apple.com/us/album/scared/1862292862</v>
       </c>
       <c r="L108" t="str">
-        <v>Por un P*****o no se llora (Salud mi Reina) - Manuel Turizo</v>
+        <v>scared - Fred again..</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Opening Night</v>
+        <v>Death of Love</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/opening-night/1870313501</v>
+        <v>https://music.apple.com/us/song/death-of-love/1862353786</v>
       </c>
       <c r="D109" t="str">
         <v>2026-01-23</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>HELP(2)</v>
+        <v>Trying Times</v>
       </c>
       <c r="G109" t="str">
-        <v>4:19</v>
+        <v>3:26</v>
       </c>
       <c r="H109" t="str">
-        <v>Arctic Monkeys</v>
+        <v>James Blake</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/arctic-monkeys/62820413</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/opening-night/1870313498</v>
+        <v>https://music.apple.com/us/album/death-of-love/1862353780</v>
       </c>
       <c r="L109" t="str">
-        <v>Opening Night - Arctic Monkeys</v>
+        <v>Death of Love - James Blake</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>L.U.C.K.Y</v>
+        <v>Big Ole Fancy House</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/l-u-c-k-y/1861895147</v>
+        <v>https://music.apple.com/us/song/big-ole-fancy-house/1862624759</v>
       </c>
       <c r="D110" t="str">
         <v>2026-01-23</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Ö</v>
+        <v>Parker McCollum (The Deluxe Edition)</v>
       </c>
       <c r="G110" t="str">
-        <v>2:18</v>
+        <v>4:03</v>
       </c>
       <c r="H110" t="str">
-        <v>Fcukers</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
+        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/l-u-c-k-y/1861895134</v>
+        <v>https://music.apple.com/us/album/big-ole-fancy-house/1862624506</v>
       </c>
       <c r="L110" t="str">
-        <v>L.U.C.K.Y - Fcukers</v>
+        <v>Big Ole Fancy House - Parker McCollum</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Reclusive</v>
+        <v>Flo Jackson</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/reclusive/1860405760</v>
+        <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
       </c>
       <c r="D111" t="str">
         <v>2026-01-23</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>sounds for someone</v>
+        <v>Flo Jackson - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>3:06</v>
+        <v>2:23</v>
       </c>
       <c r="H111" t="str">
-        <v>Elmiene</v>
+        <v>Flo Milli</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/elmiene/1599562425</v>
+        <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/reclusive/1860405416</v>
+        <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
       </c>
       <c r="L111" t="str">
-        <v>Reclusive - Elmiene</v>
+        <v>Flo Jackson - Flo Milli</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Flo Jackson</v>
+        <v>Site Unseen (feat. Waxahatchee)</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
+        <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
       </c>
       <c r="D112" t="str">
         <v>2026-01-23</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Flo Jackson - Single</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G112" t="str">
-        <v>2:23</v>
+        <v>2:46</v>
       </c>
       <c r="H112" t="str">
-        <v>Flo Milli</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
+        <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
       </c>
       <c r="L112" t="str">
-        <v>Flo Jackson - Flo Milli</v>
+        <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Site Unseen (feat. Waxahatchee)</v>
+        <v>Puppet Parade</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
+        <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
       </c>
       <c r="D113" t="str">
         <v>2026-01-23</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Creature of Habit</v>
+        <v>Megadeth</v>
       </c>
       <c r="G113" t="str">
-        <v>2:46</v>
+        <v>4:40</v>
       </c>
       <c r="H113" t="str">
-        <v>Courtney Barnett</v>
+        <v>Megadeth</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/megadeth/488289</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
+        <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
       </c>
       <c r="L113" t="str">
-        <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
+        <v>Puppet Parade - Megadeth</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Raft In The Sea</v>
+        <v>To Love Somebody</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/raft-in-the-sea/1847662987</v>
+        <v>https://music.apple.com/us/song/to-love-somebody/1859630040</v>
       </c>
       <c r="D114" t="str">
         <v>2026-01-23</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Cerulean</v>
+        <v>Cruel World</v>
       </c>
       <c r="G114" t="str">
-        <v>3:35</v>
+        <v>3:57</v>
       </c>
       <c r="H114" t="str">
-        <v>Danny L Harle</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/danny-l-harle/985576556</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/raft-in-the-sea/1847662970</v>
+        <v>https://music.apple.com/us/album/to-love-somebody/1859629846</v>
       </c>
       <c r="L114" t="str">
-        <v>Raft In The Sea - Danny L Harle</v>
+        <v>To Love Somebody - Holly Humberstone</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Good Night Baby</v>
+        <v>Nothing Is Impossible With You</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/good-night-baby/1849917462</v>
+        <v>https://music.apple.com/us/song/nothing-is-impossible-with-you/1870691236</v>
       </c>
       <c r="D115" t="str">
         <v>2026-01-23</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Butterfly</v>
+        <v>Nothing Is Impossible With You - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>4:21</v>
+        <v>4:14</v>
       </c>
       <c r="H115" t="str">
-        <v>Daphni</v>
+        <v>Cleo Sol</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/daphni/1282779393</v>
+        <v>https://music.apple.com/us/artist/cleo-sol/459710289</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/good-night-baby/1849916838</v>
+        <v>https://music.apple.com/us/album/nothing-is-impossible-with-you/1870691227</v>
       </c>
       <c r="L115" t="str">
-        <v>Good Night Baby - Daphni</v>
+        <v>Nothing Is Impossible With You - Cleo Sol</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Puppet Parade</v>
+        <v>HYPNOTIZE</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
+        <v>https://music.apple.com/us/song/hypnotize/1861009528</v>
       </c>
       <c r="D116" t="str">
         <v>2026-01-23</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Megadeth</v>
+        <v>THE CORE - 核</v>
       </c>
       <c r="G116" t="str">
-        <v>4:40</v>
+        <v>2:50</v>
       </c>
       <c r="H116" t="str">
-        <v>Megadeth</v>
+        <v>XG</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/megadeth/488289</v>
+        <v>https://music.apple.com/us/artist/xg/1609409493</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
+        <v>https://music.apple.com/us/album/hypnotize/1861009513</v>
       </c>
       <c r="L116" t="str">
-        <v>Puppet Parade - Megadeth</v>
+        <v>HYPNOTIZE - XG</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>CAMBIARÉ</v>
+        <v>Dead End</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
+        <v>https://music.apple.com/us/song/dead-end/1862845874</v>
       </c>
       <c r="D117" t="str">
         <v>2026-01-23</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>CAMBIARÉ - Single</v>
+        <v>Ricochet</v>
       </c>
       <c r="G117" t="str">
-        <v>3:01</v>
+        <v>4:05</v>
       </c>
       <c r="H117" t="str">
-        <v>Luis Fonsi</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/luis-fonsi/102834</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/cambiar%C3%A9/1867545265</v>
+        <v>https://music.apple.com/us/album/dead-end/1862845733</v>
       </c>
       <c r="L117" t="str">
-        <v>CAMBIARÉ - Luis Fonsi</v>
+        <v>Dead End - Snail Mail</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Orange County (feat. Bizarrap, Kara Jackson &amp; Anoushka Shankar)</v>
+        <v>Do I Wanna Know?</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/orange-county-feat-bizarrap-kara-jackson-anoushka-shankar/1837237867</v>
+        <v>https://music.apple.com/us/song/do-i-wanna-know/1870931500</v>
       </c>
       <c r="D118" t="str">
         <v>2026-01-23</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>The Mountain</v>
+        <v>Do I Wanna Know? - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:28</v>
+        <v>3:52</v>
       </c>
       <c r="H118" t="str">
-        <v>Gorillaz</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/gorillaz/567072</v>
+        <v>https://music.apple.com/us/artist/dove-cameron/599822740</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/orange-county-feat-bizarrap-kara-jackson-anoushka-shankar/1837237742</v>
+        <v>https://music.apple.com/us/album/do-i-wanna-know/1870931327</v>
       </c>
       <c r="L118" t="str">
-        <v>Orange County (feat. Bizarrap, Kara Jackson &amp; Anoushka Shankar) - Gorillaz</v>
+        <v>Do I Wanna Know? - Dove Cameron</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Lluvia</v>
+        <v>Una y Otra Vez</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/lluvia/1868476403</v>
+        <v>https://music.apple.com/us/song/una-y-otra-vez/1868792926</v>
       </c>
       <c r="D119" t="str">
         <v>2026-01-23</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>LA 8VA MARAVILLA</v>
+        <v>K de Karma (Apple Music Edition)</v>
       </c>
       <c r="G119" t="str">
-        <v>3:24</v>
+        <v>3:02</v>
       </c>
       <c r="H119" t="str">
-        <v>Arcángel</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/arc%C3%A1ngel/28215216</v>
+        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/lluvia/1868476390</v>
+        <v>https://music.apple.com/us/album/una-y-otra-vez/1868792704</v>
       </c>
       <c r="L119" t="str">
-        <v>Lluvia - Arcángel</v>
+        <v>Una y Otra Vez - Kenia Os</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Knife</v>
+        <v>BAD</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/knife/1862720450</v>
+        <v>https://music.apple.com/us/song/bad/1869095326</v>
       </c>
       <c r="D120" t="str">
         <v>2026-01-23</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>THE SIN : VANISH</v>
+        <v>BAD - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>2:19</v>
+        <v>2:15</v>
       </c>
       <c r="H120" t="str">
-        <v>ENHYPEN</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/enhypen/1541011620</v>
+        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/knife/1862720020</v>
+        <v>https://music.apple.com/us/album/bad/1869095325</v>
       </c>
       <c r="L120" t="str">
-        <v>Knife - ENHYPEN</v>
+        <v>BAD - Chelsea Cutler</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>bad enough</v>
+        <v>Losing You</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/bad-enough/1846949125</v>
+        <v>https://music.apple.com/us/song/losing-you/1863525495</v>
       </c>
       <c r="D121" t="str">
         <v>2026-01-23</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>locket</v>
+        <v>F.I.G</v>
       </c>
       <c r="G121" t="str">
-        <v>3:42</v>
+        <v>2:22</v>
       </c>
       <c r="H121" t="str">
-        <v>Madison Beer</v>
+        <v>Naomi Scott</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/madison-beer/696146587</v>
+        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/bad-enough/1846949115</v>
+        <v>https://music.apple.com/us/album/losing-you/1863525485</v>
       </c>
       <c r="L121" t="str">
-        <v>bad enough - Madison Beer</v>
+        <v>Losing You - Naomi Scott</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>bad</v>
+        <v>Me Voy A La C******a</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/bad/1851566880</v>
+        <v>https://music.apple.com/us/song/me-voy-a-la-c-a/1867850749</v>
       </c>
       <c r="D122" t="str">
         <v>2026-01-23</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>bad - Single</v>
+        <v>Infinito</v>
       </c>
       <c r="G122" t="str">
-        <v>2:41</v>
+        <v>2:14</v>
       </c>
       <c r="H122" t="str">
-        <v>Saint Harison</v>
+        <v>Yandel</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
+        <v>https://music.apple.com/us/artist/yandel/72929426</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/bad/1851566879</v>
+        <v>https://music.apple.com/us/album/me-voy-a-la-c-a/1867850739</v>
       </c>
       <c r="L122" t="str">
-        <v>bad - Saint Harison</v>
+        <v>Me Voy A La C******a - Yandel</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Beat Yourself Up</v>
+        <v>Sexy For Me</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/beat-yourself-up/1845189973</v>
+        <v>https://music.apple.com/us/song/sexy-for-me/1867897421</v>
       </c>
       <c r="D123" t="str">
         <v>2026-01-23</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Whatever's Clever!</v>
+        <v>The Last Dance (Part 1)</v>
       </c>
       <c r="G123" t="str">
-        <v>2:58</v>
+        <v>2:08</v>
       </c>
       <c r="H123" t="str">
-        <v>Charlie Puth</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v>https://music.apple.com/us/artist/jason-derulo/259118085</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/beat-yourself-up/1845189970</v>
+        <v>https://music.apple.com/us/album/sexy-for-me/1867897420</v>
       </c>
       <c r="L123" t="str">
-        <v>Beat Yourself Up - Charlie Puth</v>
+        <v>Sexy For Me - Jason Derulo</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Roommates</v>
+        <v>Turbulence</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/roommates/1854567105</v>
+        <v>https://music.apple.com/us/song/turbulence/1867908449</v>
       </c>
       <c r="D124" t="str">
         <v>2026-01-23</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>luck... or something</v>
+        <v>REAL, Vol. 1 - EP</v>
       </c>
       <c r="G124" t="str">
-        <v>2:52</v>
+        <v>2:25</v>
       </c>
       <c r="H124" t="str">
-        <v>Hilary Duff</v>
+        <v>Wizkid</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/hilary-duff/3296003</v>
+        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/roommates/1854567102</v>
+        <v>https://music.apple.com/us/album/turbulence/1867908237</v>
       </c>
       <c r="L124" t="str">
-        <v>Roommates - Hilary Duff</v>
+        <v>Turbulence - Wizkid</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>2SIDED</v>
+        <v>I’m Good (From The Movie “GOAT”)</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/2sided/1862571197</v>
+        <v>https://music.apple.com/us/song/im-good-from-the-movie-goat/1870623298</v>
       </c>
       <c r="D125" t="str">
         <v>2026-01-23</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Ambiguous Desire</v>
+        <v>GOAT (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G125" t="str">
-        <v>2:57</v>
+        <v>2:59</v>
       </c>
       <c r="H125" t="str">
-        <v>Arlo Parks</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/2sided/1862570378</v>
+        <v>https://music.apple.com/us/album/im-good-from-the-movie-goat/1870623290</v>
       </c>
       <c r="L125" t="str">
-        <v>2SIDED - Arlo Parks</v>
+        <v>I’m Good (From The Movie “GOAT”) - Jelly Roll</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Feel Alive</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/feel-alive/1851368171</v>
+        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
       </c>
       <c r="D126" t="str">
         <v>2026-01-23</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>ODYSSEY</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>2:48</v>
+        <v>3:47</v>
       </c>
       <c r="H126" t="str">
-        <v>ILLENIUM</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/illenium/645420096</v>
+        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/feel-alive/1851368154</v>
+        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
       </c>
       <c r="L126" t="str">
-        <v>Feel Alive - ILLENIUM</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>God Spoke</v>
+        <v>ESCONDIDAS</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/god-spoke/1853069638</v>
+        <v>https://music.apple.com/us/song/escondidas/1860972187</v>
       </c>
       <c r="D127" t="str">
         <v>2026-01-23</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>COSMIC OPERA ACT I</v>
+        <v>SILENCIO HABLA</v>
       </c>
       <c r="G127" t="str">
-        <v>1:14</v>
+        <v>2:53</v>
       </c>
       <c r="H127" t="str">
-        <v>Labrinth</v>
+        <v>Oscar Ortiz</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/oscar-ortiz/1680604969</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/god-spoke/1853069628</v>
+        <v>https://music.apple.com/us/album/escondidas/1860972173</v>
       </c>
       <c r="L127" t="str">
-        <v>God Spoke - Labrinth</v>
+        <v>ESCONDIDAS - Oscar Ortiz</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Risk Takers</v>
+        <v>Alabama Beauty Queen</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/risk-takers/1866642666</v>
+        <v>https://music.apple.com/us/song/alabama-beauty-queen/1846658485</v>
       </c>
       <c r="D128" t="str">
         <v>2026-01-23</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>El Mundo Es Tuyo (Inspired by Clika The Movie)</v>
+        <v>Act I</v>
       </c>
       <c r="G128" t="str">
-        <v>2:35</v>
+        <v>3:43</v>
       </c>
       <c r="H128" t="str">
-        <v>Herencia de Patrones</v>
+        <v>Kashus Culpepper</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/herencia-de-patrones/1295294734</v>
+        <v>https://music.apple.com/us/artist/kashus-culpepper/1634883369</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/risk-takers/1866642665</v>
+        <v>https://music.apple.com/us/album/alabama-beauty-queen/1846658477</v>
       </c>
       <c r="L128" t="str">
-        <v>Risk Takers - Herencia de Patrones</v>
+        <v>Alabama Beauty Queen - Kashus Culpepper</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Never Comin' Back</v>
+        <v>Imposter</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/never-comin-back/1862970557</v>
+        <v>https://music.apple.com/us/song/imposter/1842408050</v>
       </c>
       <c r="D129" t="str">
         <v>2026-01-23</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Never Comin' Back - Single</v>
+        <v>How Did I Get Here?</v>
       </c>
       <c r="G129" t="str">
-        <v>3:57</v>
+        <v>2:38</v>
       </c>
       <c r="H129" t="str">
-        <v>Flatland Cavalry</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/never-comin-back/1862970555</v>
+        <v>https://music.apple.com/us/album/imposter/1842408037</v>
       </c>
       <c r="L129" t="str">
-        <v>Never Comin' Back - Flatland Cavalry</v>
+        <v>Imposter - Louis Tomlinson</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Lay Your Heartache Onto Mine (Songs From and Inspired by the Paramount+ Original Series Landman (Volume II))</v>
+        <v>Puddles (Zero 7 Remix)</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/lay-your-heartache-onto-mine-songs-from-and-inspired/1867273711</v>
+        <v>https://music.apple.com/us/song/puddles-zero-7-remix/1869474314</v>
       </c>
       <c r="D130" t="str">
         <v>2026-01-23</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Lay Your Heartache Onto Mine (Songs From and Inspired by the Paramount+ Original Series Landman (Volume II)) - Single</v>
+        <v>Puddles (Zero 7 Remix) - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:18</v>
+        <v>6:01</v>
       </c>
       <c r="H130" t="str">
-        <v>Carter Faith</v>
+        <v>Not for Radio</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/carter-faith/1489205896</v>
+        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/lay-your-heartache-onto-mine-songs-from-and-inspired/1867273471</v>
+        <v>https://music.apple.com/us/album/puddles-zero-7-remix/1869474313</v>
       </c>
       <c r="L130" t="str">
-        <v>Lay Your Heartache Onto Mine (Songs From and Inspired by the Paramount+ Original Series Landman (Volume II)) - Carter Faith</v>
+        <v>Puddles (Zero 7 Remix) - Not for Radio</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
+        <v>Little Miss (Misdemeanor)</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
+        <v>https://music.apple.com/us/song/little-miss-misdemeanor/1870996491</v>
       </c>
       <c r="D131" t="str">
         <v>2026-01-23</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
+        <v>Little Miss (Misdemeanor) - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:47</v>
+        <v>2:24</v>
       </c>
       <c r="H131" t="str">
-        <v>Dolly Parton</v>
+        <v>GIRLSET</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
+        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
+        <v>https://music.apple.com/us/album/little-miss-misdemeanor/1870996490</v>
       </c>
       <c r="L131" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
+        <v>Little Miss (Misdemeanor) - GIRLSET</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Traffic Lights (feat. Thom Yorke)</v>
+        <v>I Could Get Used To This</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/traffic-lights-feat-thom-yorke/1861644315</v>
+        <v>https://music.apple.com/us/song/i-could-get-used-to-this/1867222996</v>
       </c>
       <c r="D132" t="str">
         <v>2026-01-23</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Honora</v>
+        <v>I Could Get Used To This - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>5:41</v>
+        <v>3:41</v>
       </c>
       <c r="H132" t="str">
-        <v>Flea</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/flea/463953572</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/traffic-lights-feat-thom-yorke/1861644307</v>
+        <v>https://music.apple.com/us/album/i-could-get-used-to-this/1867222992</v>
       </c>
       <c r="L132" t="str">
-        <v>Traffic Lights (feat. Thom Yorke) - Flea</v>
+        <v>I Could Get Used To This - Jessie Ware</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Inferno (from "Heated Rivalry")</v>
+        <v>LA VILLA</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/inferno-from-heated-rivalry/1868783886</v>
+        <v>https://music.apple.com/us/song/la-villa/1847678152</v>
       </c>
       <c r="D133" t="str">
         <v>2026-01-23</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Heated Rivalry (Original Series Soundtrack)</v>
+        <v>HOPI SENDÉ</v>
       </c>
       <c r="G133" t="str">
-        <v>4:26</v>
+        <v>3:12</v>
       </c>
       <c r="H133" t="str">
-        <v>Peter Peter</v>
+        <v>Ryan Castro</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/peter-peter/71305428</v>
+        <v>https://music.apple.com/us/artist/ryan-castro/1263552447</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/inferno-from-heated-rivalry/1868783596</v>
+        <v>https://music.apple.com/us/album/la-villa/1847678143</v>
       </c>
       <c r="L133" t="str">
-        <v>Inferno (from "Heated Rivalry") - Peter Peter</v>
+        <v>LA VILLA - Ryan Castro</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Yo Yan</v>
+        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700)</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/yo-yan/1867888651</v>
+        <v>https://music.apple.com/us/song/lit-effect-feat-bktherula-lazer-dim-700/1868519613</v>
       </c>
       <c r="D134" t="str">
         <v>2026-01-23</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Kora - Single</v>
+        <v>Strictly 4 The Scythe</v>
       </c>
       <c r="G134" t="str">
-        <v>2:00</v>
+        <v>3:27</v>
       </c>
       <c r="H134" t="str">
-        <v>Skrillex</v>
+        <v>Denzel Curry</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
+        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/yo-yan/1867888650</v>
+        <v>https://music.apple.com/us/album/lit-effect-feat-bktherula-lazer-dim-700/1868519270</v>
       </c>
       <c r="L134" t="str">
-        <v>Yo Yan - Skrillex</v>
+        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700) - Denzel Curry</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Jogodo</v>
+        <v>Thick One</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/jogodo/1867908454</v>
+        <v>https://music.apple.com/us/song/thick-one/1868515478</v>
       </c>
       <c r="D135" t="str">
         <v>2026-01-23</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>REAL, Vol. 1 - EP</v>
+        <v>Part 3</v>
       </c>
       <c r="G135" t="str">
-        <v>3:08</v>
+        <v>2:49</v>
       </c>
       <c r="H135" t="str">
-        <v>Wizkid</v>
+        <v>42 Dugg</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
+        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/jogodo/1867908237</v>
+        <v>https://music.apple.com/us/album/thick-one/1868515223</v>
       </c>
       <c r="L135" t="str">
-        <v>Jogodo - Wizkid</v>
+        <v>Thick One - 42 Dugg</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Made It Out Alive</v>
+        <v>How Much Did You Get For Your Soul</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/made-it-out-alive/1867596345</v>
+        <v>https://music.apple.com/us/song/how-much-did-you-get-for-your-soul/1843195678</v>
       </c>
       <c r="D136" t="str">
         <v>2026-01-23</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Suffering From Success</v>
+        <v>World's Gone Wrong</v>
       </c>
       <c r="G136" t="str">
-        <v>3:00</v>
+        <v>3:59</v>
       </c>
       <c r="H136" t="str">
-        <v>Dee Mula</v>
+        <v>Lucinda Williams</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/dee-mula/1330325377</v>
+        <v>https://music.apple.com/us/artist/lucinda-williams/267658</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/made-it-out-alive/1867596343</v>
+        <v>https://music.apple.com/us/album/how-much-did-you-get-for-your-soul/1843195660</v>
       </c>
       <c r="L136" t="str">
-        <v>Made It Out Alive - Dee Mula</v>
+        <v>How Much Did You Get For Your Soul - Lucinda Williams</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>One of Them Ones</v>
+        <v>THUM</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/one-of-them-ones/1868850365</v>
+        <v>https://music.apple.com/us/song/thum/1863009362</v>
       </c>
       <c r="D137" t="str">
         <v>2026-01-23</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>One of Them Ones - Single</v>
+        <v>THUM - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>3:05</v>
+        <v>2:11</v>
       </c>
       <c r="H137" t="str">
-        <v>Veeze</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/veeze/1464999308</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/one-of-them-ones/1868850364</v>
+        <v>https://music.apple.com/us/album/thum/1863009357</v>
       </c>
       <c r="L137" t="str">
-        <v>One of Them Ones - Veeze</v>
+        <v>THUM - Violet Grohl</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Como Es Que Se Hace</v>
+        <v>(I'm a) Rock "N" Roller</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/como-es-que-se-hace/1864227584</v>
+        <v>https://music.apple.com/us/song/im-a-rock-n-roller/1839888014</v>
       </c>
       <c r="D138" t="str">
         <v>2026-01-23</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Como Es Que Se Hace - Single</v>
+        <v>The Great Satan</v>
       </c>
       <c r="G138" t="str">
-        <v>3:25</v>
+        <v>3:32</v>
       </c>
       <c r="H138" t="str">
-        <v>Yandel</v>
+        <v>Rob Zombie</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/yandel/72929426</v>
+        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/como-es-que-se-hace/1864227582</v>
+        <v>https://music.apple.com/us/album/im-a-rock-n-roller/1839887790</v>
       </c>
       <c r="L138" t="str">
-        <v>Como Es Que Se Hace - Yandel</v>
+        <v>(I'm a) Rock "N" Roller - Rob Zombie</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Ever Since U Left Me (I Went Deaf)</v>
+        <v>Excuses For Love</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/ever-since-u-left-me-i-went-deaf/1863124175</v>
+        <v>https://music.apple.com/us/song/excuses-for-love/1856034295</v>
       </c>
       <c r="D139" t="str">
         <v>2026-01-23</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Coke Wave 3.5: Narcos</v>
+        <v>Hyperlove</v>
       </c>
       <c r="G139" t="str">
-        <v>2:16</v>
+        <v>3:04</v>
       </c>
       <c r="H139" t="str">
-        <v>French Montana</v>
+        <v>MIKA</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/french-montana/475816358</v>
+        <v>https://music.apple.com/us/artist/mika/184932871</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/ever-since-u-left-me-i-went-deaf/1863124168</v>
+        <v>https://music.apple.com/us/album/excuses-for-love/1856033810</v>
       </c>
       <c r="L139" t="str">
-        <v>Ever Since U Left Me (I Went Deaf) - French Montana</v>
+        <v>Excuses For Love - MIKA</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Ay Dale</v>
+        <v>3 Tears</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/ay-dale/1862897966</v>
+        <v>https://music.apple.com/us/song/3-tears/1861504548</v>
       </c>
       <c r="D140" t="str">
         <v>2026-01-23</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Ay Dale - Single</v>
+        <v>3 Tears - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>2:26</v>
+        <v>2:50</v>
       </c>
       <c r="H140" t="str">
-        <v>Farruko</v>
+        <v>Mergui</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/farruko/364377482</v>
+        <v>https://music.apple.com/us/artist/mergui/1423596903</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/ay-dale/1862897623</v>
+        <v>https://music.apple.com/us/album/3-tears/1861504545</v>
       </c>
       <c r="L140" t="str">
-        <v>Ay Dale - Farruko</v>
+        <v>3 Tears - Mergui</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Teary Eyes</v>
+        <v>Church Girl</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/teary-eyes/1869534187</v>
+        <v>https://music.apple.com/us/song/church-girl/1862008542</v>
       </c>
       <c r="D141" t="str">
         <v>2026-01-23</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Slime Cry</v>
+        <v>Church Girl - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>2:45</v>
+        <v>3:19</v>
       </c>
       <c r="H141" t="str">
-        <v>YoungBoy Never Broke Again</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/youngboy-never-broke-again/1168822104</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/teary-eyes/1869534167</v>
+        <v>https://music.apple.com/us/album/church-girl/1862008535</v>
       </c>
       <c r="L141" t="str">
-        <v>Teary Eyes - YoungBoy Never Broke Again</v>
+        <v>Church Girl - Carly Pearce</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Bop It</v>
+        <v>Funeral</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/bop-it/1867023470</v>
+        <v>https://music.apple.com/us/song/funeral/1867616928</v>
       </c>
       <c r="D142" t="str">
         <v>2026-01-23</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>KUNTOLOGY 101</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G142" t="str">
-        <v>2:50</v>
+        <v>4:03</v>
       </c>
       <c r="H142" t="str">
-        <v>Aliyah's Interlude</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/aliyahs-interlude/1708765232</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/bop-it/1867023466</v>
+        <v>https://music.apple.com/us/album/funeral/1867616617</v>
       </c>
       <c r="L142" t="str">
-        <v>Bop It - Aliyah's Interlude</v>
+        <v>Funeral - Dermot Kennedy</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>My Everything</v>
+        <v>Say Yes</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/my-everything/1862940302</v>
+        <v>https://music.apple.com/us/song/say-yes/1861995090</v>
       </c>
       <c r="D143" t="str">
         <v>2026-01-23</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>My Everything - Single</v>
+        <v>Say Yes - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>2:33</v>
+        <v>2:50</v>
       </c>
       <c r="H143" t="str">
-        <v>Lecrae</v>
+        <v>Marques Anthony</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/lecrae/130043072</v>
+        <v>https://music.apple.com/us/artist/marques-anthony/321321231</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/my-everything/1862940301</v>
+        <v>https://music.apple.com/us/album/say-yes/1861995089</v>
       </c>
       <c r="L143" t="str">
-        <v>My Everything - Lecrae</v>
+        <v>Say Yes - Marques Anthony</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Whole Other Life</v>
+        <v>LOVE ME (feat. Stevie Wonder)</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/whole-other-life/1858374798</v>
+        <v>https://music.apple.com/us/song/love-me-feat-stevie-wonder/1867640879</v>
       </c>
       <c r="D144" t="str">
         <v>2026-01-23</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Nat &amp; Alex Wolff</v>
+        <v>CAMPILATION</v>
       </c>
       <c r="G144" t="str">
-        <v>3:30</v>
+        <v>3:10</v>
       </c>
       <c r="H144" t="str">
-        <v>Nat &amp; Alex Wolff</v>
+        <v>Camper</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/nat-alex-wolff/470903139</v>
+        <v>https://music.apple.com/us/artist/camper/1514886616</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/whole-other-life/1858374775</v>
+        <v>https://music.apple.com/us/album/love-me-feat-stevie-wonder/1867640873</v>
       </c>
       <c r="L144" t="str">
-        <v>Whole Other Life - Nat &amp; Alex Wolff</v>
+        <v>LOVE ME (feat. Stevie Wonder) - Camper</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Belladona</v>
+        <v>UP TO MY NECK IN U</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/belladona/1862538378</v>
+        <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
       </c>
       <c r="D145" t="str">
         <v>2026-01-23</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Belladona</v>
+        <v>UP TO MY NECK IN U - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:32</v>
+        <v>2:17</v>
       </c>
       <c r="H145" t="str">
-        <v>Kenia Os</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/belladona/1862538030</v>
+        <v>https://music.apple.com/us/album/up-to-my-neck-in-u/1862550671</v>
       </c>
       <c r="L145" t="str">
-        <v>Belladona - Kenia Os</v>
+        <v>UP TO MY NECK IN U - Ledbyher</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Addicted to Love (From "Tell Me Lies (Season 3)")</v>
+        <v>Wallflower</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/addicted-to-love-from-tell-me-lies-season-3/1867024880</v>
+        <v>https://music.apple.com/us/song/wallflower/1862737077</v>
       </c>
       <c r="D146" t="str">
         <v>2026-01-23</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Addicted to Love (From "Tell Me Lies (Season 3)") - Single</v>
+        <v>Wallflower - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:05</v>
+        <v>3:25</v>
       </c>
       <c r="H146" t="str">
-        <v>CHVRCHES</v>
+        <v>Sikarus</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/chvrches/566867492</v>
+        <v>https://music.apple.com/us/artist/sikarus/1046558781</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/addicted-to-love-from-tell-me-lies-season-3/1867024879</v>
+        <v>https://music.apple.com/us/album/wallflower/1862737074</v>
       </c>
       <c r="L146" t="str">
-        <v>Addicted to Love (From "Tell Me Lies (Season 3)") - CHVRCHES</v>
+        <v>Wallflower - Sikarus</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Lie2Me</v>
+        <v>You Phase</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/lie2me/1862762675</v>
+        <v>https://music.apple.com/us/song/you-phase/1868861897</v>
       </c>
       <c r="D147" t="str">
         <v>2026-01-23</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Lie2Me - Single</v>
+        <v>You Phase - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:03</v>
+        <v>2:51</v>
       </c>
       <c r="H147" t="str">
-        <v>DC THE DON</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
+        <v>https://music.apple.com/us/artist/mitchell-tenpenny/430369368</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/lie2me/1862762674</v>
+        <v>https://music.apple.com/us/album/you-phase/1868861895</v>
       </c>
       <c r="L147" t="str">
-        <v>Lie2Me - DC THE DON</v>
+        <v>You Phase - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>High On Heaven</v>
+        <v>Miss Independent</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/high-on-heaven/1859071765</v>
+        <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
       </c>
       <c r="D148" t="str">
         <v>2026-01-23</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>High On Heaven - Single</v>
+        <v>Miss Independent - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>3:19</v>
+        <v>2:40</v>
       </c>
       <c r="H148" t="str">
-        <v>Nessa Barrett</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/high-on-heaven/1859071764</v>
+        <v>https://music.apple.com/us/album/miss-independent/1870612555</v>
       </c>
       <c r="L148" t="str">
-        <v>High On Heaven - Nessa Barrett</v>
+        <v>Miss Independent - 1Ski OG</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Most Wanted</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown)</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/most-wanted/1844866135</v>
+        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown/1870678482</v>
       </c>
       <c r="D149" t="str">
         <v>2026-01-23</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>My Ego Told Me To</v>
+        <v>SO BE IT</v>
       </c>
       <c r="G149" t="str">
-        <v>2:15</v>
+        <v>5:47</v>
       </c>
       <c r="H149" t="str">
-        <v>Leigh-Anne</v>
+        <v>Elevation Worship</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/leigh-anne/1691386195</v>
+        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/most-wanted/1844865923</v>
+        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown/1870678481</v>
       </c>
       <c r="L149" t="str">
-        <v>Most Wanted - Leigh-Anne</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) - Elevation Worship</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Anything Is Possible</v>
+        <v>go again</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/anything-is-possible/1867583228</v>
+        <v>https://music.apple.com/us/song/go-again/1868987466</v>
       </c>
       <c r="D150" t="str">
         <v>2026-01-23</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Charlie The Wonderdog (Original Songs from the Motion Picture) - Single</v>
+        <v>go again - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:57</v>
+        <v>2:07</v>
       </c>
       <c r="H150" t="str">
-        <v>Bryan Adams</v>
+        <v>NateTaylorr</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/bryan-adams/85932</v>
+        <v>https://music.apple.com/us/artist/natetaylorr/1243682934</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/anything-is-possible/1867583221</v>
+        <v>https://music.apple.com/us/album/go-again/1868987193</v>
       </c>
       <c r="L150" t="str">
-        <v>Anything Is Possible - Bryan Adams</v>
+        <v>go again - NateTaylorr</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Volcano</v>
+        <v>Autopilot</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/volcano/1862739924</v>
+        <v>https://music.apple.com/us/song/autopilot/1863072399</v>
       </c>
       <c r="D151" t="str">
         <v>2026-01-23</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Volcano - Single</v>
+        <v>Autopilot</v>
       </c>
       <c r="G151" t="str">
-        <v>2:28</v>
+        <v>2:46</v>
       </c>
       <c r="H151" t="str">
-        <v>Girl Tones</v>
+        <v>ALEXSUCKS</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/girl-tones/1761267584</v>
+        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/volcano/1862739923</v>
+        <v>https://music.apple.com/us/album/autopilot/1863072393</v>
       </c>
       <c r="L151" t="str">
-        <v>Volcano - Girl Tones</v>
+        <v>Autopilot - ALEXSUCKS</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Into Oblivion</v>
+        <v>Portrait of My Heart (feat. Brendan Yates)</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/into-oblivion/1868804164</v>
+        <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
       </c>
       <c r="D152" t="str">
         <v>2026-01-23</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Into Oblivion</v>
+        <v>Portrait of My Heart - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>3:34</v>
+        <v>3:04</v>
       </c>
       <c r="H152" t="str">
-        <v>Lamb of God</v>
+        <v>SPELLLING</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/spellling/1281213673</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/into-oblivion/1868804163</v>
+        <v>https://music.apple.com/us/album/portrait-of-my-heart-feat-brendan-yates/1862282167</v>
       </c>
       <c r="L152" t="str">
-        <v>Into Oblivion - Lamb of God</v>
+        <v>Portrait of My Heart (feat. Brendan Yates) - SPELLLING</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Beer and Blood Stains</v>
+        <v>In Violet</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/beer-and-blood-stains/1838992321</v>
+        <v>https://music.apple.com/us/song/in-violet/1839471290</v>
       </c>
       <c r="D153" t="str">
         <v>2026-01-23</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Listen Up!</v>
+        <v>Death in the Business of Whaling</v>
       </c>
       <c r="G153" t="str">
-        <v>3:19</v>
+        <v>4:09</v>
       </c>
       <c r="H153" t="str">
-        <v>New Found Glory</v>
+        <v>Searows</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/new-found-glory/65551</v>
+        <v>https://music.apple.com/us/artist/searows/1607240507</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/beer-and-blood-stains/1838991916</v>
+        <v>https://music.apple.com/us/album/in-violet/1839470844</v>
       </c>
       <c r="L153" t="str">
-        <v>Beer and Blood Stains - New Found Glory</v>
+        <v>In Violet - Searows</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Numb</v>
+        <v>Baby Run</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/numb/1860136324</v>
+        <v>https://music.apple.com/us/song/baby-run/1857658819</v>
       </c>
       <c r="D154" t="str">
         <v>2026-01-23</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Numb - Single</v>
+        <v>Baby Run - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>2:13</v>
+        <v>4:47</v>
       </c>
       <c r="H154" t="str">
-        <v>Marc E. Bassy</v>
+        <v>Jimi Jules</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/marc-e-bassy/899254194</v>
+        <v>https://music.apple.com/us/artist/jimi-jules/586933009</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/numb/1860136319</v>
+        <v>https://music.apple.com/us/album/baby-run/1857658816</v>
       </c>
       <c r="L154" t="str">
-        <v>Numb - Marc E. Bassy</v>
+        <v>Baby Run - Jimi Jules</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Foxtrot</v>
+        <v>What If We Don't</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/foxtrot/1860110201</v>
+        <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
       </c>
       <c r="D155" t="str">
         <v>2026-01-23</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Saputjiji</v>
+        <v>What If We Don't - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>1:33</v>
+        <v>3:06</v>
       </c>
       <c r="H155" t="str">
-        <v>Tanya Tagaq</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/tanya-tagaq/257545265</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/foxtrot/1860109752</v>
+        <v>https://music.apple.com/us/album/what-if-we-dont/1862668776</v>
       </c>
       <c r="L155" t="str">
-        <v>Foxtrot - Tanya Tagaq</v>
+        <v>What If We Don't - Ashley McBryde</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Digital Winter</v>
+        <v>Hagamos Que</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/digital-winter/1820332238</v>
+        <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
       </c>
       <c r="D156" t="str">
         <v>2026-01-23</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Stand On My Shoulders</v>
+        <v>Hagamos Que - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:45</v>
+        <v>2:58</v>
       </c>
       <c r="H156" t="str">
-        <v>Ya Tseen</v>
+        <v>Juanes</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/ya-tseen/1549782831</v>
+        <v>https://music.apple.com/us/artist/juanes/103856</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/digital-winter/1820332224</v>
+        <v>https://music.apple.com/us/album/hagamos-que/1861956611</v>
       </c>
       <c r="L156" t="str">
-        <v>Digital Winter - Ya Tseen</v>
+        <v>Hagamos Que - Juanes</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Back To You</v>
+        <v>World Change Me</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/back-to-you/1861380254</v>
+        <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
       </c>
       <c r="D157" t="str">
         <v>2026-01-23</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Porcelain</v>
+        <v>World Change Me - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>3:10</v>
+        <v>3:03</v>
       </c>
       <c r="H157" t="str">
-        <v>Peach PRC</v>
+        <v>Max McNown</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/peach-prc/1469263677</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/back-to-you/1861380240</v>
+        <v>https://music.apple.com/us/album/world-change-me/1860974598</v>
       </c>
       <c r="L157" t="str">
-        <v>Back To You - Peach PRC</v>
+        <v>World Change Me - Max McNown</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Sleepwalker's Pendulum</v>
+        <v>Exclusive</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/sleepwalkers-pendulum/1826115116</v>
+        <v>https://music.apple.com/us/song/exclusive/1851537672</v>
       </c>
       <c r="D158" t="str">
         <v>2026-01-23</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Dreamer+</v>
+        <v>Exclusive - EP</v>
       </c>
       <c r="G158" t="str">
-        <v>3:22</v>
+        <v>3:20</v>
       </c>
       <c r="H158" t="str">
-        <v>Sassy 009</v>
+        <v>Hudson Westbrook</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/sassy-009/1277035471</v>
+        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/sleepwalkers-pendulum/1826114506</v>
+        <v>https://music.apple.com/us/album/exclusive/1851537671</v>
       </c>
       <c r="L158" t="str">
-        <v>Sleepwalker's Pendulum - Sassy 009</v>
+        <v>Exclusive - Hudson Westbrook</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Ruin Me</v>
+        <v>Say Less</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/ruin-me/1850741533</v>
+        <v>https://music.apple.com/us/song/say-less/1867910122</v>
       </c>
       <c r="D159" t="str">
         <v>2026-01-23</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>HEAD FIRST - EP</v>
+        <v>Say Less - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>2:31</v>
+        <v>2:18</v>
       </c>
       <c r="H159" t="str">
-        <v>Corbyn Besson</v>
+        <v>JYT</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/corbyn-besson/810434797</v>
+        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/ruin-me/1850741514</v>
+        <v>https://music.apple.com/us/album/say-less/1867910115</v>
       </c>
       <c r="L159" t="str">
-        <v>Ruin Me - Corbyn Besson</v>
+        <v>Say Less - JYT</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>w-w-w-w-w</v>
+        <v>Angels Cry</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/w-w-w-w-w/1846462521</v>
+        <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
       </c>
       <c r="D160" t="str">
         <v>2026-01-23</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>the apple tree under the sea</v>
+        <v>X's for Eyes (Deluxe)</v>
       </c>
       <c r="G160" t="str">
-        <v>4:26</v>
+        <v>3:52</v>
       </c>
       <c r="H160" t="str">
-        <v>hemlocke springs</v>
+        <v>The Red Jumpsuit Apparatus</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/hemlocke-springs/1626170220</v>
+        <v>https://music.apple.com/us/artist/the-red-jumpsuit-apparatus/130037074</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/w-w-w-w-w/1846462383</v>
+        <v>https://music.apple.com/us/album/angels-cry/1862320872</v>
       </c>
       <c r="L160" t="str">
-        <v>w-w-w-w-w - hemlocke springs</v>
+        <v>Angels Cry - The Red Jumpsuit Apparatus</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Struggle Bus</v>
+        <v>Over You</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/struggle-bus/1862024076</v>
+        <v>https://music.apple.com/us/song/over-you/1846189473</v>
       </c>
       <c r="D161" t="str">
         <v>2026-01-23</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Struggle Bus - Single</v>
+        <v>A Love For Strangers</v>
       </c>
       <c r="G161" t="str">
-        <v>3:20</v>
+        <v>4:44</v>
       </c>
       <c r="H161" t="str">
-        <v>Iris Copperman</v>
+        <v>Chet Faker</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/iris-copperman/1741269048</v>
+        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/struggle-bus/1862024075</v>
+        <v>https://music.apple.com/us/album/over-you/1846189472</v>
       </c>
       <c r="L161" t="str">
-        <v>Struggle Bus - Iris Copperman</v>
+        <v>Over You - Chet Faker</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Over</v>
+        <v>Chala (My Soul Is on a Loop)</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/over/1862351820</v>
+        <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
       </c>
       <c r="D162" t="str">
         <v>2026-01-23</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Over - Single</v>
+        <v>Chala (My Soul Is on a Loop) - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:49</v>
+        <v>2:42</v>
       </c>
       <c r="H162" t="str">
-        <v>Sydney Rose</v>
+        <v>Barry Can't Swim</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/sydney-rose/354936789</v>
+        <v>https://music.apple.com/us/artist/barry-cant-swim/1492752064</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/over/1862351811</v>
+        <v>https://music.apple.com/us/album/chala-my-soul-is-on-a-loop/1857789040</v>
       </c>
       <c r="L162" t="str">
-        <v>Over - Sydney Rose</v>
+        <v>Chala (My Soul Is on a Loop) - Barry Can't Swim</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Lean</v>
+        <v>starlight feat. Madeline Follin</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/lean/1862829540</v>
+        <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
       </c>
       <c r="D163" t="str">
         <v>2026-01-23</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Lean - Single</v>
+        <v>starlight feat. Madeline Follin - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:53</v>
+        <v>3:06</v>
       </c>
       <c r="H163" t="str">
-        <v>Charlotte Day Wilson</v>
+        <v>Disco Lines</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-day-wilson/1053594538</v>
+        <v>https://music.apple.com/us/artist/disco-lines/1462793893</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/lean/1862829538</v>
+        <v>https://music.apple.com/us/album/starlight-feat-madeline-follin/1869330767</v>
       </c>
       <c r="L163" t="str">
-        <v>Lean - Charlotte Day Wilson</v>
+        <v>starlight feat. Madeline Follin - Disco Lines</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>F**k It Up</v>
+        <v>Locked In (feat. Trippie Redd)</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/f-k-it-up/1849002929</v>
+        <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
       </c>
       <c r="D164" t="str">
         <v>2026-01-23</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>F**k It Up - EP</v>
+        <v>Locked In (feat. Trippie Redd) - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:32</v>
+        <v>2:48</v>
       </c>
       <c r="H164" t="str">
-        <v>Master Peace</v>
+        <v>David Guetta</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/master-peace/1477196856</v>
+        <v>https://music.apple.com/us/artist/david-guetta/5557599</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/f-k-it-up/1849002928</v>
+        <v>https://music.apple.com/us/album/locked-in-feat-trippie-redd/1869439982</v>
       </c>
       <c r="L164" t="str">
-        <v>F**k It Up - Master Peace</v>
+        <v>Locked In (feat. Trippie Redd) - David Guetta</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>La Carrera</v>
+        <v>Rejoice</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/la-carrera/1863188476</v>
+        <v>https://music.apple.com/us/song/rejoice/1862633596</v>
       </c>
       <c r="D165" t="str">
         <v>2026-01-23</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>La Carrera - Single</v>
+        <v>Rejoice - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:40</v>
+        <v>4:20</v>
       </c>
       <c r="H165" t="str">
-        <v>Moa Rivera</v>
+        <v>Def Leppard</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/moa-rivera/1636808812</v>
+        <v>https://music.apple.com/us/artist/def-leppard/117554</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/la-carrera/1863188474</v>
+        <v>https://music.apple.com/us/album/rejoice/1862633593</v>
       </c>
       <c r="L165" t="str">
-        <v>La Carrera - Moa Rivera</v>
+        <v>Rejoice - Def Leppard</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>No Lube So Rude</v>
+        <v>Slight Werk (feat. Bree Runway) [Club Mix]</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/no-lube-so-rude/1856065376</v>
+        <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
       </c>
       <c r="D166" t="str">
         <v>2026-01-23</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>No Lube So Rude</v>
+        <v>Slight Werk (Club Mix) [feat. Bree Runway] - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>2:48</v>
+        <v>2:58</v>
       </c>
       <c r="H166" t="str">
-        <v>Peaches</v>
+        <v>Honey Dijon</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/peaches/3028600</v>
+        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/no-lube-so-rude/1856064995</v>
+        <v>https://music.apple.com/us/album/slight-werk-feat-bree-runway-club-mix/1860859551</v>
       </c>
       <c r="L166" t="str">
-        <v>No Lube So Rude - Peaches</v>
+        <v>Slight Werk (feat. Bree Runway) [Club Mix] - Honey Dijon</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Somersaults</v>
+        <v>Lucky Day</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/somersaults/1847159408</v>
+        <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
       </c>
       <c r="D167" t="str">
         <v>2026-01-23</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Somersaults</v>
+        <v>Speed Kills</v>
       </c>
       <c r="G167" t="str">
-        <v>4:32</v>
+        <v>3:13</v>
       </c>
       <c r="H167" t="str">
-        <v>deathcrash</v>
+        <v>Ally Evenson</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/deathcrash/1461469738</v>
+        <v>https://music.apple.com/us/artist/ally-evenson/283908113</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/somersaults/1847159406</v>
+        <v>https://music.apple.com/us/album/lucky-day/1849264498</v>
       </c>
       <c r="L167" t="str">
-        <v>Somersaults - deathcrash</v>
+        <v>Lucky Day - Ally Evenson</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>2005</v>
+        <v>Breathe On It</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/2005/1854873143</v>
+        <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
       </c>
       <c r="D168" t="str">
         <v>2026-01-23</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Almost There</v>
+        <v>Breathe On It - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:52</v>
+        <v>4:00</v>
       </c>
       <c r="H168" t="str">
-        <v>The Academy Is...</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/the-academy-is/75024274</v>
+        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/2005/1854873133</v>
+        <v>https://music.apple.com/us/album/breathe-on-it/1862938798</v>
       </c>
       <c r="L168" t="str">
-        <v>2005 - The Academy Is...</v>
+        <v>Breathe On It - Tauren Wells</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>I Had a Ball</v>
+        <v>Easy</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/i-had-a-ball/1863330906</v>
+        <v>https://music.apple.com/us/song/easy/1863456906</v>
       </c>
       <c r="D169" t="str">
         <v>2026-01-23</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Palm Royale Season 2 (Apple TV Original Series Soundtrack)</v>
+        <v>Easy - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>4:14</v>
+        <v>4:30</v>
       </c>
       <c r="H169" t="str">
-        <v>Kristen Wiig</v>
+        <v>lydi lynn</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/kristen-wiig/273077223</v>
+        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/i-had-a-ball/1863330900</v>
+        <v>https://music.apple.com/us/album/easy/1863456903</v>
       </c>
       <c r="L169" t="str">
-        <v>I Had a Ball - Kristen Wiig</v>
+        <v>Easy - lydi lynn</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>IDB</v>
+        <v>Break Me In</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/idb/1859084151</v>
+        <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
       </c>
       <c r="D170" t="str">
         <v>2026-01-23</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>IDB - Single</v>
+        <v>Break Me In - Single</v>
       </c>
       <c r="G170" t="str">
         <v>2:52</v>
       </c>
       <c r="H170" t="str">
-        <v>42 Dugg</v>
+        <v>Joyce Wrice</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
+        <v>https://music.apple.com/us/artist/joyce-wrice/591991458</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/idb/1859084147</v>
+        <v>https://music.apple.com/us/album/break-me-in/1862881766</v>
       </c>
       <c r="L170" t="str">
-        <v>IDB - 42 Dugg</v>
+        <v>Break Me In - Joyce Wrice</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Feel This Way</v>
+        <v>Long Live Love</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/feel-this-way/1862902478</v>
+        <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
       </c>
       <c r="D171" t="str">
         <v>2026-01-23</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Feel This Way - Single</v>
+        <v>Long Live Love - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>3:04</v>
+        <v>2:36</v>
       </c>
       <c r="H171" t="str">
-        <v>Josh Baker</v>
+        <v>Sugar</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/josh-baker/150294413</v>
+        <v>https://music.apple.com/us/artist/sugar/530175867</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/feel-this-way/1862902476</v>
+        <v>https://music.apple.com/us/album/long-live-love/1851251226</v>
       </c>
       <c r="L171" t="str">
-        <v>Feel This Way - Josh Baker</v>
+        <v>Long Live Love - Sugar</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Falling</v>
+        <v>Depressed</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/falling/1861598107</v>
+        <v>https://music.apple.com/us/song/depressed/1840400522</v>
       </c>
       <c r="D172" t="str">
         <v>2026-01-23</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Falling - Single</v>
+        <v>Boycott Heaven</v>
       </c>
       <c r="G172" t="str">
-        <v>3:02</v>
+        <v>3:32</v>
       </c>
       <c r="H172" t="str">
-        <v>Shimza</v>
+        <v>The Format</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/shimza/697739898</v>
+        <v>https://music.apple.com/us/artist/the-format/3064903</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/falling/1861598106</v>
+        <v>https://music.apple.com/us/album/depressed/1840399886</v>
       </c>
       <c r="L172" t="str">
-        <v>Falling - Shimza</v>
+        <v>Depressed - The Format</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Message to You</v>
+        <v>Empty Hands</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/message-to-you/1867275596</v>
+        <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
       </c>
       <c r="D173" t="str">
         <v>2026-01-23</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Heavy On The Soul</v>
+        <v>Empty Hands</v>
       </c>
       <c r="G173" t="str">
-        <v>3:37</v>
+        <v>3:09</v>
       </c>
       <c r="H173" t="str">
-        <v>Ty Myers</v>
+        <v>Poppy</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
+        <v>https://music.apple.com/us/artist/poppy/1004130511</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/message-to-you/1867275110</v>
+        <v>https://music.apple.com/us/album/empty-hands/1852046141</v>
       </c>
       <c r="L173" t="str">
-        <v>Message to You - Ty Myers</v>
+        <v>Empty Hands - Poppy</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>NOTHING IS REAL</v>
+        <v>The Long Surrender</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/nothing-is-real/1866859742</v>
+        <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
       </c>
       <c r="D174" t="str">
         <v>2026-01-23</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>NOTHING IS REAL - Single</v>
+        <v>The Long Surrender</v>
       </c>
       <c r="G174" t="str">
-        <v>3:06</v>
+        <v>3:45</v>
       </c>
       <c r="H174" t="str">
-        <v>DESTIN CONRAD</v>
+        <v>NEEDTOBREATHE</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/destin-conrad/852999989</v>
+        <v>https://music.apple.com/us/artist/needtobreathe/113247214</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/nothing-is-real/1866859497</v>
+        <v>https://music.apple.com/us/album/the-long-surrender/1861935699</v>
       </c>
       <c r="L174" t="str">
-        <v>NOTHING IS REAL - DESTIN CONRAD</v>
+        <v>The Long Surrender - NEEDTOBREATHE</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>CUÉNTAME</v>
+        <v>Angela</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/cu%C3%A9ntame/1862973854</v>
+        <v>https://music.apple.com/us/song/angela/1866624257</v>
       </c>
       <c r="D175" t="str">
         <v>2026-01-23</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>CUÉNTAME - Single</v>
+        <v>Angela - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:42</v>
+        <v>3:32</v>
       </c>
       <c r="H175" t="str">
-        <v>FloyyMenor</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/floyymenor/1676497551</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/cu%C3%A9ntame/1862973853</v>
+        <v>https://music.apple.com/us/album/angela/1866624256</v>
       </c>
       <c r="L175" t="str">
-        <v>CUÉNTAME - FloyyMenor</v>
+        <v>Angela - Hayden Everett</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>DANCE...</v>
+        <v>Disappear</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/dance/1867531306</v>
+        <v>https://music.apple.com/us/song/disappear/1847663553</v>
       </c>
       <c r="D176" t="str">
         <v>2026-01-23</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>WOR$T GIRL IN AMERICA</v>
+        <v>Greyhound</v>
       </c>
       <c r="G176" t="str">
-        <v>4:47</v>
+        <v>3:31</v>
       </c>
       <c r="H176" t="str">
-        <v>Slayyyter</v>
+        <v>Katie Tupper</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/katie-tupper/1395542470</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/dance/1867530577</v>
+        <v>https://music.apple.com/us/album/disappear/1847663546</v>
       </c>
       <c r="L176" t="str">
-        <v>DANCE... - Slayyyter</v>
+        <v>Disappear - Katie Tupper</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>welcome to the circus</v>
+        <v>Catapult</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/welcome-to-the-circus/1861011604</v>
+        <v>https://music.apple.com/us/song/catapult/1862951335</v>
       </c>
       <c r="D177" t="str">
         <v>2026-01-23</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>welcome to the circus - Single</v>
+        <v>Catapult - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:29</v>
+        <v>2:57</v>
       </c>
       <c r="H177" t="str">
-        <v>Jagwar Twin</v>
+        <v>Cape Francis</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/jagwar-twin/1429051937</v>
+        <v>https://music.apple.com/us/artist/cape-francis/1242523550</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/welcome-to-the-circus/1861011603</v>
+        <v>https://music.apple.com/us/album/catapult/1862951333</v>
       </c>
       <c r="L177" t="str">
-        <v>welcome to the circus - Jagwar Twin</v>
+        <v>Catapult - Cape Francis</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>playlist</v>
+        <v>Think Twice</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/playlist/1859009927</v>
+        <v>https://music.apple.com/us/song/think-twice/1850698548</v>
       </c>
       <c r="D178" t="str">
         <v>2026-01-23</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>playlist - Single</v>
+        <v>Think Twice - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:44</v>
+        <v>2:22</v>
       </c>
       <c r="H178" t="str">
-        <v>Tenroc</v>
+        <v>Leonie Biney</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/tenroc/1711844910</v>
+        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/playlist/1859009923</v>
+        <v>https://music.apple.com/us/album/think-twice/1850698545</v>
       </c>
       <c r="L178" t="str">
-        <v>playlist - Tenroc</v>
+        <v>Think Twice - Leonie Biney</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Marlboro Man</v>
+        <v>LOVESONGS</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/marlboro-man/1862008741</v>
+        <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
       </c>
       <c r="D179" t="str">
         <v>2026-01-23</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Marlboro Man - Single</v>
+        <v>BEAUTIFUL MADNESS</v>
       </c>
       <c r="G179" t="str">
-        <v>3:23</v>
+        <v>3:33</v>
       </c>
       <c r="H179" t="str">
-        <v>Midland</v>
+        <v>Agnes</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/midland/1171869852</v>
+        <v>https://music.apple.com/us/artist/agnes/42568985</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/marlboro-man/1862008740</v>
+        <v>https://music.apple.com/us/album/lovesongs/1849098275</v>
       </c>
       <c r="L179" t="str">
-        <v>Marlboro Man - Midland</v>
+        <v>LOVESONGS - Agnes</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Enabling</v>
+        <v>Down South</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/enabling/1860993048</v>
+        <v>https://music.apple.com/us/song/down-south/1861010793</v>
       </c>
       <c r="D180" t="str">
         <v>2026-01-23</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Enabling - Single</v>
+        <v>Down South - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:18</v>
+        <v>2:19</v>
       </c>
       <c r="H180" t="str">
-        <v>Tenille Townes</v>
+        <v>Trap Dickey</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/tenille-townes/1367713770</v>
+        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/enabling/1860992859</v>
+        <v>https://music.apple.com/us/album/down-south/1861010788</v>
       </c>
       <c r="L180" t="str">
-        <v>Enabling - Tenille Townes</v>
+        <v>Down South - Trap Dickey</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Two Broken Hearts</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/two-broken-hearts/1841485428</v>
+        <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
       </c>
       <c r="D181" t="str">
         <v>2026-01-23</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Steel Town</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:53</v>
+        <v>2:16</v>
       </c>
       <c r="H181" t="str">
-        <v>Morgan Evans</v>
+        <v>SALIMATA</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/morgan-evans/262665075</v>
+        <v>https://music.apple.com/us/artist/salimata/690253822</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/two-broken-hearts/1841484758</v>
+        <v>https://music.apple.com/us/album/jackpot-foil-a-colors-show/1866998655</v>
       </c>
       <c r="L181" t="str">
-        <v>Two Broken Hearts - Morgan Evans</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW - SALIMATA</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Lost in My Bed</v>
+        <v>Love Like This</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/lost-in-my-bed/1862222274</v>
+        <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
       </c>
       <c r="D182" t="str">
         <v>2026-01-23</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Lost in My Bed - Single</v>
+        <v>Love Like This - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:46</v>
+        <v>3:30</v>
       </c>
       <c r="H182" t="str">
-        <v>Khalil</v>
+        <v>Jacob Banks</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/khalil/1223181975</v>
+        <v>https://music.apple.com/us/artist/jacob-banks/625014171</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/lost-in-my-bed/1862222272</v>
+        <v>https://music.apple.com/us/album/love-like-this/1866999617</v>
       </c>
       <c r="L182" t="str">
-        <v>Lost in My Bed - Khalil</v>
+        <v>Love Like This - Jacob Banks</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Father Time</v>
+        <v>Plan Plan</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/father-time/1858611581</v>
+        <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
       </c>
       <c r="D183" t="str">
         <v>2026-01-23</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Honey Water</v>
+        <v>La Locura</v>
       </c>
       <c r="G183" t="str">
-        <v>1:58</v>
+        <v>3:10</v>
       </c>
       <c r="H183" t="str">
-        <v>Girlfriend</v>
+        <v>Funky</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/girlfriend/1511096374</v>
+        <v>https://music.apple.com/us/artist/funky/80960663</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/father-time/1858611265</v>
+        <v>https://music.apple.com/us/album/plan-plan/1867940087</v>
       </c>
       <c r="L183" t="str">
-        <v>Father Time - Girlfriend</v>
+        <v>Plan Plan - Funky</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>MVLAN</v>
+        <v>double edged sword</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/mvlan/1867584574</v>
+        <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
       </c>
       <c r="D184" t="str">
         <v>2026-01-23</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>MVLAN - Single</v>
+        <v>double edged sword - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:41</v>
+        <v>3:28</v>
       </c>
       <c r="H184" t="str">
-        <v>YOVNGCHIMI</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/yovngchimi/1558257759</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/mvlan/1867584573</v>
+        <v>https://music.apple.com/us/album/double-edged-sword/1868829044</v>
       </c>
       <c r="L184" t="str">
-        <v>MVLAN - YOVNGCHIMI</v>
+        <v>double edged sword - Hailey Picardi</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Name In Blood</v>
+        <v>SOMEWHERE IN BETWEEN</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/name-in-blood/1859687600</v>
+        <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
       </c>
       <c r="D185" t="str">
         <v>2026-01-23</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Engines of Demolition</v>
+        <v>SOMEWHERE IN BETWEEN - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>4:36</v>
+        <v>3:27</v>
       </c>
       <c r="H185" t="str">
-        <v>Black Label Society</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/black-label-society/2778807</v>
+        <v>https://music.apple.com/us/artist/matt-hansen/1442658353</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/name-in-blood/1859687597</v>
+        <v>https://music.apple.com/us/album/somewhere-in-between/1866969151</v>
       </c>
       <c r="L185" t="str">
-        <v>Name In Blood - Black Label Society</v>
+        <v>SOMEWHERE IN BETWEEN - Matt Hansen</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Eyeball</v>
+        <v>The Decay</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/eyeball/1862539350</v>
+        <v>https://music.apple.com/us/song/the-decay/1862836783</v>
       </c>
       <c r="D186" t="str">
         <v>2026-01-23</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Eyeball - EP</v>
+        <v>What Remains (Midnight Edition)</v>
       </c>
       <c r="G186" t="str">
-        <v>2:14</v>
+        <v>3:20</v>
       </c>
       <c r="H186" t="str">
-        <v>They Might Be Giants</v>
+        <v>Pop Evil</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/they-might-be-giants/149020</v>
+        <v>https://music.apple.com/us/artist/pop-evil/441597923</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/eyeball/1862539346</v>
+        <v>https://music.apple.com/us/album/the-decay/1862836507</v>
       </c>
       <c r="L186" t="str">
-        <v>Eyeball - They Might Be Giants</v>
+        <v>The Decay - Pop Evil</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Long Gone</v>
+        <v>3111</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/long-gone/1847573926</v>
+        <v>https://music.apple.com/us/song/3111/1862225387</v>
       </c>
       <c r="D187" t="str">
         <v>2026-01-23</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Tenterhooks</v>
+        <v>Goliath</v>
       </c>
       <c r="G187" t="str">
-        <v>3:55</v>
+        <v>4:08</v>
       </c>
       <c r="H187" t="str">
-        <v>Silversun Pickups</v>
+        <v>Exodus</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/silversun-pickups/74752665</v>
+        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/long-gone/1847573918</v>
+        <v>https://music.apple.com/us/album/3111/1862225385</v>
       </c>
       <c r="L187" t="str">
-        <v>Long Gone - Silversun Pickups</v>
+        <v>3111 - Exodus</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>iloveitiloveitiloveit</v>
+        <v>Touch My Love And Die</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/iloveitiloveitiloveit/1867034427</v>
+        <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
       </c>
       <c r="D188" t="str">
         <v>2026-01-23</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>iloveitiloveitiloveit - Single</v>
+        <v>Touch My Love And Die - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:03</v>
+        <v>2:57</v>
       </c>
       <c r="H188" t="str">
-        <v>Bella Kay</v>
+        <v>Myrkur</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/myrkur/293296859</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/iloveitiloveitiloveit/1867034426</v>
+        <v>https://music.apple.com/us/album/touch-my-love-and-die/1867630168</v>
       </c>
       <c r="L188" t="str">
-        <v>iloveitiloveitiloveit - Bella Kay</v>
+        <v>Touch My Love And Die - Myrkur</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>To The Edge</v>
+        <v>Bomb To A Knife Fight</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/to-the-edge/1863513891</v>
+        <v>https://music.apple.com/us/song/bomb-to-a-knife-fight/1861589406</v>
       </c>
       <c r="D189" t="str">
         <v>2026-01-23</v>
@@ -7557,790 +7557,30 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>To The Edge - Single</v>
+        <v>Bomb To A Knife Fight - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:19</v>
+        <v>2:41</v>
       </c>
       <c r="H189" t="str">
-        <v>Alex Jude</v>
+        <v>The Barbarians of California</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
+        <v>https://music.apple.com/us/artist/the-barbarians-of-california/1724096474</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/to-the-edge/1863513887</v>
+        <v>https://music.apple.com/us/album/bomb-to-a-knife-fight/1861589405</v>
       </c>
       <c r="L189" t="str">
-        <v>To The Edge - Alex Jude</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="str">
-        <v>demons</v>
-      </c>
-      <c r="B190" t="str">
-        <v/>
-      </c>
-      <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/demons/1861978106</v>
-      </c>
-      <c r="D190" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E190" t="str">
-        <v/>
-      </c>
-      <c r="F190" t="str">
-        <v>demons - Single</v>
-      </c>
-      <c r="G190" t="str">
-        <v>3:10</v>
-      </c>
-      <c r="H190" t="str">
-        <v>Josiah Queen</v>
-      </c>
-      <c r="I190" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/josiah-queen/1498117530</v>
-      </c>
-      <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/demons/1861978105</v>
-      </c>
-      <c r="L190" t="str">
-        <v>demons - Josiah Queen</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="str">
-        <v>Everyone Wants To Feel Like You Do</v>
-      </c>
-      <c r="B191" t="str">
-        <v/>
-      </c>
-      <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/everyone-wants-to-feel-like-you-do/1841949027</v>
-      </c>
-      <c r="D191" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E191" t="str">
-        <v/>
-      </c>
-      <c r="F191" t="str">
-        <v>Valentine</v>
-      </c>
-      <c r="G191" t="str">
-        <v>4:03</v>
-      </c>
-      <c r="H191" t="str">
-        <v>Courtney Marie Andrews</v>
-      </c>
-      <c r="I191" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/courtney-marie-andrews/287157006</v>
-      </c>
-      <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/everyone-wants-to-feel-like-you-do/1841948802</v>
-      </c>
-      <c r="L191" t="str">
-        <v>Everyone Wants To Feel Like You Do - Courtney Marie Andrews</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="str">
-        <v>Nothing Comes Easy</v>
-      </c>
-      <c r="B192" t="str">
-        <v/>
-      </c>
-      <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/nothing-comes-easy/1862757046</v>
-      </c>
-      <c r="D192" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E192" t="str">
-        <v/>
-      </c>
-      <c r="F192" t="str">
-        <v>Nothing Comes Easy - Single</v>
-      </c>
-      <c r="G192" t="str">
-        <v>2:54</v>
-      </c>
-      <c r="H192" t="str">
-        <v>Joy Oladokun</v>
-      </c>
-      <c r="I192" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/joy-oladokun/699636664</v>
-      </c>
-      <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/nothing-comes-easy/1862756744</v>
-      </c>
-      <c r="L192" t="str">
-        <v>Nothing Comes Easy - Joy Oladokun</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="str">
-        <v>Against the Dying of the Light</v>
-      </c>
-      <c r="B193" t="str">
-        <v/>
-      </c>
-      <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/against-the-dying-of-the-light/1860962165</v>
-      </c>
-      <c r="D193" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E193" t="str">
-        <v/>
-      </c>
-      <c r="F193" t="str">
-        <v>Against the Dying of the Light</v>
-      </c>
-      <c r="G193" t="str">
-        <v>2:28</v>
-      </c>
-      <c r="H193" t="str">
-        <v>José González</v>
-      </c>
-      <c r="I193" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/jos%C3%A9-gonz%C3%A1lez/153417030</v>
-      </c>
-      <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/against-the-dying-of-the-light/1860962162</v>
-      </c>
-      <c r="L193" t="str">
-        <v>Against the Dying of the Light - José González</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="str">
-        <v>Big Boy Problems</v>
-      </c>
-      <c r="B194" t="str">
-        <v/>
-      </c>
-      <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/big-boy-problems/1851062438</v>
-      </c>
-      <c r="D194" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E194" t="str">
-        <v/>
-      </c>
-      <c r="F194" t="str">
-        <v>Cynthia</v>
-      </c>
-      <c r="G194" t="str">
-        <v>2:30</v>
-      </c>
-      <c r="H194" t="str">
-        <v>Sydney Ross Mitchell</v>
-      </c>
-      <c r="I194" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/sydney-ross-mitchell/1373996317</v>
-      </c>
-      <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/big-boy-problems/1851062193</v>
-      </c>
-      <c r="L194" t="str">
-        <v>Big Boy Problems - Sydney Ross Mitchell</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="str">
-        <v>Griever</v>
-      </c>
-      <c r="B195" t="str">
-        <v/>
-      </c>
-      <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/griever/1860950900</v>
-      </c>
-      <c r="D195" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E195" t="str">
-        <v/>
-      </c>
-      <c r="F195" t="str">
-        <v>Griever - Single</v>
-      </c>
-      <c r="G195" t="str">
-        <v>2:31</v>
-      </c>
-      <c r="H195" t="str">
-        <v>Avery Cochrane</v>
-      </c>
-      <c r="I195" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/avery-cochrane/1556978969</v>
-      </c>
-      <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/griever/1860950897</v>
-      </c>
-      <c r="L195" t="str">
-        <v>Griever - Avery Cochrane</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="str">
-        <v>7 BESOS</v>
-      </c>
-      <c r="B196" t="str">
-        <v/>
-      </c>
-      <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/7-besos/1862927855</v>
-      </c>
-      <c r="D196" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E196" t="str">
-        <v/>
-      </c>
-      <c r="F196" t="str">
-        <v>7 BESOS - Single</v>
-      </c>
-      <c r="G196" t="str">
-        <v>3:21</v>
-      </c>
-      <c r="H196" t="str">
-        <v>LEGADO 7</v>
-      </c>
-      <c r="I196" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/legado-7/997011422</v>
-      </c>
-      <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/7-besos/1862927851</v>
-      </c>
-      <c r="L196" t="str">
-        <v>7 BESOS - LEGADO 7</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="str">
-        <v>UN LEÑO</v>
-      </c>
-      <c r="B197" t="str">
-        <v/>
-      </c>
-      <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/un-le%C3%B1o/1862904727</v>
-      </c>
-      <c r="D197" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E197" t="str">
-        <v/>
-      </c>
-      <c r="F197" t="str">
-        <v>UN LEÑO - Single</v>
-      </c>
-      <c r="G197" t="str">
-        <v>3:00</v>
-      </c>
-      <c r="H197" t="str">
-        <v>Armenta</v>
-      </c>
-      <c r="I197" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/armenta/1479504876</v>
-      </c>
-      <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/un-le%C3%B1o/1862904402</v>
-      </c>
-      <c r="L197" t="str">
-        <v>UN LEÑO - Armenta</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="str">
-        <v>Queen's Goodbye</v>
-      </c>
-      <c r="B198" t="str">
-        <v/>
-      </c>
-      <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/queens-goodbye/1858554528</v>
-      </c>
-      <c r="D198" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E198" t="str">
-        <v/>
-      </c>
-      <c r="F198" t="str">
-        <v>Mārara</v>
-      </c>
-      <c r="G198" t="str">
-        <v>3:46</v>
-      </c>
-      <c r="H198" t="str">
-        <v>15 15</v>
-      </c>
-      <c r="I198" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
-      </c>
-      <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/queens-goodbye/1858554036</v>
-      </c>
-      <c r="L198" t="str">
-        <v>Queen's Goodbye - 15 15</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="str">
-        <v>Bring Me Back To Life</v>
-      </c>
-      <c r="B199" t="str">
-        <v/>
-      </c>
-      <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/bring-me-back-to-life/1851634795</v>
-      </c>
-      <c r="D199" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E199" t="str">
-        <v/>
-      </c>
-      <c r="F199" t="str">
-        <v>Melancholia - EP</v>
-      </c>
-      <c r="G199" t="str">
-        <v>3:24</v>
-      </c>
-      <c r="H199" t="str">
-        <v>JELISA</v>
-      </c>
-      <c r="I199" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/jelisa/1588318671</v>
-      </c>
-      <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/bring-me-back-to-life/1851634783</v>
-      </c>
-      <c r="L199" t="str">
-        <v>Bring Me Back To Life - JELISA</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="str">
-        <v>I Don't Care</v>
-      </c>
-      <c r="B200" t="str">
-        <v/>
-      </c>
-      <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/i-dont-care/1868429644</v>
-      </c>
-      <c r="D200" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E200" t="str">
-        <v/>
-      </c>
-      <c r="F200" t="str">
-        <v>I Don't Care - Single</v>
-      </c>
-      <c r="G200" t="str">
-        <v>3:49</v>
-      </c>
-      <c r="H200" t="str">
-        <v>Buffalo Traffic Jam</v>
-      </c>
-      <c r="I200" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
-      </c>
-      <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/i-dont-care/1868429639</v>
-      </c>
-      <c r="L200" t="str">
-        <v>I Don't Care - Buffalo Traffic Jam</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="str">
-        <v>Elastico (feat. KATE LINN)</v>
-      </c>
-      <c r="B201" t="str">
-        <v/>
-      </c>
-      <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/elastico-feat-kate-linn/1862157500</v>
-      </c>
-      <c r="D201" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E201" t="str">
-        <v/>
-      </c>
-      <c r="F201" t="str">
-        <v>Elastico (feat. KATE LINN) - Single</v>
-      </c>
-      <c r="G201" t="str">
-        <v>3:20</v>
-      </c>
-      <c r="H201" t="str">
-        <v>Fantomel</v>
-      </c>
-      <c r="I201" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/fantomel/1736085960</v>
-      </c>
-      <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/elastico-feat-kate-linn/1862157496</v>
-      </c>
-      <c r="L201" t="str">
-        <v>Elastico (feat. KATE LINN) - Fantomel</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="str">
-        <v>Black &amp; Gold</v>
-      </c>
-      <c r="B202" t="str">
-        <v/>
-      </c>
-      <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/black-gold/1853914794</v>
-      </c>
-      <c r="D202" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E202" t="str">
-        <v/>
-      </c>
-      <c r="F202" t="str">
-        <v>Black &amp; Gold - Single</v>
-      </c>
-      <c r="G202" t="str">
-        <v>3:12</v>
-      </c>
-      <c r="H202" t="str">
-        <v>Claptone</v>
-      </c>
-      <c r="I202" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/claptone/470488523</v>
-      </c>
-      <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/black-gold/1853914793</v>
-      </c>
-      <c r="L202" t="str">
-        <v>Black &amp; Gold - Claptone</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="str">
-        <v>Close Your Eyes</v>
-      </c>
-      <c r="B203" t="str">
-        <v/>
-      </c>
-      <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/close-your-eyes/1860632907</v>
-      </c>
-      <c r="D203" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E203" t="str">
-        <v/>
-      </c>
-      <c r="F203" t="str">
-        <v>Close Your Eyes - Single</v>
-      </c>
-      <c r="G203" t="str">
-        <v>3:33</v>
-      </c>
-      <c r="H203" t="str">
-        <v>Adam Beyer</v>
-      </c>
-      <c r="I203" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/adam-beyer/101672291</v>
-      </c>
-      <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/close-your-eyes/1860632569</v>
-      </c>
-      <c r="L203" t="str">
-        <v>Close Your Eyes - Adam Beyer</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="str">
-        <v>Movement</v>
-      </c>
-      <c r="B204" t="str">
-        <v/>
-      </c>
-      <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/movement/1867063797</v>
-      </c>
-      <c r="D204" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E204" t="str">
-        <v/>
-      </c>
-      <c r="F204" t="str">
-        <v>Movement - Single</v>
-      </c>
-      <c r="G204" t="str">
-        <v>3:07</v>
-      </c>
-      <c r="H204" t="str">
-        <v>Crankdat</v>
-      </c>
-      <c r="I204" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/crankdat/1073027547</v>
-      </c>
-      <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/movement/1867063796</v>
-      </c>
-      <c r="L204" t="str">
-        <v>Movement - Crankdat</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="str">
-        <v>Ayi Giri</v>
-      </c>
-      <c r="B205" t="str">
-        <v/>
-      </c>
-      <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/ayi-giri/1867306651</v>
-      </c>
-      <c r="D205" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E205" t="str">
-        <v/>
-      </c>
-      <c r="F205" t="str">
-        <v>Ayi Giri / Dopamine Machine - Single</v>
-      </c>
-      <c r="G205" t="str">
-        <v>3:06</v>
-      </c>
-      <c r="H205" t="str">
-        <v>Lilly Palmer</v>
-      </c>
-      <c r="I205" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/lilly-palmer/340777023</v>
-      </c>
-      <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/ayi-giri/1867306650</v>
-      </c>
-      <c r="L205" t="str">
-        <v>Ayi Giri - Lilly Palmer</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="str">
-        <v>It's A Sin</v>
-      </c>
-      <c r="B206" t="str">
-        <v/>
-      </c>
-      <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/its-a-sin/1861930282</v>
-      </c>
-      <c r="D206" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E206" t="str">
-        <v/>
-      </c>
-      <c r="F206" t="str">
-        <v>It's A Sin - Single</v>
-      </c>
-      <c r="G206" t="str">
-        <v>4:40</v>
-      </c>
-      <c r="H206" t="str">
-        <v>Ghost</v>
-      </c>
-      <c r="I206" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/ghost/600730426</v>
-      </c>
-      <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/its-a-sin/1861930280</v>
-      </c>
-      <c r="L206" t="str">
-        <v>It's A Sin - Ghost</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="str">
-        <v>Krushers Of The World</v>
-      </c>
-      <c r="B207" t="str">
-        <v/>
-      </c>
-      <c r="C207" t="str">
-        <v>https://music.apple.com/us/song/krushers-of-the-world/1837718526</v>
-      </c>
-      <c r="D207" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E207" t="str">
-        <v/>
-      </c>
-      <c r="F207" t="str">
-        <v>Krushers Of The World</v>
-      </c>
-      <c r="G207" t="str">
-        <v>4:20</v>
-      </c>
-      <c r="H207" t="str">
-        <v>Kreator</v>
-      </c>
-      <c r="I207" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J207" t="str">
-        <v>https://music.apple.com/us/artist/kreator/3258504</v>
-      </c>
-      <c r="K207" t="str">
-        <v>https://music.apple.com/us/album/krushers-of-the-world/1837718517</v>
-      </c>
-      <c r="L207" t="str">
-        <v>Krushers Of The World - Kreator</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="str">
-        <v>Thoroughbreds</v>
-      </c>
-      <c r="B208" t="str">
-        <v/>
-      </c>
-      <c r="C208" t="str">
-        <v>https://music.apple.com/us/song/thoroughbreds/1863532917</v>
-      </c>
-      <c r="D208" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E208" t="str">
-        <v/>
-      </c>
-      <c r="F208" t="str">
-        <v>Peace In Place</v>
-      </c>
-      <c r="G208" t="str">
-        <v>3:24</v>
-      </c>
-      <c r="H208" t="str">
-        <v>Poison the Well</v>
-      </c>
-      <c r="I208" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J208" t="str">
-        <v>https://music.apple.com/us/artist/poison-the-well/1710155</v>
-      </c>
-      <c r="K208" t="str">
-        <v>https://music.apple.com/us/album/thoroughbreds/1863532634</v>
-      </c>
-      <c r="L208" t="str">
-        <v>Thoroughbreds - Poison the Well</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="str">
-        <v>Adversary</v>
-      </c>
-      <c r="B209" t="str">
-        <v/>
-      </c>
-      <c r="C209" t="str">
-        <v>https://music.apple.com/us/song/adversary/1861901940</v>
-      </c>
-      <c r="D209" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E209" t="str">
-        <v/>
-      </c>
-      <c r="F209" t="str">
-        <v>Descent</v>
-      </c>
-      <c r="G209" t="str">
-        <v>3:17</v>
-      </c>
-      <c r="H209" t="str">
-        <v>Immolation</v>
-      </c>
-      <c r="I209" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J209" t="str">
-        <v>https://music.apple.com/us/artist/immolation/64874488</v>
-      </c>
-      <c r="K209" t="str">
-        <v>https://music.apple.com/us/album/adversary/1861901597</v>
-      </c>
-      <c r="L209" t="str">
-        <v>Adversary - Immolation</v>
+        <v>Bomb To A Knife Fight - The Barbarians of California</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L209"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L189"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-01-week04/titles.xlsx
+++ b/data/global/2026-01-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L189"/>
+  <dimension ref="A1:L197"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video)</v>
+        <v>שמעון ביטון - תפילות קאבר להורדה</v>
       </c>
       <c r="B2" t="str">
-        <v>12 hours ago</v>
+        <v>2026-01-23</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409337&amp;sid=28578d22d6bc8863a18a652dcec3ff77</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-23</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>12 hours ago</v>
+        <v/>
       </c>
       <c r="G2" t="str">
-        <v>2:59</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>Lana Lubany</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
+        <v>שמעון ביטון - תפילות קאבר להורדה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
+        <v>נריה עובדיה - ילדה של אב קאבר להורדה</v>
       </c>
       <c r="B3" t="str">
-        <v>18 hours ago</v>
+        <v>2026-01-23</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409336&amp;sid=28578d22d6bc8863a18a652dcec3ff77</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-23</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>18 hours ago</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>4:21</v>
+        <v/>
       </c>
       <c r="H3" t="str">
-        <v>DEF LEPPARD</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
+        <v>נריה עובדיה - ילדה של אב קאבר להורדה</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
+        <v>נועם דדון - זר של נרקיסים קאבר להורדה</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>2026-01-23</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409335&amp;sid=28578d22d6bc8863a18a652dcec3ff77</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-23</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G4" t="str">
-        <v>4:09</v>
+        <v/>
       </c>
       <c r="H4" t="str">
-        <v>Dermot Kennedy</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
+        <v>נועם דדון - זר של נרקיסים קאבר להורדה</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
+        <v>יהונתן נחמיאס - מאשאפ חופות 2026 להורדה</v>
       </c>
       <c r="B5" t="str">
-        <v>2 days ago</v>
+        <v>2026-01-23</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409334&amp;sid=28578d22d6bc8863a18a652dcec3ff77</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-23</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G5" t="str">
-        <v>2:34</v>
+        <v/>
       </c>
       <c r="H5" t="str">
-        <v>Lauren Sanderson</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
+        <v>יהונתן נחמיאס - מאשאפ חופות 2026 להורדה</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
+        <v>חנוך שובל - עולם בשני צבעים קאבר להורדה</v>
       </c>
       <c r="B6" t="str">
-        <v>2 days ago</v>
+        <v>2026-01-23</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409333&amp;sid=28578d22d6bc8863a18a652dcec3ff77</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-23</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G6" t="str">
-        <v>3:10</v>
+        <v/>
       </c>
       <c r="H6" t="str">
-        <v>Olivia Dean</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
+        <v>חנוך שובל - עולם בשני צבעים קאבר להורדה</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
+        <v>חן גז - אהבה חולה קאבר להורדה</v>
       </c>
       <c r="B7" t="str">
-        <v>2 days ago</v>
+        <v>2026-01-23</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409332&amp;sid=28578d22d6bc8863a18a652dcec3ff77</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-23</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G7" t="str">
-        <v>3:21</v>
+        <v/>
       </c>
       <c r="H7" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
+        <v>חן גז - אהבה חולה קאבר להורדה</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video)</v>
+        <v>אוריאל שלום - אשת חיל שלי קאבר להורדה</v>
       </c>
       <c r="B8" t="str">
-        <v>3 days ago</v>
+        <v>2026-01-23</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409331&amp;sid=28578d22d6bc8863a18a652dcec3ff77</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-23</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G8" t="str">
-        <v>3:06</v>
+        <v/>
       </c>
       <c r="H8" t="str">
-        <v>The Avett Brothers</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
+        <v>אוריאל שלום - אשת חיל שלי קאבר להורדה</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video)</v>
+        <v>אבירם ברמי - איפה את קאבר להורדה</v>
       </c>
       <c r="B9" t="str">
-        <v>3 days ago</v>
+        <v>2026-01-23</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409330&amp;sid=28578d22d6bc8863a18a652dcec3ff77</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-23</v>
@@ -717,16 +717,16 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G9" t="str">
-        <v>3:21</v>
+        <v/>
       </c>
       <c r="H9" t="str">
-        <v>Jordana Bryant</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
+        <v>אבירם ברמי - איפה את קאבר להורדה</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
+        <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>3 days ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
+        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-23</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>3 days ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G10" t="str">
-        <v>7:21</v>
+        <v>2:59</v>
       </c>
       <c r="H10" t="str">
-        <v>Katy Perry</v>
+        <v>Lana Lubany</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
+        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>3 days ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
+        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-23</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>3 days ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:17</v>
+        <v>4:21</v>
       </c>
       <c r="H11" t="str">
-        <v>Lauren Watkins</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Just A Mess (Live acoustic studio session)</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
+        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-23</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:45</v>
+        <v>4:09</v>
       </c>
       <c r="H12" t="str">
-        <v>Tones And I</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
+        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-23</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:57</v>
+        <v>2:34</v>
       </c>
       <c r="H13" t="str">
-        <v>Ashleigh Dallas</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B14" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
+        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-23</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:03</v>
+        <v>3:10</v>
       </c>
       <c r="H14" t="str">
-        <v>Charlie Puth</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B15" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
+        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-23</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>4:27</v>
+        <v>3:21</v>
       </c>
       <c r="H15" t="str">
-        <v>Chappell Roan</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
+        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-23</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>4:34</v>
+        <v>3:06</v>
       </c>
       <c r="H16" t="str">
-        <v>Armik</v>
+        <v>The Avett Brothers</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>LØLØ - 007 (Official Music Video)</v>
+        <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
+        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-23</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>2:54</v>
+        <v>3:21</v>
       </c>
       <c r="H17" t="str">
-        <v>LØLØ</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
+        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer)</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B18" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
+        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-23</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:25</v>
+        <v>7:21</v>
       </c>
       <c r="H18" t="str">
-        <v>Tenille Townes</v>
+        <v>Katy Perry</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video)</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B19" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
+        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-23</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>2:01</v>
+        <v>3:17</v>
       </c>
       <c r="H19" t="str">
-        <v>Alan Walker</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio)</v>
+        <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B20" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
+        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-23</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>2:25</v>
+        <v>3:45</v>
       </c>
       <c r="H20" t="str">
-        <v>Charli xcx</v>
+        <v>Tones And I</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
+        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer)</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B21" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
+        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-23</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>1:14</v>
+        <v>3:57</v>
       </c>
       <c r="H21" t="str">
-        <v>Labrinth</v>
+        <v>Ashleigh Dallas</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
+        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-23</v>
@@ -1211,10 +1211,10 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>2:59</v>
+        <v>3:03</v>
       </c>
       <c r="H22" t="str">
         <v>Charlie Puth</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Girl Tones - Volcano (Visualizer)</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B23" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
+        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-23</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>2:29</v>
+        <v>4:27</v>
       </c>
       <c r="H23" t="str">
-        <v>Girl Tones</v>
+        <v>Chappell Roan</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B24" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
+        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-23</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>2:34</v>
+        <v>4:34</v>
       </c>
       <c r="H24" t="str">
-        <v>Jagwar Twin</v>
+        <v>Armik</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
+        <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
+        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-23</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:48</v>
+        <v>2:54</v>
       </c>
       <c r="H25" t="str">
-        <v>Caroline Jones</v>
+        <v>LØLØ</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
+        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
+        <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B26" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
+        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-23</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:32</v>
+        <v>3:25</v>
       </c>
       <c r="H26" t="str">
-        <v>The Beaches</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
+        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
+        <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
+        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-23</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:49</v>
+        <v>2:01</v>
       </c>
       <c r="H27" t="str">
-        <v>Dolly Parton</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
+        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Madison Beer - bad enough (Official Music Video)</v>
+        <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B28" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
+        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-23</v>
@@ -1442,10 +1442,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>4:28</v>
+        <v>2:25</v>
       </c>
       <c r="H28" t="str">
-        <v>Madison Beer</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
+        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Ty Myers - Message to You (Official Video)</v>
+        <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B29" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
+        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-23</v>
@@ -1480,10 +1480,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:37</v>
+        <v>1:14</v>
       </c>
       <c r="H29" t="str">
-        <v>Ty Myers</v>
+        <v>Labrinth</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
+        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B30" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
+        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-23</v>
@@ -1518,10 +1518,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:35</v>
+        <v>2:59</v>
       </c>
       <c r="H30" t="str">
-        <v>Megan Moroney</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
+        <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B31" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
+        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-23</v>
@@ -1556,10 +1556,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>2:31</v>
+        <v>2:29</v>
       </c>
       <c r="H31" t="str">
-        <v>Julia Cole Music</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
+        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B32" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
+        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-23</v>
@@ -1594,10 +1594,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:21</v>
+        <v>2:34</v>
       </c>
       <c r="H32" t="str">
-        <v>Lily Allen</v>
+        <v>Jagwar Twin</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B33" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
+        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-23</v>
@@ -1632,10 +1632,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>5:24</v>
+        <v>3:48</v>
       </c>
       <c r="H33" t="str">
-        <v>Nickless</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Peach PRC - Back To You (Official Audio)</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
       </c>
       <c r="B34" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
+        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-23</v>
@@ -1670,10 +1670,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:11</v>
+        <v>3:32</v>
       </c>
       <c r="H34" t="str">
-        <v>Peach PRC</v>
+        <v>The Beaches</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
       </c>
       <c r="B35" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
+        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-23</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>4:11</v>
+        <v>3:49</v>
       </c>
       <c r="H35" t="str">
-        <v>Ocean Alley</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Madison Beer - bad enough (Official Music Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
+        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-23</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:31</v>
+        <v>4:28</v>
       </c>
       <c r="H36" t="str">
-        <v>OneRepublic</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
+        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
+        <v>Ty Myers - Message to You (Official Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
+        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-23</v>
@@ -1781,10 +1781,10 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>4:16</v>
+        <v>3:37</v>
       </c>
       <c r="H37" t="str">
         <v>Ty Myers</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
+        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
+        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-23</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>4:42</v>
+        <v>3:35</v>
       </c>
       <c r="H38" t="str">
-        <v>JavaJazzFest</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video)</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
+        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-23</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>2:47</v>
+        <v>2:31</v>
       </c>
       <c r="H39" t="str">
-        <v>Teo Glacier</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
       </c>
       <c r="B40" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
+        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-23</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:59</v>
+        <v>3:21</v>
       </c>
       <c r="H40" t="str">
-        <v>Brigitte Calls Me Baby</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
       </c>
       <c r="B41" t="str">
-        <v>11 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
+        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-23</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>11 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>4:09</v>
+        <v>5:24</v>
       </c>
       <c r="H41" t="str">
-        <v>Louie TheSinger</v>
+        <v>Nickless</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ella jane - When I Was Beautiful (Live)</v>
+        <v>Peach PRC - Back To You (Official Audio)</v>
       </c>
       <c r="B42" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
+        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-23</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:24</v>
+        <v>3:11</v>
       </c>
       <c r="H42" t="str">
-        <v>ella jane</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
+        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Johnny Orlando - Emilia (Official Video)</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
       </c>
       <c r="B43" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
+        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-23</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:14</v>
+        <v>4:11</v>
       </c>
       <c r="H43" t="str">
-        <v>Johnny Orlando</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video)</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B44" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
+        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-23</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:32</v>
+        <v>3:31</v>
       </c>
       <c r="H44" t="str">
-        <v>Kungs</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
       </c>
       <c r="B45" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
+        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-23</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:15</v>
+        <v>4:16</v>
       </c>
       <c r="H45" t="str">
-        <v>Billy Raffoul</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B46" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
+        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-23</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:03</v>
+        <v>4:42</v>
       </c>
       <c r="H46" t="str">
-        <v>NathanEvanss</v>
+        <v>JavaJazzFest</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Stephen Sanchez - Sweet Love</v>
+        <v>Teo Glacier - Don't Mind (Music Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
+        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-23</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:04</v>
+        <v>2:47</v>
       </c>
       <c r="H47" t="str">
-        <v>Stephen Sanchez</v>
+        <v>Teo Glacier</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
+        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video]</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
+        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-23</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:33</v>
+        <v>3:59</v>
       </c>
       <c r="H48" t="str">
-        <v>Bruno Mars</v>
+        <v>Brigitte Calls Me Baby</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
       </c>
       <c r="B49" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
+        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-23</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>2:53</v>
+        <v>4:09</v>
       </c>
       <c r="H49" t="str">
-        <v>MAX</v>
+        <v>Louie TheSinger</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
+        <v>ella jane - When I Was Beautiful (Live)</v>
       </c>
       <c r="B50" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
+        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-23</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>4:11</v>
+        <v>3:24</v>
       </c>
       <c r="H50" t="str">
-        <v>Jessie J</v>
+        <v>ella jane</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
+        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
+        <v>Johnny Orlando - Emilia (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
+        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-23</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>2:45</v>
+        <v>3:14</v>
       </c>
       <c r="H51" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
+        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
+        <v>Kungs, Theophilus London - Galaxy (official video)</v>
       </c>
       <c r="B52" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
+        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-23</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>4:00</v>
+        <v>3:32</v>
       </c>
       <c r="H52" t="str">
-        <v>Brandon Lake and Cody Johnson</v>
+        <v>Kungs</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
+        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
       </c>
       <c r="B53" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
+        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-23</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:27</v>
+        <v>3:15</v>
       </c>
       <c r="H53" t="str">
-        <v>The Kid LAROI.</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
+        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-23</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:25</v>
+        <v>3:03</v>
       </c>
       <c r="H54" t="str">
-        <v>Olivia Dean</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Stephen Sanchez - Sweet Love</v>
       </c>
       <c r="B55" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
+        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-23</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:34</v>
+        <v>3:04</v>
       </c>
       <c r="H55" t="str">
-        <v>Demi Lovato</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Train - Mittens (Live on TODAY)</v>
+        <v>Bruno Mars - I Just Might [Official Music Video]</v>
       </c>
       <c r="B56" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=R2k_wPsAHKQ</v>
+        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-23</v>
@@ -2506,10 +2506,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:17</v>
+        <v>3:33</v>
       </c>
       <c r="H56" t="str">
-        <v>Train</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Train - Mittens (Live on TODAY) - Train</v>
+        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
       </c>
       <c r="B57" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
+        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-23</v>
@@ -2544,10 +2544,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G57" t="str">
-        <v>2:25</v>
+        <v>2:53</v>
       </c>
       <c r="H57" t="str">
-        <v>Joseph</v>
+        <v>MAX</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
       </c>
       <c r="B58" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
+        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-23</v>
@@ -2582,10 +2582,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:26</v>
+        <v>4:11</v>
       </c>
       <c r="H58" t="str">
-        <v>Demi Lovato</v>
+        <v>Jessie J</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
       </c>
       <c r="B59" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
+        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-23</v>
@@ -2620,10 +2620,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G59" t="str">
-        <v>4:46</v>
+        <v>2:45</v>
       </c>
       <c r="H59" t="str">
-        <v>Keith Urban</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
       </c>
       <c r="B60" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
+        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-23</v>
@@ -2658,10 +2658,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:24</v>
+        <v>4:00</v>
       </c>
       <c r="H60" t="str">
-        <v>Keith Urban</v>
+        <v>Brandon Lake and Cody Johnson</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
       </c>
       <c r="B61" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
+        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-23</v>
@@ -2696,10 +2696,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
-        <v>2:52</v>
+        <v>3:27</v>
       </c>
       <c r="H61" t="str">
-        <v>Madonna</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
       </c>
       <c r="B62" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
+        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-23</v>
@@ -2734,10 +2734,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
-        <v>2:06</v>
+        <v>3:25</v>
       </c>
       <c r="H62" t="str">
-        <v>Estas Tonne</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estas Tonne</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Anna Graves - Burn On (Official Music Video)</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B63" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
+        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-23</v>
@@ -2772,10 +2772,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:09</v>
+        <v>3:34</v>
       </c>
       <c r="H63" t="str">
-        <v>Anna Graves</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
+        <v>Train - Mittens (Live on TODAY)</v>
       </c>
       <c r="B64" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
+        <v>https://www.youtube.com/watch?v=R2k_wPsAHKQ</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-23</v>
@@ -2810,10 +2810,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
-        <v>5:11</v>
+        <v>3:17</v>
       </c>
       <c r="H64" t="str">
-        <v>Ocean Alley</v>
+        <v>Train</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
+        <v>Train - Mittens (Live on TODAY) - Train</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
       </c>
       <c r="B65" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
+        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-23</v>
@@ -2848,10 +2848,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:40</v>
+        <v>2:25</v>
       </c>
       <c r="H65" t="str">
-        <v>Zara Larsson</v>
+        <v>Joseph</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B66" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
+        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-23</v>
@@ -2886,10 +2886,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:49</v>
+        <v>3:26</v>
       </c>
       <c r="H66" t="str">
-        <v>Lauren Watkins</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
+        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-23</v>
@@ -2924,10 +2924,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:42</v>
+        <v>4:46</v>
       </c>
       <c r="H67" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
+        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-23</v>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>5:11</v>
+        <v>3:24</v>
       </c>
       <c r="H68" t="str">
-        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
+        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-23</v>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:57</v>
+        <v>2:52</v>
       </c>
       <c r="H69" t="str">
-        <v>Lainey Wilson</v>
+        <v>Madonna</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Grace Enger - All My Songs (Official Lyric Video)</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=gWyaiGAFVO8</v>
+        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-23</v>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:29</v>
+        <v>2:06</v>
       </c>
       <c r="H70" t="str">
-        <v>Grace Enger</v>
+        <v>Estas Tonne</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Grace Enger - All My Songs (Official Lyric Video) - Grace Enger</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estas Tonne</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Alan Walker - Broken Strings (Official Music Video)</v>
+        <v>Anna Graves - Burn On (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=jwQKcW474Tc</v>
+        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-23</v>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:10</v>
+        <v>3:09</v>
       </c>
       <c r="H71" t="str">
-        <v>Alan Walker and 2 more</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Alan Walker - Broken Strings (Official Music Video) - Alan Walker and 2 more</v>
+        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Emilia Tarrant - Break Up With Myself</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=3N7iKwqENP0</v>
+        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-23</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>4:04</v>
+        <v>5:11</v>
       </c>
       <c r="H72" t="str">
-        <v>Emilia Tarrant</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Emilia Tarrant - Break Up With Myself - Emilia Tarrant</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026)</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
       </c>
       <c r="B73" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=sKG5ZIzCnFQ</v>
+        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-23</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:09</v>
+        <v>3:40</v>
       </c>
       <c r="H73" t="str">
-        <v>Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026) - Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer)</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B74" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=Koj30I91_8k</v>
+        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-23</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>2:27</v>
+        <v>3:49</v>
       </c>
       <c r="H74" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer) - Lauren Spencer Smith</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Maggie Lindemann - fate</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B75" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=xZdWEmnRK4g</v>
+        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-23</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>2:12</v>
+        <v>3:42</v>
       </c>
       <c r="H75" t="str">
-        <v>Maggie Lindemann</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Maggie Lindemann - fate - Maggie Lindemann</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023)</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B76" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=wo9yPPCh75Q</v>
+        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-23</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>4:44</v>
+        <v>5:11</v>
       </c>
       <c r="H76" t="str">
-        <v>Cliff Richard</v>
+        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023) - Cliff Richard</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
       </c>
       <c r="B77" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=ND6maRwmzHk</v>
+        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-23</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>1:00:09</v>
+        <v>3:57</v>
       </c>
       <c r="H77" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025 - Purple Disco Machine</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>RAYE - Black Mascara. (Live at The Royal Albert Hall)</v>
+        <v>Grace Enger - All My Songs (Official Lyric Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=9jMMOYr-VhE</v>
+        <v>https://www.youtube.com/watch?v=gWyaiGAFVO8</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-23</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>4:15</v>
+        <v>3:29</v>
       </c>
       <c r="H78" t="str">
-        <v>RAYE</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>RAYE - Black Mascara. (Live at The Royal Albert Hall) - RAYE</v>
+        <v>Grace Enger - All My Songs (Official Lyric Video) - Grace Enger</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Madison Cunningham - My Full Name (Garden Session)</v>
+        <v>Alan Walker - Broken Strings (Official Music Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=o2F-QmqdNtI</v>
+        <v>https://www.youtube.com/watch?v=jwQKcW474Tc</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-23</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>4:07</v>
+        <v>3:10</v>
       </c>
       <c r="H79" t="str">
-        <v>Madison Cunningham</v>
+        <v>Alan Walker and 2 more</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Madison Cunningham - My Full Name (Garden Session) - Madison Cunningham</v>
+        <v>Alan Walker - Broken Strings (Official Music Video) - Alan Walker and 2 more</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions)</v>
+        <v>Emilia Tarrant - Break Up With Myself</v>
       </c>
       <c r="B80" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=5-6cEVLqE90</v>
+        <v>https://www.youtube.com/watch?v=3N7iKwqENP0</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-23</v>
@@ -3418,10 +3418,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:10</v>
+        <v>4:04</v>
       </c>
       <c r="H80" t="str">
-        <v>Teddy Swims</v>
+        <v>Emilia Tarrant</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions) - Teddy Swims</v>
+        <v>Emilia Tarrant - Break Up With Myself - Emilia Tarrant</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower)</v>
+        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026)</v>
       </c>
       <c r="B81" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=ivPSbcEMwCs</v>
+        <v>https://www.youtube.com/watch?v=sKG5ZIzCnFQ</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-23</v>
@@ -3456,10 +3456,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:47</v>
+        <v>3:09</v>
       </c>
       <c r="H81" t="str">
-        <v>Christina Aguilera</v>
+        <v>Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower) - Christina Aguilera</v>
+        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026) - Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025)</v>
+        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer)</v>
       </c>
       <c r="B82" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=tYpOHbXFnm0</v>
+        <v>https://www.youtube.com/watch?v=Koj30I91_8k</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-23</v>
@@ -3494,10 +3494,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:58</v>
+        <v>2:27</v>
       </c>
       <c r="H82" t="str">
-        <v>RAYE</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025) - RAYE</v>
+        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Dasha - Here For The Party (Official Audio)</v>
+        <v>Maggie Lindemann - fate</v>
       </c>
       <c r="B83" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=rSO9oYUnO2k</v>
+        <v>https://www.youtube.com/watch?v=xZdWEmnRK4g</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-23</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:30</v>
+        <v>2:12</v>
       </c>
       <c r="H83" t="str">
-        <v>Dasha</v>
+        <v>Maggie Lindemann</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Dasha - Here For The Party (Official Audio) - Dasha</v>
+        <v>Maggie Lindemann - fate - Maggie Lindemann</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Lady Gaga in Harlequin Live: One Night Only</v>
+        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023)</v>
       </c>
       <c r="B84" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=c231tCsQalU</v>
+        <v>https://www.youtube.com/watch?v=wo9yPPCh75Q</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-23</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>51:49</v>
+        <v>4:44</v>
       </c>
       <c r="H84" t="str">
-        <v>Lady Gaga and YouTube</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Lady Gaga in Harlequin Live: One Night Only - Lady Gaga and YouTube</v>
+        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023) - Cliff Richard</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Sabrina Carpenter - Such A Funny Way (Official Lyric Video)</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025</v>
       </c>
       <c r="B85" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=oaJKUCgSSkc</v>
+        <v>https://www.youtube.com/watch?v=ND6maRwmzHk</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-23</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:53</v>
+        <v>1:00:09</v>
       </c>
       <c r="H85" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Sabrina Carpenter - Such A Funny Way (Official Lyric Video) - Sabrina Carpenter</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Megan Moroney - Beautiful Things (Official Fan Video)</v>
+        <v>RAYE - Black Mascara. (Live at The Royal Albert Hall)</v>
       </c>
       <c r="B86" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=0Gxu80LxI0w</v>
+        <v>https://www.youtube.com/watch?v=9jMMOYr-VhE</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-23</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:56</v>
+        <v>4:15</v>
       </c>
       <c r="H86" t="str">
-        <v>Megan Moroney</v>
+        <v>RAYE</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Megan Moroney - Beautiful Things (Official Fan Video) - Megan Moroney</v>
+        <v>RAYE - Black Mascara. (Live at The Royal Albert Hall) - RAYE</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Jason Derulo - Miracle</v>
+        <v>Madison Cunningham - My Full Name (Garden Session)</v>
       </c>
       <c r="B87" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=7sjshHJwkOE</v>
+        <v>https://www.youtube.com/watch?v=o2F-QmqdNtI</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-23</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>4:16</v>
+        <v>4:07</v>
       </c>
       <c r="H87" t="str">
-        <v>Jason Derulo</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Jason Derulo - Miracle - Jason Derulo</v>
+        <v>Madison Cunningham - My Full Name (Garden Session) - Madison Cunningham</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Sananda Maitreya - Pretty Baby (Live)</v>
+        <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions)</v>
       </c>
       <c r="B88" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=yv1c5G5HZt8</v>
+        <v>https://www.youtube.com/watch?v=5-6cEVLqE90</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-23</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:29</v>
+        <v>3:10</v>
       </c>
       <c r="H88" t="str">
-        <v>Sananda Maitreya</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Sananda Maitreya - Pretty Baby (Live) - Sananda Maitreya</v>
+        <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions) - Teddy Swims</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Faded - 10th Anniversary (Performance Video)</v>
+        <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower)</v>
       </c>
       <c r="B89" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=EXVg23U3NRw</v>
+        <v>https://www.youtube.com/watch?v=ivPSbcEMwCs</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-23</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:25</v>
+        <v>3:47</v>
       </c>
       <c r="H89" t="str">
-        <v>Alan Walker and 2 more</v>
+        <v>Christina Aguilera</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Faded - 10th Anniversary (Performance Video) - Alan Walker and 2 more</v>
+        <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower) - Christina Aguilera</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>What Are You Doing New Year's Eve (Live from the Eiffel Tower - Official Lyric Video)</v>
+        <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025)</v>
       </c>
       <c r="B90" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=Bpb67fSUzEQ</v>
+        <v>https://www.youtube.com/watch?v=tYpOHbXFnm0</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-23</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>4:06</v>
+        <v>3:58</v>
       </c>
       <c r="H90" t="str">
-        <v>Christina Aguilera</v>
+        <v>RAYE</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>What Are You Doing New Year's Eve (Live from the Eiffel Tower - Official Lyric Video) - Christina Aguilera</v>
+        <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025) - RAYE</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Have Yourself a Merry Little Christmas (Live from the Eiffel Tower - Official Lyric Video)</v>
+        <v>Dasha - Here For The Party (Official Audio)</v>
       </c>
       <c r="B91" t="str">
         <v>4 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=gkwb6kZloLA</v>
+        <v>https://www.youtube.com/watch?v=rSO9oYUnO2k</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-23</v>
@@ -3836,10 +3836,10 @@
         <v>4 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>4:03</v>
+        <v>3:30</v>
       </c>
       <c r="H91" t="str">
-        <v>Christina Aguilera</v>
+        <v>Dasha</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Have Yourself a Merry Little Christmas (Live from the Eiffel Tower - Official Lyric Video) - Christina Aguilera</v>
+        <v>Dasha - Here For The Party (Official Audio) - Dasha</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Chris Rea - Driving Home for Christmas - (Live on National Lottery Stars, 2000)</v>
+        <v>Lady Gaga in Harlequin Live: One Night Only</v>
       </c>
       <c r="B92" t="str">
-        <v>1 year ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=Jckb3dnS5fw</v>
+        <v>https://www.youtube.com/watch?v=c231tCsQalU</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-23</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>1 year ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>4:11</v>
+        <v>51:49</v>
       </c>
       <c r="H92" t="str">
-        <v>Chris Rea Official</v>
+        <v>Lady Gaga and YouTube</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Chris Rea - Driving Home for Christmas - (Live on National Lottery Stars, 2000) - Chris Rea Official</v>
+        <v>Lady Gaga in Harlequin Live: One Night Only - Lady Gaga and YouTube</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Jessie J - I'll Never Know Why (The Royal Variety Performance 2025)</v>
+        <v>Sabrina Carpenter - Such A Funny Way (Official Lyric Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>1 month ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=DPA8v4YS8AY</v>
+        <v>https://www.youtube.com/watch?v=oaJKUCgSSkc</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-23</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>1 month ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>4:08</v>
+        <v>3:53</v>
       </c>
       <c r="H93" t="str">
-        <v>Jessie J</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Jessie J - I'll Never Know Why (The Royal Variety Performance 2025) - Jessie J</v>
+        <v>Sabrina Carpenter - Such A Funny Way (Official Lyric Video) - Sabrina Carpenter</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Craig David - Walking Away (Official HD Video)</v>
+        <v>Megan Moroney - Beautiful Things (Official Fan Video)</v>
       </c>
       <c r="B94" t="str">
-        <v>1 month ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=v8Yu21pEbqw</v>
+        <v>https://www.youtube.com/watch?v=0Gxu80LxI0w</v>
       </c>
       <c r="D94" t="str">
         <v>2026-01-23</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>1 month ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:34</v>
+        <v>3:56</v>
       </c>
       <c r="H94" t="str">
-        <v>Craig David</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Craig David - Walking Away (Official HD Video) - Craig David</v>
+        <v>Megan Moroney - Beautiful Things (Official Fan Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Christina Aguilera, Yseult - Ave Maria (Live from the Eiffel Tower - Official Video)</v>
+        <v>Jason Derulo - Miracle</v>
       </c>
       <c r="B95" t="str">
-        <v>1 month ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=sq2u9Cfn2B8</v>
+        <v>https://www.youtube.com/watch?v=7sjshHJwkOE</v>
       </c>
       <c r="D95" t="str">
         <v>2026-01-23</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>1 month ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>4:37</v>
+        <v>4:16</v>
       </c>
       <c r="H95" t="str">
-        <v>Christina Aguilera</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Christina Aguilera, Yseult - Ave Maria (Live from the Eiffel Tower - Official Video) - Christina Aguilera</v>
+        <v>Jason Derulo - Miracle - Jason Derulo</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Shawn Mendes &amp; Niall Horan - This Town (Live from London)</v>
+        <v>Sananda Maitreya - Pretty Baby (Live)</v>
       </c>
       <c r="B96" t="str">
-        <v>1 month ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=Ea2DSMNIK5w</v>
+        <v>https://www.youtube.com/watch?v=yv1c5G5HZt8</v>
       </c>
       <c r="D96" t="str">
         <v>2026-01-23</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>1 month ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>6:27</v>
+        <v>3:29</v>
       </c>
       <c r="H96" t="str">
-        <v>Shawn Mendes and Niall Horan</v>
+        <v>Sananda Maitreya</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Shawn Mendes &amp; Niall Horan - This Town (Live from London) - Shawn Mendes and Niall Horan</v>
+        <v>Sananda Maitreya - Pretty Baby (Live) - Sananda Maitreya</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Shakira - Zoo (From "Zootopia 2")</v>
+        <v>Faded - 10th Anniversary (Performance Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>1 month ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=kCIf6yaJisQ</v>
+        <v>https://www.youtube.com/watch?v=EXVg23U3NRw</v>
       </c>
       <c r="D97" t="str">
         <v>2026-01-23</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>1 month ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>2:07</v>
+        <v>3:25</v>
       </c>
       <c r="H97" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>Alan Walker and 2 more</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Shakira - Zoo (From "Zootopia 2") - DisneyMusicVEVO</v>
+        <v>Faded - 10th Anniversary (Performance Video) - Alan Walker and 2 more</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Within Temptation - Ice Queen (Acoustic) | 2025 Reimagined Edition</v>
+        <v>What Are You Doing New Year's Eve (Live from the Eiffel Tower - Official Lyric Video)</v>
       </c>
       <c r="B98" t="str">
-        <v>1 month ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=f1Iqm16vWDQ</v>
+        <v>https://www.youtube.com/watch?v=Bpb67fSUzEQ</v>
       </c>
       <c r="D98" t="str">
         <v>2026-01-23</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>1 month ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:40</v>
+        <v>4:06</v>
       </c>
       <c r="H98" t="str">
-        <v>Within Temptation</v>
+        <v>Christina Aguilera</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Within Temptation - Ice Queen (Acoustic) | 2025 Reimagined Edition - Within Temptation</v>
+        <v>What Are You Doing New Year's Eve (Live from the Eiffel Tower - Official Lyric Video) - Christina Aguilera</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>OneRepublic - Give Me Something (for Arknights Endfield) (Official Audio)</v>
+        <v>Have Yourself a Merry Little Christmas (Live from the Eiffel Tower - Official Lyric Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>1 month ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=4eqzUNO-ONs</v>
+        <v>https://www.youtube.com/watch?v=gkwb6kZloLA</v>
       </c>
       <c r="D99" t="str">
         <v>2026-01-23</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>1 month ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>2:43</v>
+        <v>4:03</v>
       </c>
       <c r="H99" t="str">
-        <v>OneRepublic</v>
+        <v>Christina Aguilera</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>OneRepublic - Give Me Something (for Arknights Endfield) (Official Audio) - OneRepublic</v>
+        <v>Have Yourself a Merry Little Christmas (Live from the Eiffel Tower - Official Lyric Video) - Christina Aguilera</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Passenger | The Road Is Long</v>
+        <v>Chris Rea - Driving Home for Christmas - (Live on National Lottery Stars, 2000)</v>
       </c>
       <c r="B100" t="str">
-        <v>1 month ago</v>
+        <v>1 year ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=oi4aTOc-IX4</v>
+        <v>https://www.youtube.com/watch?v=Jckb3dnS5fw</v>
       </c>
       <c r="D100" t="str">
         <v>2026-01-23</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>1 month ago</v>
+        <v>1 year ago</v>
       </c>
       <c r="G100" t="str">
-        <v>4:01</v>
+        <v>4:11</v>
       </c>
       <c r="H100" t="str">
-        <v>Passenger</v>
+        <v>Chris Rea Official</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Passenger | The Road Is Long - Passenger</v>
+        <v>Chris Rea - Driving Home for Christmas - (Live on National Lottery Stars, 2000) - Chris Rea Official</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Black Honey - Carroll Avenue (Live at RAK)</v>
+        <v>Jessie J - I'll Never Know Why (The Royal Variety Performance 2025)</v>
       </c>
       <c r="B101" t="str">
         <v>1 month ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=LPXTE3a6QrM</v>
+        <v>https://www.youtube.com/watch?v=DPA8v4YS8AY</v>
       </c>
       <c r="D101" t="str">
         <v>2026-01-23</v>
@@ -4216,10 +4216,10 @@
         <v>1 month ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:19</v>
+        <v>4:08</v>
       </c>
       <c r="H101" t="str">
-        <v>Black Honey</v>
+        <v>Jessie J</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Black Honey - Carroll Avenue (Live at RAK) - Black Honey</v>
+        <v>Jessie J - I'll Never Know Why (The Royal Variety Performance 2025) - Jessie J</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Aperture</v>
+        <v>Craig David - Walking Away (Official HD Video)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>1 month ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/aperture/1870984033</v>
+        <v>https://www.youtube.com/watch?v=v8Yu21pEbqw</v>
       </c>
       <c r="D102" t="str">
         <v>2026-01-23</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Kiss All The Time. Disco, Occasionally.</v>
+        <v>1 month ago</v>
       </c>
       <c r="G102" t="str">
-        <v>5:11</v>
+        <v>3:34</v>
       </c>
       <c r="H102" t="str">
-        <v>Harry Styles</v>
+        <v>Craig David</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/aperture/1870984032</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>Aperture - Harry Styles</v>
+        <v>Craig David - Walking Away (Official HD Video) - Craig David</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Opening Night</v>
+        <v>Christina Aguilera, Yseult - Ave Maria (Live from the Eiffel Tower - Official Video)</v>
       </c>
       <c r="B103" t="str">
-        <v/>
+        <v>1 month ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/opening-night/1870313501</v>
+        <v>https://www.youtube.com/watch?v=sq2u9Cfn2B8</v>
       </c>
       <c r="D103" t="str">
         <v>2026-01-23</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>HELP(2)</v>
+        <v>1 month ago</v>
       </c>
       <c r="G103" t="str">
-        <v>4:19</v>
+        <v>4:37</v>
       </c>
       <c r="H103" t="str">
-        <v>Arctic Monkeys</v>
+        <v>Christina Aguilera</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/arctic-monkeys/62820413</v>
+        <v/>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/opening-night/1870313498</v>
+        <v/>
       </c>
       <c r="L103" t="str">
-        <v>Opening Night - Arctic Monkeys</v>
+        <v>Christina Aguilera, Yseult - Ave Maria (Live from the Eiffel Tower - Official Video) - Christina Aguilera</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>FLACKITO JODYE (feat. Tokischa)</v>
+        <v>Shawn Mendes &amp; Niall Horan - This Town (Live from London)</v>
       </c>
       <c r="B104" t="str">
-        <v/>
+        <v>1 month ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/flackito-jodye-feat-tokischa/1870968779</v>
+        <v>https://www.youtube.com/watch?v=Ea2DSMNIK5w</v>
       </c>
       <c r="D104" t="str">
         <v>2026-01-23</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Don't Be Dumb</v>
+        <v>1 month ago</v>
       </c>
       <c r="G104" t="str">
-        <v>2:20</v>
+        <v>6:27</v>
       </c>
       <c r="H104" t="str">
-        <v>A$AP Rocky</v>
+        <v>Shawn Mendes and Niall Horan</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/a%24ap-rocky/481488005</v>
+        <v/>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/flackito-jodye-feat-tokischa/1870968596</v>
+        <v/>
       </c>
       <c r="L104" t="str">
-        <v>FLACKITO JODYE (feat. Tokischa) - A$AP Rocky</v>
+        <v>Shawn Mendes &amp; Niall Horan - This Town (Live from London) - Shawn Mendes and Niall Horan</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>CAMBIARÉ</v>
+        <v>Shakira - Zoo (From "Zootopia 2")</v>
       </c>
       <c r="B105" t="str">
-        <v/>
+        <v>1 month ago</v>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
+        <v>https://www.youtube.com/watch?v=kCIf6yaJisQ</v>
       </c>
       <c r="D105" t="str">
         <v>2026-01-23</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>CAMBIARÉ - Single</v>
+        <v>1 month ago</v>
       </c>
       <c r="G105" t="str">
-        <v>3:01</v>
+        <v>2:07</v>
       </c>
       <c r="H105" t="str">
-        <v>Luis Fonsi</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/luis-fonsi/102834</v>
+        <v/>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/cambiar%C3%A9/1867545265</v>
+        <v/>
       </c>
       <c r="L105" t="str">
-        <v>CAMBIARÉ - Luis Fonsi</v>
+        <v>Shakira - Zoo (From "Zootopia 2") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Last of a Dying Breed</v>
+        <v>Within Temptation - Ice Queen (Acoustic) | 2025 Reimagined Edition</v>
       </c>
       <c r="B106" t="str">
-        <v/>
+        <v>1 month ago</v>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/last-of-a-dying-breed/1849706852</v>
+        <v>https://www.youtube.com/watch?v=f1Iqm16vWDQ</v>
       </c>
       <c r="D106" t="str">
         <v>2026-01-23</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Piss In The Wind</v>
+        <v>1 month ago</v>
       </c>
       <c r="G106" t="str">
-        <v>2:29</v>
+        <v>3:40</v>
       </c>
       <c r="H106" t="str">
-        <v>Joji</v>
+        <v>Within Temptation</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/joji/1258279972</v>
+        <v/>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/last-of-a-dying-breed/1849706656</v>
+        <v/>
       </c>
       <c r="L106" t="str">
-        <v>Last of a Dying Breed - Joji</v>
+        <v>Within Temptation - Ice Queen (Acoustic) | 2025 Reimagined Edition - Within Temptation</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>High Key</v>
+        <v>OneRepublic - Give Me Something (for Arknights Endfield) (Official Audio)</v>
       </c>
       <c r="B107" t="str">
-        <v/>
+        <v>1 month ago</v>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/high-key/1847702418</v>
+        <v>https://www.youtube.com/watch?v=4eqzUNO-ONs</v>
       </c>
       <c r="D107" t="str">
         <v>2026-01-23</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Vacancy</v>
+        <v>1 month ago</v>
       </c>
       <c r="G107" t="str">
-        <v>2:12</v>
+        <v>2:43</v>
       </c>
       <c r="H107" t="str">
-        <v>Ari Lennox</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/ari-lennox/448854570</v>
+        <v/>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/high-key/1847702412</v>
+        <v/>
       </c>
       <c r="L107" t="str">
-        <v>High Key - Ari Lennox</v>
+        <v>OneRepublic - Give Me Something (for Arknights Endfield) (Official Audio) - OneRepublic</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>scared</v>
+        <v>Passenger | The Road Is Long</v>
       </c>
       <c r="B108" t="str">
-        <v/>
+        <v>1 month ago</v>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/scared/1862292863</v>
+        <v>https://www.youtube.com/watch?v=oi4aTOc-IX4</v>
       </c>
       <c r="D108" t="str">
         <v>2026-01-23</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>scared - Single</v>
+        <v>1 month ago</v>
       </c>
       <c r="G108" t="str">
-        <v>4:03</v>
+        <v>4:01</v>
       </c>
       <c r="H108" t="str">
-        <v>Fred again..</v>
+        <v>Passenger</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v/>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/scared/1862292862</v>
+        <v/>
       </c>
       <c r="L108" t="str">
-        <v>scared - Fred again..</v>
+        <v>Passenger | The Road Is Long - Passenger</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Death of Love</v>
+        <v>Black Honey - Carroll Avenue (Live at RAK)</v>
       </c>
       <c r="B109" t="str">
-        <v/>
+        <v>1 month ago</v>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/death-of-love/1862353786</v>
+        <v>https://www.youtube.com/watch?v=LPXTE3a6QrM</v>
       </c>
       <c r="D109" t="str">
         <v>2026-01-23</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Trying Times</v>
+        <v>1 month ago</v>
       </c>
       <c r="G109" t="str">
-        <v>3:26</v>
+        <v>3:19</v>
       </c>
       <c r="H109" t="str">
-        <v>James Blake</v>
+        <v>Black Honey</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v/>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/death-of-love/1862353780</v>
+        <v/>
       </c>
       <c r="L109" t="str">
-        <v>Death of Love - James Blake</v>
+        <v>Black Honey - Carroll Avenue (Live at RAK) - Black Honey</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Big Ole Fancy House</v>
+        <v>Aperture</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/big-ole-fancy-house/1862624759</v>
+        <v>https://music.apple.com/us/song/aperture/1870984033</v>
       </c>
       <c r="D110" t="str">
         <v>2026-01-23</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Parker McCollum (The Deluxe Edition)</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G110" t="str">
-        <v>4:03</v>
+        <v>5:11</v>
       </c>
       <c r="H110" t="str">
-        <v>Parker McCollum</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/big-ole-fancy-house/1862624506</v>
+        <v>https://music.apple.com/us/album/aperture/1870984032</v>
       </c>
       <c r="L110" t="str">
-        <v>Big Ole Fancy House - Parker McCollum</v>
+        <v>Aperture - Harry Styles</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Flo Jackson</v>
+        <v>Opening Night</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
+        <v>https://music.apple.com/us/song/opening-night/1870313501</v>
       </c>
       <c r="D111" t="str">
         <v>2026-01-23</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Flo Jackson - Single</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G111" t="str">
-        <v>2:23</v>
+        <v>4:19</v>
       </c>
       <c r="H111" t="str">
-        <v>Flo Milli</v>
+        <v>Arctic Monkeys</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
+        <v>https://music.apple.com/us/artist/arctic-monkeys/62820413</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
+        <v>https://music.apple.com/us/album/opening-night/1870313498</v>
       </c>
       <c r="L111" t="str">
-        <v>Flo Jackson - Flo Milli</v>
+        <v>Opening Night - Arctic Monkeys</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Site Unseen (feat. Waxahatchee)</v>
+        <v>FLACKITO JODYE (feat. Tokischa)</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
+        <v>https://music.apple.com/us/song/flackito-jodye-feat-tokischa/1870968779</v>
       </c>
       <c r="D112" t="str">
         <v>2026-01-23</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Creature of Habit</v>
+        <v>Don't Be Dumb</v>
       </c>
       <c r="G112" t="str">
-        <v>2:46</v>
+        <v>2:20</v>
       </c>
       <c r="H112" t="str">
-        <v>Courtney Barnett</v>
+        <v>A$AP Rocky</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/a%24ap-rocky/481488005</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
+        <v>https://music.apple.com/us/album/flackito-jodye-feat-tokischa/1870968596</v>
       </c>
       <c r="L112" t="str">
-        <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
+        <v>FLACKITO JODYE (feat. Tokischa) - A$AP Rocky</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Puppet Parade</v>
+        <v>CAMBIARÉ</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
+        <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
       </c>
       <c r="D113" t="str">
         <v>2026-01-23</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Megadeth</v>
+        <v>CAMBIARÉ - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>4:40</v>
+        <v>3:01</v>
       </c>
       <c r="H113" t="str">
-        <v>Megadeth</v>
+        <v>Luis Fonsi</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/megadeth/488289</v>
+        <v>https://music.apple.com/us/artist/luis-fonsi/102834</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
+        <v>https://music.apple.com/us/album/cambiar%C3%A9/1867545265</v>
       </c>
       <c r="L113" t="str">
-        <v>Puppet Parade - Megadeth</v>
+        <v>CAMBIARÉ - Luis Fonsi</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>To Love Somebody</v>
+        <v>Last of a Dying Breed</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/to-love-somebody/1859630040</v>
+        <v>https://music.apple.com/us/song/last-of-a-dying-breed/1849706852</v>
       </c>
       <c r="D114" t="str">
         <v>2026-01-23</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Cruel World</v>
+        <v>Piss In The Wind</v>
       </c>
       <c r="G114" t="str">
-        <v>3:57</v>
+        <v>2:29</v>
       </c>
       <c r="H114" t="str">
-        <v>Holly Humberstone</v>
+        <v>Joji</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/joji/1258279972</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/to-love-somebody/1859629846</v>
+        <v>https://music.apple.com/us/album/last-of-a-dying-breed/1849706656</v>
       </c>
       <c r="L114" t="str">
-        <v>To Love Somebody - Holly Humberstone</v>
+        <v>Last of a Dying Breed - Joji</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Nothing Is Impossible With You</v>
+        <v>High Key</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/nothing-is-impossible-with-you/1870691236</v>
+        <v>https://music.apple.com/us/song/high-key/1847702418</v>
       </c>
       <c r="D115" t="str">
         <v>2026-01-23</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Nothing Is Impossible With You - Single</v>
+        <v>Vacancy</v>
       </c>
       <c r="G115" t="str">
-        <v>4:14</v>
+        <v>2:12</v>
       </c>
       <c r="H115" t="str">
-        <v>Cleo Sol</v>
+        <v>Ari Lennox</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/cleo-sol/459710289</v>
+        <v>https://music.apple.com/us/artist/ari-lennox/448854570</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/nothing-is-impossible-with-you/1870691227</v>
+        <v>https://music.apple.com/us/album/high-key/1847702412</v>
       </c>
       <c r="L115" t="str">
-        <v>Nothing Is Impossible With You - Cleo Sol</v>
+        <v>High Key - Ari Lennox</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>HYPNOTIZE</v>
+        <v>scared</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/hypnotize/1861009528</v>
+        <v>https://music.apple.com/us/song/scared/1862292863</v>
       </c>
       <c r="D116" t="str">
         <v>2026-01-23</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>THE CORE - 核</v>
+        <v>scared - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>2:50</v>
+        <v>4:03</v>
       </c>
       <c r="H116" t="str">
-        <v>XG</v>
+        <v>Fred again..</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/xg/1609409493</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/hypnotize/1861009513</v>
+        <v>https://music.apple.com/us/album/scared/1862292862</v>
       </c>
       <c r="L116" t="str">
-        <v>HYPNOTIZE - XG</v>
+        <v>scared - Fred again..</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Dead End</v>
+        <v>Death of Love</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/dead-end/1862845874</v>
+        <v>https://music.apple.com/us/song/death-of-love/1862353786</v>
       </c>
       <c r="D117" t="str">
         <v>2026-01-23</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Ricochet</v>
+        <v>Trying Times</v>
       </c>
       <c r="G117" t="str">
-        <v>4:05</v>
+        <v>3:26</v>
       </c>
       <c r="H117" t="str">
-        <v>Snail Mail</v>
+        <v>James Blake</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/dead-end/1862845733</v>
+        <v>https://music.apple.com/us/album/death-of-love/1862353780</v>
       </c>
       <c r="L117" t="str">
-        <v>Dead End - Snail Mail</v>
+        <v>Death of Love - James Blake</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Do I Wanna Know?</v>
+        <v>Big Ole Fancy House</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/do-i-wanna-know/1870931500</v>
+        <v>https://music.apple.com/us/song/big-ole-fancy-house/1862624759</v>
       </c>
       <c r="D118" t="str">
         <v>2026-01-23</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Do I Wanna Know? - Single</v>
+        <v>Parker McCollum (The Deluxe Edition)</v>
       </c>
       <c r="G118" t="str">
-        <v>3:52</v>
+        <v>4:03</v>
       </c>
       <c r="H118" t="str">
-        <v>Dove Cameron</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/dove-cameron/599822740</v>
+        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/do-i-wanna-know/1870931327</v>
+        <v>https://music.apple.com/us/album/big-ole-fancy-house/1862624506</v>
       </c>
       <c r="L118" t="str">
-        <v>Do I Wanna Know? - Dove Cameron</v>
+        <v>Big Ole Fancy House - Parker McCollum</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Una y Otra Vez</v>
+        <v>Flo Jackson</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/una-y-otra-vez/1868792926</v>
+        <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
       </c>
       <c r="D119" t="str">
         <v>2026-01-23</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>K de Karma (Apple Music Edition)</v>
+        <v>Flo Jackson - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:02</v>
+        <v>2:23</v>
       </c>
       <c r="H119" t="str">
-        <v>Kenia Os</v>
+        <v>Flo Milli</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
+        <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/una-y-otra-vez/1868792704</v>
+        <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
       </c>
       <c r="L119" t="str">
-        <v>Una y Otra Vez - Kenia Os</v>
+        <v>Flo Jackson - Flo Milli</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>BAD</v>
+        <v>Site Unseen (feat. Waxahatchee)</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/bad/1869095326</v>
+        <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
       </c>
       <c r="D120" t="str">
         <v>2026-01-23</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>BAD - Single</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G120" t="str">
-        <v>2:15</v>
+        <v>2:46</v>
       </c>
       <c r="H120" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/bad/1869095325</v>
+        <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
       </c>
       <c r="L120" t="str">
-        <v>BAD - Chelsea Cutler</v>
+        <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Losing You</v>
+        <v>Puppet Parade</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/losing-you/1863525495</v>
+        <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
       </c>
       <c r="D121" t="str">
         <v>2026-01-23</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>F.I.G</v>
+        <v>Megadeth</v>
       </c>
       <c r="G121" t="str">
-        <v>2:22</v>
+        <v>4:40</v>
       </c>
       <c r="H121" t="str">
-        <v>Naomi Scott</v>
+        <v>Megadeth</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
+        <v>https://music.apple.com/us/artist/megadeth/488289</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/losing-you/1863525485</v>
+        <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
       </c>
       <c r="L121" t="str">
-        <v>Losing You - Naomi Scott</v>
+        <v>Puppet Parade - Megadeth</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Me Voy A La C******a</v>
+        <v>To Love Somebody</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/me-voy-a-la-c-a/1867850749</v>
+        <v>https://music.apple.com/us/song/to-love-somebody/1859630040</v>
       </c>
       <c r="D122" t="str">
         <v>2026-01-23</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Infinito</v>
+        <v>Cruel World</v>
       </c>
       <c r="G122" t="str">
-        <v>2:14</v>
+        <v>3:57</v>
       </c>
       <c r="H122" t="str">
-        <v>Yandel</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/yandel/72929426</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/me-voy-a-la-c-a/1867850739</v>
+        <v>https://music.apple.com/us/album/to-love-somebody/1859629846</v>
       </c>
       <c r="L122" t="str">
-        <v>Me Voy A La C******a - Yandel</v>
+        <v>To Love Somebody - Holly Humberstone</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Sexy For Me</v>
+        <v>Nothing Is Impossible With You</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/sexy-for-me/1867897421</v>
+        <v>https://music.apple.com/us/song/nothing-is-impossible-with-you/1870691236</v>
       </c>
       <c r="D123" t="str">
         <v>2026-01-23</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>The Last Dance (Part 1)</v>
+        <v>Nothing Is Impossible With You - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>2:08</v>
+        <v>4:14</v>
       </c>
       <c r="H123" t="str">
-        <v>Jason Derulo</v>
+        <v>Cleo Sol</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/jason-derulo/259118085</v>
+        <v>https://music.apple.com/us/artist/cleo-sol/459710289</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/sexy-for-me/1867897420</v>
+        <v>https://music.apple.com/us/album/nothing-is-impossible-with-you/1870691227</v>
       </c>
       <c r="L123" t="str">
-        <v>Sexy For Me - Jason Derulo</v>
+        <v>Nothing Is Impossible With You - Cleo Sol</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Turbulence</v>
+        <v>HYPNOTIZE</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/turbulence/1867908449</v>
+        <v>https://music.apple.com/us/song/hypnotize/1861009528</v>
       </c>
       <c r="D124" t="str">
         <v>2026-01-23</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>REAL, Vol. 1 - EP</v>
+        <v>THE CORE - 核</v>
       </c>
       <c r="G124" t="str">
-        <v>2:25</v>
+        <v>2:50</v>
       </c>
       <c r="H124" t="str">
-        <v>Wizkid</v>
+        <v>XG</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
+        <v>https://music.apple.com/us/artist/xg/1609409493</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/turbulence/1867908237</v>
+        <v>https://music.apple.com/us/album/hypnotize/1861009513</v>
       </c>
       <c r="L124" t="str">
-        <v>Turbulence - Wizkid</v>
+        <v>HYPNOTIZE - XG</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>I’m Good (From The Movie “GOAT”)</v>
+        <v>Dead End</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/im-good-from-the-movie-goat/1870623298</v>
+        <v>https://music.apple.com/us/song/dead-end/1862845874</v>
       </c>
       <c r="D125" t="str">
         <v>2026-01-23</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>GOAT (Original Motion Picture Soundtrack)</v>
+        <v>Ricochet</v>
       </c>
       <c r="G125" t="str">
-        <v>2:59</v>
+        <v>4:05</v>
       </c>
       <c r="H125" t="str">
-        <v>Jelly Roll</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/im-good-from-the-movie-goat/1870623290</v>
+        <v>https://music.apple.com/us/album/dead-end/1862845733</v>
       </c>
       <c r="L125" t="str">
-        <v>I’m Good (From The Movie “GOAT”) - Jelly Roll</v>
+        <v>Dead End - Snail Mail</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
+        <v>Do I Wanna Know?</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
+        <v>https://music.apple.com/us/song/do-i-wanna-know/1870931500</v>
       </c>
       <c r="D126" t="str">
         <v>2026-01-23</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
+        <v>Do I Wanna Know? - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>3:47</v>
+        <v>3:52</v>
       </c>
       <c r="H126" t="str">
-        <v>Dolly Parton</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
+        <v>https://music.apple.com/us/artist/dove-cameron/599822740</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
+        <v>https://music.apple.com/us/album/do-i-wanna-know/1870931327</v>
       </c>
       <c r="L126" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
+        <v>Do I Wanna Know? - Dove Cameron</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>ESCONDIDAS</v>
+        <v>Una y Otra Vez</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/escondidas/1860972187</v>
+        <v>https://music.apple.com/us/song/una-y-otra-vez/1868792926</v>
       </c>
       <c r="D127" t="str">
         <v>2026-01-23</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>SILENCIO HABLA</v>
+        <v>K de Karma (Apple Music Edition)</v>
       </c>
       <c r="G127" t="str">
-        <v>2:53</v>
+        <v>3:02</v>
       </c>
       <c r="H127" t="str">
-        <v>Oscar Ortiz</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/oscar-ortiz/1680604969</v>
+        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/escondidas/1860972173</v>
+        <v>https://music.apple.com/us/album/una-y-otra-vez/1868792704</v>
       </c>
       <c r="L127" t="str">
-        <v>ESCONDIDAS - Oscar Ortiz</v>
+        <v>Una y Otra Vez - Kenia Os</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Alabama Beauty Queen</v>
+        <v>BAD</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/alabama-beauty-queen/1846658485</v>
+        <v>https://music.apple.com/us/song/bad/1869095326</v>
       </c>
       <c r="D128" t="str">
         <v>2026-01-23</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Act I</v>
+        <v>BAD - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>3:43</v>
+        <v>2:15</v>
       </c>
       <c r="H128" t="str">
-        <v>Kashus Culpepper</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/kashus-culpepper/1634883369</v>
+        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/alabama-beauty-queen/1846658477</v>
+        <v>https://music.apple.com/us/album/bad/1869095325</v>
       </c>
       <c r="L128" t="str">
-        <v>Alabama Beauty Queen - Kashus Culpepper</v>
+        <v>BAD - Chelsea Cutler</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Imposter</v>
+        <v>Losing You</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/imposter/1842408050</v>
+        <v>https://music.apple.com/us/song/losing-you/1863525495</v>
       </c>
       <c r="D129" t="str">
         <v>2026-01-23</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>How Did I Get Here?</v>
+        <v>F.I.G</v>
       </c>
       <c r="G129" t="str">
-        <v>2:38</v>
+        <v>2:22</v>
       </c>
       <c r="H129" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Naomi Scott</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
+        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/imposter/1842408037</v>
+        <v>https://music.apple.com/us/album/losing-you/1863525485</v>
       </c>
       <c r="L129" t="str">
-        <v>Imposter - Louis Tomlinson</v>
+        <v>Losing You - Naomi Scott</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Puddles (Zero 7 Remix)</v>
+        <v>Me Voy A La C******a</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/puddles-zero-7-remix/1869474314</v>
+        <v>https://music.apple.com/us/song/me-voy-a-la-c-a/1867850749</v>
       </c>
       <c r="D130" t="str">
         <v>2026-01-23</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Puddles (Zero 7 Remix) - Single</v>
+        <v>Infinito</v>
       </c>
       <c r="G130" t="str">
-        <v>6:01</v>
+        <v>2:14</v>
       </c>
       <c r="H130" t="str">
-        <v>Not for Radio</v>
+        <v>Yandel</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
+        <v>https://music.apple.com/us/artist/yandel/72929426</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/puddles-zero-7-remix/1869474313</v>
+        <v>https://music.apple.com/us/album/me-voy-a-la-c-a/1867850739</v>
       </c>
       <c r="L130" t="str">
-        <v>Puddles (Zero 7 Remix) - Not for Radio</v>
+        <v>Me Voy A La C******a - Yandel</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Little Miss (Misdemeanor)</v>
+        <v>Sexy For Me</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/little-miss-misdemeanor/1870996491</v>
+        <v>https://music.apple.com/us/song/sexy-for-me/1867897421</v>
       </c>
       <c r="D131" t="str">
         <v>2026-01-23</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Little Miss (Misdemeanor) - Single</v>
+        <v>The Last Dance (Part 1)</v>
       </c>
       <c r="G131" t="str">
-        <v>2:24</v>
+        <v>2:08</v>
       </c>
       <c r="H131" t="str">
-        <v>GIRLSET</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
+        <v>https://music.apple.com/us/artist/jason-derulo/259118085</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/little-miss-misdemeanor/1870996490</v>
+        <v>https://music.apple.com/us/album/sexy-for-me/1867897420</v>
       </c>
       <c r="L131" t="str">
-        <v>Little Miss (Misdemeanor) - GIRLSET</v>
+        <v>Sexy For Me - Jason Derulo</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>I Could Get Used To This</v>
+        <v>Turbulence</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/i-could-get-used-to-this/1867222996</v>
+        <v>https://music.apple.com/us/song/turbulence/1867908449</v>
       </c>
       <c r="D132" t="str">
         <v>2026-01-23</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>I Could Get Used To This - Single</v>
+        <v>REAL, Vol. 1 - EP</v>
       </c>
       <c r="G132" t="str">
-        <v>3:41</v>
+        <v>2:25</v>
       </c>
       <c r="H132" t="str">
-        <v>Jessie Ware</v>
+        <v>Wizkid</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/i-could-get-used-to-this/1867222992</v>
+        <v>https://music.apple.com/us/album/turbulence/1867908237</v>
       </c>
       <c r="L132" t="str">
-        <v>I Could Get Used To This - Jessie Ware</v>
+        <v>Turbulence - Wizkid</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>LA VILLA</v>
+        <v>I’m Good (From The Movie “GOAT”)</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/la-villa/1847678152</v>
+        <v>https://music.apple.com/us/song/im-good-from-the-movie-goat/1870623298</v>
       </c>
       <c r="D133" t="str">
         <v>2026-01-23</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>HOPI SENDÉ</v>
+        <v>GOAT (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G133" t="str">
-        <v>3:12</v>
+        <v>2:59</v>
       </c>
       <c r="H133" t="str">
-        <v>Ryan Castro</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/ryan-castro/1263552447</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/la-villa/1847678143</v>
+        <v>https://music.apple.com/us/album/im-good-from-the-movie-goat/1870623290</v>
       </c>
       <c r="L133" t="str">
-        <v>LA VILLA - Ryan Castro</v>
+        <v>I’m Good (From The Movie “GOAT”) - Jelly Roll</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700)</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/lit-effect-feat-bktherula-lazer-dim-700/1868519613</v>
+        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
       </c>
       <c r="D134" t="str">
         <v>2026-01-23</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Strictly 4 The Scythe</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>3:27</v>
+        <v>3:47</v>
       </c>
       <c r="H134" t="str">
-        <v>Denzel Curry</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
+        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/lit-effect-feat-bktherula-lazer-dim-700/1868519270</v>
+        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
       </c>
       <c r="L134" t="str">
-        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700) - Denzel Curry</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Thick One</v>
+        <v>ESCONDIDAS</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/thick-one/1868515478</v>
+        <v>https://music.apple.com/us/song/escondidas/1860972187</v>
       </c>
       <c r="D135" t="str">
         <v>2026-01-23</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Part 3</v>
+        <v>SILENCIO HABLA</v>
       </c>
       <c r="G135" t="str">
-        <v>2:49</v>
+        <v>2:53</v>
       </c>
       <c r="H135" t="str">
-        <v>42 Dugg</v>
+        <v>Oscar Ortiz</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
+        <v>https://music.apple.com/us/artist/oscar-ortiz/1680604969</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/thick-one/1868515223</v>
+        <v>https://music.apple.com/us/album/escondidas/1860972173</v>
       </c>
       <c r="L135" t="str">
-        <v>Thick One - 42 Dugg</v>
+        <v>ESCONDIDAS - Oscar Ortiz</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>How Much Did You Get For Your Soul</v>
+        <v>Alabama Beauty Queen</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/how-much-did-you-get-for-your-soul/1843195678</v>
+        <v>https://music.apple.com/us/song/alabama-beauty-queen/1846658485</v>
       </c>
       <c r="D136" t="str">
         <v>2026-01-23</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>World's Gone Wrong</v>
+        <v>Act I</v>
       </c>
       <c r="G136" t="str">
-        <v>3:59</v>
+        <v>3:43</v>
       </c>
       <c r="H136" t="str">
-        <v>Lucinda Williams</v>
+        <v>Kashus Culpepper</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/lucinda-williams/267658</v>
+        <v>https://music.apple.com/us/artist/kashus-culpepper/1634883369</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/how-much-did-you-get-for-your-soul/1843195660</v>
+        <v>https://music.apple.com/us/album/alabama-beauty-queen/1846658477</v>
       </c>
       <c r="L136" t="str">
-        <v>How Much Did You Get For Your Soul - Lucinda Williams</v>
+        <v>Alabama Beauty Queen - Kashus Culpepper</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>THUM</v>
+        <v>Imposter</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/thum/1863009362</v>
+        <v>https://music.apple.com/us/song/imposter/1842408050</v>
       </c>
       <c r="D137" t="str">
         <v>2026-01-23</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>THUM - Single</v>
+        <v>How Did I Get Here?</v>
       </c>
       <c r="G137" t="str">
-        <v>2:11</v>
+        <v>2:38</v>
       </c>
       <c r="H137" t="str">
-        <v>Violet Grohl</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/thum/1863009357</v>
+        <v>https://music.apple.com/us/album/imposter/1842408037</v>
       </c>
       <c r="L137" t="str">
-        <v>THUM - Violet Grohl</v>
+        <v>Imposter - Louis Tomlinson</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>(I'm a) Rock "N" Roller</v>
+        <v>Puddles (Zero 7 Remix)</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/im-a-rock-n-roller/1839888014</v>
+        <v>https://music.apple.com/us/song/puddles-zero-7-remix/1869474314</v>
       </c>
       <c r="D138" t="str">
         <v>2026-01-23</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>The Great Satan</v>
+        <v>Puddles (Zero 7 Remix) - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>3:32</v>
+        <v>6:01</v>
       </c>
       <c r="H138" t="str">
-        <v>Rob Zombie</v>
+        <v>Not for Radio</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
+        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/im-a-rock-n-roller/1839887790</v>
+        <v>https://music.apple.com/us/album/puddles-zero-7-remix/1869474313</v>
       </c>
       <c r="L138" t="str">
-        <v>(I'm a) Rock "N" Roller - Rob Zombie</v>
+        <v>Puddles (Zero 7 Remix) - Not for Radio</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Excuses For Love</v>
+        <v>Little Miss (Misdemeanor)</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/excuses-for-love/1856034295</v>
+        <v>https://music.apple.com/us/song/little-miss-misdemeanor/1870996491</v>
       </c>
       <c r="D139" t="str">
         <v>2026-01-23</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Hyperlove</v>
+        <v>Little Miss (Misdemeanor) - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:04</v>
+        <v>2:24</v>
       </c>
       <c r="H139" t="str">
-        <v>MIKA</v>
+        <v>GIRLSET</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/mika/184932871</v>
+        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/excuses-for-love/1856033810</v>
+        <v>https://music.apple.com/us/album/little-miss-misdemeanor/1870996490</v>
       </c>
       <c r="L139" t="str">
-        <v>Excuses For Love - MIKA</v>
+        <v>Little Miss (Misdemeanor) - GIRLSET</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>3 Tears</v>
+        <v>I Could Get Used To This</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/3-tears/1861504548</v>
+        <v>https://music.apple.com/us/song/i-could-get-used-to-this/1867222996</v>
       </c>
       <c r="D140" t="str">
         <v>2026-01-23</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>3 Tears - Single</v>
+        <v>I Could Get Used To This - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>2:50</v>
+        <v>3:41</v>
       </c>
       <c r="H140" t="str">
-        <v>Mergui</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/mergui/1423596903</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/3-tears/1861504545</v>
+        <v>https://music.apple.com/us/album/i-could-get-used-to-this/1867222992</v>
       </c>
       <c r="L140" t="str">
-        <v>3 Tears - Mergui</v>
+        <v>I Could Get Used To This - Jessie Ware</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Church Girl</v>
+        <v>LA VILLA</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/church-girl/1862008542</v>
+        <v>https://music.apple.com/us/song/la-villa/1847678152</v>
       </c>
       <c r="D141" t="str">
         <v>2026-01-23</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Church Girl - Single</v>
+        <v>HOPI SENDÉ</v>
       </c>
       <c r="G141" t="str">
-        <v>3:19</v>
+        <v>3:12</v>
       </c>
       <c r="H141" t="str">
-        <v>Carly Pearce</v>
+        <v>Ryan Castro</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/ryan-castro/1263552447</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/church-girl/1862008535</v>
+        <v>https://music.apple.com/us/album/la-villa/1847678143</v>
       </c>
       <c r="L141" t="str">
-        <v>Church Girl - Carly Pearce</v>
+        <v>LA VILLA - Ryan Castro</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Funeral</v>
+        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700)</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/funeral/1867616928</v>
+        <v>https://music.apple.com/us/song/lit-effect-feat-bktherula-lazer-dim-700/1868519613</v>
       </c>
       <c r="D142" t="str">
         <v>2026-01-23</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>The Weight of the Woods</v>
+        <v>Strictly 4 The Scythe</v>
       </c>
       <c r="G142" t="str">
-        <v>4:03</v>
+        <v>3:27</v>
       </c>
       <c r="H142" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Denzel Curry</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/funeral/1867616617</v>
+        <v>https://music.apple.com/us/album/lit-effect-feat-bktherula-lazer-dim-700/1868519270</v>
       </c>
       <c r="L142" t="str">
-        <v>Funeral - Dermot Kennedy</v>
+        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700) - Denzel Curry</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Say Yes</v>
+        <v>Thick One</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/say-yes/1861995090</v>
+        <v>https://music.apple.com/us/song/thick-one/1868515478</v>
       </c>
       <c r="D143" t="str">
         <v>2026-01-23</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Say Yes - Single</v>
+        <v>Part 3</v>
       </c>
       <c r="G143" t="str">
-        <v>2:50</v>
+        <v>2:49</v>
       </c>
       <c r="H143" t="str">
-        <v>Marques Anthony</v>
+        <v>42 Dugg</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/marques-anthony/321321231</v>
+        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/say-yes/1861995089</v>
+        <v>https://music.apple.com/us/album/thick-one/1868515223</v>
       </c>
       <c r="L143" t="str">
-        <v>Say Yes - Marques Anthony</v>
+        <v>Thick One - 42 Dugg</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>LOVE ME (feat. Stevie Wonder)</v>
+        <v>How Much Did You Get For Your Soul</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/love-me-feat-stevie-wonder/1867640879</v>
+        <v>https://music.apple.com/us/song/how-much-did-you-get-for-your-soul/1843195678</v>
       </c>
       <c r="D144" t="str">
         <v>2026-01-23</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>CAMPILATION</v>
+        <v>World's Gone Wrong</v>
       </c>
       <c r="G144" t="str">
-        <v>3:10</v>
+        <v>3:59</v>
       </c>
       <c r="H144" t="str">
-        <v>Camper</v>
+        <v>Lucinda Williams</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/camper/1514886616</v>
+        <v>https://music.apple.com/us/artist/lucinda-williams/267658</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/love-me-feat-stevie-wonder/1867640873</v>
+        <v>https://music.apple.com/us/album/how-much-did-you-get-for-your-soul/1843195660</v>
       </c>
       <c r="L144" t="str">
-        <v>LOVE ME (feat. Stevie Wonder) - Camper</v>
+        <v>How Much Did You Get For Your Soul - Lucinda Williams</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>UP TO MY NECK IN U</v>
+        <v>THUM</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
+        <v>https://music.apple.com/us/song/thum/1863009362</v>
       </c>
       <c r="D145" t="str">
         <v>2026-01-23</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>UP TO MY NECK IN U - Single</v>
+        <v>THUM - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>2:17</v>
+        <v>2:11</v>
       </c>
       <c r="H145" t="str">
-        <v>Ledbyher</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/up-to-my-neck-in-u/1862550671</v>
+        <v>https://music.apple.com/us/album/thum/1863009357</v>
       </c>
       <c r="L145" t="str">
-        <v>UP TO MY NECK IN U - Ledbyher</v>
+        <v>THUM - Violet Grohl</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Wallflower</v>
+        <v>(I'm a) Rock "N" Roller</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/wallflower/1862737077</v>
+        <v>https://music.apple.com/us/song/im-a-rock-n-roller/1839888014</v>
       </c>
       <c r="D146" t="str">
         <v>2026-01-23</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Wallflower - Single</v>
+        <v>The Great Satan</v>
       </c>
       <c r="G146" t="str">
-        <v>3:25</v>
+        <v>3:32</v>
       </c>
       <c r="H146" t="str">
-        <v>Sikarus</v>
+        <v>Rob Zombie</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/sikarus/1046558781</v>
+        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/wallflower/1862737074</v>
+        <v>https://music.apple.com/us/album/im-a-rock-n-roller/1839887790</v>
       </c>
       <c r="L146" t="str">
-        <v>Wallflower - Sikarus</v>
+        <v>(I'm a) Rock "N" Roller - Rob Zombie</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>You Phase</v>
+        <v>Excuses For Love</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/you-phase/1868861897</v>
+        <v>https://music.apple.com/us/song/excuses-for-love/1856034295</v>
       </c>
       <c r="D147" t="str">
         <v>2026-01-23</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>You Phase - Single</v>
+        <v>Hyperlove</v>
       </c>
       <c r="G147" t="str">
-        <v>2:51</v>
+        <v>3:04</v>
       </c>
       <c r="H147" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>MIKA</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/mitchell-tenpenny/430369368</v>
+        <v>https://music.apple.com/us/artist/mika/184932871</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/you-phase/1868861895</v>
+        <v>https://music.apple.com/us/album/excuses-for-love/1856033810</v>
       </c>
       <c r="L147" t="str">
-        <v>You Phase - Mitchell Tenpenny</v>
+        <v>Excuses For Love - MIKA</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Miss Independent</v>
+        <v>3 Tears</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
+        <v>https://music.apple.com/us/song/3-tears/1861504548</v>
       </c>
       <c r="D148" t="str">
         <v>2026-01-23</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Miss Independent - Single</v>
+        <v>3 Tears - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>2:40</v>
+        <v>2:50</v>
       </c>
       <c r="H148" t="str">
-        <v>1Ski OG</v>
+        <v>Mergui</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/mergui/1423596903</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/miss-independent/1870612555</v>
+        <v>https://music.apple.com/us/album/3-tears/1861504545</v>
       </c>
       <c r="L148" t="str">
-        <v>Miss Independent - 1Ski OG</v>
+        <v>3 Tears - Mergui</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown)</v>
+        <v>Church Girl</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown/1870678482</v>
+        <v>https://music.apple.com/us/song/church-girl/1862008542</v>
       </c>
       <c r="D149" t="str">
         <v>2026-01-23</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>SO BE IT</v>
+        <v>Church Girl - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>5:47</v>
+        <v>3:19</v>
       </c>
       <c r="H149" t="str">
-        <v>Elevation Worship</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown/1870678481</v>
+        <v>https://music.apple.com/us/album/church-girl/1862008535</v>
       </c>
       <c r="L149" t="str">
-        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) - Elevation Worship</v>
+        <v>Church Girl - Carly Pearce</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>go again</v>
+        <v>Funeral</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/go-again/1868987466</v>
+        <v>https://music.apple.com/us/song/funeral/1867616928</v>
       </c>
       <c r="D150" t="str">
         <v>2026-01-23</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>go again - Single</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G150" t="str">
-        <v>2:07</v>
+        <v>4:03</v>
       </c>
       <c r="H150" t="str">
-        <v>NateTaylorr</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/natetaylorr/1243682934</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/go-again/1868987193</v>
+        <v>https://music.apple.com/us/album/funeral/1867616617</v>
       </c>
       <c r="L150" t="str">
-        <v>go again - NateTaylorr</v>
+        <v>Funeral - Dermot Kennedy</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Autopilot</v>
+        <v>Say Yes</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/autopilot/1863072399</v>
+        <v>https://music.apple.com/us/song/say-yes/1861995090</v>
       </c>
       <c r="D151" t="str">
         <v>2026-01-23</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Autopilot</v>
+        <v>Say Yes - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>2:46</v>
+        <v>2:50</v>
       </c>
       <c r="H151" t="str">
-        <v>ALEXSUCKS</v>
+        <v>Marques Anthony</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
+        <v>https://music.apple.com/us/artist/marques-anthony/321321231</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/autopilot/1863072393</v>
+        <v>https://music.apple.com/us/album/say-yes/1861995089</v>
       </c>
       <c r="L151" t="str">
-        <v>Autopilot - ALEXSUCKS</v>
+        <v>Say Yes - Marques Anthony</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Portrait of My Heart (feat. Brendan Yates)</v>
+        <v>LOVE ME (feat. Stevie Wonder)</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
+        <v>https://music.apple.com/us/song/love-me-feat-stevie-wonder/1867640879</v>
       </c>
       <c r="D152" t="str">
         <v>2026-01-23</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Portrait of My Heart - Single</v>
+        <v>CAMPILATION</v>
       </c>
       <c r="G152" t="str">
-        <v>3:04</v>
+        <v>3:10</v>
       </c>
       <c r="H152" t="str">
-        <v>SPELLLING</v>
+        <v>Camper</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/spellling/1281213673</v>
+        <v>https://music.apple.com/us/artist/camper/1514886616</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/portrait-of-my-heart-feat-brendan-yates/1862282167</v>
+        <v>https://music.apple.com/us/album/love-me-feat-stevie-wonder/1867640873</v>
       </c>
       <c r="L152" t="str">
-        <v>Portrait of My Heart (feat. Brendan Yates) - SPELLLING</v>
+        <v>LOVE ME (feat. Stevie Wonder) - Camper</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>In Violet</v>
+        <v>UP TO MY NECK IN U</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/in-violet/1839471290</v>
+        <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
       </c>
       <c r="D153" t="str">
         <v>2026-01-23</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Death in the Business of Whaling</v>
+        <v>UP TO MY NECK IN U - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>4:09</v>
+        <v>2:17</v>
       </c>
       <c r="H153" t="str">
-        <v>Searows</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/searows/1607240507</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/in-violet/1839470844</v>
+        <v>https://music.apple.com/us/album/up-to-my-neck-in-u/1862550671</v>
       </c>
       <c r="L153" t="str">
-        <v>In Violet - Searows</v>
+        <v>UP TO MY NECK IN U - Ledbyher</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Baby Run</v>
+        <v>Wallflower</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/baby-run/1857658819</v>
+        <v>https://music.apple.com/us/song/wallflower/1862737077</v>
       </c>
       <c r="D154" t="str">
         <v>2026-01-23</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Baby Run - Single</v>
+        <v>Wallflower - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>4:47</v>
+        <v>3:25</v>
       </c>
       <c r="H154" t="str">
-        <v>Jimi Jules</v>
+        <v>Sikarus</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/jimi-jules/586933009</v>
+        <v>https://music.apple.com/us/artist/sikarus/1046558781</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/baby-run/1857658816</v>
+        <v>https://music.apple.com/us/album/wallflower/1862737074</v>
       </c>
       <c r="L154" t="str">
-        <v>Baby Run - Jimi Jules</v>
+        <v>Wallflower - Sikarus</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>What If We Don't</v>
+        <v>You Phase</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
+        <v>https://music.apple.com/us/song/you-phase/1868861897</v>
       </c>
       <c r="D155" t="str">
         <v>2026-01-23</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>What If We Don't - Single</v>
+        <v>You Phase - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:06</v>
+        <v>2:51</v>
       </c>
       <c r="H155" t="str">
-        <v>Ashley McBryde</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/mitchell-tenpenny/430369368</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/what-if-we-dont/1862668776</v>
+        <v>https://music.apple.com/us/album/you-phase/1868861895</v>
       </c>
       <c r="L155" t="str">
-        <v>What If We Don't - Ashley McBryde</v>
+        <v>You Phase - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Hagamos Que</v>
+        <v>Miss Independent</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
+        <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
       </c>
       <c r="D156" t="str">
         <v>2026-01-23</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Hagamos Que - Single</v>
+        <v>Miss Independent - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>2:58</v>
+        <v>2:40</v>
       </c>
       <c r="H156" t="str">
-        <v>Juanes</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/juanes/103856</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/hagamos-que/1861956611</v>
+        <v>https://music.apple.com/us/album/miss-independent/1870612555</v>
       </c>
       <c r="L156" t="str">
-        <v>Hagamos Que - Juanes</v>
+        <v>Miss Independent - 1Ski OG</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>World Change Me</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown)</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
+        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown/1870678482</v>
       </c>
       <c r="D157" t="str">
         <v>2026-01-23</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>World Change Me - Single</v>
+        <v>SO BE IT</v>
       </c>
       <c r="G157" t="str">
-        <v>3:03</v>
+        <v>5:47</v>
       </c>
       <c r="H157" t="str">
-        <v>Max McNown</v>
+        <v>Elevation Worship</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/world-change-me/1860974598</v>
+        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown/1870678481</v>
       </c>
       <c r="L157" t="str">
-        <v>World Change Me - Max McNown</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) - Elevation Worship</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Exclusive</v>
+        <v>go again</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/exclusive/1851537672</v>
+        <v>https://music.apple.com/us/song/go-again/1868987466</v>
       </c>
       <c r="D158" t="str">
         <v>2026-01-23</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Exclusive - EP</v>
+        <v>go again - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:20</v>
+        <v>2:07</v>
       </c>
       <c r="H158" t="str">
-        <v>Hudson Westbrook</v>
+        <v>NateTaylorr</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
+        <v>https://music.apple.com/us/artist/natetaylorr/1243682934</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/exclusive/1851537671</v>
+        <v>https://music.apple.com/us/album/go-again/1868987193</v>
       </c>
       <c r="L158" t="str">
-        <v>Exclusive - Hudson Westbrook</v>
+        <v>go again - NateTaylorr</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Say Less</v>
+        <v>Autopilot</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/say-less/1867910122</v>
+        <v>https://music.apple.com/us/song/autopilot/1863072399</v>
       </c>
       <c r="D159" t="str">
         <v>2026-01-23</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Say Less - Single</v>
+        <v>Autopilot</v>
       </c>
       <c r="G159" t="str">
-        <v>2:18</v>
+        <v>2:46</v>
       </c>
       <c r="H159" t="str">
-        <v>JYT</v>
+        <v>ALEXSUCKS</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
+        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/say-less/1867910115</v>
+        <v>https://music.apple.com/us/album/autopilot/1863072393</v>
       </c>
       <c r="L159" t="str">
-        <v>Say Less - JYT</v>
+        <v>Autopilot - ALEXSUCKS</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Angels Cry</v>
+        <v>Portrait of My Heart (feat. Brendan Yates)</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
+        <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
       </c>
       <c r="D160" t="str">
         <v>2026-01-23</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>X's for Eyes (Deluxe)</v>
+        <v>Portrait of My Heart - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:52</v>
+        <v>3:04</v>
       </c>
       <c r="H160" t="str">
-        <v>The Red Jumpsuit Apparatus</v>
+        <v>SPELLLING</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/the-red-jumpsuit-apparatus/130037074</v>
+        <v>https://music.apple.com/us/artist/spellling/1281213673</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/angels-cry/1862320872</v>
+        <v>https://music.apple.com/us/album/portrait-of-my-heart-feat-brendan-yates/1862282167</v>
       </c>
       <c r="L160" t="str">
-        <v>Angels Cry - The Red Jumpsuit Apparatus</v>
+        <v>Portrait of My Heart (feat. Brendan Yates) - SPELLLING</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Over You</v>
+        <v>In Violet</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/over-you/1846189473</v>
+        <v>https://music.apple.com/us/song/in-violet/1839471290</v>
       </c>
       <c r="D161" t="str">
         <v>2026-01-23</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>A Love For Strangers</v>
+        <v>Death in the Business of Whaling</v>
       </c>
       <c r="G161" t="str">
-        <v>4:44</v>
+        <v>4:09</v>
       </c>
       <c r="H161" t="str">
-        <v>Chet Faker</v>
+        <v>Searows</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
+        <v>https://music.apple.com/us/artist/searows/1607240507</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/over-you/1846189472</v>
+        <v>https://music.apple.com/us/album/in-violet/1839470844</v>
       </c>
       <c r="L161" t="str">
-        <v>Over You - Chet Faker</v>
+        <v>In Violet - Searows</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Chala (My Soul Is on a Loop)</v>
+        <v>Baby Run</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
+        <v>https://music.apple.com/us/song/baby-run/1857658819</v>
       </c>
       <c r="D162" t="str">
         <v>2026-01-23</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Chala (My Soul Is on a Loop) - Single</v>
+        <v>Baby Run - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>2:42</v>
+        <v>4:47</v>
       </c>
       <c r="H162" t="str">
-        <v>Barry Can't Swim</v>
+        <v>Jimi Jules</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/barry-cant-swim/1492752064</v>
+        <v>https://music.apple.com/us/artist/jimi-jules/586933009</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/chala-my-soul-is-on-a-loop/1857789040</v>
+        <v>https://music.apple.com/us/album/baby-run/1857658816</v>
       </c>
       <c r="L162" t="str">
-        <v>Chala (My Soul Is on a Loop) - Barry Can't Swim</v>
+        <v>Baby Run - Jimi Jules</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>starlight feat. Madeline Follin</v>
+        <v>What If We Don't</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
+        <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
       </c>
       <c r="D163" t="str">
         <v>2026-01-23</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>starlight feat. Madeline Follin - Single</v>
+        <v>What If We Don't - Single</v>
       </c>
       <c r="G163" t="str">
         <v>3:06</v>
       </c>
       <c r="H163" t="str">
-        <v>Disco Lines</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/disco-lines/1462793893</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/starlight-feat-madeline-follin/1869330767</v>
+        <v>https://music.apple.com/us/album/what-if-we-dont/1862668776</v>
       </c>
       <c r="L163" t="str">
-        <v>starlight feat. Madeline Follin - Disco Lines</v>
+        <v>What If We Don't - Ashley McBryde</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Locked In (feat. Trippie Redd)</v>
+        <v>Hagamos Que</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
+        <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
       </c>
       <c r="D164" t="str">
         <v>2026-01-23</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Locked In (feat. Trippie Redd) - Single</v>
+        <v>Hagamos Que - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>2:48</v>
+        <v>2:58</v>
       </c>
       <c r="H164" t="str">
-        <v>David Guetta</v>
+        <v>Juanes</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/david-guetta/5557599</v>
+        <v>https://music.apple.com/us/artist/juanes/103856</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/locked-in-feat-trippie-redd/1869439982</v>
+        <v>https://music.apple.com/us/album/hagamos-que/1861956611</v>
       </c>
       <c r="L164" t="str">
-        <v>Locked In (feat. Trippie Redd) - David Guetta</v>
+        <v>Hagamos Que - Juanes</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Rejoice</v>
+        <v>World Change Me</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/rejoice/1862633596</v>
+        <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
       </c>
       <c r="D165" t="str">
         <v>2026-01-23</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Rejoice - Single</v>
+        <v>World Change Me - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>4:20</v>
+        <v>3:03</v>
       </c>
       <c r="H165" t="str">
-        <v>Def Leppard</v>
+        <v>Max McNown</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/def-leppard/117554</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/rejoice/1862633593</v>
+        <v>https://music.apple.com/us/album/world-change-me/1860974598</v>
       </c>
       <c r="L165" t="str">
-        <v>Rejoice - Def Leppard</v>
+        <v>World Change Me - Max McNown</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Slight Werk (feat. Bree Runway) [Club Mix]</v>
+        <v>Exclusive</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
+        <v>https://music.apple.com/us/song/exclusive/1851537672</v>
       </c>
       <c r="D166" t="str">
         <v>2026-01-23</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Slight Werk (Club Mix) [feat. Bree Runway] - Single</v>
+        <v>Exclusive - EP</v>
       </c>
       <c r="G166" t="str">
-        <v>2:58</v>
+        <v>3:20</v>
       </c>
       <c r="H166" t="str">
-        <v>Honey Dijon</v>
+        <v>Hudson Westbrook</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
+        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/slight-werk-feat-bree-runway-club-mix/1860859551</v>
+        <v>https://music.apple.com/us/album/exclusive/1851537671</v>
       </c>
       <c r="L166" t="str">
-        <v>Slight Werk (feat. Bree Runway) [Club Mix] - Honey Dijon</v>
+        <v>Exclusive - Hudson Westbrook</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Lucky Day</v>
+        <v>Say Less</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
+        <v>https://music.apple.com/us/song/say-less/1867910122</v>
       </c>
       <c r="D167" t="str">
         <v>2026-01-23</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Speed Kills</v>
+        <v>Say Less - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:13</v>
+        <v>2:18</v>
       </c>
       <c r="H167" t="str">
-        <v>Ally Evenson</v>
+        <v>JYT</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/ally-evenson/283908113</v>
+        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/lucky-day/1849264498</v>
+        <v>https://music.apple.com/us/album/say-less/1867910115</v>
       </c>
       <c r="L167" t="str">
-        <v>Lucky Day - Ally Evenson</v>
+        <v>Say Less - JYT</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Breathe On It</v>
+        <v>Angels Cry</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
+        <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
       </c>
       <c r="D168" t="str">
         <v>2026-01-23</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Breathe On It - Single</v>
+        <v>X's for Eyes (Deluxe)</v>
       </c>
       <c r="G168" t="str">
-        <v>4:00</v>
+        <v>3:52</v>
       </c>
       <c r="H168" t="str">
-        <v>Tauren Wells</v>
+        <v>The Red Jumpsuit Apparatus</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
+        <v>https://music.apple.com/us/artist/the-red-jumpsuit-apparatus/130037074</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/breathe-on-it/1862938798</v>
+        <v>https://music.apple.com/us/album/angels-cry/1862320872</v>
       </c>
       <c r="L168" t="str">
-        <v>Breathe On It - Tauren Wells</v>
+        <v>Angels Cry - The Red Jumpsuit Apparatus</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Easy</v>
+        <v>Over You</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/easy/1863456906</v>
+        <v>https://music.apple.com/us/song/over-you/1846189473</v>
       </c>
       <c r="D169" t="str">
         <v>2026-01-23</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Easy - Single</v>
+        <v>A Love For Strangers</v>
       </c>
       <c r="G169" t="str">
-        <v>4:30</v>
+        <v>4:44</v>
       </c>
       <c r="H169" t="str">
-        <v>lydi lynn</v>
+        <v>Chet Faker</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
+        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/easy/1863456903</v>
+        <v>https://music.apple.com/us/album/over-you/1846189472</v>
       </c>
       <c r="L169" t="str">
-        <v>Easy - lydi lynn</v>
+        <v>Over You - Chet Faker</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Break Me In</v>
+        <v>Chala (My Soul Is on a Loop)</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
+        <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
       </c>
       <c r="D170" t="str">
         <v>2026-01-23</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Break Me In - Single</v>
+        <v>Chala (My Soul Is on a Loop) - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:52</v>
+        <v>2:42</v>
       </c>
       <c r="H170" t="str">
-        <v>Joyce Wrice</v>
+        <v>Barry Can't Swim</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/joyce-wrice/591991458</v>
+        <v>https://music.apple.com/us/artist/barry-cant-swim/1492752064</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/break-me-in/1862881766</v>
+        <v>https://music.apple.com/us/album/chala-my-soul-is-on-a-loop/1857789040</v>
       </c>
       <c r="L170" t="str">
-        <v>Break Me In - Joyce Wrice</v>
+        <v>Chala (My Soul Is on a Loop) - Barry Can't Swim</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Long Live Love</v>
+        <v>starlight feat. Madeline Follin</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
+        <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
       </c>
       <c r="D171" t="str">
         <v>2026-01-23</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Long Live Love - Single</v>
+        <v>starlight feat. Madeline Follin - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:36</v>
+        <v>3:06</v>
       </c>
       <c r="H171" t="str">
-        <v>Sugar</v>
+        <v>Disco Lines</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/sugar/530175867</v>
+        <v>https://music.apple.com/us/artist/disco-lines/1462793893</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/long-live-love/1851251226</v>
+        <v>https://music.apple.com/us/album/starlight-feat-madeline-follin/1869330767</v>
       </c>
       <c r="L171" t="str">
-        <v>Long Live Love - Sugar</v>
+        <v>starlight feat. Madeline Follin - Disco Lines</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Depressed</v>
+        <v>Locked In (feat. Trippie Redd)</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/depressed/1840400522</v>
+        <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
       </c>
       <c r="D172" t="str">
         <v>2026-01-23</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Boycott Heaven</v>
+        <v>Locked In (feat. Trippie Redd) - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:32</v>
+        <v>2:48</v>
       </c>
       <c r="H172" t="str">
-        <v>The Format</v>
+        <v>David Guetta</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/the-format/3064903</v>
+        <v>https://music.apple.com/us/artist/david-guetta/5557599</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/depressed/1840399886</v>
+        <v>https://music.apple.com/us/album/locked-in-feat-trippie-redd/1869439982</v>
       </c>
       <c r="L172" t="str">
-        <v>Depressed - The Format</v>
+        <v>Locked In (feat. Trippie Redd) - David Guetta</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Empty Hands</v>
+        <v>Rejoice</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
+        <v>https://music.apple.com/us/song/rejoice/1862633596</v>
       </c>
       <c r="D173" t="str">
         <v>2026-01-23</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Empty Hands</v>
+        <v>Rejoice - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:09</v>
+        <v>4:20</v>
       </c>
       <c r="H173" t="str">
-        <v>Poppy</v>
+        <v>Def Leppard</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/poppy/1004130511</v>
+        <v>https://music.apple.com/us/artist/def-leppard/117554</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/empty-hands/1852046141</v>
+        <v>https://music.apple.com/us/album/rejoice/1862633593</v>
       </c>
       <c r="L173" t="str">
-        <v>Empty Hands - Poppy</v>
+        <v>Rejoice - Def Leppard</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>The Long Surrender</v>
+        <v>Slight Werk (feat. Bree Runway) [Club Mix]</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
+        <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
       </c>
       <c r="D174" t="str">
         <v>2026-01-23</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>The Long Surrender</v>
+        <v>Slight Werk (Club Mix) [feat. Bree Runway] - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:45</v>
+        <v>2:58</v>
       </c>
       <c r="H174" t="str">
-        <v>NEEDTOBREATHE</v>
+        <v>Honey Dijon</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/needtobreathe/113247214</v>
+        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/the-long-surrender/1861935699</v>
+        <v>https://music.apple.com/us/album/slight-werk-feat-bree-runway-club-mix/1860859551</v>
       </c>
       <c r="L174" t="str">
-        <v>The Long Surrender - NEEDTOBREATHE</v>
+        <v>Slight Werk (feat. Bree Runway) [Club Mix] - Honey Dijon</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Angela</v>
+        <v>Lucky Day</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/angela/1866624257</v>
+        <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
       </c>
       <c r="D175" t="str">
         <v>2026-01-23</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Angela - Single</v>
+        <v>Speed Kills</v>
       </c>
       <c r="G175" t="str">
-        <v>3:32</v>
+        <v>3:13</v>
       </c>
       <c r="H175" t="str">
-        <v>Hayden Everett</v>
+        <v>Ally Evenson</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/ally-evenson/283908113</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/angela/1866624256</v>
+        <v>https://music.apple.com/us/album/lucky-day/1849264498</v>
       </c>
       <c r="L175" t="str">
-        <v>Angela - Hayden Everett</v>
+        <v>Lucky Day - Ally Evenson</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Disappear</v>
+        <v>Breathe On It</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/disappear/1847663553</v>
+        <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
       </c>
       <c r="D176" t="str">
         <v>2026-01-23</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Greyhound</v>
+        <v>Breathe On It - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:31</v>
+        <v>4:00</v>
       </c>
       <c r="H176" t="str">
-        <v>Katie Tupper</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/katie-tupper/1395542470</v>
+        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/disappear/1847663546</v>
+        <v>https://music.apple.com/us/album/breathe-on-it/1862938798</v>
       </c>
       <c r="L176" t="str">
-        <v>Disappear - Katie Tupper</v>
+        <v>Breathe On It - Tauren Wells</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Catapult</v>
+        <v>Easy</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/catapult/1862951335</v>
+        <v>https://music.apple.com/us/song/easy/1863456906</v>
       </c>
       <c r="D177" t="str">
         <v>2026-01-23</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Catapult - Single</v>
+        <v>Easy - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:57</v>
+        <v>4:30</v>
       </c>
       <c r="H177" t="str">
-        <v>Cape Francis</v>
+        <v>lydi lynn</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/cape-francis/1242523550</v>
+        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/catapult/1862951333</v>
+        <v>https://music.apple.com/us/album/easy/1863456903</v>
       </c>
       <c r="L177" t="str">
-        <v>Catapult - Cape Francis</v>
+        <v>Easy - lydi lynn</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Think Twice</v>
+        <v>Break Me In</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/think-twice/1850698548</v>
+        <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
       </c>
       <c r="D178" t="str">
         <v>2026-01-23</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Think Twice - Single</v>
+        <v>Break Me In - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:22</v>
+        <v>2:52</v>
       </c>
       <c r="H178" t="str">
-        <v>Leonie Biney</v>
+        <v>Joyce Wrice</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
+        <v>https://music.apple.com/us/artist/joyce-wrice/591991458</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/think-twice/1850698545</v>
+        <v>https://music.apple.com/us/album/break-me-in/1862881766</v>
       </c>
       <c r="L178" t="str">
-        <v>Think Twice - Leonie Biney</v>
+        <v>Break Me In - Joyce Wrice</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>LOVESONGS</v>
+        <v>Long Live Love</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
+        <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
       </c>
       <c r="D179" t="str">
         <v>2026-01-23</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>BEAUTIFUL MADNESS</v>
+        <v>Long Live Love - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:33</v>
+        <v>2:36</v>
       </c>
       <c r="H179" t="str">
-        <v>Agnes</v>
+        <v>Sugar</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/agnes/42568985</v>
+        <v>https://music.apple.com/us/artist/sugar/530175867</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/lovesongs/1849098275</v>
+        <v>https://music.apple.com/us/album/long-live-love/1851251226</v>
       </c>
       <c r="L179" t="str">
-        <v>LOVESONGS - Agnes</v>
+        <v>Long Live Love - Sugar</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Down South</v>
+        <v>Depressed</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/down-south/1861010793</v>
+        <v>https://music.apple.com/us/song/depressed/1840400522</v>
       </c>
       <c r="D180" t="str">
         <v>2026-01-23</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Down South - Single</v>
+        <v>Boycott Heaven</v>
       </c>
       <c r="G180" t="str">
-        <v>2:19</v>
+        <v>3:32</v>
       </c>
       <c r="H180" t="str">
-        <v>Trap Dickey</v>
+        <v>The Format</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
+        <v>https://music.apple.com/us/artist/the-format/3064903</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/down-south/1861010788</v>
+        <v>https://music.apple.com/us/album/depressed/1840399886</v>
       </c>
       <c r="L180" t="str">
-        <v>Down South - Trap Dickey</v>
+        <v>Depressed - The Format</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW</v>
+        <v>Empty Hands</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
+        <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
       </c>
       <c r="D181" t="str">
         <v>2026-01-23</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW - Single</v>
+        <v>Empty Hands</v>
       </c>
       <c r="G181" t="str">
-        <v>2:16</v>
+        <v>3:09</v>
       </c>
       <c r="H181" t="str">
-        <v>SALIMATA</v>
+        <v>Poppy</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/salimata/690253822</v>
+        <v>https://music.apple.com/us/artist/poppy/1004130511</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/jackpot-foil-a-colors-show/1866998655</v>
+        <v>https://music.apple.com/us/album/empty-hands/1852046141</v>
       </c>
       <c r="L181" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW - SALIMATA</v>
+        <v>Empty Hands - Poppy</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Love Like This</v>
+        <v>The Long Surrender</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
+        <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
       </c>
       <c r="D182" t="str">
         <v>2026-01-23</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Love Like This - Single</v>
+        <v>The Long Surrender</v>
       </c>
       <c r="G182" t="str">
-        <v>3:30</v>
+        <v>3:45</v>
       </c>
       <c r="H182" t="str">
-        <v>Jacob Banks</v>
+        <v>NEEDTOBREATHE</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/jacob-banks/625014171</v>
+        <v>https://music.apple.com/us/artist/needtobreathe/113247214</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/love-like-this/1866999617</v>
+        <v>https://music.apple.com/us/album/the-long-surrender/1861935699</v>
       </c>
       <c r="L182" t="str">
-        <v>Love Like This - Jacob Banks</v>
+        <v>The Long Surrender - NEEDTOBREATHE</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Plan Plan</v>
+        <v>Angela</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
+        <v>https://music.apple.com/us/song/angela/1866624257</v>
       </c>
       <c r="D183" t="str">
         <v>2026-01-23</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>La Locura</v>
+        <v>Angela - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:10</v>
+        <v>3:32</v>
       </c>
       <c r="H183" t="str">
-        <v>Funky</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/funky/80960663</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/plan-plan/1867940087</v>
+        <v>https://music.apple.com/us/album/angela/1866624256</v>
       </c>
       <c r="L183" t="str">
-        <v>Plan Plan - Funky</v>
+        <v>Angela - Hayden Everett</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>double edged sword</v>
+        <v>Disappear</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
+        <v>https://music.apple.com/us/song/disappear/1847663553</v>
       </c>
       <c r="D184" t="str">
         <v>2026-01-23</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>double edged sword - Single</v>
+        <v>Greyhound</v>
       </c>
       <c r="G184" t="str">
-        <v>3:28</v>
+        <v>3:31</v>
       </c>
       <c r="H184" t="str">
-        <v>Hailey Picardi</v>
+        <v>Katie Tupper</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/katie-tupper/1395542470</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/double-edged-sword/1868829044</v>
+        <v>https://music.apple.com/us/album/disappear/1847663546</v>
       </c>
       <c r="L184" t="str">
-        <v>double edged sword - Hailey Picardi</v>
+        <v>Disappear - Katie Tupper</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>SOMEWHERE IN BETWEEN</v>
+        <v>Catapult</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
+        <v>https://music.apple.com/us/song/catapult/1862951335</v>
       </c>
       <c r="D185" t="str">
         <v>2026-01-23</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>SOMEWHERE IN BETWEEN - Single</v>
+        <v>Catapult - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:27</v>
+        <v>2:57</v>
       </c>
       <c r="H185" t="str">
-        <v>Matt Hansen</v>
+        <v>Cape Francis</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/matt-hansen/1442658353</v>
+        <v>https://music.apple.com/us/artist/cape-francis/1242523550</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/somewhere-in-between/1866969151</v>
+        <v>https://music.apple.com/us/album/catapult/1862951333</v>
       </c>
       <c r="L185" t="str">
-        <v>SOMEWHERE IN BETWEEN - Matt Hansen</v>
+        <v>Catapult - Cape Francis</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>The Decay</v>
+        <v>Think Twice</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/the-decay/1862836783</v>
+        <v>https://music.apple.com/us/song/think-twice/1850698548</v>
       </c>
       <c r="D186" t="str">
         <v>2026-01-23</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>What Remains (Midnight Edition)</v>
+        <v>Think Twice - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:20</v>
+        <v>2:22</v>
       </c>
       <c r="H186" t="str">
-        <v>Pop Evil</v>
+        <v>Leonie Biney</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/pop-evil/441597923</v>
+        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/the-decay/1862836507</v>
+        <v>https://music.apple.com/us/album/think-twice/1850698545</v>
       </c>
       <c r="L186" t="str">
-        <v>The Decay - Pop Evil</v>
+        <v>Think Twice - Leonie Biney</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>3111</v>
+        <v>LOVESONGS</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/3111/1862225387</v>
+        <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
       </c>
       <c r="D187" t="str">
         <v>2026-01-23</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Goliath</v>
+        <v>BEAUTIFUL MADNESS</v>
       </c>
       <c r="G187" t="str">
-        <v>4:08</v>
+        <v>3:33</v>
       </c>
       <c r="H187" t="str">
-        <v>Exodus</v>
+        <v>Agnes</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
+        <v>https://music.apple.com/us/artist/agnes/42568985</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/3111/1862225385</v>
+        <v>https://music.apple.com/us/album/lovesongs/1849098275</v>
       </c>
       <c r="L187" t="str">
-        <v>3111 - Exodus</v>
+        <v>LOVESONGS - Agnes</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Touch My Love And Die</v>
+        <v>Down South</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
+        <v>https://music.apple.com/us/song/down-south/1861010793</v>
       </c>
       <c r="D188" t="str">
         <v>2026-01-23</v>
@@ -7519,68 +7519,372 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Touch My Love And Die - Single</v>
+        <v>Down South - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>2:57</v>
+        <v>2:19</v>
       </c>
       <c r="H188" t="str">
-        <v>Myrkur</v>
+        <v>Trap Dickey</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/myrkur/293296859</v>
+        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/touch-my-love-and-die/1867630168</v>
+        <v>https://music.apple.com/us/album/down-south/1861010788</v>
       </c>
       <c r="L188" t="str">
-        <v>Touch My Love And Die - Myrkur</v>
+        <v>Down South - Trap Dickey</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
+        <v>Jackpot &amp; Foil - A COLORS SHOW</v>
+      </c>
+      <c r="B189" t="str">
+        <v/>
+      </c>
+      <c r="C189" t="str">
+        <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
+      </c>
+      <c r="D189" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E189" t="str">
+        <v/>
+      </c>
+      <c r="F189" t="str">
+        <v>Jackpot &amp; Foil - A COLORS SHOW - Single</v>
+      </c>
+      <c r="G189" t="str">
+        <v>2:16</v>
+      </c>
+      <c r="H189" t="str">
+        <v>SALIMATA</v>
+      </c>
+      <c r="I189" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J189" t="str">
+        <v>https://music.apple.com/us/artist/salimata/690253822</v>
+      </c>
+      <c r="K189" t="str">
+        <v>https://music.apple.com/us/album/jackpot-foil-a-colors-show/1866998655</v>
+      </c>
+      <c r="L189" t="str">
+        <v>Jackpot &amp; Foil - A COLORS SHOW - SALIMATA</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>Love Like This</v>
+      </c>
+      <c r="B190" t="str">
+        <v/>
+      </c>
+      <c r="C190" t="str">
+        <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
+      </c>
+      <c r="D190" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E190" t="str">
+        <v/>
+      </c>
+      <c r="F190" t="str">
+        <v>Love Like This - Single</v>
+      </c>
+      <c r="G190" t="str">
+        <v>3:30</v>
+      </c>
+      <c r="H190" t="str">
+        <v>Jacob Banks</v>
+      </c>
+      <c r="I190" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J190" t="str">
+        <v>https://music.apple.com/us/artist/jacob-banks/625014171</v>
+      </c>
+      <c r="K190" t="str">
+        <v>https://music.apple.com/us/album/love-like-this/1866999617</v>
+      </c>
+      <c r="L190" t="str">
+        <v>Love Like This - Jacob Banks</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>Plan Plan</v>
+      </c>
+      <c r="B191" t="str">
+        <v/>
+      </c>
+      <c r="C191" t="str">
+        <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
+      </c>
+      <c r="D191" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E191" t="str">
+        <v/>
+      </c>
+      <c r="F191" t="str">
+        <v>La Locura</v>
+      </c>
+      <c r="G191" t="str">
+        <v>3:10</v>
+      </c>
+      <c r="H191" t="str">
+        <v>Funky</v>
+      </c>
+      <c r="I191" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J191" t="str">
+        <v>https://music.apple.com/us/artist/funky/80960663</v>
+      </c>
+      <c r="K191" t="str">
+        <v>https://music.apple.com/us/album/plan-plan/1867940087</v>
+      </c>
+      <c r="L191" t="str">
+        <v>Plan Plan - Funky</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>double edged sword</v>
+      </c>
+      <c r="B192" t="str">
+        <v/>
+      </c>
+      <c r="C192" t="str">
+        <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
+      </c>
+      <c r="D192" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E192" t="str">
+        <v/>
+      </c>
+      <c r="F192" t="str">
+        <v>double edged sword - Single</v>
+      </c>
+      <c r="G192" t="str">
+        <v>3:28</v>
+      </c>
+      <c r="H192" t="str">
+        <v>Hailey Picardi</v>
+      </c>
+      <c r="I192" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J192" t="str">
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+      </c>
+      <c r="K192" t="str">
+        <v>https://music.apple.com/us/album/double-edged-sword/1868829044</v>
+      </c>
+      <c r="L192" t="str">
+        <v>double edged sword - Hailey Picardi</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>SOMEWHERE IN BETWEEN</v>
+      </c>
+      <c r="B193" t="str">
+        <v/>
+      </c>
+      <c r="C193" t="str">
+        <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
+      </c>
+      <c r="D193" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E193" t="str">
+        <v/>
+      </c>
+      <c r="F193" t="str">
+        <v>SOMEWHERE IN BETWEEN - Single</v>
+      </c>
+      <c r="G193" t="str">
+        <v>3:27</v>
+      </c>
+      <c r="H193" t="str">
+        <v>Matt Hansen</v>
+      </c>
+      <c r="I193" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J193" t="str">
+        <v>https://music.apple.com/us/artist/matt-hansen/1442658353</v>
+      </c>
+      <c r="K193" t="str">
+        <v>https://music.apple.com/us/album/somewhere-in-between/1866969151</v>
+      </c>
+      <c r="L193" t="str">
+        <v>SOMEWHERE IN BETWEEN - Matt Hansen</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>The Decay</v>
+      </c>
+      <c r="B194" t="str">
+        <v/>
+      </c>
+      <c r="C194" t="str">
+        <v>https://music.apple.com/us/song/the-decay/1862836783</v>
+      </c>
+      <c r="D194" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E194" t="str">
+        <v/>
+      </c>
+      <c r="F194" t="str">
+        <v>What Remains (Midnight Edition)</v>
+      </c>
+      <c r="G194" t="str">
+        <v>3:20</v>
+      </c>
+      <c r="H194" t="str">
+        <v>Pop Evil</v>
+      </c>
+      <c r="I194" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J194" t="str">
+        <v>https://music.apple.com/us/artist/pop-evil/441597923</v>
+      </c>
+      <c r="K194" t="str">
+        <v>https://music.apple.com/us/album/the-decay/1862836507</v>
+      </c>
+      <c r="L194" t="str">
+        <v>The Decay - Pop Evil</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>3111</v>
+      </c>
+      <c r="B195" t="str">
+        <v/>
+      </c>
+      <c r="C195" t="str">
+        <v>https://music.apple.com/us/song/3111/1862225387</v>
+      </c>
+      <c r="D195" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E195" t="str">
+        <v/>
+      </c>
+      <c r="F195" t="str">
+        <v>Goliath</v>
+      </c>
+      <c r="G195" t="str">
+        <v>4:08</v>
+      </c>
+      <c r="H195" t="str">
+        <v>Exodus</v>
+      </c>
+      <c r="I195" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J195" t="str">
+        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
+      </c>
+      <c r="K195" t="str">
+        <v>https://music.apple.com/us/album/3111/1862225385</v>
+      </c>
+      <c r="L195" t="str">
+        <v>3111 - Exodus</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>Touch My Love And Die</v>
+      </c>
+      <c r="B196" t="str">
+        <v/>
+      </c>
+      <c r="C196" t="str">
+        <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
+      </c>
+      <c r="D196" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E196" t="str">
+        <v/>
+      </c>
+      <c r="F196" t="str">
+        <v>Touch My Love And Die - Single</v>
+      </c>
+      <c r="G196" t="str">
+        <v>2:57</v>
+      </c>
+      <c r="H196" t="str">
+        <v>Myrkur</v>
+      </c>
+      <c r="I196" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J196" t="str">
+        <v>https://music.apple.com/us/artist/myrkur/293296859</v>
+      </c>
+      <c r="K196" t="str">
+        <v>https://music.apple.com/us/album/touch-my-love-and-die/1867630168</v>
+      </c>
+      <c r="L196" t="str">
+        <v>Touch My Love And Die - Myrkur</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
         <v>Bomb To A Knife Fight</v>
       </c>
-      <c r="B189" t="str">
-        <v/>
-      </c>
-      <c r="C189" t="str">
+      <c r="B197" t="str">
+        <v/>
+      </c>
+      <c r="C197" t="str">
         <v>https://music.apple.com/us/song/bomb-to-a-knife-fight/1861589406</v>
       </c>
-      <c r="D189" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E189" t="str">
-        <v/>
-      </c>
-      <c r="F189" t="str">
+      <c r="D197" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E197" t="str">
+        <v/>
+      </c>
+      <c r="F197" t="str">
         <v>Bomb To A Knife Fight - Single</v>
       </c>
-      <c r="G189" t="str">
+      <c r="G197" t="str">
         <v>2:41</v>
       </c>
-      <c r="H189" t="str">
+      <c r="H197" t="str">
         <v>The Barbarians of California</v>
       </c>
-      <c r="I189" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J189" t="str">
+      <c r="I197" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J197" t="str">
         <v>https://music.apple.com/us/artist/the-barbarians-of-california/1724096474</v>
       </c>
-      <c r="K189" t="str">
+      <c r="K197" t="str">
         <v>https://music.apple.com/us/album/bomb-to-a-knife-fight/1861589405</v>
       </c>
-      <c r="L189" t="str">
+      <c r="L197" t="str">
         <v>Bomb To A Knife Fight - The Barbarians of California</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L189"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L197"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-01-week04/titles.xlsx
+++ b/data/global/2026-01-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L197"/>
+  <dimension ref="A1:L190"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שמעון ביטון - תפילות קאבר להורדה</v>
+        <v>מאיה בלזיצמן &amp; מתן אפרת – ילדת לב</v>
       </c>
       <c r="B2" t="str">
         <v>2026-01-23</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409337&amp;sid=28578d22d6bc8863a18a652dcec3ff77</v>
+        <v>https://yosmusic.com/%d7%9e%d7%90%d7%99%d7%94-%d7%91%d7%9c%d7%96%d7%99%d7%a6%d7%9e%d7%9f-%d7%9e%d7%aa%d7%9f-%d7%90%d7%a4%d7%a8%d7%aa-%d7%99%d7%9c%d7%93%d7%aa-%d7%9c%d7%91/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-23</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>"ילדת לב” הוא שיר על רגע חמקמק ומבלבל: הזמן שבו ילד מפסיק להיות של ההורה ומתחיל להיות של עצמו. לא מרד דרמטי, לא ניתוק – אלא התרחקות עדינה, כמעט בלתי נראית, שמורגשת דווקא באינטימיות היומיומית:חדר שני, עייפות של הורה, ערב</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -460,7 +460,7 @@
         <v/>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שמעון ביטון - תפילות קאבר להורדה</v>
+        <v>מאיה בלזיצמן &amp; מתן אפרת – ילדת לב</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>נריה עובדיה - ילדה של אב קאבר להורדה</v>
+        <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-01-23</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409336&amp;sid=28578d22d6bc8863a18a652dcec3ff77</v>
+        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-23</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>14 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>2:59</v>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>Lana Lubany</v>
       </c>
       <c r="I3" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>נריה עובדיה - ילדה של אב קאבר להורדה</v>
+        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>נועם דדון - זר של נרקיסים קאבר להורדה</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-01-23</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409335&amp;sid=28578d22d6bc8863a18a652dcec3ff77</v>
+        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-23</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>20 hours ago</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>4:21</v>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I4" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>נועם דדון - זר של נרקיסים קאבר להורדה</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>יהונתן נחמיאס - מאשאפ חופות 2026 להורדה</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-01-23</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409334&amp;sid=28578d22d6bc8863a18a652dcec3ff77</v>
+        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-23</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>4:09</v>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I5" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>יהונתן נחמיאס - מאשאפ חופות 2026 להורדה</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>חנוך שובל - עולם בשני צבעים קאבר להורדה</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-01-23</v>
+        <v>2 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409333&amp;sid=28578d22d6bc8863a18a652dcec3ff77</v>
+        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-23</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>2:34</v>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I6" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>חנוך שובל - עולם בשני צבעים קאבר להורדה</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>חן גז - אהבה חולה קאבר להורדה</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-01-23</v>
+        <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409332&amp;sid=28578d22d6bc8863a18a652dcec3ff77</v>
+        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-23</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>3:10</v>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>Olivia Dean</v>
       </c>
       <c r="I7" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>חן גז - אהבה חולה קאבר להורדה</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>אוריאל שלום - אשת חיל שלי קאבר להורדה</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-01-23</v>
+        <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409331&amp;sid=28578d22d6bc8863a18a652dcec3ff77</v>
+        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-23</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v/>
+        <v>3:21</v>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I8" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>אוריאל שלום - אשת חיל שלי קאבר להורדה</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אבירם ברמי - איפה את קאבר להורדה</v>
+        <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-01-23</v>
+        <v>3 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409330&amp;sid=28578d22d6bc8863a18a652dcec3ff77</v>
+        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-23</v>
@@ -717,16 +717,16 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>3 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>3:06</v>
       </c>
       <c r="H9" t="str">
-        <v/>
+        <v>The Avett Brothers</v>
       </c>
       <c r="I9" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>אבירם ברמי - איפה את קאבר להורדה</v>
+        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video)</v>
+        <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>13 hours ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
+        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-23</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>13 hours ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>2:59</v>
+        <v>3:21</v>
       </c>
       <c r="H10" t="str">
-        <v>Lana Lubany</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
+        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B11" t="str">
-        <v>19 hours ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
+        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-23</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>19 hours ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>4:21</v>
+        <v>7:21</v>
       </c>
       <c r="H11" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Katy Perry</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B12" t="str">
-        <v>1 day ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
+        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-23</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1 day ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>4:09</v>
+        <v>3:17</v>
       </c>
       <c r="H12" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
+        <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B13" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
+        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-23</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>2:34</v>
+        <v>3:45</v>
       </c>
       <c r="H13" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Tones And I</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
+        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B14" t="str">
-        <v>2 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
+        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-23</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:10</v>
+        <v>3:57</v>
       </c>
       <c r="H14" t="str">
-        <v>Olivia Dean</v>
+        <v>Ashleigh Dallas</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>2 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
+        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-23</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>2 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:21</v>
+        <v>3:03</v>
       </c>
       <c r="H15" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video)</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B16" t="str">
-        <v>3 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
+        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-23</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>3 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:06</v>
+        <v>4:27</v>
       </c>
       <c r="H16" t="str">
-        <v>The Avett Brothers</v>
+        <v>Chappell Roan</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video)</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B17" t="str">
-        <v>3 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
+        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-23</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>3 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:21</v>
+        <v>4:34</v>
       </c>
       <c r="H17" t="str">
-        <v>Jordana Bryant</v>
+        <v>Armik</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
+        <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>3 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
+        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-23</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>3 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>7:21</v>
+        <v>2:54</v>
       </c>
       <c r="H18" t="str">
-        <v>Katy Perry</v>
+        <v>LØLØ</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
+        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
+        <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B19" t="str">
-        <v>3 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
+        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-23</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>3 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:17</v>
+        <v>3:25</v>
       </c>
       <c r="H19" t="str">
-        <v>Lauren Watkins</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Just A Mess (Live acoustic studio session)</v>
+        <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
+        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-23</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:45</v>
+        <v>2:01</v>
       </c>
       <c r="H20" t="str">
-        <v>Tones And I</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
+        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
+        <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B21" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
+        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-23</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:57</v>
+        <v>2:25</v>
       </c>
       <c r="H21" t="str">
-        <v>Ashleigh Dallas</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
+        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
+        <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B22" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
+        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-23</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:03</v>
+        <v>1:14</v>
       </c>
       <c r="H22" t="str">
-        <v>Charlie Puth</v>
+        <v>Labrinth</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
+        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B23" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
+        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-23</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>4:27</v>
+        <v>2:59</v>
       </c>
       <c r="H23" t="str">
-        <v>Chappell Roan</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B24" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
+        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-23</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>4:34</v>
+        <v>2:29</v>
       </c>
       <c r="H24" t="str">
-        <v>Armik</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>LØLØ - 007 (Official Music Video)</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B25" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
+        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-23</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:54</v>
+        <v>2:34</v>
       </c>
       <c r="H25" t="str">
-        <v>LØLØ</v>
+        <v>Jagwar Twin</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer)</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
+        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-23</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:25</v>
+        <v>3:48</v>
       </c>
       <c r="H26" t="str">
-        <v>Tenille Townes</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video)</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
       </c>
       <c r="B27" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
+        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-23</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>2:01</v>
+        <v>3:32</v>
       </c>
       <c r="H27" t="str">
-        <v>Alan Walker</v>
+        <v>The Beaches</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio)</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
       </c>
       <c r="B28" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
+        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-23</v>
@@ -1442,10 +1442,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>2:25</v>
+        <v>3:49</v>
       </c>
       <c r="H28" t="str">
-        <v>Charli xcx</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer)</v>
+        <v>Madison Beer - bad enough (Official Music Video)</v>
       </c>
       <c r="B29" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
+        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-23</v>
@@ -1480,10 +1480,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>1:14</v>
+        <v>4:28</v>
       </c>
       <c r="H29" t="str">
-        <v>Labrinth</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
+        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
+        <v>Ty Myers - Message to You (Official Video)</v>
       </c>
       <c r="B30" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
+        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-23</v>
@@ -1518,10 +1518,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:59</v>
+        <v>3:37</v>
       </c>
       <c r="H30" t="str">
-        <v>Charlie Puth</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
+        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Girl Tones - Volcano (Visualizer)</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
       </c>
       <c r="B31" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
+        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-23</v>
@@ -1556,10 +1556,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>2:29</v>
+        <v>3:35</v>
       </c>
       <c r="H31" t="str">
-        <v>Girl Tones</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
       </c>
       <c r="B32" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
+        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-23</v>
@@ -1594,10 +1594,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>2:34</v>
+        <v>2:31</v>
       </c>
       <c r="H32" t="str">
-        <v>Jagwar Twin</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
       </c>
       <c r="B33" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
+        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-23</v>
@@ -1632,10 +1632,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:48</v>
+        <v>3:21</v>
       </c>
       <c r="H33" t="str">
-        <v>Caroline Jones</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
       </c>
       <c r="B34" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
+        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-23</v>
@@ -1670,10 +1670,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:32</v>
+        <v>5:24</v>
       </c>
       <c r="H34" t="str">
-        <v>The Beaches</v>
+        <v>Nickless</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
+        <v>Peach PRC - Back To You (Official Audio)</v>
       </c>
       <c r="B35" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
+        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-23</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:49</v>
+        <v>3:11</v>
       </c>
       <c r="H35" t="str">
-        <v>Dolly Parton</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
+        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Madison Beer - bad enough (Official Music Video)</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
       </c>
       <c r="B36" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
+        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-23</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>4:28</v>
+        <v>4:11</v>
       </c>
       <c r="H36" t="str">
-        <v>Madison Beer</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Ty Myers - Message to You (Official Video)</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B37" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
+        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-23</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:37</v>
+        <v>3:31</v>
       </c>
       <c r="H37" t="str">
-        <v>Ty Myers</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
       </c>
       <c r="B38" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
+        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-23</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:35</v>
+        <v>4:16</v>
       </c>
       <c r="H38" t="str">
-        <v>Megan Moroney</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B39" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
+        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-23</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>2:31</v>
+        <v>4:42</v>
       </c>
       <c r="H39" t="str">
-        <v>Julia Cole Music</v>
+        <v>JavaJazzFest</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
+        <v>Teo Glacier - Don't Mind (Music Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
+        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-23</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:21</v>
+        <v>2:47</v>
       </c>
       <c r="H40" t="str">
-        <v>Lily Allen</v>
+        <v>Teo Glacier</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
+        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>7 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
+        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-23</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>7 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>5:24</v>
+        <v>3:59</v>
       </c>
       <c r="H41" t="str">
-        <v>Nickless</v>
+        <v>Brigitte Calls Me Baby</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Peach PRC - Back To You (Official Audio)</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
       </c>
       <c r="B42" t="str">
-        <v>8 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
+        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-23</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>8 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:11</v>
+        <v>4:09</v>
       </c>
       <c r="H42" t="str">
-        <v>Peach PRC</v>
+        <v>Louie TheSinger</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
+        <v>ella jane - When I Was Beautiful (Live)</v>
       </c>
       <c r="B43" t="str">
-        <v>8 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
+        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-23</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>8 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>4:11</v>
+        <v>3:24</v>
       </c>
       <c r="H43" t="str">
-        <v>Ocean Alley</v>
+        <v>ella jane</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
+        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Johnny Orlando - Emilia (Official Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>8 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
+        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-23</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>8 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:31</v>
+        <v>3:14</v>
       </c>
       <c r="H44" t="str">
-        <v>OneRepublic</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
+        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
+        <v>Kungs, Theophilus London - Galaxy (official video)</v>
       </c>
       <c r="B45" t="str">
-        <v>8 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
+        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-23</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>8 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>4:16</v>
+        <v>3:32</v>
       </c>
       <c r="H45" t="str">
-        <v>Ty Myers</v>
+        <v>Kungs</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
+        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
       </c>
       <c r="B46" t="str">
-        <v>8 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
+        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-23</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>8 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>4:42</v>
+        <v>3:15</v>
       </c>
       <c r="H46" t="str">
-        <v>JavaJazzFest</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video)</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>9 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
+        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-23</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>9 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>2:47</v>
+        <v>3:03</v>
       </c>
       <c r="H47" t="str">
-        <v>Teo Glacier</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
+        <v>Stephen Sanchez - Sweet Love</v>
       </c>
       <c r="B48" t="str">
-        <v>10 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
+        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-23</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>10 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:59</v>
+        <v>3:04</v>
       </c>
       <c r="H48" t="str">
-        <v>Brigitte Calls Me Baby</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
+        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
+        <v>Bruno Mars - I Just Might [Official Music Video]</v>
       </c>
       <c r="B49" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
+        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-23</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G49" t="str">
-        <v>4:09</v>
+        <v>3:33</v>
       </c>
       <c r="H49" t="str">
-        <v>Louie TheSinger</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
+        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ella jane - When I Was Beautiful (Live)</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
       </c>
       <c r="B50" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
+        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-23</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:24</v>
+        <v>2:53</v>
       </c>
       <c r="H50" t="str">
-        <v>ella jane</v>
+        <v>MAX</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Johnny Orlando - Emilia (Official Video)</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
+        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-23</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:14</v>
+        <v>4:11</v>
       </c>
       <c r="H51" t="str">
-        <v>Johnny Orlando</v>
+        <v>Jessie J</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video)</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
+        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-23</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:32</v>
+        <v>2:45</v>
       </c>
       <c r="H52" t="str">
-        <v>Kungs</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
+        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-23</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:15</v>
+        <v>4:00</v>
       </c>
       <c r="H53" t="str">
-        <v>Billy Raffoul</v>
+        <v>Brandon Lake and Cody Johnson</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
       </c>
       <c r="B54" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
+        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-23</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:03</v>
+        <v>3:27</v>
       </c>
       <c r="H54" t="str">
-        <v>NathanEvanss</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Stephen Sanchez - Sweet Love</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
       </c>
       <c r="B55" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
+        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-23</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:04</v>
+        <v>3:25</v>
       </c>
       <c r="H55" t="str">
-        <v>Stephen Sanchez</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video]</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B56" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
+        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-23</v>
@@ -2506,10 +2506,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:33</v>
+        <v>3:34</v>
       </c>
       <c r="H56" t="str">
-        <v>Bruno Mars</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
+        <v>Train - Mittens (Live on TODAY)</v>
       </c>
       <c r="B57" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
+        <v>https://www.youtube.com/watch?v=R2k_wPsAHKQ</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-23</v>
@@ -2544,10 +2544,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G57" t="str">
-        <v>2:53</v>
+        <v>3:17</v>
       </c>
       <c r="H57" t="str">
-        <v>MAX</v>
+        <v>Train</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
+        <v>Train - Mittens (Live on TODAY) - Train</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
       </c>
       <c r="B58" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
+        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-23</v>
@@ -2582,10 +2582,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
-        <v>4:11</v>
+        <v>2:25</v>
       </c>
       <c r="H58" t="str">
-        <v>Jessie J</v>
+        <v>Joseph</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B59" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
+        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-23</v>
@@ -2620,10 +2620,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:45</v>
+        <v>3:26</v>
       </c>
       <c r="H59" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B60" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
+        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-23</v>
@@ -2658,10 +2658,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
-        <v>4:00</v>
+        <v>4:46</v>
       </c>
       <c r="H60" t="str">
-        <v>Brandon Lake and Cody Johnson</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B61" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
+        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-23</v>
@@ -2696,10 +2696,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:27</v>
+        <v>3:24</v>
       </c>
       <c r="H61" t="str">
-        <v>The Kid LAROI.</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
       </c>
       <c r="B62" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
+        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-23</v>
@@ -2734,10 +2734,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:25</v>
+        <v>2:52</v>
       </c>
       <c r="H62" t="str">
-        <v>Olivia Dean</v>
+        <v>Madonna</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
       </c>
       <c r="B63" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
+        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-23</v>
@@ -2772,10 +2772,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:34</v>
+        <v>2:06</v>
       </c>
       <c r="H63" t="str">
-        <v>Demi Lovato</v>
+        <v>Estas Tonne</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estas Tonne</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Train - Mittens (Live on TODAY)</v>
+        <v>Anna Graves - Burn On (Official Music Video)</v>
       </c>
       <c r="B64" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=R2k_wPsAHKQ</v>
+        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-23</v>
@@ -2810,10 +2810,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:17</v>
+        <v>3:09</v>
       </c>
       <c r="H64" t="str">
-        <v>Train</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Train - Mittens (Live on TODAY) - Train</v>
+        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
       </c>
       <c r="B65" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
+        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-23</v>
@@ -2848,10 +2848,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
-        <v>2:25</v>
+        <v>5:11</v>
       </c>
       <c r="H65" t="str">
-        <v>Joseph</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
       </c>
       <c r="B66" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
+        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-23</v>
@@ -2886,10 +2886,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:26</v>
+        <v>3:40</v>
       </c>
       <c r="H66" t="str">
-        <v>Demi Lovato</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
+        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-23</v>
@@ -2924,10 +2924,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>4:46</v>
+        <v>3:49</v>
       </c>
       <c r="H67" t="str">
-        <v>Keith Urban</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
+        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-23</v>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:24</v>
+        <v>3:42</v>
       </c>
       <c r="H68" t="str">
-        <v>Keith Urban</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
+        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-23</v>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>2:52</v>
+        <v>5:11</v>
       </c>
       <c r="H69" t="str">
-        <v>Madonna</v>
+        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
+        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-23</v>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>2:06</v>
+        <v>3:57</v>
       </c>
       <c r="H70" t="str">
-        <v>Estas Tonne</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estas Tonne</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Anna Graves - Burn On (Official Music Video)</v>
+        <v>Grace Enger - All My Songs (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
+        <v>https://www.youtube.com/watch?v=gWyaiGAFVO8</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-23</v>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:09</v>
+        <v>3:29</v>
       </c>
       <c r="H71" t="str">
-        <v>Anna Graves</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
+        <v>Grace Enger - All My Songs (Official Lyric Video) - Grace Enger</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
+        <v>Alan Walker - Broken Strings (Official Music Video)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
+        <v>https://www.youtube.com/watch?v=jwQKcW474Tc</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-23</v>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>5:11</v>
+        <v>3:10</v>
       </c>
       <c r="H72" t="str">
-        <v>Ocean Alley</v>
+        <v>Alan Walker and 2 more</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
+        <v>Alan Walker - Broken Strings (Official Music Video) - Alan Walker and 2 more</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
+        <v>Emilia Tarrant - Break Up With Myself</v>
       </c>
       <c r="B73" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
+        <v>https://www.youtube.com/watch?v=3N7iKwqENP0</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-23</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:40</v>
+        <v>4:04</v>
       </c>
       <c r="H73" t="str">
-        <v>Zara Larsson</v>
+        <v>Emilia Tarrant</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
+        <v>Emilia Tarrant - Break Up With Myself - Emilia Tarrant</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
+        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026)</v>
       </c>
       <c r="B74" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
+        <v>https://www.youtube.com/watch?v=sKG5ZIzCnFQ</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-23</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:49</v>
+        <v>3:09</v>
       </c>
       <c r="H74" t="str">
-        <v>Lauren Watkins</v>
+        <v>Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026) - Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer)</v>
       </c>
       <c r="B75" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
+        <v>https://www.youtube.com/watch?v=Koj30I91_8k</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-23</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:42</v>
+        <v>2:27</v>
       </c>
       <c r="H75" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
+        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Maggie Lindemann - fate</v>
       </c>
       <c r="B76" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
+        <v>https://www.youtube.com/watch?v=xZdWEmnRK4g</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-23</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>5:11</v>
+        <v>2:12</v>
       </c>
       <c r="H76" t="str">
-        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Maggie Lindemann</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Maggie Lindemann - fate - Maggie Lindemann</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
+        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023)</v>
       </c>
       <c r="B77" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
+        <v>https://www.youtube.com/watch?v=wo9yPPCh75Q</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-23</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:57</v>
+        <v>4:44</v>
       </c>
       <c r="H77" t="str">
-        <v>Lainey Wilson</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
+        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023) - Cliff Richard</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Grace Enger - All My Songs (Official Lyric Video)</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025</v>
       </c>
       <c r="B78" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=gWyaiGAFVO8</v>
+        <v>https://www.youtube.com/watch?v=ND6maRwmzHk</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-23</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:29</v>
+        <v>1:00:09</v>
       </c>
       <c r="H78" t="str">
-        <v>Grace Enger</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Grace Enger - All My Songs (Official Lyric Video) - Grace Enger</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Alan Walker - Broken Strings (Official Music Video)</v>
+        <v>RAYE - Black Mascara. (Live at The Royal Albert Hall)</v>
       </c>
       <c r="B79" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=jwQKcW474Tc</v>
+        <v>https://www.youtube.com/watch?v=9jMMOYr-VhE</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-23</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:10</v>
+        <v>4:15</v>
       </c>
       <c r="H79" t="str">
-        <v>Alan Walker and 2 more</v>
+        <v>RAYE</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Alan Walker - Broken Strings (Official Music Video) - Alan Walker and 2 more</v>
+        <v>RAYE - Black Mascara. (Live at The Royal Albert Hall) - RAYE</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Emilia Tarrant - Break Up With Myself</v>
+        <v>Madison Cunningham - My Full Name (Garden Session)</v>
       </c>
       <c r="B80" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=3N7iKwqENP0</v>
+        <v>https://www.youtube.com/watch?v=o2F-QmqdNtI</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-23</v>
@@ -3418,10 +3418,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>4:04</v>
+        <v>4:07</v>
       </c>
       <c r="H80" t="str">
-        <v>Emilia Tarrant</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Emilia Tarrant - Break Up With Myself - Emilia Tarrant</v>
+        <v>Madison Cunningham - My Full Name (Garden Session) - Madison Cunningham</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026)</v>
+        <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions)</v>
       </c>
       <c r="B81" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=sKG5ZIzCnFQ</v>
+        <v>https://www.youtube.com/watch?v=5-6cEVLqE90</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-23</v>
@@ -3456,10 +3456,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:09</v>
+        <v>3:10</v>
       </c>
       <c r="H81" t="str">
-        <v>Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026) - Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions) - Teddy Swims</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer)</v>
+        <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower)</v>
       </c>
       <c r="B82" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=Koj30I91_8k</v>
+        <v>https://www.youtube.com/watch?v=ivPSbcEMwCs</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-23</v>
@@ -3494,10 +3494,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>2:27</v>
+        <v>3:47</v>
       </c>
       <c r="H82" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Christina Aguilera</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer) - Lauren Spencer Smith</v>
+        <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower) - Christina Aguilera</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Maggie Lindemann - fate</v>
+        <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025)</v>
       </c>
       <c r="B83" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=xZdWEmnRK4g</v>
+        <v>https://www.youtube.com/watch?v=tYpOHbXFnm0</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-23</v>
@@ -3532,10 +3532,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>2:12</v>
+        <v>3:58</v>
       </c>
       <c r="H83" t="str">
-        <v>Maggie Lindemann</v>
+        <v>RAYE</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Maggie Lindemann - fate - Maggie Lindemann</v>
+        <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025) - RAYE</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023)</v>
+        <v>Dasha - Here For The Party (Official Audio)</v>
       </c>
       <c r="B84" t="str">
-        <v>3 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=wo9yPPCh75Q</v>
+        <v>https://www.youtube.com/watch?v=rSO9oYUnO2k</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-23</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>3 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>4:44</v>
+        <v>3:30</v>
       </c>
       <c r="H84" t="str">
-        <v>Cliff Richard</v>
+        <v>Dasha</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023) - Cliff Richard</v>
+        <v>Dasha - Here For The Party (Official Audio) - Dasha</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025</v>
+        <v>Lady Gaga in Harlequin Live: One Night Only</v>
       </c>
       <c r="B85" t="str">
-        <v>3 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=ND6maRwmzHk</v>
+        <v>https://www.youtube.com/watch?v=c231tCsQalU</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-23</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>3 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>1:00:09</v>
+        <v>51:49</v>
       </c>
       <c r="H85" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Lady Gaga and YouTube</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025 - Purple Disco Machine</v>
+        <v>Lady Gaga in Harlequin Live: One Night Only - Lady Gaga and YouTube</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>RAYE - Black Mascara. (Live at The Royal Albert Hall)</v>
+        <v>Sabrina Carpenter - Such A Funny Way (Official Lyric Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>3 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=9jMMOYr-VhE</v>
+        <v>https://www.youtube.com/watch?v=oaJKUCgSSkc</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-23</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>3 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>4:15</v>
+        <v>3:53</v>
       </c>
       <c r="H86" t="str">
-        <v>RAYE</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>RAYE - Black Mascara. (Live at The Royal Albert Hall) - RAYE</v>
+        <v>Sabrina Carpenter - Such A Funny Way (Official Lyric Video) - Sabrina Carpenter</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Madison Cunningham - My Full Name (Garden Session)</v>
+        <v>Megan Moroney - Beautiful Things (Official Fan Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>3 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=o2F-QmqdNtI</v>
+        <v>https://www.youtube.com/watch?v=0Gxu80LxI0w</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-23</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>3 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>4:07</v>
+        <v>3:56</v>
       </c>
       <c r="H87" t="str">
-        <v>Madison Cunningham</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Madison Cunningham - My Full Name (Garden Session) - Madison Cunningham</v>
+        <v>Megan Moroney - Beautiful Things (Official Fan Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions)</v>
+        <v>Jason Derulo - Miracle</v>
       </c>
       <c r="B88" t="str">
-        <v>3 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=5-6cEVLqE90</v>
+        <v>https://www.youtube.com/watch?v=7sjshHJwkOE</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-23</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>3 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:10</v>
+        <v>4:16</v>
       </c>
       <c r="H88" t="str">
-        <v>Teddy Swims</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions) - Teddy Swims</v>
+        <v>Jason Derulo - Miracle - Jason Derulo</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower)</v>
+        <v>Sananda Maitreya - Pretty Baby (Live)</v>
       </c>
       <c r="B89" t="str">
-        <v>3 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=ivPSbcEMwCs</v>
+        <v>https://www.youtube.com/watch?v=yv1c5G5HZt8</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-23</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>3 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:47</v>
+        <v>3:29</v>
       </c>
       <c r="H89" t="str">
-        <v>Christina Aguilera</v>
+        <v>Sananda Maitreya</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower) - Christina Aguilera</v>
+        <v>Sananda Maitreya - Pretty Baby (Live) - Sananda Maitreya</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025)</v>
+        <v>Faded - 10th Anniversary (Performance Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>3 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=tYpOHbXFnm0</v>
+        <v>https://www.youtube.com/watch?v=EXVg23U3NRw</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-23</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>3 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:58</v>
+        <v>3:25</v>
       </c>
       <c r="H90" t="str">
-        <v>RAYE</v>
+        <v>Alan Walker and 2 more</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025) - RAYE</v>
+        <v>Faded - 10th Anniversary (Performance Video) - Alan Walker and 2 more</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Dasha - Here For The Party (Official Audio)</v>
+        <v>What Are You Doing New Year's Eve (Live from the Eiffel Tower - Official Lyric Video)</v>
       </c>
       <c r="B91" t="str">
         <v>4 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=rSO9oYUnO2k</v>
+        <v>https://www.youtube.com/watch?v=Bpb67fSUzEQ</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-23</v>
@@ -3836,10 +3836,10 @@
         <v>4 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:30</v>
+        <v>4:06</v>
       </c>
       <c r="H91" t="str">
-        <v>Dasha</v>
+        <v>Christina Aguilera</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Dasha - Here For The Party (Official Audio) - Dasha</v>
+        <v>What Are You Doing New Year's Eve (Live from the Eiffel Tower - Official Lyric Video) - Christina Aguilera</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Lady Gaga in Harlequin Live: One Night Only</v>
+        <v>Have Yourself a Merry Little Christmas (Live from the Eiffel Tower - Official Lyric Video)</v>
       </c>
       <c r="B92" t="str">
         <v>4 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=c231tCsQalU</v>
+        <v>https://www.youtube.com/watch?v=gkwb6kZloLA</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-23</v>
@@ -3874,10 +3874,10 @@
         <v>4 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>51:49</v>
+        <v>4:03</v>
       </c>
       <c r="H92" t="str">
-        <v>Lady Gaga and YouTube</v>
+        <v>Christina Aguilera</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Lady Gaga in Harlequin Live: One Night Only - Lady Gaga and YouTube</v>
+        <v>Have Yourself a Merry Little Christmas (Live from the Eiffel Tower - Official Lyric Video) - Christina Aguilera</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Sabrina Carpenter - Such A Funny Way (Official Lyric Video)</v>
+        <v>Chris Rea - Driving Home for Christmas - (Live on National Lottery Stars, 2000)</v>
       </c>
       <c r="B93" t="str">
-        <v>4 weeks ago</v>
+        <v>1 year ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=oaJKUCgSSkc</v>
+        <v>https://www.youtube.com/watch?v=Jckb3dnS5fw</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-23</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>4 weeks ago</v>
+        <v>1 year ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:53</v>
+        <v>4:11</v>
       </c>
       <c r="H93" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>Chris Rea Official</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Sabrina Carpenter - Such A Funny Way (Official Lyric Video) - Sabrina Carpenter</v>
+        <v>Chris Rea - Driving Home for Christmas - (Live on National Lottery Stars, 2000) - Chris Rea Official</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Megan Moroney - Beautiful Things (Official Fan Video)</v>
+        <v>Jessie J - I'll Never Know Why (The Royal Variety Performance 2025)</v>
       </c>
       <c r="B94" t="str">
-        <v>4 weeks ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=0Gxu80LxI0w</v>
+        <v>https://www.youtube.com/watch?v=DPA8v4YS8AY</v>
       </c>
       <c r="D94" t="str">
         <v>2026-01-23</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>4 weeks ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:56</v>
+        <v>4:08</v>
       </c>
       <c r="H94" t="str">
-        <v>Megan Moroney</v>
+        <v>Jessie J</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Megan Moroney - Beautiful Things (Official Fan Video) - Megan Moroney</v>
+        <v>Jessie J - I'll Never Know Why (The Royal Variety Performance 2025) - Jessie J</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Jason Derulo - Miracle</v>
+        <v>Craig David - Walking Away (Official HD Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>4 weeks ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=7sjshHJwkOE</v>
+        <v>https://www.youtube.com/watch?v=v8Yu21pEbqw</v>
       </c>
       <c r="D95" t="str">
         <v>2026-01-23</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>4 weeks ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G95" t="str">
-        <v>4:16</v>
+        <v>3:34</v>
       </c>
       <c r="H95" t="str">
-        <v>Jason Derulo</v>
+        <v>Craig David</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Jason Derulo - Miracle - Jason Derulo</v>
+        <v>Craig David - Walking Away (Official HD Video) - Craig David</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Sananda Maitreya - Pretty Baby (Live)</v>
+        <v>Christina Aguilera, Yseult - Ave Maria (Live from the Eiffel Tower - Official Video)</v>
       </c>
       <c r="B96" t="str">
-        <v>4 weeks ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=yv1c5G5HZt8</v>
+        <v>https://www.youtube.com/watch?v=sq2u9Cfn2B8</v>
       </c>
       <c r="D96" t="str">
         <v>2026-01-23</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>4 weeks ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:29</v>
+        <v>4:37</v>
       </c>
       <c r="H96" t="str">
-        <v>Sananda Maitreya</v>
+        <v>Christina Aguilera</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Sananda Maitreya - Pretty Baby (Live) - Sananda Maitreya</v>
+        <v>Christina Aguilera, Yseult - Ave Maria (Live from the Eiffel Tower - Official Video) - Christina Aguilera</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Faded - 10th Anniversary (Performance Video)</v>
+        <v>Shawn Mendes &amp; Niall Horan - This Town (Live from London)</v>
       </c>
       <c r="B97" t="str">
-        <v>4 weeks ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=EXVg23U3NRw</v>
+        <v>https://www.youtube.com/watch?v=Ea2DSMNIK5w</v>
       </c>
       <c r="D97" t="str">
         <v>2026-01-23</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>4 weeks ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:25</v>
+        <v>6:27</v>
       </c>
       <c r="H97" t="str">
-        <v>Alan Walker and 2 more</v>
+        <v>Shawn Mendes and Niall Horan</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Faded - 10th Anniversary (Performance Video) - Alan Walker and 2 more</v>
+        <v>Shawn Mendes &amp; Niall Horan - This Town (Live from London) - Shawn Mendes and Niall Horan</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>What Are You Doing New Year's Eve (Live from the Eiffel Tower - Official Lyric Video)</v>
+        <v>Shakira - Zoo (From "Zootopia 2")</v>
       </c>
       <c r="B98" t="str">
-        <v>4 weeks ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=Bpb67fSUzEQ</v>
+        <v>https://www.youtube.com/watch?v=kCIf6yaJisQ</v>
       </c>
       <c r="D98" t="str">
         <v>2026-01-23</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>4 weeks ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G98" t="str">
-        <v>4:06</v>
+        <v>2:07</v>
       </c>
       <c r="H98" t="str">
-        <v>Christina Aguilera</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>What Are You Doing New Year's Eve (Live from the Eiffel Tower - Official Lyric Video) - Christina Aguilera</v>
+        <v>Shakira - Zoo (From "Zootopia 2") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Have Yourself a Merry Little Christmas (Live from the Eiffel Tower - Official Lyric Video)</v>
+        <v>Within Temptation - Ice Queen (Acoustic) | 2025 Reimagined Edition</v>
       </c>
       <c r="B99" t="str">
-        <v>4 weeks ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=gkwb6kZloLA</v>
+        <v>https://www.youtube.com/watch?v=f1Iqm16vWDQ</v>
       </c>
       <c r="D99" t="str">
         <v>2026-01-23</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>4 weeks ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G99" t="str">
-        <v>4:03</v>
+        <v>3:40</v>
       </c>
       <c r="H99" t="str">
-        <v>Christina Aguilera</v>
+        <v>Within Temptation</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Have Yourself a Merry Little Christmas (Live from the Eiffel Tower - Official Lyric Video) - Christina Aguilera</v>
+        <v>Within Temptation - Ice Queen (Acoustic) | 2025 Reimagined Edition - Within Temptation</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Chris Rea - Driving Home for Christmas - (Live on National Lottery Stars, 2000)</v>
+        <v>OneRepublic - Give Me Something (for Arknights Endfield) (Official Audio)</v>
       </c>
       <c r="B100" t="str">
-        <v>1 year ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=Jckb3dnS5fw</v>
+        <v>https://www.youtube.com/watch?v=4eqzUNO-ONs</v>
       </c>
       <c r="D100" t="str">
         <v>2026-01-23</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>1 year ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G100" t="str">
-        <v>4:11</v>
+        <v>2:43</v>
       </c>
       <c r="H100" t="str">
-        <v>Chris Rea Official</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Chris Rea - Driving Home for Christmas - (Live on National Lottery Stars, 2000) - Chris Rea Official</v>
+        <v>OneRepublic - Give Me Something (for Arknights Endfield) (Official Audio) - OneRepublic</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Jessie J - I'll Never Know Why (The Royal Variety Performance 2025)</v>
+        <v>Passenger | The Road Is Long</v>
       </c>
       <c r="B101" t="str">
         <v>1 month ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=DPA8v4YS8AY</v>
+        <v>https://www.youtube.com/watch?v=oi4aTOc-IX4</v>
       </c>
       <c r="D101" t="str">
         <v>2026-01-23</v>
@@ -4216,10 +4216,10 @@
         <v>1 month ago</v>
       </c>
       <c r="G101" t="str">
-        <v>4:08</v>
+        <v>4:01</v>
       </c>
       <c r="H101" t="str">
-        <v>Jessie J</v>
+        <v>Passenger</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Jessie J - I'll Never Know Why (The Royal Variety Performance 2025) - Jessie J</v>
+        <v>Passenger | The Road Is Long - Passenger</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Craig David - Walking Away (Official HD Video)</v>
+        <v>Black Honey - Carroll Avenue (Live at RAK)</v>
       </c>
       <c r="B102" t="str">
         <v>1 month ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=v8Yu21pEbqw</v>
+        <v>https://www.youtube.com/watch?v=LPXTE3a6QrM</v>
       </c>
       <c r="D102" t="str">
         <v>2026-01-23</v>
@@ -4254,10 +4254,10 @@
         <v>1 month ago</v>
       </c>
       <c r="G102" t="str">
-        <v>3:34</v>
+        <v>3:19</v>
       </c>
       <c r="H102" t="str">
-        <v>Craig David</v>
+        <v>Black Honey</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4269,18 +4269,18 @@
         <v/>
       </c>
       <c r="L102" t="str">
-        <v>Craig David - Walking Away (Official HD Video) - Craig David</v>
+        <v>Black Honey - Carroll Avenue (Live at RAK) - Black Honey</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Christina Aguilera, Yseult - Ave Maria (Live from the Eiffel Tower - Official Video)</v>
+        <v>Aperture</v>
       </c>
       <c r="B103" t="str">
-        <v>1 month ago</v>
+        <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=sq2u9Cfn2B8</v>
+        <v>https://music.apple.com/us/song/aperture/1870984033</v>
       </c>
       <c r="D103" t="str">
         <v>2026-01-23</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>1 month ago</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G103" t="str">
-        <v>4:37</v>
+        <v>5:11</v>
       </c>
       <c r="H103" t="str">
-        <v>Christina Aguilera</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/aperture/1870984032</v>
       </c>
       <c r="L103" t="str">
-        <v>Christina Aguilera, Yseult - Ave Maria (Live from the Eiffel Tower - Official Video) - Christina Aguilera</v>
+        <v>Aperture - Harry Styles</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Shawn Mendes &amp; Niall Horan - This Town (Live from London)</v>
+        <v>Opening Night</v>
       </c>
       <c r="B104" t="str">
-        <v>1 month ago</v>
+        <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://www.youtube.com/watch?v=Ea2DSMNIK5w</v>
+        <v>https://music.apple.com/us/song/opening-night/1870313501</v>
       </c>
       <c r="D104" t="str">
         <v>2026-01-23</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>1 month ago</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G104" t="str">
-        <v>6:27</v>
+        <v>4:19</v>
       </c>
       <c r="H104" t="str">
-        <v>Shawn Mendes and Niall Horan</v>
+        <v>Arctic Monkeys</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/arctic-monkeys/62820413</v>
       </c>
       <c r="K104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/opening-night/1870313498</v>
       </c>
       <c r="L104" t="str">
-        <v>Shawn Mendes &amp; Niall Horan - This Town (Live from London) - Shawn Mendes and Niall Horan</v>
+        <v>Opening Night - Arctic Monkeys</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Shakira - Zoo (From "Zootopia 2")</v>
+        <v>FLACKITO JODYE (feat. Tokischa)</v>
       </c>
       <c r="B105" t="str">
-        <v>1 month ago</v>
+        <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://www.youtube.com/watch?v=kCIf6yaJisQ</v>
+        <v>https://music.apple.com/us/song/flackito-jodye-feat-tokischa/1870968779</v>
       </c>
       <c r="D105" t="str">
         <v>2026-01-23</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>1 month ago</v>
+        <v>Don't Be Dumb</v>
       </c>
       <c r="G105" t="str">
-        <v>2:07</v>
+        <v>2:20</v>
       </c>
       <c r="H105" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>A$AP Rocky</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/a%24ap-rocky/481488005</v>
       </c>
       <c r="K105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/flackito-jodye-feat-tokischa/1870968596</v>
       </c>
       <c r="L105" t="str">
-        <v>Shakira - Zoo (From "Zootopia 2") - DisneyMusicVEVO</v>
+        <v>FLACKITO JODYE (feat. Tokischa) - A$AP Rocky</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Within Temptation - Ice Queen (Acoustic) | 2025 Reimagined Edition</v>
+        <v>CAMBIARÉ</v>
       </c>
       <c r="B106" t="str">
-        <v>1 month ago</v>
+        <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://www.youtube.com/watch?v=f1Iqm16vWDQ</v>
+        <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
       </c>
       <c r="D106" t="str">
         <v>2026-01-23</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>1 month ago</v>
+        <v>CAMBIARÉ - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>3:40</v>
+        <v>3:01</v>
       </c>
       <c r="H106" t="str">
-        <v>Within Temptation</v>
+        <v>Luis Fonsi</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/luis-fonsi/102834</v>
       </c>
       <c r="K106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/cambiar%C3%A9/1867545265</v>
       </c>
       <c r="L106" t="str">
-        <v>Within Temptation - Ice Queen (Acoustic) | 2025 Reimagined Edition - Within Temptation</v>
+        <v>CAMBIARÉ - Luis Fonsi</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>OneRepublic - Give Me Something (for Arknights Endfield) (Official Audio)</v>
+        <v>Last of a Dying Breed</v>
       </c>
       <c r="B107" t="str">
-        <v>1 month ago</v>
+        <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://www.youtube.com/watch?v=4eqzUNO-ONs</v>
+        <v>https://music.apple.com/us/song/last-of-a-dying-breed/1849706852</v>
       </c>
       <c r="D107" t="str">
         <v>2026-01-23</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>1 month ago</v>
+        <v>Piss In The Wind</v>
       </c>
       <c r="G107" t="str">
-        <v>2:43</v>
+        <v>2:29</v>
       </c>
       <c r="H107" t="str">
-        <v>OneRepublic</v>
+        <v>Joji</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/joji/1258279972</v>
       </c>
       <c r="K107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/last-of-a-dying-breed/1849706656</v>
       </c>
       <c r="L107" t="str">
-        <v>OneRepublic - Give Me Something (for Arknights Endfield) (Official Audio) - OneRepublic</v>
+        <v>Last of a Dying Breed - Joji</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Passenger | The Road Is Long</v>
+        <v>High Key</v>
       </c>
       <c r="B108" t="str">
-        <v>1 month ago</v>
+        <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://www.youtube.com/watch?v=oi4aTOc-IX4</v>
+        <v>https://music.apple.com/us/song/high-key/1847702418</v>
       </c>
       <c r="D108" t="str">
         <v>2026-01-23</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>1 month ago</v>
+        <v>Vacancy</v>
       </c>
       <c r="G108" t="str">
-        <v>4:01</v>
+        <v>2:12</v>
       </c>
       <c r="H108" t="str">
-        <v>Passenger</v>
+        <v>Ari Lennox</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/ari-lennox/448854570</v>
       </c>
       <c r="K108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/high-key/1847702412</v>
       </c>
       <c r="L108" t="str">
-        <v>Passenger | The Road Is Long - Passenger</v>
+        <v>High Key - Ari Lennox</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Black Honey - Carroll Avenue (Live at RAK)</v>
+        <v>scared</v>
       </c>
       <c r="B109" t="str">
-        <v>1 month ago</v>
+        <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://www.youtube.com/watch?v=LPXTE3a6QrM</v>
+        <v>https://music.apple.com/us/song/scared/1862292863</v>
       </c>
       <c r="D109" t="str">
         <v>2026-01-23</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>1 month ago</v>
+        <v>scared - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>3:19</v>
+        <v>4:03</v>
       </c>
       <c r="H109" t="str">
-        <v>Black Honey</v>
+        <v>Fred again..</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/scared/1862292862</v>
       </c>
       <c r="L109" t="str">
-        <v>Black Honey - Carroll Avenue (Live at RAK) - Black Honey</v>
+        <v>scared - Fred again..</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Aperture</v>
+        <v>Death of Love</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/aperture/1870984033</v>
+        <v>https://music.apple.com/us/song/death-of-love/1862353786</v>
       </c>
       <c r="D110" t="str">
         <v>2026-01-23</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Kiss All The Time. Disco, Occasionally.</v>
+        <v>Trying Times</v>
       </c>
       <c r="G110" t="str">
-        <v>5:11</v>
+        <v>3:26</v>
       </c>
       <c r="H110" t="str">
-        <v>Harry Styles</v>
+        <v>James Blake</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/aperture/1870984032</v>
+        <v>https://music.apple.com/us/album/death-of-love/1862353780</v>
       </c>
       <c r="L110" t="str">
-        <v>Aperture - Harry Styles</v>
+        <v>Death of Love - James Blake</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Opening Night</v>
+        <v>Big Ole Fancy House</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/opening-night/1870313501</v>
+        <v>https://music.apple.com/us/song/big-ole-fancy-house/1862624759</v>
       </c>
       <c r="D111" t="str">
         <v>2026-01-23</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>HELP(2)</v>
+        <v>Parker McCollum (The Deluxe Edition)</v>
       </c>
       <c r="G111" t="str">
-        <v>4:19</v>
+        <v>4:03</v>
       </c>
       <c r="H111" t="str">
-        <v>Arctic Monkeys</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/arctic-monkeys/62820413</v>
+        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/opening-night/1870313498</v>
+        <v>https://music.apple.com/us/album/big-ole-fancy-house/1862624506</v>
       </c>
       <c r="L111" t="str">
-        <v>Opening Night - Arctic Monkeys</v>
+        <v>Big Ole Fancy House - Parker McCollum</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>FLACKITO JODYE (feat. Tokischa)</v>
+        <v>Flo Jackson</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/flackito-jodye-feat-tokischa/1870968779</v>
+        <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
       </c>
       <c r="D112" t="str">
         <v>2026-01-23</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Don't Be Dumb</v>
+        <v>Flo Jackson - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>2:20</v>
+        <v>2:23</v>
       </c>
       <c r="H112" t="str">
-        <v>A$AP Rocky</v>
+        <v>Flo Milli</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/a%24ap-rocky/481488005</v>
+        <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/flackito-jodye-feat-tokischa/1870968596</v>
+        <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
       </c>
       <c r="L112" t="str">
-        <v>FLACKITO JODYE (feat. Tokischa) - A$AP Rocky</v>
+        <v>Flo Jackson - Flo Milli</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>CAMBIARÉ</v>
+        <v>Site Unseen (feat. Waxahatchee)</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
+        <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
       </c>
       <c r="D113" t="str">
         <v>2026-01-23</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>CAMBIARÉ - Single</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G113" t="str">
-        <v>3:01</v>
+        <v>2:46</v>
       </c>
       <c r="H113" t="str">
-        <v>Luis Fonsi</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/luis-fonsi/102834</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/cambiar%C3%A9/1867545265</v>
+        <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
       </c>
       <c r="L113" t="str">
-        <v>CAMBIARÉ - Luis Fonsi</v>
+        <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Last of a Dying Breed</v>
+        <v>Puppet Parade</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/last-of-a-dying-breed/1849706852</v>
+        <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
       </c>
       <c r="D114" t="str">
         <v>2026-01-23</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Piss In The Wind</v>
+        <v>Megadeth</v>
       </c>
       <c r="G114" t="str">
-        <v>2:29</v>
+        <v>4:40</v>
       </c>
       <c r="H114" t="str">
-        <v>Joji</v>
+        <v>Megadeth</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/joji/1258279972</v>
+        <v>https://music.apple.com/us/artist/megadeth/488289</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/last-of-a-dying-breed/1849706656</v>
+        <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
       </c>
       <c r="L114" t="str">
-        <v>Last of a Dying Breed - Joji</v>
+        <v>Puppet Parade - Megadeth</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>High Key</v>
+        <v>To Love Somebody</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/high-key/1847702418</v>
+        <v>https://music.apple.com/us/song/to-love-somebody/1859630040</v>
       </c>
       <c r="D115" t="str">
         <v>2026-01-23</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Vacancy</v>
+        <v>Cruel World</v>
       </c>
       <c r="G115" t="str">
-        <v>2:12</v>
+        <v>3:57</v>
       </c>
       <c r="H115" t="str">
-        <v>Ari Lennox</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/ari-lennox/448854570</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/high-key/1847702412</v>
+        <v>https://music.apple.com/us/album/to-love-somebody/1859629846</v>
       </c>
       <c r="L115" t="str">
-        <v>High Key - Ari Lennox</v>
+        <v>To Love Somebody - Holly Humberstone</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>scared</v>
+        <v>Nothing Is Impossible With You</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/scared/1862292863</v>
+        <v>https://music.apple.com/us/song/nothing-is-impossible-with-you/1870691236</v>
       </c>
       <c r="D116" t="str">
         <v>2026-01-23</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>scared - Single</v>
+        <v>Nothing Is Impossible With You - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>4:03</v>
+        <v>4:14</v>
       </c>
       <c r="H116" t="str">
-        <v>Fred again..</v>
+        <v>Cleo Sol</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/cleo-sol/459710289</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/scared/1862292862</v>
+        <v>https://music.apple.com/us/album/nothing-is-impossible-with-you/1870691227</v>
       </c>
       <c r="L116" t="str">
-        <v>scared - Fred again..</v>
+        <v>Nothing Is Impossible With You - Cleo Sol</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Death of Love</v>
+        <v>HYPNOTIZE</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/death-of-love/1862353786</v>
+        <v>https://music.apple.com/us/song/hypnotize/1861009528</v>
       </c>
       <c r="D117" t="str">
         <v>2026-01-23</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Trying Times</v>
+        <v>THE CORE - 核</v>
       </c>
       <c r="G117" t="str">
-        <v>3:26</v>
+        <v>2:50</v>
       </c>
       <c r="H117" t="str">
-        <v>James Blake</v>
+        <v>XG</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/xg/1609409493</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/death-of-love/1862353780</v>
+        <v>https://music.apple.com/us/album/hypnotize/1861009513</v>
       </c>
       <c r="L117" t="str">
-        <v>Death of Love - James Blake</v>
+        <v>HYPNOTIZE - XG</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Big Ole Fancy House</v>
+        <v>Dead End</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/big-ole-fancy-house/1862624759</v>
+        <v>https://music.apple.com/us/song/dead-end/1862845874</v>
       </c>
       <c r="D118" t="str">
         <v>2026-01-23</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Parker McCollum (The Deluxe Edition)</v>
+        <v>Ricochet</v>
       </c>
       <c r="G118" t="str">
-        <v>4:03</v>
+        <v>4:05</v>
       </c>
       <c r="H118" t="str">
-        <v>Parker McCollum</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/big-ole-fancy-house/1862624506</v>
+        <v>https://music.apple.com/us/album/dead-end/1862845733</v>
       </c>
       <c r="L118" t="str">
-        <v>Big Ole Fancy House - Parker McCollum</v>
+        <v>Dead End - Snail Mail</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Flo Jackson</v>
+        <v>Do I Wanna Know?</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
+        <v>https://music.apple.com/us/song/do-i-wanna-know/1870931500</v>
       </c>
       <c r="D119" t="str">
         <v>2026-01-23</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Flo Jackson - Single</v>
+        <v>Do I Wanna Know? - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>2:23</v>
+        <v>3:52</v>
       </c>
       <c r="H119" t="str">
-        <v>Flo Milli</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
+        <v>https://music.apple.com/us/artist/dove-cameron/599822740</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
+        <v>https://music.apple.com/us/album/do-i-wanna-know/1870931327</v>
       </c>
       <c r="L119" t="str">
-        <v>Flo Jackson - Flo Milli</v>
+        <v>Do I Wanna Know? - Dove Cameron</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Site Unseen (feat. Waxahatchee)</v>
+        <v>Una y Otra Vez</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
+        <v>https://music.apple.com/us/song/una-y-otra-vez/1868792926</v>
       </c>
       <c r="D120" t="str">
         <v>2026-01-23</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Creature of Habit</v>
+        <v>K de Karma (Apple Music Edition)</v>
       </c>
       <c r="G120" t="str">
-        <v>2:46</v>
+        <v>3:02</v>
       </c>
       <c r="H120" t="str">
-        <v>Courtney Barnett</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
+        <v>https://music.apple.com/us/album/una-y-otra-vez/1868792704</v>
       </c>
       <c r="L120" t="str">
-        <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
+        <v>Una y Otra Vez - Kenia Os</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Puppet Parade</v>
+        <v>BAD</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
+        <v>https://music.apple.com/us/song/bad/1869095326</v>
       </c>
       <c r="D121" t="str">
         <v>2026-01-23</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Megadeth</v>
+        <v>BAD - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>4:40</v>
+        <v>2:15</v>
       </c>
       <c r="H121" t="str">
-        <v>Megadeth</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/megadeth/488289</v>
+        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
+        <v>https://music.apple.com/us/album/bad/1869095325</v>
       </c>
       <c r="L121" t="str">
-        <v>Puppet Parade - Megadeth</v>
+        <v>BAD - Chelsea Cutler</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>To Love Somebody</v>
+        <v>Losing You</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/to-love-somebody/1859630040</v>
+        <v>https://music.apple.com/us/song/losing-you/1863525495</v>
       </c>
       <c r="D122" t="str">
         <v>2026-01-23</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Cruel World</v>
+        <v>F.I.G</v>
       </c>
       <c r="G122" t="str">
-        <v>3:57</v>
+        <v>2:22</v>
       </c>
       <c r="H122" t="str">
-        <v>Holly Humberstone</v>
+        <v>Naomi Scott</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/to-love-somebody/1859629846</v>
+        <v>https://music.apple.com/us/album/losing-you/1863525485</v>
       </c>
       <c r="L122" t="str">
-        <v>To Love Somebody - Holly Humberstone</v>
+        <v>Losing You - Naomi Scott</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Nothing Is Impossible With You</v>
+        <v>Me Voy A La C******a</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/nothing-is-impossible-with-you/1870691236</v>
+        <v>https://music.apple.com/us/song/me-voy-a-la-c-a/1867850749</v>
       </c>
       <c r="D123" t="str">
         <v>2026-01-23</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Nothing Is Impossible With You - Single</v>
+        <v>Infinito</v>
       </c>
       <c r="G123" t="str">
-        <v>4:14</v>
+        <v>2:14</v>
       </c>
       <c r="H123" t="str">
-        <v>Cleo Sol</v>
+        <v>Yandel</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/cleo-sol/459710289</v>
+        <v>https://music.apple.com/us/artist/yandel/72929426</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/nothing-is-impossible-with-you/1870691227</v>
+        <v>https://music.apple.com/us/album/me-voy-a-la-c-a/1867850739</v>
       </c>
       <c r="L123" t="str">
-        <v>Nothing Is Impossible With You - Cleo Sol</v>
+        <v>Me Voy A La C******a - Yandel</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>HYPNOTIZE</v>
+        <v>Sexy For Me</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/hypnotize/1861009528</v>
+        <v>https://music.apple.com/us/song/sexy-for-me/1867897421</v>
       </c>
       <c r="D124" t="str">
         <v>2026-01-23</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>THE CORE - 核</v>
+        <v>The Last Dance (Part 1)</v>
       </c>
       <c r="G124" t="str">
-        <v>2:50</v>
+        <v>2:08</v>
       </c>
       <c r="H124" t="str">
-        <v>XG</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/xg/1609409493</v>
+        <v>https://music.apple.com/us/artist/jason-derulo/259118085</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/hypnotize/1861009513</v>
+        <v>https://music.apple.com/us/album/sexy-for-me/1867897420</v>
       </c>
       <c r="L124" t="str">
-        <v>HYPNOTIZE - XG</v>
+        <v>Sexy For Me - Jason Derulo</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Dead End</v>
+        <v>Turbulence</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/dead-end/1862845874</v>
+        <v>https://music.apple.com/us/song/turbulence/1867908449</v>
       </c>
       <c r="D125" t="str">
         <v>2026-01-23</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Ricochet</v>
+        <v>REAL, Vol. 1 - EP</v>
       </c>
       <c r="G125" t="str">
-        <v>4:05</v>
+        <v>2:25</v>
       </c>
       <c r="H125" t="str">
-        <v>Snail Mail</v>
+        <v>Wizkid</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/dead-end/1862845733</v>
+        <v>https://music.apple.com/us/album/turbulence/1867908237</v>
       </c>
       <c r="L125" t="str">
-        <v>Dead End - Snail Mail</v>
+        <v>Turbulence - Wizkid</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Do I Wanna Know?</v>
+        <v>I’m Good (From The Movie “GOAT”)</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/do-i-wanna-know/1870931500</v>
+        <v>https://music.apple.com/us/song/im-good-from-the-movie-goat/1870623298</v>
       </c>
       <c r="D126" t="str">
         <v>2026-01-23</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Do I Wanna Know? - Single</v>
+        <v>GOAT (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G126" t="str">
-        <v>3:52</v>
+        <v>2:59</v>
       </c>
       <c r="H126" t="str">
-        <v>Dove Cameron</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/dove-cameron/599822740</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/do-i-wanna-know/1870931327</v>
+        <v>https://music.apple.com/us/album/im-good-from-the-movie-goat/1870623290</v>
       </c>
       <c r="L126" t="str">
-        <v>Do I Wanna Know? - Dove Cameron</v>
+        <v>I’m Good (From The Movie “GOAT”) - Jelly Roll</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Una y Otra Vez</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/una-y-otra-vez/1868792926</v>
+        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
       </c>
       <c r="D127" t="str">
         <v>2026-01-23</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>K de Karma (Apple Music Edition)</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:02</v>
+        <v>3:47</v>
       </c>
       <c r="H127" t="str">
-        <v>Kenia Os</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
+        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/una-y-otra-vez/1868792704</v>
+        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
       </c>
       <c r="L127" t="str">
-        <v>Una y Otra Vez - Kenia Os</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>BAD</v>
+        <v>ESCONDIDAS</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/bad/1869095326</v>
+        <v>https://music.apple.com/us/song/escondidas/1860972187</v>
       </c>
       <c r="D128" t="str">
         <v>2026-01-23</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>BAD - Single</v>
+        <v>SILENCIO HABLA</v>
       </c>
       <c r="G128" t="str">
-        <v>2:15</v>
+        <v>2:53</v>
       </c>
       <c r="H128" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Oscar Ortiz</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
+        <v>https://music.apple.com/us/artist/oscar-ortiz/1680604969</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/bad/1869095325</v>
+        <v>https://music.apple.com/us/album/escondidas/1860972173</v>
       </c>
       <c r="L128" t="str">
-        <v>BAD - Chelsea Cutler</v>
+        <v>ESCONDIDAS - Oscar Ortiz</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Losing You</v>
+        <v>Alabama Beauty Queen</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/losing-you/1863525495</v>
+        <v>https://music.apple.com/us/song/alabama-beauty-queen/1846658485</v>
       </c>
       <c r="D129" t="str">
         <v>2026-01-23</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>F.I.G</v>
+        <v>Act I</v>
       </c>
       <c r="G129" t="str">
-        <v>2:22</v>
+        <v>3:43</v>
       </c>
       <c r="H129" t="str">
-        <v>Naomi Scott</v>
+        <v>Kashus Culpepper</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
+        <v>https://music.apple.com/us/artist/kashus-culpepper/1634883369</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/losing-you/1863525485</v>
+        <v>https://music.apple.com/us/album/alabama-beauty-queen/1846658477</v>
       </c>
       <c r="L129" t="str">
-        <v>Losing You - Naomi Scott</v>
+        <v>Alabama Beauty Queen - Kashus Culpepper</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Me Voy A La C******a</v>
+        <v>Imposter</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/me-voy-a-la-c-a/1867850749</v>
+        <v>https://music.apple.com/us/song/imposter/1842408050</v>
       </c>
       <c r="D130" t="str">
         <v>2026-01-23</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Infinito</v>
+        <v>How Did I Get Here?</v>
       </c>
       <c r="G130" t="str">
-        <v>2:14</v>
+        <v>2:38</v>
       </c>
       <c r="H130" t="str">
-        <v>Yandel</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/yandel/72929426</v>
+        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/me-voy-a-la-c-a/1867850739</v>
+        <v>https://music.apple.com/us/album/imposter/1842408037</v>
       </c>
       <c r="L130" t="str">
-        <v>Me Voy A La C******a - Yandel</v>
+        <v>Imposter - Louis Tomlinson</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Sexy For Me</v>
+        <v>Puddles (Zero 7 Remix)</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/sexy-for-me/1867897421</v>
+        <v>https://music.apple.com/us/song/puddles-zero-7-remix/1869474314</v>
       </c>
       <c r="D131" t="str">
         <v>2026-01-23</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>The Last Dance (Part 1)</v>
+        <v>Puddles (Zero 7 Remix) - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>2:08</v>
+        <v>6:01</v>
       </c>
       <c r="H131" t="str">
-        <v>Jason Derulo</v>
+        <v>Not for Radio</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/jason-derulo/259118085</v>
+        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/sexy-for-me/1867897420</v>
+        <v>https://music.apple.com/us/album/puddles-zero-7-remix/1869474313</v>
       </c>
       <c r="L131" t="str">
-        <v>Sexy For Me - Jason Derulo</v>
+        <v>Puddles (Zero 7 Remix) - Not for Radio</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Turbulence</v>
+        <v>Little Miss (Misdemeanor)</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/turbulence/1867908449</v>
+        <v>https://music.apple.com/us/song/little-miss-misdemeanor/1870996491</v>
       </c>
       <c r="D132" t="str">
         <v>2026-01-23</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>REAL, Vol. 1 - EP</v>
+        <v>Little Miss (Misdemeanor) - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>2:25</v>
+        <v>2:24</v>
       </c>
       <c r="H132" t="str">
-        <v>Wizkid</v>
+        <v>GIRLSET</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
+        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/turbulence/1867908237</v>
+        <v>https://music.apple.com/us/album/little-miss-misdemeanor/1870996490</v>
       </c>
       <c r="L132" t="str">
-        <v>Turbulence - Wizkid</v>
+        <v>Little Miss (Misdemeanor) - GIRLSET</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>I’m Good (From The Movie “GOAT”)</v>
+        <v>I Could Get Used To This</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/im-good-from-the-movie-goat/1870623298</v>
+        <v>https://music.apple.com/us/song/i-could-get-used-to-this/1867222996</v>
       </c>
       <c r="D133" t="str">
         <v>2026-01-23</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>GOAT (Original Motion Picture Soundtrack)</v>
+        <v>I Could Get Used To This - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>2:59</v>
+        <v>3:41</v>
       </c>
       <c r="H133" t="str">
-        <v>Jelly Roll</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/im-good-from-the-movie-goat/1870623290</v>
+        <v>https://music.apple.com/us/album/i-could-get-used-to-this/1867222992</v>
       </c>
       <c r="L133" t="str">
-        <v>I’m Good (From The Movie “GOAT”) - Jelly Roll</v>
+        <v>I Could Get Used To This - Jessie Ware</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
+        <v>LA VILLA</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
+        <v>https://music.apple.com/us/song/la-villa/1847678152</v>
       </c>
       <c r="D134" t="str">
         <v>2026-01-23</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
+        <v>HOPI SENDÉ</v>
       </c>
       <c r="G134" t="str">
-        <v>3:47</v>
+        <v>3:12</v>
       </c>
       <c r="H134" t="str">
-        <v>Dolly Parton</v>
+        <v>Ryan Castro</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
+        <v>https://music.apple.com/us/artist/ryan-castro/1263552447</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
+        <v>https://music.apple.com/us/album/la-villa/1847678143</v>
       </c>
       <c r="L134" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
+        <v>LA VILLA - Ryan Castro</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>ESCONDIDAS</v>
+        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700)</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/escondidas/1860972187</v>
+        <v>https://music.apple.com/us/song/lit-effect-feat-bktherula-lazer-dim-700/1868519613</v>
       </c>
       <c r="D135" t="str">
         <v>2026-01-23</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>SILENCIO HABLA</v>
+        <v>Strictly 4 The Scythe</v>
       </c>
       <c r="G135" t="str">
-        <v>2:53</v>
+        <v>3:27</v>
       </c>
       <c r="H135" t="str">
-        <v>Oscar Ortiz</v>
+        <v>Denzel Curry</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/oscar-ortiz/1680604969</v>
+        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/escondidas/1860972173</v>
+        <v>https://music.apple.com/us/album/lit-effect-feat-bktherula-lazer-dim-700/1868519270</v>
       </c>
       <c r="L135" t="str">
-        <v>ESCONDIDAS - Oscar Ortiz</v>
+        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700) - Denzel Curry</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Alabama Beauty Queen</v>
+        <v>Thick One</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/alabama-beauty-queen/1846658485</v>
+        <v>https://music.apple.com/us/song/thick-one/1868515478</v>
       </c>
       <c r="D136" t="str">
         <v>2026-01-23</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Act I</v>
+        <v>Part 3</v>
       </c>
       <c r="G136" t="str">
-        <v>3:43</v>
+        <v>2:49</v>
       </c>
       <c r="H136" t="str">
-        <v>Kashus Culpepper</v>
+        <v>42 Dugg</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/kashus-culpepper/1634883369</v>
+        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/alabama-beauty-queen/1846658477</v>
+        <v>https://music.apple.com/us/album/thick-one/1868515223</v>
       </c>
       <c r="L136" t="str">
-        <v>Alabama Beauty Queen - Kashus Culpepper</v>
+        <v>Thick One - 42 Dugg</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Imposter</v>
+        <v>How Much Did You Get For Your Soul</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/imposter/1842408050</v>
+        <v>https://music.apple.com/us/song/how-much-did-you-get-for-your-soul/1843195678</v>
       </c>
       <c r="D137" t="str">
         <v>2026-01-23</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>How Did I Get Here?</v>
+        <v>World's Gone Wrong</v>
       </c>
       <c r="G137" t="str">
-        <v>2:38</v>
+        <v>3:59</v>
       </c>
       <c r="H137" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Lucinda Williams</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
+        <v>https://music.apple.com/us/artist/lucinda-williams/267658</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/imposter/1842408037</v>
+        <v>https://music.apple.com/us/album/how-much-did-you-get-for-your-soul/1843195660</v>
       </c>
       <c r="L137" t="str">
-        <v>Imposter - Louis Tomlinson</v>
+        <v>How Much Did You Get For Your Soul - Lucinda Williams</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Puddles (Zero 7 Remix)</v>
+        <v>THUM</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/puddles-zero-7-remix/1869474314</v>
+        <v>https://music.apple.com/us/song/thum/1863009362</v>
       </c>
       <c r="D138" t="str">
         <v>2026-01-23</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Puddles (Zero 7 Remix) - Single</v>
+        <v>THUM - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>6:01</v>
+        <v>2:11</v>
       </c>
       <c r="H138" t="str">
-        <v>Not for Radio</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/puddles-zero-7-remix/1869474313</v>
+        <v>https://music.apple.com/us/album/thum/1863009357</v>
       </c>
       <c r="L138" t="str">
-        <v>Puddles (Zero 7 Remix) - Not for Radio</v>
+        <v>THUM - Violet Grohl</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Little Miss (Misdemeanor)</v>
+        <v>(I'm a) Rock "N" Roller</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/little-miss-misdemeanor/1870996491</v>
+        <v>https://music.apple.com/us/song/im-a-rock-n-roller/1839888014</v>
       </c>
       <c r="D139" t="str">
         <v>2026-01-23</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Little Miss (Misdemeanor) - Single</v>
+        <v>The Great Satan</v>
       </c>
       <c r="G139" t="str">
-        <v>2:24</v>
+        <v>3:32</v>
       </c>
       <c r="H139" t="str">
-        <v>GIRLSET</v>
+        <v>Rob Zombie</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
+        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/little-miss-misdemeanor/1870996490</v>
+        <v>https://music.apple.com/us/album/im-a-rock-n-roller/1839887790</v>
       </c>
       <c r="L139" t="str">
-        <v>Little Miss (Misdemeanor) - GIRLSET</v>
+        <v>(I'm a) Rock "N" Roller - Rob Zombie</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>I Could Get Used To This</v>
+        <v>Excuses For Love</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/i-could-get-used-to-this/1867222996</v>
+        <v>https://music.apple.com/us/song/excuses-for-love/1856034295</v>
       </c>
       <c r="D140" t="str">
         <v>2026-01-23</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>I Could Get Used To This - Single</v>
+        <v>Hyperlove</v>
       </c>
       <c r="G140" t="str">
-        <v>3:41</v>
+        <v>3:04</v>
       </c>
       <c r="H140" t="str">
-        <v>Jessie Ware</v>
+        <v>MIKA</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/mika/184932871</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/i-could-get-used-to-this/1867222992</v>
+        <v>https://music.apple.com/us/album/excuses-for-love/1856033810</v>
       </c>
       <c r="L140" t="str">
-        <v>I Could Get Used To This - Jessie Ware</v>
+        <v>Excuses For Love - MIKA</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>LA VILLA</v>
+        <v>3 Tears</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/la-villa/1847678152</v>
+        <v>https://music.apple.com/us/song/3-tears/1861504548</v>
       </c>
       <c r="D141" t="str">
         <v>2026-01-23</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>HOPI SENDÉ</v>
+        <v>3 Tears - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:12</v>
+        <v>2:50</v>
       </c>
       <c r="H141" t="str">
-        <v>Ryan Castro</v>
+        <v>Mergui</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/ryan-castro/1263552447</v>
+        <v>https://music.apple.com/us/artist/mergui/1423596903</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/la-villa/1847678143</v>
+        <v>https://music.apple.com/us/album/3-tears/1861504545</v>
       </c>
       <c r="L141" t="str">
-        <v>LA VILLA - Ryan Castro</v>
+        <v>3 Tears - Mergui</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700)</v>
+        <v>Church Girl</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/lit-effect-feat-bktherula-lazer-dim-700/1868519613</v>
+        <v>https://music.apple.com/us/song/church-girl/1862008542</v>
       </c>
       <c r="D142" t="str">
         <v>2026-01-23</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Strictly 4 The Scythe</v>
+        <v>Church Girl - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>3:27</v>
+        <v>3:19</v>
       </c>
       <c r="H142" t="str">
-        <v>Denzel Curry</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/lit-effect-feat-bktherula-lazer-dim-700/1868519270</v>
+        <v>https://music.apple.com/us/album/church-girl/1862008535</v>
       </c>
       <c r="L142" t="str">
-        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700) - Denzel Curry</v>
+        <v>Church Girl - Carly Pearce</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Thick One</v>
+        <v>Funeral</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/thick-one/1868515478</v>
+        <v>https://music.apple.com/us/song/funeral/1867616928</v>
       </c>
       <c r="D143" t="str">
         <v>2026-01-23</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Part 3</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G143" t="str">
-        <v>2:49</v>
+        <v>4:03</v>
       </c>
       <c r="H143" t="str">
-        <v>42 Dugg</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/thick-one/1868515223</v>
+        <v>https://music.apple.com/us/album/funeral/1867616617</v>
       </c>
       <c r="L143" t="str">
-        <v>Thick One - 42 Dugg</v>
+        <v>Funeral - Dermot Kennedy</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>How Much Did You Get For Your Soul</v>
+        <v>Say Yes</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/how-much-did-you-get-for-your-soul/1843195678</v>
+        <v>https://music.apple.com/us/song/say-yes/1861995090</v>
       </c>
       <c r="D144" t="str">
         <v>2026-01-23</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>World's Gone Wrong</v>
+        <v>Say Yes - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>3:59</v>
+        <v>2:50</v>
       </c>
       <c r="H144" t="str">
-        <v>Lucinda Williams</v>
+        <v>Marques Anthony</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/lucinda-williams/267658</v>
+        <v>https://music.apple.com/us/artist/marques-anthony/321321231</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/how-much-did-you-get-for-your-soul/1843195660</v>
+        <v>https://music.apple.com/us/album/say-yes/1861995089</v>
       </c>
       <c r="L144" t="str">
-        <v>How Much Did You Get For Your Soul - Lucinda Williams</v>
+        <v>Say Yes - Marques Anthony</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>THUM</v>
+        <v>LOVE ME (feat. Stevie Wonder)</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/thum/1863009362</v>
+        <v>https://music.apple.com/us/song/love-me-feat-stevie-wonder/1867640879</v>
       </c>
       <c r="D145" t="str">
         <v>2026-01-23</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>THUM - Single</v>
+        <v>CAMPILATION</v>
       </c>
       <c r="G145" t="str">
-        <v>2:11</v>
+        <v>3:10</v>
       </c>
       <c r="H145" t="str">
-        <v>Violet Grohl</v>
+        <v>Camper</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/camper/1514886616</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/thum/1863009357</v>
+        <v>https://music.apple.com/us/album/love-me-feat-stevie-wonder/1867640873</v>
       </c>
       <c r="L145" t="str">
-        <v>THUM - Violet Grohl</v>
+        <v>LOVE ME (feat. Stevie Wonder) - Camper</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>(I'm a) Rock "N" Roller</v>
+        <v>UP TO MY NECK IN U</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/im-a-rock-n-roller/1839888014</v>
+        <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
       </c>
       <c r="D146" t="str">
         <v>2026-01-23</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>The Great Satan</v>
+        <v>UP TO MY NECK IN U - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:32</v>
+        <v>2:17</v>
       </c>
       <c r="H146" t="str">
-        <v>Rob Zombie</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/im-a-rock-n-roller/1839887790</v>
+        <v>https://music.apple.com/us/album/up-to-my-neck-in-u/1862550671</v>
       </c>
       <c r="L146" t="str">
-        <v>(I'm a) Rock "N" Roller - Rob Zombie</v>
+        <v>UP TO MY NECK IN U - Ledbyher</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Excuses For Love</v>
+        <v>Wallflower</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/excuses-for-love/1856034295</v>
+        <v>https://music.apple.com/us/song/wallflower/1862737077</v>
       </c>
       <c r="D147" t="str">
         <v>2026-01-23</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Hyperlove</v>
+        <v>Wallflower - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:04</v>
+        <v>3:25</v>
       </c>
       <c r="H147" t="str">
-        <v>MIKA</v>
+        <v>Sikarus</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/mika/184932871</v>
+        <v>https://music.apple.com/us/artist/sikarus/1046558781</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/excuses-for-love/1856033810</v>
+        <v>https://music.apple.com/us/album/wallflower/1862737074</v>
       </c>
       <c r="L147" t="str">
-        <v>Excuses For Love - MIKA</v>
+        <v>Wallflower - Sikarus</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>3 Tears</v>
+        <v>You Phase</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/3-tears/1861504548</v>
+        <v>https://music.apple.com/us/song/you-phase/1868861897</v>
       </c>
       <c r="D148" t="str">
         <v>2026-01-23</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>3 Tears - Single</v>
+        <v>You Phase - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>2:50</v>
+        <v>2:51</v>
       </c>
       <c r="H148" t="str">
-        <v>Mergui</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/mergui/1423596903</v>
+        <v>https://music.apple.com/us/artist/mitchell-tenpenny/430369368</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/3-tears/1861504545</v>
+        <v>https://music.apple.com/us/album/you-phase/1868861895</v>
       </c>
       <c r="L148" t="str">
-        <v>3 Tears - Mergui</v>
+        <v>You Phase - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Church Girl</v>
+        <v>Miss Independent</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/church-girl/1862008542</v>
+        <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
       </c>
       <c r="D149" t="str">
         <v>2026-01-23</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Church Girl - Single</v>
+        <v>Miss Independent - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:19</v>
+        <v>2:40</v>
       </c>
       <c r="H149" t="str">
-        <v>Carly Pearce</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/church-girl/1862008535</v>
+        <v>https://music.apple.com/us/album/miss-independent/1870612555</v>
       </c>
       <c r="L149" t="str">
-        <v>Church Girl - Carly Pearce</v>
+        <v>Miss Independent - 1Ski OG</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Funeral</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown)</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/funeral/1867616928</v>
+        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown/1870678482</v>
       </c>
       <c r="D150" t="str">
         <v>2026-01-23</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>The Weight of the Woods</v>
+        <v>SO BE IT</v>
       </c>
       <c r="G150" t="str">
-        <v>4:03</v>
+        <v>5:47</v>
       </c>
       <c r="H150" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Elevation Worship</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/funeral/1867616617</v>
+        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown/1870678481</v>
       </c>
       <c r="L150" t="str">
-        <v>Funeral - Dermot Kennedy</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) - Elevation Worship</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Say Yes</v>
+        <v>go again</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/say-yes/1861995090</v>
+        <v>https://music.apple.com/us/song/go-again/1868987466</v>
       </c>
       <c r="D151" t="str">
         <v>2026-01-23</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Say Yes - Single</v>
+        <v>go again - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>2:50</v>
+        <v>2:07</v>
       </c>
       <c r="H151" t="str">
-        <v>Marques Anthony</v>
+        <v>NateTaylorr</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/marques-anthony/321321231</v>
+        <v>https://music.apple.com/us/artist/natetaylorr/1243682934</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/say-yes/1861995089</v>
+        <v>https://music.apple.com/us/album/go-again/1868987193</v>
       </c>
       <c r="L151" t="str">
-        <v>Say Yes - Marques Anthony</v>
+        <v>go again - NateTaylorr</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>LOVE ME (feat. Stevie Wonder)</v>
+        <v>Autopilot</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/love-me-feat-stevie-wonder/1867640879</v>
+        <v>https://music.apple.com/us/song/autopilot/1863072399</v>
       </c>
       <c r="D152" t="str">
         <v>2026-01-23</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>CAMPILATION</v>
+        <v>Autopilot</v>
       </c>
       <c r="G152" t="str">
-        <v>3:10</v>
+        <v>2:46</v>
       </c>
       <c r="H152" t="str">
-        <v>Camper</v>
+        <v>ALEXSUCKS</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/camper/1514886616</v>
+        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/love-me-feat-stevie-wonder/1867640873</v>
+        <v>https://music.apple.com/us/album/autopilot/1863072393</v>
       </c>
       <c r="L152" t="str">
-        <v>LOVE ME (feat. Stevie Wonder) - Camper</v>
+        <v>Autopilot - ALEXSUCKS</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>UP TO MY NECK IN U</v>
+        <v>Portrait of My Heart (feat. Brendan Yates)</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
+        <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
       </c>
       <c r="D153" t="str">
         <v>2026-01-23</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>UP TO MY NECK IN U - Single</v>
+        <v>Portrait of My Heart - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>2:17</v>
+        <v>3:04</v>
       </c>
       <c r="H153" t="str">
-        <v>Ledbyher</v>
+        <v>SPELLLING</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
+        <v>https://music.apple.com/us/artist/spellling/1281213673</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/up-to-my-neck-in-u/1862550671</v>
+        <v>https://music.apple.com/us/album/portrait-of-my-heart-feat-brendan-yates/1862282167</v>
       </c>
       <c r="L153" t="str">
-        <v>UP TO MY NECK IN U - Ledbyher</v>
+        <v>Portrait of My Heart (feat. Brendan Yates) - SPELLLING</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Wallflower</v>
+        <v>In Violet</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/wallflower/1862737077</v>
+        <v>https://music.apple.com/us/song/in-violet/1839471290</v>
       </c>
       <c r="D154" t="str">
         <v>2026-01-23</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Wallflower - Single</v>
+        <v>Death in the Business of Whaling</v>
       </c>
       <c r="G154" t="str">
-        <v>3:25</v>
+        <v>4:09</v>
       </c>
       <c r="H154" t="str">
-        <v>Sikarus</v>
+        <v>Searows</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/sikarus/1046558781</v>
+        <v>https://music.apple.com/us/artist/searows/1607240507</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/wallflower/1862737074</v>
+        <v>https://music.apple.com/us/album/in-violet/1839470844</v>
       </c>
       <c r="L154" t="str">
-        <v>Wallflower - Sikarus</v>
+        <v>In Violet - Searows</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>You Phase</v>
+        <v>Baby Run</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/you-phase/1868861897</v>
+        <v>https://music.apple.com/us/song/baby-run/1857658819</v>
       </c>
       <c r="D155" t="str">
         <v>2026-01-23</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>You Phase - Single</v>
+        <v>Baby Run - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>2:51</v>
+        <v>4:47</v>
       </c>
       <c r="H155" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Jimi Jules</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/mitchell-tenpenny/430369368</v>
+        <v>https://music.apple.com/us/artist/jimi-jules/586933009</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/you-phase/1868861895</v>
+        <v>https://music.apple.com/us/album/baby-run/1857658816</v>
       </c>
       <c r="L155" t="str">
-        <v>You Phase - Mitchell Tenpenny</v>
+        <v>Baby Run - Jimi Jules</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Miss Independent</v>
+        <v>What If We Don't</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
+        <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
       </c>
       <c r="D156" t="str">
         <v>2026-01-23</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Miss Independent - Single</v>
+        <v>What If We Don't - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>2:40</v>
+        <v>3:06</v>
       </c>
       <c r="H156" t="str">
-        <v>1Ski OG</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/miss-independent/1870612555</v>
+        <v>https://music.apple.com/us/album/what-if-we-dont/1862668776</v>
       </c>
       <c r="L156" t="str">
-        <v>Miss Independent - 1Ski OG</v>
+        <v>What If We Don't - Ashley McBryde</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown)</v>
+        <v>Hagamos Que</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown/1870678482</v>
+        <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
       </c>
       <c r="D157" t="str">
         <v>2026-01-23</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>SO BE IT</v>
+        <v>Hagamos Que - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>5:47</v>
+        <v>2:58</v>
       </c>
       <c r="H157" t="str">
-        <v>Elevation Worship</v>
+        <v>Juanes</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
+        <v>https://music.apple.com/us/artist/juanes/103856</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown/1870678481</v>
+        <v>https://music.apple.com/us/album/hagamos-que/1861956611</v>
       </c>
       <c r="L157" t="str">
-        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) - Elevation Worship</v>
+        <v>Hagamos Que - Juanes</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>go again</v>
+        <v>World Change Me</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/go-again/1868987466</v>
+        <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
       </c>
       <c r="D158" t="str">
         <v>2026-01-23</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>go again - Single</v>
+        <v>World Change Me - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>2:07</v>
+        <v>3:03</v>
       </c>
       <c r="H158" t="str">
-        <v>NateTaylorr</v>
+        <v>Max McNown</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/natetaylorr/1243682934</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/go-again/1868987193</v>
+        <v>https://music.apple.com/us/album/world-change-me/1860974598</v>
       </c>
       <c r="L158" t="str">
-        <v>go again - NateTaylorr</v>
+        <v>World Change Me - Max McNown</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Autopilot</v>
+        <v>Exclusive</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/autopilot/1863072399</v>
+        <v>https://music.apple.com/us/song/exclusive/1851537672</v>
       </c>
       <c r="D159" t="str">
         <v>2026-01-23</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Autopilot</v>
+        <v>Exclusive - EP</v>
       </c>
       <c r="G159" t="str">
-        <v>2:46</v>
+        <v>3:20</v>
       </c>
       <c r="H159" t="str">
-        <v>ALEXSUCKS</v>
+        <v>Hudson Westbrook</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
+        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/autopilot/1863072393</v>
+        <v>https://music.apple.com/us/album/exclusive/1851537671</v>
       </c>
       <c r="L159" t="str">
-        <v>Autopilot - ALEXSUCKS</v>
+        <v>Exclusive - Hudson Westbrook</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Portrait of My Heart (feat. Brendan Yates)</v>
+        <v>Say Less</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
+        <v>https://music.apple.com/us/song/say-less/1867910122</v>
       </c>
       <c r="D160" t="str">
         <v>2026-01-23</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Portrait of My Heart - Single</v>
+        <v>Say Less - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:04</v>
+        <v>2:18</v>
       </c>
       <c r="H160" t="str">
-        <v>SPELLLING</v>
+        <v>JYT</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/spellling/1281213673</v>
+        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/portrait-of-my-heart-feat-brendan-yates/1862282167</v>
+        <v>https://music.apple.com/us/album/say-less/1867910115</v>
       </c>
       <c r="L160" t="str">
-        <v>Portrait of My Heart (feat. Brendan Yates) - SPELLLING</v>
+        <v>Say Less - JYT</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>In Violet</v>
+        <v>Angels Cry</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/in-violet/1839471290</v>
+        <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
       </c>
       <c r="D161" t="str">
         <v>2026-01-23</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Death in the Business of Whaling</v>
+        <v>X's for Eyes (Deluxe)</v>
       </c>
       <c r="G161" t="str">
-        <v>4:09</v>
+        <v>3:52</v>
       </c>
       <c r="H161" t="str">
-        <v>Searows</v>
+        <v>The Red Jumpsuit Apparatus</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/searows/1607240507</v>
+        <v>https://music.apple.com/us/artist/the-red-jumpsuit-apparatus/130037074</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/in-violet/1839470844</v>
+        <v>https://music.apple.com/us/album/angels-cry/1862320872</v>
       </c>
       <c r="L161" t="str">
-        <v>In Violet - Searows</v>
+        <v>Angels Cry - The Red Jumpsuit Apparatus</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Baby Run</v>
+        <v>Over You</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/baby-run/1857658819</v>
+        <v>https://music.apple.com/us/song/over-you/1846189473</v>
       </c>
       <c r="D162" t="str">
         <v>2026-01-23</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Baby Run - Single</v>
+        <v>A Love For Strangers</v>
       </c>
       <c r="G162" t="str">
-        <v>4:47</v>
+        <v>4:44</v>
       </c>
       <c r="H162" t="str">
-        <v>Jimi Jules</v>
+        <v>Chet Faker</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/jimi-jules/586933009</v>
+        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/baby-run/1857658816</v>
+        <v>https://music.apple.com/us/album/over-you/1846189472</v>
       </c>
       <c r="L162" t="str">
-        <v>Baby Run - Jimi Jules</v>
+        <v>Over You - Chet Faker</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>What If We Don't</v>
+        <v>Chala (My Soul Is on a Loop)</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
+        <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
       </c>
       <c r="D163" t="str">
         <v>2026-01-23</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>What If We Don't - Single</v>
+        <v>Chala (My Soul Is on a Loop) - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:06</v>
+        <v>2:42</v>
       </c>
       <c r="H163" t="str">
-        <v>Ashley McBryde</v>
+        <v>Barry Can't Swim</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/barry-cant-swim/1492752064</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/what-if-we-dont/1862668776</v>
+        <v>https://music.apple.com/us/album/chala-my-soul-is-on-a-loop/1857789040</v>
       </c>
       <c r="L163" t="str">
-        <v>What If We Don't - Ashley McBryde</v>
+        <v>Chala (My Soul Is on a Loop) - Barry Can't Swim</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Hagamos Que</v>
+        <v>starlight feat. Madeline Follin</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
+        <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
       </c>
       <c r="D164" t="str">
         <v>2026-01-23</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Hagamos Que - Single</v>
+        <v>starlight feat. Madeline Follin - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>2:58</v>
+        <v>3:06</v>
       </c>
       <c r="H164" t="str">
-        <v>Juanes</v>
+        <v>Disco Lines</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/juanes/103856</v>
+        <v>https://music.apple.com/us/artist/disco-lines/1462793893</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/hagamos-que/1861956611</v>
+        <v>https://music.apple.com/us/album/starlight-feat-madeline-follin/1869330767</v>
       </c>
       <c r="L164" t="str">
-        <v>Hagamos Que - Juanes</v>
+        <v>starlight feat. Madeline Follin - Disco Lines</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>World Change Me</v>
+        <v>Locked In (feat. Trippie Redd)</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
+        <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
       </c>
       <c r="D165" t="str">
         <v>2026-01-23</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>World Change Me - Single</v>
+        <v>Locked In (feat. Trippie Redd) - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:03</v>
+        <v>2:48</v>
       </c>
       <c r="H165" t="str">
-        <v>Max McNown</v>
+        <v>David Guetta</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/david-guetta/5557599</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/world-change-me/1860974598</v>
+        <v>https://music.apple.com/us/album/locked-in-feat-trippie-redd/1869439982</v>
       </c>
       <c r="L165" t="str">
-        <v>World Change Me - Max McNown</v>
+        <v>Locked In (feat. Trippie Redd) - David Guetta</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Exclusive</v>
+        <v>Rejoice</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/exclusive/1851537672</v>
+        <v>https://music.apple.com/us/song/rejoice/1862633596</v>
       </c>
       <c r="D166" t="str">
         <v>2026-01-23</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Exclusive - EP</v>
+        <v>Rejoice - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:20</v>
+        <v>4:20</v>
       </c>
       <c r="H166" t="str">
-        <v>Hudson Westbrook</v>
+        <v>Def Leppard</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
+        <v>https://music.apple.com/us/artist/def-leppard/117554</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/exclusive/1851537671</v>
+        <v>https://music.apple.com/us/album/rejoice/1862633593</v>
       </c>
       <c r="L166" t="str">
-        <v>Exclusive - Hudson Westbrook</v>
+        <v>Rejoice - Def Leppard</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Say Less</v>
+        <v>Slight Werk (feat. Bree Runway) [Club Mix]</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/say-less/1867910122</v>
+        <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
       </c>
       <c r="D167" t="str">
         <v>2026-01-23</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Say Less - Single</v>
+        <v>Slight Werk (Club Mix) [feat. Bree Runway] - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>2:18</v>
+        <v>2:58</v>
       </c>
       <c r="H167" t="str">
-        <v>JYT</v>
+        <v>Honey Dijon</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
+        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/say-less/1867910115</v>
+        <v>https://music.apple.com/us/album/slight-werk-feat-bree-runway-club-mix/1860859551</v>
       </c>
       <c r="L167" t="str">
-        <v>Say Less - JYT</v>
+        <v>Slight Werk (feat. Bree Runway) [Club Mix] - Honey Dijon</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Angels Cry</v>
+        <v>Lucky Day</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
+        <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
       </c>
       <c r="D168" t="str">
         <v>2026-01-23</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>X's for Eyes (Deluxe)</v>
+        <v>Speed Kills</v>
       </c>
       <c r="G168" t="str">
-        <v>3:52</v>
+        <v>3:13</v>
       </c>
       <c r="H168" t="str">
-        <v>The Red Jumpsuit Apparatus</v>
+        <v>Ally Evenson</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/the-red-jumpsuit-apparatus/130037074</v>
+        <v>https://music.apple.com/us/artist/ally-evenson/283908113</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/angels-cry/1862320872</v>
+        <v>https://music.apple.com/us/album/lucky-day/1849264498</v>
       </c>
       <c r="L168" t="str">
-        <v>Angels Cry - The Red Jumpsuit Apparatus</v>
+        <v>Lucky Day - Ally Evenson</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Over You</v>
+        <v>Breathe On It</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/over-you/1846189473</v>
+        <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
       </c>
       <c r="D169" t="str">
         <v>2026-01-23</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>A Love For Strangers</v>
+        <v>Breathe On It - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>4:44</v>
+        <v>4:00</v>
       </c>
       <c r="H169" t="str">
-        <v>Chet Faker</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
+        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/over-you/1846189472</v>
+        <v>https://music.apple.com/us/album/breathe-on-it/1862938798</v>
       </c>
       <c r="L169" t="str">
-        <v>Over You - Chet Faker</v>
+        <v>Breathe On It - Tauren Wells</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Chala (My Soul Is on a Loop)</v>
+        <v>Easy</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
+        <v>https://music.apple.com/us/song/easy/1863456906</v>
       </c>
       <c r="D170" t="str">
         <v>2026-01-23</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Chala (My Soul Is on a Loop) - Single</v>
+        <v>Easy - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:42</v>
+        <v>4:30</v>
       </c>
       <c r="H170" t="str">
-        <v>Barry Can't Swim</v>
+        <v>lydi lynn</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/barry-cant-swim/1492752064</v>
+        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/chala-my-soul-is-on-a-loop/1857789040</v>
+        <v>https://music.apple.com/us/album/easy/1863456903</v>
       </c>
       <c r="L170" t="str">
-        <v>Chala (My Soul Is on a Loop) - Barry Can't Swim</v>
+        <v>Easy - lydi lynn</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>starlight feat. Madeline Follin</v>
+        <v>Break Me In</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
+        <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
       </c>
       <c r="D171" t="str">
         <v>2026-01-23</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>starlight feat. Madeline Follin - Single</v>
+        <v>Break Me In - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>3:06</v>
+        <v>2:52</v>
       </c>
       <c r="H171" t="str">
-        <v>Disco Lines</v>
+        <v>Joyce Wrice</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/disco-lines/1462793893</v>
+        <v>https://music.apple.com/us/artist/joyce-wrice/591991458</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/starlight-feat-madeline-follin/1869330767</v>
+        <v>https://music.apple.com/us/album/break-me-in/1862881766</v>
       </c>
       <c r="L171" t="str">
-        <v>starlight feat. Madeline Follin - Disco Lines</v>
+        <v>Break Me In - Joyce Wrice</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Locked In (feat. Trippie Redd)</v>
+        <v>Long Live Love</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
+        <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
       </c>
       <c r="D172" t="str">
         <v>2026-01-23</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Locked In (feat. Trippie Redd) - Single</v>
+        <v>Long Live Love - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>2:48</v>
+        <v>2:36</v>
       </c>
       <c r="H172" t="str">
-        <v>David Guetta</v>
+        <v>Sugar</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/david-guetta/5557599</v>
+        <v>https://music.apple.com/us/artist/sugar/530175867</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/locked-in-feat-trippie-redd/1869439982</v>
+        <v>https://music.apple.com/us/album/long-live-love/1851251226</v>
       </c>
       <c r="L172" t="str">
-        <v>Locked In (feat. Trippie Redd) - David Guetta</v>
+        <v>Long Live Love - Sugar</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Rejoice</v>
+        <v>Depressed</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/rejoice/1862633596</v>
+        <v>https://music.apple.com/us/song/depressed/1840400522</v>
       </c>
       <c r="D173" t="str">
         <v>2026-01-23</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Rejoice - Single</v>
+        <v>Boycott Heaven</v>
       </c>
       <c r="G173" t="str">
-        <v>4:20</v>
+        <v>3:32</v>
       </c>
       <c r="H173" t="str">
-        <v>Def Leppard</v>
+        <v>The Format</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/def-leppard/117554</v>
+        <v>https://music.apple.com/us/artist/the-format/3064903</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/rejoice/1862633593</v>
+        <v>https://music.apple.com/us/album/depressed/1840399886</v>
       </c>
       <c r="L173" t="str">
-        <v>Rejoice - Def Leppard</v>
+        <v>Depressed - The Format</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Slight Werk (feat. Bree Runway) [Club Mix]</v>
+        <v>Empty Hands</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
+        <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
       </c>
       <c r="D174" t="str">
         <v>2026-01-23</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Slight Werk (Club Mix) [feat. Bree Runway] - Single</v>
+        <v>Empty Hands</v>
       </c>
       <c r="G174" t="str">
-        <v>2:58</v>
+        <v>3:09</v>
       </c>
       <c r="H174" t="str">
-        <v>Honey Dijon</v>
+        <v>Poppy</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
+        <v>https://music.apple.com/us/artist/poppy/1004130511</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/slight-werk-feat-bree-runway-club-mix/1860859551</v>
+        <v>https://music.apple.com/us/album/empty-hands/1852046141</v>
       </c>
       <c r="L174" t="str">
-        <v>Slight Werk (feat. Bree Runway) [Club Mix] - Honey Dijon</v>
+        <v>Empty Hands - Poppy</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Lucky Day</v>
+        <v>The Long Surrender</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
+        <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
       </c>
       <c r="D175" t="str">
         <v>2026-01-23</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Speed Kills</v>
+        <v>The Long Surrender</v>
       </c>
       <c r="G175" t="str">
-        <v>3:13</v>
+        <v>3:45</v>
       </c>
       <c r="H175" t="str">
-        <v>Ally Evenson</v>
+        <v>NEEDTOBREATHE</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/ally-evenson/283908113</v>
+        <v>https://music.apple.com/us/artist/needtobreathe/113247214</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/lucky-day/1849264498</v>
+        <v>https://music.apple.com/us/album/the-long-surrender/1861935699</v>
       </c>
       <c r="L175" t="str">
-        <v>Lucky Day - Ally Evenson</v>
+        <v>The Long Surrender - NEEDTOBREATHE</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Breathe On It</v>
+        <v>Angela</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
+        <v>https://music.apple.com/us/song/angela/1866624257</v>
       </c>
       <c r="D176" t="str">
         <v>2026-01-23</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Breathe On It - Single</v>
+        <v>Angela - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>4:00</v>
+        <v>3:32</v>
       </c>
       <c r="H176" t="str">
-        <v>Tauren Wells</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/breathe-on-it/1862938798</v>
+        <v>https://music.apple.com/us/album/angela/1866624256</v>
       </c>
       <c r="L176" t="str">
-        <v>Breathe On It - Tauren Wells</v>
+        <v>Angela - Hayden Everett</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Easy</v>
+        <v>Disappear</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/easy/1863456906</v>
+        <v>https://music.apple.com/us/song/disappear/1847663553</v>
       </c>
       <c r="D177" t="str">
         <v>2026-01-23</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Easy - Single</v>
+        <v>Greyhound</v>
       </c>
       <c r="G177" t="str">
-        <v>4:30</v>
+        <v>3:31</v>
       </c>
       <c r="H177" t="str">
-        <v>lydi lynn</v>
+        <v>Katie Tupper</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
+        <v>https://music.apple.com/us/artist/katie-tupper/1395542470</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/easy/1863456903</v>
+        <v>https://music.apple.com/us/album/disappear/1847663546</v>
       </c>
       <c r="L177" t="str">
-        <v>Easy - lydi lynn</v>
+        <v>Disappear - Katie Tupper</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Break Me In</v>
+        <v>Catapult</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
+        <v>https://music.apple.com/us/song/catapult/1862951335</v>
       </c>
       <c r="D178" t="str">
         <v>2026-01-23</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Break Me In - Single</v>
+        <v>Catapult - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:52</v>
+        <v>2:57</v>
       </c>
       <c r="H178" t="str">
-        <v>Joyce Wrice</v>
+        <v>Cape Francis</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/joyce-wrice/591991458</v>
+        <v>https://music.apple.com/us/artist/cape-francis/1242523550</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/break-me-in/1862881766</v>
+        <v>https://music.apple.com/us/album/catapult/1862951333</v>
       </c>
       <c r="L178" t="str">
-        <v>Break Me In - Joyce Wrice</v>
+        <v>Catapult - Cape Francis</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Long Live Love</v>
+        <v>Think Twice</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
+        <v>https://music.apple.com/us/song/think-twice/1850698548</v>
       </c>
       <c r="D179" t="str">
         <v>2026-01-23</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Long Live Love - Single</v>
+        <v>Think Twice - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>2:36</v>
+        <v>2:22</v>
       </c>
       <c r="H179" t="str">
-        <v>Sugar</v>
+        <v>Leonie Biney</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/sugar/530175867</v>
+        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/long-live-love/1851251226</v>
+        <v>https://music.apple.com/us/album/think-twice/1850698545</v>
       </c>
       <c r="L179" t="str">
-        <v>Long Live Love - Sugar</v>
+        <v>Think Twice - Leonie Biney</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Depressed</v>
+        <v>LOVESONGS</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/depressed/1840400522</v>
+        <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
       </c>
       <c r="D180" t="str">
         <v>2026-01-23</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Boycott Heaven</v>
+        <v>BEAUTIFUL MADNESS</v>
       </c>
       <c r="G180" t="str">
-        <v>3:32</v>
+        <v>3:33</v>
       </c>
       <c r="H180" t="str">
-        <v>The Format</v>
+        <v>Agnes</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/the-format/3064903</v>
+        <v>https://music.apple.com/us/artist/agnes/42568985</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/depressed/1840399886</v>
+        <v>https://music.apple.com/us/album/lovesongs/1849098275</v>
       </c>
       <c r="L180" t="str">
-        <v>Depressed - The Format</v>
+        <v>LOVESONGS - Agnes</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Empty Hands</v>
+        <v>Down South</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
+        <v>https://music.apple.com/us/song/down-south/1861010793</v>
       </c>
       <c r="D181" t="str">
         <v>2026-01-23</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Empty Hands</v>
+        <v>Down South - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:09</v>
+        <v>2:19</v>
       </c>
       <c r="H181" t="str">
-        <v>Poppy</v>
+        <v>Trap Dickey</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/poppy/1004130511</v>
+        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/empty-hands/1852046141</v>
+        <v>https://music.apple.com/us/album/down-south/1861010788</v>
       </c>
       <c r="L181" t="str">
-        <v>Empty Hands - Poppy</v>
+        <v>Down South - Trap Dickey</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>The Long Surrender</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
+        <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
       </c>
       <c r="D182" t="str">
         <v>2026-01-23</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>The Long Surrender</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:45</v>
+        <v>2:16</v>
       </c>
       <c r="H182" t="str">
-        <v>NEEDTOBREATHE</v>
+        <v>SALIMATA</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/needtobreathe/113247214</v>
+        <v>https://music.apple.com/us/artist/salimata/690253822</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/the-long-surrender/1861935699</v>
+        <v>https://music.apple.com/us/album/jackpot-foil-a-colors-show/1866998655</v>
       </c>
       <c r="L182" t="str">
-        <v>The Long Surrender - NEEDTOBREATHE</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW - SALIMATA</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Angela</v>
+        <v>Love Like This</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/angela/1866624257</v>
+        <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
       </c>
       <c r="D183" t="str">
         <v>2026-01-23</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Angela - Single</v>
+        <v>Love Like This - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:32</v>
+        <v>3:30</v>
       </c>
       <c r="H183" t="str">
-        <v>Hayden Everett</v>
+        <v>Jacob Banks</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/jacob-banks/625014171</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/angela/1866624256</v>
+        <v>https://music.apple.com/us/album/love-like-this/1866999617</v>
       </c>
       <c r="L183" t="str">
-        <v>Angela - Hayden Everett</v>
+        <v>Love Like This - Jacob Banks</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Disappear</v>
+        <v>Plan Plan</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/disappear/1847663553</v>
+        <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
       </c>
       <c r="D184" t="str">
         <v>2026-01-23</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Greyhound</v>
+        <v>La Locura</v>
       </c>
       <c r="G184" t="str">
-        <v>3:31</v>
+        <v>3:10</v>
       </c>
       <c r="H184" t="str">
-        <v>Katie Tupper</v>
+        <v>Funky</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/katie-tupper/1395542470</v>
+        <v>https://music.apple.com/us/artist/funky/80960663</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/disappear/1847663546</v>
+        <v>https://music.apple.com/us/album/plan-plan/1867940087</v>
       </c>
       <c r="L184" t="str">
-        <v>Disappear - Katie Tupper</v>
+        <v>Plan Plan - Funky</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Catapult</v>
+        <v>double edged sword</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/catapult/1862951335</v>
+        <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
       </c>
       <c r="D185" t="str">
         <v>2026-01-23</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Catapult - Single</v>
+        <v>double edged sword - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:57</v>
+        <v>3:28</v>
       </c>
       <c r="H185" t="str">
-        <v>Cape Francis</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/cape-francis/1242523550</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/catapult/1862951333</v>
+        <v>https://music.apple.com/us/album/double-edged-sword/1868829044</v>
       </c>
       <c r="L185" t="str">
-        <v>Catapult - Cape Francis</v>
+        <v>double edged sword - Hailey Picardi</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Think Twice</v>
+        <v>SOMEWHERE IN BETWEEN</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/think-twice/1850698548</v>
+        <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
       </c>
       <c r="D186" t="str">
         <v>2026-01-23</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Think Twice - Single</v>
+        <v>SOMEWHERE IN BETWEEN - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>2:22</v>
+        <v>3:27</v>
       </c>
       <c r="H186" t="str">
-        <v>Leonie Biney</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
+        <v>https://music.apple.com/us/artist/matt-hansen/1442658353</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/think-twice/1850698545</v>
+        <v>https://music.apple.com/us/album/somewhere-in-between/1866969151</v>
       </c>
       <c r="L186" t="str">
-        <v>Think Twice - Leonie Biney</v>
+        <v>SOMEWHERE IN BETWEEN - Matt Hansen</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>LOVESONGS</v>
+        <v>The Decay</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
+        <v>https://music.apple.com/us/song/the-decay/1862836783</v>
       </c>
       <c r="D187" t="str">
         <v>2026-01-23</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>BEAUTIFUL MADNESS</v>
+        <v>What Remains (Midnight Edition)</v>
       </c>
       <c r="G187" t="str">
-        <v>3:33</v>
+        <v>3:20</v>
       </c>
       <c r="H187" t="str">
-        <v>Agnes</v>
+        <v>Pop Evil</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/agnes/42568985</v>
+        <v>https://music.apple.com/us/artist/pop-evil/441597923</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/lovesongs/1849098275</v>
+        <v>https://music.apple.com/us/album/the-decay/1862836507</v>
       </c>
       <c r="L187" t="str">
-        <v>LOVESONGS - Agnes</v>
+        <v>The Decay - Pop Evil</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Down South</v>
+        <v>3111</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/down-south/1861010793</v>
+        <v>https://music.apple.com/us/song/3111/1862225387</v>
       </c>
       <c r="D188" t="str">
         <v>2026-01-23</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Down South - Single</v>
+        <v>Goliath</v>
       </c>
       <c r="G188" t="str">
-        <v>2:19</v>
+        <v>4:08</v>
       </c>
       <c r="H188" t="str">
-        <v>Trap Dickey</v>
+        <v>Exodus</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
+        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/down-south/1861010788</v>
+        <v>https://music.apple.com/us/album/3111/1862225385</v>
       </c>
       <c r="L188" t="str">
-        <v>Down South - Trap Dickey</v>
+        <v>3111 - Exodus</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW</v>
+        <v>Touch My Love And Die</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
+        <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
       </c>
       <c r="D189" t="str">
         <v>2026-01-23</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW - Single</v>
+        <v>Touch My Love And Die - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>2:16</v>
+        <v>2:57</v>
       </c>
       <c r="H189" t="str">
-        <v>SALIMATA</v>
+        <v>Myrkur</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/salimata/690253822</v>
+        <v>https://music.apple.com/us/artist/myrkur/293296859</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/jackpot-foil-a-colors-show/1866998655</v>
+        <v>https://music.apple.com/us/album/touch-my-love-and-die/1867630168</v>
       </c>
       <c r="L189" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW - SALIMATA</v>
+        <v>Touch My Love And Die - Myrkur</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Love Like This</v>
+        <v>Bomb To A Knife Fight</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
+        <v>https://music.apple.com/us/song/bomb-to-a-knife-fight/1861589406</v>
       </c>
       <c r="D190" t="str">
         <v>2026-01-23</v>
@@ -7595,296 +7595,30 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Love Like This - Single</v>
+        <v>Bomb To A Knife Fight - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:30</v>
+        <v>2:41</v>
       </c>
       <c r="H190" t="str">
-        <v>Jacob Banks</v>
+        <v>The Barbarians of California</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/jacob-banks/625014171</v>
+        <v>https://music.apple.com/us/artist/the-barbarians-of-california/1724096474</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/love-like-this/1866999617</v>
+        <v>https://music.apple.com/us/album/bomb-to-a-knife-fight/1861589405</v>
       </c>
       <c r="L190" t="str">
-        <v>Love Like This - Jacob Banks</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="str">
-        <v>Plan Plan</v>
-      </c>
-      <c r="B191" t="str">
-        <v/>
-      </c>
-      <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
-      </c>
-      <c r="D191" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E191" t="str">
-        <v/>
-      </c>
-      <c r="F191" t="str">
-        <v>La Locura</v>
-      </c>
-      <c r="G191" t="str">
-        <v>3:10</v>
-      </c>
-      <c r="H191" t="str">
-        <v>Funky</v>
-      </c>
-      <c r="I191" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/funky/80960663</v>
-      </c>
-      <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/plan-plan/1867940087</v>
-      </c>
-      <c r="L191" t="str">
-        <v>Plan Plan - Funky</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="str">
-        <v>double edged sword</v>
-      </c>
-      <c r="B192" t="str">
-        <v/>
-      </c>
-      <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
-      </c>
-      <c r="D192" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E192" t="str">
-        <v/>
-      </c>
-      <c r="F192" t="str">
-        <v>double edged sword - Single</v>
-      </c>
-      <c r="G192" t="str">
-        <v>3:28</v>
-      </c>
-      <c r="H192" t="str">
-        <v>Hailey Picardi</v>
-      </c>
-      <c r="I192" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
-      </c>
-      <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/double-edged-sword/1868829044</v>
-      </c>
-      <c r="L192" t="str">
-        <v>double edged sword - Hailey Picardi</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="str">
-        <v>SOMEWHERE IN BETWEEN</v>
-      </c>
-      <c r="B193" t="str">
-        <v/>
-      </c>
-      <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
-      </c>
-      <c r="D193" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E193" t="str">
-        <v/>
-      </c>
-      <c r="F193" t="str">
-        <v>SOMEWHERE IN BETWEEN - Single</v>
-      </c>
-      <c r="G193" t="str">
-        <v>3:27</v>
-      </c>
-      <c r="H193" t="str">
-        <v>Matt Hansen</v>
-      </c>
-      <c r="I193" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/matt-hansen/1442658353</v>
-      </c>
-      <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/somewhere-in-between/1866969151</v>
-      </c>
-      <c r="L193" t="str">
-        <v>SOMEWHERE IN BETWEEN - Matt Hansen</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="str">
-        <v>The Decay</v>
-      </c>
-      <c r="B194" t="str">
-        <v/>
-      </c>
-      <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/the-decay/1862836783</v>
-      </c>
-      <c r="D194" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E194" t="str">
-        <v/>
-      </c>
-      <c r="F194" t="str">
-        <v>What Remains (Midnight Edition)</v>
-      </c>
-      <c r="G194" t="str">
-        <v>3:20</v>
-      </c>
-      <c r="H194" t="str">
-        <v>Pop Evil</v>
-      </c>
-      <c r="I194" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/pop-evil/441597923</v>
-      </c>
-      <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/the-decay/1862836507</v>
-      </c>
-      <c r="L194" t="str">
-        <v>The Decay - Pop Evil</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="str">
-        <v>3111</v>
-      </c>
-      <c r="B195" t="str">
-        <v/>
-      </c>
-      <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/3111/1862225387</v>
-      </c>
-      <c r="D195" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E195" t="str">
-        <v/>
-      </c>
-      <c r="F195" t="str">
-        <v>Goliath</v>
-      </c>
-      <c r="G195" t="str">
-        <v>4:08</v>
-      </c>
-      <c r="H195" t="str">
-        <v>Exodus</v>
-      </c>
-      <c r="I195" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
-      </c>
-      <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/3111/1862225385</v>
-      </c>
-      <c r="L195" t="str">
-        <v>3111 - Exodus</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="str">
-        <v>Touch My Love And Die</v>
-      </c>
-      <c r="B196" t="str">
-        <v/>
-      </c>
-      <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
-      </c>
-      <c r="D196" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E196" t="str">
-        <v/>
-      </c>
-      <c r="F196" t="str">
-        <v>Touch My Love And Die - Single</v>
-      </c>
-      <c r="G196" t="str">
-        <v>2:57</v>
-      </c>
-      <c r="H196" t="str">
-        <v>Myrkur</v>
-      </c>
-      <c r="I196" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/myrkur/293296859</v>
-      </c>
-      <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/touch-my-love-and-die/1867630168</v>
-      </c>
-      <c r="L196" t="str">
-        <v>Touch My Love And Die - Myrkur</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="str">
-        <v>Bomb To A Knife Fight</v>
-      </c>
-      <c r="B197" t="str">
-        <v/>
-      </c>
-      <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/bomb-to-a-knife-fight/1861589406</v>
-      </c>
-      <c r="D197" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E197" t="str">
-        <v/>
-      </c>
-      <c r="F197" t="str">
-        <v>Bomb To A Knife Fight - Single</v>
-      </c>
-      <c r="G197" t="str">
-        <v>2:41</v>
-      </c>
-      <c r="H197" t="str">
-        <v>The Barbarians of California</v>
-      </c>
-      <c r="I197" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/the-barbarians-of-california/1724096474</v>
-      </c>
-      <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/bomb-to-a-knife-fight/1861589405</v>
-      </c>
-      <c r="L197" t="str">
         <v>Bomb To A Knife Fight - The Barbarians of California</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L197"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L190"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-01-week04/titles.xlsx
+++ b/data/global/2026-01-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L190"/>
+  <dimension ref="A1:L189"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מאיה בלזיצמן &amp; מתן אפרת – ילדת לב</v>
+        <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-01-23</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%90%d7%99%d7%94-%d7%91%d7%9c%d7%96%d7%99%d7%a6%d7%9e%d7%9f-%d7%9e%d7%aa%d7%9f-%d7%90%d7%a4%d7%a8%d7%aa-%d7%99%d7%9c%d7%93%d7%aa-%d7%9c%d7%91/</v>
+        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-23</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"ילדת לב” הוא שיר על רגע חמקמק ומבלבל: הזמן שבו ילד מפסיק להיות של ההורה ומתחיל להיות של עצמו. לא מרד דרמטי, לא ניתוק – אלא התרחקות עדינה, כמעט בלתי נראית, שמורגשת דווקא באינטימיות היומיומית:חדר שני, עייפות של הורה, ערב</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>2:59</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Lana Lubany</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מאיה בלזיצמן &amp; מתן אפרת – ילדת לב</v>
+        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video)</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>14 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
+        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-23</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>14 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>2:59</v>
+        <v>4:21</v>
       </c>
       <c r="H3" t="str">
-        <v>Lana Lubany</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>20 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
+        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-23</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>20 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
-        <v>4:21</v>
+        <v>4:09</v>
       </c>
       <c r="H4" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
+        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-23</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G5" t="str">
-        <v>4:09</v>
+        <v>2:34</v>
       </c>
       <c r="H5" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B6" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
+        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-23</v>
@@ -606,10 +606,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G6" t="str">
-        <v>2:34</v>
+        <v>3:10</v>
       </c>
       <c r="H6" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B7" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
+        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-23</v>
@@ -644,10 +644,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v>3:10</v>
+        <v>3:21</v>
       </c>
       <c r="H7" t="str">
-        <v>Olivia Dean</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
+        <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
+        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-23</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>3:21</v>
+        <v>3:06</v>
       </c>
       <c r="H8" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>The Avett Brothers</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
+        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video)</v>
+        <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B9" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
+        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-23</v>
@@ -720,10 +720,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>3:06</v>
+        <v>3:21</v>
       </c>
       <c r="H9" t="str">
-        <v>The Avett Brothers</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
+        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video)</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B10" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
+        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-23</v>
@@ -758,10 +758,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:21</v>
+        <v>7:21</v>
       </c>
       <c r="H10" t="str">
-        <v>Jordana Bryant</v>
+        <v>Katy Perry</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B11" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
+        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-23</v>
@@ -796,10 +796,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>7:21</v>
+        <v>3:17</v>
       </c>
       <c r="H11" t="str">
-        <v>Katy Perry</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
+        <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B12" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
+        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-23</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:17</v>
+        <v>3:45</v>
       </c>
       <c r="H12" t="str">
-        <v>Lauren Watkins</v>
+        <v>Tones And I</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Just A Mess (Live acoustic studio session)</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B13" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
+        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-23</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:45</v>
+        <v>3:57</v>
       </c>
       <c r="H13" t="str">
-        <v>Tones And I</v>
+        <v>Ashleigh Dallas</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
+        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-23</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:57</v>
+        <v>3:03</v>
       </c>
       <c r="H14" t="str">
-        <v>Ashleigh Dallas</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B15" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
+        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-23</v>
@@ -948,10 +948,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:03</v>
+        <v>4:27</v>
       </c>
       <c r="H15" t="str">
-        <v>Charlie Puth</v>
+        <v>Chappell Roan</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B16" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
+        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-23</v>
@@ -986,10 +986,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>4:27</v>
+        <v>4:34</v>
       </c>
       <c r="H16" t="str">
-        <v>Chappell Roan</v>
+        <v>Armik</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B17" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
+        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-23</v>
@@ -1024,10 +1024,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>4:34</v>
+        <v>2:54</v>
       </c>
       <c r="H17" t="str">
-        <v>Armik</v>
+        <v>LØLØ</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>LØLØ - 007 (Official Music Video)</v>
+        <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B18" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
+        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-23</v>
@@ -1062,10 +1062,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>2:54</v>
+        <v>3:25</v>
       </c>
       <c r="H18" t="str">
-        <v>LØLØ</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
+        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer)</v>
+        <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
+        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-23</v>
@@ -1100,10 +1100,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:25</v>
+        <v>2:01</v>
       </c>
       <c r="H19" t="str">
-        <v>Tenille Townes</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
+        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video)</v>
+        <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
+        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-23</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>2:01</v>
+        <v>2:25</v>
       </c>
       <c r="H20" t="str">
-        <v>Alan Walker</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
+        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio)</v>
+        <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B21" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
+        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-23</v>
@@ -1176,10 +1176,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>2:25</v>
+        <v>1:14</v>
       </c>
       <c r="H21" t="str">
-        <v>Charli xcx</v>
+        <v>Labrinth</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
+        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer)</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B22" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
+        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-23</v>
@@ -1214,10 +1214,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>1:14</v>
+        <v>2:59</v>
       </c>
       <c r="H22" t="str">
-        <v>Labrinth</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
+        <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B23" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
+        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-23</v>
@@ -1252,10 +1252,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>2:59</v>
+        <v>2:29</v>
       </c>
       <c r="H23" t="str">
-        <v>Charlie Puth</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
+        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Girl Tones - Volcano (Visualizer)</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B24" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
+        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-23</v>
@@ -1290,10 +1290,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>2:29</v>
+        <v>2:34</v>
       </c>
       <c r="H24" t="str">
-        <v>Girl Tones</v>
+        <v>Jagwar Twin</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B25" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
+        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-23</v>
@@ -1328,10 +1328,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:34</v>
+        <v>3:48</v>
       </c>
       <c r="H25" t="str">
-        <v>Jagwar Twin</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
       </c>
       <c r="B26" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
+        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-23</v>
@@ -1366,10 +1366,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:48</v>
+        <v>3:32</v>
       </c>
       <c r="H26" t="str">
-        <v>Caroline Jones</v>
+        <v>The Beaches</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
       </c>
       <c r="B27" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
+        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-23</v>
@@ -1404,10 +1404,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:32</v>
+        <v>3:49</v>
       </c>
       <c r="H27" t="str">
-        <v>The Beaches</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
+        <v>Madison Beer - bad enough (Official Music Video)</v>
       </c>
       <c r="B28" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
+        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-23</v>
@@ -1442,10 +1442,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:49</v>
+        <v>4:28</v>
       </c>
       <c r="H28" t="str">
-        <v>Dolly Parton</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
+        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Madison Beer - bad enough (Official Music Video)</v>
+        <v>Ty Myers - Message to You (Official Video)</v>
       </c>
       <c r="B29" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
+        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-23</v>
@@ -1480,10 +1480,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>4:28</v>
+        <v>3:37</v>
       </c>
       <c r="H29" t="str">
-        <v>Madison Beer</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
+        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Ty Myers - Message to You (Official Video)</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
       </c>
       <c r="B30" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
+        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-23</v>
@@ -1518,10 +1518,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:37</v>
+        <v>3:35</v>
       </c>
       <c r="H30" t="str">
-        <v>Ty Myers</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
       </c>
       <c r="B31" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
+        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-23</v>
@@ -1556,10 +1556,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:35</v>
+        <v>2:31</v>
       </c>
       <c r="H31" t="str">
-        <v>Megan Moroney</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
       </c>
       <c r="B32" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
+        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-23</v>
@@ -1594,10 +1594,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>2:31</v>
+        <v>3:21</v>
       </c>
       <c r="H32" t="str">
-        <v>Julia Cole Music</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
       </c>
       <c r="B33" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
+        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-23</v>
@@ -1632,10 +1632,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:21</v>
+        <v>5:24</v>
       </c>
       <c r="H33" t="str">
-        <v>Lily Allen</v>
+        <v>Nickless</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
+        <v>Peach PRC - Back To You (Official Audio)</v>
       </c>
       <c r="B34" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
+        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-23</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>5:24</v>
+        <v>3:11</v>
       </c>
       <c r="H34" t="str">
-        <v>Nickless</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
+        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Peach PRC - Back To You (Official Audio)</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
       </c>
       <c r="B35" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
+        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-23</v>
@@ -1708,10 +1708,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:11</v>
+        <v>4:11</v>
       </c>
       <c r="H35" t="str">
-        <v>Peach PRC</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B36" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
+        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-23</v>
@@ -1746,10 +1746,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>4:11</v>
+        <v>3:31</v>
       </c>
       <c r="H36" t="str">
-        <v>Ocean Alley</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
       </c>
       <c r="B37" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
+        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-23</v>
@@ -1784,10 +1784,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:31</v>
+        <v>4:16</v>
       </c>
       <c r="H37" t="str">
-        <v>OneRepublic</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B38" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
+        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-23</v>
@@ -1822,10 +1822,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>4:16</v>
+        <v>4:42</v>
       </c>
       <c r="H38" t="str">
-        <v>Ty Myers</v>
+        <v>JavaJazzFest</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
+        <v>Teo Glacier - Don't Mind (Music Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>8 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
+        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-23</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>8 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>4:42</v>
+        <v>2:47</v>
       </c>
       <c r="H39" t="str">
-        <v>JavaJazzFest</v>
+        <v>Teo Glacier</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
+        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video)</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
+        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-23</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>2:47</v>
+        <v>3:59</v>
       </c>
       <c r="H40" t="str">
-        <v>Teo Glacier</v>
+        <v>Brigitte Calls Me Baby</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
       </c>
       <c r="B41" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
+        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-23</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:59</v>
+        <v>4:09</v>
       </c>
       <c r="H41" t="str">
-        <v>Brigitte Calls Me Baby</v>
+        <v>Louie TheSinger</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
+        <v>ella jane - When I Was Beautiful (Live)</v>
       </c>
       <c r="B42" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
+        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-23</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>4:09</v>
+        <v>3:24</v>
       </c>
       <c r="H42" t="str">
-        <v>Louie TheSinger</v>
+        <v>ella jane</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
+        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ella jane - When I Was Beautiful (Live)</v>
+        <v>Johnny Orlando - Emilia (Official Video)</v>
       </c>
       <c r="B43" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
+        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-23</v>
@@ -2012,10 +2012,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:24</v>
+        <v>3:14</v>
       </c>
       <c r="H43" t="str">
-        <v>ella jane</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
+        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Johnny Orlando - Emilia (Official Video)</v>
+        <v>Kungs, Theophilus London - Galaxy (official video)</v>
       </c>
       <c r="B44" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
+        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-23</v>
@@ -2050,10 +2050,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:14</v>
+        <v>3:32</v>
       </c>
       <c r="H44" t="str">
-        <v>Johnny Orlando</v>
+        <v>Kungs</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
+        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video)</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) (Official Music Video)</v>
       </c>
       <c r="B45" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
+        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-23</v>
@@ -2088,10 +2088,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:32</v>
+        <v>3:15</v>
       </c>
       <c r="H45" t="str">
-        <v>Kungs</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) (Official Music Video) - Billy Raffoul</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
       </c>
       <c r="B46" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
+        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-23</v>
@@ -2126,10 +2126,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:15</v>
+        <v>3:03</v>
       </c>
       <c r="H46" t="str">
-        <v>Billy Raffoul</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
+        <v>Stephen Sanchez - Sweet Love</v>
       </c>
       <c r="B47" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
+        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-23</v>
@@ -2164,10 +2164,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:03</v>
+        <v>3:04</v>
       </c>
       <c r="H47" t="str">
-        <v>NathanEvanss</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
+        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Stephen Sanchez - Sweet Love</v>
+        <v>Bruno Mars - I Just Might [Official Music Video]</v>
       </c>
       <c r="B48" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
+        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-23</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:04</v>
+        <v>3:33</v>
       </c>
       <c r="H48" t="str">
-        <v>Stephen Sanchez</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
+        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video]</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
       </c>
       <c r="B49" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
+        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-23</v>
@@ -2240,10 +2240,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:33</v>
+        <v>2:53</v>
       </c>
       <c r="H49" t="str">
-        <v>Bruno Mars</v>
+        <v>MAX</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
       </c>
       <c r="B50" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
+        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-23</v>
@@ -2278,10 +2278,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G50" t="str">
-        <v>2:53</v>
+        <v>4:11</v>
       </c>
       <c r="H50" t="str">
-        <v>MAX</v>
+        <v>Jessie J</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
       </c>
       <c r="B51" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
+        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-23</v>
@@ -2316,10 +2316,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G51" t="str">
-        <v>4:11</v>
+        <v>2:45</v>
       </c>
       <c r="H51" t="str">
-        <v>Jessie J</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
       </c>
       <c r="B52" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
+        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-23</v>
@@ -2354,10 +2354,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G52" t="str">
-        <v>2:45</v>
+        <v>4:00</v>
       </c>
       <c r="H52" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Brandon Lake and Cody Johnson</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
       </c>
       <c r="B53" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
+        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-23</v>
@@ -2392,10 +2392,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G53" t="str">
-        <v>4:00</v>
+        <v>3:27</v>
       </c>
       <c r="H53" t="str">
-        <v>Brandon Lake and Cody Johnson</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
       </c>
       <c r="B54" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
+        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-23</v>
@@ -2430,10 +2430,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:27</v>
+        <v>3:25</v>
       </c>
       <c r="H54" t="str">
-        <v>The Kid LAROI.</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B55" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
+        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-23</v>
@@ -2468,10 +2468,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:25</v>
+        <v>3:34</v>
       </c>
       <c r="H55" t="str">
-        <v>Olivia Dean</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Train - Mittens (Live on TODAY)</v>
       </c>
       <c r="B56" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
+        <v>https://www.youtube.com/watch?v=R2k_wPsAHKQ</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-23</v>
@@ -2506,10 +2506,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:34</v>
+        <v>3:17</v>
       </c>
       <c r="H56" t="str">
-        <v>Demi Lovato</v>
+        <v>Train</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>Train - Mittens (Live on TODAY) - Train</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Train - Mittens (Live on TODAY)</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
       </c>
       <c r="B57" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=R2k_wPsAHKQ</v>
+        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-23</v>
@@ -2544,10 +2544,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:17</v>
+        <v>2:25</v>
       </c>
       <c r="H57" t="str">
-        <v>Train</v>
+        <v>Joseph</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Train - Mittens (Live on TODAY) - Train</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B58" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
+        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-23</v>
@@ -2582,10 +2582,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
-        <v>2:25</v>
+        <v>3:26</v>
       </c>
       <c r="H58" t="str">
-        <v>Joseph</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B59" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
+        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-23</v>
@@ -2620,10 +2620,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:26</v>
+        <v>4:46</v>
       </c>
       <c r="H59" t="str">
-        <v>Demi Lovato</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B60" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
+        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-23</v>
@@ -2658,7 +2658,7 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
-        <v>4:46</v>
+        <v>3:24</v>
       </c>
       <c r="H60" t="str">
         <v>Keith Urban</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
       </c>
       <c r="B61" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
+        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-23</v>
@@ -2696,10 +2696,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:24</v>
+        <v>2:52</v>
       </c>
       <c r="H61" t="str">
-        <v>Keith Urban</v>
+        <v>Madonna</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
       </c>
       <c r="B62" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
+        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-23</v>
@@ -2734,10 +2734,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
-        <v>2:52</v>
+        <v>2:06</v>
       </c>
       <c r="H62" t="str">
-        <v>Madonna</v>
+        <v>Estas Tonne</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estas Tonne</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
+        <v>Anna Graves - Burn On (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
+        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-23</v>
@@ -2772,10 +2772,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
-        <v>2:06</v>
+        <v>3:09</v>
       </c>
       <c r="H63" t="str">
-        <v>Estas Tonne</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estas Tonne</v>
+        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Anna Graves - Burn On (Official Music Video)</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
       </c>
       <c r="B64" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
+        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-23</v>
@@ -2810,10 +2810,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:09</v>
+        <v>5:11</v>
       </c>
       <c r="H64" t="str">
-        <v>Anna Graves</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
       </c>
       <c r="B65" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
+        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-23</v>
@@ -2848,10 +2848,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
-        <v>5:11</v>
+        <v>3:40</v>
       </c>
       <c r="H65" t="str">
-        <v>Ocean Alley</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B66" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
+        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-23</v>
@@ -2886,10 +2886,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:40</v>
+        <v>3:49</v>
       </c>
       <c r="H66" t="str">
-        <v>Zara Larsson</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
+        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-23</v>
@@ -2924,10 +2924,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:49</v>
+        <v>3:42</v>
       </c>
       <c r="H67" t="str">
-        <v>Lauren Watkins</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
+        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-23</v>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:42</v>
+        <v>5:11</v>
       </c>
       <c r="H68" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
+        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-23</v>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>5:11</v>
+        <v>3:57</v>
       </c>
       <c r="H69" t="str">
-        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
+        <v>Grace Enger - All My Songs (Official Lyric Video)</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
+        <v>https://www.youtube.com/watch?v=gWyaiGAFVO8</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-23</v>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:57</v>
+        <v>3:29</v>
       </c>
       <c r="H70" t="str">
-        <v>Lainey Wilson</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
+        <v>Grace Enger - All My Songs (Official Lyric Video) - Grace Enger</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Grace Enger - All My Songs (Official Lyric Video)</v>
+        <v>Alan Walker - Broken Strings (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=gWyaiGAFVO8</v>
+        <v>https://www.youtube.com/watch?v=jwQKcW474Tc</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-23</v>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:29</v>
+        <v>3:10</v>
       </c>
       <c r="H71" t="str">
-        <v>Grace Enger</v>
+        <v>Alan Walker and 2 more</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Grace Enger - All My Songs (Official Lyric Video) - Grace Enger</v>
+        <v>Alan Walker - Broken Strings (Official Music Video) - Alan Walker and 2 more</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Alan Walker - Broken Strings (Official Music Video)</v>
+        <v>Emilia Tarrant - Break Up With Myself</v>
       </c>
       <c r="B72" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=jwQKcW474Tc</v>
+        <v>https://www.youtube.com/watch?v=3N7iKwqENP0</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-23</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:10</v>
+        <v>4:04</v>
       </c>
       <c r="H72" t="str">
-        <v>Alan Walker and 2 more</v>
+        <v>Emilia Tarrant</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Alan Walker - Broken Strings (Official Music Video) - Alan Walker and 2 more</v>
+        <v>Emilia Tarrant - Break Up With Myself - Emilia Tarrant</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Emilia Tarrant - Break Up With Myself</v>
+        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026)</v>
       </c>
       <c r="B73" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=3N7iKwqENP0</v>
+        <v>https://www.youtube.com/watch?v=sKG5ZIzCnFQ</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-23</v>
@@ -3152,10 +3152,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>4:04</v>
+        <v>3:09</v>
       </c>
       <c r="H73" t="str">
-        <v>Emilia Tarrant</v>
+        <v>Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Emilia Tarrant - Break Up With Myself - Emilia Tarrant</v>
+        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026) - Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026)</v>
+        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer)</v>
       </c>
       <c r="B74" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=sKG5ZIzCnFQ</v>
+        <v>https://www.youtube.com/watch?v=Koj30I91_8k</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-23</v>
@@ -3190,10 +3190,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:09</v>
+        <v>2:27</v>
       </c>
       <c r="H74" t="str">
-        <v>Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026) - Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer)</v>
+        <v>Maggie Lindemann - fate</v>
       </c>
       <c r="B75" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=Koj30I91_8k</v>
+        <v>https://www.youtube.com/watch?v=xZdWEmnRK4g</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-23</v>
@@ -3228,10 +3228,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>2:27</v>
+        <v>2:12</v>
       </c>
       <c r="H75" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Maggie Lindemann</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer) - Lauren Spencer Smith</v>
+        <v>Maggie Lindemann - fate - Maggie Lindemann</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Maggie Lindemann - fate</v>
+        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023)</v>
       </c>
       <c r="B76" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=xZdWEmnRK4g</v>
+        <v>https://www.youtube.com/watch?v=wo9yPPCh75Q</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-23</v>
@@ -3266,10 +3266,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>2:12</v>
+        <v>4:44</v>
       </c>
       <c r="H76" t="str">
-        <v>Maggie Lindemann</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Maggie Lindemann - fate - Maggie Lindemann</v>
+        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023) - Cliff Richard</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023)</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025</v>
       </c>
       <c r="B77" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=wo9yPPCh75Q</v>
+        <v>https://www.youtube.com/watch?v=ND6maRwmzHk</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-23</v>
@@ -3304,10 +3304,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>4:44</v>
+        <v>1:00:09</v>
       </c>
       <c r="H77" t="str">
-        <v>Cliff Richard</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023) - Cliff Richard</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025</v>
+        <v>RAYE - Black Mascara. (Live at The Royal Albert Hall)</v>
       </c>
       <c r="B78" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=ND6maRwmzHk</v>
+        <v>https://www.youtube.com/watch?v=9jMMOYr-VhE</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-23</v>
@@ -3342,10 +3342,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>1:00:09</v>
+        <v>4:15</v>
       </c>
       <c r="H78" t="str">
-        <v>Purple Disco Machine</v>
+        <v>RAYE</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025 - Purple Disco Machine</v>
+        <v>RAYE - Black Mascara. (Live at The Royal Albert Hall) - RAYE</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>RAYE - Black Mascara. (Live at The Royal Albert Hall)</v>
+        <v>Madison Cunningham - My Full Name (Garden Session)</v>
       </c>
       <c r="B79" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=9jMMOYr-VhE</v>
+        <v>https://www.youtube.com/watch?v=o2F-QmqdNtI</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-23</v>
@@ -3380,10 +3380,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>4:15</v>
+        <v>4:07</v>
       </c>
       <c r="H79" t="str">
-        <v>RAYE</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>RAYE - Black Mascara. (Live at The Royal Albert Hall) - RAYE</v>
+        <v>Madison Cunningham - My Full Name (Garden Session) - Madison Cunningham</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Madison Cunningham - My Full Name (Garden Session)</v>
+        <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions)</v>
       </c>
       <c r="B80" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=o2F-QmqdNtI</v>
+        <v>https://www.youtube.com/watch?v=5-6cEVLqE90</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-23</v>
@@ -3418,10 +3418,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>4:07</v>
+        <v>3:10</v>
       </c>
       <c r="H80" t="str">
-        <v>Madison Cunningham</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Madison Cunningham - My Full Name (Garden Session) - Madison Cunningham</v>
+        <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions) - Teddy Swims</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions)</v>
+        <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower)</v>
       </c>
       <c r="B81" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=5-6cEVLqE90</v>
+        <v>https://www.youtube.com/watch?v=ivPSbcEMwCs</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-23</v>
@@ -3456,10 +3456,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:10</v>
+        <v>3:47</v>
       </c>
       <c r="H81" t="str">
-        <v>Teddy Swims</v>
+        <v>Christina Aguilera</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions) - Teddy Swims</v>
+        <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower) - Christina Aguilera</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower)</v>
+        <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025)</v>
       </c>
       <c r="B82" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=ivPSbcEMwCs</v>
+        <v>https://www.youtube.com/watch?v=tYpOHbXFnm0</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-23</v>
@@ -3494,10 +3494,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:47</v>
+        <v>3:58</v>
       </c>
       <c r="H82" t="str">
-        <v>Christina Aguilera</v>
+        <v>RAYE</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower) - Christina Aguilera</v>
+        <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025) - RAYE</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025)</v>
+        <v>Dasha - Here For The Party (Official Audio)</v>
       </c>
       <c r="B83" t="str">
-        <v>3 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=tYpOHbXFnm0</v>
+        <v>https://www.youtube.com/watch?v=rSO9oYUnO2k</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-23</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>3 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:58</v>
+        <v>3:30</v>
       </c>
       <c r="H83" t="str">
-        <v>RAYE</v>
+        <v>Dasha</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025) - RAYE</v>
+        <v>Dasha - Here For The Party (Official Audio) - Dasha</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Dasha - Here For The Party (Official Audio)</v>
+        <v>Lady Gaga in Harlequin Live: One Night Only</v>
       </c>
       <c r="B84" t="str">
         <v>4 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=rSO9oYUnO2k</v>
+        <v>https://www.youtube.com/watch?v=c231tCsQalU</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-23</v>
@@ -3570,10 +3570,10 @@
         <v>4 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:30</v>
+        <v>51:49</v>
       </c>
       <c r="H84" t="str">
-        <v>Dasha</v>
+        <v>Lady Gaga and YouTube</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Dasha - Here For The Party (Official Audio) - Dasha</v>
+        <v>Lady Gaga in Harlequin Live: One Night Only - Lady Gaga and YouTube</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Lady Gaga in Harlequin Live: One Night Only</v>
+        <v>Sabrina Carpenter - Such A Funny Way (Official Lyric Video)</v>
       </c>
       <c r="B85" t="str">
         <v>4 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=c231tCsQalU</v>
+        <v>https://www.youtube.com/watch?v=oaJKUCgSSkc</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-23</v>
@@ -3608,10 +3608,10 @@
         <v>4 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>51:49</v>
+        <v>3:53</v>
       </c>
       <c r="H85" t="str">
-        <v>Lady Gaga and YouTube</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Lady Gaga in Harlequin Live: One Night Only - Lady Gaga and YouTube</v>
+        <v>Sabrina Carpenter - Such A Funny Way (Official Lyric Video) - Sabrina Carpenter</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Sabrina Carpenter - Such A Funny Way (Official Lyric Video)</v>
+        <v>Megan Moroney - Beautiful Things (Official Fan Video)</v>
       </c>
       <c r="B86" t="str">
         <v>4 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=oaJKUCgSSkc</v>
+        <v>https://www.youtube.com/watch?v=0Gxu80LxI0w</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-23</v>
@@ -3646,10 +3646,10 @@
         <v>4 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:53</v>
+        <v>3:56</v>
       </c>
       <c r="H86" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Sabrina Carpenter - Such A Funny Way (Official Lyric Video) - Sabrina Carpenter</v>
+        <v>Megan Moroney - Beautiful Things (Official Fan Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Megan Moroney - Beautiful Things (Official Fan Video)</v>
+        <v>Jason Derulo - Miracle</v>
       </c>
       <c r="B87" t="str">
         <v>4 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=0Gxu80LxI0w</v>
+        <v>https://www.youtube.com/watch?v=7sjshHJwkOE</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-23</v>
@@ -3684,10 +3684,10 @@
         <v>4 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:56</v>
+        <v>4:16</v>
       </c>
       <c r="H87" t="str">
-        <v>Megan Moroney</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Megan Moroney - Beautiful Things (Official Fan Video) - Megan Moroney</v>
+        <v>Jason Derulo - Miracle - Jason Derulo</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Jason Derulo - Miracle</v>
+        <v>Sananda Maitreya - Pretty Baby (Live)</v>
       </c>
       <c r="B88" t="str">
         <v>4 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=7sjshHJwkOE</v>
+        <v>https://www.youtube.com/watch?v=yv1c5G5HZt8</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-23</v>
@@ -3722,10 +3722,10 @@
         <v>4 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>4:16</v>
+        <v>3:29</v>
       </c>
       <c r="H88" t="str">
-        <v>Jason Derulo</v>
+        <v>Sananda Maitreya</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Jason Derulo - Miracle - Jason Derulo</v>
+        <v>Sananda Maitreya - Pretty Baby (Live) - Sananda Maitreya</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Sananda Maitreya - Pretty Baby (Live)</v>
+        <v>Faded - 10th Anniversary (Performance Video)</v>
       </c>
       <c r="B89" t="str">
         <v>4 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=yv1c5G5HZt8</v>
+        <v>https://www.youtube.com/watch?v=EXVg23U3NRw</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-23</v>
@@ -3760,10 +3760,10 @@
         <v>4 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:29</v>
+        <v>3:25</v>
       </c>
       <c r="H89" t="str">
-        <v>Sananda Maitreya</v>
+        <v>Alan Walker and 2 more</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Sananda Maitreya - Pretty Baby (Live) - Sananda Maitreya</v>
+        <v>Faded - 10th Anniversary (Performance Video) - Alan Walker and 2 more</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Faded - 10th Anniversary (Performance Video)</v>
+        <v>What Are You Doing New Year's Eve (Live from the Eiffel Tower - Official Lyric Video)</v>
       </c>
       <c r="B90" t="str">
         <v>4 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=EXVg23U3NRw</v>
+        <v>https://www.youtube.com/watch?v=Bpb67fSUzEQ</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-23</v>
@@ -3798,10 +3798,10 @@
         <v>4 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:25</v>
+        <v>4:06</v>
       </c>
       <c r="H90" t="str">
-        <v>Alan Walker and 2 more</v>
+        <v>Christina Aguilera</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Faded - 10th Anniversary (Performance Video) - Alan Walker and 2 more</v>
+        <v>What Are You Doing New Year's Eve (Live from the Eiffel Tower - Official Lyric Video) - Christina Aguilera</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>What Are You Doing New Year's Eve (Live from the Eiffel Tower - Official Lyric Video)</v>
+        <v>Have Yourself a Merry Little Christmas (Live from the Eiffel Tower - Official Lyric Video)</v>
       </c>
       <c r="B91" t="str">
         <v>4 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=Bpb67fSUzEQ</v>
+        <v>https://www.youtube.com/watch?v=gkwb6kZloLA</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-23</v>
@@ -3836,7 +3836,7 @@
         <v>4 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>4:06</v>
+        <v>4:03</v>
       </c>
       <c r="H91" t="str">
         <v>Christina Aguilera</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>What Are You Doing New Year's Eve (Live from the Eiffel Tower - Official Lyric Video) - Christina Aguilera</v>
+        <v>Have Yourself a Merry Little Christmas (Live from the Eiffel Tower - Official Lyric Video) - Christina Aguilera</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Have Yourself a Merry Little Christmas (Live from the Eiffel Tower - Official Lyric Video)</v>
+        <v>Chris Rea - Driving Home for Christmas - (Live on National Lottery Stars, 2000)</v>
       </c>
       <c r="B92" t="str">
-        <v>4 weeks ago</v>
+        <v>1 year ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=gkwb6kZloLA</v>
+        <v>https://www.youtube.com/watch?v=Jckb3dnS5fw</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-23</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>4 weeks ago</v>
+        <v>1 year ago</v>
       </c>
       <c r="G92" t="str">
-        <v>4:03</v>
+        <v>4:11</v>
       </c>
       <c r="H92" t="str">
-        <v>Christina Aguilera</v>
+        <v>Chris Rea Official</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Have Yourself a Merry Little Christmas (Live from the Eiffel Tower - Official Lyric Video) - Christina Aguilera</v>
+        <v>Chris Rea - Driving Home for Christmas - (Live on National Lottery Stars, 2000) - Chris Rea Official</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Chris Rea - Driving Home for Christmas - (Live on National Lottery Stars, 2000)</v>
+        <v>Jessie J - I'll Never Know Why (The Royal Variety Performance 2025)</v>
       </c>
       <c r="B93" t="str">
-        <v>1 year ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=Jckb3dnS5fw</v>
+        <v>https://www.youtube.com/watch?v=DPA8v4YS8AY</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-23</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>1 year ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G93" t="str">
-        <v>4:11</v>
+        <v>4:08</v>
       </c>
       <c r="H93" t="str">
-        <v>Chris Rea Official</v>
+        <v>Jessie J</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Chris Rea - Driving Home for Christmas - (Live on National Lottery Stars, 2000) - Chris Rea Official</v>
+        <v>Jessie J - I'll Never Know Why (The Royal Variety Performance 2025) - Jessie J</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Jessie J - I'll Never Know Why (The Royal Variety Performance 2025)</v>
+        <v>Craig David - Walking Away (Official HD Video)</v>
       </c>
       <c r="B94" t="str">
         <v>1 month ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=DPA8v4YS8AY</v>
+        <v>https://www.youtube.com/watch?v=v8Yu21pEbqw</v>
       </c>
       <c r="D94" t="str">
         <v>2026-01-23</v>
@@ -3950,10 +3950,10 @@
         <v>1 month ago</v>
       </c>
       <c r="G94" t="str">
-        <v>4:08</v>
+        <v>3:34</v>
       </c>
       <c r="H94" t="str">
-        <v>Jessie J</v>
+        <v>Craig David</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Jessie J - I'll Never Know Why (The Royal Variety Performance 2025) - Jessie J</v>
+        <v>Craig David - Walking Away (Official HD Video) - Craig David</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Craig David - Walking Away (Official HD Video)</v>
+        <v>Christina Aguilera, Yseult - Ave Maria (Live from the Eiffel Tower - Official Video)</v>
       </c>
       <c r="B95" t="str">
         <v>1 month ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=v8Yu21pEbqw</v>
+        <v>https://www.youtube.com/watch?v=sq2u9Cfn2B8</v>
       </c>
       <c r="D95" t="str">
         <v>2026-01-23</v>
@@ -3988,10 +3988,10 @@
         <v>1 month ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:34</v>
+        <v>4:37</v>
       </c>
       <c r="H95" t="str">
-        <v>Craig David</v>
+        <v>Christina Aguilera</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Craig David - Walking Away (Official HD Video) - Craig David</v>
+        <v>Christina Aguilera, Yseult - Ave Maria (Live from the Eiffel Tower - Official Video) - Christina Aguilera</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Christina Aguilera, Yseult - Ave Maria (Live from the Eiffel Tower - Official Video)</v>
+        <v>Shawn Mendes &amp; Niall Horan - This Town (Live from London)</v>
       </c>
       <c r="B96" t="str">
         <v>1 month ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=sq2u9Cfn2B8</v>
+        <v>https://www.youtube.com/watch?v=Ea2DSMNIK5w</v>
       </c>
       <c r="D96" t="str">
         <v>2026-01-23</v>
@@ -4026,10 +4026,10 @@
         <v>1 month ago</v>
       </c>
       <c r="G96" t="str">
-        <v>4:37</v>
+        <v>6:27</v>
       </c>
       <c r="H96" t="str">
-        <v>Christina Aguilera</v>
+        <v>Shawn Mendes and Niall Horan</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Christina Aguilera, Yseult - Ave Maria (Live from the Eiffel Tower - Official Video) - Christina Aguilera</v>
+        <v>Shawn Mendes &amp; Niall Horan - This Town (Live from London) - Shawn Mendes and Niall Horan</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Shawn Mendes &amp; Niall Horan - This Town (Live from London)</v>
+        <v>Shakira - Zoo (From "Zootopia 2")</v>
       </c>
       <c r="B97" t="str">
         <v>1 month ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=Ea2DSMNIK5w</v>
+        <v>https://www.youtube.com/watch?v=kCIf6yaJisQ</v>
       </c>
       <c r="D97" t="str">
         <v>2026-01-23</v>
@@ -4064,10 +4064,10 @@
         <v>1 month ago</v>
       </c>
       <c r="G97" t="str">
-        <v>6:27</v>
+        <v>2:07</v>
       </c>
       <c r="H97" t="str">
-        <v>Shawn Mendes and Niall Horan</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Shawn Mendes &amp; Niall Horan - This Town (Live from London) - Shawn Mendes and Niall Horan</v>
+        <v>Shakira - Zoo (From "Zootopia 2") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Shakira - Zoo (From "Zootopia 2")</v>
+        <v>Within Temptation - Ice Queen (Acoustic) | 2025 Reimagined Edition</v>
       </c>
       <c r="B98" t="str">
         <v>1 month ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=kCIf6yaJisQ</v>
+        <v>https://www.youtube.com/watch?v=f1Iqm16vWDQ</v>
       </c>
       <c r="D98" t="str">
         <v>2026-01-23</v>
@@ -4102,10 +4102,10 @@
         <v>1 month ago</v>
       </c>
       <c r="G98" t="str">
-        <v>2:07</v>
+        <v>3:40</v>
       </c>
       <c r="H98" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>Within Temptation</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Shakira - Zoo (From "Zootopia 2") - DisneyMusicVEVO</v>
+        <v>Within Temptation - Ice Queen (Acoustic) | 2025 Reimagined Edition - Within Temptation</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Within Temptation - Ice Queen (Acoustic) | 2025 Reimagined Edition</v>
+        <v>OneRepublic - Give Me Something (for Arknights Endfield) (Official Audio)</v>
       </c>
       <c r="B99" t="str">
         <v>1 month ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=f1Iqm16vWDQ</v>
+        <v>https://www.youtube.com/watch?v=4eqzUNO-ONs</v>
       </c>
       <c r="D99" t="str">
         <v>2026-01-23</v>
@@ -4140,10 +4140,10 @@
         <v>1 month ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:40</v>
+        <v>2:43</v>
       </c>
       <c r="H99" t="str">
-        <v>Within Temptation</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Within Temptation - Ice Queen (Acoustic) | 2025 Reimagined Edition - Within Temptation</v>
+        <v>OneRepublic - Give Me Something (for Arknights Endfield) (Official Audio) - OneRepublic</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>OneRepublic - Give Me Something (for Arknights Endfield) (Official Audio)</v>
+        <v>Passenger | The Road Is Long</v>
       </c>
       <c r="B100" t="str">
         <v>1 month ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=4eqzUNO-ONs</v>
+        <v>https://www.youtube.com/watch?v=oi4aTOc-IX4</v>
       </c>
       <c r="D100" t="str">
         <v>2026-01-23</v>
@@ -4178,10 +4178,10 @@
         <v>1 month ago</v>
       </c>
       <c r="G100" t="str">
-        <v>2:43</v>
+        <v>4:01</v>
       </c>
       <c r="H100" t="str">
-        <v>OneRepublic</v>
+        <v>Passenger</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>OneRepublic - Give Me Something (for Arknights Endfield) (Official Audio) - OneRepublic</v>
+        <v>Passenger | The Road Is Long - Passenger</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Passenger | The Road Is Long</v>
+        <v>Black Honey - Carroll Avenue (Live at RAK)</v>
       </c>
       <c r="B101" t="str">
         <v>1 month ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=oi4aTOc-IX4</v>
+        <v>https://www.youtube.com/watch?v=LPXTE3a6QrM</v>
       </c>
       <c r="D101" t="str">
         <v>2026-01-23</v>
@@ -4216,10 +4216,10 @@
         <v>1 month ago</v>
       </c>
       <c r="G101" t="str">
-        <v>4:01</v>
+        <v>3:19</v>
       </c>
       <c r="H101" t="str">
-        <v>Passenger</v>
+        <v>Black Honey</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Passenger | The Road Is Long - Passenger</v>
+        <v>Black Honey - Carroll Avenue (Live at RAK) - Black Honey</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Black Honey - Carroll Avenue (Live at RAK)</v>
+        <v>Aperture</v>
       </c>
       <c r="B102" t="str">
-        <v>1 month ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=LPXTE3a6QrM</v>
+        <v>https://music.apple.com/us/song/aperture/1870984033</v>
       </c>
       <c r="D102" t="str">
         <v>2026-01-23</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>1 month ago</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G102" t="str">
-        <v>3:19</v>
+        <v>5:11</v>
       </c>
       <c r="H102" t="str">
-        <v>Black Honey</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/aperture/1870984032</v>
       </c>
       <c r="L102" t="str">
-        <v>Black Honey - Carroll Avenue (Live at RAK) - Black Honey</v>
+        <v>Aperture - Harry Styles</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Aperture</v>
+        <v>Opening Night</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/aperture/1870984033</v>
+        <v>https://music.apple.com/us/song/opening-night/1870313501</v>
       </c>
       <c r="D103" t="str">
         <v>2026-01-23</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Kiss All The Time. Disco, Occasionally.</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G103" t="str">
-        <v>5:11</v>
+        <v>4:19</v>
       </c>
       <c r="H103" t="str">
-        <v>Harry Styles</v>
+        <v>Arctic Monkeys</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
+        <v>https://music.apple.com/us/artist/arctic-monkeys/62820413</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/aperture/1870984032</v>
+        <v>https://music.apple.com/us/album/opening-night/1870313498</v>
       </c>
       <c r="L103" t="str">
-        <v>Aperture - Harry Styles</v>
+        <v>Opening Night - Arctic Monkeys</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Opening Night</v>
+        <v>FLACKITO JODYE (feat. Tokischa)</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/opening-night/1870313501</v>
+        <v>https://music.apple.com/us/song/flackito-jodye-feat-tokischa/1870968779</v>
       </c>
       <c r="D104" t="str">
         <v>2026-01-23</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>HELP(2)</v>
+        <v>Don't Be Dumb</v>
       </c>
       <c r="G104" t="str">
-        <v>4:19</v>
+        <v>2:20</v>
       </c>
       <c r="H104" t="str">
-        <v>Arctic Monkeys</v>
+        <v>A$AP Rocky</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/arctic-monkeys/62820413</v>
+        <v>https://music.apple.com/us/artist/a%24ap-rocky/481488005</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/opening-night/1870313498</v>
+        <v>https://music.apple.com/us/album/flackito-jodye-feat-tokischa/1870968596</v>
       </c>
       <c r="L104" t="str">
-        <v>Opening Night - Arctic Monkeys</v>
+        <v>FLACKITO JODYE (feat. Tokischa) - A$AP Rocky</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>FLACKITO JODYE (feat. Tokischa)</v>
+        <v>CAMBIARÉ</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/flackito-jodye-feat-tokischa/1870968779</v>
+        <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
       </c>
       <c r="D105" t="str">
         <v>2026-01-23</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Don't Be Dumb</v>
+        <v>CAMBIARÉ - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>2:20</v>
+        <v>3:01</v>
       </c>
       <c r="H105" t="str">
-        <v>A$AP Rocky</v>
+        <v>Luis Fonsi</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/a%24ap-rocky/481488005</v>
+        <v>https://music.apple.com/us/artist/luis-fonsi/102834</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/flackito-jodye-feat-tokischa/1870968596</v>
+        <v>https://music.apple.com/us/album/cambiar%C3%A9/1867545265</v>
       </c>
       <c r="L105" t="str">
-        <v>FLACKITO JODYE (feat. Tokischa) - A$AP Rocky</v>
+        <v>CAMBIARÉ - Luis Fonsi</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>CAMBIARÉ</v>
+        <v>Last of a Dying Breed</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
+        <v>https://music.apple.com/us/song/last-of-a-dying-breed/1849706852</v>
       </c>
       <c r="D106" t="str">
         <v>2026-01-23</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>CAMBIARÉ - Single</v>
+        <v>Piss In The Wind</v>
       </c>
       <c r="G106" t="str">
-        <v>3:01</v>
+        <v>2:29</v>
       </c>
       <c r="H106" t="str">
-        <v>Luis Fonsi</v>
+        <v>Joji</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/luis-fonsi/102834</v>
+        <v>https://music.apple.com/us/artist/joji/1258279972</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/cambiar%C3%A9/1867545265</v>
+        <v>https://music.apple.com/us/album/last-of-a-dying-breed/1849706656</v>
       </c>
       <c r="L106" t="str">
-        <v>CAMBIARÉ - Luis Fonsi</v>
+        <v>Last of a Dying Breed - Joji</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Last of a Dying Breed</v>
+        <v>High Key</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/last-of-a-dying-breed/1849706852</v>
+        <v>https://music.apple.com/us/song/high-key/1847702418</v>
       </c>
       <c r="D107" t="str">
         <v>2026-01-23</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Piss In The Wind</v>
+        <v>Vacancy</v>
       </c>
       <c r="G107" t="str">
-        <v>2:29</v>
+        <v>2:12</v>
       </c>
       <c r="H107" t="str">
-        <v>Joji</v>
+        <v>Ari Lennox</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/joji/1258279972</v>
+        <v>https://music.apple.com/us/artist/ari-lennox/448854570</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/last-of-a-dying-breed/1849706656</v>
+        <v>https://music.apple.com/us/album/high-key/1847702412</v>
       </c>
       <c r="L107" t="str">
-        <v>Last of a Dying Breed - Joji</v>
+        <v>High Key - Ari Lennox</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>High Key</v>
+        <v>scared</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/high-key/1847702418</v>
+        <v>https://music.apple.com/us/song/scared/1862292863</v>
       </c>
       <c r="D108" t="str">
         <v>2026-01-23</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Vacancy</v>
+        <v>scared - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>2:12</v>
+        <v>4:03</v>
       </c>
       <c r="H108" t="str">
-        <v>Ari Lennox</v>
+        <v>Fred again..</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/ari-lennox/448854570</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/high-key/1847702412</v>
+        <v>https://music.apple.com/us/album/scared/1862292862</v>
       </c>
       <c r="L108" t="str">
-        <v>High Key - Ari Lennox</v>
+        <v>scared - Fred again..</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>scared</v>
+        <v>Death of Love</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/scared/1862292863</v>
+        <v>https://music.apple.com/us/song/death-of-love/1862353786</v>
       </c>
       <c r="D109" t="str">
         <v>2026-01-23</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>scared - Single</v>
+        <v>Trying Times</v>
       </c>
       <c r="G109" t="str">
-        <v>4:03</v>
+        <v>3:26</v>
       </c>
       <c r="H109" t="str">
-        <v>Fred again..</v>
+        <v>James Blake</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/scared/1862292862</v>
+        <v>https://music.apple.com/us/album/death-of-love/1862353780</v>
       </c>
       <c r="L109" t="str">
-        <v>scared - Fred again..</v>
+        <v>Death of Love - James Blake</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Death of Love</v>
+        <v>Big Ole Fancy House</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/death-of-love/1862353786</v>
+        <v>https://music.apple.com/us/song/big-ole-fancy-house/1862624759</v>
       </c>
       <c r="D110" t="str">
         <v>2026-01-23</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Trying Times</v>
+        <v>Parker McCollum (The Deluxe Edition)</v>
       </c>
       <c r="G110" t="str">
-        <v>3:26</v>
+        <v>4:03</v>
       </c>
       <c r="H110" t="str">
-        <v>James Blake</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/death-of-love/1862353780</v>
+        <v>https://music.apple.com/us/album/big-ole-fancy-house/1862624506</v>
       </c>
       <c r="L110" t="str">
-        <v>Death of Love - James Blake</v>
+        <v>Big Ole Fancy House - Parker McCollum</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Big Ole Fancy House</v>
+        <v>Flo Jackson</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/big-ole-fancy-house/1862624759</v>
+        <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
       </c>
       <c r="D111" t="str">
         <v>2026-01-23</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Parker McCollum (The Deluxe Edition)</v>
+        <v>Flo Jackson - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>4:03</v>
+        <v>2:23</v>
       </c>
       <c r="H111" t="str">
-        <v>Parker McCollum</v>
+        <v>Flo Milli</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
+        <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/big-ole-fancy-house/1862624506</v>
+        <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
       </c>
       <c r="L111" t="str">
-        <v>Big Ole Fancy House - Parker McCollum</v>
+        <v>Flo Jackson - Flo Milli</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Flo Jackson</v>
+        <v>Site Unseen (feat. Waxahatchee)</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
+        <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
       </c>
       <c r="D112" t="str">
         <v>2026-01-23</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Flo Jackson - Single</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G112" t="str">
-        <v>2:23</v>
+        <v>2:46</v>
       </c>
       <c r="H112" t="str">
-        <v>Flo Milli</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
+        <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
       </c>
       <c r="L112" t="str">
-        <v>Flo Jackson - Flo Milli</v>
+        <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Site Unseen (feat. Waxahatchee)</v>
+        <v>Puppet Parade</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
+        <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
       </c>
       <c r="D113" t="str">
         <v>2026-01-23</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Creature of Habit</v>
+        <v>Megadeth</v>
       </c>
       <c r="G113" t="str">
-        <v>2:46</v>
+        <v>4:40</v>
       </c>
       <c r="H113" t="str">
-        <v>Courtney Barnett</v>
+        <v>Megadeth</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/megadeth/488289</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
+        <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
       </c>
       <c r="L113" t="str">
-        <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
+        <v>Puppet Parade - Megadeth</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Puppet Parade</v>
+        <v>To Love Somebody</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
+        <v>https://music.apple.com/us/song/to-love-somebody/1859630040</v>
       </c>
       <c r="D114" t="str">
         <v>2026-01-23</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Megadeth</v>
+        <v>Cruel World</v>
       </c>
       <c r="G114" t="str">
-        <v>4:40</v>
+        <v>3:57</v>
       </c>
       <c r="H114" t="str">
-        <v>Megadeth</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/megadeth/488289</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
+        <v>https://music.apple.com/us/album/to-love-somebody/1859629846</v>
       </c>
       <c r="L114" t="str">
-        <v>Puppet Parade - Megadeth</v>
+        <v>To Love Somebody - Holly Humberstone</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>To Love Somebody</v>
+        <v>Nothing Is Impossible With You</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/to-love-somebody/1859630040</v>
+        <v>https://music.apple.com/us/song/nothing-is-impossible-with-you/1870691236</v>
       </c>
       <c r="D115" t="str">
         <v>2026-01-23</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Cruel World</v>
+        <v>Nothing Is Impossible With You - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:57</v>
+        <v>4:14</v>
       </c>
       <c r="H115" t="str">
-        <v>Holly Humberstone</v>
+        <v>Cleo Sol</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/cleo-sol/459710289</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/to-love-somebody/1859629846</v>
+        <v>https://music.apple.com/us/album/nothing-is-impossible-with-you/1870691227</v>
       </c>
       <c r="L115" t="str">
-        <v>To Love Somebody - Holly Humberstone</v>
+        <v>Nothing Is Impossible With You - Cleo Sol</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Nothing Is Impossible With You</v>
+        <v>HYPNOTIZE</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/nothing-is-impossible-with-you/1870691236</v>
+        <v>https://music.apple.com/us/song/hypnotize/1861009528</v>
       </c>
       <c r="D116" t="str">
         <v>2026-01-23</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Nothing Is Impossible With You - Single</v>
+        <v>THE CORE - 核</v>
       </c>
       <c r="G116" t="str">
-        <v>4:14</v>
+        <v>2:50</v>
       </c>
       <c r="H116" t="str">
-        <v>Cleo Sol</v>
+        <v>XG</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/cleo-sol/459710289</v>
+        <v>https://music.apple.com/us/artist/xg/1609409493</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/nothing-is-impossible-with-you/1870691227</v>
+        <v>https://music.apple.com/us/album/hypnotize/1861009513</v>
       </c>
       <c r="L116" t="str">
-        <v>Nothing Is Impossible With You - Cleo Sol</v>
+        <v>HYPNOTIZE - XG</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>HYPNOTIZE</v>
+        <v>Dead End</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/hypnotize/1861009528</v>
+        <v>https://music.apple.com/us/song/dead-end/1862845874</v>
       </c>
       <c r="D117" t="str">
         <v>2026-01-23</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>THE CORE - 核</v>
+        <v>Ricochet</v>
       </c>
       <c r="G117" t="str">
-        <v>2:50</v>
+        <v>4:05</v>
       </c>
       <c r="H117" t="str">
-        <v>XG</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/xg/1609409493</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/hypnotize/1861009513</v>
+        <v>https://music.apple.com/us/album/dead-end/1862845733</v>
       </c>
       <c r="L117" t="str">
-        <v>HYPNOTIZE - XG</v>
+        <v>Dead End - Snail Mail</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Dead End</v>
+        <v>Do I Wanna Know?</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/dead-end/1862845874</v>
+        <v>https://music.apple.com/us/song/do-i-wanna-know/1870931500</v>
       </c>
       <c r="D118" t="str">
         <v>2026-01-23</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Ricochet</v>
+        <v>Do I Wanna Know? - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>4:05</v>
+        <v>3:52</v>
       </c>
       <c r="H118" t="str">
-        <v>Snail Mail</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v>https://music.apple.com/us/artist/dove-cameron/599822740</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/dead-end/1862845733</v>
+        <v>https://music.apple.com/us/album/do-i-wanna-know/1870931327</v>
       </c>
       <c r="L118" t="str">
-        <v>Dead End - Snail Mail</v>
+        <v>Do I Wanna Know? - Dove Cameron</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Do I Wanna Know?</v>
+        <v>Una y Otra Vez</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/do-i-wanna-know/1870931500</v>
+        <v>https://music.apple.com/us/song/una-y-otra-vez/1868792926</v>
       </c>
       <c r="D119" t="str">
         <v>2026-01-23</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Do I Wanna Know? - Single</v>
+        <v>K de Karma (Apple Music Edition)</v>
       </c>
       <c r="G119" t="str">
-        <v>3:52</v>
+        <v>3:02</v>
       </c>
       <c r="H119" t="str">
-        <v>Dove Cameron</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/dove-cameron/599822740</v>
+        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/do-i-wanna-know/1870931327</v>
+        <v>https://music.apple.com/us/album/una-y-otra-vez/1868792704</v>
       </c>
       <c r="L119" t="str">
-        <v>Do I Wanna Know? - Dove Cameron</v>
+        <v>Una y Otra Vez - Kenia Os</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Una y Otra Vez</v>
+        <v>BAD</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/una-y-otra-vez/1868792926</v>
+        <v>https://music.apple.com/us/song/bad/1869095326</v>
       </c>
       <c r="D120" t="str">
         <v>2026-01-23</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>K de Karma (Apple Music Edition)</v>
+        <v>BAD - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:02</v>
+        <v>2:15</v>
       </c>
       <c r="H120" t="str">
-        <v>Kenia Os</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
+        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/una-y-otra-vez/1868792704</v>
+        <v>https://music.apple.com/us/album/bad/1869095325</v>
       </c>
       <c r="L120" t="str">
-        <v>Una y Otra Vez - Kenia Os</v>
+        <v>BAD - Chelsea Cutler</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>BAD</v>
+        <v>Losing You</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/bad/1869095326</v>
+        <v>https://music.apple.com/us/song/losing-you/1863525495</v>
       </c>
       <c r="D121" t="str">
         <v>2026-01-23</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>BAD - Single</v>
+        <v>F.I.G</v>
       </c>
       <c r="G121" t="str">
-        <v>2:15</v>
+        <v>2:22</v>
       </c>
       <c r="H121" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Naomi Scott</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
+        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/bad/1869095325</v>
+        <v>https://music.apple.com/us/album/losing-you/1863525485</v>
       </c>
       <c r="L121" t="str">
-        <v>BAD - Chelsea Cutler</v>
+        <v>Losing You - Naomi Scott</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Losing You</v>
+        <v>Me Voy A La C******a</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/losing-you/1863525495</v>
+        <v>https://music.apple.com/us/song/me-voy-a-la-c-a/1867850749</v>
       </c>
       <c r="D122" t="str">
         <v>2026-01-23</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>F.I.G</v>
+        <v>Infinito</v>
       </c>
       <c r="G122" t="str">
-        <v>2:22</v>
+        <v>2:14</v>
       </c>
       <c r="H122" t="str">
-        <v>Naomi Scott</v>
+        <v>Yandel</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
+        <v>https://music.apple.com/us/artist/yandel/72929426</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/losing-you/1863525485</v>
+        <v>https://music.apple.com/us/album/me-voy-a-la-c-a/1867850739</v>
       </c>
       <c r="L122" t="str">
-        <v>Losing You - Naomi Scott</v>
+        <v>Me Voy A La C******a - Yandel</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Me Voy A La C******a</v>
+        <v>Sexy For Me</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/me-voy-a-la-c-a/1867850749</v>
+        <v>https://music.apple.com/us/song/sexy-for-me/1867897421</v>
       </c>
       <c r="D123" t="str">
         <v>2026-01-23</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Infinito</v>
+        <v>The Last Dance (Part 1)</v>
       </c>
       <c r="G123" t="str">
-        <v>2:14</v>
+        <v>2:08</v>
       </c>
       <c r="H123" t="str">
-        <v>Yandel</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/yandel/72929426</v>
+        <v>https://music.apple.com/us/artist/jason-derulo/259118085</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/me-voy-a-la-c-a/1867850739</v>
+        <v>https://music.apple.com/us/album/sexy-for-me/1867897420</v>
       </c>
       <c r="L123" t="str">
-        <v>Me Voy A La C******a - Yandel</v>
+        <v>Sexy For Me - Jason Derulo</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Sexy For Me</v>
+        <v>Turbulence</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/sexy-for-me/1867897421</v>
+        <v>https://music.apple.com/us/song/turbulence/1867908449</v>
       </c>
       <c r="D124" t="str">
         <v>2026-01-23</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>The Last Dance (Part 1)</v>
+        <v>REAL, Vol. 1 - EP</v>
       </c>
       <c r="G124" t="str">
-        <v>2:08</v>
+        <v>2:25</v>
       </c>
       <c r="H124" t="str">
-        <v>Jason Derulo</v>
+        <v>Wizkid</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/jason-derulo/259118085</v>
+        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/sexy-for-me/1867897420</v>
+        <v>https://music.apple.com/us/album/turbulence/1867908237</v>
       </c>
       <c r="L124" t="str">
-        <v>Sexy For Me - Jason Derulo</v>
+        <v>Turbulence - Wizkid</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Turbulence</v>
+        <v>I’m Good (From The Movie “GOAT”)</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/turbulence/1867908449</v>
+        <v>https://music.apple.com/us/song/im-good-from-the-movie-goat/1870623298</v>
       </c>
       <c r="D125" t="str">
         <v>2026-01-23</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>REAL, Vol. 1 - EP</v>
+        <v>GOAT (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G125" t="str">
-        <v>2:25</v>
+        <v>2:59</v>
       </c>
       <c r="H125" t="str">
-        <v>Wizkid</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/turbulence/1867908237</v>
+        <v>https://music.apple.com/us/album/im-good-from-the-movie-goat/1870623290</v>
       </c>
       <c r="L125" t="str">
-        <v>Turbulence - Wizkid</v>
+        <v>I’m Good (From The Movie “GOAT”) - Jelly Roll</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>I’m Good (From The Movie “GOAT”)</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/im-good-from-the-movie-goat/1870623298</v>
+        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
       </c>
       <c r="D126" t="str">
         <v>2026-01-23</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>GOAT (Original Motion Picture Soundtrack)</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>2:59</v>
+        <v>3:47</v>
       </c>
       <c r="H126" t="str">
-        <v>Jelly Roll</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/im-good-from-the-movie-goat/1870623290</v>
+        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
       </c>
       <c r="L126" t="str">
-        <v>I’m Good (From The Movie “GOAT”) - Jelly Roll</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
+        <v>ESCONDIDAS</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
+        <v>https://music.apple.com/us/song/escondidas/1860972187</v>
       </c>
       <c r="D127" t="str">
         <v>2026-01-23</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
+        <v>SILENCIO HABLA</v>
       </c>
       <c r="G127" t="str">
-        <v>3:47</v>
+        <v>2:53</v>
       </c>
       <c r="H127" t="str">
-        <v>Dolly Parton</v>
+        <v>Oscar Ortiz</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
+        <v>https://music.apple.com/us/artist/oscar-ortiz/1680604969</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
+        <v>https://music.apple.com/us/album/escondidas/1860972173</v>
       </c>
       <c r="L127" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
+        <v>ESCONDIDAS - Oscar Ortiz</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>ESCONDIDAS</v>
+        <v>Alabama Beauty Queen</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/escondidas/1860972187</v>
+        <v>https://music.apple.com/us/song/alabama-beauty-queen/1846658485</v>
       </c>
       <c r="D128" t="str">
         <v>2026-01-23</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>SILENCIO HABLA</v>
+        <v>Act I</v>
       </c>
       <c r="G128" t="str">
-        <v>2:53</v>
+        <v>3:43</v>
       </c>
       <c r="H128" t="str">
-        <v>Oscar Ortiz</v>
+        <v>Kashus Culpepper</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/oscar-ortiz/1680604969</v>
+        <v>https://music.apple.com/us/artist/kashus-culpepper/1634883369</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/escondidas/1860972173</v>
+        <v>https://music.apple.com/us/album/alabama-beauty-queen/1846658477</v>
       </c>
       <c r="L128" t="str">
-        <v>ESCONDIDAS - Oscar Ortiz</v>
+        <v>Alabama Beauty Queen - Kashus Culpepper</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Alabama Beauty Queen</v>
+        <v>Imposter</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/alabama-beauty-queen/1846658485</v>
+        <v>https://music.apple.com/us/song/imposter/1842408050</v>
       </c>
       <c r="D129" t="str">
         <v>2026-01-23</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Act I</v>
+        <v>How Did I Get Here?</v>
       </c>
       <c r="G129" t="str">
-        <v>3:43</v>
+        <v>2:38</v>
       </c>
       <c r="H129" t="str">
-        <v>Kashus Culpepper</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/kashus-culpepper/1634883369</v>
+        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/alabama-beauty-queen/1846658477</v>
+        <v>https://music.apple.com/us/album/imposter/1842408037</v>
       </c>
       <c r="L129" t="str">
-        <v>Alabama Beauty Queen - Kashus Culpepper</v>
+        <v>Imposter - Louis Tomlinson</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Imposter</v>
+        <v>Puddles (Zero 7 Remix)</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/imposter/1842408050</v>
+        <v>https://music.apple.com/us/song/puddles-zero-7-remix/1869474314</v>
       </c>
       <c r="D130" t="str">
         <v>2026-01-23</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>How Did I Get Here?</v>
+        <v>Puddles (Zero 7 Remix) - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>2:38</v>
+        <v>6:01</v>
       </c>
       <c r="H130" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Not for Radio</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
+        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/imposter/1842408037</v>
+        <v>https://music.apple.com/us/album/puddles-zero-7-remix/1869474313</v>
       </c>
       <c r="L130" t="str">
-        <v>Imposter - Louis Tomlinson</v>
+        <v>Puddles (Zero 7 Remix) - Not for Radio</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Puddles (Zero 7 Remix)</v>
+        <v>Little Miss (Misdemeanor)</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/puddles-zero-7-remix/1869474314</v>
+        <v>https://music.apple.com/us/song/little-miss-misdemeanor/1870996491</v>
       </c>
       <c r="D131" t="str">
         <v>2026-01-23</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Puddles (Zero 7 Remix) - Single</v>
+        <v>Little Miss (Misdemeanor) - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>6:01</v>
+        <v>2:24</v>
       </c>
       <c r="H131" t="str">
-        <v>Not for Radio</v>
+        <v>GIRLSET</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
+        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/puddles-zero-7-remix/1869474313</v>
+        <v>https://music.apple.com/us/album/little-miss-misdemeanor/1870996490</v>
       </c>
       <c r="L131" t="str">
-        <v>Puddles (Zero 7 Remix) - Not for Radio</v>
+        <v>Little Miss (Misdemeanor) - GIRLSET</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Little Miss (Misdemeanor)</v>
+        <v>I Could Get Used To This</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/little-miss-misdemeanor/1870996491</v>
+        <v>https://music.apple.com/us/song/i-could-get-used-to-this/1867222996</v>
       </c>
       <c r="D132" t="str">
         <v>2026-01-23</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Little Miss (Misdemeanor) - Single</v>
+        <v>I Could Get Used To This - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>2:24</v>
+        <v>3:41</v>
       </c>
       <c r="H132" t="str">
-        <v>GIRLSET</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/little-miss-misdemeanor/1870996490</v>
+        <v>https://music.apple.com/us/album/i-could-get-used-to-this/1867222992</v>
       </c>
       <c r="L132" t="str">
-        <v>Little Miss (Misdemeanor) - GIRLSET</v>
+        <v>I Could Get Used To This - Jessie Ware</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>I Could Get Used To This</v>
+        <v>LA VILLA</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/i-could-get-used-to-this/1867222996</v>
+        <v>https://music.apple.com/us/song/la-villa/1847678152</v>
       </c>
       <c r="D133" t="str">
         <v>2026-01-23</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>I Could Get Used To This - Single</v>
+        <v>HOPI SENDÉ</v>
       </c>
       <c r="G133" t="str">
-        <v>3:41</v>
+        <v>3:12</v>
       </c>
       <c r="H133" t="str">
-        <v>Jessie Ware</v>
+        <v>Ryan Castro</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/ryan-castro/1263552447</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/i-could-get-used-to-this/1867222992</v>
+        <v>https://music.apple.com/us/album/la-villa/1847678143</v>
       </c>
       <c r="L133" t="str">
-        <v>I Could Get Used To This - Jessie Ware</v>
+        <v>LA VILLA - Ryan Castro</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>LA VILLA</v>
+        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700)</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/la-villa/1847678152</v>
+        <v>https://music.apple.com/us/song/lit-effect-feat-bktherula-lazer-dim-700/1868519613</v>
       </c>
       <c r="D134" t="str">
         <v>2026-01-23</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>HOPI SENDÉ</v>
+        <v>Strictly 4 The Scythe</v>
       </c>
       <c r="G134" t="str">
-        <v>3:12</v>
+        <v>3:27</v>
       </c>
       <c r="H134" t="str">
-        <v>Ryan Castro</v>
+        <v>Denzel Curry</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/ryan-castro/1263552447</v>
+        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/la-villa/1847678143</v>
+        <v>https://music.apple.com/us/album/lit-effect-feat-bktherula-lazer-dim-700/1868519270</v>
       </c>
       <c r="L134" t="str">
-        <v>LA VILLA - Ryan Castro</v>
+        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700) - Denzel Curry</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700)</v>
+        <v>Thick One</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/lit-effect-feat-bktherula-lazer-dim-700/1868519613</v>
+        <v>https://music.apple.com/us/song/thick-one/1868515478</v>
       </c>
       <c r="D135" t="str">
         <v>2026-01-23</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Strictly 4 The Scythe</v>
+        <v>Part 3</v>
       </c>
       <c r="G135" t="str">
-        <v>3:27</v>
+        <v>2:49</v>
       </c>
       <c r="H135" t="str">
-        <v>Denzel Curry</v>
+        <v>42 Dugg</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
+        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/lit-effect-feat-bktherula-lazer-dim-700/1868519270</v>
+        <v>https://music.apple.com/us/album/thick-one/1868515223</v>
       </c>
       <c r="L135" t="str">
-        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700) - Denzel Curry</v>
+        <v>Thick One - 42 Dugg</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Thick One</v>
+        <v>How Much Did You Get For Your Soul</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/thick-one/1868515478</v>
+        <v>https://music.apple.com/us/song/how-much-did-you-get-for-your-soul/1843195678</v>
       </c>
       <c r="D136" t="str">
         <v>2026-01-23</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Part 3</v>
+        <v>World's Gone Wrong</v>
       </c>
       <c r="G136" t="str">
-        <v>2:49</v>
+        <v>3:59</v>
       </c>
       <c r="H136" t="str">
-        <v>42 Dugg</v>
+        <v>Lucinda Williams</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
+        <v>https://music.apple.com/us/artist/lucinda-williams/267658</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/thick-one/1868515223</v>
+        <v>https://music.apple.com/us/album/how-much-did-you-get-for-your-soul/1843195660</v>
       </c>
       <c r="L136" t="str">
-        <v>Thick One - 42 Dugg</v>
+        <v>How Much Did You Get For Your Soul - Lucinda Williams</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>How Much Did You Get For Your Soul</v>
+        <v>THUM</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/how-much-did-you-get-for-your-soul/1843195678</v>
+        <v>https://music.apple.com/us/song/thum/1863009362</v>
       </c>
       <c r="D137" t="str">
         <v>2026-01-23</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>World's Gone Wrong</v>
+        <v>THUM - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>3:59</v>
+        <v>2:11</v>
       </c>
       <c r="H137" t="str">
-        <v>Lucinda Williams</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/lucinda-williams/267658</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/how-much-did-you-get-for-your-soul/1843195660</v>
+        <v>https://music.apple.com/us/album/thum/1863009357</v>
       </c>
       <c r="L137" t="str">
-        <v>How Much Did You Get For Your Soul - Lucinda Williams</v>
+        <v>THUM - Violet Grohl</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>THUM</v>
+        <v>(I'm a) Rock "N" Roller</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/thum/1863009362</v>
+        <v>https://music.apple.com/us/song/im-a-rock-n-roller/1839888014</v>
       </c>
       <c r="D138" t="str">
         <v>2026-01-23</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>THUM - Single</v>
+        <v>The Great Satan</v>
       </c>
       <c r="G138" t="str">
-        <v>2:11</v>
+        <v>3:32</v>
       </c>
       <c r="H138" t="str">
-        <v>Violet Grohl</v>
+        <v>Rob Zombie</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/thum/1863009357</v>
+        <v>https://music.apple.com/us/album/im-a-rock-n-roller/1839887790</v>
       </c>
       <c r="L138" t="str">
-        <v>THUM - Violet Grohl</v>
+        <v>(I'm a) Rock "N" Roller - Rob Zombie</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>(I'm a) Rock "N" Roller</v>
+        <v>Excuses For Love</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/im-a-rock-n-roller/1839888014</v>
+        <v>https://music.apple.com/us/song/excuses-for-love/1856034295</v>
       </c>
       <c r="D139" t="str">
         <v>2026-01-23</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>The Great Satan</v>
+        <v>Hyperlove</v>
       </c>
       <c r="G139" t="str">
-        <v>3:32</v>
+        <v>3:04</v>
       </c>
       <c r="H139" t="str">
-        <v>Rob Zombie</v>
+        <v>MIKA</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
+        <v>https://music.apple.com/us/artist/mika/184932871</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/im-a-rock-n-roller/1839887790</v>
+        <v>https://music.apple.com/us/album/excuses-for-love/1856033810</v>
       </c>
       <c r="L139" t="str">
-        <v>(I'm a) Rock "N" Roller - Rob Zombie</v>
+        <v>Excuses For Love - MIKA</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Excuses For Love</v>
+        <v>3 Tears</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/excuses-for-love/1856034295</v>
+        <v>https://music.apple.com/us/song/3-tears/1861504548</v>
       </c>
       <c r="D140" t="str">
         <v>2026-01-23</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Hyperlove</v>
+        <v>3 Tears - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:04</v>
+        <v>2:50</v>
       </c>
       <c r="H140" t="str">
-        <v>MIKA</v>
+        <v>Mergui</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/mika/184932871</v>
+        <v>https://music.apple.com/us/artist/mergui/1423596903</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/excuses-for-love/1856033810</v>
+        <v>https://music.apple.com/us/album/3-tears/1861504545</v>
       </c>
       <c r="L140" t="str">
-        <v>Excuses For Love - MIKA</v>
+        <v>3 Tears - Mergui</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>3 Tears</v>
+        <v>Church Girl</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/3-tears/1861504548</v>
+        <v>https://music.apple.com/us/song/church-girl/1862008542</v>
       </c>
       <c r="D141" t="str">
         <v>2026-01-23</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>3 Tears - Single</v>
+        <v>Church Girl - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>2:50</v>
+        <v>3:19</v>
       </c>
       <c r="H141" t="str">
-        <v>Mergui</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/mergui/1423596903</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/3-tears/1861504545</v>
+        <v>https://music.apple.com/us/album/church-girl/1862008535</v>
       </c>
       <c r="L141" t="str">
-        <v>3 Tears - Mergui</v>
+        <v>Church Girl - Carly Pearce</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Church Girl</v>
+        <v>Funeral</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/church-girl/1862008542</v>
+        <v>https://music.apple.com/us/song/funeral/1867616928</v>
       </c>
       <c r="D142" t="str">
         <v>2026-01-23</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Church Girl - Single</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G142" t="str">
-        <v>3:19</v>
+        <v>4:03</v>
       </c>
       <c r="H142" t="str">
-        <v>Carly Pearce</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/church-girl/1862008535</v>
+        <v>https://music.apple.com/us/album/funeral/1867616617</v>
       </c>
       <c r="L142" t="str">
-        <v>Church Girl - Carly Pearce</v>
+        <v>Funeral - Dermot Kennedy</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Funeral</v>
+        <v>Say Yes</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/funeral/1867616928</v>
+        <v>https://music.apple.com/us/song/say-yes/1861995090</v>
       </c>
       <c r="D143" t="str">
         <v>2026-01-23</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>The Weight of the Woods</v>
+        <v>Say Yes - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>4:03</v>
+        <v>2:50</v>
       </c>
       <c r="H143" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Marques Anthony</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/marques-anthony/321321231</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/funeral/1867616617</v>
+        <v>https://music.apple.com/us/album/say-yes/1861995089</v>
       </c>
       <c r="L143" t="str">
-        <v>Funeral - Dermot Kennedy</v>
+        <v>Say Yes - Marques Anthony</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Say Yes</v>
+        <v>LOVE ME (feat. Stevie Wonder)</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/say-yes/1861995090</v>
+        <v>https://music.apple.com/us/song/love-me-feat-stevie-wonder/1867640879</v>
       </c>
       <c r="D144" t="str">
         <v>2026-01-23</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Say Yes - Single</v>
+        <v>CAMPILATION</v>
       </c>
       <c r="G144" t="str">
-        <v>2:50</v>
+        <v>3:10</v>
       </c>
       <c r="H144" t="str">
-        <v>Marques Anthony</v>
+        <v>Camper</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/marques-anthony/321321231</v>
+        <v>https://music.apple.com/us/artist/camper/1514886616</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/say-yes/1861995089</v>
+        <v>https://music.apple.com/us/album/love-me-feat-stevie-wonder/1867640873</v>
       </c>
       <c r="L144" t="str">
-        <v>Say Yes - Marques Anthony</v>
+        <v>LOVE ME (feat. Stevie Wonder) - Camper</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>LOVE ME (feat. Stevie Wonder)</v>
+        <v>UP TO MY NECK IN U</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/love-me-feat-stevie-wonder/1867640879</v>
+        <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
       </c>
       <c r="D145" t="str">
         <v>2026-01-23</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>CAMPILATION</v>
+        <v>UP TO MY NECK IN U - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:10</v>
+        <v>2:17</v>
       </c>
       <c r="H145" t="str">
-        <v>Camper</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/camper/1514886616</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/love-me-feat-stevie-wonder/1867640873</v>
+        <v>https://music.apple.com/us/album/up-to-my-neck-in-u/1862550671</v>
       </c>
       <c r="L145" t="str">
-        <v>LOVE ME (feat. Stevie Wonder) - Camper</v>
+        <v>UP TO MY NECK IN U - Ledbyher</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>UP TO MY NECK IN U</v>
+        <v>Wallflower</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
+        <v>https://music.apple.com/us/song/wallflower/1862737077</v>
       </c>
       <c r="D146" t="str">
         <v>2026-01-23</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>UP TO MY NECK IN U - Single</v>
+        <v>Wallflower - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>2:17</v>
+        <v>3:25</v>
       </c>
       <c r="H146" t="str">
-        <v>Ledbyher</v>
+        <v>Sikarus</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
+        <v>https://music.apple.com/us/artist/sikarus/1046558781</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/up-to-my-neck-in-u/1862550671</v>
+        <v>https://music.apple.com/us/album/wallflower/1862737074</v>
       </c>
       <c r="L146" t="str">
-        <v>UP TO MY NECK IN U - Ledbyher</v>
+        <v>Wallflower - Sikarus</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Wallflower</v>
+        <v>You Phase</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/wallflower/1862737077</v>
+        <v>https://music.apple.com/us/song/you-phase/1868861897</v>
       </c>
       <c r="D147" t="str">
         <v>2026-01-23</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Wallflower - Single</v>
+        <v>You Phase - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:25</v>
+        <v>2:51</v>
       </c>
       <c r="H147" t="str">
-        <v>Sikarus</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/sikarus/1046558781</v>
+        <v>https://music.apple.com/us/artist/mitchell-tenpenny/430369368</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/wallflower/1862737074</v>
+        <v>https://music.apple.com/us/album/you-phase/1868861895</v>
       </c>
       <c r="L147" t="str">
-        <v>Wallflower - Sikarus</v>
+        <v>You Phase - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>You Phase</v>
+        <v>Miss Independent</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/you-phase/1868861897</v>
+        <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
       </c>
       <c r="D148" t="str">
         <v>2026-01-23</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>You Phase - Single</v>
+        <v>Miss Independent - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>2:51</v>
+        <v>2:40</v>
       </c>
       <c r="H148" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/mitchell-tenpenny/430369368</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/you-phase/1868861895</v>
+        <v>https://music.apple.com/us/album/miss-independent/1870612555</v>
       </c>
       <c r="L148" t="str">
-        <v>You Phase - Mitchell Tenpenny</v>
+        <v>Miss Independent - 1Ski OG</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Miss Independent</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown)</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
+        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown/1870678482</v>
       </c>
       <c r="D149" t="str">
         <v>2026-01-23</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Miss Independent - Single</v>
+        <v>SO BE IT</v>
       </c>
       <c r="G149" t="str">
-        <v>2:40</v>
+        <v>5:47</v>
       </c>
       <c r="H149" t="str">
-        <v>1Ski OG</v>
+        <v>Elevation Worship</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/miss-independent/1870612555</v>
+        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown/1870678481</v>
       </c>
       <c r="L149" t="str">
-        <v>Miss Independent - 1Ski OG</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) - Elevation Worship</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown)</v>
+        <v>go again</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown/1870678482</v>
+        <v>https://music.apple.com/us/song/go-again/1868987466</v>
       </c>
       <c r="D150" t="str">
         <v>2026-01-23</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>SO BE IT</v>
+        <v>go again - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>5:47</v>
+        <v>2:07</v>
       </c>
       <c r="H150" t="str">
-        <v>Elevation Worship</v>
+        <v>NateTaylorr</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
+        <v>https://music.apple.com/us/artist/natetaylorr/1243682934</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown/1870678481</v>
+        <v>https://music.apple.com/us/album/go-again/1868987193</v>
       </c>
       <c r="L150" t="str">
-        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) - Elevation Worship</v>
+        <v>go again - NateTaylorr</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>go again</v>
+        <v>Autopilot</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/go-again/1868987466</v>
+        <v>https://music.apple.com/us/song/autopilot/1863072399</v>
       </c>
       <c r="D151" t="str">
         <v>2026-01-23</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>go again - Single</v>
+        <v>Autopilot</v>
       </c>
       <c r="G151" t="str">
-        <v>2:07</v>
+        <v>2:46</v>
       </c>
       <c r="H151" t="str">
-        <v>NateTaylorr</v>
+        <v>ALEXSUCKS</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/natetaylorr/1243682934</v>
+        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/go-again/1868987193</v>
+        <v>https://music.apple.com/us/album/autopilot/1863072393</v>
       </c>
       <c r="L151" t="str">
-        <v>go again - NateTaylorr</v>
+        <v>Autopilot - ALEXSUCKS</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Autopilot</v>
+        <v>Portrait of My Heart (feat. Brendan Yates)</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/autopilot/1863072399</v>
+        <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
       </c>
       <c r="D152" t="str">
         <v>2026-01-23</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Autopilot</v>
+        <v>Portrait of My Heart - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>2:46</v>
+        <v>3:04</v>
       </c>
       <c r="H152" t="str">
-        <v>ALEXSUCKS</v>
+        <v>SPELLLING</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
+        <v>https://music.apple.com/us/artist/spellling/1281213673</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/autopilot/1863072393</v>
+        <v>https://music.apple.com/us/album/portrait-of-my-heart-feat-brendan-yates/1862282167</v>
       </c>
       <c r="L152" t="str">
-        <v>Autopilot - ALEXSUCKS</v>
+        <v>Portrait of My Heart (feat. Brendan Yates) - SPELLLING</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Portrait of My Heart (feat. Brendan Yates)</v>
+        <v>In Violet</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
+        <v>https://music.apple.com/us/song/in-violet/1839471290</v>
       </c>
       <c r="D153" t="str">
         <v>2026-01-23</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Portrait of My Heart - Single</v>
+        <v>Death in the Business of Whaling</v>
       </c>
       <c r="G153" t="str">
-        <v>3:04</v>
+        <v>4:09</v>
       </c>
       <c r="H153" t="str">
-        <v>SPELLLING</v>
+        <v>Searows</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/spellling/1281213673</v>
+        <v>https://music.apple.com/us/artist/searows/1607240507</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/portrait-of-my-heart-feat-brendan-yates/1862282167</v>
+        <v>https://music.apple.com/us/album/in-violet/1839470844</v>
       </c>
       <c r="L153" t="str">
-        <v>Portrait of My Heart (feat. Brendan Yates) - SPELLLING</v>
+        <v>In Violet - Searows</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>In Violet</v>
+        <v>Baby Run</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/in-violet/1839471290</v>
+        <v>https://music.apple.com/us/song/baby-run/1857658819</v>
       </c>
       <c r="D154" t="str">
         <v>2026-01-23</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Death in the Business of Whaling</v>
+        <v>Baby Run - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>4:09</v>
+        <v>4:47</v>
       </c>
       <c r="H154" t="str">
-        <v>Searows</v>
+        <v>Jimi Jules</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/searows/1607240507</v>
+        <v>https://music.apple.com/us/artist/jimi-jules/586933009</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/in-violet/1839470844</v>
+        <v>https://music.apple.com/us/album/baby-run/1857658816</v>
       </c>
       <c r="L154" t="str">
-        <v>In Violet - Searows</v>
+        <v>Baby Run - Jimi Jules</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Baby Run</v>
+        <v>What If We Don't</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/baby-run/1857658819</v>
+        <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
       </c>
       <c r="D155" t="str">
         <v>2026-01-23</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Baby Run - Single</v>
+        <v>What If We Don't - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>4:47</v>
+        <v>3:06</v>
       </c>
       <c r="H155" t="str">
-        <v>Jimi Jules</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/jimi-jules/586933009</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/baby-run/1857658816</v>
+        <v>https://music.apple.com/us/album/what-if-we-dont/1862668776</v>
       </c>
       <c r="L155" t="str">
-        <v>Baby Run - Jimi Jules</v>
+        <v>What If We Don't - Ashley McBryde</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>What If We Don't</v>
+        <v>Hagamos Que</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
+        <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
       </c>
       <c r="D156" t="str">
         <v>2026-01-23</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>What If We Don't - Single</v>
+        <v>Hagamos Que - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:06</v>
+        <v>2:58</v>
       </c>
       <c r="H156" t="str">
-        <v>Ashley McBryde</v>
+        <v>Juanes</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/juanes/103856</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/what-if-we-dont/1862668776</v>
+        <v>https://music.apple.com/us/album/hagamos-que/1861956611</v>
       </c>
       <c r="L156" t="str">
-        <v>What If We Don't - Ashley McBryde</v>
+        <v>Hagamos Que - Juanes</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Hagamos Que</v>
+        <v>World Change Me</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
+        <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
       </c>
       <c r="D157" t="str">
         <v>2026-01-23</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Hagamos Que - Single</v>
+        <v>World Change Me - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>2:58</v>
+        <v>3:03</v>
       </c>
       <c r="H157" t="str">
-        <v>Juanes</v>
+        <v>Max McNown</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/juanes/103856</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/hagamos-que/1861956611</v>
+        <v>https://music.apple.com/us/album/world-change-me/1860974598</v>
       </c>
       <c r="L157" t="str">
-        <v>Hagamos Que - Juanes</v>
+        <v>World Change Me - Max McNown</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>World Change Me</v>
+        <v>Exclusive</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
+        <v>https://music.apple.com/us/song/exclusive/1851537672</v>
       </c>
       <c r="D158" t="str">
         <v>2026-01-23</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>World Change Me - Single</v>
+        <v>Exclusive - EP</v>
       </c>
       <c r="G158" t="str">
-        <v>3:03</v>
+        <v>3:20</v>
       </c>
       <c r="H158" t="str">
-        <v>Max McNown</v>
+        <v>Hudson Westbrook</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/world-change-me/1860974598</v>
+        <v>https://music.apple.com/us/album/exclusive/1851537671</v>
       </c>
       <c r="L158" t="str">
-        <v>World Change Me - Max McNown</v>
+        <v>Exclusive - Hudson Westbrook</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Exclusive</v>
+        <v>Say Less</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/exclusive/1851537672</v>
+        <v>https://music.apple.com/us/song/say-less/1867910122</v>
       </c>
       <c r="D159" t="str">
         <v>2026-01-23</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Exclusive - EP</v>
+        <v>Say Less - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:20</v>
+        <v>2:18</v>
       </c>
       <c r="H159" t="str">
-        <v>Hudson Westbrook</v>
+        <v>JYT</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
+        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/exclusive/1851537671</v>
+        <v>https://music.apple.com/us/album/say-less/1867910115</v>
       </c>
       <c r="L159" t="str">
-        <v>Exclusive - Hudson Westbrook</v>
+        <v>Say Less - JYT</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Say Less</v>
+        <v>Angels Cry</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/say-less/1867910122</v>
+        <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
       </c>
       <c r="D160" t="str">
         <v>2026-01-23</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Say Less - Single</v>
+        <v>X's for Eyes (Deluxe)</v>
       </c>
       <c r="G160" t="str">
-        <v>2:18</v>
+        <v>3:52</v>
       </c>
       <c r="H160" t="str">
-        <v>JYT</v>
+        <v>The Red Jumpsuit Apparatus</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
+        <v>https://music.apple.com/us/artist/the-red-jumpsuit-apparatus/130037074</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/say-less/1867910115</v>
+        <v>https://music.apple.com/us/album/angels-cry/1862320872</v>
       </c>
       <c r="L160" t="str">
-        <v>Say Less - JYT</v>
+        <v>Angels Cry - The Red Jumpsuit Apparatus</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Angels Cry</v>
+        <v>Over You</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
+        <v>https://music.apple.com/us/song/over-you/1846189473</v>
       </c>
       <c r="D161" t="str">
         <v>2026-01-23</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>X's for Eyes (Deluxe)</v>
+        <v>A Love For Strangers</v>
       </c>
       <c r="G161" t="str">
-        <v>3:52</v>
+        <v>4:44</v>
       </c>
       <c r="H161" t="str">
-        <v>The Red Jumpsuit Apparatus</v>
+        <v>Chet Faker</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/the-red-jumpsuit-apparatus/130037074</v>
+        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/angels-cry/1862320872</v>
+        <v>https://music.apple.com/us/album/over-you/1846189472</v>
       </c>
       <c r="L161" t="str">
-        <v>Angels Cry - The Red Jumpsuit Apparatus</v>
+        <v>Over You - Chet Faker</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Over You</v>
+        <v>Chala (My Soul Is on a Loop)</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/over-you/1846189473</v>
+        <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
       </c>
       <c r="D162" t="str">
         <v>2026-01-23</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>A Love For Strangers</v>
+        <v>Chala (My Soul Is on a Loop) - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>4:44</v>
+        <v>2:42</v>
       </c>
       <c r="H162" t="str">
-        <v>Chet Faker</v>
+        <v>Barry Can't Swim</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
+        <v>https://music.apple.com/us/artist/barry-cant-swim/1492752064</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/over-you/1846189472</v>
+        <v>https://music.apple.com/us/album/chala-my-soul-is-on-a-loop/1857789040</v>
       </c>
       <c r="L162" t="str">
-        <v>Over You - Chet Faker</v>
+        <v>Chala (My Soul Is on a Loop) - Barry Can't Swim</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Chala (My Soul Is on a Loop)</v>
+        <v>starlight feat. Madeline Follin</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
+        <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
       </c>
       <c r="D163" t="str">
         <v>2026-01-23</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Chala (My Soul Is on a Loop) - Single</v>
+        <v>starlight feat. Madeline Follin - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>2:42</v>
+        <v>3:06</v>
       </c>
       <c r="H163" t="str">
-        <v>Barry Can't Swim</v>
+        <v>Disco Lines</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/barry-cant-swim/1492752064</v>
+        <v>https://music.apple.com/us/artist/disco-lines/1462793893</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/chala-my-soul-is-on-a-loop/1857789040</v>
+        <v>https://music.apple.com/us/album/starlight-feat-madeline-follin/1869330767</v>
       </c>
       <c r="L163" t="str">
-        <v>Chala (My Soul Is on a Loop) - Barry Can't Swim</v>
+        <v>starlight feat. Madeline Follin - Disco Lines</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>starlight feat. Madeline Follin</v>
+        <v>Locked In (feat. Trippie Redd)</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
+        <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
       </c>
       <c r="D164" t="str">
         <v>2026-01-23</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>starlight feat. Madeline Follin - Single</v>
+        <v>Locked In (feat. Trippie Redd) - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:06</v>
+        <v>2:48</v>
       </c>
       <c r="H164" t="str">
-        <v>Disco Lines</v>
+        <v>David Guetta</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/disco-lines/1462793893</v>
+        <v>https://music.apple.com/us/artist/david-guetta/5557599</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/starlight-feat-madeline-follin/1869330767</v>
+        <v>https://music.apple.com/us/album/locked-in-feat-trippie-redd/1869439982</v>
       </c>
       <c r="L164" t="str">
-        <v>starlight feat. Madeline Follin - Disco Lines</v>
+        <v>Locked In (feat. Trippie Redd) - David Guetta</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Locked In (feat. Trippie Redd)</v>
+        <v>Rejoice</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
+        <v>https://music.apple.com/us/song/rejoice/1862633596</v>
       </c>
       <c r="D165" t="str">
         <v>2026-01-23</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Locked In (feat. Trippie Redd) - Single</v>
+        <v>Rejoice - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>2:48</v>
+        <v>4:20</v>
       </c>
       <c r="H165" t="str">
-        <v>David Guetta</v>
+        <v>Def Leppard</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/david-guetta/5557599</v>
+        <v>https://music.apple.com/us/artist/def-leppard/117554</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/locked-in-feat-trippie-redd/1869439982</v>
+        <v>https://music.apple.com/us/album/rejoice/1862633593</v>
       </c>
       <c r="L165" t="str">
-        <v>Locked In (feat. Trippie Redd) - David Guetta</v>
+        <v>Rejoice - Def Leppard</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Rejoice</v>
+        <v>Slight Werk (feat. Bree Runway) [Club Mix]</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/rejoice/1862633596</v>
+        <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
       </c>
       <c r="D166" t="str">
         <v>2026-01-23</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Rejoice - Single</v>
+        <v>Slight Werk (Club Mix) [feat. Bree Runway] - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>4:20</v>
+        <v>2:58</v>
       </c>
       <c r="H166" t="str">
-        <v>Def Leppard</v>
+        <v>Honey Dijon</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/def-leppard/117554</v>
+        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/rejoice/1862633593</v>
+        <v>https://music.apple.com/us/album/slight-werk-feat-bree-runway-club-mix/1860859551</v>
       </c>
       <c r="L166" t="str">
-        <v>Rejoice - Def Leppard</v>
+        <v>Slight Werk (feat. Bree Runway) [Club Mix] - Honey Dijon</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Slight Werk (feat. Bree Runway) [Club Mix]</v>
+        <v>Lucky Day</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
+        <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
       </c>
       <c r="D167" t="str">
         <v>2026-01-23</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Slight Werk (Club Mix) [feat. Bree Runway] - Single</v>
+        <v>Speed Kills</v>
       </c>
       <c r="G167" t="str">
-        <v>2:58</v>
+        <v>3:13</v>
       </c>
       <c r="H167" t="str">
-        <v>Honey Dijon</v>
+        <v>Ally Evenson</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
+        <v>https://music.apple.com/us/artist/ally-evenson/283908113</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/slight-werk-feat-bree-runway-club-mix/1860859551</v>
+        <v>https://music.apple.com/us/album/lucky-day/1849264498</v>
       </c>
       <c r="L167" t="str">
-        <v>Slight Werk (feat. Bree Runway) [Club Mix] - Honey Dijon</v>
+        <v>Lucky Day - Ally Evenson</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Lucky Day</v>
+        <v>Breathe On It</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
+        <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
       </c>
       <c r="D168" t="str">
         <v>2026-01-23</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Speed Kills</v>
+        <v>Breathe On It - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:13</v>
+        <v>4:00</v>
       </c>
       <c r="H168" t="str">
-        <v>Ally Evenson</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/ally-evenson/283908113</v>
+        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/lucky-day/1849264498</v>
+        <v>https://music.apple.com/us/album/breathe-on-it/1862938798</v>
       </c>
       <c r="L168" t="str">
-        <v>Lucky Day - Ally Evenson</v>
+        <v>Breathe On It - Tauren Wells</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Breathe On It</v>
+        <v>Easy</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
+        <v>https://music.apple.com/us/song/easy/1863456906</v>
       </c>
       <c r="D169" t="str">
         <v>2026-01-23</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Breathe On It - Single</v>
+        <v>Easy - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>4:00</v>
+        <v>4:30</v>
       </c>
       <c r="H169" t="str">
-        <v>Tauren Wells</v>
+        <v>lydi lynn</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
+        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/breathe-on-it/1862938798</v>
+        <v>https://music.apple.com/us/album/easy/1863456903</v>
       </c>
       <c r="L169" t="str">
-        <v>Breathe On It - Tauren Wells</v>
+        <v>Easy - lydi lynn</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Easy</v>
+        <v>Break Me In</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/easy/1863456906</v>
+        <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
       </c>
       <c r="D170" t="str">
         <v>2026-01-23</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Easy - Single</v>
+        <v>Break Me In - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>4:30</v>
+        <v>2:52</v>
       </c>
       <c r="H170" t="str">
-        <v>lydi lynn</v>
+        <v>Joyce Wrice</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
+        <v>https://music.apple.com/us/artist/joyce-wrice/591991458</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/easy/1863456903</v>
+        <v>https://music.apple.com/us/album/break-me-in/1862881766</v>
       </c>
       <c r="L170" t="str">
-        <v>Easy - lydi lynn</v>
+        <v>Break Me In - Joyce Wrice</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Break Me In</v>
+        <v>Long Live Love</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
+        <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
       </c>
       <c r="D171" t="str">
         <v>2026-01-23</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Break Me In - Single</v>
+        <v>Long Live Love - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:52</v>
+        <v>2:36</v>
       </c>
       <c r="H171" t="str">
-        <v>Joyce Wrice</v>
+        <v>Sugar</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/joyce-wrice/591991458</v>
+        <v>https://music.apple.com/us/artist/sugar/530175867</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/break-me-in/1862881766</v>
+        <v>https://music.apple.com/us/album/long-live-love/1851251226</v>
       </c>
       <c r="L171" t="str">
-        <v>Break Me In - Joyce Wrice</v>
+        <v>Long Live Love - Sugar</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Long Live Love</v>
+        <v>Depressed</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
+        <v>https://music.apple.com/us/song/depressed/1840400522</v>
       </c>
       <c r="D172" t="str">
         <v>2026-01-23</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Long Live Love - Single</v>
+        <v>Boycott Heaven</v>
       </c>
       <c r="G172" t="str">
-        <v>2:36</v>
+        <v>3:32</v>
       </c>
       <c r="H172" t="str">
-        <v>Sugar</v>
+        <v>The Format</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/sugar/530175867</v>
+        <v>https://music.apple.com/us/artist/the-format/3064903</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/long-live-love/1851251226</v>
+        <v>https://music.apple.com/us/album/depressed/1840399886</v>
       </c>
       <c r="L172" t="str">
-        <v>Long Live Love - Sugar</v>
+        <v>Depressed - The Format</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Depressed</v>
+        <v>Empty Hands</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/depressed/1840400522</v>
+        <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
       </c>
       <c r="D173" t="str">
         <v>2026-01-23</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Boycott Heaven</v>
+        <v>Empty Hands</v>
       </c>
       <c r="G173" t="str">
-        <v>3:32</v>
+        <v>3:09</v>
       </c>
       <c r="H173" t="str">
-        <v>The Format</v>
+        <v>Poppy</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/the-format/3064903</v>
+        <v>https://music.apple.com/us/artist/poppy/1004130511</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/depressed/1840399886</v>
+        <v>https://music.apple.com/us/album/empty-hands/1852046141</v>
       </c>
       <c r="L173" t="str">
-        <v>Depressed - The Format</v>
+        <v>Empty Hands - Poppy</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Empty Hands</v>
+        <v>The Long Surrender</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
+        <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
       </c>
       <c r="D174" t="str">
         <v>2026-01-23</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Empty Hands</v>
+        <v>The Long Surrender</v>
       </c>
       <c r="G174" t="str">
-        <v>3:09</v>
+        <v>3:45</v>
       </c>
       <c r="H174" t="str">
-        <v>Poppy</v>
+        <v>NEEDTOBREATHE</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/poppy/1004130511</v>
+        <v>https://music.apple.com/us/artist/needtobreathe/113247214</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/empty-hands/1852046141</v>
+        <v>https://music.apple.com/us/album/the-long-surrender/1861935699</v>
       </c>
       <c r="L174" t="str">
-        <v>Empty Hands - Poppy</v>
+        <v>The Long Surrender - NEEDTOBREATHE</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>The Long Surrender</v>
+        <v>Angela</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
+        <v>https://music.apple.com/us/song/angela/1866624257</v>
       </c>
       <c r="D175" t="str">
         <v>2026-01-23</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>The Long Surrender</v>
+        <v>Angela - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>3:45</v>
+        <v>3:32</v>
       </c>
       <c r="H175" t="str">
-        <v>NEEDTOBREATHE</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/needtobreathe/113247214</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/the-long-surrender/1861935699</v>
+        <v>https://music.apple.com/us/album/angela/1866624256</v>
       </c>
       <c r="L175" t="str">
-        <v>The Long Surrender - NEEDTOBREATHE</v>
+        <v>Angela - Hayden Everett</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Angela</v>
+        <v>Disappear</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/angela/1866624257</v>
+        <v>https://music.apple.com/us/song/disappear/1847663553</v>
       </c>
       <c r="D176" t="str">
         <v>2026-01-23</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Angela - Single</v>
+        <v>Greyhound</v>
       </c>
       <c r="G176" t="str">
-        <v>3:32</v>
+        <v>3:31</v>
       </c>
       <c r="H176" t="str">
-        <v>Hayden Everett</v>
+        <v>Katie Tupper</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/katie-tupper/1395542470</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/angela/1866624256</v>
+        <v>https://music.apple.com/us/album/disappear/1847663546</v>
       </c>
       <c r="L176" t="str">
-        <v>Angela - Hayden Everett</v>
+        <v>Disappear - Katie Tupper</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Disappear</v>
+        <v>Catapult</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/disappear/1847663553</v>
+        <v>https://music.apple.com/us/song/catapult/1862951335</v>
       </c>
       <c r="D177" t="str">
         <v>2026-01-23</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Greyhound</v>
+        <v>Catapult - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:31</v>
+        <v>2:57</v>
       </c>
       <c r="H177" t="str">
-        <v>Katie Tupper</v>
+        <v>Cape Francis</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/katie-tupper/1395542470</v>
+        <v>https://music.apple.com/us/artist/cape-francis/1242523550</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/disappear/1847663546</v>
+        <v>https://music.apple.com/us/album/catapult/1862951333</v>
       </c>
       <c r="L177" t="str">
-        <v>Disappear - Katie Tupper</v>
+        <v>Catapult - Cape Francis</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Catapult</v>
+        <v>Think Twice</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/catapult/1862951335</v>
+        <v>https://music.apple.com/us/song/think-twice/1850698548</v>
       </c>
       <c r="D178" t="str">
         <v>2026-01-23</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Catapult - Single</v>
+        <v>Think Twice - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:57</v>
+        <v>2:22</v>
       </c>
       <c r="H178" t="str">
-        <v>Cape Francis</v>
+        <v>Leonie Biney</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/cape-francis/1242523550</v>
+        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/catapult/1862951333</v>
+        <v>https://music.apple.com/us/album/think-twice/1850698545</v>
       </c>
       <c r="L178" t="str">
-        <v>Catapult - Cape Francis</v>
+        <v>Think Twice - Leonie Biney</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Think Twice</v>
+        <v>LOVESONGS</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/think-twice/1850698548</v>
+        <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
       </c>
       <c r="D179" t="str">
         <v>2026-01-23</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Think Twice - Single</v>
+        <v>BEAUTIFUL MADNESS</v>
       </c>
       <c r="G179" t="str">
-        <v>2:22</v>
+        <v>3:33</v>
       </c>
       <c r="H179" t="str">
-        <v>Leonie Biney</v>
+        <v>Agnes</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
+        <v>https://music.apple.com/us/artist/agnes/42568985</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/think-twice/1850698545</v>
+        <v>https://music.apple.com/us/album/lovesongs/1849098275</v>
       </c>
       <c r="L179" t="str">
-        <v>Think Twice - Leonie Biney</v>
+        <v>LOVESONGS - Agnes</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>LOVESONGS</v>
+        <v>Down South</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
+        <v>https://music.apple.com/us/song/down-south/1861010793</v>
       </c>
       <c r="D180" t="str">
         <v>2026-01-23</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>BEAUTIFUL MADNESS</v>
+        <v>Down South - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:33</v>
+        <v>2:19</v>
       </c>
       <c r="H180" t="str">
-        <v>Agnes</v>
+        <v>Trap Dickey</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/agnes/42568985</v>
+        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/lovesongs/1849098275</v>
+        <v>https://music.apple.com/us/album/down-south/1861010788</v>
       </c>
       <c r="L180" t="str">
-        <v>LOVESONGS - Agnes</v>
+        <v>Down South - Trap Dickey</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Down South</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/down-south/1861010793</v>
+        <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
       </c>
       <c r="D181" t="str">
         <v>2026-01-23</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Down South - Single</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:19</v>
+        <v>2:16</v>
       </c>
       <c r="H181" t="str">
-        <v>Trap Dickey</v>
+        <v>SALIMATA</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
+        <v>https://music.apple.com/us/artist/salimata/690253822</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/down-south/1861010788</v>
+        <v>https://music.apple.com/us/album/jackpot-foil-a-colors-show/1866998655</v>
       </c>
       <c r="L181" t="str">
-        <v>Down South - Trap Dickey</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW - SALIMATA</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW</v>
+        <v>Love Like This</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
+        <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
       </c>
       <c r="D182" t="str">
         <v>2026-01-23</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW - Single</v>
+        <v>Love Like This - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:16</v>
+        <v>3:30</v>
       </c>
       <c r="H182" t="str">
-        <v>SALIMATA</v>
+        <v>Jacob Banks</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/salimata/690253822</v>
+        <v>https://music.apple.com/us/artist/jacob-banks/625014171</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/jackpot-foil-a-colors-show/1866998655</v>
+        <v>https://music.apple.com/us/album/love-like-this/1866999617</v>
       </c>
       <c r="L182" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW - SALIMATA</v>
+        <v>Love Like This - Jacob Banks</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Love Like This</v>
+        <v>Plan Plan</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
+        <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
       </c>
       <c r="D183" t="str">
         <v>2026-01-23</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Love Like This - Single</v>
+        <v>La Locura</v>
       </c>
       <c r="G183" t="str">
-        <v>3:30</v>
+        <v>3:10</v>
       </c>
       <c r="H183" t="str">
-        <v>Jacob Banks</v>
+        <v>Funky</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/jacob-banks/625014171</v>
+        <v>https://music.apple.com/us/artist/funky/80960663</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/love-like-this/1866999617</v>
+        <v>https://music.apple.com/us/album/plan-plan/1867940087</v>
       </c>
       <c r="L183" t="str">
-        <v>Love Like This - Jacob Banks</v>
+        <v>Plan Plan - Funky</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Plan Plan</v>
+        <v>double edged sword</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
+        <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
       </c>
       <c r="D184" t="str">
         <v>2026-01-23</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>La Locura</v>
+        <v>double edged sword - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:10</v>
+        <v>3:28</v>
       </c>
       <c r="H184" t="str">
-        <v>Funky</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/funky/80960663</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/plan-plan/1867940087</v>
+        <v>https://music.apple.com/us/album/double-edged-sword/1868829044</v>
       </c>
       <c r="L184" t="str">
-        <v>Plan Plan - Funky</v>
+        <v>double edged sword - Hailey Picardi</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>double edged sword</v>
+        <v>SOMEWHERE IN BETWEEN</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
+        <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
       </c>
       <c r="D185" t="str">
         <v>2026-01-23</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>double edged sword - Single</v>
+        <v>SOMEWHERE IN BETWEEN - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:28</v>
+        <v>3:27</v>
       </c>
       <c r="H185" t="str">
-        <v>Hailey Picardi</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/matt-hansen/1442658353</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/double-edged-sword/1868829044</v>
+        <v>https://music.apple.com/us/album/somewhere-in-between/1866969151</v>
       </c>
       <c r="L185" t="str">
-        <v>double edged sword - Hailey Picardi</v>
+        <v>SOMEWHERE IN BETWEEN - Matt Hansen</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>SOMEWHERE IN BETWEEN</v>
+        <v>The Decay</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
+        <v>https://music.apple.com/us/song/the-decay/1862836783</v>
       </c>
       <c r="D186" t="str">
         <v>2026-01-23</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>SOMEWHERE IN BETWEEN - Single</v>
+        <v>What Remains (Midnight Edition)</v>
       </c>
       <c r="G186" t="str">
-        <v>3:27</v>
+        <v>3:20</v>
       </c>
       <c r="H186" t="str">
-        <v>Matt Hansen</v>
+        <v>Pop Evil</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/matt-hansen/1442658353</v>
+        <v>https://music.apple.com/us/artist/pop-evil/441597923</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/somewhere-in-between/1866969151</v>
+        <v>https://music.apple.com/us/album/the-decay/1862836507</v>
       </c>
       <c r="L186" t="str">
-        <v>SOMEWHERE IN BETWEEN - Matt Hansen</v>
+        <v>The Decay - Pop Evil</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>The Decay</v>
+        <v>3111</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/the-decay/1862836783</v>
+        <v>https://music.apple.com/us/song/3111/1862225387</v>
       </c>
       <c r="D187" t="str">
         <v>2026-01-23</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>What Remains (Midnight Edition)</v>
+        <v>Goliath</v>
       </c>
       <c r="G187" t="str">
-        <v>3:20</v>
+        <v>4:08</v>
       </c>
       <c r="H187" t="str">
-        <v>Pop Evil</v>
+        <v>Exodus</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/pop-evil/441597923</v>
+        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/the-decay/1862836507</v>
+        <v>https://music.apple.com/us/album/3111/1862225385</v>
       </c>
       <c r="L187" t="str">
-        <v>The Decay - Pop Evil</v>
+        <v>3111 - Exodus</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>3111</v>
+        <v>Touch My Love And Die</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/3111/1862225387</v>
+        <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
       </c>
       <c r="D188" t="str">
         <v>2026-01-23</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Goliath</v>
+        <v>Touch My Love And Die - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>4:08</v>
+        <v>2:57</v>
       </c>
       <c r="H188" t="str">
-        <v>Exodus</v>
+        <v>Myrkur</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
+        <v>https://music.apple.com/us/artist/myrkur/293296859</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/3111/1862225385</v>
+        <v>https://music.apple.com/us/album/touch-my-love-and-die/1867630168</v>
       </c>
       <c r="L188" t="str">
-        <v>3111 - Exodus</v>
+        <v>Touch My Love And Die - Myrkur</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Touch My Love And Die</v>
+        <v>Bomb To A Knife Fight</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
+        <v>https://music.apple.com/us/song/bomb-to-a-knife-fight/1861589406</v>
       </c>
       <c r="D189" t="str">
         <v>2026-01-23</v>
@@ -7557,68 +7557,30 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Touch My Love And Die - Single</v>
+        <v>Bomb To A Knife Fight - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>2:57</v>
+        <v>2:41</v>
       </c>
       <c r="H189" t="str">
-        <v>Myrkur</v>
+        <v>The Barbarians of California</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/myrkur/293296859</v>
+        <v>https://music.apple.com/us/artist/the-barbarians-of-california/1724096474</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/touch-my-love-and-die/1867630168</v>
+        <v>https://music.apple.com/us/album/bomb-to-a-knife-fight/1861589405</v>
       </c>
       <c r="L189" t="str">
-        <v>Touch My Love And Die - Myrkur</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="str">
-        <v>Bomb To A Knife Fight</v>
-      </c>
-      <c r="B190" t="str">
-        <v/>
-      </c>
-      <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/bomb-to-a-knife-fight/1861589406</v>
-      </c>
-      <c r="D190" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E190" t="str">
-        <v/>
-      </c>
-      <c r="F190" t="str">
-        <v>Bomb To A Knife Fight - Single</v>
-      </c>
-      <c r="G190" t="str">
-        <v>2:41</v>
-      </c>
-      <c r="H190" t="str">
-        <v>The Barbarians of California</v>
-      </c>
-      <c r="I190" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/the-barbarians-of-california/1724096474</v>
-      </c>
-      <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/bomb-to-a-knife-fight/1861589405</v>
-      </c>
-      <c r="L190" t="str">
         <v>Bomb To A Knife Fight - The Barbarians of California</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L190"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L189"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-01-week04/titles.xlsx
+++ b/data/global/2026-01-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>6 hours ago</v>
+        <v>2 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
+        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-23</v>
@@ -451,13 +451,13 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>6 hours ago</v>
+        <v>2 hours ago</v>
       </c>
       <c r="G2" t="str">
-        <v>4:10</v>
+        <v>3:59</v>
       </c>
       <c r="H2" t="str">
-        <v>Parker McCollum</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Lyric Video)</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B3" t="str">
-        <v>6 hours ago</v>
+        <v>3 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
+        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-23</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>6 hours ago</v>
+        <v>3 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>3:26</v>
+        <v>2:56</v>
       </c>
       <c r="H3" t="str">
-        <v>Matt Hansen</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Lyric Video) - Matt Hansen</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video)</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
+        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-23</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="G4" t="str">
-        <v>2:56</v>
+        <v>3:46</v>
       </c>
       <c r="H4" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
+        <v>Dean Lewis - I Am Getting Well</v>
       </c>
       <c r="B5" t="str">
-        <v>6 hours ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
+        <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-23</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>6 hours ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="G5" t="str">
-        <v>2:56</v>
+        <v>2:47</v>
       </c>
       <c r="H5" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
+        <v>Dean Lewis - I Am Getting Well - Dean Lewis</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
+        <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B6" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
+        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-23</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G6" t="str">
-        <v>4:01</v>
+        <v>4:37</v>
       </c>
       <c r="H6" t="str">
-        <v>Tauren Wells</v>
+        <v>Bella White</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
+        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
+        <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
+        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-23</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G7" t="str">
-        <v>3:05</v>
+        <v>4:06</v>
       </c>
       <c r="H7" t="str">
-        <v>Maiah Manser</v>
+        <v>Ryan Wright</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
+        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B8" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
+        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-23</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G8" t="str">
-        <v>2:27</v>
+        <v>3:54</v>
       </c>
       <c r="H8" t="str">
-        <v>Taylor Austin Dye</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Chelsea Cutler - BAD (Official Video)</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
+        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-23</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G9" t="str">
-        <v>2:34</v>
+        <v>4:10</v>
       </c>
       <c r="H9" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Lyric Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
+        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-23</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:13</v>
+        <v>3:26</v>
       </c>
       <c r="H10" t="str">
-        <v>Ashley Kutcher</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
+        <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>6 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
+        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-23</v>
@@ -793,10 +793,10 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>6 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:13</v>
+        <v>2:56</v>
       </c>
       <c r="H11" t="str">
         <v>Louis Tomlinson</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
+        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
+        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-23</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:08</v>
+        <v>2:56</v>
       </c>
       <c r="H12" t="str">
-        <v>CAIN</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Harry Styles - Aperture (Official Audio)</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>11 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
+        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-23</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>11 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G13" t="str">
-        <v>5:14</v>
+        <v>4:01</v>
       </c>
       <c r="H13" t="str">
-        <v>Harry Styles</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video)</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>18 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
+        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-23</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>18 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G14" t="str">
-        <v>2:59</v>
+        <v>3:05</v>
       </c>
       <c r="H14" t="str">
-        <v>Lana Lubany</v>
+        <v>Maiah Manser</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>1 day ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
+        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-23</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>1 day ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G15" t="str">
-        <v>4:21</v>
+        <v>2:27</v>
       </c>
       <c r="H15" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Taylor Austin Dye</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
+        <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>1 day ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
+        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-23</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>1 day ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G16" t="str">
-        <v>4:09</v>
+        <v>2:34</v>
       </c>
       <c r="H16" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
+        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>2 days ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
+        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-23</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>2 days ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G17" t="str">
-        <v>2:34</v>
+        <v>3:13</v>
       </c>
       <c r="H17" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Ashley Kutcher</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B18" t="str">
-        <v>2 days ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
+        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-23</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>2 days ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:10</v>
+        <v>3:13</v>
       </c>
       <c r="H18" t="str">
-        <v>Olivia Dean</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>2 days ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
+        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-23</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>2 days ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:21</v>
+        <v>3:08</v>
       </c>
       <c r="H19" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>CAIN</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video)</v>
+        <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>3 days ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
+        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-23</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>3 days ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:06</v>
+        <v>5:14</v>
       </c>
       <c r="H20" t="str">
-        <v>The Avett Brothers</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
+        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video)</v>
+        <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>3 days ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
+        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-23</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>3 days ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:21</v>
+        <v>2:59</v>
       </c>
       <c r="H21" t="str">
-        <v>Jordana Bryant</v>
+        <v>Lana Lubany</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
+        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
+        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-23</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G22" t="str">
-        <v>7:21</v>
+        <v>4:21</v>
       </c>
       <c r="H22" t="str">
-        <v>Katy Perry</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
+        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-23</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:17</v>
+        <v>4:09</v>
       </c>
       <c r="H23" t="str">
-        <v>Lauren Watkins</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Just A Mess (Live acoustic studio session)</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
+        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-23</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:45</v>
+        <v>2:34</v>
       </c>
       <c r="H24" t="str">
-        <v>Tones And I</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B25" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
+        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-23</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:57</v>
+        <v>3:10</v>
       </c>
       <c r="H25" t="str">
-        <v>Ashleigh Dallas</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B26" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
+        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-23</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:03</v>
+        <v>3:21</v>
       </c>
       <c r="H26" t="str">
-        <v>Charlie Puth</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
+        <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
+        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-23</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>4:27</v>
+        <v>3:06</v>
       </c>
       <c r="H27" t="str">
-        <v>Chappell Roan</v>
+        <v>The Avett Brothers</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
+        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
+        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-23</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>4:34</v>
+        <v>3:21</v>
       </c>
       <c r="H28" t="str">
-        <v>Armik</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>LØLØ - 007 (Official Music Video)</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B29" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
+        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-23</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>2:54</v>
+        <v>7:21</v>
       </c>
       <c r="H29" t="str">
-        <v>LØLØ</v>
+        <v>Katy Perry</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer)</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B30" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
+        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-23</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:25</v>
+        <v>3:17</v>
       </c>
       <c r="H30" t="str">
-        <v>Tenille Townes</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video)</v>
+        <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B31" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
+        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-23</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>2:01</v>
+        <v>3:45</v>
       </c>
       <c r="H31" t="str">
-        <v>Alan Walker</v>
+        <v>Tones And I</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
+        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio)</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B32" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
+        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-23</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>2:25</v>
+        <v>3:57</v>
       </c>
       <c r="H32" t="str">
-        <v>Charli xcx</v>
+        <v>Ashleigh Dallas</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer)</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
+        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-23</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>1:14</v>
+        <v>3:03</v>
       </c>
       <c r="H33" t="str">
-        <v>Labrinth</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B34" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
+        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-23</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>2:59</v>
+        <v>4:27</v>
       </c>
       <c r="H34" t="str">
-        <v>Charlie Puth</v>
+        <v>Chappell Roan</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Girl Tones - Volcano (Visualizer)</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B35" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
+        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-23</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>2:29</v>
+        <v>4:34</v>
       </c>
       <c r="H35" t="str">
-        <v>Girl Tones</v>
+        <v>Armik</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
+        <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
+        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-23</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>2:34</v>
+        <v>2:54</v>
       </c>
       <c r="H36" t="str">
-        <v>Jagwar Twin</v>
+        <v>LØLØ</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
+        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
+        <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B37" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
+        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-23</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:48</v>
+        <v>3:25</v>
       </c>
       <c r="H37" t="str">
-        <v>Caroline Jones</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
+        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
+        <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B38" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
+        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-23</v>
@@ -1822,10 +1822,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:32</v>
+        <v>2:01</v>
       </c>
       <c r="H38" t="str">
-        <v>The Beaches</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
+        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
+        <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B39" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
+        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-23</v>
@@ -1860,10 +1860,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:49</v>
+        <v>2:25</v>
       </c>
       <c r="H39" t="str">
-        <v>Dolly Parton</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
+        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Madison Beer - bad enough (Official Music Video)</v>
+        <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B40" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
+        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-23</v>
@@ -1898,10 +1898,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>4:28</v>
+        <v>1:14</v>
       </c>
       <c r="H40" t="str">
-        <v>Madison Beer</v>
+        <v>Labrinth</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
+        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Ty Myers - Message to You (Official Video)</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B41" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
+        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-23</v>
@@ -1936,10 +1936,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:37</v>
+        <v>2:59</v>
       </c>
       <c r="H41" t="str">
-        <v>Ty Myers</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
+        <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B42" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
+        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-23</v>
@@ -1974,10 +1974,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:35</v>
+        <v>2:29</v>
       </c>
       <c r="H42" t="str">
-        <v>Megan Moroney</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
+        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B43" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
+        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-23</v>
@@ -2012,10 +2012,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>2:31</v>
+        <v>2:34</v>
       </c>
       <c r="H43" t="str">
-        <v>Julia Cole Music</v>
+        <v>Jagwar Twin</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B44" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
+        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-23</v>
@@ -2050,10 +2050,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:21</v>
+        <v>3:48</v>
       </c>
       <c r="H44" t="str">
-        <v>Lily Allen</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
       </c>
       <c r="B45" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
+        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-23</v>
@@ -2088,10 +2088,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>5:24</v>
+        <v>3:32</v>
       </c>
       <c r="H45" t="str">
-        <v>Nickless</v>
+        <v>The Beaches</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Peach PRC - Back To You (Official Audio)</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
       </c>
       <c r="B46" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
+        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-23</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:11</v>
+        <v>3:49</v>
       </c>
       <c r="H46" t="str">
-        <v>Peach PRC</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
+        <v>Madison Beer - bad enough (Official Music Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
+        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-23</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>4:11</v>
+        <v>4:28</v>
       </c>
       <c r="H47" t="str">
-        <v>Ocean Alley</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
+        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Ty Myers - Message to You (Official Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
+        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-23</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:31</v>
+        <v>3:37</v>
       </c>
       <c r="H48" t="str">
-        <v>OneRepublic</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
+        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
+        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-23</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>4:16</v>
+        <v>3:35</v>
       </c>
       <c r="H49" t="str">
-        <v>Ty Myers</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
+        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-23</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>4:42</v>
+        <v>2:31</v>
       </c>
       <c r="H50" t="str">
-        <v>JavaJazzFest</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video)</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
       </c>
       <c r="B51" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
+        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-23</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>2:47</v>
+        <v>3:21</v>
       </c>
       <c r="H51" t="str">
-        <v>Teo Glacier</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
       </c>
       <c r="B52" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
+        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-23</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:59</v>
+        <v>5:24</v>
       </c>
       <c r="H52" t="str">
-        <v>Brigitte Calls Me Baby</v>
+        <v>Nickless</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
+        <v>Peach PRC - Back To You (Official Audio)</v>
       </c>
       <c r="B53" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
+        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-23</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>4:09</v>
+        <v>3:11</v>
       </c>
       <c r="H53" t="str">
-        <v>Louie TheSinger</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
+        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ella jane - When I Was Beautiful (Live)</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
       </c>
       <c r="B54" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
+        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-23</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:24</v>
+        <v>4:11</v>
       </c>
       <c r="H54" t="str">
-        <v>ella jane</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Johnny Orlando - Emilia (Official Video)</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B55" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
+        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-23</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:14</v>
+        <v>3:31</v>
       </c>
       <c r="H55" t="str">
-        <v>Johnny Orlando</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video)</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
       </c>
       <c r="B56" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
+        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-23</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:32</v>
+        <v>4:16</v>
       </c>
       <c r="H56" t="str">
-        <v>Kungs</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B57" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
+        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-23</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:15</v>
+        <v>4:42</v>
       </c>
       <c r="H57" t="str">
-        <v>Billy Raffoul</v>
+        <v>JavaJazzFest</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
+        <v>Teo Glacier - Don't Mind (Music Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
+        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-23</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:03</v>
+        <v>2:47</v>
       </c>
       <c r="H58" t="str">
-        <v>NathanEvanss</v>
+        <v>Teo Glacier</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
+        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Stephen Sanchez - Sweet Love</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
+        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-23</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:04</v>
+        <v>3:59</v>
       </c>
       <c r="H59" t="str">
-        <v>Stephen Sanchez</v>
+        <v>Brigitte Calls Me Baby</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video]</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
       </c>
       <c r="B60" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
+        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-23</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:33</v>
+        <v>4:09</v>
       </c>
       <c r="H60" t="str">
-        <v>Bruno Mars</v>
+        <v>Louie TheSinger</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
+        <v>ella jane - When I Was Beautiful (Live)</v>
       </c>
       <c r="B61" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
+        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-23</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>2:53</v>
+        <v>3:24</v>
       </c>
       <c r="H61" t="str">
-        <v>MAX</v>
+        <v>ella jane</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
+        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
+        <v>Johnny Orlando - Emilia (Official Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
+        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-23</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>4:11</v>
+        <v>3:14</v>
       </c>
       <c r="H62" t="str">
-        <v>Jessie J</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
+        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
+        <v>Kungs, Theophilus London - Galaxy (official video)</v>
       </c>
       <c r="B63" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
+        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-23</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>2:45</v>
+        <v>3:32</v>
       </c>
       <c r="H63" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Kungs</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
+        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
       </c>
       <c r="B64" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
+        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-23</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>4:00</v>
+        <v>3:15</v>
       </c>
       <c r="H64" t="str">
-        <v>Brandon Lake and Cody Johnson</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
+        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-23</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:27</v>
+        <v>3:03</v>
       </c>
       <c r="H65" t="str">
-        <v>The Kid LAROI.</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
+        <v>Stephen Sanchez - Sweet Love</v>
       </c>
       <c r="B66" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
+        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-23</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:25</v>
+        <v>3:04</v>
       </c>
       <c r="H66" t="str">
-        <v>Olivia Dean</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
+        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Bruno Mars - I Just Might [Official Music Video]</v>
       </c>
       <c r="B67" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
+        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-23</v>
@@ -2924,10 +2924,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:34</v>
+        <v>3:33</v>
       </c>
       <c r="H67" t="str">
-        <v>Demi Lovato</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Train - Mittens (Live on TODAY)</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=R2k_wPsAHKQ</v>
+        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-23</v>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:17</v>
+        <v>2:53</v>
       </c>
       <c r="H68" t="str">
-        <v>Train</v>
+        <v>MAX</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Train - Mittens (Live on TODAY) - Train</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
+        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-23</v>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>2:25</v>
+        <v>4:11</v>
       </c>
       <c r="H69" t="str">
-        <v>Joseph</v>
+        <v>Jessie J</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
+        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-23</v>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:26</v>
+        <v>2:45</v>
       </c>
       <c r="H70" t="str">
-        <v>Demi Lovato</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
+        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-23</v>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>4:46</v>
+        <v>4:00</v>
       </c>
       <c r="H71" t="str">
-        <v>Keith Urban</v>
+        <v>Brandon Lake and Cody Johnson</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
+        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-23</v>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:24</v>
+        <v>3:27</v>
       </c>
       <c r="H72" t="str">
-        <v>Keith Urban</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
+        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-23</v>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>2:52</v>
+        <v>3:25</v>
       </c>
       <c r="H73" t="str">
-        <v>Madonna</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
+        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-23</v>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>2:06</v>
+        <v>3:34</v>
       </c>
       <c r="H74" t="str">
-        <v>Estas Tonne</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estas Tonne</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Anna Graves - Burn On (Official Music Video)</v>
+        <v>Train - Mittens (Live on TODAY)</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
+        <v>https://www.youtube.com/watch?v=R2k_wPsAHKQ</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-23</v>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:09</v>
+        <v>3:17</v>
       </c>
       <c r="H75" t="str">
-        <v>Anna Graves</v>
+        <v>Train</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
+        <v>Train - Mittens (Live on TODAY) - Train</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
+        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-23</v>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>5:11</v>
+        <v>2:25</v>
       </c>
       <c r="H76" t="str">
-        <v>Ocean Alley</v>
+        <v>Joseph</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
+        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-23</v>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:40</v>
+        <v>3:26</v>
       </c>
       <c r="H77" t="str">
-        <v>Zara Larsson</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
+        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-23</v>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:49</v>
+        <v>4:46</v>
       </c>
       <c r="H78" t="str">
-        <v>Lauren Watkins</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
+        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-23</v>
@@ -3380,10 +3380,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:42</v>
+        <v>3:24</v>
       </c>
       <c r="H79" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
+        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-23</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>5:11</v>
+        <v>2:52</v>
       </c>
       <c r="H80" t="str">
-        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Madonna</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
+        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-23</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:57</v>
+        <v>2:06</v>
       </c>
       <c r="H81" t="str">
-        <v>Lainey Wilson</v>
+        <v>Estas Tonne</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estas Tonne</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Grace Enger - All My Songs (Official Lyric Video)</v>
+        <v>Anna Graves - Burn On (Official Music Video)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=gWyaiGAFVO8</v>
+        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-23</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:29</v>
+        <v>3:09</v>
       </c>
       <c r="H82" t="str">
-        <v>Grace Enger</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Grace Enger - All My Songs (Official Lyric Video) - Grace Enger</v>
+        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Alan Walker - Broken Strings (Official Music Video)</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=jwQKcW474Tc</v>
+        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-23</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:10</v>
+        <v>5:11</v>
       </c>
       <c r="H83" t="str">
-        <v>Alan Walker and 2 more</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Alan Walker - Broken Strings (Official Music Video) - Alan Walker and 2 more</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Emilia Tarrant - Break Up With Myself</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
       </c>
       <c r="B84" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=3N7iKwqENP0</v>
+        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-23</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>4:04</v>
+        <v>3:40</v>
       </c>
       <c r="H84" t="str">
-        <v>Emilia Tarrant</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Emilia Tarrant - Break Up With Myself - Emilia Tarrant</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026)</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B85" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=sKG5ZIzCnFQ</v>
+        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-23</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:09</v>
+        <v>3:49</v>
       </c>
       <c r="H85" t="str">
-        <v>Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026) - Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer)</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B86" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=Koj30I91_8k</v>
+        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-23</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>2:27</v>
+        <v>3:42</v>
       </c>
       <c r="H86" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer) - Lauren Spencer Smith</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Maggie Lindemann - fate</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B87" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=xZdWEmnRK4g</v>
+        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-23</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:12</v>
+        <v>5:11</v>
       </c>
       <c r="H87" t="str">
-        <v>Maggie Lindemann</v>
+        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Maggie Lindemann - fate - Maggie Lindemann</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023)</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
       </c>
       <c r="B88" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=wo9yPPCh75Q</v>
+        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-23</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>4:44</v>
+        <v>3:57</v>
       </c>
       <c r="H88" t="str">
-        <v>Cliff Richard</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023) - Cliff Richard</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025</v>
+        <v>Grace Enger - All My Songs (Official Lyric Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=ND6maRwmzHk</v>
+        <v>https://www.youtube.com/watch?v=gWyaiGAFVO8</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-23</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>1:00:09</v>
+        <v>3:29</v>
       </c>
       <c r="H89" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025 - Purple Disco Machine</v>
+        <v>Grace Enger - All My Songs (Official Lyric Video) - Grace Enger</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>RAYE - Black Mascara. (Live at The Royal Albert Hall)</v>
+        <v>Alan Walker - Broken Strings (Official Music Video)</v>
       </c>
       <c r="B90" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=9jMMOYr-VhE</v>
+        <v>https://www.youtube.com/watch?v=jwQKcW474Tc</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-23</v>
@@ -3798,10 +3798,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>4:15</v>
+        <v>3:10</v>
       </c>
       <c r="H90" t="str">
-        <v>RAYE</v>
+        <v>Alan Walker and 2 more</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>RAYE - Black Mascara. (Live at The Royal Albert Hall) - RAYE</v>
+        <v>Alan Walker - Broken Strings (Official Music Video) - Alan Walker and 2 more</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Madison Cunningham - My Full Name (Garden Session)</v>
+        <v>Emilia Tarrant - Break Up With Myself</v>
       </c>
       <c r="B91" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=o2F-QmqdNtI</v>
+        <v>https://www.youtube.com/watch?v=3N7iKwqENP0</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-23</v>
@@ -3836,10 +3836,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>4:07</v>
+        <v>4:04</v>
       </c>
       <c r="H91" t="str">
-        <v>Madison Cunningham</v>
+        <v>Emilia Tarrant</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Madison Cunningham - My Full Name (Garden Session) - Madison Cunningham</v>
+        <v>Emilia Tarrant - Break Up With Myself - Emilia Tarrant</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions)</v>
+        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026)</v>
       </c>
       <c r="B92" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=5-6cEVLqE90</v>
+        <v>https://www.youtube.com/watch?v=sKG5ZIzCnFQ</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-23</v>
@@ -3874,10 +3874,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:10</v>
+        <v>3:09</v>
       </c>
       <c r="H92" t="str">
-        <v>Teddy Swims</v>
+        <v>Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions) - Teddy Swims</v>
+        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026) - Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower)</v>
+        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer)</v>
       </c>
       <c r="B93" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=ivPSbcEMwCs</v>
+        <v>https://www.youtube.com/watch?v=Koj30I91_8k</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-23</v>
@@ -3912,10 +3912,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:47</v>
+        <v>2:27</v>
       </c>
       <c r="H93" t="str">
-        <v>Christina Aguilera</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower) - Christina Aguilera</v>
+        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025)</v>
+        <v>Maggie Lindemann - fate</v>
       </c>
       <c r="B94" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=tYpOHbXFnm0</v>
+        <v>https://www.youtube.com/watch?v=xZdWEmnRK4g</v>
       </c>
       <c r="D94" t="str">
         <v>2026-01-23</v>
@@ -3950,10 +3950,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:58</v>
+        <v>2:12</v>
       </c>
       <c r="H94" t="str">
-        <v>RAYE</v>
+        <v>Maggie Lindemann</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025) - RAYE</v>
+        <v>Maggie Lindemann - fate - Maggie Lindemann</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Dasha - Here For The Party (Official Audio)</v>
+        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023)</v>
       </c>
       <c r="B95" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=rSO9oYUnO2k</v>
+        <v>https://www.youtube.com/watch?v=wo9yPPCh75Q</v>
       </c>
       <c r="D95" t="str">
         <v>2026-01-23</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:30</v>
+        <v>4:44</v>
       </c>
       <c r="H95" t="str">
-        <v>Dasha</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Dasha - Here For The Party (Official Audio) - Dasha</v>
+        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023) - Cliff Richard</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Lady Gaga in Harlequin Live: One Night Only</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025</v>
       </c>
       <c r="B96" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=c231tCsQalU</v>
+        <v>https://www.youtube.com/watch?v=ND6maRwmzHk</v>
       </c>
       <c r="D96" t="str">
         <v>2026-01-23</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>51:49</v>
+        <v>1:00:09</v>
       </c>
       <c r="H96" t="str">
-        <v>Lady Gaga and YouTube</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Lady Gaga in Harlequin Live: One Night Only - Lady Gaga and YouTube</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Sabrina Carpenter - Such A Funny Way (Official Lyric Video)</v>
+        <v>RAYE - Black Mascara. (Live at The Royal Albert Hall)</v>
       </c>
       <c r="B97" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=oaJKUCgSSkc</v>
+        <v>https://www.youtube.com/watch?v=9jMMOYr-VhE</v>
       </c>
       <c r="D97" t="str">
         <v>2026-01-23</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:53</v>
+        <v>4:15</v>
       </c>
       <c r="H97" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>RAYE</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Sabrina Carpenter - Such A Funny Way (Official Lyric Video) - Sabrina Carpenter</v>
+        <v>RAYE - Black Mascara. (Live at The Royal Albert Hall) - RAYE</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Megan Moroney - Beautiful Things (Official Fan Video)</v>
+        <v>Madison Cunningham - My Full Name (Garden Session)</v>
       </c>
       <c r="B98" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=0Gxu80LxI0w</v>
+        <v>https://www.youtube.com/watch?v=o2F-QmqdNtI</v>
       </c>
       <c r="D98" t="str">
         <v>2026-01-23</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:56</v>
+        <v>4:07</v>
       </c>
       <c r="H98" t="str">
-        <v>Megan Moroney</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Megan Moroney - Beautiful Things (Official Fan Video) - Megan Moroney</v>
+        <v>Madison Cunningham - My Full Name (Garden Session) - Madison Cunningham</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Jason Derulo - Miracle</v>
+        <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions)</v>
       </c>
       <c r="B99" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=7sjshHJwkOE</v>
+        <v>https://www.youtube.com/watch?v=5-6cEVLqE90</v>
       </c>
       <c r="D99" t="str">
         <v>2026-01-23</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>4:16</v>
+        <v>3:10</v>
       </c>
       <c r="H99" t="str">
-        <v>Jason Derulo</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Jason Derulo - Miracle - Jason Derulo</v>
+        <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions) - Teddy Swims</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Sananda Maitreya - Pretty Baby (Live)</v>
+        <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower)</v>
       </c>
       <c r="B100" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=yv1c5G5HZt8</v>
+        <v>https://www.youtube.com/watch?v=ivPSbcEMwCs</v>
       </c>
       <c r="D100" t="str">
         <v>2026-01-23</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:29</v>
+        <v>3:47</v>
       </c>
       <c r="H100" t="str">
-        <v>Sananda Maitreya</v>
+        <v>Christina Aguilera</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Sananda Maitreya - Pretty Baby (Live) - Sananda Maitreya</v>
+        <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower) - Christina Aguilera</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Faded - 10th Anniversary (Performance Video)</v>
+        <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025)</v>
       </c>
       <c r="B101" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=EXVg23U3NRw</v>
+        <v>https://www.youtube.com/watch?v=tYpOHbXFnm0</v>
       </c>
       <c r="D101" t="str">
         <v>2026-01-23</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:25</v>
+        <v>3:58</v>
       </c>
       <c r="H101" t="str">
-        <v>Alan Walker and 2 more</v>
+        <v>RAYE</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Faded - 10th Anniversary (Performance Video) - Alan Walker and 2 more</v>
+        <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025) - RAYE</v>
       </c>
     </row>
     <row r="102">

--- a/data/global/2026-01-week04/titles.xlsx
+++ b/data/global/2026-01-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L189"/>
+  <dimension ref="A1:L190"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
+        <v>נדב גדג’ - בלי יד על הדופק</v>
       </c>
       <c r="B2" t="str">
-        <v>2 hours ago</v>
+        <v>2026-01-22</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24441&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-23</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>2 hours ago</v>
+        <v>23:52</v>
       </c>
       <c r="G2" t="str">
-        <v>3:59</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>Holly Humberstone</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
+        <v>נדב גדג’ - בלי יד על הדופק</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B3" t="str">
         <v>3 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
+        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-23</v>
@@ -492,10 +492,10 @@
         <v>3 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>2:56</v>
+        <v>3:59</v>
       </c>
       <c r="H3" t="str">
-        <v>Cliff Richard</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B4" t="str">
         <v>4 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
+        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-23</v>
@@ -530,10 +530,10 @@
         <v>4 hours ago</v>
       </c>
       <c r="G4" t="str">
-        <v>3:46</v>
+        <v>2:56</v>
       </c>
       <c r="H4" t="str">
-        <v>Jessie Ware</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Dean Lewis - I Am Getting Well</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>4 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
+        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-23</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>4 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="G5" t="str">
-        <v>2:47</v>
+        <v>3:46</v>
       </c>
       <c r="H5" t="str">
-        <v>Dean Lewis</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Dean Lewis - I Am Getting Well - Dean Lewis</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Bella White - Dream Song (Official Audio)</v>
+        <v>Dean Lewis - I Am Getting Well</v>
       </c>
       <c r="B6" t="str">
-        <v>7 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
+        <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-23</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>7 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="G6" t="str">
-        <v>4:37</v>
+        <v>2:47</v>
       </c>
       <c r="H6" t="str">
-        <v>Bella White</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
+        <v>Dean Lewis - I Am Getting Well - Dean Lewis</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video)</v>
+        <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B7" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
+        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-23</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G7" t="str">
-        <v>4:06</v>
+        <v>4:37</v>
       </c>
       <c r="H7" t="str">
-        <v>Ryan Wright</v>
+        <v>Bella White</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
+        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
+        <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
+        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-23</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G8" t="str">
-        <v>3:54</v>
+        <v>4:06</v>
       </c>
       <c r="H8" t="str">
-        <v>Dove Cameron</v>
+        <v>Ryan Wright</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
+        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B9" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
+        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-23</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G9" t="str">
-        <v>4:10</v>
+        <v>3:54</v>
       </c>
       <c r="H9" t="str">
-        <v>Parker McCollum</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Lyric Video)</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
+        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-23</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:26</v>
+        <v>4:10</v>
       </c>
       <c r="H10" t="str">
-        <v>Matt Hansen</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Lyric Video) - Matt Hansen</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video)</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Lyric Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
+        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-23</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G11" t="str">
-        <v>2:56</v>
+        <v>3:26</v>
       </c>
       <c r="H11" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
+        <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>7 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
+        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-23</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>7 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
         <v>2:56</v>
       </c>
       <c r="H12" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
+        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
+        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-23</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G13" t="str">
-        <v>4:01</v>
+        <v>2:56</v>
       </c>
       <c r="H13" t="str">
-        <v>Tauren Wells</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
+        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-23</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:05</v>
+        <v>4:01</v>
       </c>
       <c r="H14" t="str">
-        <v>Maiah Manser</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
+        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-23</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G15" t="str">
-        <v>2:27</v>
+        <v>3:05</v>
       </c>
       <c r="H15" t="str">
-        <v>Taylor Austin Dye</v>
+        <v>Maiah Manser</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Chelsea Cutler - BAD (Official Video)</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
+        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-23</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G16" t="str">
-        <v>2:34</v>
+        <v>2:27</v>
       </c>
       <c r="H16" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Taylor Austin Dye</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
+        <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
+        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-23</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:13</v>
+        <v>2:34</v>
       </c>
       <c r="H17" t="str">
-        <v>Ashley Kutcher</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
+        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
+        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-23</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:13</v>
       </c>
       <c r="H18" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Ashley Kutcher</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B19" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
+        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-23</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:08</v>
+        <v>3:13</v>
       </c>
       <c r="H19" t="str">
-        <v>CAIN</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Harry Styles - Aperture (Official Audio)</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>12 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
+        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-23</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>12 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G20" t="str">
-        <v>5:14</v>
+        <v>3:08</v>
       </c>
       <c r="H20" t="str">
-        <v>Harry Styles</v>
+        <v>CAIN</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video)</v>
+        <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B21" t="str">
-        <v>20 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
+        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-23</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>20 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G21" t="str">
-        <v>2:59</v>
+        <v>5:14</v>
       </c>
       <c r="H21" t="str">
-        <v>Lana Lubany</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
+        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
+        <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>1 day ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
+        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-23</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>1 day ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G22" t="str">
-        <v>4:21</v>
+        <v>2:59</v>
       </c>
       <c r="H22" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Lana Lubany</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
+        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B23" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
+        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-23</v>
@@ -1252,10 +1252,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G23" t="str">
-        <v>4:09</v>
+        <v>4:21</v>
       </c>
       <c r="H23" t="str">
-        <v>Dermot Kennedy</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
+        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-23</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G24" t="str">
-        <v>2:34</v>
+        <v>4:09</v>
       </c>
       <c r="H24" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B25" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
+        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-23</v>
@@ -1328,10 +1328,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:10</v>
+        <v>2:34</v>
       </c>
       <c r="H25" t="str">
-        <v>Olivia Dean</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B26" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
+        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-23</v>
@@ -1366,10 +1366,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:21</v>
+        <v>3:10</v>
       </c>
       <c r="H26" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B27" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
+        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-23</v>
@@ -1404,10 +1404,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:06</v>
+        <v>3:21</v>
       </c>
       <c r="H27" t="str">
-        <v>The Avett Brothers</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video)</v>
+        <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B28" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
+        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-23</v>
@@ -1442,10 +1442,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:21</v>
+        <v>3:06</v>
       </c>
       <c r="H28" t="str">
-        <v>Jordana Bryant</v>
+        <v>The Avett Brothers</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
+        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
+        <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B29" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
+        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-23</v>
@@ -1480,10 +1480,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>7:21</v>
+        <v>3:21</v>
       </c>
       <c r="H29" t="str">
-        <v>Katy Perry</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
+        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B30" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
+        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-23</v>
@@ -1518,10 +1518,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:17</v>
+        <v>7:21</v>
       </c>
       <c r="H30" t="str">
-        <v>Lauren Watkins</v>
+        <v>Katy Perry</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Just A Mess (Live acoustic studio session)</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B31" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
+        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-23</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:45</v>
+        <v>3:17</v>
       </c>
       <c r="H31" t="str">
-        <v>Tones And I</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
+        <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B32" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
+        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-23</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:57</v>
+        <v>3:45</v>
       </c>
       <c r="H32" t="str">
-        <v>Ashleigh Dallas</v>
+        <v>Tones And I</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
+        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B33" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
+        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-23</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:03</v>
+        <v>3:57</v>
       </c>
       <c r="H33" t="str">
-        <v>Charlie Puth</v>
+        <v>Ashleigh Dallas</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B34" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
+        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-23</v>
@@ -1670,10 +1670,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>4:27</v>
+        <v>3:03</v>
       </c>
       <c r="H34" t="str">
-        <v>Chappell Roan</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B35" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
+        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-23</v>
@@ -1708,10 +1708,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>4:34</v>
+        <v>4:27</v>
       </c>
       <c r="H35" t="str">
-        <v>Armik</v>
+        <v>Chappell Roan</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>LØLØ - 007 (Official Music Video)</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B36" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
+        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-23</v>
@@ -1746,10 +1746,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>2:54</v>
+        <v>4:34</v>
       </c>
       <c r="H36" t="str">
-        <v>LØLØ</v>
+        <v>Armik</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer)</v>
+        <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B37" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
+        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-23</v>
@@ -1784,10 +1784,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:25</v>
+        <v>2:54</v>
       </c>
       <c r="H37" t="str">
-        <v>Tenille Townes</v>
+        <v>LØLØ</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
+        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video)</v>
+        <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B38" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
+        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-23</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:01</v>
+        <v>3:25</v>
       </c>
       <c r="H38" t="str">
-        <v>Alan Walker</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
+        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio)</v>
+        <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B39" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
+        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-23</v>
@@ -1860,10 +1860,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>2:25</v>
+        <v>2:01</v>
       </c>
       <c r="H39" t="str">
-        <v>Charli xcx</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
+        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer)</v>
+        <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B40" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
+        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-23</v>
@@ -1898,10 +1898,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>1:14</v>
+        <v>2:25</v>
       </c>
       <c r="H40" t="str">
-        <v>Labrinth</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
+        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
+        <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B41" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
+        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-23</v>
@@ -1936,10 +1936,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>2:59</v>
+        <v>1:14</v>
       </c>
       <c r="H41" t="str">
-        <v>Charlie Puth</v>
+        <v>Labrinth</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
+        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Girl Tones - Volcano (Visualizer)</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B42" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
+        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-23</v>
@@ -1974,10 +1974,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>2:29</v>
+        <v>2:59</v>
       </c>
       <c r="H42" t="str">
-        <v>Girl Tones</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
+        <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B43" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
+        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-23</v>
@@ -2012,10 +2012,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>2:34</v>
+        <v>2:29</v>
       </c>
       <c r="H43" t="str">
-        <v>Jagwar Twin</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
+        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B44" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
+        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-23</v>
@@ -2050,10 +2050,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:48</v>
+        <v>2:34</v>
       </c>
       <c r="H44" t="str">
-        <v>Caroline Jones</v>
+        <v>Jagwar Twin</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B45" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
+        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-23</v>
@@ -2088,10 +2088,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:32</v>
+        <v>3:48</v>
       </c>
       <c r="H45" t="str">
-        <v>The Beaches</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
       </c>
       <c r="B46" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
+        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-23</v>
@@ -2126,10 +2126,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:49</v>
+        <v>3:32</v>
       </c>
       <c r="H46" t="str">
-        <v>Dolly Parton</v>
+        <v>The Beaches</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Madison Beer - bad enough (Official Music Video)</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
       </c>
       <c r="B47" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
+        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-23</v>
@@ -2164,10 +2164,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>4:28</v>
+        <v>3:49</v>
       </c>
       <c r="H47" t="str">
-        <v>Madison Beer</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Ty Myers - Message to You (Official Video)</v>
+        <v>Madison Beer - bad enough (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
+        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-23</v>
@@ -2202,10 +2202,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:37</v>
+        <v>4:28</v>
       </c>
       <c r="H48" t="str">
-        <v>Ty Myers</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
+        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
+        <v>Ty Myers - Message to You (Official Video)</v>
       </c>
       <c r="B49" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
+        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-23</v>
@@ -2240,10 +2240,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:35</v>
+        <v>3:37</v>
       </c>
       <c r="H49" t="str">
-        <v>Megan Moroney</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
+        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
       </c>
       <c r="B50" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
+        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-23</v>
@@ -2278,10 +2278,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>2:31</v>
+        <v>3:35</v>
       </c>
       <c r="H50" t="str">
-        <v>Julia Cole Music</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
       </c>
       <c r="B51" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
+        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-23</v>
@@ -2316,10 +2316,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:21</v>
+        <v>2:31</v>
       </c>
       <c r="H51" t="str">
-        <v>Lily Allen</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
       </c>
       <c r="B52" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
+        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-23</v>
@@ -2354,10 +2354,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>5:24</v>
+        <v>3:21</v>
       </c>
       <c r="H52" t="str">
-        <v>Nickless</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Peach PRC - Back To You (Official Audio)</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
       </c>
       <c r="B53" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
+        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-23</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:11</v>
+        <v>5:24</v>
       </c>
       <c r="H53" t="str">
-        <v>Peach PRC</v>
+        <v>Nickless</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
+        <v>Peach PRC - Back To You (Official Audio)</v>
       </c>
       <c r="B54" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
+        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-23</v>
@@ -2430,10 +2430,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>4:11</v>
+        <v>3:11</v>
       </c>
       <c r="H54" t="str">
-        <v>Ocean Alley</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
+        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
       </c>
       <c r="B55" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
+        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-23</v>
@@ -2468,10 +2468,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:31</v>
+        <v>4:11</v>
       </c>
       <c r="H55" t="str">
-        <v>OneRepublic</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B56" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
+        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-23</v>
@@ -2506,10 +2506,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>4:16</v>
+        <v>3:31</v>
       </c>
       <c r="H56" t="str">
-        <v>Ty Myers</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
       </c>
       <c r="B57" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
+        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-23</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>4:42</v>
+        <v>4:16</v>
       </c>
       <c r="H57" t="str">
-        <v>JavaJazzFest</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video)</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B58" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
+        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-23</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>2:47</v>
+        <v>4:42</v>
       </c>
       <c r="H58" t="str">
-        <v>Teo Glacier</v>
+        <v>JavaJazzFest</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
+        <v>Teo Glacier - Don't Mind (Music Video)</v>
       </c>
       <c r="B59" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
+        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-23</v>
@@ -2620,10 +2620,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:59</v>
+        <v>2:47</v>
       </c>
       <c r="H59" t="str">
-        <v>Brigitte Calls Me Baby</v>
+        <v>Teo Glacier</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
+        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
+        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-23</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>4:09</v>
+        <v>3:59</v>
       </c>
       <c r="H60" t="str">
-        <v>Louie TheSinger</v>
+        <v>Brigitte Calls Me Baby</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ella jane - When I Was Beautiful (Live)</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
       </c>
       <c r="B61" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
+        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-23</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>13 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:24</v>
+        <v>4:09</v>
       </c>
       <c r="H61" t="str">
-        <v>ella jane</v>
+        <v>Louie TheSinger</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Johnny Orlando - Emilia (Official Video)</v>
+        <v>ella jane - When I Was Beautiful (Live)</v>
       </c>
       <c r="B62" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
+        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-23</v>
@@ -2734,10 +2734,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:14</v>
+        <v>3:24</v>
       </c>
       <c r="H62" t="str">
-        <v>Johnny Orlando</v>
+        <v>ella jane</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
+        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video)</v>
+        <v>Johnny Orlando - Emilia (Official Video)</v>
       </c>
       <c r="B63" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
+        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-23</v>
@@ -2772,10 +2772,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:32</v>
+        <v>3:14</v>
       </c>
       <c r="H63" t="str">
-        <v>Kungs</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
+        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
+        <v>Kungs, Theophilus London - Galaxy (official video)</v>
       </c>
       <c r="B64" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
+        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-23</v>
@@ -2810,10 +2810,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:15</v>
+        <v>3:32</v>
       </c>
       <c r="H64" t="str">
-        <v>Billy Raffoul</v>
+        <v>Kungs</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
+        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
       </c>
       <c r="B65" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
+        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-23</v>
@@ -2848,10 +2848,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:03</v>
+        <v>3:15</v>
       </c>
       <c r="H65" t="str">
-        <v>NathanEvanss</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Stephen Sanchez - Sweet Love</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
       </c>
       <c r="B66" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
+        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-23</v>
@@ -2886,10 +2886,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:04</v>
+        <v>3:03</v>
       </c>
       <c r="H66" t="str">
-        <v>Stephen Sanchez</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video]</v>
+        <v>Stephen Sanchez - Sweet Love</v>
       </c>
       <c r="B67" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
+        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-23</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:33</v>
+        <v>3:04</v>
       </c>
       <c r="H67" t="str">
-        <v>Bruno Mars</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
+        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
+        <v>Bruno Mars - I Just Might [Official Music Video]</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
+        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-23</v>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>2:53</v>
+        <v>3:33</v>
       </c>
       <c r="H68" t="str">
-        <v>MAX</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
+        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
+        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-23</v>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>4:11</v>
+        <v>2:53</v>
       </c>
       <c r="H69" t="str">
-        <v>Jessie J</v>
+        <v>MAX</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
+        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-23</v>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>2:45</v>
+        <v>4:11</v>
       </c>
       <c r="H70" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Jessie J</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
+        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-23</v>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>4:00</v>
+        <v>2:45</v>
       </c>
       <c r="H71" t="str">
-        <v>Brandon Lake and Cody Johnson</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
+        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-23</v>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:27</v>
+        <v>4:00</v>
       </c>
       <c r="H72" t="str">
-        <v>The Kid LAROI.</v>
+        <v>Brandon Lake and Cody Johnson</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
+        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-23</v>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:25</v>
+        <v>3:27</v>
       </c>
       <c r="H73" t="str">
-        <v>Olivia Dean</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
+        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-23</v>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:34</v>
+        <v>3:25</v>
       </c>
       <c r="H74" t="str">
-        <v>Demi Lovato</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Train - Mittens (Live on TODAY)</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=R2k_wPsAHKQ</v>
+        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-23</v>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:17</v>
+        <v>3:34</v>
       </c>
       <c r="H75" t="str">
-        <v>Train</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Train - Mittens (Live on TODAY) - Train</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
+        <v>Train - Mittens (Live on TODAY)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
+        <v>https://www.youtube.com/watch?v=R2k_wPsAHKQ</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-23</v>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>2:25</v>
+        <v>3:17</v>
       </c>
       <c r="H76" t="str">
-        <v>Joseph</v>
+        <v>Train</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
+        <v>Train - Mittens (Live on TODAY) - Train</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
+        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-23</v>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:26</v>
+        <v>2:25</v>
       </c>
       <c r="H77" t="str">
-        <v>Demi Lovato</v>
+        <v>Joseph</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
+        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-23</v>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>4:46</v>
+        <v>3:26</v>
       </c>
       <c r="H78" t="str">
-        <v>Keith Urban</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
+        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-23</v>
@@ -3380,7 +3380,7 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:24</v>
+        <v>4:46</v>
       </c>
       <c r="H79" t="str">
         <v>Keith Urban</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
+        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-23</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>2:52</v>
+        <v>3:24</v>
       </c>
       <c r="H80" t="str">
-        <v>Madonna</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
+        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-23</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>2:06</v>
+        <v>2:52</v>
       </c>
       <c r="H81" t="str">
-        <v>Estas Tonne</v>
+        <v>Madonna</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estas Tonne</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Anna Graves - Burn On (Official Music Video)</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
+        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-23</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:09</v>
+        <v>2:06</v>
       </c>
       <c r="H82" t="str">
-        <v>Anna Graves</v>
+        <v>Estas Tonne</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estas Tonne</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
+        <v>Anna Graves - Burn On (Official Music Video)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
+        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-23</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>5:11</v>
+        <v>3:09</v>
       </c>
       <c r="H83" t="str">
-        <v>Ocean Alley</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
+        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
+        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-23</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:40</v>
+        <v>5:11</v>
       </c>
       <c r="H84" t="str">
-        <v>Zara Larsson</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
+        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-23</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:49</v>
+        <v>3:40</v>
       </c>
       <c r="H85" t="str">
-        <v>Lauren Watkins</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
+        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-23</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:42</v>
+        <v>3:49</v>
       </c>
       <c r="H86" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
+        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-23</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>5:11</v>
+        <v>3:42</v>
       </c>
       <c r="H87" t="str">
-        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
+        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-23</v>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:57</v>
+        <v>5:11</v>
       </c>
       <c r="H88" t="str">
-        <v>Lainey Wilson</v>
+        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Grace Enger - All My Songs (Official Lyric Video)</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=gWyaiGAFVO8</v>
+        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-23</v>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:29</v>
+        <v>3:57</v>
       </c>
       <c r="H89" t="str">
-        <v>Grace Enger</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Grace Enger - All My Songs (Official Lyric Video) - Grace Enger</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Alan Walker - Broken Strings (Official Music Video)</v>
+        <v>Grace Enger - All My Songs (Official Lyric Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=jwQKcW474Tc</v>
+        <v>https://www.youtube.com/watch?v=gWyaiGAFVO8</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-23</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:10</v>
+        <v>3:29</v>
       </c>
       <c r="H90" t="str">
-        <v>Alan Walker and 2 more</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Alan Walker - Broken Strings (Official Music Video) - Alan Walker and 2 more</v>
+        <v>Grace Enger - All My Songs (Official Lyric Video) - Grace Enger</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Emilia Tarrant - Break Up With Myself</v>
+        <v>Alan Walker - Broken Strings (Official Music Video)</v>
       </c>
       <c r="B91" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=3N7iKwqENP0</v>
+        <v>https://www.youtube.com/watch?v=jwQKcW474Tc</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-23</v>
@@ -3836,10 +3836,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>4:04</v>
+        <v>3:10</v>
       </c>
       <c r="H91" t="str">
-        <v>Emilia Tarrant</v>
+        <v>Alan Walker and 2 more</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Emilia Tarrant - Break Up With Myself - Emilia Tarrant</v>
+        <v>Alan Walker - Broken Strings (Official Music Video) - Alan Walker and 2 more</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026)</v>
+        <v>Emilia Tarrant - Break Up With Myself</v>
       </c>
       <c r="B92" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=sKG5ZIzCnFQ</v>
+        <v>https://www.youtube.com/watch?v=3N7iKwqENP0</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-23</v>
@@ -3874,10 +3874,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:09</v>
+        <v>4:04</v>
       </c>
       <c r="H92" t="str">
-        <v>Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Emilia Tarrant</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026) - Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Emilia Tarrant - Break Up With Myself - Emilia Tarrant</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer)</v>
+        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026)</v>
       </c>
       <c r="B93" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=Koj30I91_8k</v>
+        <v>https://www.youtube.com/watch?v=sKG5ZIzCnFQ</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-23</v>
@@ -3912,10 +3912,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>2:27</v>
+        <v>3:09</v>
       </c>
       <c r="H93" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer) - Lauren Spencer Smith</v>
+        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026) - Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Maggie Lindemann - fate</v>
+        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer)</v>
       </c>
       <c r="B94" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=xZdWEmnRK4g</v>
+        <v>https://www.youtube.com/watch?v=Koj30I91_8k</v>
       </c>
       <c r="D94" t="str">
         <v>2026-01-23</v>
@@ -3950,10 +3950,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>2:12</v>
+        <v>2:27</v>
       </c>
       <c r="H94" t="str">
-        <v>Maggie Lindemann</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Maggie Lindemann - fate - Maggie Lindemann</v>
+        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023)</v>
+        <v>Maggie Lindemann - fate</v>
       </c>
       <c r="B95" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=wo9yPPCh75Q</v>
+        <v>https://www.youtube.com/watch?v=xZdWEmnRK4g</v>
       </c>
       <c r="D95" t="str">
         <v>2026-01-23</v>
@@ -3988,10 +3988,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>4:44</v>
+        <v>2:12</v>
       </c>
       <c r="H95" t="str">
-        <v>Cliff Richard</v>
+        <v>Maggie Lindemann</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023) - Cliff Richard</v>
+        <v>Maggie Lindemann - fate - Maggie Lindemann</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025</v>
+        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023)</v>
       </c>
       <c r="B96" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=ND6maRwmzHk</v>
+        <v>https://www.youtube.com/watch?v=wo9yPPCh75Q</v>
       </c>
       <c r="D96" t="str">
         <v>2026-01-23</v>
@@ -4026,10 +4026,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>1:00:09</v>
+        <v>4:44</v>
       </c>
       <c r="H96" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025 - Purple Disco Machine</v>
+        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023) - Cliff Richard</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>RAYE - Black Mascara. (Live at The Royal Albert Hall)</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025</v>
       </c>
       <c r="B97" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=9jMMOYr-VhE</v>
+        <v>https://www.youtube.com/watch?v=ND6maRwmzHk</v>
       </c>
       <c r="D97" t="str">
         <v>2026-01-23</v>
@@ -4064,10 +4064,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>4:15</v>
+        <v>1:00:09</v>
       </c>
       <c r="H97" t="str">
-        <v>RAYE</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>RAYE - Black Mascara. (Live at The Royal Albert Hall) - RAYE</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Madison Cunningham - My Full Name (Garden Session)</v>
+        <v>RAYE - Black Mascara. (Live at The Royal Albert Hall)</v>
       </c>
       <c r="B98" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=o2F-QmqdNtI</v>
+        <v>https://www.youtube.com/watch?v=9jMMOYr-VhE</v>
       </c>
       <c r="D98" t="str">
         <v>2026-01-23</v>
@@ -4102,10 +4102,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>4:07</v>
+        <v>4:15</v>
       </c>
       <c r="H98" t="str">
-        <v>Madison Cunningham</v>
+        <v>RAYE</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Madison Cunningham - My Full Name (Garden Session) - Madison Cunningham</v>
+        <v>RAYE - Black Mascara. (Live at The Royal Albert Hall) - RAYE</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions)</v>
+        <v>Madison Cunningham - My Full Name (Garden Session)</v>
       </c>
       <c r="B99" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=5-6cEVLqE90</v>
+        <v>https://www.youtube.com/watch?v=o2F-QmqdNtI</v>
       </c>
       <c r="D99" t="str">
         <v>2026-01-23</v>
@@ -4140,10 +4140,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:10</v>
+        <v>4:07</v>
       </c>
       <c r="H99" t="str">
-        <v>Teddy Swims</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions) - Teddy Swims</v>
+        <v>Madison Cunningham - My Full Name (Garden Session) - Madison Cunningham</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower)</v>
+        <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions)</v>
       </c>
       <c r="B100" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=ivPSbcEMwCs</v>
+        <v>https://www.youtube.com/watch?v=5-6cEVLqE90</v>
       </c>
       <c r="D100" t="str">
         <v>2026-01-23</v>
@@ -4178,10 +4178,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:47</v>
+        <v>3:10</v>
       </c>
       <c r="H100" t="str">
-        <v>Christina Aguilera</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower) - Christina Aguilera</v>
+        <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions) - Teddy Swims</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025)</v>
+        <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower)</v>
       </c>
       <c r="B101" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=tYpOHbXFnm0</v>
+        <v>https://www.youtube.com/watch?v=ivPSbcEMwCs</v>
       </c>
       <c r="D101" t="str">
         <v>2026-01-23</v>
@@ -4216,10 +4216,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:58</v>
+        <v>3:47</v>
       </c>
       <c r="H101" t="str">
-        <v>RAYE</v>
+        <v>Christina Aguilera</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025) - RAYE</v>
+        <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower) - Christina Aguilera</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Aperture</v>
+        <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>3 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/aperture/1870984033</v>
+        <v>https://www.youtube.com/watch?v=tYpOHbXFnm0</v>
       </c>
       <c r="D102" t="str">
         <v>2026-01-23</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Kiss All The Time. Disco, Occasionally.</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>5:11</v>
+        <v>3:58</v>
       </c>
       <c r="H102" t="str">
-        <v>Harry Styles</v>
+        <v>RAYE</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/aperture/1870984032</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>Aperture - Harry Styles</v>
+        <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025) - RAYE</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Opening Night</v>
+        <v>Aperture</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/opening-night/1870313501</v>
+        <v>https://music.apple.com/us/song/aperture/1870984033</v>
       </c>
       <c r="D103" t="str">
         <v>2026-01-23</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>HELP(2)</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G103" t="str">
-        <v>4:19</v>
+        <v>5:11</v>
       </c>
       <c r="H103" t="str">
-        <v>Arctic Monkeys</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/arctic-monkeys/62820413</v>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/opening-night/1870313498</v>
+        <v>https://music.apple.com/us/album/aperture/1870984032</v>
       </c>
       <c r="L103" t="str">
-        <v>Opening Night - Arctic Monkeys</v>
+        <v>Aperture - Harry Styles</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>FLACKITO JODYE (feat. Tokischa)</v>
+        <v>Opening Night</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/flackito-jodye-feat-tokischa/1870968779</v>
+        <v>https://music.apple.com/us/song/opening-night/1870313501</v>
       </c>
       <c r="D104" t="str">
         <v>2026-01-23</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Don't Be Dumb</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G104" t="str">
-        <v>2:20</v>
+        <v>4:19</v>
       </c>
       <c r="H104" t="str">
-        <v>A$AP Rocky</v>
+        <v>Arctic Monkeys</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/a%24ap-rocky/481488005</v>
+        <v>https://music.apple.com/us/artist/arctic-monkeys/62820413</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/flackito-jodye-feat-tokischa/1870968596</v>
+        <v>https://music.apple.com/us/album/opening-night/1870313498</v>
       </c>
       <c r="L104" t="str">
-        <v>FLACKITO JODYE (feat. Tokischa) - A$AP Rocky</v>
+        <v>Opening Night - Arctic Monkeys</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>CAMBIARÉ</v>
+        <v>FLACKITO JODYE (feat. Tokischa)</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
+        <v>https://music.apple.com/us/song/flackito-jodye-feat-tokischa/1870968779</v>
       </c>
       <c r="D105" t="str">
         <v>2026-01-23</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>CAMBIARÉ - Single</v>
+        <v>Don't Be Dumb</v>
       </c>
       <c r="G105" t="str">
-        <v>3:01</v>
+        <v>2:20</v>
       </c>
       <c r="H105" t="str">
-        <v>Luis Fonsi</v>
+        <v>A$AP Rocky</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/luis-fonsi/102834</v>
+        <v>https://music.apple.com/us/artist/a%24ap-rocky/481488005</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/cambiar%C3%A9/1867545265</v>
+        <v>https://music.apple.com/us/album/flackito-jodye-feat-tokischa/1870968596</v>
       </c>
       <c r="L105" t="str">
-        <v>CAMBIARÉ - Luis Fonsi</v>
+        <v>FLACKITO JODYE (feat. Tokischa) - A$AP Rocky</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Last of a Dying Breed</v>
+        <v>CAMBIARÉ</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/last-of-a-dying-breed/1849706852</v>
+        <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
       </c>
       <c r="D106" t="str">
         <v>2026-01-23</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Piss In The Wind</v>
+        <v>CAMBIARÉ - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>2:29</v>
+        <v>3:01</v>
       </c>
       <c r="H106" t="str">
-        <v>Joji</v>
+        <v>Luis Fonsi</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/joji/1258279972</v>
+        <v>https://music.apple.com/us/artist/luis-fonsi/102834</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/last-of-a-dying-breed/1849706656</v>
+        <v>https://music.apple.com/us/album/cambiar%C3%A9/1867545265</v>
       </c>
       <c r="L106" t="str">
-        <v>Last of a Dying Breed - Joji</v>
+        <v>CAMBIARÉ - Luis Fonsi</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>High Key</v>
+        <v>Last of a Dying Breed</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/high-key/1847702418</v>
+        <v>https://music.apple.com/us/song/last-of-a-dying-breed/1849706852</v>
       </c>
       <c r="D107" t="str">
         <v>2026-01-23</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Vacancy</v>
+        <v>Piss In The Wind</v>
       </c>
       <c r="G107" t="str">
-        <v>2:12</v>
+        <v>2:29</v>
       </c>
       <c r="H107" t="str">
-        <v>Ari Lennox</v>
+        <v>Joji</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/ari-lennox/448854570</v>
+        <v>https://music.apple.com/us/artist/joji/1258279972</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/high-key/1847702412</v>
+        <v>https://music.apple.com/us/album/last-of-a-dying-breed/1849706656</v>
       </c>
       <c r="L107" t="str">
-        <v>High Key - Ari Lennox</v>
+        <v>Last of a Dying Breed - Joji</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>scared</v>
+        <v>High Key</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/scared/1862292863</v>
+        <v>https://music.apple.com/us/song/high-key/1847702418</v>
       </c>
       <c r="D108" t="str">
         <v>2026-01-23</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>scared - Single</v>
+        <v>Vacancy</v>
       </c>
       <c r="G108" t="str">
-        <v>3:46</v>
+        <v>2:12</v>
       </c>
       <c r="H108" t="str">
-        <v>Fred again..</v>
+        <v>Ari Lennox</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/ari-lennox/448854570</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/scared/1862292862</v>
+        <v>https://music.apple.com/us/album/high-key/1847702412</v>
       </c>
       <c r="L108" t="str">
-        <v>scared - Fred again..</v>
+        <v>High Key - Ari Lennox</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Death of Love</v>
+        <v>scared</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/death-of-love/1862353786</v>
+        <v>https://music.apple.com/us/song/scared/1862292863</v>
       </c>
       <c r="D109" t="str">
         <v>2026-01-23</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Trying Times</v>
+        <v>scared - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>3:26</v>
+        <v>3:46</v>
       </c>
       <c r="H109" t="str">
-        <v>James Blake</v>
+        <v>Fred again..</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/death-of-love/1862353780</v>
+        <v>https://music.apple.com/us/album/scared/1862292862</v>
       </c>
       <c r="L109" t="str">
-        <v>Death of Love - James Blake</v>
+        <v>scared - Fred again..</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Big Ole Fancy House</v>
+        <v>Death of Love</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/big-ole-fancy-house/1862624759</v>
+        <v>https://music.apple.com/us/song/death-of-love/1862353786</v>
       </c>
       <c r="D110" t="str">
         <v>2026-01-23</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Parker McCollum (The Deluxe Edition)</v>
+        <v>Trying Times</v>
       </c>
       <c r="G110" t="str">
-        <v>4:03</v>
+        <v>3:26</v>
       </c>
       <c r="H110" t="str">
-        <v>Parker McCollum</v>
+        <v>James Blake</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/big-ole-fancy-house/1862624506</v>
+        <v>https://music.apple.com/us/album/death-of-love/1862353780</v>
       </c>
       <c r="L110" t="str">
-        <v>Big Ole Fancy House - Parker McCollum</v>
+        <v>Death of Love - James Blake</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Flo Jackson</v>
+        <v>Big Ole Fancy House</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
+        <v>https://music.apple.com/us/song/big-ole-fancy-house/1862624759</v>
       </c>
       <c r="D111" t="str">
         <v>2026-01-23</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Flo Jackson - Single</v>
+        <v>Parker McCollum (The Deluxe Edition)</v>
       </c>
       <c r="G111" t="str">
-        <v>2:23</v>
+        <v>4:03</v>
       </c>
       <c r="H111" t="str">
-        <v>Flo Milli</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
+        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
+        <v>https://music.apple.com/us/album/big-ole-fancy-house/1862624506</v>
       </c>
       <c r="L111" t="str">
-        <v>Flo Jackson - Flo Milli</v>
+        <v>Big Ole Fancy House - Parker McCollum</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Site Unseen (feat. Waxahatchee)</v>
+        <v>Flo Jackson</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
+        <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
       </c>
       <c r="D112" t="str">
         <v>2026-01-23</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Creature of Habit</v>
+        <v>Flo Jackson - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>2:46</v>
+        <v>2:23</v>
       </c>
       <c r="H112" t="str">
-        <v>Courtney Barnett</v>
+        <v>Flo Milli</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
+        <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
       </c>
       <c r="L112" t="str">
-        <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
+        <v>Flo Jackson - Flo Milli</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Puppet Parade</v>
+        <v>Site Unseen (feat. Waxahatchee)</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
+        <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
       </c>
       <c r="D113" t="str">
         <v>2026-01-23</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Megadeth</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G113" t="str">
-        <v>4:40</v>
+        <v>2:46</v>
       </c>
       <c r="H113" t="str">
-        <v>Megadeth</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/megadeth/488289</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
+        <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
       </c>
       <c r="L113" t="str">
-        <v>Puppet Parade - Megadeth</v>
+        <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>To Love Somebody</v>
+        <v>Puppet Parade</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/to-love-somebody/1859630040</v>
+        <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
       </c>
       <c r="D114" t="str">
         <v>2026-01-23</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Cruel World</v>
+        <v>Megadeth</v>
       </c>
       <c r="G114" t="str">
-        <v>3:57</v>
+        <v>4:40</v>
       </c>
       <c r="H114" t="str">
-        <v>Holly Humberstone</v>
+        <v>Megadeth</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/megadeth/488289</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/to-love-somebody/1859629846</v>
+        <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
       </c>
       <c r="L114" t="str">
-        <v>To Love Somebody - Holly Humberstone</v>
+        <v>Puppet Parade - Megadeth</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Nothing Is Impossible With You</v>
+        <v>To Love Somebody</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/nothing-is-impossible-with-you/1870691236</v>
+        <v>https://music.apple.com/us/song/to-love-somebody/1859630040</v>
       </c>
       <c r="D115" t="str">
         <v>2026-01-23</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Nothing Is Impossible With You - Single</v>
+        <v>Cruel World</v>
       </c>
       <c r="G115" t="str">
-        <v>4:14</v>
+        <v>3:57</v>
       </c>
       <c r="H115" t="str">
-        <v>Cleo Sol</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/cleo-sol/459710289</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/nothing-is-impossible-with-you/1870691227</v>
+        <v>https://music.apple.com/us/album/to-love-somebody/1859629846</v>
       </c>
       <c r="L115" t="str">
-        <v>Nothing Is Impossible With You - Cleo Sol</v>
+        <v>To Love Somebody - Holly Humberstone</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>HYPNOTIZE</v>
+        <v>Nothing Is Impossible With You</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/hypnotize/1861009528</v>
+        <v>https://music.apple.com/us/song/nothing-is-impossible-with-you/1870691236</v>
       </c>
       <c r="D116" t="str">
         <v>2026-01-23</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>THE CORE - 核</v>
+        <v>Nothing Is Impossible With You - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>2:50</v>
+        <v>4:14</v>
       </c>
       <c r="H116" t="str">
-        <v>XG</v>
+        <v>Cleo Sol</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/xg/1609409493</v>
+        <v>https://music.apple.com/us/artist/cleo-sol/459710289</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/hypnotize/1861009513</v>
+        <v>https://music.apple.com/us/album/nothing-is-impossible-with-you/1870691227</v>
       </c>
       <c r="L116" t="str">
-        <v>HYPNOTIZE - XG</v>
+        <v>Nothing Is Impossible With You - Cleo Sol</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Dead End</v>
+        <v>HYPNOTIZE</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/dead-end/1862845874</v>
+        <v>https://music.apple.com/us/song/hypnotize/1861009528</v>
       </c>
       <c r="D117" t="str">
         <v>2026-01-23</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Ricochet</v>
+        <v>THE CORE - 核</v>
       </c>
       <c r="G117" t="str">
-        <v>4:05</v>
+        <v>2:50</v>
       </c>
       <c r="H117" t="str">
-        <v>Snail Mail</v>
+        <v>XG</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v>https://music.apple.com/us/artist/xg/1609409493</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/dead-end/1862845733</v>
+        <v>https://music.apple.com/us/album/hypnotize/1861009513</v>
       </c>
       <c r="L117" t="str">
-        <v>Dead End - Snail Mail</v>
+        <v>HYPNOTIZE - XG</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Do I Wanna Know?</v>
+        <v>Dead End</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/do-i-wanna-know/1870931500</v>
+        <v>https://music.apple.com/us/song/dead-end/1862845874</v>
       </c>
       <c r="D118" t="str">
         <v>2026-01-23</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Do I Wanna Know? - Single</v>
+        <v>Ricochet</v>
       </c>
       <c r="G118" t="str">
-        <v>3:52</v>
+        <v>4:05</v>
       </c>
       <c r="H118" t="str">
-        <v>Dove Cameron</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/dove-cameron/599822740</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/do-i-wanna-know/1870931327</v>
+        <v>https://music.apple.com/us/album/dead-end/1862845733</v>
       </c>
       <c r="L118" t="str">
-        <v>Do I Wanna Know? - Dove Cameron</v>
+        <v>Dead End - Snail Mail</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Una y Otra Vez</v>
+        <v>Do I Wanna Know?</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/una-y-otra-vez/1868792926</v>
+        <v>https://music.apple.com/us/song/do-i-wanna-know/1870931500</v>
       </c>
       <c r="D119" t="str">
         <v>2026-01-23</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>K de Karma (Apple Music Edition)</v>
+        <v>Do I Wanna Know? - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:02</v>
+        <v>3:52</v>
       </c>
       <c r="H119" t="str">
-        <v>Kenia Os</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
+        <v>https://music.apple.com/us/artist/dove-cameron/599822740</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/una-y-otra-vez/1868792704</v>
+        <v>https://music.apple.com/us/album/do-i-wanna-know/1870931327</v>
       </c>
       <c r="L119" t="str">
-        <v>Una y Otra Vez - Kenia Os</v>
+        <v>Do I Wanna Know? - Dove Cameron</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>BAD</v>
+        <v>Una y Otra Vez</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/bad/1869095326</v>
+        <v>https://music.apple.com/us/song/una-y-otra-vez/1868792926</v>
       </c>
       <c r="D120" t="str">
         <v>2026-01-23</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>BAD - Single</v>
+        <v>K de Karma (Apple Music Edition)</v>
       </c>
       <c r="G120" t="str">
-        <v>2:15</v>
+        <v>3:02</v>
       </c>
       <c r="H120" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
+        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/bad/1869095325</v>
+        <v>https://music.apple.com/us/album/una-y-otra-vez/1868792704</v>
       </c>
       <c r="L120" t="str">
-        <v>BAD - Chelsea Cutler</v>
+        <v>Una y Otra Vez - Kenia Os</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Losing You</v>
+        <v>BAD</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/losing-you/1863525495</v>
+        <v>https://music.apple.com/us/song/bad/1869095326</v>
       </c>
       <c r="D121" t="str">
         <v>2026-01-23</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>F.I.G</v>
+        <v>BAD - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>2:22</v>
+        <v>2:15</v>
       </c>
       <c r="H121" t="str">
-        <v>Naomi Scott</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
+        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/losing-you/1863525485</v>
+        <v>https://music.apple.com/us/album/bad/1869095325</v>
       </c>
       <c r="L121" t="str">
-        <v>Losing You - Naomi Scott</v>
+        <v>BAD - Chelsea Cutler</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Me Voy A La C******a</v>
+        <v>Losing You</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/me-voy-a-la-c-a/1867850749</v>
+        <v>https://music.apple.com/us/song/losing-you/1863525495</v>
       </c>
       <c r="D122" t="str">
         <v>2026-01-23</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Infinito</v>
+        <v>F.I.G</v>
       </c>
       <c r="G122" t="str">
-        <v>2:14</v>
+        <v>2:22</v>
       </c>
       <c r="H122" t="str">
-        <v>Yandel</v>
+        <v>Naomi Scott</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/yandel/72929426</v>
+        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/me-voy-a-la-c-a/1867850739</v>
+        <v>https://music.apple.com/us/album/losing-you/1863525485</v>
       </c>
       <c r="L122" t="str">
-        <v>Me Voy A La C******a - Yandel</v>
+        <v>Losing You - Naomi Scott</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Sexy For Me</v>
+        <v>Me Voy A La C******a</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/sexy-for-me/1867897421</v>
+        <v>https://music.apple.com/us/song/me-voy-a-la-c-a/1867850749</v>
       </c>
       <c r="D123" t="str">
         <v>2026-01-23</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>The Last Dance (Part 1)</v>
+        <v>Infinito</v>
       </c>
       <c r="G123" t="str">
-        <v>2:08</v>
+        <v>2:14</v>
       </c>
       <c r="H123" t="str">
-        <v>Jason Derulo</v>
+        <v>Yandel</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/jason-derulo/259118085</v>
+        <v>https://music.apple.com/us/artist/yandel/72929426</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/sexy-for-me/1867897420</v>
+        <v>https://music.apple.com/us/album/me-voy-a-la-c-a/1867850739</v>
       </c>
       <c r="L123" t="str">
-        <v>Sexy For Me - Jason Derulo</v>
+        <v>Me Voy A La C******a - Yandel</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Turbulence</v>
+        <v>Sexy For Me</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/turbulence/1867908449</v>
+        <v>https://music.apple.com/us/song/sexy-for-me/1867897421</v>
       </c>
       <c r="D124" t="str">
         <v>2026-01-23</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>REAL, Vol. 1 - EP</v>
+        <v>The Last Dance (Part 1)</v>
       </c>
       <c r="G124" t="str">
-        <v>2:25</v>
+        <v>2:08</v>
       </c>
       <c r="H124" t="str">
-        <v>Wizkid</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
+        <v>https://music.apple.com/us/artist/jason-derulo/259118085</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/turbulence/1867908237</v>
+        <v>https://music.apple.com/us/album/sexy-for-me/1867897420</v>
       </c>
       <c r="L124" t="str">
-        <v>Turbulence - Wizkid</v>
+        <v>Sexy For Me - Jason Derulo</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>I’m Good (From The Movie “GOAT”)</v>
+        <v>Turbulence</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/im-good-from-the-movie-goat/1870623298</v>
+        <v>https://music.apple.com/us/song/turbulence/1867908449</v>
       </c>
       <c r="D125" t="str">
         <v>2026-01-23</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>GOAT (Original Motion Picture Soundtrack)</v>
+        <v>REAL, Vol. 1 - EP</v>
       </c>
       <c r="G125" t="str">
-        <v>2:59</v>
+        <v>2:25</v>
       </c>
       <c r="H125" t="str">
-        <v>Jelly Roll</v>
+        <v>Wizkid</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/im-good-from-the-movie-goat/1870623290</v>
+        <v>https://music.apple.com/us/album/turbulence/1867908237</v>
       </c>
       <c r="L125" t="str">
-        <v>I’m Good (From The Movie “GOAT”) - Jelly Roll</v>
+        <v>Turbulence - Wizkid</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
+        <v>I’m Good (From The Movie “GOAT”)</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
+        <v>https://music.apple.com/us/song/im-good-from-the-movie-goat/1870623298</v>
       </c>
       <c r="D126" t="str">
         <v>2026-01-23</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
+        <v>GOAT (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G126" t="str">
-        <v>3:47</v>
+        <v>2:59</v>
       </c>
       <c r="H126" t="str">
-        <v>Dolly Parton</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
+        <v>https://music.apple.com/us/album/im-good-from-the-movie-goat/1870623290</v>
       </c>
       <c r="L126" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
+        <v>I’m Good (From The Movie “GOAT”) - Jelly Roll</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>ESCONDIDAS</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/escondidas/1860972187</v>
+        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
       </c>
       <c r="D127" t="str">
         <v>2026-01-23</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>SILENCIO HABLA</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>2:53</v>
+        <v>3:47</v>
       </c>
       <c r="H127" t="str">
-        <v>Oscar Ortiz</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/oscar-ortiz/1680604969</v>
+        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/escondidas/1860972173</v>
+        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
       </c>
       <c r="L127" t="str">
-        <v>ESCONDIDAS - Oscar Ortiz</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Alabama Beauty Queen</v>
+        <v>ESCONDIDAS</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/alabama-beauty-queen/1846658485</v>
+        <v>https://music.apple.com/us/song/escondidas/1860972187</v>
       </c>
       <c r="D128" t="str">
         <v>2026-01-23</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Act I</v>
+        <v>SILENCIO HABLA</v>
       </c>
       <c r="G128" t="str">
-        <v>3:43</v>
+        <v>2:53</v>
       </c>
       <c r="H128" t="str">
-        <v>Kashus Culpepper</v>
+        <v>Oscar Ortiz</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/kashus-culpepper/1634883369</v>
+        <v>https://music.apple.com/us/artist/oscar-ortiz/1680604969</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/alabama-beauty-queen/1846658477</v>
+        <v>https://music.apple.com/us/album/escondidas/1860972173</v>
       </c>
       <c r="L128" t="str">
-        <v>Alabama Beauty Queen - Kashus Culpepper</v>
+        <v>ESCONDIDAS - Oscar Ortiz</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Imposter</v>
+        <v>Alabama Beauty Queen</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/imposter/1842408050</v>
+        <v>https://music.apple.com/us/song/alabama-beauty-queen/1846658485</v>
       </c>
       <c r="D129" t="str">
         <v>2026-01-23</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>How Did I Get Here?</v>
+        <v>Act I</v>
       </c>
       <c r="G129" t="str">
-        <v>2:38</v>
+        <v>3:43</v>
       </c>
       <c r="H129" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Kashus Culpepper</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
+        <v>https://music.apple.com/us/artist/kashus-culpepper/1634883369</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/imposter/1842408037</v>
+        <v>https://music.apple.com/us/album/alabama-beauty-queen/1846658477</v>
       </c>
       <c r="L129" t="str">
-        <v>Imposter - Louis Tomlinson</v>
+        <v>Alabama Beauty Queen - Kashus Culpepper</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Puddles (Zero 7 Remix)</v>
+        <v>Imposter</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/puddles-zero-7-remix/1869474314</v>
+        <v>https://music.apple.com/us/song/imposter/1842408050</v>
       </c>
       <c r="D130" t="str">
         <v>2026-01-23</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Puddles (Zero 7 Remix) - Single</v>
+        <v>How Did I Get Here?</v>
       </c>
       <c r="G130" t="str">
-        <v>6:01</v>
+        <v>2:38</v>
       </c>
       <c r="H130" t="str">
-        <v>Not for Radio</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
+        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/puddles-zero-7-remix/1869474313</v>
+        <v>https://music.apple.com/us/album/imposter/1842408037</v>
       </c>
       <c r="L130" t="str">
-        <v>Puddles (Zero 7 Remix) - Not for Radio</v>
+        <v>Imposter - Louis Tomlinson</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Little Miss (Misdemeanor)</v>
+        <v>Puddles (Zero 7 Remix)</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/little-miss-misdemeanor/1870996491</v>
+        <v>https://music.apple.com/us/song/puddles-zero-7-remix/1869474314</v>
       </c>
       <c r="D131" t="str">
         <v>2026-01-23</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Little Miss (Misdemeanor) - Single</v>
+        <v>Puddles (Zero 7 Remix) - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>2:24</v>
+        <v>6:01</v>
       </c>
       <c r="H131" t="str">
-        <v>GIRLSET</v>
+        <v>Not for Radio</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
+        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/little-miss-misdemeanor/1870996490</v>
+        <v>https://music.apple.com/us/album/puddles-zero-7-remix/1869474313</v>
       </c>
       <c r="L131" t="str">
-        <v>Little Miss (Misdemeanor) - GIRLSET</v>
+        <v>Puddles (Zero 7 Remix) - Not for Radio</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>I Could Get Used To This</v>
+        <v>Little Miss (Misdemeanor)</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/i-could-get-used-to-this/1867222996</v>
+        <v>https://music.apple.com/us/song/little-miss-misdemeanor/1870996491</v>
       </c>
       <c r="D132" t="str">
         <v>2026-01-23</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>I Could Get Used To This - Single</v>
+        <v>Little Miss (Misdemeanor) - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>3:41</v>
+        <v>2:24</v>
       </c>
       <c r="H132" t="str">
-        <v>Jessie Ware</v>
+        <v>GIRLSET</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/i-could-get-used-to-this/1867222992</v>
+        <v>https://music.apple.com/us/album/little-miss-misdemeanor/1870996490</v>
       </c>
       <c r="L132" t="str">
-        <v>I Could Get Used To This - Jessie Ware</v>
+        <v>Little Miss (Misdemeanor) - GIRLSET</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>LA VILLA</v>
+        <v>I Could Get Used To This</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/la-villa/1847678152</v>
+        <v>https://music.apple.com/us/song/i-could-get-used-to-this/1867222996</v>
       </c>
       <c r="D133" t="str">
         <v>2026-01-23</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>HOPI SENDÉ</v>
+        <v>I Could Get Used To This - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>3:12</v>
+        <v>3:41</v>
       </c>
       <c r="H133" t="str">
-        <v>Ryan Castro</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/ryan-castro/1263552447</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/la-villa/1847678143</v>
+        <v>https://music.apple.com/us/album/i-could-get-used-to-this/1867222992</v>
       </c>
       <c r="L133" t="str">
-        <v>LA VILLA - Ryan Castro</v>
+        <v>I Could Get Used To This - Jessie Ware</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700)</v>
+        <v>LA VILLA</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/lit-effect-feat-bktherula-lazer-dim-700/1868519613</v>
+        <v>https://music.apple.com/us/song/la-villa/1847678152</v>
       </c>
       <c r="D134" t="str">
         <v>2026-01-23</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Strictly 4 The Scythe</v>
+        <v>HOPI SENDÉ</v>
       </c>
       <c r="G134" t="str">
-        <v>3:27</v>
+        <v>3:12</v>
       </c>
       <c r="H134" t="str">
-        <v>Denzel Curry</v>
+        <v>Ryan Castro</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
+        <v>https://music.apple.com/us/artist/ryan-castro/1263552447</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/lit-effect-feat-bktherula-lazer-dim-700/1868519270</v>
+        <v>https://music.apple.com/us/album/la-villa/1847678143</v>
       </c>
       <c r="L134" t="str">
-        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700) - Denzel Curry</v>
+        <v>LA VILLA - Ryan Castro</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Thick One</v>
+        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700)</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/thick-one/1868515478</v>
+        <v>https://music.apple.com/us/song/lit-effect-feat-bktherula-lazer-dim-700/1868519613</v>
       </c>
       <c r="D135" t="str">
         <v>2026-01-23</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Part 3</v>
+        <v>Strictly 4 The Scythe</v>
       </c>
       <c r="G135" t="str">
-        <v>2:49</v>
+        <v>3:27</v>
       </c>
       <c r="H135" t="str">
-        <v>42 Dugg</v>
+        <v>Denzel Curry</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
+        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/thick-one/1868515223</v>
+        <v>https://music.apple.com/us/album/lit-effect-feat-bktherula-lazer-dim-700/1868519270</v>
       </c>
       <c r="L135" t="str">
-        <v>Thick One - 42 Dugg</v>
+        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700) - Denzel Curry</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>How Much Did You Get For Your Soul</v>
+        <v>Thick One</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/how-much-did-you-get-for-your-soul/1843195678</v>
+        <v>https://music.apple.com/us/song/thick-one/1868515478</v>
       </c>
       <c r="D136" t="str">
         <v>2026-01-23</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>World's Gone Wrong</v>
+        <v>Part 3</v>
       </c>
       <c r="G136" t="str">
-        <v>3:59</v>
+        <v>2:49</v>
       </c>
       <c r="H136" t="str">
-        <v>Lucinda Williams</v>
+        <v>42 Dugg</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/lucinda-williams/267658</v>
+        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/how-much-did-you-get-for-your-soul/1843195660</v>
+        <v>https://music.apple.com/us/album/thick-one/1868515223</v>
       </c>
       <c r="L136" t="str">
-        <v>How Much Did You Get For Your Soul - Lucinda Williams</v>
+        <v>Thick One - 42 Dugg</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>THUM</v>
+        <v>How Much Did You Get For Your Soul</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/thum/1863009362</v>
+        <v>https://music.apple.com/us/song/how-much-did-you-get-for-your-soul/1843195678</v>
       </c>
       <c r="D137" t="str">
         <v>2026-01-23</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>THUM - Single</v>
+        <v>World's Gone Wrong</v>
       </c>
       <c r="G137" t="str">
-        <v>2:11</v>
+        <v>3:59</v>
       </c>
       <c r="H137" t="str">
-        <v>Violet Grohl</v>
+        <v>Lucinda Williams</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/lucinda-williams/267658</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/thum/1863009357</v>
+        <v>https://music.apple.com/us/album/how-much-did-you-get-for-your-soul/1843195660</v>
       </c>
       <c r="L137" t="str">
-        <v>THUM - Violet Grohl</v>
+        <v>How Much Did You Get For Your Soul - Lucinda Williams</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>(I'm a) Rock "N" Roller</v>
+        <v>THUM</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/im-a-rock-n-roller/1839888014</v>
+        <v>https://music.apple.com/us/song/thum/1863009362</v>
       </c>
       <c r="D138" t="str">
         <v>2026-01-23</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>The Great Satan</v>
+        <v>THUM - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>3:32</v>
+        <v>2:11</v>
       </c>
       <c r="H138" t="str">
-        <v>Rob Zombie</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/im-a-rock-n-roller/1839887790</v>
+        <v>https://music.apple.com/us/album/thum/1863009357</v>
       </c>
       <c r="L138" t="str">
-        <v>(I'm a) Rock "N" Roller - Rob Zombie</v>
+        <v>THUM - Violet Grohl</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Excuses For Love</v>
+        <v>(I'm a) Rock "N" Roller</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/excuses-for-love/1856034295</v>
+        <v>https://music.apple.com/us/song/im-a-rock-n-roller/1839888014</v>
       </c>
       <c r="D139" t="str">
         <v>2026-01-23</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Hyperlove</v>
+        <v>The Great Satan</v>
       </c>
       <c r="G139" t="str">
-        <v>3:04</v>
+        <v>3:32</v>
       </c>
       <c r="H139" t="str">
-        <v>MIKA</v>
+        <v>Rob Zombie</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/mika/184932871</v>
+        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/excuses-for-love/1856033810</v>
+        <v>https://music.apple.com/us/album/im-a-rock-n-roller/1839887790</v>
       </c>
       <c r="L139" t="str">
-        <v>Excuses For Love - MIKA</v>
+        <v>(I'm a) Rock "N" Roller - Rob Zombie</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>3 Tears</v>
+        <v>Excuses For Love</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/3-tears/1861504548</v>
+        <v>https://music.apple.com/us/song/excuses-for-love/1856034295</v>
       </c>
       <c r="D140" t="str">
         <v>2026-01-23</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>3 Tears - Single</v>
+        <v>Hyperlove</v>
       </c>
       <c r="G140" t="str">
-        <v>2:50</v>
+        <v>3:04</v>
       </c>
       <c r="H140" t="str">
-        <v>Mergui</v>
+        <v>MIKA</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/mergui/1423596903</v>
+        <v>https://music.apple.com/us/artist/mika/184932871</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/3-tears/1861504545</v>
+        <v>https://music.apple.com/us/album/excuses-for-love/1856033810</v>
       </c>
       <c r="L140" t="str">
-        <v>3 Tears - Mergui</v>
+        <v>Excuses For Love - MIKA</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Church Girl</v>
+        <v>3 Tears</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/church-girl/1862008542</v>
+        <v>https://music.apple.com/us/song/3-tears/1861504548</v>
       </c>
       <c r="D141" t="str">
         <v>2026-01-23</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Church Girl - Single</v>
+        <v>3 Tears - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:19</v>
+        <v>2:50</v>
       </c>
       <c r="H141" t="str">
-        <v>Carly Pearce</v>
+        <v>Mergui</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/mergui/1423596903</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/church-girl/1862008535</v>
+        <v>https://music.apple.com/us/album/3-tears/1861504545</v>
       </c>
       <c r="L141" t="str">
-        <v>Church Girl - Carly Pearce</v>
+        <v>3 Tears - Mergui</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Funeral</v>
+        <v>Church Girl</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/funeral/1867616928</v>
+        <v>https://music.apple.com/us/song/church-girl/1862008542</v>
       </c>
       <c r="D142" t="str">
         <v>2026-01-23</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>The Weight of the Woods</v>
+        <v>Church Girl - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>4:03</v>
+        <v>3:19</v>
       </c>
       <c r="H142" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/funeral/1867616617</v>
+        <v>https://music.apple.com/us/album/church-girl/1862008535</v>
       </c>
       <c r="L142" t="str">
-        <v>Funeral - Dermot Kennedy</v>
+        <v>Church Girl - Carly Pearce</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Say Yes</v>
+        <v>Funeral</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/say-yes/1861995090</v>
+        <v>https://music.apple.com/us/song/funeral/1867616928</v>
       </c>
       <c r="D143" t="str">
         <v>2026-01-23</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Say Yes - Single</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G143" t="str">
-        <v>2:50</v>
+        <v>4:03</v>
       </c>
       <c r="H143" t="str">
-        <v>Marques Anthony</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/marques-anthony/321321231</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/say-yes/1861995089</v>
+        <v>https://music.apple.com/us/album/funeral/1867616617</v>
       </c>
       <c r="L143" t="str">
-        <v>Say Yes - Marques Anthony</v>
+        <v>Funeral - Dermot Kennedy</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>LOVE ME (feat. Stevie Wonder)</v>
+        <v>Say Yes</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/love-me-feat-stevie-wonder/1867640879</v>
+        <v>https://music.apple.com/us/song/say-yes/1861995090</v>
       </c>
       <c r="D144" t="str">
         <v>2026-01-23</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>CAMPILATION</v>
+        <v>Say Yes - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>3:10</v>
+        <v>2:50</v>
       </c>
       <c r="H144" t="str">
-        <v>Camper</v>
+        <v>Marques Anthony</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/camper/1514886616</v>
+        <v>https://music.apple.com/us/artist/marques-anthony/321321231</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/love-me-feat-stevie-wonder/1867640873</v>
+        <v>https://music.apple.com/us/album/say-yes/1861995089</v>
       </c>
       <c r="L144" t="str">
-        <v>LOVE ME (feat. Stevie Wonder) - Camper</v>
+        <v>Say Yes - Marques Anthony</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>UP TO MY NECK IN U</v>
+        <v>LOVE ME (feat. Stevie Wonder)</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
+        <v>https://music.apple.com/us/song/love-me-feat-stevie-wonder/1867640879</v>
       </c>
       <c r="D145" t="str">
         <v>2026-01-23</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>UP TO MY NECK IN U - Single</v>
+        <v>CAMPILATION</v>
       </c>
       <c r="G145" t="str">
-        <v>2:17</v>
+        <v>3:10</v>
       </c>
       <c r="H145" t="str">
-        <v>Ledbyher</v>
+        <v>Camper</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
+        <v>https://music.apple.com/us/artist/camper/1514886616</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/up-to-my-neck-in-u/1862550671</v>
+        <v>https://music.apple.com/us/album/love-me-feat-stevie-wonder/1867640873</v>
       </c>
       <c r="L145" t="str">
-        <v>UP TO MY NECK IN U - Ledbyher</v>
+        <v>LOVE ME (feat. Stevie Wonder) - Camper</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Wallflower</v>
+        <v>UP TO MY NECK IN U</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/wallflower/1862737077</v>
+        <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
       </c>
       <c r="D146" t="str">
         <v>2026-01-23</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Wallflower - Single</v>
+        <v>UP TO MY NECK IN U - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:25</v>
+        <v>2:17</v>
       </c>
       <c r="H146" t="str">
-        <v>Sikarus</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/sikarus/1046558781</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/wallflower/1862737074</v>
+        <v>https://music.apple.com/us/album/up-to-my-neck-in-u/1862550671</v>
       </c>
       <c r="L146" t="str">
-        <v>Wallflower - Sikarus</v>
+        <v>UP TO MY NECK IN U - Ledbyher</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>You Phase</v>
+        <v>Wallflower</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/you-phase/1868861897</v>
+        <v>https://music.apple.com/us/song/wallflower/1862737077</v>
       </c>
       <c r="D147" t="str">
         <v>2026-01-23</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>You Phase - Single</v>
+        <v>Wallflower - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>2:51</v>
+        <v>3:25</v>
       </c>
       <c r="H147" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Sikarus</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/mitchell-tenpenny/430369368</v>
+        <v>https://music.apple.com/us/artist/sikarus/1046558781</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/you-phase/1868861895</v>
+        <v>https://music.apple.com/us/album/wallflower/1862737074</v>
       </c>
       <c r="L147" t="str">
-        <v>You Phase - Mitchell Tenpenny</v>
+        <v>Wallflower - Sikarus</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Miss Independent</v>
+        <v>You Phase</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
+        <v>https://music.apple.com/us/song/you-phase/1868861897</v>
       </c>
       <c r="D148" t="str">
         <v>2026-01-23</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Miss Independent - Single</v>
+        <v>You Phase - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>2:40</v>
+        <v>2:51</v>
       </c>
       <c r="H148" t="str">
-        <v>1Ski OG</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/mitchell-tenpenny/430369368</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/miss-independent/1870612555</v>
+        <v>https://music.apple.com/us/album/you-phase/1868861895</v>
       </c>
       <c r="L148" t="str">
-        <v>Miss Independent - 1Ski OG</v>
+        <v>You Phase - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live]</v>
+        <v>Miss Independent</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678482</v>
+        <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
       </c>
       <c r="D149" t="str">
         <v>2026-01-23</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>SO BE IT (Live)</v>
+        <v>Miss Independent - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>5:47</v>
+        <v>2:40</v>
       </c>
       <c r="H149" t="str">
-        <v>Elevation Worship</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678481</v>
+        <v>https://music.apple.com/us/album/miss-independent/1870612555</v>
       </c>
       <c r="L149" t="str">
-        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live] - Elevation Worship</v>
+        <v>Miss Independent - 1Ski OG</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>go again</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live]</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/go-again/1868987466</v>
+        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678482</v>
       </c>
       <c r="D150" t="str">
         <v>2026-01-23</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>go again - Single</v>
+        <v>SO BE IT (Live)</v>
       </c>
       <c r="G150" t="str">
-        <v>2:07</v>
+        <v>5:47</v>
       </c>
       <c r="H150" t="str">
-        <v>NateTaylorr</v>
+        <v>Elevation Worship</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/natetaylorr/1243682934</v>
+        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/go-again/1868987193</v>
+        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678481</v>
       </c>
       <c r="L150" t="str">
-        <v>go again - NateTaylorr</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live] - Elevation Worship</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Autopilot</v>
+        <v>go again</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/autopilot/1863072399</v>
+        <v>https://music.apple.com/us/song/go-again/1868987466</v>
       </c>
       <c r="D151" t="str">
         <v>2026-01-23</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Autopilot</v>
+        <v>go again - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>2:46</v>
+        <v>2:07</v>
       </c>
       <c r="H151" t="str">
-        <v>ALEXSUCKS</v>
+        <v>NateTaylorr</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
+        <v>https://music.apple.com/us/artist/natetaylorr/1243682934</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/autopilot/1863072393</v>
+        <v>https://music.apple.com/us/album/go-again/1868987193</v>
       </c>
       <c r="L151" t="str">
-        <v>Autopilot - ALEXSUCKS</v>
+        <v>go again - NateTaylorr</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Portrait of My Heart (feat. Brendan Yates)</v>
+        <v>Autopilot</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
+        <v>https://music.apple.com/us/song/autopilot/1863072399</v>
       </c>
       <c r="D152" t="str">
         <v>2026-01-23</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Portrait of My Heart - Single</v>
+        <v>Autopilot</v>
       </c>
       <c r="G152" t="str">
-        <v>3:04</v>
+        <v>2:46</v>
       </c>
       <c r="H152" t="str">
-        <v>SPELLLING</v>
+        <v>ALEXSUCKS</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/spellling/1281213673</v>
+        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/portrait-of-my-heart-feat-brendan-yates/1862282167</v>
+        <v>https://music.apple.com/us/album/autopilot/1863072393</v>
       </c>
       <c r="L152" t="str">
-        <v>Portrait of My Heart (feat. Brendan Yates) - SPELLLING</v>
+        <v>Autopilot - ALEXSUCKS</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>In Violet</v>
+        <v>Portrait of My Heart (feat. Brendan Yates)</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/in-violet/1839471290</v>
+        <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
       </c>
       <c r="D153" t="str">
         <v>2026-01-23</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Death in the Business of Whaling</v>
+        <v>Portrait of My Heart - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>4:09</v>
+        <v>3:04</v>
       </c>
       <c r="H153" t="str">
-        <v>Searows</v>
+        <v>SPELLLING</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/searows/1607240507</v>
+        <v>https://music.apple.com/us/artist/spellling/1281213673</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/in-violet/1839470844</v>
+        <v>https://music.apple.com/us/album/portrait-of-my-heart-feat-brendan-yates/1862282167</v>
       </c>
       <c r="L153" t="str">
-        <v>In Violet - Searows</v>
+        <v>Portrait of My Heart (feat. Brendan Yates) - SPELLLING</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Baby Run</v>
+        <v>In Violet</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/baby-run/1857658819</v>
+        <v>https://music.apple.com/us/song/in-violet/1839471290</v>
       </c>
       <c r="D154" t="str">
         <v>2026-01-23</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Baby Run - Single</v>
+        <v>Death in the Business of Whaling</v>
       </c>
       <c r="G154" t="str">
-        <v>4:47</v>
+        <v>4:09</v>
       </c>
       <c r="H154" t="str">
-        <v>Jimi Jules</v>
+        <v>Searows</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/jimi-jules/586933009</v>
+        <v>https://music.apple.com/us/artist/searows/1607240507</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/baby-run/1857658816</v>
+        <v>https://music.apple.com/us/album/in-violet/1839470844</v>
       </c>
       <c r="L154" t="str">
-        <v>Baby Run - Jimi Jules</v>
+        <v>In Violet - Searows</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>What If We Don't</v>
+        <v>Baby Run</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
+        <v>https://music.apple.com/us/song/baby-run/1857658819</v>
       </c>
       <c r="D155" t="str">
         <v>2026-01-23</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>What If We Don't - Single</v>
+        <v>Baby Run - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:06</v>
+        <v>4:47</v>
       </c>
       <c r="H155" t="str">
-        <v>Ashley McBryde</v>
+        <v>Jimi Jules</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/jimi-jules/586933009</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/what-if-we-dont/1862668776</v>
+        <v>https://music.apple.com/us/album/baby-run/1857658816</v>
       </c>
       <c r="L155" t="str">
-        <v>What If We Don't - Ashley McBryde</v>
+        <v>Baby Run - Jimi Jules</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Hagamos Que</v>
+        <v>What If We Don't</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
+        <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
       </c>
       <c r="D156" t="str">
         <v>2026-01-23</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Hagamos Que - Single</v>
+        <v>What If We Don't - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>2:58</v>
+        <v>3:06</v>
       </c>
       <c r="H156" t="str">
-        <v>Juanes</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/juanes/103856</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/hagamos-que/1861956611</v>
+        <v>https://music.apple.com/us/album/what-if-we-dont/1862668776</v>
       </c>
       <c r="L156" t="str">
-        <v>Hagamos Que - Juanes</v>
+        <v>What If We Don't - Ashley McBryde</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>World Change Me</v>
+        <v>Hagamos Que</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
+        <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
       </c>
       <c r="D157" t="str">
         <v>2026-01-23</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>World Change Me - Single</v>
+        <v>Hagamos Que - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>3:03</v>
+        <v>2:58</v>
       </c>
       <c r="H157" t="str">
-        <v>Max McNown</v>
+        <v>Juanes</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/juanes/103856</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/world-change-me/1860974598</v>
+        <v>https://music.apple.com/us/album/hagamos-que/1861956611</v>
       </c>
       <c r="L157" t="str">
-        <v>World Change Me - Max McNown</v>
+        <v>Hagamos Que - Juanes</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Exclusive</v>
+        <v>World Change Me</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/exclusive/1851537672</v>
+        <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
       </c>
       <c r="D158" t="str">
         <v>2026-01-23</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Exclusive - EP</v>
+        <v>World Change Me - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:20</v>
+        <v>3:03</v>
       </c>
       <c r="H158" t="str">
-        <v>Hudson Westbrook</v>
+        <v>Max McNown</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/exclusive/1851537671</v>
+        <v>https://music.apple.com/us/album/world-change-me/1860974598</v>
       </c>
       <c r="L158" t="str">
-        <v>Exclusive - Hudson Westbrook</v>
+        <v>World Change Me - Max McNown</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Say Less</v>
+        <v>Exclusive</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/say-less/1867910122</v>
+        <v>https://music.apple.com/us/song/exclusive/1851537672</v>
       </c>
       <c r="D159" t="str">
         <v>2026-01-23</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Say Less - Single</v>
+        <v>Exclusive - EP</v>
       </c>
       <c r="G159" t="str">
-        <v>2:18</v>
+        <v>3:20</v>
       </c>
       <c r="H159" t="str">
-        <v>JYT</v>
+        <v>Hudson Westbrook</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
+        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/say-less/1867910115</v>
+        <v>https://music.apple.com/us/album/exclusive/1851537671</v>
       </c>
       <c r="L159" t="str">
-        <v>Say Less - JYT</v>
+        <v>Exclusive - Hudson Westbrook</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Angels Cry</v>
+        <v>Say Less</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
+        <v>https://music.apple.com/us/song/say-less/1867910122</v>
       </c>
       <c r="D160" t="str">
         <v>2026-01-23</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>X's for Eyes (Deluxe)</v>
+        <v>Say Less - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:52</v>
+        <v>2:18</v>
       </c>
       <c r="H160" t="str">
-        <v>The Red Jumpsuit Apparatus</v>
+        <v>JYT</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/the-red-jumpsuit-apparatus/130037074</v>
+        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/angels-cry/1862320872</v>
+        <v>https://music.apple.com/us/album/say-less/1867910115</v>
       </c>
       <c r="L160" t="str">
-        <v>Angels Cry - The Red Jumpsuit Apparatus</v>
+        <v>Say Less - JYT</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Over You</v>
+        <v>Angels Cry</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/over-you/1846189473</v>
+        <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
       </c>
       <c r="D161" t="str">
         <v>2026-01-23</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>A Love For Strangers</v>
+        <v>X's for Eyes (Deluxe)</v>
       </c>
       <c r="G161" t="str">
-        <v>4:44</v>
+        <v>3:52</v>
       </c>
       <c r="H161" t="str">
-        <v>Chet Faker</v>
+        <v>The Red Jumpsuit Apparatus</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
+        <v>https://music.apple.com/us/artist/the-red-jumpsuit-apparatus/130037074</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/over-you/1846189472</v>
+        <v>https://music.apple.com/us/album/angels-cry/1862320872</v>
       </c>
       <c r="L161" t="str">
-        <v>Over You - Chet Faker</v>
+        <v>Angels Cry - The Red Jumpsuit Apparatus</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Chala (My Soul Is on a Loop)</v>
+        <v>Over You</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
+        <v>https://music.apple.com/us/song/over-you/1846189473</v>
       </c>
       <c r="D162" t="str">
         <v>2026-01-23</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Chala (My Soul Is on a Loop) - Single</v>
+        <v>A Love For Strangers</v>
       </c>
       <c r="G162" t="str">
-        <v>2:42</v>
+        <v>4:44</v>
       </c>
       <c r="H162" t="str">
-        <v>Barry Can't Swim</v>
+        <v>Chet Faker</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/barry-cant-swim/1492752064</v>
+        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/chala-my-soul-is-on-a-loop/1857789040</v>
+        <v>https://music.apple.com/us/album/over-you/1846189472</v>
       </c>
       <c r="L162" t="str">
-        <v>Chala (My Soul Is on a Loop) - Barry Can't Swim</v>
+        <v>Over You - Chet Faker</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>starlight feat. Madeline Follin</v>
+        <v>Chala (My Soul Is on a Loop)</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
+        <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
       </c>
       <c r="D163" t="str">
         <v>2026-01-23</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>starlight feat. Madeline Follin - Single</v>
+        <v>Chala (My Soul Is on a Loop) - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:06</v>
+        <v>2:42</v>
       </c>
       <c r="H163" t="str">
-        <v>Disco Lines</v>
+        <v>Barry Can't Swim</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/disco-lines/1462793893</v>
+        <v>https://music.apple.com/us/artist/barry-cant-swim/1492752064</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/starlight-feat-madeline-follin/1869330767</v>
+        <v>https://music.apple.com/us/album/chala-my-soul-is-on-a-loop/1857789040</v>
       </c>
       <c r="L163" t="str">
-        <v>starlight feat. Madeline Follin - Disco Lines</v>
+        <v>Chala (My Soul Is on a Loop) - Barry Can't Swim</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Locked In (feat. Trippie Redd)</v>
+        <v>starlight feat. Madeline Follin</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
+        <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
       </c>
       <c r="D164" t="str">
         <v>2026-01-23</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Locked In (feat. Trippie Redd) - Single</v>
+        <v>starlight feat. Madeline Follin - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>2:48</v>
+        <v>3:06</v>
       </c>
       <c r="H164" t="str">
-        <v>David Guetta</v>
+        <v>Disco Lines</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/david-guetta/5557599</v>
+        <v>https://music.apple.com/us/artist/disco-lines/1462793893</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/locked-in-feat-trippie-redd/1869439982</v>
+        <v>https://music.apple.com/us/album/starlight-feat-madeline-follin/1869330767</v>
       </c>
       <c r="L164" t="str">
-        <v>Locked In (feat. Trippie Redd) - David Guetta</v>
+        <v>starlight feat. Madeline Follin - Disco Lines</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Rejoice</v>
+        <v>Locked In (feat. Trippie Redd)</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/rejoice/1862633596</v>
+        <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
       </c>
       <c r="D165" t="str">
         <v>2026-01-23</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Rejoice - Single</v>
+        <v>Locked In (feat. Trippie Redd) - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>4:20</v>
+        <v>2:48</v>
       </c>
       <c r="H165" t="str">
-        <v>Def Leppard</v>
+        <v>David Guetta</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/def-leppard/117554</v>
+        <v>https://music.apple.com/us/artist/david-guetta/5557599</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/rejoice/1862633593</v>
+        <v>https://music.apple.com/us/album/locked-in-feat-trippie-redd/1869439982</v>
       </c>
       <c r="L165" t="str">
-        <v>Rejoice - Def Leppard</v>
+        <v>Locked In (feat. Trippie Redd) - David Guetta</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Slight Werk (feat. Bree Runway) [Club Mix]</v>
+        <v>Rejoice</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
+        <v>https://music.apple.com/us/song/rejoice/1862633596</v>
       </c>
       <c r="D166" t="str">
         <v>2026-01-23</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Slight Werk (Club Mix) [feat. Bree Runway] - Single</v>
+        <v>Rejoice - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>2:58</v>
+        <v>4:20</v>
       </c>
       <c r="H166" t="str">
-        <v>Honey Dijon</v>
+        <v>Def Leppard</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
+        <v>https://music.apple.com/us/artist/def-leppard/117554</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/slight-werk-feat-bree-runway-club-mix/1860859551</v>
+        <v>https://music.apple.com/us/album/rejoice/1862633593</v>
       </c>
       <c r="L166" t="str">
-        <v>Slight Werk (feat. Bree Runway) [Club Mix] - Honey Dijon</v>
+        <v>Rejoice - Def Leppard</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Lucky Day</v>
+        <v>Slight Werk (feat. Bree Runway) [Club Mix]</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
+        <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
       </c>
       <c r="D167" t="str">
         <v>2026-01-23</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Speed Kills</v>
+        <v>Slight Werk (Club Mix) [feat. Bree Runway] - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:13</v>
+        <v>2:58</v>
       </c>
       <c r="H167" t="str">
-        <v>Ally Evenson</v>
+        <v>Honey Dijon</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/ally-evenson/283908113</v>
+        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/lucky-day/1849264498</v>
+        <v>https://music.apple.com/us/album/slight-werk-feat-bree-runway-club-mix/1860859551</v>
       </c>
       <c r="L167" t="str">
-        <v>Lucky Day - Ally Evenson</v>
+        <v>Slight Werk (feat. Bree Runway) [Club Mix] - Honey Dijon</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Breathe On It</v>
+        <v>Lucky Day</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
+        <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
       </c>
       <c r="D168" t="str">
         <v>2026-01-23</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Breathe On It - Single</v>
+        <v>Speed Kills</v>
       </c>
       <c r="G168" t="str">
-        <v>4:00</v>
+        <v>3:13</v>
       </c>
       <c r="H168" t="str">
-        <v>Tauren Wells</v>
+        <v>Ally Evenson</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
+        <v>https://music.apple.com/us/artist/ally-evenson/283908113</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/breathe-on-it/1862938798</v>
+        <v>https://music.apple.com/us/album/lucky-day/1849264498</v>
       </c>
       <c r="L168" t="str">
-        <v>Breathe On It - Tauren Wells</v>
+        <v>Lucky Day - Ally Evenson</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Easy</v>
+        <v>Breathe On It</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/easy/1863456906</v>
+        <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
       </c>
       <c r="D169" t="str">
         <v>2026-01-23</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Easy - Single</v>
+        <v>Breathe On It - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>4:30</v>
+        <v>4:00</v>
       </c>
       <c r="H169" t="str">
-        <v>lydi lynn</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
+        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/easy/1863456903</v>
+        <v>https://music.apple.com/us/album/breathe-on-it/1862938798</v>
       </c>
       <c r="L169" t="str">
-        <v>Easy - lydi lynn</v>
+        <v>Breathe On It - Tauren Wells</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Break Me In</v>
+        <v>Easy</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
+        <v>https://music.apple.com/us/song/easy/1863456906</v>
       </c>
       <c r="D170" t="str">
         <v>2026-01-23</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Break Me In - Single</v>
+        <v>Easy - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:52</v>
+        <v>4:30</v>
       </c>
       <c r="H170" t="str">
-        <v>Joyce Wrice</v>
+        <v>lydi lynn</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/joyce-wrice/591991458</v>
+        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/break-me-in/1862881766</v>
+        <v>https://music.apple.com/us/album/easy/1863456903</v>
       </c>
       <c r="L170" t="str">
-        <v>Break Me In - Joyce Wrice</v>
+        <v>Easy - lydi lynn</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Long Live Love</v>
+        <v>Break Me In</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
+        <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
       </c>
       <c r="D171" t="str">
         <v>2026-01-23</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Long Live Love - Single</v>
+        <v>Break Me In - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:36</v>
+        <v>2:52</v>
       </c>
       <c r="H171" t="str">
-        <v>Sugar</v>
+        <v>Joyce Wrice</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/sugar/530175867</v>
+        <v>https://music.apple.com/us/artist/joyce-wrice/591991458</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/long-live-love/1851251226</v>
+        <v>https://music.apple.com/us/album/break-me-in/1862881766</v>
       </c>
       <c r="L171" t="str">
-        <v>Long Live Love - Sugar</v>
+        <v>Break Me In - Joyce Wrice</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Depressed</v>
+        <v>Long Live Love</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/depressed/1840400522</v>
+        <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
       </c>
       <c r="D172" t="str">
         <v>2026-01-23</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Boycott Heaven</v>
+        <v>Long Live Love - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:32</v>
+        <v>2:36</v>
       </c>
       <c r="H172" t="str">
-        <v>The Format</v>
+        <v>Sugar</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/the-format/3064903</v>
+        <v>https://music.apple.com/us/artist/sugar/530175867</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/depressed/1840399886</v>
+        <v>https://music.apple.com/us/album/long-live-love/1851251226</v>
       </c>
       <c r="L172" t="str">
-        <v>Depressed - The Format</v>
+        <v>Long Live Love - Sugar</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Empty Hands</v>
+        <v>Depressed</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
+        <v>https://music.apple.com/us/song/depressed/1840400522</v>
       </c>
       <c r="D173" t="str">
         <v>2026-01-23</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Empty Hands</v>
+        <v>Boycott Heaven</v>
       </c>
       <c r="G173" t="str">
-        <v>3:09</v>
+        <v>3:32</v>
       </c>
       <c r="H173" t="str">
-        <v>Poppy</v>
+        <v>The Format</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/poppy/1004130511</v>
+        <v>https://music.apple.com/us/artist/the-format/3064903</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/empty-hands/1852046141</v>
+        <v>https://music.apple.com/us/album/depressed/1840399886</v>
       </c>
       <c r="L173" t="str">
-        <v>Empty Hands - Poppy</v>
+        <v>Depressed - The Format</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>The Long Surrender</v>
+        <v>Empty Hands</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
+        <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
       </c>
       <c r="D174" t="str">
         <v>2026-01-23</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>The Long Surrender</v>
+        <v>Empty Hands</v>
       </c>
       <c r="G174" t="str">
-        <v>3:45</v>
+        <v>3:09</v>
       </c>
       <c r="H174" t="str">
-        <v>NEEDTOBREATHE</v>
+        <v>Poppy</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/needtobreathe/113247214</v>
+        <v>https://music.apple.com/us/artist/poppy/1004130511</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/the-long-surrender/1861935699</v>
+        <v>https://music.apple.com/us/album/empty-hands/1852046141</v>
       </c>
       <c r="L174" t="str">
-        <v>The Long Surrender - NEEDTOBREATHE</v>
+        <v>Empty Hands - Poppy</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Angela</v>
+        <v>The Long Surrender</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/angela/1866624257</v>
+        <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
       </c>
       <c r="D175" t="str">
         <v>2026-01-23</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Angela - Single</v>
+        <v>The Long Surrender</v>
       </c>
       <c r="G175" t="str">
-        <v>3:32</v>
+        <v>3:45</v>
       </c>
       <c r="H175" t="str">
-        <v>Hayden Everett</v>
+        <v>NEEDTOBREATHE</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/needtobreathe/113247214</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/angela/1866624256</v>
+        <v>https://music.apple.com/us/album/the-long-surrender/1861935699</v>
       </c>
       <c r="L175" t="str">
-        <v>Angela - Hayden Everett</v>
+        <v>The Long Surrender - NEEDTOBREATHE</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Disappear</v>
+        <v>Angela</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/disappear/1847663553</v>
+        <v>https://music.apple.com/us/song/angela/1866624257</v>
       </c>
       <c r="D176" t="str">
         <v>2026-01-23</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Greyhound</v>
+        <v>Angela - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:31</v>
+        <v>3:32</v>
       </c>
       <c r="H176" t="str">
-        <v>Katie Tupper</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/katie-tupper/1395542470</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/disappear/1847663546</v>
+        <v>https://music.apple.com/us/album/angela/1866624256</v>
       </c>
       <c r="L176" t="str">
-        <v>Disappear - Katie Tupper</v>
+        <v>Angela - Hayden Everett</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Catapult</v>
+        <v>Disappear</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/catapult/1862951335</v>
+        <v>https://music.apple.com/us/song/disappear/1847663553</v>
       </c>
       <c r="D177" t="str">
         <v>2026-01-23</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Catapult - Single</v>
+        <v>Greyhound</v>
       </c>
       <c r="G177" t="str">
-        <v>2:57</v>
+        <v>3:31</v>
       </c>
       <c r="H177" t="str">
-        <v>Cape Francis</v>
+        <v>Katie Tupper</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/cape-francis/1242523550</v>
+        <v>https://music.apple.com/us/artist/katie-tupper/1395542470</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/catapult/1862951333</v>
+        <v>https://music.apple.com/us/album/disappear/1847663546</v>
       </c>
       <c r="L177" t="str">
-        <v>Catapult - Cape Francis</v>
+        <v>Disappear - Katie Tupper</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Think Twice</v>
+        <v>Catapult</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/think-twice/1850698548</v>
+        <v>https://music.apple.com/us/song/catapult/1862951335</v>
       </c>
       <c r="D178" t="str">
         <v>2026-01-23</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Think Twice - Single</v>
+        <v>Catapult - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:22</v>
+        <v>2:57</v>
       </c>
       <c r="H178" t="str">
-        <v>Leonie Biney</v>
+        <v>Cape Francis</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
+        <v>https://music.apple.com/us/artist/cape-francis/1242523550</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/think-twice/1850698545</v>
+        <v>https://music.apple.com/us/album/catapult/1862951333</v>
       </c>
       <c r="L178" t="str">
-        <v>Think Twice - Leonie Biney</v>
+        <v>Catapult - Cape Francis</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>LOVESONGS</v>
+        <v>Think Twice</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
+        <v>https://music.apple.com/us/song/think-twice/1850698548</v>
       </c>
       <c r="D179" t="str">
         <v>2026-01-23</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>BEAUTIFUL MADNESS</v>
+        <v>Think Twice - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:33</v>
+        <v>2:22</v>
       </c>
       <c r="H179" t="str">
-        <v>Agnes</v>
+        <v>Leonie Biney</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/agnes/42568985</v>
+        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/lovesongs/1849098275</v>
+        <v>https://music.apple.com/us/album/think-twice/1850698545</v>
       </c>
       <c r="L179" t="str">
-        <v>LOVESONGS - Agnes</v>
+        <v>Think Twice - Leonie Biney</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Down South</v>
+        <v>LOVESONGS</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/down-south/1861010793</v>
+        <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
       </c>
       <c r="D180" t="str">
         <v>2026-01-23</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Down South - Single</v>
+        <v>BEAUTIFUL MADNESS</v>
       </c>
       <c r="G180" t="str">
-        <v>2:19</v>
+        <v>3:33</v>
       </c>
       <c r="H180" t="str">
-        <v>Trap Dickey</v>
+        <v>Agnes</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
+        <v>https://music.apple.com/us/artist/agnes/42568985</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/down-south/1861010788</v>
+        <v>https://music.apple.com/us/album/lovesongs/1849098275</v>
       </c>
       <c r="L180" t="str">
-        <v>Down South - Trap Dickey</v>
+        <v>LOVESONGS - Agnes</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW</v>
+        <v>Down South</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
+        <v>https://music.apple.com/us/song/down-south/1861010793</v>
       </c>
       <c r="D181" t="str">
         <v>2026-01-23</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW - Single</v>
+        <v>Down South - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:16</v>
+        <v>2:19</v>
       </c>
       <c r="H181" t="str">
-        <v>SALIMATA</v>
+        <v>Trap Dickey</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/salimata/690253822</v>
+        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/jackpot-foil-a-colors-show/1866998655</v>
+        <v>https://music.apple.com/us/album/down-south/1861010788</v>
       </c>
       <c r="L181" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW - SALIMATA</v>
+        <v>Down South - Trap Dickey</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Love Like This</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
+        <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
       </c>
       <c r="D182" t="str">
         <v>2026-01-23</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Love Like This - Single</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:30</v>
+        <v>2:16</v>
       </c>
       <c r="H182" t="str">
-        <v>Jacob Banks</v>
+        <v>SALIMATA</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/jacob-banks/625014171</v>
+        <v>https://music.apple.com/us/artist/salimata/690253822</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/love-like-this/1866999617</v>
+        <v>https://music.apple.com/us/album/jackpot-foil-a-colors-show/1866998655</v>
       </c>
       <c r="L182" t="str">
-        <v>Love Like This - Jacob Banks</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW - SALIMATA</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Plan Plan</v>
+        <v>Love Like This</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
+        <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
       </c>
       <c r="D183" t="str">
         <v>2026-01-23</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>La Locura</v>
+        <v>Love Like This - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:10</v>
+        <v>3:30</v>
       </c>
       <c r="H183" t="str">
-        <v>Funky</v>
+        <v>Jacob Banks</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/funky/80960663</v>
+        <v>https://music.apple.com/us/artist/jacob-banks/625014171</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/plan-plan/1867940087</v>
+        <v>https://music.apple.com/us/album/love-like-this/1866999617</v>
       </c>
       <c r="L183" t="str">
-        <v>Plan Plan - Funky</v>
+        <v>Love Like This - Jacob Banks</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>double edged sword</v>
+        <v>Plan Plan</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
+        <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
       </c>
       <c r="D184" t="str">
         <v>2026-01-23</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>double edged sword - Single</v>
+        <v>La Locura</v>
       </c>
       <c r="G184" t="str">
-        <v>3:28</v>
+        <v>3:10</v>
       </c>
       <c r="H184" t="str">
-        <v>Hailey Picardi</v>
+        <v>Funky</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/funky/80960663</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/double-edged-sword/1868829044</v>
+        <v>https://music.apple.com/us/album/plan-plan/1867940087</v>
       </c>
       <c r="L184" t="str">
-        <v>double edged sword - Hailey Picardi</v>
+        <v>Plan Plan - Funky</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>SOMEWHERE IN BETWEEN</v>
+        <v>double edged sword</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
+        <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
       </c>
       <c r="D185" t="str">
         <v>2026-01-23</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>SOMEWHERE IN BETWEEN - Single</v>
+        <v>double edged sword - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:27</v>
+        <v>3:28</v>
       </c>
       <c r="H185" t="str">
-        <v>Matt Hansen</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/matt-hansen/1442658353</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/somewhere-in-between/1866969151</v>
+        <v>https://music.apple.com/us/album/double-edged-sword/1868829044</v>
       </c>
       <c r="L185" t="str">
-        <v>SOMEWHERE IN BETWEEN - Matt Hansen</v>
+        <v>double edged sword - Hailey Picardi</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>The Decay</v>
+        <v>SOMEWHERE IN BETWEEN</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/the-decay/1862836783</v>
+        <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
       </c>
       <c r="D186" t="str">
         <v>2026-01-23</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>What Remains (Midnight Edition)</v>
+        <v>SOMEWHERE IN BETWEEN - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:20</v>
+        <v>3:27</v>
       </c>
       <c r="H186" t="str">
-        <v>Pop Evil</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/pop-evil/441597923</v>
+        <v>https://music.apple.com/us/artist/matt-hansen/1442658353</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/the-decay/1862836507</v>
+        <v>https://music.apple.com/us/album/somewhere-in-between/1866969151</v>
       </c>
       <c r="L186" t="str">
-        <v>The Decay - Pop Evil</v>
+        <v>SOMEWHERE IN BETWEEN - Matt Hansen</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>3111</v>
+        <v>The Decay</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/3111/1862225387</v>
+        <v>https://music.apple.com/us/song/the-decay/1862836783</v>
       </c>
       <c r="D187" t="str">
         <v>2026-01-23</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Goliath</v>
+        <v>What Remains (Midnight Edition)</v>
       </c>
       <c r="G187" t="str">
-        <v>4:08</v>
+        <v>3:20</v>
       </c>
       <c r="H187" t="str">
-        <v>Exodus</v>
+        <v>Pop Evil</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
+        <v>https://music.apple.com/us/artist/pop-evil/441597923</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/3111/1862225385</v>
+        <v>https://music.apple.com/us/album/the-decay/1862836507</v>
       </c>
       <c r="L187" t="str">
-        <v>3111 - Exodus</v>
+        <v>The Decay - Pop Evil</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Touch My Love And Die</v>
+        <v>3111</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
+        <v>https://music.apple.com/us/song/3111/1862225387</v>
       </c>
       <c r="D188" t="str">
         <v>2026-01-23</v>
@@ -7519,68 +7519,106 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Touch My Love And Die - Single</v>
+        <v>Goliath</v>
       </c>
       <c r="G188" t="str">
-        <v>2:57</v>
+        <v>4:08</v>
       </c>
       <c r="H188" t="str">
-        <v>Myrkur</v>
+        <v>Exodus</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/myrkur/293296859</v>
+        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/touch-my-love-and-die/1867630168</v>
+        <v>https://music.apple.com/us/album/3111/1862225385</v>
       </c>
       <c r="L188" t="str">
-        <v>Touch My Love And Die - Myrkur</v>
+        <v>3111 - Exodus</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
+        <v>Touch My Love And Die</v>
+      </c>
+      <c r="B189" t="str">
+        <v/>
+      </c>
+      <c r="C189" t="str">
+        <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
+      </c>
+      <c r="D189" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E189" t="str">
+        <v/>
+      </c>
+      <c r="F189" t="str">
+        <v>Touch My Love And Die - Single</v>
+      </c>
+      <c r="G189" t="str">
+        <v>2:57</v>
+      </c>
+      <c r="H189" t="str">
+        <v>Myrkur</v>
+      </c>
+      <c r="I189" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J189" t="str">
+        <v>https://music.apple.com/us/artist/myrkur/293296859</v>
+      </c>
+      <c r="K189" t="str">
+        <v>https://music.apple.com/us/album/touch-my-love-and-die/1867630168</v>
+      </c>
+      <c r="L189" t="str">
+        <v>Touch My Love And Die - Myrkur</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
         <v>Bomb To A Knife Fight</v>
       </c>
-      <c r="B189" t="str">
-        <v/>
-      </c>
-      <c r="C189" t="str">
+      <c r="B190" t="str">
+        <v/>
+      </c>
+      <c r="C190" t="str">
         <v>https://music.apple.com/us/song/bomb-to-a-knife-fight/1861589406</v>
       </c>
-      <c r="D189" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E189" t="str">
-        <v/>
-      </c>
-      <c r="F189" t="str">
+      <c r="D190" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E190" t="str">
+        <v/>
+      </c>
+      <c r="F190" t="str">
         <v>Bomb To A Knife Fight - Single</v>
       </c>
-      <c r="G189" t="str">
+      <c r="G190" t="str">
         <v>2:41</v>
       </c>
-      <c r="H189" t="str">
+      <c r="H190" t="str">
         <v>The Barbarians of California</v>
       </c>
-      <c r="I189" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J189" t="str">
+      <c r="I190" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J190" t="str">
         <v>https://music.apple.com/us/artist/the-barbarians-of-california/1724096474</v>
       </c>
-      <c r="K189" t="str">
+      <c r="K190" t="str">
         <v>https://music.apple.com/us/album/bomb-to-a-knife-fight/1861589405</v>
       </c>
-      <c r="L189" t="str">
+      <c r="L190" t="str">
         <v>Bomb To A Knife Fight - The Barbarians of California</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L189"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L190"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-01-week04/titles.xlsx
+++ b/data/global/2026-01-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L190"/>
+  <dimension ref="A1:L189"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נדב גדג’ - בלי יד על הדופק</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-01-22</v>
+        <v>4 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24441&amp;forum=music&amp;viewmode=all</v>
+        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-23</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>23:52</v>
+        <v>4 hours ago</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>3:59</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I2" t="str">
-        <v>אלבומים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נדב גדג’ - בלי יד על הדופק</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B3" t="str">
-        <v>3 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
+        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-23</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>3 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>3:59</v>
+        <v>2:56</v>
       </c>
       <c r="H3" t="str">
-        <v>Holly Humberstone</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>4 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
+        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-23</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>4 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G4" t="str">
-        <v>2:56</v>
+        <v>3:46</v>
       </c>
       <c r="H4" t="str">
-        <v>Cliff Richard</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
+        <v>Dean Lewis - I Am Getting Well</v>
       </c>
       <c r="B5" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
+        <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-23</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G5" t="str">
-        <v>3:46</v>
+        <v>2:47</v>
       </c>
       <c r="H5" t="str">
-        <v>Jessie Ware</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
+        <v>Dean Lewis - I Am Getting Well - Dean Lewis</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Dean Lewis - I Am Getting Well</v>
+        <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B6" t="str">
-        <v>5 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
+        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-23</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>5 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G6" t="str">
-        <v>2:47</v>
+        <v>4:37</v>
       </c>
       <c r="H6" t="str">
-        <v>Dean Lewis</v>
+        <v>Bella White</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Dean Lewis - I Am Getting Well - Dean Lewis</v>
+        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Bella White - Dream Song (Official Audio)</v>
+        <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
+        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-23</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G7" t="str">
-        <v>4:37</v>
+        <v>4:06</v>
       </c>
       <c r="H7" t="str">
-        <v>Bella White</v>
+        <v>Ryan Wright</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
+        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video)</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B8" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
+        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-23</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G8" t="str">
-        <v>4:06</v>
+        <v>3:54</v>
       </c>
       <c r="H8" t="str">
-        <v>Ryan Wright</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
+        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-23</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G9" t="str">
-        <v>3:54</v>
+        <v>4:10</v>
       </c>
       <c r="H9" t="str">
-        <v>Dove Cameron</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
+        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Lyric Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
+        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-23</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G10" t="str">
-        <v>4:10</v>
+        <v>3:26</v>
       </c>
       <c r="H10" t="str">
-        <v>Parker McCollum</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Lyric Video)</v>
+        <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>8 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
+        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-23</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>8 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:26</v>
+        <v>2:56</v>
       </c>
       <c r="H11" t="str">
-        <v>Matt Hansen</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Lyric Video) - Matt Hansen</v>
+        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video)</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>1 day ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
+        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-23</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1 day ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G12" t="str">
         <v>2:56</v>
       </c>
       <c r="H12" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Louis Tomlinson - Imposter (Official Video) - Louis Tomlinson</v>
+        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
+        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-23</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G13" t="str">
-        <v>2:56</v>
+        <v>4:01</v>
       </c>
       <c r="H13" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Mitchell Tenpenny - You Phase (Official Music Video) - Mitchell Tenpenny</v>
+        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
+        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-23</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G14" t="str">
-        <v>4:01</v>
+        <v>3:05</v>
       </c>
       <c r="H14" t="str">
-        <v>Tauren Wells</v>
+        <v>Maiah Manser</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Tauren Wells - Breathe On It (Official Lyric Video) - Tauren Wells</v>
+        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video)</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
+        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-23</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:05</v>
+        <v>2:27</v>
       </c>
       <c r="H15" t="str">
-        <v>Maiah Manser</v>
+        <v>Taylor Austin Dye</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Maiah Manser - Feeling it All (Official Music Video) - Maiah Manser</v>
+        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
+        <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
+        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-23</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G16" t="str">
-        <v>2:27</v>
+        <v>2:34</v>
       </c>
       <c r="H16" t="str">
-        <v>Taylor Austin Dye</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Taylor Austin Dye - Man For That (Official Music Video) - Taylor Austin Dye</v>
+        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Chelsea Cutler - BAD (Official Video)</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
+        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-23</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G17" t="str">
-        <v>2:34</v>
+        <v>3:13</v>
       </c>
       <c r="H17" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Ashley Kutcher</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Chelsea Cutler - BAD (Official Video) - Chelsea Cutler</v>
+        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B18" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
+        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-23</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:13</v>
       </c>
       <c r="H18" t="str">
-        <v>Ashley Kutcher</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video) - Ashley Kutcher</v>
+        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
+        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-23</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:13</v>
+        <v>3:08</v>
       </c>
       <c r="H19" t="str">
-        <v>Louis Tomlinson</v>
+        <v>CAIN</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Louis Tomlinson - Dark To Light (Visualiser) - Louis Tomlinson</v>
+        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video)</v>
+        <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>8 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
+        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-23</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>8 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:08</v>
+        <v>5:14</v>
       </c>
       <c r="H20" t="str">
-        <v>CAIN</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>CAIN - So Long Sad Songs (Lyric Video) - CAIN</v>
+        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Harry Styles - Aperture (Official Audio)</v>
+        <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>13 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
+        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-23</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>13 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G21" t="str">
-        <v>5:14</v>
+        <v>2:59</v>
       </c>
       <c r="H21" t="str">
-        <v>Harry Styles</v>
+        <v>Lana Lubany</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Harry Styles - Aperture (Official Audio) - Harry Styles</v>
+        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video)</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
+        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-23</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G22" t="str">
-        <v>2:59</v>
+        <v>4:21</v>
       </c>
       <c r="H22" t="str">
-        <v>Lana Lubany</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Lana Lubany - BAD IDEA (Official Video) - Lana Lubany</v>
+        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video)</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B23" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=zy2TLLeNgp0</v>
+        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-23</v>
@@ -1252,10 +1252,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G23" t="str">
-        <v>4:21</v>
+        <v>4:09</v>
       </c>
       <c r="H23" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>DEF LEPPARD - Rejoice (Official Lyric Video) - DEF LEPPARD</v>
+        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video)</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
+        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-23</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>4:09</v>
+        <v>2:34</v>
       </c>
       <c r="H24" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Dermot Kennedy - Funeral (Official Music Video) - Dermot Kennedy</v>
+        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video)</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
       </c>
       <c r="B25" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=kfF0bVZMCw0</v>
+        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-23</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:34</v>
+        <v>3:10</v>
       </c>
       <c r="H25" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Lauren Sanderson - SPELL IT OUT (Official Music Video) - Lauren Sanderson</v>
+        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show]</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
       </c>
       <c r="B26" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=dLzpNstMHZY</v>
+        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-23</v>
@@ -1366,10 +1366,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:10</v>
+        <v>3:21</v>
       </c>
       <c r="H26" t="str">
-        <v>Olivia Dean</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Olivia Dean - So Easy (To Fall In Love) [Live on The Graham Norton Show] - Olivia Dean</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel)</v>
+        <v>The Avett Brothers - Matrimony (Official Video)</v>
       </c>
       <c r="B27" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=fo_j8Fqag8I</v>
+        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-23</v>
@@ -1404,10 +1404,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:21</v>
+        <v>3:06</v>
       </c>
       <c r="H27" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>The Avett Brothers</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Chapel) - David Guetta and Tones And I</v>
+        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video)</v>
+        <v>Jordana Bryant - Love Like That (Official Video)</v>
       </c>
       <c r="B28" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=7sD9-MtV9CY</v>
+        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-23</v>
@@ -1442,10 +1442,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:06</v>
+        <v>3:21</v>
       </c>
       <c r="H28" t="str">
-        <v>The Avett Brothers</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>The Avett Brothers - Matrimony (Official Video) - The Avett Brothers</v>
+        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video)</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
       </c>
       <c r="B29" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=3ATlH-Rtzmk</v>
+        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-23</v>
@@ -1480,10 +1480,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:21</v>
+        <v>7:21</v>
       </c>
       <c r="H29" t="str">
-        <v>Jordana Bryant</v>
+        <v>Katy Perry</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Jordana Bryant - Love Like That (Official Video) - Jordana Bryant</v>
+        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B30" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=kIRmKmEb2g0</v>
+        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-23</v>
@@ -1518,10 +1518,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>7:21</v>
+        <v>3:17</v>
       </c>
       <c r="H30" t="str">
-        <v>Katy Perry</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Katy Perry Roar-Dark Horse-Firework | Live @ Joy Awards - Katy Perry</v>
+        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
+        <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B31" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
+        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-23</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:17</v>
+        <v>3:45</v>
       </c>
       <c r="H31" t="str">
-        <v>Lauren Watkins</v>
+        <v>Tones And I</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Just A Mess (Live acoustic studio session)</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
       </c>
       <c r="B32" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
+        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
       </c>
       <c r="D32" t="str">
         <v>2026-01-23</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:45</v>
+        <v>3:57</v>
       </c>
       <c r="H32" t="str">
-        <v>Tones And I</v>
+        <v>Ashleigh Dallas</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Just A Mess (Live acoustic studio session) - Tones And I</v>
+        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio)</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=66PDbaI-BVA</v>
+        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
       </c>
       <c r="D33" t="str">
         <v>2026-01-23</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:57</v>
+        <v>3:03</v>
       </c>
       <c r="H33" t="str">
-        <v>Ashleigh Dallas</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Ashleigh Dallas - Sail Away (Official Audio) - Ashleigh Dallas</v>
+        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video)</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B34" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=4tmW_JSXHII</v>
+        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
       </c>
       <c r="D34" t="str">
         <v>2026-01-23</v>
@@ -1670,10 +1670,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:03</v>
+        <v>4:27</v>
       </c>
       <c r="H34" t="str">
-        <v>Charlie Puth</v>
+        <v>Chappell Roan</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Performance Video) - Charlie Puth</v>
+        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City)</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B35" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
+        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
       </c>
       <c r="D35" t="str">
         <v>2026-01-23</v>
@@ -1708,10 +1708,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>4:27</v>
+        <v>4:34</v>
       </c>
       <c r="H35" t="str">
-        <v>Chappell Roan</v>
+        <v>Armik</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Chappell Roan - The Subway (Live from Kansas City) - Chappell Roan</v>
+        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B36" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
+        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
       </c>
       <c r="D36" t="str">
         <v>2026-01-23</v>
@@ -1746,10 +1746,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>4:34</v>
+        <v>2:54</v>
       </c>
       <c r="H36" t="str">
-        <v>Armik</v>
+        <v>LØLØ</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>LØLØ - 007 (Official Music Video)</v>
+        <v>Tenille Townes - enabling (Official Visualizer)</v>
       </c>
       <c r="B37" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
+        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
       </c>
       <c r="D37" t="str">
         <v>2026-01-23</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>2:54</v>
+        <v>3:25</v>
       </c>
       <c r="H37" t="str">
-        <v>LØLØ</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>LØLØ - 007 (Official Music Video) - LØLØ</v>
+        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer)</v>
+        <v>Alan Walker - Not Home (Official Lyric Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=yL_TxDF8WtI</v>
+        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
       </c>
       <c r="D38" t="str">
         <v>2026-01-23</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:25</v>
+        <v>2:01</v>
       </c>
       <c r="H38" t="str">
-        <v>Tenille Townes</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Tenille Townes - enabling (Official Visualizer) - Tenille Townes</v>
+        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video)</v>
+        <v>Charli xcx - Wall of Sound (Official Audio)</v>
       </c>
       <c r="B39" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=0m45tTheoCs</v>
+        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
       </c>
       <c r="D39" t="str">
         <v>2026-01-23</v>
@@ -1860,10 +1860,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>2:01</v>
+        <v>2:25</v>
       </c>
       <c r="H39" t="str">
-        <v>Alan Walker</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Alan Walker - Not Home (Official Lyric Video) - Alan Walker</v>
+        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio)</v>
+        <v>Labrinth - God Spoke (Official Visualizer)</v>
       </c>
       <c r="B40" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=AHm1i212UP4</v>
+        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
       </c>
       <c r="D40" t="str">
         <v>2026-01-23</v>
@@ -1898,10 +1898,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>2:25</v>
+        <v>1:14</v>
       </c>
       <c r="H40" t="str">
-        <v>Charli xcx</v>
+        <v>Labrinth</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Charli xcx - Wall of Sound (Official Audio) - Charli xcx</v>
+        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer)</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
       </c>
       <c r="B41" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=Srb2P9efFHY</v>
+        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
       </c>
       <c r="D41" t="str">
         <v>2026-01-23</v>
@@ -1936,10 +1936,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>1:14</v>
+        <v>2:59</v>
       </c>
       <c r="H41" t="str">
-        <v>Labrinth</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Labrinth - God Spoke (Official Visualizer) - Labrinth</v>
+        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio)</v>
+        <v>Girl Tones - Volcano (Visualizer)</v>
       </c>
       <c r="B42" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=NvHXKIrBiR8</v>
+        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
       </c>
       <c r="D42" t="str">
         <v>2026-01-23</v>
@@ -1974,10 +1974,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>2:59</v>
+        <v>2:29</v>
       </c>
       <c r="H42" t="str">
-        <v>Charlie Puth</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Charlie Puth - Beat Yourself Up (Official Audio) - Charlie Puth</v>
+        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Girl Tones - Volcano (Visualizer)</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
       </c>
       <c r="B43" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=D2-t5SDV1IE</v>
+        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
       </c>
       <c r="D43" t="str">
         <v>2026-01-23</v>
@@ -2012,10 +2012,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>2:29</v>
+        <v>2:34</v>
       </c>
       <c r="H43" t="str">
-        <v>Girl Tones</v>
+        <v>Jagwar Twin</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Girl Tones - Volcano (Visualizer) - Girl Tones</v>
+        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer)</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
       </c>
       <c r="B44" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=BouRN2QuXV8</v>
+        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
       </c>
       <c r="D44" t="str">
         <v>2026-01-23</v>
@@ -2050,10 +2050,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>2:34</v>
+        <v>3:48</v>
       </c>
       <c r="H44" t="str">
-        <v>Jagwar Twin</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Jagwar Twin, sir lucius - welcome to the circus (Visualizer) - Jagwar Twin</v>
+        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video)</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
       </c>
       <c r="B45" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=IyPD6AnWlRg</v>
+        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
       </c>
       <c r="D45" t="str">
         <v>2026-01-23</v>
@@ -2088,10 +2088,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:48</v>
+        <v>3:32</v>
       </c>
       <c r="H45" t="str">
-        <v>Caroline Jones</v>
+        <v>The Beaches</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Caroline Jones - You're It For Me, Honey. (Lyric Video) - Caroline Jones</v>
+        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
       </c>
       <c r="B46" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=7_i2R-EU-Eg</v>
+        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
       </c>
       <c r="D46" t="str">
         <v>2026-01-23</v>
@@ -2126,10 +2126,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:32</v>
+        <v>3:49</v>
       </c>
       <c r="H46" t="str">
-        <v>The Beaches</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>The Beaches - I Ran (So Far Away) Official Audio - The Beaches</v>
+        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba</v>
+        <v>Madison Beer - bad enough (Official Music Video)</v>
       </c>
       <c r="B47" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=McaD2PG8jOE</v>
+        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
       </c>
       <c r="D47" t="str">
         <v>2026-01-23</v>
@@ -2164,10 +2164,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:49</v>
+        <v>4:28</v>
       </c>
       <c r="H47" t="str">
-        <v>Dolly Parton</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Dolly Parton - Light of a Clear Blue Morning ft. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba - Dolly Parton</v>
+        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Madison Beer - bad enough (Official Music Video)</v>
+        <v>Ty Myers - Message to You (Official Video)</v>
       </c>
       <c r="B48" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=07SeT_QSJ08</v>
+        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
       </c>
       <c r="D48" t="str">
         <v>2026-01-23</v>
@@ -2202,10 +2202,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>4:28</v>
+        <v>3:37</v>
       </c>
       <c r="H48" t="str">
-        <v>Madison Beer</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Madison Beer - bad enough (Official Music Video) - Madison Beer</v>
+        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Ty Myers - Message to You (Official Video)</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
       </c>
       <c r="B49" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=mhw8eAtgnRk</v>
+        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
       </c>
       <c r="D49" t="str">
         <v>2026-01-23</v>
@@ -2240,10 +2240,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:37</v>
+        <v>3:35</v>
       </c>
       <c r="H49" t="str">
-        <v>Ty Myers</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Ty Myers - Message to You (Official Video) - Ty Myers</v>
+        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video)</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
       </c>
       <c r="B50" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=plbNzv3KvWs</v>
+        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
       </c>
       <c r="D50" t="str">
         <v>2026-01-23</v>
@@ -2278,10 +2278,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:35</v>
+        <v>2:31</v>
       </c>
       <c r="H50" t="str">
-        <v>Megan Moroney</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Megan Moroney - Wish I Didn't (Official Video) - Megan Moroney</v>
+        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video)</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
       </c>
       <c r="B51" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=GSkO7B_RbQE</v>
+        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
       </c>
       <c r="D51" t="str">
         <v>2026-01-23</v>
@@ -2316,10 +2316,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>2:31</v>
+        <v>3:21</v>
       </c>
       <c r="H51" t="str">
-        <v>Julia Cole Music</v>
+        <v>Lily Allen</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Julia Cole - What Could Go Wrong (Official Lyric Video) - Julia Cole Music</v>
+        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL)</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
       </c>
       <c r="B52" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
+        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
       </c>
       <c r="D52" t="str">
         <v>2026-01-23</v>
@@ -2354,10 +2354,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:21</v>
+        <v>5:24</v>
       </c>
       <c r="H52" t="str">
-        <v>Lily Allen</v>
+        <v>Nickless</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Lily Allen - Sleepwalking (Live on SNL) - Lily Allen</v>
+        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
+        <v>Peach PRC - Back To You (Official Audio)</v>
       </c>
       <c r="B53" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
+        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
       </c>
       <c r="D53" t="str">
         <v>2026-01-23</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>5:24</v>
+        <v>3:11</v>
       </c>
       <c r="H53" t="str">
-        <v>Nickless</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Nickless - Don't Stop The Car (live @ Powerplay Studios) - Nickless</v>
+        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Peach PRC - Back To You (Official Audio)</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
       </c>
       <c r="B54" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=upfuNpZvNZc</v>
+        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
       </c>
       <c r="D54" t="str">
         <v>2026-01-23</v>
@@ -2430,10 +2430,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:11</v>
+        <v>4:11</v>
       </c>
       <c r="H54" t="str">
-        <v>Peach PRC</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Peach PRC - Back To You (Official Audio) - Peach PRC</v>
+        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace)</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B55" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=Tmhor_vJeT8</v>
+        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
       </c>
       <c r="D55" t="str">
         <v>2026-01-23</v>
@@ -2468,10 +2468,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>4:11</v>
+        <v>3:31</v>
       </c>
       <c r="H55" t="str">
-        <v>Ocean Alley</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>OCEAN ALLEY - DRENCHED (Live at Alexandra Palace) - Ocean Alley</v>
+        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
       </c>
       <c r="B56" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=jqfvSd7LvAg</v>
+        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
       </c>
       <c r="D56" t="str">
         <v>2026-01-23</v>
@@ -2506,10 +2506,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:31</v>
+        <v>4:16</v>
       </c>
       <c r="H56" t="str">
-        <v>OneRepublic</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>OneRepublic - Counting Stars (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - OneRepublic</v>
+        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon)</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
       </c>
       <c r="B57" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=7Re1iBMyJzo</v>
+        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
       </c>
       <c r="D57" t="str">
         <v>2026-01-23</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>4:16</v>
+        <v>4:42</v>
       </c>
       <c r="H57" t="str">
-        <v>Ty Myers</v>
+        <v>JavaJazzFest</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Ty Myers - Thought It Was Love (Live From The Tonight Show Starring Jimmy Fallon) - Ty Myers</v>
+        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025</v>
+        <v>Teo Glacier - Don't Mind (Music Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=SI-M8USfkvs</v>
+        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
       </c>
       <c r="D58" t="str">
         <v>2026-01-23</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>4:42</v>
+        <v>2:47</v>
       </c>
       <c r="H58" t="str">
-        <v>JavaJazzFest</v>
+        <v>Teo Glacier</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>The Stevie Wonder Celebration "Superstition" Live at Java Jazz Festival 2025 - JavaJazzFest</v>
+        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video)</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
       </c>
       <c r="B59" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=0_Aefy7OSBU</v>
+        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
       </c>
       <c r="D59" t="str">
         <v>2026-01-23</v>
@@ -2620,10 +2620,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:47</v>
+        <v>3:59</v>
       </c>
       <c r="H59" t="str">
-        <v>Teo Glacier</v>
+        <v>Brigitte Calls Me Baby</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Teo Glacier - Don't Mind (Music Video) - Teo Glacier</v>
+        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video)</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
       </c>
       <c r="B60" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=t9rEZzMN0YU</v>
+        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
       </c>
       <c r="D60" t="str">
         <v>2026-01-23</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:59</v>
+        <v>4:09</v>
       </c>
       <c r="H60" t="str">
-        <v>Brigitte Calls Me Baby</v>
+        <v>Louie TheSinger</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Brigitte Calls Me Baby - Slumber Party (Official Video) - Brigitte Calls Me Baby</v>
+        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video</v>
+        <v>ella jane - When I Was Beautiful (Live)</v>
       </c>
       <c r="B61" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=VcBw_y9pc2E</v>
+        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
       </c>
       <c r="D61" t="str">
         <v>2026-01-23</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>4:09</v>
+        <v>3:24</v>
       </c>
       <c r="H61" t="str">
-        <v>Louie TheSinger</v>
+        <v>ella jane</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Louie TheSinger "Texas Gold" Official Music Video - Louie TheSinger</v>
+        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ella jane - When I Was Beautiful (Live)</v>
+        <v>Johnny Orlando - Emilia (Official Video)</v>
       </c>
       <c r="B62" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
+        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
       </c>
       <c r="D62" t="str">
         <v>2026-01-23</v>
@@ -2734,10 +2734,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:24</v>
+        <v>3:14</v>
       </c>
       <c r="H62" t="str">
-        <v>ella jane</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>ella jane - When I Was Beautiful (Live) - ella jane</v>
+        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Johnny Orlando - Emilia (Official Video)</v>
+        <v>Kungs, Theophilus London - Galaxy (official video)</v>
       </c>
       <c r="B63" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
+        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
       </c>
       <c r="D63" t="str">
         <v>2026-01-23</v>
@@ -2772,10 +2772,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:14</v>
+        <v>3:32</v>
       </c>
       <c r="H63" t="str">
-        <v>Johnny Orlando</v>
+        <v>Kungs</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Johnny Orlando - Emilia (Official Video) - Johnny Orlando</v>
+        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video)</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
       </c>
       <c r="B64" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
+        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
       </c>
       <c r="D64" t="str">
         <v>2026-01-23</v>
@@ -2810,10 +2810,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:32</v>
+        <v>3:15</v>
       </c>
       <c r="H64" t="str">
-        <v>Kungs</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Kungs, Theophilus London - Galaxy (official video) - Kungs</v>
+        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
       </c>
       <c r="B65" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
+        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
       </c>
       <c r="D65" t="str">
         <v>2026-01-23</v>
@@ -2848,10 +2848,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:15</v>
+        <v>3:03</v>
       </c>
       <c r="H65" t="str">
-        <v>Billy Raffoul</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version) - Billy Raffoul</v>
+        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
+        <v>Stephen Sanchez - Sweet Love</v>
       </c>
       <c r="B66" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
+        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
       </c>
       <c r="D66" t="str">
         <v>2026-01-23</v>
@@ -2886,10 +2886,10 @@
         <v>13 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:03</v>
+        <v>3:04</v>
       </c>
       <c r="H66" t="str">
-        <v>NathanEvanss</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Nathan Evans x Saint PNHX - Happy Place (Official Video) - NathanEvanss</v>
+        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Stephen Sanchez - Sweet Love</v>
+        <v>Bruno Mars - I Just Might [Official Music Video]</v>
       </c>
       <c r="B67" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
+        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
       </c>
       <c r="D67" t="str">
         <v>2026-01-23</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:04</v>
+        <v>3:33</v>
       </c>
       <c r="H67" t="str">
-        <v>Stephen Sanchez</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Stephen Sanchez - Sweet Love - Stephen Sanchez</v>
+        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video]</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
       </c>
       <c r="B68" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=mrV8kK5t0V8</v>
+        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
       </c>
       <c r="D68" t="str">
         <v>2026-01-23</v>
@@ -2962,10 +2962,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:33</v>
+        <v>2:53</v>
       </c>
       <c r="H68" t="str">
-        <v>Bruno Mars</v>
+        <v>MAX</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Bruno Mars - I Just Might [Official Music Video] - Bruno Mars</v>
+        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio]</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
       </c>
       <c r="B69" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=bVMtC6oL414</v>
+        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
       </c>
       <c r="D69" t="str">
         <v>2026-01-23</v>
@@ -3000,10 +3000,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
-        <v>2:53</v>
+        <v>4:11</v>
       </c>
       <c r="H69" t="str">
-        <v>MAX</v>
+        <v>Jessie J</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>MAX &amp; Andy Grammer - The Thing I Love (Wedding Version) [Official Audio] - MAX</v>
+        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video)</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
       </c>
       <c r="B70" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=bFiHNU-TPkI</v>
+        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
       </c>
       <c r="D70" t="str">
         <v>2026-01-23</v>
@@ -3038,10 +3038,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
-        <v>4:11</v>
+        <v>2:45</v>
       </c>
       <c r="H70" t="str">
-        <v>Jessie J</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Jessie J - I'll Never Know Why (Live from St Paul's Church, Covent Garden) (Lyric Video) - Jessie J</v>
+        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video)</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=Oct351qJkmI</v>
+        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
       </c>
       <c r="D71" t="str">
         <v>2026-01-23</v>
@@ -3076,10 +3076,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
-        <v>2:45</v>
+        <v>4:00</v>
       </c>
       <c r="H71" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Brandon Lake and Cody Johnson</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Claire Rosinkranz - Chronic (Official Music Video) - Claire Rosinkranz</v>
+        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video)</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=MC6FYj7zdWY</v>
+        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
       </c>
       <c r="D72" t="str">
         <v>2026-01-23</v>
@@ -3114,10 +3114,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
-        <v>4:00</v>
+        <v>3:27</v>
       </c>
       <c r="H72" t="str">
-        <v>Brandon Lake and Cody Johnson</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Brandon Lake, Cody Johnson - When A Cowboy Prays (with Cody Johnson Official Studio Video) - Brandon Lake and Cody Johnson</v>
+        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer)</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
       </c>
       <c r="B73" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=4669MlmzqO0</v>
+        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
       </c>
       <c r="D73" t="str">
         <v>2026-01-23</v>
@@ -3152,10 +3152,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:27</v>
+        <v>3:25</v>
       </c>
       <c r="H73" t="str">
-        <v>The Kid LAROI.</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>The Kid LAROI - I'M SO IN LOVE WITH YOU (Official Visualizer) - The Kid LAROI.</v>
+        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live")</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B74" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=hg17Eo3SZ-s</v>
+        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
       </c>
       <c r="D74" t="str">
         <v>2026-01-23</v>
@@ -3190,10 +3190,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:25</v>
+        <v>3:34</v>
       </c>
       <c r="H74" t="str">
-        <v>Olivia Dean</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Olivia Dean - Let Alone The One You Love (Live From "Saturday Night Live") - Olivia Dean</v>
+        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Train - Mittens (Live on TODAY)</v>
       </c>
       <c r="B75" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=oKqjUFvLPOc</v>
+        <v>https://www.youtube.com/watch?v=R2k_wPsAHKQ</v>
       </c>
       <c r="D75" t="str">
         <v>2026-01-23</v>
@@ -3228,10 +3228,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:34</v>
+        <v>3:17</v>
       </c>
       <c r="H75" t="str">
-        <v>Demi Lovato</v>
+        <v>Train</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Demi Lovato - Heart Attack (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>Train - Mittens (Live on TODAY) - Train</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Train - Mittens (Live on TODAY)</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
       </c>
       <c r="B76" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=R2k_wPsAHKQ</v>
+        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
       </c>
       <c r="D76" t="str">
         <v>2026-01-23</v>
@@ -3266,10 +3266,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:17</v>
+        <v>2:25</v>
       </c>
       <c r="H76" t="str">
-        <v>Train</v>
+        <v>Joseph</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Train - Mittens (Live on TODAY) - Train</v>
+        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video)</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
       </c>
       <c r="B77" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=HKCzv78bS34</v>
+        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
       </c>
       <c r="D77" t="str">
         <v>2026-01-23</v>
@@ -3304,10 +3304,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>2:25</v>
+        <v>3:26</v>
       </c>
       <c r="H77" t="str">
-        <v>Joseph</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>JOSEPH and Becca Mancari - I Believe in Myself (Official Lyric Video) - Joseph</v>
+        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026)</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=4DV87lqAOyE</v>
+        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
       </c>
       <c r="D78" t="str">
         <v>2026-01-23</v>
@@ -3342,10 +3342,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:26</v>
+        <v>4:46</v>
       </c>
       <c r="H78" t="str">
-        <v>Demi Lovato</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Demi Lovato - Sorry Not Sorry (Live On Dick Clark’s New Year’s Rockin’ Eve With Ryan Seacrest 2026) - Demi Lovato</v>
+        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
       </c>
       <c r="B79" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=v2iCMxHeCDo</v>
+        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
       </c>
       <c r="D79" t="str">
         <v>2026-01-23</v>
@@ -3380,7 +3380,7 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
-        <v>4:46</v>
+        <v>3:24</v>
       </c>
       <c r="H79" t="str">
         <v>Keith Urban</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Keith Urban - Straight Line (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025)</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
       </c>
       <c r="B80" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=UGkefbUWwUY</v>
+        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
       </c>
       <c r="D80" t="str">
         <v>2026-01-23</v>
@@ -3418,10 +3418,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:24</v>
+        <v>2:52</v>
       </c>
       <c r="H80" t="str">
-        <v>Keith Urban</v>
+        <v>Madonna</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Keith Urban - You Get What You Give (New Year's Eve Live: Nashville's Big Bash 2025) - Keith Urban</v>
+        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one)</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
       </c>
       <c r="B81" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=MN1EQau44Xc</v>
+        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
       </c>
       <c r="D81" t="str">
         <v>2026-01-23</v>
@@ -3456,10 +3456,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
-        <v>2:52</v>
+        <v>2:06</v>
       </c>
       <c r="H81" t="str">
-        <v>Madonna</v>
+        <v>Estas Tonne</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>LA BAMBOLA (FOR DOLCE &amp; GABBANA - the one) - Madonna</v>
+        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estas Tonne</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026</v>
+        <v>Anna Graves - Burn On (Official Music Video)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=dj4a8zoEdwY</v>
+        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
       </c>
       <c r="D82" t="str">
         <v>2026-01-23</v>
@@ -3494,10 +3494,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
-        <v>2:06</v>
+        <v>3:09</v>
       </c>
       <c r="H82" t="str">
-        <v>Estas Tonne</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Estas Tonne &amp; Friends || Announcing Sound Ceremony audio premier 22.01.2026 - Estas Tonne</v>
+        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Anna Graves - Burn On (Official Music Video)</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=8lHZIQcOXIE</v>
+        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
       </c>
       <c r="D83" t="str">
         <v>2026-01-23</v>
@@ -3532,10 +3532,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:09</v>
+        <v>5:11</v>
       </c>
       <c r="H83" t="str">
-        <v>Anna Graves</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Anna Graves - Burn On (Official Music Video) - Anna Graves</v>
+        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video)</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=eRZYOPRLh2Q</v>
+        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
       </c>
       <c r="D84" t="str">
         <v>2026-01-23</v>
@@ -3570,10 +3570,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
-        <v>5:11</v>
+        <v>3:40</v>
       </c>
       <c r="H84" t="str">
-        <v>Ocean Alley</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>OCEAN ALLEY - FIRST BLUSH (Official Video) - Ocean Alley</v>
+        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve)</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=5jrn4IfWYa4</v>
+        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
       </c>
       <c r="D85" t="str">
         <v>2026-01-23</v>
@@ -3608,10 +3608,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:40</v>
+        <v>3:49</v>
       </c>
       <c r="H85" t="str">
-        <v>Zara Larsson</v>
+        <v>Lauren Watkins</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Zara Larsson - Lush Life and Midnight Sun (Live from New Year's Rocking Eve) - Zara Larsson</v>
+        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session)</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=T-M4pLSFS24</v>
+        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
       </c>
       <c r="D86" t="str">
         <v>2026-01-23</v>
@@ -3646,10 +3646,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:49</v>
+        <v>3:42</v>
       </c>
       <c r="H86" t="str">
-        <v>Lauren Watkins</v>
+        <v>Goo Goo Dolls</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Lauren Watkins - Average Joe &amp; Plain Jane (In A Perfect World: Petal Session) - Lauren Watkins</v>
+        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=ykIx-N3utNo</v>
+        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
       </c>
       <c r="D87" t="str">
         <v>2026-01-23</v>
@@ -3684,10 +3684,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:42</v>
+        <v>5:11</v>
       </c>
       <c r="H87" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Goo Goo Dolls - Iris [Live from Dick Clark's New Year's Rockin' Eve] - Goo Goo Dolls</v>
+        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve]</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=tF9KOmrDYL4</v>
+        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
       </c>
       <c r="D88" t="str">
         <v>2026-01-23</v>
@@ -3722,10 +3722,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
-        <v>5:11</v>
+        <v>3:57</v>
       </c>
       <c r="H88" t="str">
-        <v>Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Maren Morris - Medley [2026 Dick Clark's New Year's Rockin' Eve] - Maren Morris and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance)</v>
+        <v>Grace Enger - All My Songs (Official Lyric Video)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=as2yQlc9Tvc</v>
+        <v>https://www.youtube.com/watch?v=gWyaiGAFVO8</v>
       </c>
       <c r="D89" t="str">
         <v>2026-01-23</v>
@@ -3760,10 +3760,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:57</v>
+        <v>3:29</v>
       </c>
       <c r="H89" t="str">
-        <v>Lainey Wilson</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Lainey Wilson - Hang Tight Honey (New Year's Eve Live: Nashville's Big Bash 2025 Performance) - Lainey Wilson</v>
+        <v>Grace Enger - All My Songs (Official Lyric Video) - Grace Enger</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Grace Enger - All My Songs (Official Lyric Video)</v>
+        <v>Alan Walker - Broken Strings (Official Music Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=gWyaiGAFVO8</v>
+        <v>https://www.youtube.com/watch?v=jwQKcW474Tc</v>
       </c>
       <c r="D90" t="str">
         <v>2026-01-23</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:29</v>
+        <v>3:10</v>
       </c>
       <c r="H90" t="str">
-        <v>Grace Enger</v>
+        <v>Alan Walker and 2 more</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Grace Enger - All My Songs (Official Lyric Video) - Grace Enger</v>
+        <v>Alan Walker - Broken Strings (Official Music Video) - Alan Walker and 2 more</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Alan Walker - Broken Strings (Official Music Video)</v>
+        <v>Emilia Tarrant - Break Up With Myself</v>
       </c>
       <c r="B91" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=jwQKcW474Tc</v>
+        <v>https://www.youtube.com/watch?v=3N7iKwqENP0</v>
       </c>
       <c r="D91" t="str">
         <v>2026-01-23</v>
@@ -3836,10 +3836,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:10</v>
+        <v>4:04</v>
       </c>
       <c r="H91" t="str">
-        <v>Alan Walker and 2 more</v>
+        <v>Emilia Tarrant</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Alan Walker - Broken Strings (Official Music Video) - Alan Walker and 2 more</v>
+        <v>Emilia Tarrant - Break Up With Myself - Emilia Tarrant</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Emilia Tarrant - Break Up With Myself</v>
+        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026)</v>
       </c>
       <c r="B92" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=3N7iKwqENP0</v>
+        <v>https://www.youtube.com/watch?v=sKG5ZIzCnFQ</v>
       </c>
       <c r="D92" t="str">
         <v>2026-01-23</v>
@@ -3874,10 +3874,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>4:04</v>
+        <v>3:09</v>
       </c>
       <c r="H92" t="str">
-        <v>Emilia Tarrant</v>
+        <v>Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Emilia Tarrant - Break Up With Myself - Emilia Tarrant</v>
+        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026) - Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026)</v>
+        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer)</v>
       </c>
       <c r="B93" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=sKG5ZIzCnFQ</v>
+        <v>https://www.youtube.com/watch?v=Koj30I91_8k</v>
       </c>
       <c r="D93" t="str">
         <v>2026-01-23</v>
@@ -3912,10 +3912,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:09</v>
+        <v>2:27</v>
       </c>
       <c r="H93" t="str">
-        <v>Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Jess Glynne - Rather Be (Live at Dick Clark’s New Year’s Rockin’ Eve 2026) - Jess Glynne and Dick Clark's New Year's Rockin' Eve</v>
+        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer)</v>
+        <v>Maggie Lindemann - fate</v>
       </c>
       <c r="B94" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=Koj30I91_8k</v>
+        <v>https://www.youtube.com/watch?v=xZdWEmnRK4g</v>
       </c>
       <c r="D94" t="str">
         <v>2026-01-23</v>
@@ -3950,10 +3950,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>2:27</v>
+        <v>2:12</v>
       </c>
       <c r="H94" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Maggie Lindemann</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Lauren Spencer Smith - Looking Up (Official Fan Visualizer) - Lauren Spencer Smith</v>
+        <v>Maggie Lindemann - fate - Maggie Lindemann</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Maggie Lindemann - fate</v>
+        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023)</v>
       </c>
       <c r="B95" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=xZdWEmnRK4g</v>
+        <v>https://www.youtube.com/watch?v=wo9yPPCh75Q</v>
       </c>
       <c r="D95" t="str">
         <v>2026-01-23</v>
@@ -3988,10 +3988,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>2:12</v>
+        <v>4:44</v>
       </c>
       <c r="H95" t="str">
-        <v>Maggie Lindemann</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Maggie Lindemann - fate - Maggie Lindemann</v>
+        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023) - Cliff Richard</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023)</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025</v>
       </c>
       <c r="B96" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=wo9yPPCh75Q</v>
+        <v>https://www.youtube.com/watch?v=ND6maRwmzHk</v>
       </c>
       <c r="D96" t="str">
         <v>2026-01-23</v>
@@ -4026,10 +4026,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>4:44</v>
+        <v>1:00:09</v>
       </c>
       <c r="H96" t="str">
-        <v>Cliff Richard</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Cliff Richard - The Millennium Prayer (The Blue Sapphire Tour 2023) - Cliff Richard</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025</v>
+        <v>RAYE - Black Mascara. (Live at The Royal Albert Hall)</v>
       </c>
       <c r="B97" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=ND6maRwmzHk</v>
+        <v>https://www.youtube.com/watch?v=9jMMOYr-VhE</v>
       </c>
       <c r="D97" t="str">
         <v>2026-01-23</v>
@@ -4064,10 +4064,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>1:00:09</v>
+        <v>4:15</v>
       </c>
       <c r="H97" t="str">
-        <v>Purple Disco Machine</v>
+        <v>RAYE</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES DECEMBER 2025 - Purple Disco Machine</v>
+        <v>RAYE - Black Mascara. (Live at The Royal Albert Hall) - RAYE</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>RAYE - Black Mascara. (Live at The Royal Albert Hall)</v>
+        <v>Madison Cunningham - My Full Name (Garden Session)</v>
       </c>
       <c r="B98" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=9jMMOYr-VhE</v>
+        <v>https://www.youtube.com/watch?v=o2F-QmqdNtI</v>
       </c>
       <c r="D98" t="str">
         <v>2026-01-23</v>
@@ -4102,10 +4102,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>4:15</v>
+        <v>4:07</v>
       </c>
       <c r="H98" t="str">
-        <v>RAYE</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>RAYE - Black Mascara. (Live at The Royal Albert Hall) - RAYE</v>
+        <v>Madison Cunningham - My Full Name (Garden Session) - Madison Cunningham</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Madison Cunningham - My Full Name (Garden Session)</v>
+        <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions)</v>
       </c>
       <c r="B99" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=o2F-QmqdNtI</v>
+        <v>https://www.youtube.com/watch?v=5-6cEVLqE90</v>
       </c>
       <c r="D99" t="str">
         <v>2026-01-23</v>
@@ -4140,10 +4140,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>4:07</v>
+        <v>3:10</v>
       </c>
       <c r="H99" t="str">
-        <v>Madison Cunningham</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Madison Cunningham - My Full Name (Garden Session) - Madison Cunningham</v>
+        <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions) - Teddy Swims</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions)</v>
+        <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower)</v>
       </c>
       <c r="B100" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=5-6cEVLqE90</v>
+        <v>https://www.youtube.com/watch?v=ivPSbcEMwCs</v>
       </c>
       <c r="D100" t="str">
         <v>2026-01-23</v>
@@ -4178,10 +4178,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:10</v>
+        <v>3:47</v>
       </c>
       <c r="H100" t="str">
-        <v>Teddy Swims</v>
+        <v>Christina Aguilera</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Teddy Swims - God Went Crazy (Live - Green Room Sessions) - Teddy Swims</v>
+        <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower) - Christina Aguilera</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower)</v>
+        <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025)</v>
       </c>
       <c r="B101" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=ivPSbcEMwCs</v>
+        <v>https://www.youtube.com/watch?v=tYpOHbXFnm0</v>
       </c>
       <c r="D101" t="str">
         <v>2026-01-23</v>
@@ -4216,10 +4216,10 @@
         <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:47</v>
+        <v>3:58</v>
       </c>
       <c r="H101" t="str">
-        <v>Christina Aguilera</v>
+        <v>RAYE</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Christina Aguilera - What Are You Doing New Year's Eve (Live from the Eiffel Tower) - Christina Aguilera</v>
+        <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025) - RAYE</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025)</v>
+        <v>Aperture</v>
       </c>
       <c r="B102" t="str">
-        <v>3 weeks ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=tYpOHbXFnm0</v>
+        <v>https://music.apple.com/us/song/aperture/1870984033</v>
       </c>
       <c r="D102" t="str">
         <v>2026-01-23</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>3 weeks ago</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G102" t="str">
-        <v>3:58</v>
+        <v>5:11</v>
       </c>
       <c r="H102" t="str">
-        <v>RAYE</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/aperture/1870984032</v>
       </c>
       <c r="L102" t="str">
-        <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025) - RAYE</v>
+        <v>Aperture - Harry Styles</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Aperture</v>
+        <v>Opening Night</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/aperture/1870984033</v>
+        <v>https://music.apple.com/us/song/opening-night/1870313501</v>
       </c>
       <c r="D103" t="str">
         <v>2026-01-23</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Kiss All The Time. Disco, Occasionally.</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G103" t="str">
-        <v>5:11</v>
+        <v>4:19</v>
       </c>
       <c r="H103" t="str">
-        <v>Harry Styles</v>
+        <v>Arctic Monkeys</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
+        <v>https://music.apple.com/us/artist/arctic-monkeys/62820413</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/aperture/1870984032</v>
+        <v>https://music.apple.com/us/album/opening-night/1870313498</v>
       </c>
       <c r="L103" t="str">
-        <v>Aperture - Harry Styles</v>
+        <v>Opening Night - Arctic Monkeys</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Opening Night</v>
+        <v>FLACKITO JODYE (feat. Tokischa)</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/opening-night/1870313501</v>
+        <v>https://music.apple.com/us/song/flackito-jodye-feat-tokischa/1870968779</v>
       </c>
       <c r="D104" t="str">
         <v>2026-01-23</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>HELP(2)</v>
+        <v>Don't Be Dumb</v>
       </c>
       <c r="G104" t="str">
-        <v>4:19</v>
+        <v>2:20</v>
       </c>
       <c r="H104" t="str">
-        <v>Arctic Monkeys</v>
+        <v>A$AP Rocky</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/arctic-monkeys/62820413</v>
+        <v>https://music.apple.com/us/artist/a%24ap-rocky/481488005</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/opening-night/1870313498</v>
+        <v>https://music.apple.com/us/album/flackito-jodye-feat-tokischa/1870968596</v>
       </c>
       <c r="L104" t="str">
-        <v>Opening Night - Arctic Monkeys</v>
+        <v>FLACKITO JODYE (feat. Tokischa) - A$AP Rocky</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>FLACKITO JODYE (feat. Tokischa)</v>
+        <v>CAMBIARÉ</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/flackito-jodye-feat-tokischa/1870968779</v>
+        <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
       </c>
       <c r="D105" t="str">
         <v>2026-01-23</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Don't Be Dumb</v>
+        <v>CAMBIARÉ - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>2:20</v>
+        <v>3:01</v>
       </c>
       <c r="H105" t="str">
-        <v>A$AP Rocky</v>
+        <v>Luis Fonsi</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/a%24ap-rocky/481488005</v>
+        <v>https://music.apple.com/us/artist/luis-fonsi/102834</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/flackito-jodye-feat-tokischa/1870968596</v>
+        <v>https://music.apple.com/us/album/cambiar%C3%A9/1867545265</v>
       </c>
       <c r="L105" t="str">
-        <v>FLACKITO JODYE (feat. Tokischa) - A$AP Rocky</v>
+        <v>CAMBIARÉ - Luis Fonsi</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>CAMBIARÉ</v>
+        <v>Last of a Dying Breed</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/cambiar%C3%A9/1867545266</v>
+        <v>https://music.apple.com/us/song/last-of-a-dying-breed/1849706852</v>
       </c>
       <c r="D106" t="str">
         <v>2026-01-23</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>CAMBIARÉ - Single</v>
+        <v>Piss In The Wind</v>
       </c>
       <c r="G106" t="str">
-        <v>3:01</v>
+        <v>2:29</v>
       </c>
       <c r="H106" t="str">
-        <v>Luis Fonsi</v>
+        <v>Joji</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/luis-fonsi/102834</v>
+        <v>https://music.apple.com/us/artist/joji/1258279972</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/cambiar%C3%A9/1867545265</v>
+        <v>https://music.apple.com/us/album/last-of-a-dying-breed/1849706656</v>
       </c>
       <c r="L106" t="str">
-        <v>CAMBIARÉ - Luis Fonsi</v>
+        <v>Last of a Dying Breed - Joji</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Last of a Dying Breed</v>
+        <v>High Key</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/last-of-a-dying-breed/1849706852</v>
+        <v>https://music.apple.com/us/song/high-key/1847702418</v>
       </c>
       <c r="D107" t="str">
         <v>2026-01-23</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Piss In The Wind</v>
+        <v>Vacancy</v>
       </c>
       <c r="G107" t="str">
-        <v>2:29</v>
+        <v>2:12</v>
       </c>
       <c r="H107" t="str">
-        <v>Joji</v>
+        <v>Ari Lennox</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/joji/1258279972</v>
+        <v>https://music.apple.com/us/artist/ari-lennox/448854570</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/last-of-a-dying-breed/1849706656</v>
+        <v>https://music.apple.com/us/album/high-key/1847702412</v>
       </c>
       <c r="L107" t="str">
-        <v>Last of a Dying Breed - Joji</v>
+        <v>High Key - Ari Lennox</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>High Key</v>
+        <v>scared</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/high-key/1847702418</v>
+        <v>https://music.apple.com/us/song/scared/1862292863</v>
       </c>
       <c r="D108" t="str">
         <v>2026-01-23</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Vacancy</v>
+        <v>scared - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>2:12</v>
+        <v>3:46</v>
       </c>
       <c r="H108" t="str">
-        <v>Ari Lennox</v>
+        <v>Fred again..</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/ari-lennox/448854570</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/high-key/1847702412</v>
+        <v>https://music.apple.com/us/album/scared/1862292862</v>
       </c>
       <c r="L108" t="str">
-        <v>High Key - Ari Lennox</v>
+        <v>scared - Fred again..</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>scared</v>
+        <v>Death of Love</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/scared/1862292863</v>
+        <v>https://music.apple.com/us/song/death-of-love/1862353786</v>
       </c>
       <c r="D109" t="str">
         <v>2026-01-23</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>scared - Single</v>
+        <v>Trying Times</v>
       </c>
       <c r="G109" t="str">
-        <v>3:46</v>
+        <v>3:26</v>
       </c>
       <c r="H109" t="str">
-        <v>Fred again..</v>
+        <v>James Blake</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/scared/1862292862</v>
+        <v>https://music.apple.com/us/album/death-of-love/1862353780</v>
       </c>
       <c r="L109" t="str">
-        <v>scared - Fred again..</v>
+        <v>Death of Love - James Blake</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Death of Love</v>
+        <v>Big Ole Fancy House</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/death-of-love/1862353786</v>
+        <v>https://music.apple.com/us/song/big-ole-fancy-house/1862624759</v>
       </c>
       <c r="D110" t="str">
         <v>2026-01-23</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Trying Times</v>
+        <v>Parker McCollum (The Deluxe Edition)</v>
       </c>
       <c r="G110" t="str">
-        <v>3:26</v>
+        <v>4:03</v>
       </c>
       <c r="H110" t="str">
-        <v>James Blake</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/death-of-love/1862353780</v>
+        <v>https://music.apple.com/us/album/big-ole-fancy-house/1862624506</v>
       </c>
       <c r="L110" t="str">
-        <v>Death of Love - James Blake</v>
+        <v>Big Ole Fancy House - Parker McCollum</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Big Ole Fancy House</v>
+        <v>Flo Jackson</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/big-ole-fancy-house/1862624759</v>
+        <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
       </c>
       <c r="D111" t="str">
         <v>2026-01-23</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Parker McCollum (The Deluxe Edition)</v>
+        <v>Flo Jackson - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>4:03</v>
+        <v>2:23</v>
       </c>
       <c r="H111" t="str">
-        <v>Parker McCollum</v>
+        <v>Flo Milli</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
+        <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/big-ole-fancy-house/1862624506</v>
+        <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
       </c>
       <c r="L111" t="str">
-        <v>Big Ole Fancy House - Parker McCollum</v>
+        <v>Flo Jackson - Flo Milli</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Flo Jackson</v>
+        <v>Site Unseen (feat. Waxahatchee)</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/flo-jackson/1870644907</v>
+        <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
       </c>
       <c r="D112" t="str">
         <v>2026-01-23</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Flo Jackson - Single</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G112" t="str">
-        <v>2:23</v>
+        <v>2:46</v>
       </c>
       <c r="H112" t="str">
-        <v>Flo Milli</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/flo-milli/1263242099</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/flo-jackson/1870644658</v>
+        <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
       </c>
       <c r="L112" t="str">
-        <v>Flo Jackson - Flo Milli</v>
+        <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Site Unseen (feat. Waxahatchee)</v>
+        <v>Puppet Parade</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/site-unseen-feat-waxahatchee/1868686716</v>
+        <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
       </c>
       <c r="D113" t="str">
         <v>2026-01-23</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Creature of Habit</v>
+        <v>Megadeth</v>
       </c>
       <c r="G113" t="str">
-        <v>2:46</v>
+        <v>4:40</v>
       </c>
       <c r="H113" t="str">
-        <v>Courtney Barnett</v>
+        <v>Megadeth</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/megadeth/488289</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/site-unseen-feat-waxahatchee/1868686713</v>
+        <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
       </c>
       <c r="L113" t="str">
-        <v>Site Unseen (feat. Waxahatchee) - Courtney Barnett</v>
+        <v>Puppet Parade - Megadeth</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Puppet Parade</v>
+        <v>To Love Somebody</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/puppet-parade/1840222357</v>
+        <v>https://music.apple.com/us/song/to-love-somebody/1859630040</v>
       </c>
       <c r="D114" t="str">
         <v>2026-01-23</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Megadeth</v>
+        <v>Cruel World</v>
       </c>
       <c r="G114" t="str">
-        <v>4:40</v>
+        <v>3:57</v>
       </c>
       <c r="H114" t="str">
-        <v>Megadeth</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/megadeth/488289</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/puppet-parade/1840222160</v>
+        <v>https://music.apple.com/us/album/to-love-somebody/1859629846</v>
       </c>
       <c r="L114" t="str">
-        <v>Puppet Parade - Megadeth</v>
+        <v>To Love Somebody - Holly Humberstone</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>To Love Somebody</v>
+        <v>Nothing Is Impossible With You</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/to-love-somebody/1859630040</v>
+        <v>https://music.apple.com/us/song/nothing-is-impossible-with-you/1870691236</v>
       </c>
       <c r="D115" t="str">
         <v>2026-01-23</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Cruel World</v>
+        <v>Nothing Is Impossible With You - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:57</v>
+        <v>4:14</v>
       </c>
       <c r="H115" t="str">
-        <v>Holly Humberstone</v>
+        <v>Cleo Sol</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/cleo-sol/459710289</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/to-love-somebody/1859629846</v>
+        <v>https://music.apple.com/us/album/nothing-is-impossible-with-you/1870691227</v>
       </c>
       <c r="L115" t="str">
-        <v>To Love Somebody - Holly Humberstone</v>
+        <v>Nothing Is Impossible With You - Cleo Sol</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Nothing Is Impossible With You</v>
+        <v>HYPNOTIZE</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/nothing-is-impossible-with-you/1870691236</v>
+        <v>https://music.apple.com/us/song/hypnotize/1861009528</v>
       </c>
       <c r="D116" t="str">
         <v>2026-01-23</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Nothing Is Impossible With You - Single</v>
+        <v>THE CORE - 核</v>
       </c>
       <c r="G116" t="str">
-        <v>4:14</v>
+        <v>2:50</v>
       </c>
       <c r="H116" t="str">
-        <v>Cleo Sol</v>
+        <v>XG</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/cleo-sol/459710289</v>
+        <v>https://music.apple.com/us/artist/xg/1609409493</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/nothing-is-impossible-with-you/1870691227</v>
+        <v>https://music.apple.com/us/album/hypnotize/1861009513</v>
       </c>
       <c r="L116" t="str">
-        <v>Nothing Is Impossible With You - Cleo Sol</v>
+        <v>HYPNOTIZE - XG</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>HYPNOTIZE</v>
+        <v>Dead End</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/hypnotize/1861009528</v>
+        <v>https://music.apple.com/us/song/dead-end/1862845874</v>
       </c>
       <c r="D117" t="str">
         <v>2026-01-23</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>THE CORE - 核</v>
+        <v>Ricochet</v>
       </c>
       <c r="G117" t="str">
-        <v>2:50</v>
+        <v>4:05</v>
       </c>
       <c r="H117" t="str">
-        <v>XG</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/xg/1609409493</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/hypnotize/1861009513</v>
+        <v>https://music.apple.com/us/album/dead-end/1862845733</v>
       </c>
       <c r="L117" t="str">
-        <v>HYPNOTIZE - XG</v>
+        <v>Dead End - Snail Mail</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Dead End</v>
+        <v>Do I Wanna Know?</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/dead-end/1862845874</v>
+        <v>https://music.apple.com/us/song/do-i-wanna-know/1870931500</v>
       </c>
       <c r="D118" t="str">
         <v>2026-01-23</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Ricochet</v>
+        <v>Do I Wanna Know? - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>4:05</v>
+        <v>3:52</v>
       </c>
       <c r="H118" t="str">
-        <v>Snail Mail</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v>https://music.apple.com/us/artist/dove-cameron/599822740</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/dead-end/1862845733</v>
+        <v>https://music.apple.com/us/album/do-i-wanna-know/1870931327</v>
       </c>
       <c r="L118" t="str">
-        <v>Dead End - Snail Mail</v>
+        <v>Do I Wanna Know? - Dove Cameron</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Do I Wanna Know?</v>
+        <v>Una y Otra Vez</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/do-i-wanna-know/1870931500</v>
+        <v>https://music.apple.com/us/song/una-y-otra-vez/1868792926</v>
       </c>
       <c r="D119" t="str">
         <v>2026-01-23</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Do I Wanna Know? - Single</v>
+        <v>K de Karma (Apple Music Edition)</v>
       </c>
       <c r="G119" t="str">
-        <v>3:52</v>
+        <v>3:02</v>
       </c>
       <c r="H119" t="str">
-        <v>Dove Cameron</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/dove-cameron/599822740</v>
+        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/do-i-wanna-know/1870931327</v>
+        <v>https://music.apple.com/us/album/una-y-otra-vez/1868792704</v>
       </c>
       <c r="L119" t="str">
-        <v>Do I Wanna Know? - Dove Cameron</v>
+        <v>Una y Otra Vez - Kenia Os</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Una y Otra Vez</v>
+        <v>BAD</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/una-y-otra-vez/1868792926</v>
+        <v>https://music.apple.com/us/song/bad/1869095326</v>
       </c>
       <c r="D120" t="str">
         <v>2026-01-23</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>K de Karma (Apple Music Edition)</v>
+        <v>BAD - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:02</v>
+        <v>2:15</v>
       </c>
       <c r="H120" t="str">
-        <v>Kenia Os</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
+        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/una-y-otra-vez/1868792704</v>
+        <v>https://music.apple.com/us/album/bad/1869095325</v>
       </c>
       <c r="L120" t="str">
-        <v>Una y Otra Vez - Kenia Os</v>
+        <v>BAD - Chelsea Cutler</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>BAD</v>
+        <v>Losing You</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/bad/1869095326</v>
+        <v>https://music.apple.com/us/song/losing-you/1863525495</v>
       </c>
       <c r="D121" t="str">
         <v>2026-01-23</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>BAD - Single</v>
+        <v>F.I.G</v>
       </c>
       <c r="G121" t="str">
-        <v>2:15</v>
+        <v>2:22</v>
       </c>
       <c r="H121" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Naomi Scott</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-cutler/398935148</v>
+        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/bad/1869095325</v>
+        <v>https://music.apple.com/us/album/losing-you/1863525485</v>
       </c>
       <c r="L121" t="str">
-        <v>BAD - Chelsea Cutler</v>
+        <v>Losing You - Naomi Scott</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Losing You</v>
+        <v>Me Voy A La C******a</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/losing-you/1863525495</v>
+        <v>https://music.apple.com/us/song/me-voy-a-la-c-a/1867850749</v>
       </c>
       <c r="D122" t="str">
         <v>2026-01-23</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>F.I.G</v>
+        <v>Infinito</v>
       </c>
       <c r="G122" t="str">
-        <v>2:22</v>
+        <v>2:14</v>
       </c>
       <c r="H122" t="str">
-        <v>Naomi Scott</v>
+        <v>Yandel</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
+        <v>https://music.apple.com/us/artist/yandel/72929426</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/losing-you/1863525485</v>
+        <v>https://music.apple.com/us/album/me-voy-a-la-c-a/1867850739</v>
       </c>
       <c r="L122" t="str">
-        <v>Losing You - Naomi Scott</v>
+        <v>Me Voy A La C******a - Yandel</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Me Voy A La C******a</v>
+        <v>Sexy For Me</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/me-voy-a-la-c-a/1867850749</v>
+        <v>https://music.apple.com/us/song/sexy-for-me/1867897421</v>
       </c>
       <c r="D123" t="str">
         <v>2026-01-23</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Infinito</v>
+        <v>The Last Dance (Part 1)</v>
       </c>
       <c r="G123" t="str">
-        <v>2:14</v>
+        <v>2:08</v>
       </c>
       <c r="H123" t="str">
-        <v>Yandel</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/yandel/72929426</v>
+        <v>https://music.apple.com/us/artist/jason-derulo/259118085</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/me-voy-a-la-c-a/1867850739</v>
+        <v>https://music.apple.com/us/album/sexy-for-me/1867897420</v>
       </c>
       <c r="L123" t="str">
-        <v>Me Voy A La C******a - Yandel</v>
+        <v>Sexy For Me - Jason Derulo</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Sexy For Me</v>
+        <v>Turbulence</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/sexy-for-me/1867897421</v>
+        <v>https://music.apple.com/us/song/turbulence/1867908449</v>
       </c>
       <c r="D124" t="str">
         <v>2026-01-23</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>The Last Dance (Part 1)</v>
+        <v>REAL, Vol. 1 - EP</v>
       </c>
       <c r="G124" t="str">
-        <v>2:08</v>
+        <v>2:25</v>
       </c>
       <c r="H124" t="str">
-        <v>Jason Derulo</v>
+        <v>Wizkid</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/jason-derulo/259118085</v>
+        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/sexy-for-me/1867897420</v>
+        <v>https://music.apple.com/us/album/turbulence/1867908237</v>
       </c>
       <c r="L124" t="str">
-        <v>Sexy For Me - Jason Derulo</v>
+        <v>Turbulence - Wizkid</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Turbulence</v>
+        <v>I’m Good (From The Movie “GOAT”)</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/turbulence/1867908449</v>
+        <v>https://music.apple.com/us/song/im-good-from-the-movie-goat/1870623298</v>
       </c>
       <c r="D125" t="str">
         <v>2026-01-23</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>REAL, Vol. 1 - EP</v>
+        <v>GOAT (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G125" t="str">
-        <v>2:25</v>
+        <v>2:59</v>
       </c>
       <c r="H125" t="str">
-        <v>Wizkid</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/wizkid/309335750</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/turbulence/1867908237</v>
+        <v>https://music.apple.com/us/album/im-good-from-the-movie-goat/1870623290</v>
       </c>
       <c r="L125" t="str">
-        <v>Turbulence - Wizkid</v>
+        <v>I’m Good (From The Movie “GOAT”) - Jelly Roll</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>I’m Good (From The Movie “GOAT”)</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/im-good-from-the-movie-goat/1870623298</v>
+        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
       </c>
       <c r="D126" t="str">
         <v>2026-01-23</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>GOAT (Original Motion Picture Soundtrack)</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>2:59</v>
+        <v>3:47</v>
       </c>
       <c r="H126" t="str">
-        <v>Jelly Roll</v>
+        <v>Dolly Parton</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
+        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/im-good-from-the-movie-goat/1870623290</v>
+        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
       </c>
       <c r="L126" t="str">
-        <v>I’m Good (From The Movie “GOAT”) - Jelly Roll</v>
+        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire)</v>
+        <v>ESCONDIDAS</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899463</v>
+        <v>https://music.apple.com/us/song/escondidas/1860972187</v>
       </c>
       <c r="D127" t="str">
         <v>2026-01-23</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Single</v>
+        <v>SILENCIO HABLA</v>
       </c>
       <c r="G127" t="str">
-        <v>3:47</v>
+        <v>2:53</v>
       </c>
       <c r="H127" t="str">
-        <v>Dolly Parton</v>
+        <v>Oscar Ortiz</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/dolly-parton/535066</v>
+        <v>https://music.apple.com/us/artist/oscar-ortiz/1680604969</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/light-of-a-clear-blue-morning-feat-lainey-wilson/1867899461</v>
+        <v>https://music.apple.com/us/album/escondidas/1860972173</v>
       </c>
       <c r="L127" t="str">
-        <v>Light of a Clear Blue Morning (feat. Lainey Wilson, Miley Cyrus, Queen Latifah &amp; Reba McEntire) - Dolly Parton</v>
+        <v>ESCONDIDAS - Oscar Ortiz</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>ESCONDIDAS</v>
+        <v>Alabama Beauty Queen</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/escondidas/1860972187</v>
+        <v>https://music.apple.com/us/song/alabama-beauty-queen/1846658485</v>
       </c>
       <c r="D128" t="str">
         <v>2026-01-23</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>SILENCIO HABLA</v>
+        <v>Act I</v>
       </c>
       <c r="G128" t="str">
-        <v>2:53</v>
+        <v>3:43</v>
       </c>
       <c r="H128" t="str">
-        <v>Oscar Ortiz</v>
+        <v>Kashus Culpepper</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/oscar-ortiz/1680604969</v>
+        <v>https://music.apple.com/us/artist/kashus-culpepper/1634883369</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/escondidas/1860972173</v>
+        <v>https://music.apple.com/us/album/alabama-beauty-queen/1846658477</v>
       </c>
       <c r="L128" t="str">
-        <v>ESCONDIDAS - Oscar Ortiz</v>
+        <v>Alabama Beauty Queen - Kashus Culpepper</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Alabama Beauty Queen</v>
+        <v>Imposter</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/alabama-beauty-queen/1846658485</v>
+        <v>https://music.apple.com/us/song/imposter/1842408050</v>
       </c>
       <c r="D129" t="str">
         <v>2026-01-23</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Act I</v>
+        <v>How Did I Get Here?</v>
       </c>
       <c r="G129" t="str">
-        <v>3:43</v>
+        <v>2:38</v>
       </c>
       <c r="H129" t="str">
-        <v>Kashus Culpepper</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/kashus-culpepper/1634883369</v>
+        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/alabama-beauty-queen/1846658477</v>
+        <v>https://music.apple.com/us/album/imposter/1842408037</v>
       </c>
       <c r="L129" t="str">
-        <v>Alabama Beauty Queen - Kashus Culpepper</v>
+        <v>Imposter - Louis Tomlinson</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Imposter</v>
+        <v>Puddles (Zero 7 Remix)</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/imposter/1842408050</v>
+        <v>https://music.apple.com/us/song/puddles-zero-7-remix/1869474314</v>
       </c>
       <c r="D130" t="str">
         <v>2026-01-23</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>How Did I Get Here?</v>
+        <v>Puddles (Zero 7 Remix) - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>2:38</v>
+        <v>6:01</v>
       </c>
       <c r="H130" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Not for Radio</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/louis-tomlinson/471260295</v>
+        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/imposter/1842408037</v>
+        <v>https://music.apple.com/us/album/puddles-zero-7-remix/1869474313</v>
       </c>
       <c r="L130" t="str">
-        <v>Imposter - Louis Tomlinson</v>
+        <v>Puddles (Zero 7 Remix) - Not for Radio</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Puddles (Zero 7 Remix)</v>
+        <v>Little Miss (Misdemeanor)</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/puddles-zero-7-remix/1869474314</v>
+        <v>https://music.apple.com/us/song/little-miss-misdemeanor/1870996491</v>
       </c>
       <c r="D131" t="str">
         <v>2026-01-23</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Puddles (Zero 7 Remix) - Single</v>
+        <v>Little Miss (Misdemeanor) - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>6:01</v>
+        <v>2:24</v>
       </c>
       <c r="H131" t="str">
-        <v>Not for Radio</v>
+        <v>GIRLSET</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
+        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/puddles-zero-7-remix/1869474313</v>
+        <v>https://music.apple.com/us/album/little-miss-misdemeanor/1870996490</v>
       </c>
       <c r="L131" t="str">
-        <v>Puddles (Zero 7 Remix) - Not for Radio</v>
+        <v>Little Miss (Misdemeanor) - GIRLSET</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Little Miss (Misdemeanor)</v>
+        <v>I Could Get Used To This</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/little-miss-misdemeanor/1870996491</v>
+        <v>https://music.apple.com/us/song/i-could-get-used-to-this/1867222996</v>
       </c>
       <c r="D132" t="str">
         <v>2026-01-23</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Little Miss (Misdemeanor) - Single</v>
+        <v>I Could Get Used To This - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>2:24</v>
+        <v>3:41</v>
       </c>
       <c r="H132" t="str">
-        <v>GIRLSET</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/little-miss-misdemeanor/1870996490</v>
+        <v>https://music.apple.com/us/album/i-could-get-used-to-this/1867222992</v>
       </c>
       <c r="L132" t="str">
-        <v>Little Miss (Misdemeanor) - GIRLSET</v>
+        <v>I Could Get Used To This - Jessie Ware</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>I Could Get Used To This</v>
+        <v>LA VILLA</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/i-could-get-used-to-this/1867222996</v>
+        <v>https://music.apple.com/us/song/la-villa/1847678152</v>
       </c>
       <c r="D133" t="str">
         <v>2026-01-23</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>I Could Get Used To This - Single</v>
+        <v>HOPI SENDÉ</v>
       </c>
       <c r="G133" t="str">
-        <v>3:41</v>
+        <v>3:12</v>
       </c>
       <c r="H133" t="str">
-        <v>Jessie Ware</v>
+        <v>Ryan Castro</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/ryan-castro/1263552447</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/i-could-get-used-to-this/1867222992</v>
+        <v>https://music.apple.com/us/album/la-villa/1847678143</v>
       </c>
       <c r="L133" t="str">
-        <v>I Could Get Used To This - Jessie Ware</v>
+        <v>LA VILLA - Ryan Castro</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>LA VILLA</v>
+        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700)</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/la-villa/1847678152</v>
+        <v>https://music.apple.com/us/song/lit-effect-feat-bktherula-lazer-dim-700/1868519613</v>
       </c>
       <c r="D134" t="str">
         <v>2026-01-23</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>HOPI SENDÉ</v>
+        <v>Strictly 4 The Scythe</v>
       </c>
       <c r="G134" t="str">
-        <v>3:12</v>
+        <v>3:27</v>
       </c>
       <c r="H134" t="str">
-        <v>Ryan Castro</v>
+        <v>Denzel Curry</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/ryan-castro/1263552447</v>
+        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/la-villa/1847678143</v>
+        <v>https://music.apple.com/us/album/lit-effect-feat-bktherula-lazer-dim-700/1868519270</v>
       </c>
       <c r="L134" t="str">
-        <v>LA VILLA - Ryan Castro</v>
+        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700) - Denzel Curry</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700)</v>
+        <v>Thick One</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/lit-effect-feat-bktherula-lazer-dim-700/1868519613</v>
+        <v>https://music.apple.com/us/song/thick-one/1868515478</v>
       </c>
       <c r="D135" t="str">
         <v>2026-01-23</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Strictly 4 The Scythe</v>
+        <v>Part 3</v>
       </c>
       <c r="G135" t="str">
-        <v>3:27</v>
+        <v>2:49</v>
       </c>
       <c r="H135" t="str">
-        <v>Denzel Curry</v>
+        <v>42 Dugg</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
+        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/lit-effect-feat-bktherula-lazer-dim-700/1868519270</v>
+        <v>https://music.apple.com/us/album/thick-one/1868515223</v>
       </c>
       <c r="L135" t="str">
-        <v>LIT EFFECT (feat. Bktherula &amp; LAZER DIM 700) - Denzel Curry</v>
+        <v>Thick One - 42 Dugg</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Thick One</v>
+        <v>How Much Did You Get For Your Soul</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/thick-one/1868515478</v>
+        <v>https://music.apple.com/us/song/how-much-did-you-get-for-your-soul/1843195678</v>
       </c>
       <c r="D136" t="str">
         <v>2026-01-23</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Part 3</v>
+        <v>World's Gone Wrong</v>
       </c>
       <c r="G136" t="str">
-        <v>2:49</v>
+        <v>3:59</v>
       </c>
       <c r="H136" t="str">
-        <v>42 Dugg</v>
+        <v>Lucinda Williams</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/42-dugg/1277595465</v>
+        <v>https://music.apple.com/us/artist/lucinda-williams/267658</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/thick-one/1868515223</v>
+        <v>https://music.apple.com/us/album/how-much-did-you-get-for-your-soul/1843195660</v>
       </c>
       <c r="L136" t="str">
-        <v>Thick One - 42 Dugg</v>
+        <v>How Much Did You Get For Your Soul - Lucinda Williams</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>How Much Did You Get For Your Soul</v>
+        <v>THUM</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/how-much-did-you-get-for-your-soul/1843195678</v>
+        <v>https://music.apple.com/us/song/thum/1863009362</v>
       </c>
       <c r="D137" t="str">
         <v>2026-01-23</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>World's Gone Wrong</v>
+        <v>THUM - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>3:59</v>
+        <v>2:11</v>
       </c>
       <c r="H137" t="str">
-        <v>Lucinda Williams</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/lucinda-williams/267658</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/how-much-did-you-get-for-your-soul/1843195660</v>
+        <v>https://music.apple.com/us/album/thum/1863009357</v>
       </c>
       <c r="L137" t="str">
-        <v>How Much Did You Get For Your Soul - Lucinda Williams</v>
+        <v>THUM - Violet Grohl</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>THUM</v>
+        <v>(I'm a) Rock "N" Roller</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/thum/1863009362</v>
+        <v>https://music.apple.com/us/song/im-a-rock-n-roller/1839888014</v>
       </c>
       <c r="D138" t="str">
         <v>2026-01-23</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>THUM - Single</v>
+        <v>The Great Satan</v>
       </c>
       <c r="G138" t="str">
-        <v>2:11</v>
+        <v>3:32</v>
       </c>
       <c r="H138" t="str">
-        <v>Violet Grohl</v>
+        <v>Rob Zombie</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/thum/1863009357</v>
+        <v>https://music.apple.com/us/album/im-a-rock-n-roller/1839887790</v>
       </c>
       <c r="L138" t="str">
-        <v>THUM - Violet Grohl</v>
+        <v>(I'm a) Rock "N" Roller - Rob Zombie</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>(I'm a) Rock "N" Roller</v>
+        <v>Excuses For Love</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/im-a-rock-n-roller/1839888014</v>
+        <v>https://music.apple.com/us/song/excuses-for-love/1856034295</v>
       </c>
       <c r="D139" t="str">
         <v>2026-01-23</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>The Great Satan</v>
+        <v>Hyperlove</v>
       </c>
       <c r="G139" t="str">
-        <v>3:32</v>
+        <v>3:04</v>
       </c>
       <c r="H139" t="str">
-        <v>Rob Zombie</v>
+        <v>MIKA</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
+        <v>https://music.apple.com/us/artist/mika/184932871</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/im-a-rock-n-roller/1839887790</v>
+        <v>https://music.apple.com/us/album/excuses-for-love/1856033810</v>
       </c>
       <c r="L139" t="str">
-        <v>(I'm a) Rock "N" Roller - Rob Zombie</v>
+        <v>Excuses For Love - MIKA</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Excuses For Love</v>
+        <v>3 Tears</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/excuses-for-love/1856034295</v>
+        <v>https://music.apple.com/us/song/3-tears/1861504548</v>
       </c>
       <c r="D140" t="str">
         <v>2026-01-23</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Hyperlove</v>
+        <v>3 Tears - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:04</v>
+        <v>2:50</v>
       </c>
       <c r="H140" t="str">
-        <v>MIKA</v>
+        <v>Mergui</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/mika/184932871</v>
+        <v>https://music.apple.com/us/artist/mergui/1423596903</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/excuses-for-love/1856033810</v>
+        <v>https://music.apple.com/us/album/3-tears/1861504545</v>
       </c>
       <c r="L140" t="str">
-        <v>Excuses For Love - MIKA</v>
+        <v>3 Tears - Mergui</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>3 Tears</v>
+        <v>Church Girl</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/3-tears/1861504548</v>
+        <v>https://music.apple.com/us/song/church-girl/1862008542</v>
       </c>
       <c r="D141" t="str">
         <v>2026-01-23</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>3 Tears - Single</v>
+        <v>Church Girl - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>2:50</v>
+        <v>3:19</v>
       </c>
       <c r="H141" t="str">
-        <v>Mergui</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/mergui/1423596903</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/3-tears/1861504545</v>
+        <v>https://music.apple.com/us/album/church-girl/1862008535</v>
       </c>
       <c r="L141" t="str">
-        <v>3 Tears - Mergui</v>
+        <v>Church Girl - Carly Pearce</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Church Girl</v>
+        <v>Funeral</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/church-girl/1862008542</v>
+        <v>https://music.apple.com/us/song/funeral/1867616928</v>
       </c>
       <c r="D142" t="str">
         <v>2026-01-23</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Church Girl - Single</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G142" t="str">
-        <v>3:19</v>
+        <v>4:03</v>
       </c>
       <c r="H142" t="str">
-        <v>Carly Pearce</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/church-girl/1862008535</v>
+        <v>https://music.apple.com/us/album/funeral/1867616617</v>
       </c>
       <c r="L142" t="str">
-        <v>Church Girl - Carly Pearce</v>
+        <v>Funeral - Dermot Kennedy</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Funeral</v>
+        <v>Say Yes</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/funeral/1867616928</v>
+        <v>https://music.apple.com/us/song/say-yes/1861995090</v>
       </c>
       <c r="D143" t="str">
         <v>2026-01-23</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>The Weight of the Woods</v>
+        <v>Say Yes - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>4:03</v>
+        <v>2:50</v>
       </c>
       <c r="H143" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Marques Anthony</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/marques-anthony/321321231</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/funeral/1867616617</v>
+        <v>https://music.apple.com/us/album/say-yes/1861995089</v>
       </c>
       <c r="L143" t="str">
-        <v>Funeral - Dermot Kennedy</v>
+        <v>Say Yes - Marques Anthony</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Say Yes</v>
+        <v>LOVE ME (feat. Stevie Wonder)</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/say-yes/1861995090</v>
+        <v>https://music.apple.com/us/song/love-me-feat-stevie-wonder/1867640879</v>
       </c>
       <c r="D144" t="str">
         <v>2026-01-23</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Say Yes - Single</v>
+        <v>CAMPILATION</v>
       </c>
       <c r="G144" t="str">
-        <v>2:50</v>
+        <v>3:10</v>
       </c>
       <c r="H144" t="str">
-        <v>Marques Anthony</v>
+        <v>Camper</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/marques-anthony/321321231</v>
+        <v>https://music.apple.com/us/artist/camper/1514886616</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/say-yes/1861995089</v>
+        <v>https://music.apple.com/us/album/love-me-feat-stevie-wonder/1867640873</v>
       </c>
       <c r="L144" t="str">
-        <v>Say Yes - Marques Anthony</v>
+        <v>LOVE ME (feat. Stevie Wonder) - Camper</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>LOVE ME (feat. Stevie Wonder)</v>
+        <v>UP TO MY NECK IN U</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/love-me-feat-stevie-wonder/1867640879</v>
+        <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
       </c>
       <c r="D145" t="str">
         <v>2026-01-23</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>CAMPILATION</v>
+        <v>UP TO MY NECK IN U - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:10</v>
+        <v>2:17</v>
       </c>
       <c r="H145" t="str">
-        <v>Camper</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/camper/1514886616</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/love-me-feat-stevie-wonder/1867640873</v>
+        <v>https://music.apple.com/us/album/up-to-my-neck-in-u/1862550671</v>
       </c>
       <c r="L145" t="str">
-        <v>LOVE ME (feat. Stevie Wonder) - Camper</v>
+        <v>UP TO MY NECK IN U - Ledbyher</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>UP TO MY NECK IN U</v>
+        <v>Wallflower</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
+        <v>https://music.apple.com/us/song/wallflower/1862737077</v>
       </c>
       <c r="D146" t="str">
         <v>2026-01-23</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>UP TO MY NECK IN U - Single</v>
+        <v>Wallflower - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>2:17</v>
+        <v>3:25</v>
       </c>
       <c r="H146" t="str">
-        <v>Ledbyher</v>
+        <v>Sikarus</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
+        <v>https://music.apple.com/us/artist/sikarus/1046558781</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/up-to-my-neck-in-u/1862550671</v>
+        <v>https://music.apple.com/us/album/wallflower/1862737074</v>
       </c>
       <c r="L146" t="str">
-        <v>UP TO MY NECK IN U - Ledbyher</v>
+        <v>Wallflower - Sikarus</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Wallflower</v>
+        <v>You Phase</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/wallflower/1862737077</v>
+        <v>https://music.apple.com/us/song/you-phase/1868861897</v>
       </c>
       <c r="D147" t="str">
         <v>2026-01-23</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Wallflower - Single</v>
+        <v>You Phase - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:25</v>
+        <v>2:51</v>
       </c>
       <c r="H147" t="str">
-        <v>Sikarus</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/sikarus/1046558781</v>
+        <v>https://music.apple.com/us/artist/mitchell-tenpenny/430369368</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/wallflower/1862737074</v>
+        <v>https://music.apple.com/us/album/you-phase/1868861895</v>
       </c>
       <c r="L147" t="str">
-        <v>Wallflower - Sikarus</v>
+        <v>You Phase - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>You Phase</v>
+        <v>Miss Independent</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/you-phase/1868861897</v>
+        <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
       </c>
       <c r="D148" t="str">
         <v>2026-01-23</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>You Phase - Single</v>
+        <v>Miss Independent - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>2:51</v>
+        <v>2:40</v>
       </c>
       <c r="H148" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/mitchell-tenpenny/430369368</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/you-phase/1868861895</v>
+        <v>https://music.apple.com/us/album/miss-independent/1870612555</v>
       </c>
       <c r="L148" t="str">
-        <v>You Phase - Mitchell Tenpenny</v>
+        <v>Miss Independent - 1Ski OG</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Miss Independent</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live]</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
+        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678482</v>
       </c>
       <c r="D149" t="str">
         <v>2026-01-23</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Miss Independent - Single</v>
+        <v>SO BE IT (Live)</v>
       </c>
       <c r="G149" t="str">
-        <v>2:40</v>
+        <v>5:47</v>
       </c>
       <c r="H149" t="str">
-        <v>1Ski OG</v>
+        <v>Elevation Worship</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/miss-independent/1870612555</v>
+        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678481</v>
       </c>
       <c r="L149" t="str">
-        <v>Miss Independent - 1Ski OG</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live] - Elevation Worship</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live]</v>
+        <v>go again</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678482</v>
+        <v>https://music.apple.com/us/song/go-again/1868987466</v>
       </c>
       <c r="D150" t="str">
         <v>2026-01-23</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>SO BE IT (Live)</v>
+        <v>go again - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>5:47</v>
+        <v>2:07</v>
       </c>
       <c r="H150" t="str">
-        <v>Elevation Worship</v>
+        <v>NateTaylorr</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
+        <v>https://music.apple.com/us/artist/natetaylorr/1243682934</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678481</v>
+        <v>https://music.apple.com/us/album/go-again/1868987193</v>
       </c>
       <c r="L150" t="str">
-        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live] - Elevation Worship</v>
+        <v>go again - NateTaylorr</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>go again</v>
+        <v>Autopilot</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/go-again/1868987466</v>
+        <v>https://music.apple.com/us/song/autopilot/1863072399</v>
       </c>
       <c r="D151" t="str">
         <v>2026-01-23</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>go again - Single</v>
+        <v>Autopilot</v>
       </c>
       <c r="G151" t="str">
-        <v>2:07</v>
+        <v>2:46</v>
       </c>
       <c r="H151" t="str">
-        <v>NateTaylorr</v>
+        <v>ALEXSUCKS</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/natetaylorr/1243682934</v>
+        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/go-again/1868987193</v>
+        <v>https://music.apple.com/us/album/autopilot/1863072393</v>
       </c>
       <c r="L151" t="str">
-        <v>go again - NateTaylorr</v>
+        <v>Autopilot - ALEXSUCKS</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Autopilot</v>
+        <v>Portrait of My Heart (feat. Brendan Yates)</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/autopilot/1863072399</v>
+        <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
       </c>
       <c r="D152" t="str">
         <v>2026-01-23</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Autopilot</v>
+        <v>Portrait of My Heart - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>2:46</v>
+        <v>3:04</v>
       </c>
       <c r="H152" t="str">
-        <v>ALEXSUCKS</v>
+        <v>SPELLLING</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
+        <v>https://music.apple.com/us/artist/spellling/1281213673</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/autopilot/1863072393</v>
+        <v>https://music.apple.com/us/album/portrait-of-my-heart-feat-brendan-yates/1862282167</v>
       </c>
       <c r="L152" t="str">
-        <v>Autopilot - ALEXSUCKS</v>
+        <v>Portrait of My Heart (feat. Brendan Yates) - SPELLLING</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Portrait of My Heart (feat. Brendan Yates)</v>
+        <v>In Violet</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
+        <v>https://music.apple.com/us/song/in-violet/1839471290</v>
       </c>
       <c r="D153" t="str">
         <v>2026-01-23</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Portrait of My Heart - Single</v>
+        <v>Death in the Business of Whaling</v>
       </c>
       <c r="G153" t="str">
-        <v>3:04</v>
+        <v>4:09</v>
       </c>
       <c r="H153" t="str">
-        <v>SPELLLING</v>
+        <v>Searows</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/spellling/1281213673</v>
+        <v>https://music.apple.com/us/artist/searows/1607240507</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/portrait-of-my-heart-feat-brendan-yates/1862282167</v>
+        <v>https://music.apple.com/us/album/in-violet/1839470844</v>
       </c>
       <c r="L153" t="str">
-        <v>Portrait of My Heart (feat. Brendan Yates) - SPELLLING</v>
+        <v>In Violet - Searows</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>In Violet</v>
+        <v>Baby Run</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/in-violet/1839471290</v>
+        <v>https://music.apple.com/us/song/baby-run/1857658819</v>
       </c>
       <c r="D154" t="str">
         <v>2026-01-23</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Death in the Business of Whaling</v>
+        <v>Baby Run - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>4:09</v>
+        <v>4:47</v>
       </c>
       <c r="H154" t="str">
-        <v>Searows</v>
+        <v>Jimi Jules</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/searows/1607240507</v>
+        <v>https://music.apple.com/us/artist/jimi-jules/586933009</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/in-violet/1839470844</v>
+        <v>https://music.apple.com/us/album/baby-run/1857658816</v>
       </c>
       <c r="L154" t="str">
-        <v>In Violet - Searows</v>
+        <v>Baby Run - Jimi Jules</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Baby Run</v>
+        <v>What If We Don't</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/baby-run/1857658819</v>
+        <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
       </c>
       <c r="D155" t="str">
         <v>2026-01-23</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Baby Run - Single</v>
+        <v>What If We Don't - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>4:47</v>
+        <v>3:06</v>
       </c>
       <c r="H155" t="str">
-        <v>Jimi Jules</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/jimi-jules/586933009</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/baby-run/1857658816</v>
+        <v>https://music.apple.com/us/album/what-if-we-dont/1862668776</v>
       </c>
       <c r="L155" t="str">
-        <v>Baby Run - Jimi Jules</v>
+        <v>What If We Don't - Ashley McBryde</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>What If We Don't</v>
+        <v>Hagamos Que</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
+        <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
       </c>
       <c r="D156" t="str">
         <v>2026-01-23</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>What If We Don't - Single</v>
+        <v>Hagamos Que - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:06</v>
+        <v>2:58</v>
       </c>
       <c r="H156" t="str">
-        <v>Ashley McBryde</v>
+        <v>Juanes</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/juanes/103856</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/what-if-we-dont/1862668776</v>
+        <v>https://music.apple.com/us/album/hagamos-que/1861956611</v>
       </c>
       <c r="L156" t="str">
-        <v>What If We Don't - Ashley McBryde</v>
+        <v>Hagamos Que - Juanes</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Hagamos Que</v>
+        <v>World Change Me</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
+        <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
       </c>
       <c r="D157" t="str">
         <v>2026-01-23</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Hagamos Que - Single</v>
+        <v>World Change Me - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>2:58</v>
+        <v>3:03</v>
       </c>
       <c r="H157" t="str">
-        <v>Juanes</v>
+        <v>Max McNown</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/juanes/103856</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/hagamos-que/1861956611</v>
+        <v>https://music.apple.com/us/album/world-change-me/1860974598</v>
       </c>
       <c r="L157" t="str">
-        <v>Hagamos Que - Juanes</v>
+        <v>World Change Me - Max McNown</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>World Change Me</v>
+        <v>Exclusive</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
+        <v>https://music.apple.com/us/song/exclusive/1851537672</v>
       </c>
       <c r="D158" t="str">
         <v>2026-01-23</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>World Change Me - Single</v>
+        <v>Exclusive - EP</v>
       </c>
       <c r="G158" t="str">
-        <v>3:03</v>
+        <v>3:20</v>
       </c>
       <c r="H158" t="str">
-        <v>Max McNown</v>
+        <v>Hudson Westbrook</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/world-change-me/1860974598</v>
+        <v>https://music.apple.com/us/album/exclusive/1851537671</v>
       </c>
       <c r="L158" t="str">
-        <v>World Change Me - Max McNown</v>
+        <v>Exclusive - Hudson Westbrook</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Exclusive</v>
+        <v>Say Less</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/exclusive/1851537672</v>
+        <v>https://music.apple.com/us/song/say-less/1867910122</v>
       </c>
       <c r="D159" t="str">
         <v>2026-01-23</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Exclusive - EP</v>
+        <v>Say Less - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:20</v>
+        <v>2:18</v>
       </c>
       <c r="H159" t="str">
-        <v>Hudson Westbrook</v>
+        <v>JYT</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
+        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/exclusive/1851537671</v>
+        <v>https://music.apple.com/us/album/say-less/1867910115</v>
       </c>
       <c r="L159" t="str">
-        <v>Exclusive - Hudson Westbrook</v>
+        <v>Say Less - JYT</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Say Less</v>
+        <v>Angels Cry</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/say-less/1867910122</v>
+        <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
       </c>
       <c r="D160" t="str">
         <v>2026-01-23</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Say Less - Single</v>
+        <v>X's for Eyes (Deluxe)</v>
       </c>
       <c r="G160" t="str">
-        <v>2:18</v>
+        <v>3:52</v>
       </c>
       <c r="H160" t="str">
-        <v>JYT</v>
+        <v>The Red Jumpsuit Apparatus</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
+        <v>https://music.apple.com/us/artist/the-red-jumpsuit-apparatus/130037074</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/say-less/1867910115</v>
+        <v>https://music.apple.com/us/album/angels-cry/1862320872</v>
       </c>
       <c r="L160" t="str">
-        <v>Say Less - JYT</v>
+        <v>Angels Cry - The Red Jumpsuit Apparatus</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Angels Cry</v>
+        <v>Over You</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
+        <v>https://music.apple.com/us/song/over-you/1846189473</v>
       </c>
       <c r="D161" t="str">
         <v>2026-01-23</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>X's for Eyes (Deluxe)</v>
+        <v>A Love For Strangers</v>
       </c>
       <c r="G161" t="str">
-        <v>3:52</v>
+        <v>4:44</v>
       </c>
       <c r="H161" t="str">
-        <v>The Red Jumpsuit Apparatus</v>
+        <v>Chet Faker</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/the-red-jumpsuit-apparatus/130037074</v>
+        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/angels-cry/1862320872</v>
+        <v>https://music.apple.com/us/album/over-you/1846189472</v>
       </c>
       <c r="L161" t="str">
-        <v>Angels Cry - The Red Jumpsuit Apparatus</v>
+        <v>Over You - Chet Faker</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Over You</v>
+        <v>Chala (My Soul Is on a Loop)</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/over-you/1846189473</v>
+        <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
       </c>
       <c r="D162" t="str">
         <v>2026-01-23</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>A Love For Strangers</v>
+        <v>Chala (My Soul Is on a Loop) - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>4:44</v>
+        <v>2:42</v>
       </c>
       <c r="H162" t="str">
-        <v>Chet Faker</v>
+        <v>Barry Can't Swim</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
+        <v>https://music.apple.com/us/artist/barry-cant-swim/1492752064</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/over-you/1846189472</v>
+        <v>https://music.apple.com/us/album/chala-my-soul-is-on-a-loop/1857789040</v>
       </c>
       <c r="L162" t="str">
-        <v>Over You - Chet Faker</v>
+        <v>Chala (My Soul Is on a Loop) - Barry Can't Swim</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Chala (My Soul Is on a Loop)</v>
+        <v>starlight feat. Madeline Follin</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
+        <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
       </c>
       <c r="D163" t="str">
         <v>2026-01-23</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Chala (My Soul Is on a Loop) - Single</v>
+        <v>starlight feat. Madeline Follin - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>2:42</v>
+        <v>3:06</v>
       </c>
       <c r="H163" t="str">
-        <v>Barry Can't Swim</v>
+        <v>Disco Lines</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/barry-cant-swim/1492752064</v>
+        <v>https://music.apple.com/us/artist/disco-lines/1462793893</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/chala-my-soul-is-on-a-loop/1857789040</v>
+        <v>https://music.apple.com/us/album/starlight-feat-madeline-follin/1869330767</v>
       </c>
       <c r="L163" t="str">
-        <v>Chala (My Soul Is on a Loop) - Barry Can't Swim</v>
+        <v>starlight feat. Madeline Follin - Disco Lines</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>starlight feat. Madeline Follin</v>
+        <v>Locked In (feat. Trippie Redd)</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
+        <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
       </c>
       <c r="D164" t="str">
         <v>2026-01-23</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>starlight feat. Madeline Follin - Single</v>
+        <v>Locked In (feat. Trippie Redd) - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:06</v>
+        <v>2:48</v>
       </c>
       <c r="H164" t="str">
-        <v>Disco Lines</v>
+        <v>David Guetta</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/disco-lines/1462793893</v>
+        <v>https://music.apple.com/us/artist/david-guetta/5557599</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/starlight-feat-madeline-follin/1869330767</v>
+        <v>https://music.apple.com/us/album/locked-in-feat-trippie-redd/1869439982</v>
       </c>
       <c r="L164" t="str">
-        <v>starlight feat. Madeline Follin - Disco Lines</v>
+        <v>Locked In (feat. Trippie Redd) - David Guetta</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Locked In (feat. Trippie Redd)</v>
+        <v>Rejoice</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
+        <v>https://music.apple.com/us/song/rejoice/1862633596</v>
       </c>
       <c r="D165" t="str">
         <v>2026-01-23</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Locked In (feat. Trippie Redd) - Single</v>
+        <v>Rejoice - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>2:48</v>
+        <v>4:20</v>
       </c>
       <c r="H165" t="str">
-        <v>David Guetta</v>
+        <v>Def Leppard</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/david-guetta/5557599</v>
+        <v>https://music.apple.com/us/artist/def-leppard/117554</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/locked-in-feat-trippie-redd/1869439982</v>
+        <v>https://music.apple.com/us/album/rejoice/1862633593</v>
       </c>
       <c r="L165" t="str">
-        <v>Locked In (feat. Trippie Redd) - David Guetta</v>
+        <v>Rejoice - Def Leppard</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Rejoice</v>
+        <v>Slight Werk (feat. Bree Runway) [Club Mix]</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/rejoice/1862633596</v>
+        <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
       </c>
       <c r="D166" t="str">
         <v>2026-01-23</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Rejoice - Single</v>
+        <v>Slight Werk (Club Mix) [feat. Bree Runway] - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>4:20</v>
+        <v>2:58</v>
       </c>
       <c r="H166" t="str">
-        <v>Def Leppard</v>
+        <v>Honey Dijon</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/def-leppard/117554</v>
+        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/rejoice/1862633593</v>
+        <v>https://music.apple.com/us/album/slight-werk-feat-bree-runway-club-mix/1860859551</v>
       </c>
       <c r="L166" t="str">
-        <v>Rejoice - Def Leppard</v>
+        <v>Slight Werk (feat. Bree Runway) [Club Mix] - Honey Dijon</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Slight Werk (feat. Bree Runway) [Club Mix]</v>
+        <v>Lucky Day</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
+        <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
       </c>
       <c r="D167" t="str">
         <v>2026-01-23</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Slight Werk (Club Mix) [feat. Bree Runway] - Single</v>
+        <v>Speed Kills</v>
       </c>
       <c r="G167" t="str">
-        <v>2:58</v>
+        <v>3:13</v>
       </c>
       <c r="H167" t="str">
-        <v>Honey Dijon</v>
+        <v>Ally Evenson</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
+        <v>https://music.apple.com/us/artist/ally-evenson/283908113</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/slight-werk-feat-bree-runway-club-mix/1860859551</v>
+        <v>https://music.apple.com/us/album/lucky-day/1849264498</v>
       </c>
       <c r="L167" t="str">
-        <v>Slight Werk (feat. Bree Runway) [Club Mix] - Honey Dijon</v>
+        <v>Lucky Day - Ally Evenson</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Lucky Day</v>
+        <v>Breathe On It</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
+        <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
       </c>
       <c r="D168" t="str">
         <v>2026-01-23</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Speed Kills</v>
+        <v>Breathe On It - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:13</v>
+        <v>4:00</v>
       </c>
       <c r="H168" t="str">
-        <v>Ally Evenson</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/ally-evenson/283908113</v>
+        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/lucky-day/1849264498</v>
+        <v>https://music.apple.com/us/album/breathe-on-it/1862938798</v>
       </c>
       <c r="L168" t="str">
-        <v>Lucky Day - Ally Evenson</v>
+        <v>Breathe On It - Tauren Wells</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Breathe On It</v>
+        <v>Easy</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
+        <v>https://music.apple.com/us/song/easy/1863456906</v>
       </c>
       <c r="D169" t="str">
         <v>2026-01-23</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Breathe On It - Single</v>
+        <v>Easy - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>4:00</v>
+        <v>4:30</v>
       </c>
       <c r="H169" t="str">
-        <v>Tauren Wells</v>
+        <v>lydi lynn</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
+        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/breathe-on-it/1862938798</v>
+        <v>https://music.apple.com/us/album/easy/1863456903</v>
       </c>
       <c r="L169" t="str">
-        <v>Breathe On It - Tauren Wells</v>
+        <v>Easy - lydi lynn</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Easy</v>
+        <v>Break Me In</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/easy/1863456906</v>
+        <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
       </c>
       <c r="D170" t="str">
         <v>2026-01-23</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Easy - Single</v>
+        <v>Break Me In - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>4:30</v>
+        <v>2:52</v>
       </c>
       <c r="H170" t="str">
-        <v>lydi lynn</v>
+        <v>Joyce Wrice</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
+        <v>https://music.apple.com/us/artist/joyce-wrice/591991458</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/easy/1863456903</v>
+        <v>https://music.apple.com/us/album/break-me-in/1862881766</v>
       </c>
       <c r="L170" t="str">
-        <v>Easy - lydi lynn</v>
+        <v>Break Me In - Joyce Wrice</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Break Me In</v>
+        <v>Long Live Love</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
+        <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
       </c>
       <c r="D171" t="str">
         <v>2026-01-23</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Break Me In - Single</v>
+        <v>Long Live Love - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:52</v>
+        <v>2:36</v>
       </c>
       <c r="H171" t="str">
-        <v>Joyce Wrice</v>
+        <v>Sugar</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/joyce-wrice/591991458</v>
+        <v>https://music.apple.com/us/artist/sugar/530175867</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/break-me-in/1862881766</v>
+        <v>https://music.apple.com/us/album/long-live-love/1851251226</v>
       </c>
       <c r="L171" t="str">
-        <v>Break Me In - Joyce Wrice</v>
+        <v>Long Live Love - Sugar</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Long Live Love</v>
+        <v>Depressed</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
+        <v>https://music.apple.com/us/song/depressed/1840400522</v>
       </c>
       <c r="D172" t="str">
         <v>2026-01-23</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Long Live Love - Single</v>
+        <v>Boycott Heaven</v>
       </c>
       <c r="G172" t="str">
-        <v>2:36</v>
+        <v>3:32</v>
       </c>
       <c r="H172" t="str">
-        <v>Sugar</v>
+        <v>The Format</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/sugar/530175867</v>
+        <v>https://music.apple.com/us/artist/the-format/3064903</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/long-live-love/1851251226</v>
+        <v>https://music.apple.com/us/album/depressed/1840399886</v>
       </c>
       <c r="L172" t="str">
-        <v>Long Live Love - Sugar</v>
+        <v>Depressed - The Format</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Depressed</v>
+        <v>Empty Hands</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/depressed/1840400522</v>
+        <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
       </c>
       <c r="D173" t="str">
         <v>2026-01-23</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Boycott Heaven</v>
+        <v>Empty Hands</v>
       </c>
       <c r="G173" t="str">
-        <v>3:32</v>
+        <v>3:09</v>
       </c>
       <c r="H173" t="str">
-        <v>The Format</v>
+        <v>Poppy</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/the-format/3064903</v>
+        <v>https://music.apple.com/us/artist/poppy/1004130511</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/depressed/1840399886</v>
+        <v>https://music.apple.com/us/album/empty-hands/1852046141</v>
       </c>
       <c r="L173" t="str">
-        <v>Depressed - The Format</v>
+        <v>Empty Hands - Poppy</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Empty Hands</v>
+        <v>The Long Surrender</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
+        <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
       </c>
       <c r="D174" t="str">
         <v>2026-01-23</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Empty Hands</v>
+        <v>The Long Surrender</v>
       </c>
       <c r="G174" t="str">
-        <v>3:09</v>
+        <v>3:45</v>
       </c>
       <c r="H174" t="str">
-        <v>Poppy</v>
+        <v>NEEDTOBREATHE</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/poppy/1004130511</v>
+        <v>https://music.apple.com/us/artist/needtobreathe/113247214</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/empty-hands/1852046141</v>
+        <v>https://music.apple.com/us/album/the-long-surrender/1861935699</v>
       </c>
       <c r="L174" t="str">
-        <v>Empty Hands - Poppy</v>
+        <v>The Long Surrender - NEEDTOBREATHE</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>The Long Surrender</v>
+        <v>Angela</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
+        <v>https://music.apple.com/us/song/angela/1866624257</v>
       </c>
       <c r="D175" t="str">
         <v>2026-01-23</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>The Long Surrender</v>
+        <v>Angela - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>3:45</v>
+        <v>3:32</v>
       </c>
       <c r="H175" t="str">
-        <v>NEEDTOBREATHE</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/needtobreathe/113247214</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/the-long-surrender/1861935699</v>
+        <v>https://music.apple.com/us/album/angela/1866624256</v>
       </c>
       <c r="L175" t="str">
-        <v>The Long Surrender - NEEDTOBREATHE</v>
+        <v>Angela - Hayden Everett</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Angela</v>
+        <v>Disappear</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/angela/1866624257</v>
+        <v>https://music.apple.com/us/song/disappear/1847663553</v>
       </c>
       <c r="D176" t="str">
         <v>2026-01-23</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Angela - Single</v>
+        <v>Greyhound</v>
       </c>
       <c r="G176" t="str">
-        <v>3:32</v>
+        <v>3:31</v>
       </c>
       <c r="H176" t="str">
-        <v>Hayden Everett</v>
+        <v>Katie Tupper</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/katie-tupper/1395542470</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/angela/1866624256</v>
+        <v>https://music.apple.com/us/album/disappear/1847663546</v>
       </c>
       <c r="L176" t="str">
-        <v>Angela - Hayden Everett</v>
+        <v>Disappear - Katie Tupper</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Disappear</v>
+        <v>Catapult</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/disappear/1847663553</v>
+        <v>https://music.apple.com/us/song/catapult/1862951335</v>
       </c>
       <c r="D177" t="str">
         <v>2026-01-23</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Greyhound</v>
+        <v>Catapult - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:31</v>
+        <v>2:57</v>
       </c>
       <c r="H177" t="str">
-        <v>Katie Tupper</v>
+        <v>Cape Francis</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/katie-tupper/1395542470</v>
+        <v>https://music.apple.com/us/artist/cape-francis/1242523550</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/disappear/1847663546</v>
+        <v>https://music.apple.com/us/album/catapult/1862951333</v>
       </c>
       <c r="L177" t="str">
-        <v>Disappear - Katie Tupper</v>
+        <v>Catapult - Cape Francis</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Catapult</v>
+        <v>Think Twice</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/catapult/1862951335</v>
+        <v>https://music.apple.com/us/song/think-twice/1850698548</v>
       </c>
       <c r="D178" t="str">
         <v>2026-01-23</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Catapult - Single</v>
+        <v>Think Twice - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:57</v>
+        <v>2:22</v>
       </c>
       <c r="H178" t="str">
-        <v>Cape Francis</v>
+        <v>Leonie Biney</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/cape-francis/1242523550</v>
+        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/catapult/1862951333</v>
+        <v>https://music.apple.com/us/album/think-twice/1850698545</v>
       </c>
       <c r="L178" t="str">
-        <v>Catapult - Cape Francis</v>
+        <v>Think Twice - Leonie Biney</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Think Twice</v>
+        <v>LOVESONGS</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/think-twice/1850698548</v>
+        <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
       </c>
       <c r="D179" t="str">
         <v>2026-01-23</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Think Twice - Single</v>
+        <v>BEAUTIFUL MADNESS</v>
       </c>
       <c r="G179" t="str">
-        <v>2:22</v>
+        <v>3:33</v>
       </c>
       <c r="H179" t="str">
-        <v>Leonie Biney</v>
+        <v>Agnes</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
+        <v>https://music.apple.com/us/artist/agnes/42568985</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/think-twice/1850698545</v>
+        <v>https://music.apple.com/us/album/lovesongs/1849098275</v>
       </c>
       <c r="L179" t="str">
-        <v>Think Twice - Leonie Biney</v>
+        <v>LOVESONGS - Agnes</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>LOVESONGS</v>
+        <v>Down South</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
+        <v>https://music.apple.com/us/song/down-south/1861010793</v>
       </c>
       <c r="D180" t="str">
         <v>2026-01-23</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>BEAUTIFUL MADNESS</v>
+        <v>Down South - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:33</v>
+        <v>2:19</v>
       </c>
       <c r="H180" t="str">
-        <v>Agnes</v>
+        <v>Trap Dickey</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/agnes/42568985</v>
+        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/lovesongs/1849098275</v>
+        <v>https://music.apple.com/us/album/down-south/1861010788</v>
       </c>
       <c r="L180" t="str">
-        <v>LOVESONGS - Agnes</v>
+        <v>Down South - Trap Dickey</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Down South</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/down-south/1861010793</v>
+        <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
       </c>
       <c r="D181" t="str">
         <v>2026-01-23</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Down South - Single</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:19</v>
+        <v>2:16</v>
       </c>
       <c r="H181" t="str">
-        <v>Trap Dickey</v>
+        <v>SALIMATA</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
+        <v>https://music.apple.com/us/artist/salimata/690253822</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/down-south/1861010788</v>
+        <v>https://music.apple.com/us/album/jackpot-foil-a-colors-show/1866998655</v>
       </c>
       <c r="L181" t="str">
-        <v>Down South - Trap Dickey</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW - SALIMATA</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW</v>
+        <v>Love Like This</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
+        <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
       </c>
       <c r="D182" t="str">
         <v>2026-01-23</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW - Single</v>
+        <v>Love Like This - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:16</v>
+        <v>3:30</v>
       </c>
       <c r="H182" t="str">
-        <v>SALIMATA</v>
+        <v>Jacob Banks</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/salimata/690253822</v>
+        <v>https://music.apple.com/us/artist/jacob-banks/625014171</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/jackpot-foil-a-colors-show/1866998655</v>
+        <v>https://music.apple.com/us/album/love-like-this/1866999617</v>
       </c>
       <c r="L182" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW - SALIMATA</v>
+        <v>Love Like This - Jacob Banks</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Love Like This</v>
+        <v>Plan Plan</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
+        <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
       </c>
       <c r="D183" t="str">
         <v>2026-01-23</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Love Like This - Single</v>
+        <v>La Locura</v>
       </c>
       <c r="G183" t="str">
-        <v>3:30</v>
+        <v>3:10</v>
       </c>
       <c r="H183" t="str">
-        <v>Jacob Banks</v>
+        <v>Funky</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/jacob-banks/625014171</v>
+        <v>https://music.apple.com/us/artist/funky/80960663</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/love-like-this/1866999617</v>
+        <v>https://music.apple.com/us/album/plan-plan/1867940087</v>
       </c>
       <c r="L183" t="str">
-        <v>Love Like This - Jacob Banks</v>
+        <v>Plan Plan - Funky</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Plan Plan</v>
+        <v>double edged sword</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
+        <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
       </c>
       <c r="D184" t="str">
         <v>2026-01-23</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>La Locura</v>
+        <v>double edged sword - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:10</v>
+        <v>3:28</v>
       </c>
       <c r="H184" t="str">
-        <v>Funky</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/funky/80960663</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/plan-plan/1867940087</v>
+        <v>https://music.apple.com/us/album/double-edged-sword/1868829044</v>
       </c>
       <c r="L184" t="str">
-        <v>Plan Plan - Funky</v>
+        <v>double edged sword - Hailey Picardi</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>double edged sword</v>
+        <v>SOMEWHERE IN BETWEEN</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
+        <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
       </c>
       <c r="D185" t="str">
         <v>2026-01-23</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>double edged sword - Single</v>
+        <v>SOMEWHERE IN BETWEEN - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:28</v>
+        <v>3:27</v>
       </c>
       <c r="H185" t="str">
-        <v>Hailey Picardi</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/matt-hansen/1442658353</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/double-edged-sword/1868829044</v>
+        <v>https://music.apple.com/us/album/somewhere-in-between/1866969151</v>
       </c>
       <c r="L185" t="str">
-        <v>double edged sword - Hailey Picardi</v>
+        <v>SOMEWHERE IN BETWEEN - Matt Hansen</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>SOMEWHERE IN BETWEEN</v>
+        <v>The Decay</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
+        <v>https://music.apple.com/us/song/the-decay/1862836783</v>
       </c>
       <c r="D186" t="str">
         <v>2026-01-23</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>SOMEWHERE IN BETWEEN - Single</v>
+        <v>What Remains (Midnight Edition)</v>
       </c>
       <c r="G186" t="str">
-        <v>3:27</v>
+        <v>3:20</v>
       </c>
       <c r="H186" t="str">
-        <v>Matt Hansen</v>
+        <v>Pop Evil</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/matt-hansen/1442658353</v>
+        <v>https://music.apple.com/us/artist/pop-evil/441597923</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/somewhere-in-between/1866969151</v>
+        <v>https://music.apple.com/us/album/the-decay/1862836507</v>
       </c>
       <c r="L186" t="str">
-        <v>SOMEWHERE IN BETWEEN - Matt Hansen</v>
+        <v>The Decay - Pop Evil</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>The Decay</v>
+        <v>3111</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/the-decay/1862836783</v>
+        <v>https://music.apple.com/us/song/3111/1862225387</v>
       </c>
       <c r="D187" t="str">
         <v>2026-01-23</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>What Remains (Midnight Edition)</v>
+        <v>Goliath</v>
       </c>
       <c r="G187" t="str">
-        <v>3:20</v>
+        <v>4:08</v>
       </c>
       <c r="H187" t="str">
-        <v>Pop Evil</v>
+        <v>Exodus</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/pop-evil/441597923</v>
+        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/the-decay/1862836507</v>
+        <v>https://music.apple.com/us/album/3111/1862225385</v>
       </c>
       <c r="L187" t="str">
-        <v>The Decay - Pop Evil</v>
+        <v>3111 - Exodus</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>3111</v>
+        <v>Touch My Love And Die</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/3111/1862225387</v>
+        <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
       </c>
       <c r="D188" t="str">
         <v>2026-01-23</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Goliath</v>
+        <v>Touch My Love And Die - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>4:08</v>
+        <v>2:57</v>
       </c>
       <c r="H188" t="str">
-        <v>Exodus</v>
+        <v>Myrkur</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
+        <v>https://music.apple.com/us/artist/myrkur/293296859</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/3111/1862225385</v>
+        <v>https://music.apple.com/us/album/touch-my-love-and-die/1867630168</v>
       </c>
       <c r="L188" t="str">
-        <v>3111 - Exodus</v>
+        <v>Touch My Love And Die - Myrkur</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Touch My Love And Die</v>
+        <v>Bomb To A Knife Fight</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
+        <v>https://music.apple.com/us/song/bomb-to-a-knife-fight/1861589406</v>
       </c>
       <c r="D189" t="str">
         <v>2026-01-23</v>
@@ -7557,68 +7557,30 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Touch My Love And Die - Single</v>
+        <v>Bomb To A Knife Fight - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>2:57</v>
+        <v>2:41</v>
       </c>
       <c r="H189" t="str">
-        <v>Myrkur</v>
+        <v>The Barbarians of California</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/myrkur/293296859</v>
+        <v>https://music.apple.com/us/artist/the-barbarians-of-california/1724096474</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/touch-my-love-and-die/1867630168</v>
+        <v>https://music.apple.com/us/album/bomb-to-a-knife-fight/1861589405</v>
       </c>
       <c r="L189" t="str">
-        <v>Touch My Love And Die - Myrkur</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="str">
-        <v>Bomb To A Knife Fight</v>
-      </c>
-      <c r="B190" t="str">
-        <v/>
-      </c>
-      <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/bomb-to-a-knife-fight/1861589406</v>
-      </c>
-      <c r="D190" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E190" t="str">
-        <v/>
-      </c>
-      <c r="F190" t="str">
-        <v>Bomb To A Knife Fight - Single</v>
-      </c>
-      <c r="G190" t="str">
-        <v>2:41</v>
-      </c>
-      <c r="H190" t="str">
-        <v>The Barbarians of California</v>
-      </c>
-      <c r="I190" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/the-barbarians-of-california/1724096474</v>
-      </c>
-      <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/bomb-to-a-knife-fight/1861589405</v>
-      </c>
-      <c r="L190" t="str">
         <v>Bomb To A Knife Fight - The Barbarians of California</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L190"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L189"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-01-week04/titles.xlsx
+++ b/data/global/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>4 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>4 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:59</v>
@@ -477,7 +477,7 @@
         <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B3" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:56</v>
@@ -515,7 +515,7 @@
         <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:46</v>
@@ -553,7 +553,7 @@
         <v>Dean Lewis - I Am Getting Well</v>
       </c>
       <c r="B5" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:47</v>
@@ -591,7 +591,7 @@
         <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B6" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>4:37</v>
@@ -629,7 +629,7 @@
         <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:06</v>
@@ -667,7 +667,7 @@
         <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B8" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:54</v>
@@ -705,7 +705,7 @@
         <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>4:10</v>
@@ -740,10 +740,10 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Lyric Video)</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:26</v>
@@ -773,7 +773,7 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Lyric Video) - Matt Hansen</v>
+        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="11">
@@ -819,7 +819,7 @@
         <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G12" t="str">
         <v>2:56</v>
@@ -857,7 +857,7 @@
         <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G13" t="str">
         <v>4:01</v>
@@ -895,7 +895,7 @@
         <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:05</v>
@@ -933,7 +933,7 @@
         <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G15" t="str">
         <v>2:27</v>
@@ -971,7 +971,7 @@
         <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G16" t="str">
         <v>2:34</v>
@@ -1009,7 +1009,7 @@
         <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G17" t="str">
         <v>3:13</v>
@@ -1047,7 +1047,7 @@
         <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B18" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:13</v>
@@ -1085,7 +1085,7 @@
         <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G19" t="str">
         <v>3:08</v>
@@ -1123,7 +1123,7 @@
         <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G20" t="str">
         <v>5:14</v>
@@ -1161,7 +1161,7 @@
         <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G21" t="str">
         <v>2:59</v>
@@ -1731,7 +1731,7 @@
         <v>LØLØ - 007 (Official Music Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=4okJouEbZ_s</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>2:54</v>
@@ -2871,7 +2871,7 @@
         <v>Stephen Sanchez - Sweet Love</v>
       </c>
       <c r="B66" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=B62HyHDheIE</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
         <v>3:04</v>
@@ -4201,7 +4201,7 @@
         <v>RAYE - WHERE IS MY HUSBAND! (Live at The Fashion Awards 2025)</v>
       </c>
       <c r="B101" t="str">
-        <v>3 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=tYpOHbXFnm0</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>3 weeks ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v>3:58</v>

--- a/data/global/2026-01-week04/titles.xlsx
+++ b/data/global/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>5 hours ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:59</v>
@@ -477,7 +477,7 @@
         <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B3" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:56</v>
@@ -515,7 +515,7 @@
         <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:46</v>
@@ -553,7 +553,7 @@
         <v>Dean Lewis - I Am Getting Well</v>
       </c>
       <c r="B5" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:47</v>
@@ -591,7 +591,7 @@
         <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B6" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>4:37</v>
@@ -629,7 +629,7 @@
         <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:06</v>
@@ -667,7 +667,7 @@
         <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B8" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:54</v>
@@ -705,7 +705,7 @@
         <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>4:10</v>
@@ -743,7 +743,7 @@
         <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:26</v>
@@ -819,7 +819,7 @@
         <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G12" t="str">
         <v>2:56</v>
@@ -857,7 +857,7 @@
         <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G13" t="str">
         <v>4:01</v>
@@ -895,7 +895,7 @@
         <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:05</v>
@@ -933,7 +933,7 @@
         <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G15" t="str">
         <v>2:27</v>
@@ -971,7 +971,7 @@
         <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G16" t="str">
         <v>2:34</v>
@@ -1009,7 +1009,7 @@
         <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G17" t="str">
         <v>3:13</v>
@@ -1047,7 +1047,7 @@
         <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B18" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:13</v>
@@ -1085,7 +1085,7 @@
         <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G19" t="str">
         <v>3:08</v>
@@ -1123,7 +1123,7 @@
         <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G20" t="str">
         <v>5:14</v>
@@ -1161,7 +1161,7 @@
         <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G21" t="str">
         <v>2:59</v>
@@ -1541,7 +1541,7 @@
         <v>Just A Mess (Live acoustic studio session)</v>
       </c>
       <c r="B31" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=ShW-I63KD8w</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>3:45</v>
@@ -2339,7 +2339,7 @@
         <v>Nickless - Don't Stop The Car (live @ Powerplay Studios)</v>
       </c>
       <c r="B52" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=R0vVYP8tSIw</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
         <v>5:24</v>
@@ -2795,7 +2795,7 @@
         <v>Billy Raffoul &amp; Donovan Woods - The Love of My Life (Great Lakes Version)</v>
       </c>
       <c r="B64" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=zqO1pEdNagY</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
         <v>3:15</v>
@@ -2833,7 +2833,7 @@
         <v>Nathan Evans x Saint PNHX - Happy Place (Official Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=2F4VCeuV898</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
         <v>3:03</v>

--- a/data/global/2026-01-week04/titles.xlsx
+++ b/data/global/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:59</v>
@@ -477,7 +477,7 @@
         <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B3" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:56</v>
@@ -515,7 +515,7 @@
         <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:46</v>
@@ -553,7 +553,7 @@
         <v>Dean Lewis - I Am Getting Well</v>
       </c>
       <c r="B5" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:47</v>
@@ -591,7 +591,7 @@
         <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B6" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>4:37</v>
@@ -629,7 +629,7 @@
         <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:06</v>
@@ -667,7 +667,7 @@
         <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B8" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:54</v>
@@ -705,7 +705,7 @@
         <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>4:10</v>
@@ -743,7 +743,7 @@
         <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:26</v>
@@ -781,7 +781,7 @@
         <v>Louis Tomlinson - Imposter (Official Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=rzuD5szQhso</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
         <v>2:56</v>
@@ -819,7 +819,7 @@
         <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G12" t="str">
         <v>2:56</v>
@@ -857,7 +857,7 @@
         <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G13" t="str">
         <v>4:01</v>
@@ -895,7 +895,7 @@
         <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:05</v>
@@ -933,7 +933,7 @@
         <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G15" t="str">
         <v>2:27</v>
@@ -971,7 +971,7 @@
         <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G16" t="str">
         <v>2:34</v>
@@ -1009,7 +1009,7 @@
         <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G17" t="str">
         <v>3:13</v>
@@ -1047,7 +1047,7 @@
         <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B18" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:13</v>
@@ -1085,7 +1085,7 @@
         <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G19" t="str">
         <v>3:08</v>
@@ -1123,7 +1123,7 @@
         <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G20" t="str">
         <v>5:14</v>
@@ -1161,7 +1161,7 @@
         <v>Lana Lubany - BAD IDEA (Official Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=MQHj9eGCHZY</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G21" t="str">
         <v>2:59</v>
@@ -1655,7 +1655,7 @@
         <v>Chappell Roan - The Subway (Live from Kansas City)</v>
       </c>
       <c r="B34" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=6kZVtF8iaWw</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>4:27</v>
@@ -2719,7 +2719,7 @@
         <v>Johnny Orlando - Emilia (Official Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=fALGXLRIT2s</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
         <v>3:14</v>
@@ -2757,7 +2757,7 @@
         <v>Kungs, Theophilus London - Galaxy (official video)</v>
       </c>
       <c r="B63" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=GlPee9bF2u0</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
         <v>3:32</v>
@@ -3745,7 +3745,7 @@
         <v>Grace Enger - All My Songs (Official Lyric Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=gWyaiGAFVO8</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G89" t="str">
         <v>3:29</v>

--- a/data/global/2026-01-week04/titles.xlsx
+++ b/data/global/2026-01-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:59</v>
@@ -477,7 +477,7 @@
         <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B3" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:56</v>
@@ -515,7 +515,7 @@
         <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:46</v>
@@ -553,7 +553,7 @@
         <v>Dean Lewis - I Am Getting Well</v>
       </c>
       <c r="B5" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:47</v>
@@ -591,7 +591,7 @@
         <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B6" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>4:37</v>
@@ -629,7 +629,7 @@
         <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:06</v>
@@ -667,7 +667,7 @@
         <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B8" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:54</v>
@@ -705,7 +705,7 @@
         <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>4:10</v>
@@ -743,7 +743,7 @@
         <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:26</v>
@@ -819,7 +819,7 @@
         <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G12" t="str">
         <v>2:56</v>
@@ -857,7 +857,7 @@
         <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G13" t="str">
         <v>4:01</v>
@@ -895,7 +895,7 @@
         <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:05</v>
@@ -933,7 +933,7 @@
         <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G15" t="str">
         <v>2:27</v>
@@ -971,7 +971,7 @@
         <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G16" t="str">
         <v>2:34</v>
@@ -1009,7 +1009,7 @@
         <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G17" t="str">
         <v>3:13</v>
@@ -1047,7 +1047,7 @@
         <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B18" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:13</v>
@@ -1085,7 +1085,7 @@
         <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G19" t="str">
         <v>3:08</v>
@@ -1123,7 +1123,7 @@
         <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G20" t="str">
         <v>5:14</v>
@@ -1693,7 +1693,7 @@
         <v>Armik - Rumba De Noche (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B35" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=guUvgEKkk1U</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>4:34</v>
@@ -2301,7 +2301,7 @@
         <v>Lily Allen - Sleepwalking (Live on SNL)</v>
       </c>
       <c r="B51" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=vH5ewjAQfNc</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>3:21</v>

--- a/data/global/2026-01-week04/titles.xlsx
+++ b/data/global/2026-01-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L189"/>
+  <dimension ref="A1:L191"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -439,7 +439,7 @@
         <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:59</v>
@@ -477,7 +477,7 @@
         <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B3" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>2:56</v>
@@ -515,7 +515,7 @@
         <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:46</v>
@@ -553,7 +553,7 @@
         <v>Dean Lewis - I Am Getting Well</v>
       </c>
       <c r="B5" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=e3cy18_1eoU</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>2:47</v>
@@ -591,7 +591,7 @@
         <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B6" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>4:37</v>
@@ -629,7 +629,7 @@
         <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:06</v>
@@ -667,7 +667,7 @@
         <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B8" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:54</v>
@@ -705,7 +705,7 @@
         <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>4:10</v>
@@ -743,7 +743,7 @@
         <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:26</v>
@@ -819,7 +819,7 @@
         <v>Mitchell Tenpenny - You Phase (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=UPuK6wV5Zco</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G12" t="str">
         <v>2:56</v>
@@ -857,7 +857,7 @@
         <v>Tauren Wells - Breathe On It (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=9hW9sNMn2A0</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G13" t="str">
         <v>4:01</v>
@@ -895,7 +895,7 @@
         <v>Maiah Manser - Feeling it All (Official Music Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=JMYvXleIwfU</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:05</v>
@@ -933,7 +933,7 @@
         <v>Taylor Austin Dye - Man For That (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=vOzX-o11seI</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G15" t="str">
         <v>2:27</v>
@@ -971,7 +971,7 @@
         <v>Chelsea Cutler - BAD (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=86k4E6ydHVU</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G16" t="str">
         <v>2:34</v>
@@ -1009,7 +1009,7 @@
         <v>Ashley Kutcher - Dig 'Em Up (Official Lyric Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=-UWIFAiOOPE</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G17" t="str">
         <v>3:13</v>
@@ -1047,7 +1047,7 @@
         <v>Louis Tomlinson - Dark To Light (Visualiser)</v>
       </c>
       <c r="B18" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=02QyA29poAM</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:13</v>
@@ -1085,7 +1085,7 @@
         <v>CAIN - So Long Sad Songs (Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=feOv8nufa_I</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G19" t="str">
         <v>3:08</v>
@@ -1123,7 +1123,7 @@
         <v>Harry Styles - Aperture (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=rA_eCxPay7E</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G20" t="str">
         <v>5:14</v>
@@ -1237,7 +1237,7 @@
         <v>Dermot Kennedy - Funeral (Official Music Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=JzOUJZPky6o</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>4:09</v>
@@ -1503,7 +1503,7 @@
         <v>Lauren Watkins - Pretty Please (In A Perfect World: Petal Session)</v>
       </c>
       <c r="B30" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=oJ-l2ptQwbQ</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>3:17</v>
@@ -2681,7 +2681,7 @@
         <v>ella jane - When I Was Beautiful (Live)</v>
       </c>
       <c r="B61" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=_R5wJ7PkJew</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
         <v>3:24</v>
@@ -5870,13 +5870,13 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>UP TO MY NECK IN U</v>
+        <v>Ojalá</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
+        <v>https://music.apple.com/us/song/ojal%C3%A1/1867866690</v>
       </c>
       <c r="D145" t="str">
         <v>2026-01-23</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>UP TO MY NECK IN U - Single</v>
+        <v>Ojalá - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>2:17</v>
+        <v>4:11</v>
       </c>
       <c r="H145" t="str">
-        <v>Ledbyher</v>
+        <v>Lunay</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
+        <v>https://music.apple.com/us/artist/lunay/938127685</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/up-to-my-neck-in-u/1862550671</v>
+        <v>https://music.apple.com/us/album/ojal%C3%A1/1867866683</v>
       </c>
       <c r="L145" t="str">
-        <v>UP TO MY NECK IN U - Ledbyher</v>
+        <v>Ojalá - Lunay</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Wallflower</v>
+        <v>UP TO MY NECK IN U</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/wallflower/1862737077</v>
+        <v>https://music.apple.com/us/song/up-to-my-neck-in-u/1862550673</v>
       </c>
       <c r="D146" t="str">
         <v>2026-01-23</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Wallflower - Single</v>
+        <v>UP TO MY NECK IN U - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:25</v>
+        <v>2:17</v>
       </c>
       <c r="H146" t="str">
-        <v>Sikarus</v>
+        <v>Ledbyher</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/sikarus/1046558781</v>
+        <v>https://music.apple.com/us/artist/ledbyher/1516066807</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/wallflower/1862737074</v>
+        <v>https://music.apple.com/us/album/up-to-my-neck-in-u/1862550671</v>
       </c>
       <c r="L146" t="str">
-        <v>Wallflower - Sikarus</v>
+        <v>UP TO MY NECK IN U - Ledbyher</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>You Phase</v>
+        <v>Wallflower</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/you-phase/1868861897</v>
+        <v>https://music.apple.com/us/song/wallflower/1862737077</v>
       </c>
       <c r="D147" t="str">
         <v>2026-01-23</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>You Phase - Single</v>
+        <v>Wallflower - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>2:51</v>
+        <v>3:25</v>
       </c>
       <c r="H147" t="str">
-        <v>Mitchell Tenpenny</v>
+        <v>Sikarus</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/mitchell-tenpenny/430369368</v>
+        <v>https://music.apple.com/us/artist/sikarus/1046558781</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/you-phase/1868861895</v>
+        <v>https://music.apple.com/us/album/wallflower/1862737074</v>
       </c>
       <c r="L147" t="str">
-        <v>You Phase - Mitchell Tenpenny</v>
+        <v>Wallflower - Sikarus</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Miss Independent</v>
+        <v>You Phase</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
+        <v>https://music.apple.com/us/song/you-phase/1868861897</v>
       </c>
       <c r="D148" t="str">
         <v>2026-01-23</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Miss Independent - Single</v>
+        <v>You Phase - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>2:40</v>
+        <v>2:51</v>
       </c>
       <c r="H148" t="str">
-        <v>1Ski OG</v>
+        <v>Mitchell Tenpenny</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/mitchell-tenpenny/430369368</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/miss-independent/1870612555</v>
+        <v>https://music.apple.com/us/album/you-phase/1868861895</v>
       </c>
       <c r="L148" t="str">
-        <v>Miss Independent - 1Ski OG</v>
+        <v>You Phase - Mitchell Tenpenny</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live]</v>
+        <v>Miss Independent</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678482</v>
+        <v>https://music.apple.com/us/song/miss-independent/1870612557</v>
       </c>
       <c r="D149" t="str">
         <v>2026-01-23</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>SO BE IT (Live)</v>
+        <v>Miss Independent - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>5:47</v>
+        <v>2:40</v>
       </c>
       <c r="H149" t="str">
-        <v>Elevation Worship</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678481</v>
+        <v>https://music.apple.com/us/album/miss-independent/1870612555</v>
       </c>
       <c r="L149" t="str">
-        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live] - Elevation Worship</v>
+        <v>Miss Independent - 1Ski OG</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>go again</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live]</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/go-again/1868987466</v>
+        <v>https://music.apple.com/us/song/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678482</v>
       </c>
       <c r="D150" t="str">
         <v>2026-01-23</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>go again - Single</v>
+        <v>SO BE IT (Live)</v>
       </c>
       <c r="G150" t="str">
-        <v>2:07</v>
+        <v>5:47</v>
       </c>
       <c r="H150" t="str">
-        <v>NateTaylorr</v>
+        <v>Elevation Worship</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/natetaylorr/1243682934</v>
+        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/go-again/1868987193</v>
+        <v>https://music.apple.com/us/album/so-be-it-feat-tiffany-hudson-chris-brown-live/1870678481</v>
       </c>
       <c r="L150" t="str">
-        <v>go again - NateTaylorr</v>
+        <v>SO BE IT (feat. Tiffany Hudson &amp; Chris Brown) [Live] - Elevation Worship</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Autopilot</v>
+        <v>go again</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/autopilot/1863072399</v>
+        <v>https://music.apple.com/us/song/go-again/1868987466</v>
       </c>
       <c r="D151" t="str">
         <v>2026-01-23</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Autopilot</v>
+        <v>go again - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>2:46</v>
+        <v>2:07</v>
       </c>
       <c r="H151" t="str">
-        <v>ALEXSUCKS</v>
+        <v>NateTaylorr</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
+        <v>https://music.apple.com/us/artist/natetaylorr/1243682934</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/autopilot/1863072393</v>
+        <v>https://music.apple.com/us/album/go-again/1868987193</v>
       </c>
       <c r="L151" t="str">
-        <v>Autopilot - ALEXSUCKS</v>
+        <v>go again - NateTaylorr</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Portrait of My Heart (feat. Brendan Yates)</v>
+        <v>Autopilot</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
+        <v>https://music.apple.com/us/song/autopilot/1863072399</v>
       </c>
       <c r="D152" t="str">
         <v>2026-01-23</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Portrait of My Heart - Single</v>
+        <v>Autopilot</v>
       </c>
       <c r="G152" t="str">
-        <v>3:04</v>
+        <v>2:46</v>
       </c>
       <c r="H152" t="str">
-        <v>SPELLLING</v>
+        <v>ALEXSUCKS</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/spellling/1281213673</v>
+        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/portrait-of-my-heart-feat-brendan-yates/1862282167</v>
+        <v>https://music.apple.com/us/album/autopilot/1863072393</v>
       </c>
       <c r="L152" t="str">
-        <v>Portrait of My Heart (feat. Brendan Yates) - SPELLLING</v>
+        <v>Autopilot - ALEXSUCKS</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>In Violet</v>
+        <v>Portrait of My Heart (feat. Brendan Yates)</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/in-violet/1839471290</v>
+        <v>https://music.apple.com/us/song/portrait-of-my-heart-feat-brendan-yates/1862282168</v>
       </c>
       <c r="D153" t="str">
         <v>2026-01-23</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Death in the Business of Whaling</v>
+        <v>Portrait of My Heart - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>4:09</v>
+        <v>3:04</v>
       </c>
       <c r="H153" t="str">
-        <v>Searows</v>
+        <v>SPELLLING</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/searows/1607240507</v>
+        <v>https://music.apple.com/us/artist/spellling/1281213673</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/in-violet/1839470844</v>
+        <v>https://music.apple.com/us/album/portrait-of-my-heart-feat-brendan-yates/1862282167</v>
       </c>
       <c r="L153" t="str">
-        <v>In Violet - Searows</v>
+        <v>Portrait of My Heart (feat. Brendan Yates) - SPELLLING</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Baby Run</v>
+        <v>In Violet</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/baby-run/1857658819</v>
+        <v>https://music.apple.com/us/song/in-violet/1839471290</v>
       </c>
       <c r="D154" t="str">
         <v>2026-01-23</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Baby Run - Single</v>
+        <v>Death in the Business of Whaling</v>
       </c>
       <c r="G154" t="str">
-        <v>4:47</v>
+        <v>4:09</v>
       </c>
       <c r="H154" t="str">
-        <v>Jimi Jules</v>
+        <v>Searows</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/jimi-jules/586933009</v>
+        <v>https://music.apple.com/us/artist/searows/1607240507</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/baby-run/1857658816</v>
+        <v>https://music.apple.com/us/album/in-violet/1839470844</v>
       </c>
       <c r="L154" t="str">
-        <v>Baby Run - Jimi Jules</v>
+        <v>In Violet - Searows</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>What If We Don't</v>
+        <v>Baby Run</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
+        <v>https://music.apple.com/us/song/baby-run/1857658819</v>
       </c>
       <c r="D155" t="str">
         <v>2026-01-23</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>What If We Don't - Single</v>
+        <v>Baby Run - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:06</v>
+        <v>4:47</v>
       </c>
       <c r="H155" t="str">
-        <v>Ashley McBryde</v>
+        <v>Jimi Jules</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/jimi-jules/586933009</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/what-if-we-dont/1862668776</v>
+        <v>https://music.apple.com/us/album/baby-run/1857658816</v>
       </c>
       <c r="L155" t="str">
-        <v>What If We Don't - Ashley McBryde</v>
+        <v>Baby Run - Jimi Jules</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Hagamos Que</v>
+        <v>What If We Don't</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
+        <v>https://music.apple.com/us/song/what-if-we-dont/1862668777</v>
       </c>
       <c r="D156" t="str">
         <v>2026-01-23</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Hagamos Que - Single</v>
+        <v>What If We Don't - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>2:58</v>
+        <v>3:06</v>
       </c>
       <c r="H156" t="str">
-        <v>Juanes</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/juanes/103856</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/hagamos-que/1861956611</v>
+        <v>https://music.apple.com/us/album/what-if-we-dont/1862668776</v>
       </c>
       <c r="L156" t="str">
-        <v>Hagamos Que - Juanes</v>
+        <v>What If We Don't - Ashley McBryde</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>World Change Me</v>
+        <v>Hagamos Que</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
+        <v>https://music.apple.com/us/song/hagamos-que/1861956612</v>
       </c>
       <c r="D157" t="str">
         <v>2026-01-23</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>World Change Me - Single</v>
+        <v>Hagamos Que - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>3:03</v>
+        <v>2:58</v>
       </c>
       <c r="H157" t="str">
-        <v>Max McNown</v>
+        <v>Juanes</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/juanes/103856</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/world-change-me/1860974598</v>
+        <v>https://music.apple.com/us/album/hagamos-que/1861956611</v>
       </c>
       <c r="L157" t="str">
-        <v>World Change Me - Max McNown</v>
+        <v>Hagamos Que - Juanes</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Exclusive</v>
+        <v>World Change Me</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/exclusive/1851537672</v>
+        <v>https://music.apple.com/us/song/world-change-me/1860974599</v>
       </c>
       <c r="D158" t="str">
         <v>2026-01-23</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Exclusive - EP</v>
+        <v>World Change Me - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:20</v>
+        <v>3:03</v>
       </c>
       <c r="H158" t="str">
-        <v>Hudson Westbrook</v>
+        <v>Max McNown</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/exclusive/1851537671</v>
+        <v>https://music.apple.com/us/album/world-change-me/1860974598</v>
       </c>
       <c r="L158" t="str">
-        <v>Exclusive - Hudson Westbrook</v>
+        <v>World Change Me - Max McNown</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Say Less</v>
+        <v>Exclusive</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/say-less/1867910122</v>
+        <v>https://music.apple.com/us/song/exclusive/1851537672</v>
       </c>
       <c r="D159" t="str">
         <v>2026-01-23</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Say Less - Single</v>
+        <v>Exclusive - EP</v>
       </c>
       <c r="G159" t="str">
-        <v>2:18</v>
+        <v>3:20</v>
       </c>
       <c r="H159" t="str">
-        <v>JYT</v>
+        <v>Hudson Westbrook</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
+        <v>https://music.apple.com/us/artist/hudson-westbrook/1740125054</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/say-less/1867910115</v>
+        <v>https://music.apple.com/us/album/exclusive/1851537671</v>
       </c>
       <c r="L159" t="str">
-        <v>Say Less - JYT</v>
+        <v>Exclusive - Hudson Westbrook</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Angels Cry</v>
+        <v>Say Less</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
+        <v>https://music.apple.com/us/song/say-less/1867910122</v>
       </c>
       <c r="D160" t="str">
         <v>2026-01-23</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>X's for Eyes (Deluxe)</v>
+        <v>Say Less - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:52</v>
+        <v>2:18</v>
       </c>
       <c r="H160" t="str">
-        <v>The Red Jumpsuit Apparatus</v>
+        <v>JYT</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/the-red-jumpsuit-apparatus/130037074</v>
+        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/angels-cry/1862320872</v>
+        <v>https://music.apple.com/us/album/say-less/1867910115</v>
       </c>
       <c r="L160" t="str">
-        <v>Angels Cry - The Red Jumpsuit Apparatus</v>
+        <v>Say Less - JYT</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Over You</v>
+        <v>Angels Cry</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/over-you/1846189473</v>
+        <v>https://music.apple.com/us/song/angels-cry/1862320879</v>
       </c>
       <c r="D161" t="str">
         <v>2026-01-23</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>A Love For Strangers</v>
+        <v>X's for Eyes (Deluxe)</v>
       </c>
       <c r="G161" t="str">
-        <v>4:44</v>
+        <v>3:52</v>
       </c>
       <c r="H161" t="str">
-        <v>Chet Faker</v>
+        <v>The Red Jumpsuit Apparatus</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
+        <v>https://music.apple.com/us/artist/the-red-jumpsuit-apparatus/130037074</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/over-you/1846189472</v>
+        <v>https://music.apple.com/us/album/angels-cry/1862320872</v>
       </c>
       <c r="L161" t="str">
-        <v>Over You - Chet Faker</v>
+        <v>Angels Cry - The Red Jumpsuit Apparatus</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Chala (My Soul Is on a Loop)</v>
+        <v>Over You</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
+        <v>https://music.apple.com/us/song/over-you/1846189473</v>
       </c>
       <c r="D162" t="str">
         <v>2026-01-23</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Chala (My Soul Is on a Loop) - Single</v>
+        <v>A Love For Strangers</v>
       </c>
       <c r="G162" t="str">
-        <v>2:42</v>
+        <v>4:44</v>
       </c>
       <c r="H162" t="str">
-        <v>Barry Can't Swim</v>
+        <v>Chet Faker</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/barry-cant-swim/1492752064</v>
+        <v>https://music.apple.com/us/artist/chet-faker/439036555</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/chala-my-soul-is-on-a-loop/1857789040</v>
+        <v>https://music.apple.com/us/album/over-you/1846189472</v>
       </c>
       <c r="L162" t="str">
-        <v>Chala (My Soul Is on a Loop) - Barry Can't Swim</v>
+        <v>Over You - Chet Faker</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>starlight feat. Madeline Follin</v>
+        <v>Chala (My Soul Is on a Loop)</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
+        <v>https://music.apple.com/us/song/chala-my-soul-is-on-a-loop/1857789041</v>
       </c>
       <c r="D163" t="str">
         <v>2026-01-23</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>starlight feat. Madeline Follin - Single</v>
+        <v>Chala (My Soul Is on a Loop) - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:06</v>
+        <v>2:42</v>
       </c>
       <c r="H163" t="str">
-        <v>Disco Lines</v>
+        <v>Barry Can't Swim</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/disco-lines/1462793893</v>
+        <v>https://music.apple.com/us/artist/barry-cant-swim/1492752064</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/starlight-feat-madeline-follin/1869330767</v>
+        <v>https://music.apple.com/us/album/chala-my-soul-is-on-a-loop/1857789040</v>
       </c>
       <c r="L163" t="str">
-        <v>starlight feat. Madeline Follin - Disco Lines</v>
+        <v>Chala (My Soul Is on a Loop) - Barry Can't Swim</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Locked In (feat. Trippie Redd)</v>
+        <v>starlight feat. Madeline Follin</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
+        <v>https://music.apple.com/us/song/starlight-feat-madeline-follin/1869330768</v>
       </c>
       <c r="D164" t="str">
         <v>2026-01-23</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Locked In (feat. Trippie Redd) - Single</v>
+        <v>starlight feat. Madeline Follin - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>2:48</v>
+        <v>3:06</v>
       </c>
       <c r="H164" t="str">
-        <v>David Guetta</v>
+        <v>Disco Lines</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/david-guetta/5557599</v>
+        <v>https://music.apple.com/us/artist/disco-lines/1462793893</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/locked-in-feat-trippie-redd/1869439982</v>
+        <v>https://music.apple.com/us/album/starlight-feat-madeline-follin/1869330767</v>
       </c>
       <c r="L164" t="str">
-        <v>Locked In (feat. Trippie Redd) - David Guetta</v>
+        <v>starlight feat. Madeline Follin - Disco Lines</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Rejoice</v>
+        <v>Locked In (feat. Trippie Redd)</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/rejoice/1862633596</v>
+        <v>https://music.apple.com/us/song/locked-in-feat-trippie-redd/1869439983</v>
       </c>
       <c r="D165" t="str">
         <v>2026-01-23</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Rejoice - Single</v>
+        <v>Locked In (feat. Trippie Redd) - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>4:20</v>
+        <v>2:48</v>
       </c>
       <c r="H165" t="str">
-        <v>Def Leppard</v>
+        <v>David Guetta</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/def-leppard/117554</v>
+        <v>https://music.apple.com/us/artist/david-guetta/5557599</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/rejoice/1862633593</v>
+        <v>https://music.apple.com/us/album/locked-in-feat-trippie-redd/1869439982</v>
       </c>
       <c r="L165" t="str">
-        <v>Rejoice - Def Leppard</v>
+        <v>Locked In (feat. Trippie Redd) - David Guetta</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Slight Werk (feat. Bree Runway) [Club Mix]</v>
+        <v>Rejoice</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
+        <v>https://music.apple.com/us/song/rejoice/1862633596</v>
       </c>
       <c r="D166" t="str">
         <v>2026-01-23</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Slight Werk (Club Mix) [feat. Bree Runway] - Single</v>
+        <v>Rejoice - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>2:58</v>
+        <v>4:20</v>
       </c>
       <c r="H166" t="str">
-        <v>Honey Dijon</v>
+        <v>Def Leppard</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
+        <v>https://music.apple.com/us/artist/def-leppard/117554</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/slight-werk-feat-bree-runway-club-mix/1860859551</v>
+        <v>https://music.apple.com/us/album/rejoice/1862633593</v>
       </c>
       <c r="L166" t="str">
-        <v>Slight Werk (feat. Bree Runway) [Club Mix] - Honey Dijon</v>
+        <v>Rejoice - Def Leppard</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Lucky Day</v>
+        <v>Slight Werk (feat. Bree Runway) [Club Mix]</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
+        <v>https://music.apple.com/us/song/slight-werk-feat-bree-runway-club-mix/1860859555</v>
       </c>
       <c r="D167" t="str">
         <v>2026-01-23</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Speed Kills</v>
+        <v>Slight Werk (Club Mix) [feat. Bree Runway] - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:13</v>
+        <v>2:58</v>
       </c>
       <c r="H167" t="str">
-        <v>Ally Evenson</v>
+        <v>Honey Dijon</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/ally-evenson/283908113</v>
+        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/lucky-day/1849264498</v>
+        <v>https://music.apple.com/us/album/slight-werk-feat-bree-runway-club-mix/1860859551</v>
       </c>
       <c r="L167" t="str">
-        <v>Lucky Day - Ally Evenson</v>
+        <v>Slight Werk (feat. Bree Runway) [Club Mix] - Honey Dijon</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Breathe On It</v>
+        <v>Odisea</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
+        <v>https://music.apple.com/us/song/odisea/1866927906</v>
       </c>
       <c r="D168" t="str">
         <v>2026-01-23</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Breathe On It - Single</v>
+        <v>Odisea - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>4:00</v>
+        <v>3:56</v>
       </c>
       <c r="H168" t="str">
-        <v>Tauren Wells</v>
+        <v>BASSYY</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
+        <v>https://music.apple.com/us/artist/bassyy/1770667085</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/breathe-on-it/1862938798</v>
+        <v>https://music.apple.com/us/album/odisea/1866927904</v>
       </c>
       <c r="L168" t="str">
-        <v>Breathe On It - Tauren Wells</v>
+        <v>Odisea - BASSYY</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Easy</v>
+        <v>Lucky Day</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/easy/1863456906</v>
+        <v>https://music.apple.com/us/song/lucky-day/1849264582</v>
       </c>
       <c r="D169" t="str">
         <v>2026-01-23</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Easy - Single</v>
+        <v>Speed Kills</v>
       </c>
       <c r="G169" t="str">
-        <v>4:30</v>
+        <v>3:13</v>
       </c>
       <c r="H169" t="str">
-        <v>lydi lynn</v>
+        <v>Ally Evenson</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
+        <v>https://music.apple.com/us/artist/ally-evenson/283908113</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/easy/1863456903</v>
+        <v>https://music.apple.com/us/album/lucky-day/1849264498</v>
       </c>
       <c r="L169" t="str">
-        <v>Easy - lydi lynn</v>
+        <v>Lucky Day - Ally Evenson</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Break Me In</v>
+        <v>Breathe On It</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
+        <v>https://music.apple.com/us/song/breathe-on-it/1862938800</v>
       </c>
       <c r="D170" t="str">
         <v>2026-01-23</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Break Me In - Single</v>
+        <v>Breathe On It - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:52</v>
+        <v>4:00</v>
       </c>
       <c r="H170" t="str">
-        <v>Joyce Wrice</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/joyce-wrice/591991458</v>
+        <v>https://music.apple.com/us/artist/tauren-wells/433402803</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/break-me-in/1862881766</v>
+        <v>https://music.apple.com/us/album/breathe-on-it/1862938798</v>
       </c>
       <c r="L170" t="str">
-        <v>Break Me In - Joyce Wrice</v>
+        <v>Breathe On It - Tauren Wells</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Long Live Love</v>
+        <v>Easy</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
+        <v>https://music.apple.com/us/song/easy/1863456906</v>
       </c>
       <c r="D171" t="str">
         <v>2026-01-23</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Long Live Love - Single</v>
+        <v>Easy - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:36</v>
+        <v>4:30</v>
       </c>
       <c r="H171" t="str">
-        <v>Sugar</v>
+        <v>lydi lynn</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/sugar/530175867</v>
+        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/long-live-love/1851251226</v>
+        <v>https://music.apple.com/us/album/easy/1863456903</v>
       </c>
       <c r="L171" t="str">
-        <v>Long Live Love - Sugar</v>
+        <v>Easy - lydi lynn</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Depressed</v>
+        <v>Break Me In</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/depressed/1840400522</v>
+        <v>https://music.apple.com/us/song/break-me-in/1862881777</v>
       </c>
       <c r="D172" t="str">
         <v>2026-01-23</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Boycott Heaven</v>
+        <v>Break Me In - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:32</v>
+        <v>2:52</v>
       </c>
       <c r="H172" t="str">
-        <v>The Format</v>
+        <v>Joyce Wrice</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/the-format/3064903</v>
+        <v>https://music.apple.com/us/artist/joyce-wrice/591991458</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/depressed/1840399886</v>
+        <v>https://music.apple.com/us/album/break-me-in/1862881766</v>
       </c>
       <c r="L172" t="str">
-        <v>Depressed - The Format</v>
+        <v>Break Me In - Joyce Wrice</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Empty Hands</v>
+        <v>Long Live Love</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
+        <v>https://music.apple.com/us/song/long-live-love/1851251349</v>
       </c>
       <c r="D173" t="str">
         <v>2026-01-23</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Empty Hands</v>
+        <v>Long Live Love - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:09</v>
+        <v>2:36</v>
       </c>
       <c r="H173" t="str">
-        <v>Poppy</v>
+        <v>Sugar</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/poppy/1004130511</v>
+        <v>https://music.apple.com/us/artist/sugar/530175867</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/empty-hands/1852046141</v>
+        <v>https://music.apple.com/us/album/long-live-love/1851251226</v>
       </c>
       <c r="L173" t="str">
-        <v>Empty Hands - Poppy</v>
+        <v>Long Live Love - Sugar</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>The Long Surrender</v>
+        <v>Depressed</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
+        <v>https://music.apple.com/us/song/depressed/1840400522</v>
       </c>
       <c r="D174" t="str">
         <v>2026-01-23</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>The Long Surrender</v>
+        <v>Boycott Heaven</v>
       </c>
       <c r="G174" t="str">
-        <v>3:45</v>
+        <v>3:32</v>
       </c>
       <c r="H174" t="str">
-        <v>NEEDTOBREATHE</v>
+        <v>The Format</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/needtobreathe/113247214</v>
+        <v>https://music.apple.com/us/artist/the-format/3064903</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/the-long-surrender/1861935699</v>
+        <v>https://music.apple.com/us/album/depressed/1840399886</v>
       </c>
       <c r="L174" t="str">
-        <v>The Long Surrender - NEEDTOBREATHE</v>
+        <v>Depressed - The Format</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Angela</v>
+        <v>Empty Hands</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/angela/1866624257</v>
+        <v>https://music.apple.com/us/song/empty-hands/1852046632</v>
       </c>
       <c r="D175" t="str">
         <v>2026-01-23</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Angela - Single</v>
+        <v>Empty Hands</v>
       </c>
       <c r="G175" t="str">
-        <v>3:32</v>
+        <v>3:09</v>
       </c>
       <c r="H175" t="str">
-        <v>Hayden Everett</v>
+        <v>Poppy</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/poppy/1004130511</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/angela/1866624256</v>
+        <v>https://music.apple.com/us/album/empty-hands/1852046141</v>
       </c>
       <c r="L175" t="str">
-        <v>Angela - Hayden Everett</v>
+        <v>Empty Hands - Poppy</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Disappear</v>
+        <v>The Long Surrender</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/disappear/1847663553</v>
+        <v>https://music.apple.com/us/song/the-long-surrender/1861935700</v>
       </c>
       <c r="D176" t="str">
         <v>2026-01-23</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Greyhound</v>
+        <v>The Long Surrender</v>
       </c>
       <c r="G176" t="str">
-        <v>3:31</v>
+        <v>3:45</v>
       </c>
       <c r="H176" t="str">
-        <v>Katie Tupper</v>
+        <v>NEEDTOBREATHE</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/katie-tupper/1395542470</v>
+        <v>https://music.apple.com/us/artist/needtobreathe/113247214</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/disappear/1847663546</v>
+        <v>https://music.apple.com/us/album/the-long-surrender/1861935699</v>
       </c>
       <c r="L176" t="str">
-        <v>Disappear - Katie Tupper</v>
+        <v>The Long Surrender - NEEDTOBREATHE</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Catapult</v>
+        <v>Angela</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/catapult/1862951335</v>
+        <v>https://music.apple.com/us/song/angela/1866624257</v>
       </c>
       <c r="D177" t="str">
         <v>2026-01-23</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Catapult - Single</v>
+        <v>Angela - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:57</v>
+        <v>3:32</v>
       </c>
       <c r="H177" t="str">
-        <v>Cape Francis</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/cape-francis/1242523550</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/catapult/1862951333</v>
+        <v>https://music.apple.com/us/album/angela/1866624256</v>
       </c>
       <c r="L177" t="str">
-        <v>Catapult - Cape Francis</v>
+        <v>Angela - Hayden Everett</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Think Twice</v>
+        <v>Disappear</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/think-twice/1850698548</v>
+        <v>https://music.apple.com/us/song/disappear/1847663553</v>
       </c>
       <c r="D178" t="str">
         <v>2026-01-23</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Think Twice - Single</v>
+        <v>Greyhound</v>
       </c>
       <c r="G178" t="str">
-        <v>2:22</v>
+        <v>3:31</v>
       </c>
       <c r="H178" t="str">
-        <v>Leonie Biney</v>
+        <v>Katie Tupper</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
+        <v>https://music.apple.com/us/artist/katie-tupper/1395542470</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/think-twice/1850698545</v>
+        <v>https://music.apple.com/us/album/disappear/1847663546</v>
       </c>
       <c r="L178" t="str">
-        <v>Think Twice - Leonie Biney</v>
+        <v>Disappear - Katie Tupper</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>LOVESONGS</v>
+        <v>Catapult</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
+        <v>https://music.apple.com/us/song/catapult/1862951335</v>
       </c>
       <c r="D179" t="str">
         <v>2026-01-23</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>BEAUTIFUL MADNESS</v>
+        <v>Catapult - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:33</v>
+        <v>2:57</v>
       </c>
       <c r="H179" t="str">
-        <v>Agnes</v>
+        <v>Cape Francis</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/agnes/42568985</v>
+        <v>https://music.apple.com/us/artist/cape-francis/1242523550</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/lovesongs/1849098275</v>
+        <v>https://music.apple.com/us/album/catapult/1862951333</v>
       </c>
       <c r="L179" t="str">
-        <v>LOVESONGS - Agnes</v>
+        <v>Catapult - Cape Francis</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Down South</v>
+        <v>Think Twice</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/down-south/1861010793</v>
+        <v>https://music.apple.com/us/song/think-twice/1850698548</v>
       </c>
       <c r="D180" t="str">
         <v>2026-01-23</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Down South - Single</v>
+        <v>Think Twice - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:19</v>
+        <v>2:22</v>
       </c>
       <c r="H180" t="str">
-        <v>Trap Dickey</v>
+        <v>Leonie Biney</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
+        <v>https://music.apple.com/us/artist/leonie-biney/1709535671</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/down-south/1861010788</v>
+        <v>https://music.apple.com/us/album/think-twice/1850698545</v>
       </c>
       <c r="L180" t="str">
-        <v>Down South - Trap Dickey</v>
+        <v>Think Twice - Leonie Biney</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW</v>
+        <v>LOVESONGS</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
+        <v>https://music.apple.com/us/song/lovesongs/1849098503</v>
       </c>
       <c r="D181" t="str">
         <v>2026-01-23</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW - Single</v>
+        <v>BEAUTIFUL MADNESS</v>
       </c>
       <c r="G181" t="str">
-        <v>2:16</v>
+        <v>3:33</v>
       </c>
       <c r="H181" t="str">
-        <v>SALIMATA</v>
+        <v>Agnes</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/salimata/690253822</v>
+        <v>https://music.apple.com/us/artist/agnes/42568985</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/jackpot-foil-a-colors-show/1866998655</v>
+        <v>https://music.apple.com/us/album/lovesongs/1849098275</v>
       </c>
       <c r="L181" t="str">
-        <v>Jackpot &amp; Foil - A COLORS SHOW - SALIMATA</v>
+        <v>LOVESONGS - Agnes</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Love Like This</v>
+        <v>Down South</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
+        <v>https://music.apple.com/us/song/down-south/1861010793</v>
       </c>
       <c r="D182" t="str">
         <v>2026-01-23</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Love Like This - Single</v>
+        <v>Down South - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:30</v>
+        <v>2:19</v>
       </c>
       <c r="H182" t="str">
-        <v>Jacob Banks</v>
+        <v>Trap Dickey</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/jacob-banks/625014171</v>
+        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/love-like-this/1866999617</v>
+        <v>https://music.apple.com/us/album/down-south/1861010788</v>
       </c>
       <c r="L182" t="str">
-        <v>Love Like This - Jacob Banks</v>
+        <v>Down South - Trap Dickey</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Plan Plan</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
+        <v>https://music.apple.com/us/song/jackpot-foil-a-colors-show/1866998656</v>
       </c>
       <c r="D183" t="str">
         <v>2026-01-23</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>La Locura</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:10</v>
+        <v>2:16</v>
       </c>
       <c r="H183" t="str">
-        <v>Funky</v>
+        <v>SALIMATA</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/funky/80960663</v>
+        <v>https://music.apple.com/us/artist/salimata/690253822</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/plan-plan/1867940087</v>
+        <v>https://music.apple.com/us/album/jackpot-foil-a-colors-show/1866998655</v>
       </c>
       <c r="L183" t="str">
-        <v>Plan Plan - Funky</v>
+        <v>Jackpot &amp; Foil - A COLORS SHOW - SALIMATA</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>double edged sword</v>
+        <v>Love Like This</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
+        <v>https://music.apple.com/us/song/love-like-this/1866999618</v>
       </c>
       <c r="D184" t="str">
         <v>2026-01-23</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>double edged sword - Single</v>
+        <v>Love Like This - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:28</v>
+        <v>3:30</v>
       </c>
       <c r="H184" t="str">
-        <v>Hailey Picardi</v>
+        <v>Jacob Banks</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/jacob-banks/625014171</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/double-edged-sword/1868829044</v>
+        <v>https://music.apple.com/us/album/love-like-this/1866999617</v>
       </c>
       <c r="L184" t="str">
-        <v>double edged sword - Hailey Picardi</v>
+        <v>Love Like This - Jacob Banks</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>SOMEWHERE IN BETWEEN</v>
+        <v>Plan Plan</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
+        <v>https://music.apple.com/us/song/plan-plan/1867940099</v>
       </c>
       <c r="D185" t="str">
         <v>2026-01-23</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>SOMEWHERE IN BETWEEN - Single</v>
+        <v>La Locura</v>
       </c>
       <c r="G185" t="str">
-        <v>3:27</v>
+        <v>3:10</v>
       </c>
       <c r="H185" t="str">
-        <v>Matt Hansen</v>
+        <v>Funky</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/matt-hansen/1442658353</v>
+        <v>https://music.apple.com/us/artist/funky/80960663</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/somewhere-in-between/1866969151</v>
+        <v>https://music.apple.com/us/album/plan-plan/1867940087</v>
       </c>
       <c r="L185" t="str">
-        <v>SOMEWHERE IN BETWEEN - Matt Hansen</v>
+        <v>Plan Plan - Funky</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>The Decay</v>
+        <v>double edged sword</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/the-decay/1862836783</v>
+        <v>https://music.apple.com/us/song/double-edged-sword/1868829337</v>
       </c>
       <c r="D186" t="str">
         <v>2026-01-23</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>What Remains (Midnight Edition)</v>
+        <v>double edged sword - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:20</v>
+        <v>3:28</v>
       </c>
       <c r="H186" t="str">
-        <v>Pop Evil</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/pop-evil/441597923</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/the-decay/1862836507</v>
+        <v>https://music.apple.com/us/album/double-edged-sword/1868829044</v>
       </c>
       <c r="L186" t="str">
-        <v>The Decay - Pop Evil</v>
+        <v>double edged sword - Hailey Picardi</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>3111</v>
+        <v>SOMEWHERE IN BETWEEN</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/3111/1862225387</v>
+        <v>https://music.apple.com/us/song/somewhere-in-between/1866969152</v>
       </c>
       <c r="D187" t="str">
         <v>2026-01-23</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Goliath</v>
+        <v>SOMEWHERE IN BETWEEN - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>4:08</v>
+        <v>3:27</v>
       </c>
       <c r="H187" t="str">
-        <v>Exodus</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
+        <v>https://music.apple.com/us/artist/matt-hansen/1442658353</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/3111/1862225385</v>
+        <v>https://music.apple.com/us/album/somewhere-in-between/1866969151</v>
       </c>
       <c r="L187" t="str">
-        <v>3111 - Exodus</v>
+        <v>SOMEWHERE IN BETWEEN - Matt Hansen</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Touch My Love And Die</v>
+        <v>The Decay</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
+        <v>https://music.apple.com/us/song/the-decay/1862836783</v>
       </c>
       <c r="D188" t="str">
         <v>2026-01-23</v>
@@ -7519,68 +7519,144 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Touch My Love And Die - Single</v>
+        <v>What Remains (Midnight Edition)</v>
       </c>
       <c r="G188" t="str">
-        <v>2:57</v>
+        <v>3:20</v>
       </c>
       <c r="H188" t="str">
-        <v>Myrkur</v>
+        <v>Pop Evil</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/myrkur/293296859</v>
+        <v>https://music.apple.com/us/artist/pop-evil/441597923</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/touch-my-love-and-die/1867630168</v>
+        <v>https://music.apple.com/us/album/the-decay/1862836507</v>
       </c>
       <c r="L188" t="str">
-        <v>Touch My Love And Die - Myrkur</v>
+        <v>The Decay - Pop Evil</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
+        <v>3111</v>
+      </c>
+      <c r="B189" t="str">
+        <v/>
+      </c>
+      <c r="C189" t="str">
+        <v>https://music.apple.com/us/song/3111/1862225387</v>
+      </c>
+      <c r="D189" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E189" t="str">
+        <v/>
+      </c>
+      <c r="F189" t="str">
+        <v>Goliath</v>
+      </c>
+      <c r="G189" t="str">
+        <v>4:08</v>
+      </c>
+      <c r="H189" t="str">
+        <v>Exodus</v>
+      </c>
+      <c r="I189" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J189" t="str">
+        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
+      </c>
+      <c r="K189" t="str">
+        <v>https://music.apple.com/us/album/3111/1862225385</v>
+      </c>
+      <c r="L189" t="str">
+        <v>3111 - Exodus</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>Touch My Love And Die</v>
+      </c>
+      <c r="B190" t="str">
+        <v/>
+      </c>
+      <c r="C190" t="str">
+        <v>https://music.apple.com/us/song/touch-my-love-and-die/1867630177</v>
+      </c>
+      <c r="D190" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E190" t="str">
+        <v/>
+      </c>
+      <c r="F190" t="str">
+        <v>Touch My Love And Die - Single</v>
+      </c>
+      <c r="G190" t="str">
+        <v>2:57</v>
+      </c>
+      <c r="H190" t="str">
+        <v>Myrkur</v>
+      </c>
+      <c r="I190" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J190" t="str">
+        <v>https://music.apple.com/us/artist/myrkur/293296859</v>
+      </c>
+      <c r="K190" t="str">
+        <v>https://music.apple.com/us/album/touch-my-love-and-die/1867630168</v>
+      </c>
+      <c r="L190" t="str">
+        <v>Touch My Love And Die - Myrkur</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
         <v>Bomb To A Knife Fight</v>
       </c>
-      <c r="B189" t="str">
-        <v/>
-      </c>
-      <c r="C189" t="str">
+      <c r="B191" t="str">
+        <v/>
+      </c>
+      <c r="C191" t="str">
         <v>https://music.apple.com/us/song/bomb-to-a-knife-fight/1861589406</v>
       </c>
-      <c r="D189" t="str">
-        <v>2026-01-23</v>
-      </c>
-      <c r="E189" t="str">
-        <v/>
-      </c>
-      <c r="F189" t="str">
+      <c r="D191" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r=